--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="2006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="2007">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31059074401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13427257537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11721229553223</t>
+    <t xml:space="preserve">9.31058979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13427352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11721134185791</t>
   </si>
   <si>
     <t xml:space="preserve">9.02052211761475</t>
@@ -59,136 +59,136 @@
     <t xml:space="preserve">8.76457977294922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88970756530762</t>
+    <t xml:space="preserve">8.8897066116333</t>
   </si>
   <si>
     <t xml:space="preserve">9.06602191925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95795631408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75889301300049</t>
+    <t xml:space="preserve">8.95795917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75889205932617</t>
   </si>
   <si>
     <t xml:space="preserve">8.57120227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63376522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29250907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44607448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48588752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30957221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04794216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93987798690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568689346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84318923950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41661977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23461771011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15499114990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161270141602</t>
+    <t xml:space="preserve">8.63376617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29251098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44607543945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48588848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30957412719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04794311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93987941741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568784713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84318971633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23461866378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1549916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161222457886</t>
   </si>
   <si>
     <t xml:space="preserve">6.74548435211182</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47248077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81373643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23360204696655</t>
+    <t xml:space="preserve">6.47247982025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81373500823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23360013961792</t>
   </si>
   <si>
     <t xml:space="preserve">6.34166574478149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59760713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62035894393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392244338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72842216491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66017150878906</t>
+    <t xml:space="preserve">6.59760665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62035799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72842168807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66017198562622</t>
   </si>
   <si>
     <t xml:space="preserve">6.89905023574829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89336156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95592498779297</t>
+    <t xml:space="preserve">6.89336204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95592641830444</t>
   </si>
   <si>
     <t xml:space="preserve">7.26305627822876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28580665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45074558258057</t>
+    <t xml:space="preserve">7.28580570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643472671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45074653625488</t>
   </si>
   <si>
     <t xml:space="preserve">7.37680816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24599361419678</t>
+    <t xml:space="preserve">7.24599313735962</t>
   </si>
   <si>
     <t xml:space="preserve">7.31993198394775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38249492645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37112092971802</t>
+    <t xml:space="preserve">7.38249635696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3711199760437</t>
   </si>
   <si>
     <t xml:space="preserve">7.90575408935547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83750295639038</t>
+    <t xml:space="preserve">7.83750247955322</t>
   </si>
   <si>
     <t xml:space="preserve">7.79200220108032</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">7.76356410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67256212234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587385177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037118911743</t>
+    <t xml:space="preserve">7.67256164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037309646606</t>
   </si>
   <si>
     <t xml:space="preserve">7.36543226242065</t>
@@ -221,388 +221,388 @@
     <t xml:space="preserve">7.48487186431885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41093349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755409240723</t>
+    <t xml:space="preserve">7.41093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30286931991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755456924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.98436403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00711393356323</t>
+    <t xml:space="preserve">7.00711345672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.85354900360107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05261516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13792848587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067981719971</t>
+    <t xml:space="preserve">7.05261373519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13792943954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067886352539</t>
   </si>
   <si>
     <t xml:space="preserve">7.4336838722229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49624681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4791841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862327575684</t>
+    <t xml:space="preserve">7.4962477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918319702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862375259399</t>
   </si>
   <si>
     <t xml:space="preserve">7.75219011306763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83181524276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80337619781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77493906021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018661499023</t>
+    <t xml:space="preserve">7.83181476593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631448745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456466674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80337810516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7749400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
   </si>
   <si>
     <t xml:space="preserve">7.39387035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35405731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53606128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1663670539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05830144882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517953872681</t>
+    <t xml:space="preserve">7.35405683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53605937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105230331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16636562347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05830192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517858505249</t>
   </si>
   <si>
     <t xml:space="preserve">7.25168132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31798839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994827270508</t>
+    <t xml:space="preserve">7.31798791885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994874954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.8484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90873193740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.944899559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85448026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228446960449</t>
+    <t xml:space="preserve">7.90873336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94490098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85447978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228351593018</t>
   </si>
   <si>
     <t xml:space="preserve">7.76406097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54705286026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53499794006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158485412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77008819580078</t>
+    <t xml:space="preserve">7.54705381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53499555587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625629425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7700891494751</t>
   </si>
   <si>
     <t xml:space="preserve">7.42046451568604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17934370040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850511550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014026641846</t>
+    <t xml:space="preserve">7.17934465408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439289093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9201397895813</t>
   </si>
   <si>
     <t xml:space="preserve">7.1914005279541</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40840864181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54102516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58322048187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02498292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11841678619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26308870315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187236785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25103282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13047361373901</t>
+    <t xml:space="preserve">7.40840911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54102373123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58257246017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02498340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11841726303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26308965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953664779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4318733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25103330612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13047313690186</t>
   </si>
   <si>
     <t xml:space="preserve">5.91647863388062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92853498458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7634129524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69710397720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87191534042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560970306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84780359268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7754693031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73327302932739</t>
+    <t xml:space="preserve">5.92853450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790006637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76341247558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69710493087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8719162940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80561017990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8417763710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738668441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84780502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77546882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73327255249023</t>
   </si>
   <si>
     <t xml:space="preserve">6.68504858016968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81163692474365</t>
+    <t xml:space="preserve">6.81163597106934</t>
   </si>
   <si>
     <t xml:space="preserve">6.62476825714111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10097980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083988189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79355239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06481313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387617111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7393012046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04070091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01658916473389</t>
+    <t xml:space="preserve">7.10098075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07084083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7935528755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06481218338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948362350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990530014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808343887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73930168151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04069995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01658821105957</t>
   </si>
   <si>
     <t xml:space="preserve">6.81766557693481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74532794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271238327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149652481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425249099731</t>
+    <t xml:space="preserve">6.74532842636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425296783447</t>
   </si>
   <si>
     <t xml:space="preserve">6.99247598648071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93822574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88397216796875</t>
+    <t xml:space="preserve">6.93822479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88397264480591</t>
   </si>
   <si>
     <t xml:space="preserve">6.98042058944702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15523338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313215255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72724485397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7995810508728</t>
+    <t xml:space="preserve">7.15523147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313167572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79958057403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.75135660171509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59462881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56448841094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57654523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668563842773</t>
+    <t xml:space="preserve">6.59462785720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56448984146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57654476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6066837310791</t>
   </si>
   <si>
     <t xml:space="preserve">6.54640436172485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51626586914062</t>
+    <t xml:space="preserve">6.51626491546631</t>
   </si>
   <si>
     <t xml:space="preserve">6.49818086624146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76943969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18537330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1672887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784894943237</t>
+    <t xml:space="preserve">6.76944065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18537282943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16728830337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742727279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784799575806</t>
   </si>
   <si>
     <t xml:space="preserve">7.26976490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33004426956177</t>
+    <t xml:space="preserve">7.33004474639893</t>
   </si>
   <si>
     <t xml:space="preserve">7.31196022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14317655563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09495401382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98644971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0889253616333</t>
+    <t xml:space="preserve">7.1431770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09495306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98644828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08892440795898</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686901092529</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">6.8779444694519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02261638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82369089126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854808807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35415649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73392009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68031597137451</t>
+    <t xml:space="preserve">7.02261734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82369232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35415601730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73392057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6803150177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.45125293731689</t>
@@ -638,46 +638,46 @@
     <t xml:space="preserve">8.47536373138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41508293151855</t>
+    <t xml:space="preserve">8.41508388519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.33069133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.541672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5597562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63812065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58386898040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59592437744141</t>
+    <t xml:space="preserve">8.54167175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55975723266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6381196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5838680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59592533111572</t>
   </si>
   <si>
     <t xml:space="preserve">8.6622314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66826057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5537281036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50550365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5115327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71045589447021</t>
+    <t xml:space="preserve">8.6682596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55372714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51153182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71045398712158</t>
   </si>
   <si>
     <t xml:space="preserve">8.75265216827393</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">8.69840049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71648406982422</t>
+    <t xml:space="preserve">8.71648502349854</t>
   </si>
   <si>
     <t xml:space="preserve">8.52358818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48741912841797</t>
+    <t xml:space="preserve">8.4874210357666</t>
   </si>
   <si>
     <t xml:space="preserve">8.38494396209717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25835514068604</t>
+    <t xml:space="preserve">8.25835609436035</t>
   </si>
   <si>
     <t xml:space="preserve">8.23424434661865</t>
@@ -710,58 +710,58 @@
     <t xml:space="preserve">8.27041244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26438426971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58989715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2951717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38559150695801</t>
+    <t xml:space="preserve">8.26438331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5898962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29517269134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38559246063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.4217586517334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28311634063721</t>
+    <t xml:space="preserve">9.28311443328857</t>
   </si>
   <si>
     <t xml:space="preserve">8.98774433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88526725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84909915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00582790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993869781494</t>
+    <t xml:space="preserve">8.88526821136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84910011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00582885742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993965148926</t>
   </si>
   <si>
     <t xml:space="preserve">8.81895923614502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77073764801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67428874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74059677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90335178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04802322387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87923812866211</t>
+    <t xml:space="preserve">8.77073574066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67428779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74059581756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90335083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04802417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87923908233643</t>
   </si>
   <si>
     <t xml:space="preserve">8.90937995910645</t>
@@ -770,43 +770,43 @@
     <t xml:space="preserve">8.95760250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83101654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81293106079102</t>
+    <t xml:space="preserve">8.83101463317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81293296813965</t>
   </si>
   <si>
     <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49947547912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14985179901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27644062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54769897460938</t>
+    <t xml:space="preserve">8.65620422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49947738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14985370635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27643966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54769992828369</t>
   </si>
   <si>
     <t xml:space="preserve">8.46330833435059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56578540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.788818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80087661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484748840332</t>
+    <t xml:space="preserve">8.56578350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78882122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484844207764</t>
   </si>
   <si>
     <t xml:space="preserve">8.78279209136963</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">8.6320915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60797882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46933460235596</t>
+    <t xml:space="preserve">8.6079797744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46933555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93349075317383</t>
+    <t xml:space="preserve">8.93349170684814</t>
   </si>
   <si>
     <t xml:space="preserve">8.75867938995361</t>
@@ -845,49 +845,49 @@
     <t xml:space="preserve">9.04199600219727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1926965713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21077919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24091911315918</t>
+    <t xml:space="preserve">9.19269561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21078014373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2409200668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.21680641174316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94554710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89129447937012</t>
+    <t xml:space="preserve">8.94554901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89129638671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.03596782684326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07213497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.120361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30493068695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33675289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18400478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15854740142822</t>
+    <t xml:space="preserve">9.07213592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12035846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33675384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18400382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15854644775391</t>
   </si>
   <si>
     <t xml:space="preserve">9.13308906555176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94851779937744</t>
+    <t xml:space="preserve">8.94851684570312</t>
   </si>
   <si>
     <t xml:space="preserve">8.83395671844482</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">8.94215393066406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03762054443359</t>
+    <t xml:space="preserve">9.03762245178223</t>
   </si>
   <si>
     <t xml:space="preserve">8.81486225128174</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">8.75758266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73848819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89123821258545</t>
+    <t xml:space="preserve">8.73848915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89123725891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.95488262176514</t>
@@ -923,25 +923,25 @@
     <t xml:space="preserve">9.2349214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17127513885498</t>
+    <t xml:space="preserve">9.1712760925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.28583717346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29856491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19037055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34948062896729</t>
+    <t xml:space="preserve">9.2985668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34948253631592</t>
   </si>
   <si>
     <t xml:space="preserve">9.25401496887207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22219276428223</t>
+    <t xml:space="preserve">9.22219085693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.24765110015869</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">9.33038902282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38130474090576</t>
+    <t xml:space="preserve">9.38130569458008</t>
   </si>
   <si>
     <t xml:space="preserve">9.57860660552979</t>
@@ -962,34 +962,34 @@
     <t xml:space="preserve">9.54678249359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54041862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64861488342285</t>
+    <t xml:space="preserve">9.54041767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64861583709717</t>
   </si>
   <si>
     <t xml:space="preserve">9.79499912261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85864353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862602233887</t>
+    <t xml:space="preserve">9.858642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862506866455</t>
   </si>
   <si>
     <t xml:space="preserve">9.68680191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56587600708008</t>
+    <t xml:space="preserve">9.56587505340576</t>
   </si>
   <si>
     <t xml:space="preserve">9.52768898010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75681209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77590560913086</t>
+    <t xml:space="preserve">9.75681114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77590656280518</t>
   </si>
   <si>
     <t xml:space="preserve">9.80136299133301</t>
@@ -998,22 +998,22 @@
     <t xml:space="preserve">10.0750389099121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0877676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1386823654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2341508865356</t>
+    <t xml:space="preserve">10.0877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1386833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2341499328613</t>
   </si>
   <si>
     <t xml:space="preserve">10.1959648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.062310218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0050287246704</t>
+    <t xml:space="preserve">10.0623073577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0050296783447</t>
   </si>
   <si>
     <t xml:space="preserve">9.82682132720947</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">9.90319633483887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82045745849609</t>
+    <t xml:space="preserve">9.82045650482178</t>
   </si>
   <si>
     <t xml:space="preserve">9.87137317657471</t>
@@ -1037,37 +1037,37 @@
     <t xml:space="preserve">9.71226119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6995325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6804370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69316673278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134357452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5340518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52132415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57224082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61679267883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.674072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62952136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59769821166992</t>
+    <t xml:space="preserve">9.69953155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68043804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69316577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53405284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52132511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57224178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61679172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67407321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6295223236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59769916534424</t>
   </si>
   <si>
     <t xml:space="preserve">9.89046669006348</t>
@@ -1076,22 +1076,22 @@
     <t xml:space="preserve">9.9477481842041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75044822692871</t>
+    <t xml:space="preserve">9.75044727325439</t>
   </si>
   <si>
     <t xml:space="preserve">9.89683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91592502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87773895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0304861068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686721801758</t>
+    <t xml:space="preserve">9.91592597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8777379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0304880142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686731338501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1323184967041</t>
@@ -1103,58 +1103,58 @@
     <t xml:space="preserve">9.84591579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85228061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83318519592285</t>
+    <t xml:space="preserve">9.85227870941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83318614959717</t>
   </si>
   <si>
     <t xml:space="preserve">9.72498989105225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99866390228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96047687530518</t>
+    <t xml:space="preserve">9.9986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96047592163086</t>
   </si>
   <si>
     <t xml:space="preserve">10.0177574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9541130065918</t>
+    <t xml:space="preserve">9.95411205291748</t>
   </si>
   <si>
     <t xml:space="preserve">10.1259536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0241212844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94138336181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88410186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0368518829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78863430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63588523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58497047424316</t>
+    <t xml:space="preserve">10.0241222381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94138431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8841028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0368509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78863334655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63588619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58496952056885</t>
   </si>
   <si>
     <t xml:space="preserve">9.61042881011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6677074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74408340454102</t>
+    <t xml:space="preserve">9.66770839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74408435821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.73135375976562</t>
@@ -1163,28 +1163,28 @@
     <t xml:space="preserve">9.8077278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73771858215332</t>
+    <t xml:space="preserve">9.73771953582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.70589637756348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55951118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47677421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97320556640625</t>
+    <t xml:space="preserve">9.5595121383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47677230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97320652008057</t>
   </si>
   <si>
     <t xml:space="preserve">9.97957134246826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0814018249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.055944442749</t>
+    <t xml:space="preserve">10.0814037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0559453964233</t>
   </si>
   <si>
     <t xml:space="preserve">10.291431427002</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">10.3041610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023305892944</t>
+    <t xml:space="preserve">10.2023277282715</t>
   </si>
   <si>
     <t xml:space="preserve">10.3105268478394</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">10.3232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641416549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1482305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99230003356934</t>
+    <t xml:space="preserve">10.1736879348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641407012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1482315063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99229907989502</t>
   </si>
   <si>
     <t xml:space="preserve">9.76954174041748</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">9.77908802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8140926361084</t>
+    <t xml:space="preserve">9.81409358978271</t>
   </si>
   <si>
     <t xml:space="preserve">9.80454635620117</t>
@@ -1235,97 +1235,97 @@
     <t xml:space="preserve">9.36857604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65179920196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85546112060547</t>
+    <t xml:space="preserve">9.6517972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85546207427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.74726486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0082120895386</t>
+    <t xml:space="preserve">10.0082111358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.98593425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92865371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94456577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97002220153809</t>
+    <t xml:space="preserve">9.9286527633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94456481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9700231552124</t>
   </si>
   <si>
     <t xml:space="preserve">10.04958152771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1609601974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3137083053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2946128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455295562744</t>
+    <t xml:space="preserve">10.1609582901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3137073516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2946147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455286026001</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5301008224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6382999420166</t>
+    <t xml:space="preserve">10.530101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.638298034668</t>
   </si>
   <si>
     <t xml:space="preserve">10.765588760376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8546905517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6319332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178525924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5841999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6542091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.708309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7051248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.679669380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269193649292</t>
+    <t xml:space="preserve">10.8546915054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6319341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5841989517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6542081832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7083082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7051258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6796674728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269203186035</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4409990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5014610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078258514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.297797203064</t>
+    <t xml:space="preserve">10.4409980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5014619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078268051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2977962493896</t>
   </si>
   <si>
     <t xml:space="preserve">10.3328018188477</t>
@@ -1334,13 +1334,13 @@
     <t xml:space="preserve">10.2596092224121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2864847183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.252890586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319532394409</t>
+    <t xml:space="preserve">10.2864856719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2528915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1319522857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.0143737792969</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">9.83968448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49702548980713</t>
+    <t xml:space="preserve">9.49702644348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.55413627624512</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">9.77585601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88335704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86991691589355</t>
+    <t xml:space="preserve">9.88335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86991882324219</t>
   </si>
   <si>
     <t xml:space="preserve">9.65491676330566</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">9.52054214477539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79937171936035</t>
+    <t xml:space="preserve">9.79937076568604</t>
   </si>
   <si>
     <t xml:space="preserve">9.75233936309814</t>
@@ -1388,40 +1388,40 @@
     <t xml:space="preserve">9.90015411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80609035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76241874694824</t>
+    <t xml:space="preserve">9.80609130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76241683959961</t>
   </si>
   <si>
     <t xml:space="preserve">9.82960605621338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69858837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76913642883301</t>
+    <t xml:space="preserve">9.69859027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76913738250732</t>
   </si>
   <si>
     <t xml:space="preserve">9.60116767883301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61796283721924</t>
+    <t xml:space="preserve">9.61796379089355</t>
   </si>
   <si>
     <t xml:space="preserve">9.52390098571777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51718235015869</t>
+    <t xml:space="preserve">9.51718139648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.61124515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59108829498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80945014953613</t>
+    <t xml:space="preserve">9.59108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80944919586182</t>
   </si>
   <si>
     <t xml:space="preserve">9.77249526977539</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65155696868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163635253906</t>
+    <t xml:space="preserve">9.65155792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163730621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
@@ -1442,28 +1442,28 @@
     <t xml:space="preserve">9.84976291656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85648250579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8161678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74898147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89007568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90351390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92367076873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0479679107666</t>
+    <t xml:space="preserve">9.85648155212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81616878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74898052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89007663726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90351295471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92366886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070217132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.047966003418</t>
   </si>
   <si>
     <t xml:space="preserve">10.2125778198242</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">10.1117973327637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95390510559082</t>
+    <t xml:space="preserve">9.95390224456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0378894805908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009365081787</t>
+    <t xml:space="preserve">10.0009355545044</t>
   </si>
   <si>
     <t xml:space="preserve">10.0681238174438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748414993286</t>
+    <t xml:space="preserve">10.0916395187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.86655902862549</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">9.71202659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73218441009521</t>
+    <t xml:space="preserve">9.7321834564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.85312175750732</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">9.98077869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92030906677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6381196975708</t>
+    <t xml:space="preserve">9.92031002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63812065124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.76577758789062</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">9.93710708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9606237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94382476806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1621875762939</t>
+    <t xml:space="preserve">9.96062183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94382572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1621856689453</t>
   </si>
   <si>
     <t xml:space="preserve">10.1017179489136</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">10.1722650527954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1823434829712</t>
+    <t xml:space="preserve">10.1823425292969</t>
   </si>
   <si>
     <t xml:space="preserve">10.2965631484985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4141416549683</t>
+    <t xml:space="preserve">10.4141426086426</t>
   </si>
   <si>
     <t xml:space="preserve">10.4309387207031</t>
@@ -1556,19 +1556,19 @@
     <t xml:space="preserve">10.3704700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99757766723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88671684265137</t>
+    <t xml:space="preserve">9.99757671356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88671588897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.96734142303467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93038845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70866680145264</t>
+    <t xml:space="preserve">9.93038749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70866775512695</t>
   </si>
   <si>
     <t xml:space="preserve">9.69187068939209</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">9.59444808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50038433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61460590362549</t>
+    <t xml:space="preserve">9.50038528442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61460494995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.56421375274658</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">9.41304111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43991565704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40968132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28874397277832</t>
+    <t xml:space="preserve">9.43991661071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40968036651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28874206542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.23835182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43655681610107</t>
+    <t xml:space="preserve">9.43655586242676</t>
   </si>
   <si>
     <t xml:space="preserve">9.3324146270752</t>
@@ -1610,34 +1610,34 @@
     <t xml:space="preserve">9.53397846221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66499614715576</t>
+    <t xml:space="preserve">9.66499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.62468338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65827751159668</t>
+    <t xml:space="preserve">9.65827655792236</t>
   </si>
   <si>
     <t xml:space="preserve">9.66835498809814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63476085662842</t>
+    <t xml:space="preserve">9.63476181030273</t>
   </si>
   <si>
     <t xml:space="preserve">9.57429122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71538639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51382255554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59780788421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55749416351318</t>
+    <t xml:space="preserve">9.71538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51382160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59780693054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5574951171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.57765102386475</t>
@@ -1646,55 +1646,55 @@
     <t xml:space="preserve">9.8195276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87663841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0042943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084921836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97406101226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57093238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64483833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562168121338</t>
+    <t xml:space="preserve">9.87663745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9135913848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0042953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0849208831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97406005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6448392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562072753906</t>
   </si>
   <si>
     <t xml:space="preserve">9.89679336547852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85984039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95054531097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.021092414856</t>
+    <t xml:space="preserve">9.85984134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9505443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0210914611816</t>
   </si>
   <si>
     <t xml:space="preserve">10.0446081161499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0647640228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327346801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3267974853516</t>
+    <t xml:space="preserve">10.0647649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3267955780029</t>
   </si>
   <si>
     <t xml:space="preserve">10.3435955047607</t>
@@ -1703,16 +1703,16 @@
     <t xml:space="preserve">10.2898435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3335161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3133602142334</t>
+    <t xml:space="preserve">10.333517074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3133592605591</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771877288818</t>
+    <t xml:space="preserve">10.3771886825562</t>
   </si>
   <si>
     <t xml:space="preserve">10.2764072418213</t>
@@ -1727,25 +1727,25 @@
     <t xml:space="preserve">10.2932033538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0714836120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1285934448242</t>
+    <t xml:space="preserve">10.0714826583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1285924911499</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058591842651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2831249237061</t>
+    <t xml:space="preserve">10.2831258773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1890621185303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2293748855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260160446167</t>
+    <t xml:space="preserve">10.2293758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226016998291</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730474472046</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">10.4342985153198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5451593399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089868545532</t>
+    <t xml:space="preserve">10.5451574325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089878082275</t>
   </si>
   <si>
     <t xml:space="preserve">10.672815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6660966873169</t>
+    <t xml:space="preserve">10.6660976409912</t>
   </si>
   <si>
     <t xml:space="preserve">10.7400035858154</t>
@@ -1784,31 +1784,31 @@
     <t xml:space="preserve">10.6157064437866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.62242603302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7534408569336</t>
+    <t xml:space="preserve">10.5921907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6224250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7534399032593</t>
   </si>
   <si>
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.072585105896</t>
+    <t xml:space="preserve">11.0725841522217</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591459274292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0322723388672</t>
+    <t xml:space="preserve">11.0322732925415</t>
   </si>
   <si>
     <t xml:space="preserve">11.0692253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9852409362793</t>
+    <t xml:space="preserve">10.985239982605</t>
   </si>
   <si>
     <t xml:space="preserve">10.9718017578125</t>
@@ -1817,28 +1817,28 @@
     <t xml:space="preserve">11.0087566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0860214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2035989761353</t>
+    <t xml:space="preserve">11.0860223770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2036008834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.1767253875732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2304763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2237577438354</t>
+    <t xml:space="preserve">11.2304754257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2237586975098</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733655929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002401351929</t>
+    <t xml:space="preserve">11.2170381546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002410888672</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271165847778</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">11.2976636886597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.35813331604</t>
+    <t xml:space="preserve">11.3581352233887</t>
   </si>
   <si>
     <t xml:space="preserve">11.4219617843628</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">11.5563373565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521970748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4286804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4622755050659</t>
+    <t xml:space="preserve">11.4521980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4286813735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4622745513916</t>
   </si>
   <si>
     <t xml:space="preserve">11.583212852478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.552978515625</t>
+    <t xml:space="preserve">11.5529775619507</t>
   </si>
   <si>
     <t xml:space="preserve">11.6235246658325</t>
@@ -1877,22 +1877,22 @@
     <t xml:space="preserve">11.6201667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6302423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5261030197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4689931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3245391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648529052734</t>
+    <t xml:space="preserve">11.6302442550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5261039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.468994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.324538230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648519515991</t>
   </si>
   <si>
     <t xml:space="preserve">11.4152431488037</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">11.4253206253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5636587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5849418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.560112953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3189086914062</t>
+    <t xml:space="preserve">11.5636577606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.584942817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5601119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3189067840576</t>
   </si>
   <si>
     <t xml:space="preserve">11.5459241867065</t>
@@ -1925,37 +1925,37 @@
     <t xml:space="preserve">11.3330965042114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124929428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1486463546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1238145828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2727956771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2195873260498</t>
+    <t xml:space="preserve">11.2124938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.148645401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.123815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2727947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1805696487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2195863723755</t>
   </si>
   <si>
     <t xml:space="preserve">11.2479639053345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3366432189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4536981582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4288682937622</t>
+    <t xml:space="preserve">11.3366422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4288673400879</t>
   </si>
   <si>
     <t xml:space="preserve">11.4785280227661</t>
@@ -1970,19 +1970,19 @@
     <t xml:space="preserve">11.7445631027222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811957359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8332424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8403367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7871294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7481088638306</t>
+    <t xml:space="preserve">11.8119583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8332433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8403358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7871284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7481107711792</t>
   </si>
   <si>
     <t xml:space="preserve">11.7126398086548</t>
@@ -1991,25 +1991,25 @@
     <t xml:space="preserve">11.7977695465088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8935422897339</t>
+    <t xml:space="preserve">11.8935432434082</t>
   </si>
   <si>
     <t xml:space="preserve">12.1063718795776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1312017440796</t>
+    <t xml:space="preserve">12.1312026977539</t>
   </si>
   <si>
     <t xml:space="preserve">12.0708999633789</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1418428421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1773138046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2092370986938</t>
+    <t xml:space="preserve">12.1418418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1773147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2092380523682</t>
   </si>
   <si>
     <t xml:space="preserve">12.2056913375854</t>
@@ -2018,31 +2018,31 @@
     <t xml:space="preserve">12.1560316085815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1170120239258</t>
+    <t xml:space="preserve">12.1808614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1170139312744</t>
   </si>
   <si>
     <t xml:space="preserve">11.989315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.024787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106000900269</t>
+    <t xml:space="preserve">12.0247869491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105991363525</t>
   </si>
   <si>
     <t xml:space="preserve">12.0567121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9751262664795</t>
+    <t xml:space="preserve">11.9751272201538</t>
   </si>
   <si>
     <t xml:space="preserve">11.996410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8545246124268</t>
+    <t xml:space="preserve">11.8545236587524</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467506408691</t>
@@ -2051,19 +2051,19 @@
     <t xml:space="preserve">11.9573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6629800796509</t>
+    <t xml:space="preserve">11.6629791259766</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884876251221</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6594324111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3437356948853</t>
+    <t xml:space="preserve">11.5707540512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6594305038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3437366485596</t>
   </si>
   <si>
     <t xml:space="preserve">11.3792085647583</t>
@@ -2075,31 +2075,31 @@
     <t xml:space="preserve">11.29407787323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4749803543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5069046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5778465270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.467887878418</t>
+    <t xml:space="preserve">11.4749813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5069055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5778474807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4678869247437</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820747375488</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6558837890625</t>
+    <t xml:space="preserve">11.6558847427368</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487913131714</t>
+    <t xml:space="preserve">11.6487922668457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6842613220215</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7374696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9432020187378</t>
+    <t xml:space="preserve">11.7374677658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9432010650635</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921831130981</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">12.1347484588623</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2021427154541</t>
+    <t xml:space="preserve">12.2021436691284</t>
   </si>
   <si>
     <t xml:space="preserve">12.1844072341919</t>
@@ -2135,43 +2135,43 @@
     <t xml:space="preserve">12.3972368240356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3262920379639</t>
+    <t xml:space="preserve">12.3262929916382</t>
   </si>
   <si>
     <t xml:space="preserve">12.2908239364624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881017684937</t>
+    <t xml:space="preserve">12.6880989074707</t>
   </si>
   <si>
     <t xml:space="preserve">12.6597242355347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7058382034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6739110946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.741307258606</t>
+    <t xml:space="preserve">12.7058362960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7413082122803</t>
   </si>
   <si>
     <t xml:space="preserve">12.6987419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6703653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5852346420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433488845825</t>
+    <t xml:space="preserve">12.6703662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6136121749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5852327346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433479309082</t>
   </si>
   <si>
     <t xml:space="preserve">12.5213851928711</t>
@@ -2180,28 +2180,28 @@
     <t xml:space="preserve">12.606517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5887823104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6490821838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6774587631226</t>
+    <t xml:space="preserve">12.5887813568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6490812301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6774606704712</t>
   </si>
   <si>
     <t xml:space="preserve">12.8157997131348</t>
   </si>
   <si>
-    <t xml:space="preserve">12.744854927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8406276702881</t>
+    <t xml:space="preserve">12.7448539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441753387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477201461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.840630531311</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080228805542</t>
@@ -2210,49 +2210,49 @@
     <t xml:space="preserve">13.0357208251953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0215320587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0463609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0534563064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0499105453491</t>
+    <t xml:space="preserve">13.0215330123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0463600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0534553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0499095916748</t>
   </si>
   <si>
     <t xml:space="preserve">13.0286254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9364004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8938360214233</t>
+    <t xml:space="preserve">12.9364023208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938341140747</t>
   </si>
   <si>
     <t xml:space="preserve">13.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1882486343384</t>
+    <t xml:space="preserve">13.1882467269897</t>
   </si>
   <si>
     <t xml:space="preserve">13.1917943954468</t>
   </si>
   <si>
-    <t xml:space="preserve">13.642279624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338251113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167701721191</t>
+    <t xml:space="preserve">13.6422786712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338270187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167682647705</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997161865234</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">13.5145826339722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2662839889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2343597412109</t>
+    <t xml:space="preserve">13.2662858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2343606948853</t>
   </si>
   <si>
     <t xml:space="preserve">13.1527767181396</t>
@@ -2279,211 +2279,211 @@
     <t xml:space="preserve">13.2627363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1456813812256</t>
+    <t xml:space="preserve">13.1456832885742</t>
   </si>
   <si>
     <t xml:space="preserve">12.9754209518433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9612312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9399471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9186630249023</t>
+    <t xml:space="preserve">12.9612302780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9399480819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9186658859253</t>
   </si>
   <si>
     <t xml:space="preserve">12.9257593154907</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9541358947754</t>
+    <t xml:space="preserve">12.9541368484497</t>
   </si>
   <si>
     <t xml:space="preserve">13.0250806808472</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0108909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1314945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1776084899902</t>
+    <t xml:space="preserve">13.010890007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137571334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1314935684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1776056289673</t>
   </si>
   <si>
     <t xml:space="preserve">13.1208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4613761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520961761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953411102295</t>
+    <t xml:space="preserve">13.4613771438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953420639038</t>
   </si>
   <si>
     <t xml:space="preserve">13.0640983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9683246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1031169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0747385025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9115715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9789667129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9860610961914</t>
+    <t xml:space="preserve">12.9683256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1031150817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0747394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9115695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9860601425171</t>
   </si>
   <si>
     <t xml:space="preserve">12.9505882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235717773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690052032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5710439682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434976577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6916475296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4823665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5462160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7306661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002489089966</t>
+    <t xml:space="preserve">12.86545753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235708236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690061569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5710458755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6916484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4823656082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7306671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002498626709</t>
   </si>
   <si>
     <t xml:space="preserve">13.0818338394165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2804708480835</t>
+    <t xml:space="preserve">13.2804718017578</t>
   </si>
   <si>
     <t xml:space="preserve">13.3194904327393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3939809799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3688592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2979145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.248254776001</t>
+    <t xml:space="preserve">13.3230390548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3939800262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3688583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2979154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2482557296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.5352830886841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4004917144775</t>
+    <t xml:space="preserve">11.4004907608032</t>
   </si>
   <si>
     <t xml:space="preserve">11.1628332138062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8116664886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76171684265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6127347946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36769104003906</t>
+    <t xml:space="preserve">10.8116674423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76171588897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36769199371338</t>
   </si>
   <si>
     <t xml:space="preserve">8.56278324127197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01297855377197</t>
+    <t xml:space="preserve">8.01297760009766</t>
   </si>
   <si>
     <t xml:space="preserve">7.6972827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36740016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569833755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72566032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920703887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58406543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83236503601074</t>
+    <t xml:space="preserve">7.36739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72565984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58406639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83236598968506</t>
   </si>
   <si>
     <t xml:space="preserve">8.98134517669678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7791576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77206420898438</t>
+    <t xml:space="preserve">8.77915859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77206516265869</t>
   </si>
   <si>
     <t xml:space="preserve">8.80398845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58051872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74723434448242</t>
+    <t xml:space="preserve">8.58052062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74723529815674</t>
   </si>
   <si>
     <t xml:space="preserve">8.64436817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89976215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07002449035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1303243637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31832313537598</t>
+    <t xml:space="preserve">8.89976119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07002258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13032531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31832408905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.9387788772583</t>
@@ -2492,22 +2492,22 @@
     <t xml:space="preserve">8.7898006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88912010192871</t>
+    <t xml:space="preserve">8.88911914825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.63017845153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84300708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04164695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20126819610596</t>
+    <t xml:space="preserve">8.84300804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77561092376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04164600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20126628875732</t>
   </si>
   <si>
     <t xml:space="preserve">9.43537902832031</t>
@@ -2519,370 +2519,370 @@
     <t xml:space="preserve">9.00972270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17643642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0345516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09485244750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20481491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12323188781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0842113494873</t>
+    <t xml:space="preserve">9.17643737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03455257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0948543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20481586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12323093414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08421230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91040134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80044078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17268943786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01014614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05817031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78849506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20963382720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43867206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22440910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52363967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81178665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3031148910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3474445343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6282052993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5395431518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3215856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9226131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91891860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90414047241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1257925033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.051908493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92630672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0592985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80070400238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82656383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91522407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95216655731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94847297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2218427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553468704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2587852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1627359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0777683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.129487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2107591629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.114709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3289747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2772550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0408267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98541450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97433185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46453189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35370635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40911960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55688762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63077068328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38695526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78592681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73051452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68618392944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53841590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70835018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62707614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56058025360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76376247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78223419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60860633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62338256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61968994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57535839080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47192001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37217807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56796932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47561454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36478900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1061954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75155258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70352745056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66658496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59639644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88454437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76632881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91779136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14313697814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1135835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29829406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24288082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22071552276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12466716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12097263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80327224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96950912475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01753520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03969860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81435394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82543563842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.91040229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17269039154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01014614105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05817031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78849411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99536991119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96212291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20963287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43867301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22440814971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52363872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81178569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3031148910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3474454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6282043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540651321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5395441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3215856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92261409759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91891956329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90414142608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1257934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92630672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0592966079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80070400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9152250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95216655731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94847202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2218418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1553468704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2587842941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1627359390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675235748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.07776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1294870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2107591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1147108078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3289747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2772550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0408267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98541450500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97433090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46453285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35370635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40911865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55688667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63077259063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78592777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73051452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68618392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53841590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70834922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62707710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56058120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76376247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78223323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60860633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62338256835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61968898773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57535839080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47192001342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37217807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56796932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48669719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47561454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36478900909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1061954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75155258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70352745056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66658592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59639644622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88454246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76632976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91779041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14313697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1135835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2982931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24288082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2207145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12097263336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80327033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96951007843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03969955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81435394287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82543563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91040325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77371692657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39321517944336</t>
+    <t xml:space="preserve">8.77371883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39321613311768</t>
   </si>
   <si>
     <t xml:space="preserve">8.41907501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.721999168396</t>
+    <t xml:space="preserve">8.50404262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72199821472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.89193153381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.013840675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14683246612549</t>
+    <t xml:space="preserve">9.01383972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">9.72312641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95955371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94477653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0740737915039</t>
+    <t xml:space="preserve">9.95955467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9447774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0740747451782</t>
   </si>
   <si>
     <t xml:space="preserve">10.3178911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4398002624512</t>
+    <t xml:space="preserve">10.4398012161255</t>
   </si>
   <si>
     <t xml:space="preserve">10.5136833190918</t>
@@ -2891,19 +2891,19 @@
     <t xml:space="preserve">10.3954696655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4952116012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5062971115112</t>
+    <t xml:space="preserve">10.495213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5062952041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.6245098114014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7094774246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910047531128</t>
+    <t xml:space="preserve">10.7094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">10.5801792144775</t>
@@ -2912,37 +2912,37 @@
     <t xml:space="preserve">10.6577577590942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7648887634277</t>
+    <t xml:space="preserve">10.7648897171021</t>
   </si>
   <si>
     <t xml:space="preserve">10.713171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6097316741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838747024536</t>
+    <t xml:space="preserve">10.6097326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838737487793</t>
   </si>
   <si>
     <t xml:space="preserve">10.6060390472412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4065532684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5358505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617074966431</t>
+    <t xml:space="preserve">10.4065523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358486175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617084503174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2624788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4176349639893</t>
+    <t xml:space="preserve">10.4176359176636</t>
   </si>
   <si>
     <t xml:space="preserve">10.6134271621704</t>
@@ -2951,22 +2951,22 @@
     <t xml:space="preserve">10.5764846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.698392868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7464179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6392879486084</t>
+    <t xml:space="preserve">10.2809505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6983938217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7464189529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6392860412598</t>
   </si>
   <si>
     <t xml:space="preserve">10.6836175918579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7168655395508</t>
+    <t xml:space="preserve">10.7168645858765</t>
   </si>
   <si>
     <t xml:space="preserve">10.942211151123</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">10.7205600738525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6429805755615</t>
+    <t xml:space="preserve">10.6429815292358</t>
   </si>
   <si>
     <t xml:space="preserve">10.4102478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5321550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6947002410889</t>
+    <t xml:space="preserve">10.5321559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6946992874146</t>
   </si>
   <si>
     <t xml:space="preserve">11.0456485748291</t>
@@ -2996,28 +2996,28 @@
     <t xml:space="preserve">11.3929033279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4778690338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145553588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6884384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6441087722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.599778175354</t>
+    <t xml:space="preserve">11.4778699874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.688437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6441078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5997772216797</t>
   </si>
   <si>
     <t xml:space="preserve">11.5739183425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6921329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.63671875</t>
+    <t xml:space="preserve">11.6921319961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367206573486</t>
   </si>
   <si>
     <t xml:space="preserve">11.5665302276611</t>
@@ -3026,55 +3026,55 @@
     <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111169815063</t>
+    <t xml:space="preserve">11.5111179351807</t>
   </si>
   <si>
     <t xml:space="preserve">11.4815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4557037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6995210647583</t>
+    <t xml:space="preserve">11.4557046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6995220184326</t>
   </si>
   <si>
     <t xml:space="preserve">11.4889526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6958265304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7290744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8435964584351</t>
+    <t xml:space="preserve">11.6958284378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7290754318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8435955047607</t>
   </si>
   <si>
     <t xml:space="preserve">11.8768434524536</t>
   </si>
   <si>
-    <t xml:space="preserve">11.825122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1908493041992</t>
+    <t xml:space="preserve">11.8251237869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908502578735</t>
   </si>
   <si>
     <t xml:space="preserve">12.2130155563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2795104980469</t>
+    <t xml:space="preserve">12.2795124053955</t>
   </si>
   <si>
     <t xml:space="preserve">12.3866415023804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4900789260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4383592605591</t>
+    <t xml:space="preserve">12.4900817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4383602142334</t>
   </si>
   <si>
     <t xml:space="preserve">12.4789953231812</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">12.4568319320679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3607816696167</t>
+    <t xml:space="preserve">12.360782623291</t>
   </si>
   <si>
     <t xml:space="preserve">12.4161949157715</t>
@@ -3098,28 +3098,28 @@
     <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048551559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6045999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.66370677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6600131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6378479003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344095230103</t>
+    <t xml:space="preserve">12.5048561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6637048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5824346542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6600141525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858711242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6378488540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344104766846</t>
   </si>
   <si>
     <t xml:space="preserve">12.6119871139526</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">12.6489305496216</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4457483291626</t>
+    <t xml:space="preserve">12.7265071868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4457492828369</t>
   </si>
   <si>
     <t xml:space="preserve">12.4679145812988</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">12.3977251052856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3275346755981</t>
+    <t xml:space="preserve">12.3275337219238</t>
   </si>
   <si>
     <t xml:space="preserve">12.5602693557739</t>
@@ -3155,40 +3155,40 @@
     <t xml:space="preserve">12.4420547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5972099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7228126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8336410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9149122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9592428207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368204116821</t>
+    <t xml:space="preserve">12.5972108840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7228136062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8336391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740209579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631944656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9149112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9592418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368213653564</t>
   </si>
   <si>
     <t xml:space="preserve">13.0626792907715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8890523910522</t>
+    <t xml:space="preserve">12.881664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8890514373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479030609131</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">13.2438173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1184320449829</t>
+    <t xml:space="preserve">13.1184310913086</t>
   </si>
   <si>
     <t xml:space="preserve">12.9773731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910034179688</t>
+    <t xml:space="preserve">13.0910043716431</t>
   </si>
   <si>
     <t xml:space="preserve">13.2007160186768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1772060394287</t>
+    <t xml:space="preserve">13.177206993103</t>
   </si>
   <si>
     <t xml:space="preserve">13.2673273086548</t>
@@ -3221,25 +3221,25 @@
     <t xml:space="preserve">13.3887929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5180978775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4985065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4632415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4201393127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4318952560425</t>
+    <t xml:space="preserve">13.5180988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985055923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4632425308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4201402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4318933486938</t>
   </si>
   <si>
     <t xml:space="preserve">13.4397315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4514865875244</t>
+    <t xml:space="preserve">13.4514875411987</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102596282959</t>
@@ -3248,52 +3248,52 @@
     <t xml:space="preserve">13.2359800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.232063293457</t>
+    <t xml:space="preserve">13.2712459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2320613861084</t>
   </si>
   <si>
     <t xml:space="preserve">13.0518207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3339366912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1262674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2477359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3731212615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3221836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4358139038086</t>
+    <t xml:space="preserve">13.3339385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2477369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3731203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3221826553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4358129501343</t>
   </si>
   <si>
     <t xml:space="preserve">13.196798324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9852104187012</t>
+    <t xml:space="preserve">12.9852094650269</t>
   </si>
   <si>
     <t xml:space="preserve">13.3261003494263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3300189971924</t>
+    <t xml:space="preserve">13.3300199508667</t>
   </si>
   <si>
     <t xml:space="preserve">13.2634077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1654510498047</t>
+    <t xml:space="preserve">13.1654500961304</t>
   </si>
   <si>
     <t xml:space="preserve">13.1145143508911</t>
@@ -3302,22 +3302,22 @@
     <t xml:space="preserve">12.7148485183716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8441505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1223516464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1576166152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1301860809326</t>
+    <t xml:space="preserve">12.8441524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1223497390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1301870346069</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046346664429</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0674924850464</t>
+    <t xml:space="preserve">13.067494392395</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891290664673</t>
@@ -3326,31 +3326,31 @@
     <t xml:space="preserve">13.0283117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281436920166</t>
+    <t xml:space="preserve">13.2281446456909</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947559356689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456945419312</t>
+    <t xml:space="preserve">13.3456935882568</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5690355300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6160545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5376882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5416088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3770380020142</t>
+    <t xml:space="preserve">13.569034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6160535812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5376892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5416069030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3770389556885</t>
   </si>
   <si>
     <t xml:space="preserve">13.4436502456665</t>
@@ -3359,19 +3359,19 @@
     <t xml:space="preserve">13.4240579605103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3848762512207</t>
+    <t xml:space="preserve">13.384877204895</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5337705612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5964622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6121368408203</t>
+    <t xml:space="preserve">13.5337715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5964632034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.612135887146</t>
   </si>
   <si>
     <t xml:space="preserve">13.5729532241821</t>
@@ -3380,88 +3380,88 @@
     <t xml:space="preserve">13.7414398193359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8393974304199</t>
+    <t xml:space="preserve">13.8393964767456</t>
   </si>
   <si>
     <t xml:space="preserve">13.9060087203979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6591558456421</t>
+    <t xml:space="preserve">13.6591548919678</t>
   </si>
   <si>
     <t xml:space="preserve">13.8315601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7923784255981</t>
+    <t xml:space="preserve">13.7923774719238</t>
   </si>
   <si>
     <t xml:space="preserve">13.8824977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0039653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0901660919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2037973403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3644485473633</t>
+    <t xml:space="preserve">14.0039663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748304367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0901670455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2037982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.364447593689</t>
   </si>
   <si>
     <t xml:space="preserve">14.5956268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3017559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349775314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4114665985107</t>
+    <t xml:space="preserve">14.3017549514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4114656448364</t>
   </si>
   <si>
     <t xml:space="preserve">14.4271402359009</t>
   </si>
   <si>
-    <t xml:space="preserve">14.399712562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6896667480469</t>
+    <t xml:space="preserve">14.3997135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6896677017212</t>
   </si>
   <si>
     <t xml:space="preserve">14.5642805099487</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7014207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7288484573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816633224487</t>
+    <t xml:space="preserve">14.7014198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7288475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8072156906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816614151001</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6739950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7249317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851810455322</t>
+    <t xml:space="preserve">14.6739940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.724928855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851800918579</t>
   </si>
   <si>
     <t xml:space="preserve">14.8494472503662</t>
@@ -3470,40 +3470,40 @@
     <t xml:space="preserve">14.9739608764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9217472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9538793563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141286849976</t>
+    <t xml:space="preserve">14.9217462539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9538774490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141277313232</t>
   </si>
   <si>
     <t xml:space="preserve">15.1185598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0663423538208</t>
+    <t xml:space="preserve">15.0663414001465</t>
   </si>
   <si>
     <t xml:space="preserve">15.1346263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470903396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3234090805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2591419219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3475074768066</t>
+    <t xml:space="preserve">15.1426601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310247421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.247091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3234081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2591400146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3475065231323</t>
   </si>
   <si>
     <t xml:space="preserve">15.2430753707886</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">15.2511081695557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.279224395752</t>
+    <t xml:space="preserve">15.2792253494263</t>
   </si>
   <si>
     <t xml:space="preserve">15.38365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3716068267822</t>
+    <t xml:space="preserve">15.3716058731079</t>
   </si>
   <si>
     <t xml:space="preserve">15.4559545516968</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">15.0743751525879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9418287277222</t>
+    <t xml:space="preserve">14.9418277740479</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887817382812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7811632156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7570638656616</t>
+    <t xml:space="preserve">14.7811641693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7570657730103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7168979644775</t>
@@ -3545,31 +3545,31 @@
     <t xml:space="preserve">14.1867036819458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.299168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2429370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5642671585083</t>
+    <t xml:space="preserve">14.2991666793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2429351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5642652511597</t>
   </si>
   <si>
     <t xml:space="preserve">14.4919662475586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6124649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498605728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0221605300903</t>
+    <t xml:space="preserve">14.6124658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.022162437439</t>
   </si>
   <si>
     <t xml:space="preserve">14.857479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9297780990601</t>
+    <t xml:space="preserve">14.9297771453857</t>
   </si>
   <si>
     <t xml:space="preserve">14.8614959716797</t>
@@ -3584,43 +3584,43 @@
     <t xml:space="preserve">14.7731304168701</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9699459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9016618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623273849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060939788818</t>
+    <t xml:space="preserve">14.9699449539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9016628265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060949325562</t>
   </si>
   <si>
     <t xml:space="preserve">14.9659261703491</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2671728134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788091659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9177284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8293619155884</t>
+    <t xml:space="preserve">15.2671747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9177274703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8293628692627</t>
   </si>
   <si>
     <t xml:space="preserve">14.9337959289551</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0583124160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422458648682</t>
+    <t xml:space="preserve">15.058310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422449111938</t>
   </si>
   <si>
     <t xml:space="preserve">14.8132972717285</t>
@@ -3629,55 +3629,55 @@
     <t xml:space="preserve">14.9257621765137</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1466760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0382242202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627426147461</t>
+    <t xml:space="preserve">15.1466770172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0382251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627416610718</t>
   </si>
   <si>
     <t xml:space="preserve">14.3754854202271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4999990463257</t>
+    <t xml:space="preserve">14.5</t>
   </si>
   <si>
     <t xml:space="preserve">14.6847658157349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6727142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9940452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7369785308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9819946289062</t>
+    <t xml:space="preserve">14.6727151870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9940462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7369804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9819936752319</t>
   </si>
   <si>
     <t xml:space="preserve">14.957896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7450151443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270088195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.893630027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5562324523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.596399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0300559997559</t>
+    <t xml:space="preserve">14.7450141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8936290740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5562334060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5964002609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0300550460815</t>
   </si>
   <si>
     <t xml:space="preserve">14.3714666366577</t>
@@ -3686,13 +3686,13 @@
     <t xml:space="preserve">13.9256229400635</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8372583389282</t>
+    <t xml:space="preserve">13.8372573852539</t>
   </si>
   <si>
     <t xml:space="preserve">13.7770080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379495620728</t>
+    <t xml:space="preserve">13.0379505157471</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447376251221</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">13.6243753433228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4958438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930765151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1746530532837</t>
+    <t xml:space="preserve">13.4958448410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1746549606323</t>
   </si>
   <si>
     <t xml:space="preserve">14.3875350952148</t>
@@ -3722,28 +3722,28 @@
     <t xml:space="preserve">15.0502767562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1667594909668</t>
+    <t xml:space="preserve">15.1667585372925</t>
   </si>
   <si>
     <t xml:space="preserve">15.3153743743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6005525588989</t>
+    <t xml:space="preserve">15.6005544662476</t>
   </si>
   <si>
     <t xml:space="preserve">16.1789455413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8495836257935</t>
+    <t xml:space="preserve">15.8495855331421</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6850433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9581718444824</t>
+    <t xml:space="preserve">16.6850414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074798583984</t>
@@ -3755,61 +3755,61 @@
     <t xml:space="preserve">16.0504150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7331027984619</t>
+    <t xml:space="preserve">15.5523548126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7331008911133</t>
   </si>
   <si>
     <t xml:space="preserve">15.6166210174561</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4840707778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4117736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4760370254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7932138442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080327987671</t>
+    <t xml:space="preserve">15.4840726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4117746353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.476037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9980611801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7932157516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080318450928</t>
   </si>
   <si>
     <t xml:space="preserve">14.5441818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4598350524902</t>
+    <t xml:space="preserve">14.4598340988159</t>
   </si>
   <si>
     <t xml:space="preserve">14.5401668548584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4196691513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7048482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6204996109009</t>
+    <t xml:space="preserve">14.4196672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7048473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204986572266</t>
   </si>
   <si>
     <t xml:space="preserve">14.4518003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2469539642334</t>
+    <t xml:space="preserve">14.2469549179077</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268686294556</t>
+    <t xml:space="preserve">14.2268695831299</t>
   </si>
   <si>
     <t xml:space="preserve">14.2670364379883</t>
@@ -3818,28 +3818,28 @@
     <t xml:space="preserve">14.1947364807129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3112182617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4558181762695</t>
+    <t xml:space="preserve">14.3112201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4558172225952</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7547540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8230838775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8828706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5882034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5540409088135</t>
+    <t xml:space="preserve">14.7547550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8230848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8828716278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5882043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5540390014648</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
@@ -3848,10 +3848,10 @@
     <t xml:space="preserve">14.4430055618286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2764539718628</t>
+    <t xml:space="preserve">14.3789472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2764530181885</t>
   </si>
   <si>
     <t xml:space="preserve">14.4643564224243</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344398498535</t>
+    <t xml:space="preserve">13.3924493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344388961792</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881788253784</t>
+    <t xml:space="preserve">13.3881797790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3887,16 +3887,16 @@
     <t xml:space="preserve">13.5803537368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3967199325562</t>
+    <t xml:space="preserve">13.3967208862305</t>
   </si>
   <si>
     <t xml:space="preserve">13.2557926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828479766846</t>
+    <t xml:space="preserve">13.1917343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828470230103</t>
   </si>
   <si>
     <t xml:space="preserve">13.2686033248901</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038290023804</t>
+    <t xml:space="preserve">13.0038299560547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2942266464233</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">13.1661100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4187641143799</t>
+    <t xml:space="preserve">12.4187631607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596923828125</t>
@@ -3929,28 +3929,28 @@
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568529129028</t>
+    <t xml:space="preserve">12.9568538665771</t>
   </si>
   <si>
     <t xml:space="preserve">12.995288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7774906158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3547058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4401168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230337142944</t>
+    <t xml:space="preserve">12.7774896621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3547048568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4401159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230346679688</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838836669922</t>
+    <t xml:space="preserve">12.1838846206665</t>
   </si>
   <si>
     <t xml:space="preserve">12.1625299453735</t>
@@ -3971,16 +3971,16 @@
     <t xml:space="preserve">12.3333530426025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4571990966797</t>
+    <t xml:space="preserve">12.4571981430054</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">12.470009803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.534068107605</t>
+    <t xml:space="preserve">12.4700107574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5340690612793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408319473267</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">12.8458185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141473770142</t>
+    <t xml:space="preserve">12.9141483306885</t>
   </si>
   <si>
     <t xml:space="preserve">13.0508050918579</t>
@@ -4004,19 +4004,19 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618394851685</t>
+    <t xml:space="preserve">13.1618385314941</t>
   </si>
   <si>
     <t xml:space="preserve">12.897066116333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7646780014038</t>
+    <t xml:space="preserve">12.7646789550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.7006206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8757133483887</t>
+    <t xml:space="preserve">12.8757123947144</t>
   </si>
   <si>
     <t xml:space="preserve">12.576774597168</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">12.6579141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5041761398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3931407928467</t>
+    <t xml:space="preserve">12.5041751861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3931398391724</t>
   </si>
   <si>
     <t xml:space="preserve">12.8330068588257</t>
@@ -4046,13 +4046,13 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7689485549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1703815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9696655273438</t>
+    <t xml:space="preserve">12.768949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1703805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9696645736694</t>
   </si>
   <si>
     <t xml:space="preserve">13.0892400741577</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7048902511597</t>
+    <t xml:space="preserve">12.704891204834</t>
   </si>
   <si>
     <t xml:space="preserve">12.7390546798706</t>
@@ -4088,55 +4088,55 @@
     <t xml:space="preserve">12.3845996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1326360702515</t>
+    <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
     <t xml:space="preserve">11.8550519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7397451400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7909927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0045213699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.158260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2991886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3632478713989</t>
+    <t xml:space="preserve">11.73974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7909936904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0045204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1582593917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2991876602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3632469177246</t>
   </si>
   <si>
     <t xml:space="preserve">12.5169858932495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3376226425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6749963760376</t>
+    <t xml:space="preserve">12.3376235961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6749973297119</t>
   </si>
   <si>
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091617584229</t>
+    <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9739351272583</t>
+    <t xml:space="preserve">12.973934173584</t>
   </si>
   <si>
     <t xml:space="preserve">13.0977811813354</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">13.0251817703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532983779907</t>
+    <t xml:space="preserve">13.153299331665</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">13.8493986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9433517456055</t>
+    <t xml:space="preserve">13.9433507919312</t>
   </si>
   <si>
     <t xml:space="preserve">14.2294778823853</t>
@@ -4163,22 +4163,22 @@
     <t xml:space="preserve">14.4045705795288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6095571517944</t>
+    <t xml:space="preserve">14.6095561981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.5839338302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5156059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7419443130493</t>
+    <t xml:space="preserve">14.515604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741943359375</t>
   </si>
   <si>
     <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5027914047241</t>
+    <t xml:space="preserve">14.5027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600877761841</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6266374588013</t>
+    <t xml:space="preserve">14.4686298370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6266393661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163200378418</t>
@@ -4205,28 +4205,28 @@
     <t xml:space="preserve">14.7931909561157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6906967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7889194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7462129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999538421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8444356918335</t>
+    <t xml:space="preserve">14.6906976699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7889204025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7462139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8444366455078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2508296966553</t>
+    <t xml:space="preserve">14.0928201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2508306503296</t>
   </si>
   <si>
     <t xml:space="preserve">14.2892637252808</t>
@@ -4235,37 +4235,37 @@
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3490524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3106174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2593717575073</t>
+    <t xml:space="preserve">14.3490533828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3106184005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.259370803833</t>
   </si>
   <si>
     <t xml:space="preserve">14.3618650436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1910419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3277006149292</t>
+    <t xml:space="preserve">14.1910429000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3276996612549</t>
   </si>
   <si>
     <t xml:space="preserve">14.3917589187622</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7504854202271</t>
+    <t xml:space="preserve">14.7504844665527</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6736154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017311096191</t>
+    <t xml:space="preserve">14.6736164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017320632935</t>
   </si>
   <si>
     <t xml:space="preserve">14.8615198135376</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">14.8487071990967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9554719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8358964920044</t>
+    <t xml:space="preserve">14.9554710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9682817459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8358974456787</t>
   </si>
   <si>
     <t xml:space="preserve">15.168999671936</t>
@@ -4292,79 +4292,79 @@
     <t xml:space="preserve">15.3013868331909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2586793899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270101547241</t>
+    <t xml:space="preserve">15.2586803436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270092010498</t>
   </si>
   <si>
     <t xml:space="preserve">15.3825263977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2885732650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319948196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4679384231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4636659622192</t>
+    <t xml:space="preserve">15.28857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5021018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4679374694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4636669158936</t>
   </si>
   <si>
     <t xml:space="preserve">15.5063734054565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5618896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6003246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.587513923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344900131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6857357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850206375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106420516968</t>
+    <t xml:space="preserve">15.5618906021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6003255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5875129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473016738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857347488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106449127197</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9804029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223934173584</t>
+    <t xml:space="preserve">15.9804019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266649246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223915100098</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4376,31 +4376,31 @@
     <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0658149719238</t>
+    <t xml:space="preserve">16.0658130645752</t>
   </si>
   <si>
     <t xml:space="preserve">15.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7327117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2031631469727</t>
+    <t xml:space="preserve">15.7327108383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.203161239624</t>
   </si>
   <si>
     <t xml:space="preserve">15.7540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8316249847412</t>
+    <t xml:space="preserve">14.8316259384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450855255127</t>
+    <t xml:space="preserve">15.0451526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4508562088013</t>
   </si>
   <si>
     <t xml:space="preserve">15.4081497192383</t>
@@ -4412,25 +4412,25 @@
     <t xml:space="preserve">15.2501392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4423131942749</t>
+    <t xml:space="preserve">15.4423151016235</t>
   </si>
   <si>
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985464096069</t>
+    <t xml:space="preserve">15.6985473632812</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6216793060303</t>
+    <t xml:space="preserve">15.621678352356</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437461853027</t>
+    <t xml:space="preserve">15.8437471389771</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">16.1683082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0401916503906</t>
+    <t xml:space="preserve">16.040189743042</t>
   </si>
   <si>
     <t xml:space="preserve">16.1384143829346</t>
@@ -4451,7 +4451,7 @@
     <t xml:space="preserve">16.2836132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3049640655518</t>
+    <t xml:space="preserve">16.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">16.3092365264893</t>
@@ -4466,16 +4466,16 @@
     <t xml:space="preserve">16.1298732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.232364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.125602722168</t>
+    <t xml:space="preserve">16.2323665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1256008148193</t>
   </si>
   <si>
     <t xml:space="preserve">15.8693695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9334278106689</t>
+    <t xml:space="preserve">15.9334297180176</t>
   </si>
   <si>
     <t xml:space="preserve">15.8053112030029</t>
@@ -4487,19 +4487,19 @@
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8907203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889421463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1127891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0316524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.912073135376</t>
+    <t xml:space="preserve">15.890721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889430999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1127910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0316505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9120721817017</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">16.4688701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596569061279</t>
+    <t xml:space="preserve">16.2596549987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.332426071167</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">16.4188404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5188999176025</t>
+    <t xml:space="preserve">16.5189018249512</t>
   </si>
   <si>
     <t xml:space="preserve">16.6462478637695</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">16.9236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1010646820068</t>
+    <t xml:space="preserve">17.1010627746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2193164825439</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">16.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7963390350342</t>
+    <t xml:space="preserve">16.7963371276855</t>
   </si>
   <si>
     <t xml:space="preserve">16.6689910888672</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">16.6280574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235660552979</t>
+    <t xml:space="preserve">16.7235679626465</t>
   </si>
   <si>
     <t xml:space="preserve">16.6917304992676</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">16.9373321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4330787658691</t>
+    <t xml:space="preserve">17.5103969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4330806732178</t>
   </si>
   <si>
     <t xml:space="preserve">17.2056732177734</t>
@@ -4607,10 +4607,10 @@
     <t xml:space="preserve">17.1783828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920261383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0692272186279</t>
+    <t xml:space="preserve">17.1920280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">17.2829914093018</t>
@@ -4619,13 +4619,13 @@
     <t xml:space="preserve">17.3648567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3739547729492</t>
+    <t xml:space="preserve">17.3739528656006</t>
   </si>
   <si>
     <t xml:space="preserve">17.3330192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3284702301025</t>
+    <t xml:space="preserve">17.3284721374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.5149459838867</t>
@@ -4634,10 +4634,10 @@
     <t xml:space="preserve">17.5240421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6286487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4057922363281</t>
+    <t xml:space="preserve">17.6286506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4057903289795</t>
   </si>
   <si>
     <t xml:space="preserve">17.037389755249</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">17.091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7190170288086</t>
+    <t xml:space="preserve">16.9737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7190189361572</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8736553192139</t>
+    <t xml:space="preserve">16.8736572265625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7417602539062</t>
@@ -4670,13 +4670,13 @@
     <t xml:space="preserve">16.7645015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281764984131</t>
+    <t xml:space="preserve">16.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">16.8418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9282341003418</t>
+    <t xml:space="preserve">16.9282360076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.0737762451172</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">17.442174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4012432098389</t>
+    <t xml:space="preserve">17.4012413024902</t>
   </si>
   <si>
     <t xml:space="preserve">17.292085647583</t>
@@ -4694,13 +4694,13 @@
     <t xml:space="preserve">17.3011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6013603210449</t>
+    <t xml:space="preserve">17.6013622283936</t>
   </si>
   <si>
     <t xml:space="preserve">17.7150650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7332572937012</t>
+    <t xml:space="preserve">17.7332592010498</t>
   </si>
   <si>
     <t xml:space="preserve">18.0197906494141</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">18.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1926212310791</t>
+    <t xml:space="preserve">18.1926231384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.0470809936523</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">17.7878360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059093475342</t>
+    <t xml:space="preserve">17.6059074401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6832294464111</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">16.8918476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3239231109619</t>
+    <t xml:space="preserve">17.3239250183105</t>
   </si>
   <si>
     <t xml:space="preserve">17.4876575469971</t>
@@ -4793,16 +4793,16 @@
     <t xml:space="preserve">17.0510349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2966327667236</t>
+    <t xml:space="preserve">17.2966346740723</t>
   </si>
   <si>
     <t xml:space="preserve">17.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1465454101562</t>
+    <t xml:space="preserve">17.1238040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1465473175049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2511539459229</t>
@@ -4820,16 +4820,16 @@
     <t xml:space="preserve">17.8787994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8151245117188</t>
+    <t xml:space="preserve">17.8151226043701</t>
   </si>
   <si>
     <t xml:space="preserve">17.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4922046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.314826965332</t>
+    <t xml:space="preserve">17.4922065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3148288726807</t>
   </si>
   <si>
     <t xml:space="preserve">17.187479019165</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">17.242057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1419982910156</t>
+    <t xml:space="preserve">17.141996383667</t>
   </si>
   <si>
     <t xml:space="preserve">17.2284126281738</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">17.4103393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.414888381958</t>
+    <t xml:space="preserve">17.4148864746094</t>
   </si>
   <si>
     <t xml:space="preserve">17.496753692627</t>
@@ -4898,13 +4898,13 @@
     <t xml:space="preserve">17.9561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0061454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.901538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9515705108643</t>
+    <t xml:space="preserve">18.0061473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9015407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9515686035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.9379234313965</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">18.6201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5473785400391</t>
+    <t xml:space="preserve">18.5473766326904</t>
   </si>
   <si>
     <t xml:space="preserve">18.5655708312988</t>
@@ -4946,10 +4946,10 @@
     <t xml:space="preserve">18.6656303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6929187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8202686309814</t>
+    <t xml:space="preserve">18.6929168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8202667236328</t>
   </si>
   <si>
     <t xml:space="preserve">18.629243850708</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">18.7565937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6838245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5564746856689</t>
+    <t xml:space="preserve">18.6838226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5564727783203</t>
   </si>
   <si>
     <t xml:space="preserve">18.8384590148926</t>
@@ -4988,25 +4988,25 @@
     <t xml:space="preserve">19.5024909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.139232635498</t>
+    <t xml:space="preserve">20.1392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9118232727051</t>
+    <t xml:space="preserve">19.9118251800537</t>
   </si>
   <si>
     <t xml:space="preserve">19.9664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0027885437012</t>
+    <t xml:space="preserve">20.0027866363525</t>
   </si>
   <si>
     <t xml:space="preserve">20.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1574230194092</t>
+    <t xml:space="preserve">20.1574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">20.0755577087402</t>
@@ -5015,16 +5015,16 @@
     <t xml:space="preserve">20.2120018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2847728729248</t>
+    <t xml:space="preserve">20.2847709655762</t>
   </si>
   <si>
     <t xml:space="preserve">20.393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5940456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6122398376465</t>
+    <t xml:space="preserve">20.5940475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6122417449951</t>
   </si>
   <si>
     <t xml:space="preserve">20.6759147644043</t>
@@ -5045,10 +5045,10 @@
     <t xml:space="preserve">21.1034412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3399429321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127178192139</t>
+    <t xml:space="preserve">21.3399448394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127159118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.5309677124023</t>
@@ -5063,10 +5063,10 @@
     <t xml:space="preserve">20.8669376373291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0306701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7304916381836</t>
+    <t xml:space="preserve">21.0306720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7304935455322</t>
   </si>
   <si>
     <t xml:space="preserve">20.7577800750732</t>
@@ -5075,13 +5075,13 @@
     <t xml:space="preserve">20.6031436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7032051086426</t>
+    <t xml:space="preserve">20.7032032012939</t>
   </si>
   <si>
     <t xml:space="preserve">20.3393516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4394111633301</t>
+    <t xml:space="preserve">20.4394092559814</t>
   </si>
   <si>
     <t xml:space="preserve">20.4939880371094</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">20.6213359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7123012542725</t>
+    <t xml:space="preserve">20.7122993469238</t>
   </si>
   <si>
     <t xml:space="preserve">21.003381729126</t>
@@ -5114,13 +5114,13 @@
     <t xml:space="preserve">21.2307891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7765674591064</t>
+    <t xml:space="preserve">21.7765693664551</t>
   </si>
   <si>
     <t xml:space="preserve">21.7401809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9039154052734</t>
+    <t xml:space="preserve">21.9039173126221</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949977874756</t>
@@ -6030,6 +6030,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -71004,7 +71007,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6496412037</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>1525386</v>
@@ -71025,6 +71028,32 @@
         <v>2004</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6515625</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>1534992</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>33.3899993896484</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>33.0299987792969</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>33.2999992370605</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>33.1399993896484</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2006</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21390056610107</t>
+    <t xml:space="preserve">9.21390151977539</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
@@ -50,22 +50,22 @@
     <t xml:space="preserve">9.13427352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11721229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02052211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76457977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88970756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06602191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95795917510986</t>
+    <t xml:space="preserve">9.11721038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02052116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76458072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8897066116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0660228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95795822143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.75889205932617</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">8.57120227813721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63376617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29251003265381</t>
+    <t xml:space="preserve">8.63376522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29251098632812</t>
   </si>
   <si>
     <t xml:space="preserve">8.44607543945312</t>
@@ -92,145 +92,145 @@
     <t xml:space="preserve">8.04794311523438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93987846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668745040894</t>
+    <t xml:space="preserve">7.93988084793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568689346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668840408325</t>
   </si>
   <si>
     <t xml:space="preserve">7.41662168502808</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23461771011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15499114990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161222457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7454833984375</t>
+    <t xml:space="preserve">7.234619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15499210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161365509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74548482894897</t>
   </si>
   <si>
     <t xml:space="preserve">6.47248077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8137354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23360109329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34166479110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59760713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62035894393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392292022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72842311859131</t>
+    <t xml:space="preserve">6.81373596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23360252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34166574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59760761260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62035846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392244338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72842264175415</t>
   </si>
   <si>
     <t xml:space="preserve">6.66017150878906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89905023574829</t>
+    <t xml:space="preserve">6.89905071258545</t>
   </si>
   <si>
     <t xml:space="preserve">6.8933629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95592451095581</t>
+    <t xml:space="preserve">6.95592498779297</t>
   </si>
   <si>
     <t xml:space="preserve">7.2630558013916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28580522537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643377304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45074653625488</t>
+    <t xml:space="preserve">7.28580713272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643329620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45074558258057</t>
   </si>
   <si>
     <t xml:space="preserve">7.37680768966675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24599266052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3711199760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7920036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731599807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89437818527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67256355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587194442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037071228027</t>
+    <t xml:space="preserve">7.2459921836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31993103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249540328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37112140655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750104904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79200172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731695175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437913894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256116867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037261962891</t>
   </si>
   <si>
     <t xml:space="preserve">7.3654317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42799615859985</t>
+    <t xml:space="preserve">7.4279956817627</t>
   </si>
   <si>
     <t xml:space="preserve">7.48487234115601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41093254089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98436403274536</t>
+    <t xml:space="preserve">7.4109320640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30287027359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755456924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9843635559082</t>
   </si>
   <si>
     <t xml:space="preserve">7.00711441040039</t>
@@ -242,109 +242,109 @@
     <t xml:space="preserve">7.05261468887329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13792943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067934036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43368482589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49624824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4791841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743528366089</t>
+    <t xml:space="preserve">7.13793039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4336838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49624729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918462753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743623733521</t>
   </si>
   <si>
     <t xml:space="preserve">7.59862375259399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75218915939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181476593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456514358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80337715148926</t>
+    <t xml:space="preserve">7.75218868255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.854567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80337619781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.77493858337402</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57018518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387083053589</t>
+    <t xml:space="preserve">7.57018709182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387130737305</t>
   </si>
   <si>
     <t xml:space="preserve">7.35405778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53605937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105278015137</t>
+    <t xml:space="preserve">7.53606128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105230331421</t>
   </si>
   <si>
     <t xml:space="preserve">7.1663670539856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0583028793335</t>
+    <t xml:space="preserve">7.05830192565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.11517858505249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25168180465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798839569092</t>
+    <t xml:space="preserve">7.25167989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798887252808</t>
   </si>
   <si>
     <t xml:space="preserve">7.73994970321655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84845352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90873241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94490098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85448026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228399276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76406145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54705429077148</t>
+    <t xml:space="preserve">7.8484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90873193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94490003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85447931289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228542327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76406097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54705238342285</t>
   </si>
   <si>
     <t xml:space="preserve">7.534996509552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66158437728882</t>
+    <t xml:space="preserve">7.6615834236145</t>
   </si>
   <si>
     <t xml:space="preserve">7.80625534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77008867263794</t>
+    <t xml:space="preserve">7.7700891494751</t>
   </si>
   <si>
     <t xml:space="preserve">7.42046546936035</t>
@@ -353,121 +353,121 @@
     <t xml:space="preserve">7.17934417724609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850511550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1914005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4084095954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54102373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5832200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257246017456</t>
+    <t xml:space="preserve">6.97439289093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850416183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92014122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40840911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54102468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58322095870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5825719833374</t>
   </si>
   <si>
     <t xml:space="preserve">6.02498292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11841726303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26308917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953569412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4318733215332</t>
+    <t xml:space="preserve">6.11841630935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26308870315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953664779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43187236785889</t>
   </si>
   <si>
     <t xml:space="preserve">6.25103282928467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13047313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91647863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92853498458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76341342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69710397720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8719162940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560922622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177684783936</t>
+    <t xml:space="preserve">6.13047361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91647911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9285364151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7634129524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69710493087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87191581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560874938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84177732467651</t>
   </si>
   <si>
     <t xml:space="preserve">6.75738430023193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8478045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7754693031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73327350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68504858016968</t>
+    <t xml:space="preserve">6.84780502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77546787261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73327255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68504810333252</t>
   </si>
   <si>
     <t xml:space="preserve">6.81163692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62476873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10098075866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07084083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79355335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06481218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2094841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210014343262</t>
+    <t xml:space="preserve">6.62476778030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10098171234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07084035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79355239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948505401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990339279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34209966659546</t>
   </si>
   <si>
     <t xml:space="preserve">7.08289670944214</t>
@@ -476,85 +476,85 @@
     <t xml:space="preserve">6.89000034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90808439254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73930072784424</t>
+    <t xml:space="preserve">6.90808534622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7393012046814</t>
   </si>
   <si>
     <t xml:space="preserve">7.04070043563843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01658964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8176646232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74532842636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271333694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149604797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425344467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247646331787</t>
+    <t xml:space="preserve">7.01658916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74532890319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271238327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247694015503</t>
   </si>
   <si>
     <t xml:space="preserve">6.93822431564331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88397216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042058944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079738616943</t>
+    <t xml:space="preserve">6.88397359848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523290634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770854949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313405990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079643249512</t>
   </si>
   <si>
     <t xml:space="preserve">6.72724390029907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79958152770996</t>
+    <t xml:space="preserve">6.79958009719849</t>
   </si>
   <si>
     <t xml:space="preserve">6.75135612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59462928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56448841094971</t>
+    <t xml:space="preserve">6.59462785720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56448936462402</t>
   </si>
   <si>
     <t xml:space="preserve">6.57654476165771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60668516159058</t>
+    <t xml:space="preserve">6.60668563842773</t>
   </si>
   <si>
     <t xml:space="preserve">6.54640483856201</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51626443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4981803894043</t>
+    <t xml:space="preserve">6.51626634597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49817991256714</t>
   </si>
   <si>
     <t xml:space="preserve">6.76943969726562</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">6.85986137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85383319854736</t>
+    <t xml:space="preserve">6.85383272171021</t>
   </si>
   <si>
     <t xml:space="preserve">7.1853723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16728973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742774963379</t>
+    <t xml:space="preserve">7.16728830337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742727279663</t>
   </si>
   <si>
     <t xml:space="preserve">7.28784894943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26976490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33004379272461</t>
+    <t xml:space="preserve">7.26976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33004474639893</t>
   </si>
   <si>
     <t xml:space="preserve">7.31196117401123</t>
@@ -590,22 +590,22 @@
     <t xml:space="preserve">7.14317655563354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09495258331299</t>
+    <t xml:space="preserve">7.09495162963867</t>
   </si>
   <si>
     <t xml:space="preserve">6.98644828796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67299270629883</t>
+    <t xml:space="preserve">6.67299318313599</t>
   </si>
   <si>
     <t xml:space="preserve">6.83574914932251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08892440795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07686805725098</t>
+    <t xml:space="preserve">7.08892488479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07686853408813</t>
   </si>
   <si>
     <t xml:space="preserve">6.87794494628906</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">6.82369232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43854856491089</t>
+    <t xml:space="preserve">7.43854808807373</t>
   </si>
   <si>
     <t xml:space="preserve">7.35415649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73392057418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055236816406</t>
+    <t xml:space="preserve">7.7339186668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055332183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.6803150177002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45125293731689</t>
+    <t xml:space="preserve">8.45125198364258</t>
   </si>
   <si>
     <t xml:space="preserve">8.47536373138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41508293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33069133758545</t>
+    <t xml:space="preserve">8.41508483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33069038391113</t>
   </si>
   <si>
     <t xml:space="preserve">8.541672706604</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">8.6381196975708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58386707305908</t>
+    <t xml:space="preserve">8.5838680267334</t>
   </si>
   <si>
     <t xml:space="preserve">8.59592437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66223239898682</t>
+    <t xml:space="preserve">8.6622314453125</t>
   </si>
   <si>
     <t xml:space="preserve">8.6682596206665</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">8.5537281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50550365447998</t>
+    <t xml:space="preserve">8.50550270080566</t>
   </si>
   <si>
     <t xml:space="preserve">8.51153182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65017604827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71045589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75265312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69839954376221</t>
+    <t xml:space="preserve">8.65017700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7104549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75265121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69840049743652</t>
   </si>
   <si>
     <t xml:space="preserve">8.71648406982422</t>
@@ -695,34 +695,34 @@
     <t xml:space="preserve">8.48742008209229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38494300842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25835704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23424339294434</t>
+    <t xml:space="preserve">8.38494491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25835609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23424434661865</t>
   </si>
   <si>
     <t xml:space="preserve">8.16793632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27041339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26438331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5898962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2951717376709</t>
+    <t xml:space="preserve">8.27041149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26438522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58989524841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29517078399658</t>
   </si>
   <si>
     <t xml:space="preserve">9.38559055328369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42176055908203</t>
+    <t xml:space="preserve">9.4217586517334</t>
   </si>
   <si>
     <t xml:space="preserve">9.28311538696289</t>
@@ -731,43 +731,43 @@
     <t xml:space="preserve">8.98774337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88526725769043</t>
+    <t xml:space="preserve">8.88526821136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00582695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993869781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81895923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77073574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67428684234619</t>
+    <t xml:space="preserve">9.00582790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02994060516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81896114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77073669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67428874969482</t>
   </si>
   <si>
     <t xml:space="preserve">8.74059581756592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90335273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04802513122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87924003601074</t>
+    <t xml:space="preserve">8.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04802322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87923908233643</t>
   </si>
   <si>
     <t xml:space="preserve">8.90937900543213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95760345458984</t>
+    <t xml:space="preserve">8.95760250091553</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101558685303</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49947643280029</t>
+    <t xml:space="preserve">8.65620231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49947738647461</t>
   </si>
   <si>
     <t xml:space="preserve">8.14985179901123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27643966674805</t>
+    <t xml:space="preserve">8.27644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.54770088195801</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">8.46330833435059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56578350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78882122039795</t>
+    <t xml:space="preserve">8.56578254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78882026672363</t>
   </si>
   <si>
     <t xml:space="preserve">8.80087566375732</t>
@@ -809,34 +809,34 @@
     <t xml:space="preserve">8.794846534729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78279209136963</t>
+    <t xml:space="preserve">8.78279113769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.86718368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98171424865723</t>
+    <t xml:space="preserve">8.98171615600586</t>
   </si>
   <si>
     <t xml:space="preserve">8.80690383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63209247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60798072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46933555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36083221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93349266052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75868034362793</t>
+    <t xml:space="preserve">8.6320915222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60797882080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46933650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36083126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93349075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7586784362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.87321281433105</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">9.04199600219727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19269561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24092102050781</t>
+    <t xml:space="preserve">9.1926965713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21077823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2409200668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.2168083190918</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">9.03596687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07213687896729</t>
+    <t xml:space="preserve">9.07213497161865</t>
   </si>
   <si>
     <t xml:space="preserve">9.12035942077637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.304931640625</t>
+    <t xml:space="preserve">9.30493068695068</t>
   </si>
   <si>
     <t xml:space="preserve">9.33675384521484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18400573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15854740142822</t>
+    <t xml:space="preserve">9.18400478363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15854835510254</t>
   </si>
   <si>
     <t xml:space="preserve">9.13308906555176</t>
@@ -890,67 +890,67 @@
     <t xml:space="preserve">8.94851779937744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83395576477051</t>
+    <t xml:space="preserve">8.83395671844482</t>
   </si>
   <si>
     <t xml:space="preserve">8.94215393066406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03762054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81486320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73848819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89123916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95488166809082</t>
+    <t xml:space="preserve">9.03762149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81486225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73848915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89123725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95488262176514</t>
   </si>
   <si>
     <t xml:space="preserve">9.05035018920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22855758666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23492050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17127704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2858362197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29856586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34948348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2540168762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24765014648438</t>
+    <t xml:space="preserve">9.22855567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23492240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1712760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28583717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2985668182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19037055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34948253631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25401496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24765110015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.29220199584961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33038997650146</t>
+    <t xml:space="preserve">9.33038902282715</t>
   </si>
   <si>
     <t xml:space="preserve">9.38130474090576</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">9.54041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64861392974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79499912261963</t>
+    <t xml:space="preserve">9.64861679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79500007629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.85864353179932</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">9.71862506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68680191040039</t>
+    <t xml:space="preserve">9.68680286407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.56587600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52768993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75681209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77590656280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0877666473389</t>
+    <t xml:space="preserve">9.52768898010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75681114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0877676010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.1386833190918</t>
@@ -1007,76 +1007,76 @@
     <t xml:space="preserve">10.2341508865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1959648132324</t>
+    <t xml:space="preserve">10.1959638595581</t>
   </si>
   <si>
     <t xml:space="preserve">10.0623092651367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0050277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82682228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8650074005127</t>
+    <t xml:space="preserve">10.0050296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82682037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86500835418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.90319633483887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82045745849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87137317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78226947784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71225929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69952964782715</t>
+    <t xml:space="preserve">9.82045841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87137222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78227043151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71226024627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69953060150146</t>
   </si>
   <si>
     <t xml:space="preserve">9.68043899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69316673278809</t>
+    <t xml:space="preserve">9.6931676864624</t>
   </si>
   <si>
     <t xml:space="preserve">9.66134357452393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53405380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52132511138916</t>
+    <t xml:space="preserve">9.53405284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52132415771484</t>
   </si>
   <si>
     <t xml:space="preserve">9.57224178314209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61679267883301</t>
+    <t xml:space="preserve">9.61679172515869</t>
   </si>
   <si>
     <t xml:space="preserve">9.674072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62952136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59769916534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89046669006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94774723052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75044822692871</t>
+    <t xml:space="preserve">9.62952041625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59770011901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89046573638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9477481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75044727325439</t>
   </si>
   <si>
     <t xml:space="preserve">9.89683246612549</t>
@@ -1088,76 +1088,76 @@
     <t xml:space="preserve">9.8777379989624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0304870605469</t>
+    <t xml:space="preserve">10.0304861068726</t>
   </si>
   <si>
     <t xml:space="preserve">10.0686740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1323194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93501758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84591484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85227966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72498893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9986629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96047782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0177564620972</t>
+    <t xml:space="preserve">10.1323204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93501853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84591579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85228061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83318710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72498989105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99866390228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96047687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0177583694458</t>
   </si>
   <si>
     <t xml:space="preserve">9.95411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1259546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0241222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94138240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8841028213501</t>
+    <t xml:space="preserve">10.1259536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0241212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94138336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88410186767578</t>
   </si>
   <si>
     <t xml:space="preserve">10.0368509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78863620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63588523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58497047424316</t>
+    <t xml:space="preserve">9.78863430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63588619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58496952056885</t>
   </si>
   <si>
     <t xml:space="preserve">9.61042785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66770935058594</t>
+    <t xml:space="preserve">9.66770839691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.74408340454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73135280609131</t>
+    <t xml:space="preserve">9.73135471343994</t>
   </si>
   <si>
     <t xml:space="preserve">9.8077278137207</t>
@@ -1166,52 +1166,52 @@
     <t xml:space="preserve">9.73771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589733123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55951309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47677326202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97320652008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97956943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0814037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0559463500977</t>
+    <t xml:space="preserve">9.70589542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5595121383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47677230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97957038879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0814027786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.055944442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.291431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3041610717773</t>
+    <t xml:space="preserve">10.3041620254517</t>
   </si>
   <si>
     <t xml:space="preserve">10.2023296356201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.310525894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641416549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.148229598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9922981262207</t>
+    <t xml:space="preserve">10.3105268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736879348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641407012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1482305526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99230003356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.76954078674316</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">9.77908802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81409358978271</t>
+    <t xml:space="preserve">9.8140926361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.80454540252686</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">10.0082101821899</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98593425750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92865467071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94456481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9700231552124</t>
+    <t xml:space="preserve">9.98593521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92865371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94456577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97002410888672</t>
   </si>
   <si>
     <t xml:space="preserve">10.0495805740356</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">10.1609582901001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3137073516846</t>
+    <t xml:space="preserve">10.3137083053589</t>
   </si>
   <si>
     <t xml:space="preserve">10.2946138381958</t>
@@ -1274,58 +1274,58 @@
     <t xml:space="preserve">10.3455305099487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346342086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.530101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.638298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.765588760376</t>
+    <t xml:space="preserve">10.4346332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5301008224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6382970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7655897140503</t>
   </si>
   <si>
     <t xml:space="preserve">10.8546915054321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6319332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178544998169</t>
+    <t xml:space="preserve">10.6319341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178554534912</t>
   </si>
   <si>
     <t xml:space="preserve">10.5841979980469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6542081832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.708309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7051267623901</t>
+    <t xml:space="preserve">10.6542091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7083072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5269203186035</t>
+    <t xml:space="preserve">10.5269193649292</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4409980773926</t>
+    <t xml:space="preserve">10.4409999847412</t>
   </si>
   <si>
     <t xml:space="preserve">10.5014610290527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5078268051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2977962493896</t>
+    <t xml:space="preserve">10.5078258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.297797203064</t>
   </si>
   <si>
     <t xml:space="preserve">10.3328018188477</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">10.252890586853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1319522857666</t>
+    <t xml:space="preserve">10.1319532394409</t>
   </si>
   <si>
     <t xml:space="preserve">10.0143737792969</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">9.99421691894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83968448638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49702644348145</t>
+    <t xml:space="preserve">9.83968544006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49702548980713</t>
   </si>
   <si>
     <t xml:space="preserve">9.5541353225708</t>
@@ -1367,34 +1367,34 @@
     <t xml:space="preserve">9.86991882324219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65491771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67843437194824</t>
+    <t xml:space="preserve">9.6549186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">9.52054214477539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79937076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75233936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78257465362549</t>
+    <t xml:space="preserve">9.79937171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75234031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78257369995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.90015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80608940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76241779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82960510253906</t>
+    <t xml:space="preserve">9.80609130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76241874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82960605621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.69859027862549</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">9.76913738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60116577148438</t>
+    <t xml:space="preserve">9.60116767883301</t>
   </si>
   <si>
     <t xml:space="preserve">9.61796283721924</t>
@@ -1415,43 +1415,43 @@
     <t xml:space="preserve">9.51718235015869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61124610900879</t>
+    <t xml:space="preserve">9.61124515533447</t>
   </si>
   <si>
     <t xml:space="preserve">9.59108829498291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77249526977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7288236618042</t>
+    <t xml:space="preserve">9.80945014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77249622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72882270812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.65155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66163635253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70530700683594</t>
+    <t xml:space="preserve">9.66163730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70530891418457</t>
   </si>
   <si>
     <t xml:space="preserve">9.84976291656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85648250579834</t>
+    <t xml:space="preserve">9.85648155212402</t>
   </si>
   <si>
     <t xml:space="preserve">9.81616878509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74898052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89007663726807</t>
+    <t xml:space="preserve">9.74898147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89007472991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.90351295471191</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.0479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2125778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1117963790894</t>
+    <t xml:space="preserve">10.2125768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.111795425415</t>
   </si>
   <si>
     <t xml:space="preserve">9.95390319824219</t>
@@ -1478,37 +1478,37 @@
     <t xml:space="preserve">10.0378894805908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009355545044</t>
+    <t xml:space="preserve">10.0009365081787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0681228637695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916404724121</t>
+    <t xml:space="preserve">10.0916395187378</t>
   </si>
   <si>
     <t xml:space="preserve">10.0748414993286</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8665599822998</t>
+    <t xml:space="preserve">9.86655902862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.71202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312175750732</t>
+    <t xml:space="preserve">9.73218250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312271118164</t>
   </si>
   <si>
     <t xml:space="preserve">9.92702865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98078060150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92031002044678</t>
+    <t xml:space="preserve">9.98077869415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92031097412109</t>
   </si>
   <si>
     <t xml:space="preserve">9.6381196975708</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">9.76577758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93710803985596</t>
+    <t xml:space="preserve">9.93710613250732</t>
   </si>
   <si>
     <t xml:space="preserve">9.96062278747559</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">9.94382572174072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1621875762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1017179489136</t>
+    <t xml:space="preserve">10.1621866226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1017169952393</t>
   </si>
   <si>
     <t xml:space="preserve">10.0882797241211</t>
@@ -1544,40 +1544,40 @@
     <t xml:space="preserve">10.1823434829712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2965631484985</t>
+    <t xml:space="preserve">10.2965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">10.4141416549683</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4309387207031</t>
+    <t xml:space="preserve">10.4309368133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.3704700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9975757598877</t>
+    <t xml:space="preserve">9.99757671356201</t>
   </si>
   <si>
     <t xml:space="preserve">9.88671588897705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96734237670898</t>
+    <t xml:space="preserve">9.96734142303467</t>
   </si>
   <si>
     <t xml:space="preserve">9.93038749694824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70866680145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69187068939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59444808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50038528442383</t>
+    <t xml:space="preserve">9.70866775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59444713592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">9.61460494995117</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">9.56421279907227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41304111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43991565704346</t>
+    <t xml:space="preserve">9.4130392074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43991661071777</t>
   </si>
   <si>
     <t xml:space="preserve">9.40968036651611</t>
@@ -1598,28 +1598,28 @@
     <t xml:space="preserve">9.288743019104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23835182189941</t>
+    <t xml:space="preserve">9.2383508682251</t>
   </si>
   <si>
     <t xml:space="preserve">9.43655586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3324146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53397750854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62468242645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65827655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835498809814</t>
+    <t xml:space="preserve">9.33241558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53397941589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66499710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62468433380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65827751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835594177246</t>
   </si>
   <si>
     <t xml:space="preserve">9.63476085662842</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">9.57429122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71538639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51382160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59780788421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55749416351318</t>
+    <t xml:space="preserve">9.71538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51382255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59780693054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5574951171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.57765197753906</t>
@@ -1649,88 +1649,88 @@
     <t xml:space="preserve">9.87663745880127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91359233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0042953491211</t>
+    <t xml:space="preserve">9.91359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0042943954468</t>
   </si>
   <si>
     <t xml:space="preserve">10.0849208831787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97406005859375</t>
+    <t xml:space="preserve">9.97406101226807</t>
   </si>
   <si>
     <t xml:space="preserve">9.57093143463135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64484024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7456226348877</t>
+    <t xml:space="preserve">9.6448392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562072753906</t>
   </si>
   <si>
     <t xml:space="preserve">9.89679336547852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85984039306641</t>
+    <t xml:space="preserve">9.85984230041504</t>
   </si>
   <si>
     <t xml:space="preserve">9.95054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0210914611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0446081161499</t>
+    <t xml:space="preserve">10.021092414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0446090698242</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647630691528</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327337265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3267984390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3435935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898445129395</t>
+    <t xml:space="preserve">10.2327346801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3267974853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3435955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898435592651</t>
   </si>
   <si>
     <t xml:space="preserve">10.3335161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3133602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839082717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3771877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2764053344727</t>
+    <t xml:space="preserve">10.3133592605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839063644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3771886825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2764072418213</t>
   </si>
   <si>
     <t xml:space="preserve">10.1991395950317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2461719512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932043075562</t>
+    <t xml:space="preserve">10.2461709976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932033538818</t>
   </si>
   <si>
     <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1285934448242</t>
+    <t xml:space="preserve">10.1285924911499</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058591842651</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">10.1890621185303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2293748855591</t>
+    <t xml:space="preserve">10.2293758392334</t>
   </si>
   <si>
     <t xml:space="preserve">10.2260160446167</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">10.2730474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805475234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4275808334351</t>
+    <t xml:space="preserve">10.3805484771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4275798797607</t>
   </si>
   <si>
     <t xml:space="preserve">10.4342975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5451583862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.672815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660976409912</t>
+    <t xml:space="preserve">10.5451574325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6728162765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
     <t xml:space="preserve">10.7400035858154</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">10.6123466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.565315246582</t>
+    <t xml:space="preserve">10.5653142929077</t>
   </si>
   <si>
     <t xml:space="preserve">10.6157054901123</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">10.6224250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7534408569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9785203933716</t>
+    <t xml:space="preserve">10.7534418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
     <t xml:space="preserve">11.072585105896</t>
@@ -1814,82 +1814,82 @@
     <t xml:space="preserve">10.9718027114868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0087556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0860214233398</t>
+    <t xml:space="preserve">11.0087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0860223770142</t>
   </si>
   <si>
     <t xml:space="preserve">11.2036008834839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1767244338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2304763793945</t>
+    <t xml:space="preserve">11.1767263412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2304754257202</t>
   </si>
   <si>
     <t xml:space="preserve">11.2237577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1733655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2170381546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2271184921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35813331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4219608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5563383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521970748901</t>
+    <t xml:space="preserve">11.1733646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2271175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4219617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5563373565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521980285645</t>
   </si>
   <si>
     <t xml:space="preserve">11.4286813735962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622755050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5832138061523</t>
+    <t xml:space="preserve">11.4622735977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5832147598267</t>
   </si>
   <si>
     <t xml:space="preserve">11.5529775619507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6235256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6201658248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5261039733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4689931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3245391845703</t>
+    <t xml:space="preserve">11.6235265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6201667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6302442550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.526104927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824304580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4689922332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.324538230896</t>
   </si>
   <si>
     <t xml:space="preserve">11.3648529052734</t>
@@ -1901,64 +1901,64 @@
     <t xml:space="preserve">11.5093059539795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4253206253052</t>
+    <t xml:space="preserve">11.4253196716309</t>
   </si>
   <si>
     <t xml:space="preserve">11.5636587142944</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5849418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5601110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3189077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5459251403809</t>
+    <t xml:space="preserve">11.584942817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5601119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3189067840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5459241867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.4146795272827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3330955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2124929428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763414382935</t>
+    <t xml:space="preserve">11.3330965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2124948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763404846191</t>
   </si>
   <si>
     <t xml:space="preserve">11.148645401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.123815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2727947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1805696487427</t>
+    <t xml:space="preserve">11.1238145828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2727937698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1805686950684</t>
   </si>
   <si>
     <t xml:space="preserve">11.2195873260498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2479648590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3366422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4536981582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4288682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4785280227661</t>
+    <t xml:space="preserve">11.2479639053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3366432189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4288702011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4785289764404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4466047286987</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">11.8119592666626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8332424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8403358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7871294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7481107711792</t>
+    <t xml:space="preserve">11.8332414627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8403348922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7871284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7481098175049</t>
   </si>
   <si>
     <t xml:space="preserve">11.7126398086548</t>
@@ -1994,85 +1994,85 @@
     <t xml:space="preserve">11.8935432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.106372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1312017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0708999633789</t>
+    <t xml:space="preserve">12.1063718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1312026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0708990097046</t>
   </si>
   <si>
     <t xml:space="preserve">12.1418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1773147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2092380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2056903839111</t>
+    <t xml:space="preserve">12.1773157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2092370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2056913375854</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560316085815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808605194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1170139312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.989315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0106000900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9751262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.996410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8545255661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9467506408691</t>
+    <t xml:space="preserve">12.1808595657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1170129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9893159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247869491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105991363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9751272201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9964113235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8545246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9467496871948</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6629791259766</t>
+    <t xml:space="preserve">11.6629800796509</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884876251221</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707540512085</t>
+    <t xml:space="preserve">11.5707530975342</t>
   </si>
   <si>
     <t xml:space="preserve">11.6594314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3437376022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3792085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.29407787323</t>
+    <t xml:space="preserve">11.3437366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3792095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430561065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2940769195557</t>
   </si>
   <si>
     <t xml:space="preserve">11.4749813079834</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">11.5069046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6168670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5778474807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4678869247437</t>
+    <t xml:space="preserve">11.6168661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5778484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.467887878418</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820747375488</t>
@@ -2096,16 +2096,16 @@
     <t xml:space="preserve">11.6558847427368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5388298034668</t>
+    <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
     <t xml:space="preserve">11.6487913131714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6842613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7090911865234</t>
+    <t xml:space="preserve">11.6842622756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7090921401978</t>
   </si>
   <si>
     <t xml:space="preserve">11.7374687194824</t>
@@ -2117,40 +2117,40 @@
     <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1347484588623</t>
+    <t xml:space="preserve">12.1347494125366</t>
   </si>
   <si>
     <t xml:space="preserve">12.2021436691284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1844072341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3014621734619</t>
+    <t xml:space="preserve">12.1844062805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3014631271362</t>
   </si>
   <si>
     <t xml:space="preserve">12.4149723052979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3972368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2908239364624</t>
+    <t xml:space="preserve">12.39723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2908229827881</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881017684937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6597232818604</t>
+    <t xml:space="preserve">12.6597242355347</t>
   </si>
   <si>
     <t xml:space="preserve">12.7058372497559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6739130020142</t>
+    <t xml:space="preserve">12.6739120483398</t>
   </si>
   <si>
     <t xml:space="preserve">12.741307258606</t>
@@ -2162,31 +2162,31 @@
     <t xml:space="preserve">12.6703662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6136131286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5852336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5213832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.606517791748</t>
+    <t xml:space="preserve">12.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5852346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5213842391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6065168380737</t>
   </si>
   <si>
     <t xml:space="preserve">12.5887823104858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6490821838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6774625778198</t>
+    <t xml:space="preserve">12.6490831375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6774616241455</t>
   </si>
   <si>
     <t xml:space="preserve">12.8157987594604</t>
@@ -2195,76 +2195,76 @@
     <t xml:space="preserve">12.744854927063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8441743850708</t>
+    <t xml:space="preserve">12.8441753387451</t>
   </si>
   <si>
     <t xml:space="preserve">12.8477220535278</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8406276702881</t>
+    <t xml:space="preserve">12.8406286239624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080219268799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0357208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0463619232178</t>
+    <t xml:space="preserve">13.035719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215330123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0463600158691</t>
   </si>
   <si>
     <t xml:space="preserve">13.0534553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0499086380005</t>
+    <t xml:space="preserve">13.0499076843262</t>
   </si>
   <si>
     <t xml:space="preserve">13.0286254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9364004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8938331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.124400138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882457733154</t>
+    <t xml:space="preserve">12.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1243991851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882476806641</t>
   </si>
   <si>
     <t xml:space="preserve">13.1917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.642279624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338251113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167701721191</t>
+    <t xml:space="preserve">13.6422824859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167692184448</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5145826339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2662839889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237186431885</t>
+    <t xml:space="preserve">13.5145835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2662858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237195968628</t>
   </si>
   <si>
     <t xml:space="preserve">13.2343597412109</t>
@@ -2273,13 +2273,13 @@
     <t xml:space="preserve">13.1527757644653</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2591896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456842422485</t>
+    <t xml:space="preserve">13.2591915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627382278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456813812256</t>
   </si>
   <si>
     <t xml:space="preserve">12.9754190444946</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">12.9612312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9399471282959</t>
+    <t xml:space="preserve">12.9399480819702</t>
   </si>
   <si>
     <t xml:space="preserve">12.918664932251</t>
@@ -2306,25 +2306,25 @@
     <t xml:space="preserve">13.0108909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1137561798096</t>
+    <t xml:space="preserve">13.1137580871582</t>
   </si>
   <si>
     <t xml:space="preserve">13.1314935684204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1776075363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1208515167236</t>
+    <t xml:space="preserve">13.1776065826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1208534240723</t>
   </si>
   <si>
     <t xml:space="preserve">13.4613771438599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2520961761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953401565552</t>
+    <t xml:space="preserve">13.2520942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953420639038</t>
   </si>
   <si>
     <t xml:space="preserve">13.0640993118286</t>
@@ -2336,40 +2336,40 @@
     <t xml:space="preserve">13.1031160354614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0747375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9115705490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.978967666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9860610961914</t>
+    <t xml:space="preserve">13.0747394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9115715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9860601425171</t>
   </si>
   <si>
     <t xml:space="preserve">12.9505882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654584884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434947967529</t>
+    <t xml:space="preserve">12.86545753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235708236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5710458755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434957504272</t>
   </si>
   <si>
     <t xml:space="preserve">12.6916475296021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.482367515564</t>
+    <t xml:space="preserve">12.4823665618896</t>
   </si>
   <si>
     <t xml:space="preserve">12.5462141036987</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">12.7306661605835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0002489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804727554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194904327393</t>
+    <t xml:space="preserve">13.0002508163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194913864136</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230390548706</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">13.3939800262451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3688583374023</t>
+    <t xml:space="preserve">12.3688592910767</t>
   </si>
   <si>
     <t xml:space="preserve">12.2979164123535</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">12.2482557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5352840423584</t>
+    <t xml:space="preserve">11.5352821350098</t>
   </si>
   <si>
     <t xml:space="preserve">11.4004907608032</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">10.8116664886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76171493530273</t>
+    <t xml:space="preserve">9.76171398162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.61273574829102</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">8.56278228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01297664642334</t>
+    <t xml:space="preserve">8.01297760009766</t>
   </si>
   <si>
     <t xml:space="preserve">7.6972827911377</t>
@@ -2438,28 +2438,28 @@
     <t xml:space="preserve">7.36739921569824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61569738388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72565937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920703887939</t>
+    <t xml:space="preserve">7.61569881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72565984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920751571655</t>
   </si>
   <si>
     <t xml:space="preserve">8.58406639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83236503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98134613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7791576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77206516265869</t>
+    <t xml:space="preserve">8.83236598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98134422302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77915859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77206325531006</t>
   </si>
   <si>
     <t xml:space="preserve">8.80398845672607</t>
@@ -2468,28 +2468,28 @@
     <t xml:space="preserve">8.58051872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74723434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64436721801758</t>
+    <t xml:space="preserve">8.74723339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64436817169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.89976119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07002353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1303243637085</t>
+    <t xml:space="preserve">9.07002449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13032531738281</t>
   </si>
   <si>
     <t xml:space="preserve">9.31832218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93877983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7898006439209</t>
+    <t xml:space="preserve">8.93878078460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78979969024658</t>
   </si>
   <si>
     <t xml:space="preserve">8.88911914825439</t>
@@ -2498,25 +2498,25 @@
     <t xml:space="preserve">8.6301794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84300708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04164600372314</t>
+    <t xml:space="preserve">8.84300804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77561092376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04164791107178</t>
   </si>
   <si>
     <t xml:space="preserve">9.20126724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43537902832031</t>
+    <t xml:space="preserve">9.435378074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.23319244384766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00972270965576</t>
+    <t xml:space="preserve">9.00972175598145</t>
   </si>
   <si>
     <t xml:space="preserve">9.17643737792969</t>
@@ -2525,28 +2525,28 @@
     <t xml:space="preserve">9.0345516204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09485340118408</t>
+    <t xml:space="preserve">9.0948543548584</t>
   </si>
   <si>
     <t xml:space="preserve">9.20481491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12323093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08421325683594</t>
+    <t xml:space="preserve">9.12322998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08421230316162</t>
   </si>
   <si>
     <t xml:space="preserve">8.91040325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044269561768</t>
+    <t xml:space="preserve">8.80044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">9.17269039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01014614105225</t>
+    <t xml:space="preserve">9.01014518737793</t>
   </si>
   <si>
     <t xml:space="preserve">9.05817031860352</t>
@@ -2558,58 +2558,58 @@
     <t xml:space="preserve">8.99536895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96212291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20963287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43867301940918</t>
+    <t xml:space="preserve">8.96212196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20963382720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803791046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43867206573486</t>
   </si>
   <si>
     <t xml:space="preserve">9.22440910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52363872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81178569793701</t>
+    <t xml:space="preserve">9.52363967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81178665161133</t>
   </si>
   <si>
     <t xml:space="preserve">10.3031148910522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3474445343018</t>
+    <t xml:space="preserve">10.3474454879761</t>
   </si>
   <si>
     <t xml:space="preserve">10.6282043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540641784668</t>
+    <t xml:space="preserve">10.6540632247925</t>
   </si>
   <si>
     <t xml:space="preserve">10.5395441055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3215856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9226131439209</t>
+    <t xml:space="preserve">10.3215866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92261219024658</t>
   </si>
   <si>
     <t xml:space="preserve">9.91891860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90414047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1257934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519094467163</t>
+    <t xml:space="preserve">9.90414142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1257944107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.051908493042</t>
   </si>
   <si>
     <t xml:space="preserve">9.92630672454834</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">10.0592985153198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0703811645508</t>
+    <t xml:space="preserve">10.0703802108765</t>
   </si>
   <si>
     <t xml:space="preserve">9.80070400238037</t>
@@ -2627,34 +2627,34 @@
     <t xml:space="preserve">9.82656383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91522407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95216655731201</t>
+    <t xml:space="preserve">9.91522312164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9521656036377</t>
   </si>
   <si>
     <t xml:space="preserve">9.94847202301025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2218427658081</t>
+    <t xml:space="preserve">10.2218437194824</t>
   </si>
   <si>
     <t xml:space="preserve">10.1553478240967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2587842941284</t>
+    <t xml:space="preserve">10.2587852478027</t>
   </si>
   <si>
     <t xml:space="preserve">10.1627359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89675426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063636779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0777683258057</t>
+    <t xml:space="preserve">9.89675331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.07776927948</t>
   </si>
   <si>
     <t xml:space="preserve">10.129487991333</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">10.2070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2107591629028</t>
+    <t xml:space="preserve">10.2107601165771</t>
   </si>
   <si>
     <t xml:space="preserve">10.114709854126</t>
@@ -2672,19 +2672,19 @@
     <t xml:space="preserve">10.1812057495117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3289747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2772560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0408267974854</t>
+    <t xml:space="preserve">10.3289737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2772550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.040825843811</t>
   </si>
   <si>
     <t xml:space="preserve">9.98541450500488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97433090209961</t>
+    <t xml:space="preserve">9.97433185577393</t>
   </si>
   <si>
     <t xml:space="preserve">9.46453189849854</t>
@@ -2693,16 +2693,16 @@
     <t xml:space="preserve">9.35370635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40911960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55688762664795</t>
+    <t xml:space="preserve">9.40911865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55688667297363</t>
   </si>
   <si>
     <t xml:space="preserve">9.63077068328857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38695430755615</t>
+    <t xml:space="preserve">9.38695526123047</t>
   </si>
   <si>
     <t xml:space="preserve">9.78592777252197</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">9.73051452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68618392944336</t>
+    <t xml:space="preserve">9.68618297576904</t>
   </si>
   <si>
     <t xml:space="preserve">9.53841590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70834827423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62707710266113</t>
+    <t xml:space="preserve">9.70835018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62707614898682</t>
   </si>
   <si>
     <t xml:space="preserve">9.56058120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76376247406006</t>
+    <t xml:space="preserve">9.76376152038574</t>
   </si>
   <si>
     <t xml:space="preserve">9.81917476654053</t>
@@ -2744,19 +2744,19 @@
     <t xml:space="preserve">9.61968898773193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57535839080811</t>
+    <t xml:space="preserve">9.57535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">9.47192096710205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37217807769775</t>
+    <t xml:space="preserve">9.37217712402344</t>
   </si>
   <si>
     <t xml:space="preserve">9.56796932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48669719696045</t>
+    <t xml:space="preserve">9.48669815063477</t>
   </si>
   <si>
     <t xml:space="preserve">9.47561454772949</t>
@@ -2774,28 +2774,28 @@
     <t xml:space="preserve">8.75155258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70352649688721</t>
+    <t xml:space="preserve">8.70352745056152</t>
   </si>
   <si>
     <t xml:space="preserve">8.66658496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59639549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359413146973</t>
+    <t xml:space="preserve">8.59639644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359508514404</t>
   </si>
   <si>
     <t xml:space="preserve">8.86976718902588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88454246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76632881164551</t>
+    <t xml:space="preserve">8.81804847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88454341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76632976531982</t>
   </si>
   <si>
     <t xml:space="preserve">8.91779041290283</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">9.14313697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1135835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2982931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24288082122803</t>
+    <t xml:space="preserve">9.11358261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29829406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24287986755371</t>
   </si>
   <si>
     <t xml:space="preserve">9.2207145690918</t>
@@ -2819,10 +2819,10 @@
     <t xml:space="preserve">9.12466621398926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1209716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80327129364014</t>
+    <t xml:space="preserve">9.12097263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80327033996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.96951007843018</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">9.01753425598145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03969955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81435298919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82543563842773</t>
+    <t xml:space="preserve">9.03969860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81435394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82543659210205</t>
   </si>
   <si>
     <t xml:space="preserve">8.91040229797363</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">8.77371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39321422576904</t>
+    <t xml:space="preserve">8.39321517944336</t>
   </si>
   <si>
     <t xml:space="preserve">8.41907501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404071807861</t>
+    <t xml:space="preserve">8.50404167175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.721999168396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89193248748779</t>
+    <t xml:space="preserve">8.89193153381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.01383972167969</t>
@@ -2867,19 +2867,19 @@
     <t xml:space="preserve">9.14683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72312545776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95955371856689</t>
+    <t xml:space="preserve">9.72312641143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95955467224121</t>
   </si>
   <si>
     <t xml:space="preserve">9.94477844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0740737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3178911209106</t>
+    <t xml:space="preserve">10.0740747451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.317892074585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4398002624512</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">10.5136833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3954696655273</t>
+    <t xml:space="preserve">10.395468711853</t>
   </si>
   <si>
     <t xml:space="preserve">10.4952125549316</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">10.5062961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6245107650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7094774246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910057067871</t>
+    <t xml:space="preserve">10.6245098114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">10.5801792144775</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">10.6577577590942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7648897171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713171005249</t>
+    <t xml:space="preserve">10.7648906707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7131700515747</t>
   </si>
   <si>
     <t xml:space="preserve">10.6097326278687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5838737487793</t>
+    <t xml:space="preserve">10.5838747024536</t>
   </si>
   <si>
     <t xml:space="preserve">10.6060390472412</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">10.4065523147583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5358505249023</t>
+    <t xml:space="preserve">10.535849571228</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506258010864</t>
@@ -2939,22 +2939,22 @@
     <t xml:space="preserve">10.5617084503174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2624788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176349639893</t>
+    <t xml:space="preserve">10.2624778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176359176636</t>
   </si>
   <si>
     <t xml:space="preserve">10.6134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5764846801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.698392868042</t>
+    <t xml:space="preserve">10.5764856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6983938217163</t>
   </si>
   <si>
     <t xml:space="preserve">10.7464179992676</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">10.6392869949341</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6836175918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7168655395508</t>
+    <t xml:space="preserve">10.6836166381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7168645858765</t>
   </si>
   <si>
     <t xml:space="preserve">10.942211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8276920318604</t>
+    <t xml:space="preserve">10.8276901245117</t>
   </si>
   <si>
     <t xml:space="preserve">10.7205591201782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6429815292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4102458953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5321559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6946992874146</t>
+    <t xml:space="preserve">10.6429805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4102468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5321550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6947002410889</t>
   </si>
   <si>
     <t xml:space="preserve">11.0456485748291</t>
@@ -2996,16 +2996,16 @@
     <t xml:space="preserve">11.3929033279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4778690338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145553588867</t>
+    <t xml:space="preserve">11.4778699874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145544052124</t>
   </si>
   <si>
     <t xml:space="preserve">11.6884384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441097259521</t>
+    <t xml:space="preserve">11.6441078186035</t>
   </si>
   <si>
     <t xml:space="preserve">11.599778175354</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">11.6921319961548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6367216110229</t>
+    <t xml:space="preserve">11.6367206573486</t>
   </si>
   <si>
     <t xml:space="preserve">11.5665292739868</t>
@@ -3026,52 +3026,52 @@
     <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111179351807</t>
+    <t xml:space="preserve">11.5111169815063</t>
   </si>
   <si>
     <t xml:space="preserve">11.4815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4557037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000343322754</t>
+    <t xml:space="preserve">11.4557046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000352859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.6995220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4889516830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6958265304565</t>
+    <t xml:space="preserve">11.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6958274841309</t>
   </si>
   <si>
     <t xml:space="preserve">11.7290754318237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435964584351</t>
+    <t xml:space="preserve">11.8435955047607</t>
   </si>
   <si>
     <t xml:space="preserve">11.8768434524536</t>
   </si>
   <si>
-    <t xml:space="preserve">11.825122833252</t>
+    <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.1908502578735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2130155563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2795114517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3866415023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4900808334351</t>
+    <t xml:space="preserve">12.2130146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2795124053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3866424560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4900798797607</t>
   </si>
   <si>
     <t xml:space="preserve">12.4383592605591</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">12.3755588531494</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4568328857422</t>
+    <t xml:space="preserve">12.4568319320679</t>
   </si>
   <si>
     <t xml:space="preserve">12.3607816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4161949157715</t>
+    <t xml:space="preserve">12.4161968231201</t>
   </si>
   <si>
     <t xml:space="preserve">12.4125003814697</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">12.5048561096191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6045989990234</t>
+    <t xml:space="preserve">12.6045999526978</t>
   </si>
   <si>
     <t xml:space="preserve">12.6637058258057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5824327468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6600141525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858711242676</t>
+    <t xml:space="preserve">12.5824337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6600131988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858701705933</t>
   </si>
   <si>
     <t xml:space="preserve">12.6378479003906</t>
@@ -3128,25 +3128,25 @@
     <t xml:space="preserve">12.6230697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5787382125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6489295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4457483291626</t>
+    <t xml:space="preserve">12.5787391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265071868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4457492828369</t>
   </si>
   <si>
     <t xml:space="preserve">12.4679136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3977251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3275337219238</t>
+    <t xml:space="preserve">12.39772605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3275327682495</t>
   </si>
   <si>
     <t xml:space="preserve">12.5602684020996</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">12.4420547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5972118377686</t>
+    <t xml:space="preserve">12.5972108840942</t>
   </si>
   <si>
     <t xml:space="preserve">12.7228145599365</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8336410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631925582886</t>
+    <t xml:space="preserve">12.8336400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740200042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631935119629</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9592418670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331258773804</t>
+    <t xml:space="preserve">12.9592437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331268310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368223190308</t>
@@ -3191,31 +3191,31 @@
     <t xml:space="preserve">12.8890523910522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479021072388</t>
+    <t xml:space="preserve">13.0479040145874</t>
   </si>
   <si>
     <t xml:space="preserve">13.2438173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1184310913086</t>
+    <t xml:space="preserve">13.1184320449829</t>
   </si>
   <si>
     <t xml:space="preserve">12.9773731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910053253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2007160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2673282623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2829999923706</t>
+    <t xml:space="preserve">13.0910043716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2007169723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1772060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2673273086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887929916382</t>
@@ -3224,25 +3224,25 @@
     <t xml:space="preserve">13.5180978775024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4985065460205</t>
+    <t xml:space="preserve">13.4985055923462</t>
   </si>
   <si>
     <t xml:space="preserve">13.4632425308228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201402664185</t>
+    <t xml:space="preserve">13.4201412200928</t>
   </si>
   <si>
     <t xml:space="preserve">13.4318943023682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4514875411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102615356445</t>
+    <t xml:space="preserve">13.4397315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.451488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102605819702</t>
   </si>
   <si>
     <t xml:space="preserve">13.2359790802002</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">13.2712459564209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2320613861084</t>
+    <t xml:space="preserve">13.2320623397827</t>
   </si>
   <si>
     <t xml:space="preserve">13.0518207550049</t>
@@ -3266,22 +3266,22 @@
     <t xml:space="preserve">13.1732873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2477369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.373122215271</t>
+    <t xml:space="preserve">13.2477359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3731212615967</t>
   </si>
   <si>
     <t xml:space="preserve">13.3221826553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4358139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.196798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9852094650269</t>
+    <t xml:space="preserve">13.4358129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1967973709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9852085113525</t>
   </si>
   <si>
     <t xml:space="preserve">13.3261003494263</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">13.2634086608887</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1654510498047</t>
+    <t xml:space="preserve">13.1654500961304</t>
   </si>
   <si>
     <t xml:space="preserve">13.1145143508911</t>
@@ -3302,22 +3302,22 @@
     <t xml:space="preserve">12.7148485183716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8441524505615</t>
+    <t xml:space="preserve">12.8441514968872</t>
   </si>
   <si>
     <t xml:space="preserve">13.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1576166152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1301851272583</t>
+    <t xml:space="preserve">13.1576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1301870346069</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0674934387207</t>
+    <t xml:space="preserve">13.067494392395</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891290664673</t>
@@ -3332,13 +3332,13 @@
     <t xml:space="preserve">13.2947559356689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456916809082</t>
+    <t xml:space="preserve">13.3456926345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5690355300903</t>
+    <t xml:space="preserve">13.569034576416</t>
   </si>
   <si>
     <t xml:space="preserve">13.6160545349121</t>
@@ -3347,61 +3347,61 @@
     <t xml:space="preserve">13.5376892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5416069030762</t>
+    <t xml:space="preserve">13.5416078567505</t>
   </si>
   <si>
     <t xml:space="preserve">13.3770389556885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4436502456665</t>
+    <t xml:space="preserve">13.4436511993408</t>
   </si>
   <si>
     <t xml:space="preserve">13.4240579605103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.384877204895</t>
+    <t xml:space="preserve">13.3848762512207</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5337705612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5964632034302</t>
+    <t xml:space="preserve">13.5337715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5964641571045</t>
   </si>
   <si>
     <t xml:space="preserve">13.6121368408203</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5729541778564</t>
+    <t xml:space="preserve">13.5729532241821</t>
   </si>
   <si>
     <t xml:space="preserve">13.7414407730103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8393964767456</t>
+    <t xml:space="preserve">13.8393983840942</t>
   </si>
   <si>
     <t xml:space="preserve">13.9060096740723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6591548919678</t>
+    <t xml:space="preserve">13.6591558456421</t>
   </si>
   <si>
     <t xml:space="preserve">13.8315591812134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7923784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8824987411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0039672851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589868545532</t>
+    <t xml:space="preserve">13.7923765182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8824977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0039663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589878082275</t>
   </si>
   <si>
     <t xml:space="preserve">13.6748304367065</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">14.0901679992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2037992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3644495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956268310547</t>
+    <t xml:space="preserve">14.2037982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3644485473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956258773804</t>
   </si>
   <si>
     <t xml:space="preserve">14.3017549514771</t>
@@ -3425,16 +3425,16 @@
     <t xml:space="preserve">14.4349765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4114675521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4271411895752</t>
+    <t xml:space="preserve">14.4114665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4271402359009</t>
   </si>
   <si>
     <t xml:space="preserve">14.399712562561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6896677017212</t>
+    <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
     <t xml:space="preserve">14.564281463623</t>
@@ -3443,79 +3443,79 @@
     <t xml:space="preserve">14.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7288475036621</t>
+    <t xml:space="preserve">14.7288494110107</t>
   </si>
   <si>
     <t xml:space="preserve">14.8072156906128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8816595077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6622362136841</t>
+    <t xml:space="preserve">14.8816604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6622371673584</t>
   </si>
   <si>
     <t xml:space="preserve">14.6739940643311</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7249317169189</t>
+    <t xml:space="preserve">14.7249307632446</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9217462539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141277313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1185598373413</t>
+    <t xml:space="preserve">14.8494453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.921745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9538793563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141286849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1185579299927</t>
   </si>
   <si>
     <t xml:space="preserve">15.0663423538208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1346282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310247421265</t>
+    <t xml:space="preserve">15.1346263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310256958008</t>
   </si>
   <si>
     <t xml:space="preserve">15.247091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3234071731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2591438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3475074768066</t>
+    <t xml:space="preserve">15.3234081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2591409683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3475065231323</t>
   </si>
   <si>
     <t xml:space="preserve">15.2430753707886</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.279224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.38365650177</t>
+    <t xml:space="preserve">15.2511081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2792253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3836545944214</t>
   </si>
   <si>
     <t xml:space="preserve">15.3716087341309</t>
@@ -3524,22 +3524,22 @@
     <t xml:space="preserve">15.4559545516968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0743770599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418287277222</t>
+    <t xml:space="preserve">15.0743780136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418277740479</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887807846069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7811622619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7570638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168979644775</t>
+    <t xml:space="preserve">14.7811632156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7570657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168960571289</t>
   </si>
   <si>
     <t xml:space="preserve">14.1867036819458</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">14.299168586731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2429370880127</t>
+    <t xml:space="preserve">14.2429361343384</t>
   </si>
   <si>
     <t xml:space="preserve">14.564266204834</t>
@@ -3557,10 +3557,10 @@
     <t xml:space="preserve">14.4919681549072</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6124658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498615264893</t>
+    <t xml:space="preserve">14.6124649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498624801636</t>
   </si>
   <si>
     <t xml:space="preserve">15.0221605300903</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">14.861496925354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8213300704956</t>
+    <t xml:space="preserve">14.8213319778442</t>
   </si>
   <si>
     <t xml:space="preserve">14.6767311096191</t>
@@ -3587,31 +3587,31 @@
     <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9016609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623273849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060939788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9659271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671747207642</t>
+    <t xml:space="preserve">14.9016618728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060930252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9659261703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671737670898</t>
   </si>
   <si>
     <t xml:space="preserve">15.1788091659546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8333806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9177265167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8293609619141</t>
+    <t xml:space="preserve">14.8333787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9177293777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8293628692627</t>
   </si>
   <si>
     <t xml:space="preserve">14.9337949752808</t>
@@ -3629,22 +3629,22 @@
     <t xml:space="preserve">14.9257621765137</t>
   </si>
   <si>
-    <t xml:space="preserve">15.146674156189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0382251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3754854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847658157349</t>
+    <t xml:space="preserve">15.1466760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0382261276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627416610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3754863739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4999980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847639083862</t>
   </si>
   <si>
     <t xml:space="preserve">14.6727142333984</t>
@@ -3653,19 +3653,19 @@
     <t xml:space="preserve">14.9940462112427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7369794845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9819955825806</t>
+    <t xml:space="preserve">14.7369804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9819946289062</t>
   </si>
   <si>
     <t xml:space="preserve">14.957896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7450151443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270088195801</t>
+    <t xml:space="preserve">14.7450132369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270069122314</t>
   </si>
   <si>
     <t xml:space="preserve">14.893630027771</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">14.5562324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.596399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0300559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.371467590332</t>
+    <t xml:space="preserve">14.5963973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0300550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714666366577</t>
   </si>
   <si>
     <t xml:space="preserve">13.9256219863892</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">13.7770090103149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379495620728</t>
+    <t xml:space="preserve">13.0379505157471</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447366714478</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">12.993766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243762969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4958438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1746530532837</t>
+    <t xml:space="preserve">13.6243753433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4958448410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.174654006958</t>
   </si>
   <si>
     <t xml:space="preserve">14.3875341415405</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">15.0824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0502767562866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1667575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3153743743896</t>
+    <t xml:space="preserve">15.0502786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1667604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3153734207153</t>
   </si>
   <si>
     <t xml:space="preserve">15.6005544662476</t>
@@ -3734,58 +3734,58 @@
     <t xml:space="preserve">16.1789455413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8495855331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1628799438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6850433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3074779510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.235179901123</t>
+    <t xml:space="preserve">15.8495826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1628818511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6850414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9581718444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3074798583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2351779937744</t>
   </si>
   <si>
     <t xml:space="preserve">16.0504150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523548126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7331027984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6166210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4840707778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.411771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4760389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9980621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7932138442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080318450928</t>
+    <t xml:space="preserve">15.5523567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7331008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6166219711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.484073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4117727279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.476037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9980611801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7932147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080337524414</t>
   </si>
   <si>
     <t xml:space="preserve">14.5441827774048</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4598340988159</t>
+    <t xml:space="preserve">14.4598331451416</t>
   </si>
   <si>
     <t xml:space="preserve">14.5401668548584</t>
@@ -3794,31 +3794,31 @@
     <t xml:space="preserve">14.4196681976318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7048473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6204996109009</t>
+    <t xml:space="preserve">14.7048482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204986572266</t>
   </si>
   <si>
     <t xml:space="preserve">14.4518013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2469549179077</t>
+    <t xml:space="preserve">14.2469530105591</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268695831299</t>
+    <t xml:space="preserve">14.2268686294556</t>
   </si>
   <si>
     <t xml:space="preserve">14.2670364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947364807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3112192153931</t>
+    <t xml:space="preserve">14.1947374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3112182617188</t>
   </si>
   <si>
     <t xml:space="preserve">14.4558181762695</t>
@@ -3827,13 +3827,13 @@
     <t xml:space="preserve">14.8871431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7547540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8230848312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8828706741333</t>
+    <t xml:space="preserve">14.7547550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8230838775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8828716278076</t>
   </si>
   <si>
     <t xml:space="preserve">14.5882034301758</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430065155029</t>
+    <t xml:space="preserve">14.4430046081543</t>
   </si>
   <si>
     <t xml:space="preserve">14.3789463043213</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">14.2764539718628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4643564224243</t>
+    <t xml:space="preserve">14.4643573760986</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344388961792</t>
+    <t xml:space="preserve">13.3924493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">13.336932182312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5803537368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3967208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2557916641235</t>
+    <t xml:space="preserve">13.5803527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3967199325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2557926177979</t>
   </si>
   <si>
     <t xml:space="preserve">13.1917333602905</t>
@@ -3899,19 +3899,19 @@
     <t xml:space="preserve">13.6828479766846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2686033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4266147613525</t>
+    <t xml:space="preserve">13.2686042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4266138076782</t>
   </si>
   <si>
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2942276000977</t>
+    <t xml:space="preserve">13.0038290023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2942266464233</t>
   </si>
   <si>
     <t xml:space="preserve">13.1661100387573</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568538665771</t>
+    <t xml:space="preserve">12.9568529129028</t>
   </si>
   <si>
     <t xml:space="preserve">12.995288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7774896621704</t>
+    <t xml:space="preserve">12.7774906158447</t>
   </si>
   <si>
     <t xml:space="preserve">12.3547058105469</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">12.4401159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4230346679688</t>
+    <t xml:space="preserve">12.4230337142944</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">12.1838836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1625299453735</t>
+    <t xml:space="preserve">12.1625308990479</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095069885254</t>
@@ -3962,16 +3962,16 @@
     <t xml:space="preserve">12.4273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796131134033</t>
+    <t xml:space="preserve">12.1796140670776</t>
   </si>
   <si>
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333530426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4571990966797</t>
+    <t xml:space="preserve">12.3333520889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4571981430054</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134323120117</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">12.4700107574463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.534068107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6408319473267</t>
+    <t xml:space="preserve">12.5340690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.640832901001</t>
   </si>
   <si>
     <t xml:space="preserve">12.8458185195923</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">13.0508050918579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191329956055</t>
+    <t xml:space="preserve">13.1191339492798</t>
   </si>
   <si>
     <t xml:space="preserve">13.2258977890015</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">13.1618394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8970651626587</t>
+    <t xml:space="preserve">12.897066116333</t>
   </si>
   <si>
     <t xml:space="preserve">12.7646780014038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7006196975708</t>
+    <t xml:space="preserve">12.7006206512451</t>
   </si>
   <si>
     <t xml:space="preserve">12.8757123947144</t>
@@ -4025,16 +4025,16 @@
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579141616821</t>
+    <t xml:space="preserve">12.6579151153564</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3931407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8330059051514</t>
+    <t xml:space="preserve">12.3931398391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8330068588257</t>
   </si>
   <si>
     <t xml:space="preserve">12.4828224182129</t>
@@ -4046,25 +4046,25 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7689485549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1703805923462</t>
+    <t xml:space="preserve">12.768949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1703815460205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9696645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.089241027832</t>
+    <t xml:space="preserve">13.0892400741577</t>
   </si>
   <si>
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7048902511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7390546798706</t>
+    <t xml:space="preserve">12.704891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7390556335449</t>
   </si>
   <si>
     <t xml:space="preserve">12.3248119354248</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">12.4443864822388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1411790847778</t>
+    <t xml:space="preserve">12.1411781311035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0173320770264</t>
@@ -4091,25 +4091,25 @@
     <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8550519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.73974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575433731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447326660156</t>
+    <t xml:space="preserve">11.8550510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7397451400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447317123413</t>
   </si>
   <si>
     <t xml:space="preserve">11.7909927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0045204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1582593917847</t>
+    <t xml:space="preserve">12.0045213699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.158260345459</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991876602173</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">12.3632469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5169858932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3376235961914</t>
+    <t xml:space="preserve">12.5169868469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3376226425171</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749973297119</t>
@@ -4136,16 +4136,16 @@
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.973934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0977821350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.153299331665</t>
+    <t xml:space="preserve">12.9739351272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0251817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1532983779907</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
@@ -4175,19 +4175,19 @@
     <t xml:space="preserve">14.7419443130493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796632766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5027923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600868225098</t>
+    <t xml:space="preserve">14.579662322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5027933120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686279296875</t>
+    <t xml:space="preserve">14.4686298370361</t>
   </si>
   <si>
     <t xml:space="preserve">14.6266384124756</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">14.7163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7035093307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6992378234863</t>
+    <t xml:space="preserve">14.7035083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.699236869812</t>
   </si>
   <si>
     <t xml:space="preserve">14.7931909561157</t>
@@ -4208,22 +4208,22 @@
     <t xml:space="preserve">14.6906976699829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7889194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7462139129639</t>
+    <t xml:space="preserve">14.7889204025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7462129592896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8999538421631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8444366455078</t>
+    <t xml:space="preserve">14.8444356918335</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928201675415</t>
+    <t xml:space="preserve">14.0928192138672</t>
   </si>
   <si>
     <t xml:space="preserve">14.2508296966553</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">14.3490524291992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3106184005737</t>
+    <t xml:space="preserve">14.3106174468994</t>
   </si>
   <si>
     <t xml:space="preserve">14.2593717575073</t>
@@ -4250,13 +4250,13 @@
     <t xml:space="preserve">14.1910419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3276996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917589187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504844665527</t>
+    <t xml:space="preserve">14.3277006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504854202271</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
@@ -4271,16 +4271,16 @@
     <t xml:space="preserve">14.8615188598633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8487071990967</t>
+    <t xml:space="preserve">14.848708152771</t>
   </si>
   <si>
     <t xml:space="preserve">14.9554719924927</t>
   </si>
   <si>
-    <t xml:space="preserve">14.968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8358974456787</t>
+    <t xml:space="preserve">14.9682836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8358964920044</t>
   </si>
   <si>
     <t xml:space="preserve">15.168999671936</t>
@@ -4289,79 +4289,79 @@
     <t xml:space="preserve">15.2373285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3013868331909</t>
+    <t xml:space="preserve">15.3013877868652</t>
   </si>
   <si>
     <t xml:space="preserve">15.2586803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2971153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270092010498</t>
+    <t xml:space="preserve">15.2971162796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270101547241</t>
   </si>
   <si>
     <t xml:space="preserve">15.3825263977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.28857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5021018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.416690826416</t>
+    <t xml:space="preserve">15.2885751724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319948196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166898727417</t>
   </si>
   <si>
     <t xml:space="preserve">15.4679374694824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4636669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063734054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5618886947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.600323677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686525344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473016738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.685736656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850196838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106430053711</t>
+    <t xml:space="preserve">15.4636659622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5618877410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5875120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106420516968</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9804019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266630172729</t>
+    <t xml:space="preserve">15.9804029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266639709473</t>
   </si>
   <si>
     <t xml:space="preserve">15.8223934173584</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">16.0231094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.027379989624</t>
+    <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.0658149719238</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">15.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7327108383179</t>
+    <t xml:space="preserve">15.7327117919922</t>
   </si>
   <si>
     <t xml:space="preserve">15.2031631469727</t>
@@ -4391,25 +4391,25 @@
     <t xml:space="preserve">15.7540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8316259384155</t>
+    <t xml:space="preserve">14.8316249847412</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4508543014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081516265869</t>
+    <t xml:space="preserve">15.0451536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.450855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.1092128753662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2501392364502</t>
+    <t xml:space="preserve">15.2501401901245</t>
   </si>
   <si>
     <t xml:space="preserve">15.4423131942749</t>
@@ -4418,25 +4418,25 @@
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985454559326</t>
+    <t xml:space="preserve">15.6985464096069</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.621678352356</t>
+    <t xml:space="preserve">15.6216773986816</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437452316284</t>
+    <t xml:space="preserve">15.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0914402008057</t>
+    <t xml:space="preserve">16.091438293457</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683082580566</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">16.0401916503906</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1384143829346</t>
+    <t xml:space="preserve">16.1384162902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.2836132049561</t>
@@ -4454,10 +4454,10 @@
     <t xml:space="preserve">16.3049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3092365264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3434028625488</t>
+    <t xml:space="preserve">16.3092346191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3434009552002</t>
   </si>
   <si>
     <t xml:space="preserve">16.219554901123</t>
@@ -4469,37 +4469,37 @@
     <t xml:space="preserve">16.2323665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1256008148193</t>
+    <t xml:space="preserve">16.125602722168</t>
   </si>
   <si>
     <t xml:space="preserve">15.8693695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9334297180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8053112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2067432403564</t>
+    <t xml:space="preserve">15.9334278106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8053102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2067451477051</t>
   </si>
   <si>
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890721321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1127891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0316505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9120740890503</t>
+    <t xml:space="preserve">15.8907222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1127910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0316524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.912073135376</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -71120,7 +71120,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6495717593</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>2531949</v>
@@ -71141,6 +71141,32 @@
         <v>2009</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494907407</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>3553283</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>32.3300018310547</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>31.7600002288818</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>32.2799987792969</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>31.9300003051758</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1963</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="2010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="2011">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21389961242676</t>
+    <t xml:space="preserve">9.21390151977539</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31058979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13427448272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11721229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02052211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88970756530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06602096557617</t>
+    <t xml:space="preserve">9.31058883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13427257537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11720943450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02052307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76457977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8897066116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0660228729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.95795917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75889301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376522064209</t>
+    <t xml:space="preserve">8.75889205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376426696777</t>
   </si>
   <si>
     <t xml:space="preserve">8.29251003265381</t>
@@ -83,43 +83,43 @@
     <t xml:space="preserve">8.44607639312744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48588943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30957317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04794311523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93988037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568689346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84318876266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41662073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23461771011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15499210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161317825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74548387527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47248029708862</t>
+    <t xml:space="preserve">8.48588752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30957412719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04794406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93987894058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568593978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662168502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23461818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1549916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161365509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74548578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47248077392578</t>
   </si>
   <si>
     <t xml:space="preserve">6.81373643875122</t>
@@ -134,109 +134,109 @@
     <t xml:space="preserve">6.59760808944702</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62035799026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392244338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72842121124268</t>
+    <t xml:space="preserve">6.62035703659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72842168807983</t>
   </si>
   <si>
     <t xml:space="preserve">6.6601710319519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89905071258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89336156845093</t>
+    <t xml:space="preserve">6.89905023574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89336204528809</t>
   </si>
   <si>
     <t xml:space="preserve">6.95592594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26305532455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28580617904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643329620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45074558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680816650391</t>
+    <t xml:space="preserve">7.26305675506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28580665588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643377304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4507474899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680864334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.24599313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249540328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37111949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750247955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79200124740601</t>
+    <t xml:space="preserve">7.3199315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249492645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37112092971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575265884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79200172424316</t>
   </si>
   <si>
     <t xml:space="preserve">7.87731599807739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89437913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67256164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587432861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037166595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543130874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42799615859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48487091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41093349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286931991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755456924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98436307907104</t>
+    <t xml:space="preserve">7.89438009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4279956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48487186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41093254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30286884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755504608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9843635559082</t>
   </si>
   <si>
     <t xml:space="preserve">7.00711441040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85354995727539</t>
+    <t xml:space="preserve">6.85354948043823</t>
   </si>
   <si>
     <t xml:space="preserve">7.05261516571045</t>
@@ -245,61 +245,61 @@
     <t xml:space="preserve">7.13792991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16067981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43368291854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49624681472778</t>
+    <t xml:space="preserve">7.16067886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43368244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4962477684021</t>
   </si>
   <si>
     <t xml:space="preserve">7.47918367385864</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54743528366089</t>
+    <t xml:space="preserve">7.54743576049805</t>
   </si>
   <si>
     <t xml:space="preserve">7.59862279891968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75218820571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631353378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456562042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8033766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77493906021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018661499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35405683517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53605937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105230331421</t>
+    <t xml:space="preserve">7.75218963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181476593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456514358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80337715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77493953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39386987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35405778884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53606081008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105278015137</t>
   </si>
   <si>
     <t xml:space="preserve">7.16636657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05830144882202</t>
+    <t xml:space="preserve">7.05830192565918</t>
   </si>
   <si>
     <t xml:space="preserve">7.11517810821533</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">7.31798839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73994779586792</t>
+    <t xml:space="preserve">7.73994874954224</t>
   </si>
   <si>
     <t xml:space="preserve">7.8484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90873241424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.944899559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85447978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228351593018</t>
+    <t xml:space="preserve">7.90873289108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94490098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85448026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228542327881</t>
   </si>
   <si>
     <t xml:space="preserve">7.76406097412109</t>
@@ -335,112 +335,112 @@
     <t xml:space="preserve">7.54705238342285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.534996509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625534057617</t>
+    <t xml:space="preserve">7.53499603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6615834236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625438690186</t>
   </si>
   <si>
     <t xml:space="preserve">7.7700891494751</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42046499252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17934465408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97439289093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40840816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54102373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58322095870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02498292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11841726303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26308870315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187236785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25103378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13047218322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91647863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92853498458862</t>
+    <t xml:space="preserve">7.42046594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17934370040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850416183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92014074325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40840911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54102420806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58257341384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02498340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11841678619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26308917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953664779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43187379837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25103282928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13047313690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91647911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92853546142578</t>
   </si>
   <si>
     <t xml:space="preserve">6.38967752456665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43790054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7634129524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69710493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87191581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560970306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84780502319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77546882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73327207565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68504858016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81163692474365</t>
+    <t xml:space="preserve">6.43790149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76341342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69710540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87191772460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560922622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8417763710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8478045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7754693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73327255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68504905700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81163644790649</t>
   </si>
   <si>
     <t xml:space="preserve">6.62476921081543</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">7.10098075866699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07083940505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79355239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06481266021729</t>
+    <t xml:space="preserve">7.07084035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79355192184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06481218338013</t>
   </si>
   <si>
     <t xml:space="preserve">7.20948505401611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29387664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000177383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808439254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04070091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01658868789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8176646232605</t>
+    <t xml:space="preserve">7.29387617111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0828971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73930215835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04070138931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766557693481</t>
   </si>
   <si>
     <t xml:space="preserve">6.74532842636108</t>
@@ -497,43 +497,43 @@
     <t xml:space="preserve">6.61271286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78149700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247646331787</t>
+    <t xml:space="preserve">6.78149747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247741699219</t>
   </si>
   <si>
     <t xml:space="preserve">6.93822479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88397121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523290634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313358306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72724533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79958009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75135707855225</t>
+    <t xml:space="preserve">6.88397169113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98042011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72724485397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79957962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75135517120361</t>
   </si>
   <si>
     <t xml:space="preserve">6.59462881088257</t>
@@ -542,88 +542,88 @@
     <t xml:space="preserve">6.56448936462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57654476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668516159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5464038848877</t>
+    <t xml:space="preserve">6.57654428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54640531539917</t>
   </si>
   <si>
     <t xml:space="preserve">6.51626491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49818086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7694411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18537378311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16728925704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26976490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33004283905029</t>
+    <t xml:space="preserve">6.4981803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76944017410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18537282943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16728830337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742870330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2697639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33004426956177</t>
   </si>
   <si>
     <t xml:space="preserve">7.31196069717407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14317655563354</t>
+    <t xml:space="preserve">7.14317798614502</t>
   </si>
   <si>
     <t xml:space="preserve">7.09495306015015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98644781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07686805725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87794399261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02261590957642</t>
+    <t xml:space="preserve">6.98644876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08892488479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07686853408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8779444694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0226149559021</t>
   </si>
   <si>
     <t xml:space="preserve">6.82369327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43854808807373</t>
+    <t xml:space="preserve">7.43854856491089</t>
   </si>
   <si>
     <t xml:space="preserve">7.35415649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7339186668396</t>
+    <t xml:space="preserve">7.73392009735107</t>
   </si>
   <si>
     <t xml:space="preserve">8.30055332183838</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">8.45125198364258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47536468505859</t>
+    <t xml:space="preserve">8.47536373138428</t>
   </si>
   <si>
     <t xml:space="preserve">8.41508483886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33069133758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54167079925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55975723266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63811874389648</t>
+    <t xml:space="preserve">8.33069229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.541672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5597562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63812065124512</t>
   </si>
   <si>
     <t xml:space="preserve">8.5838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59592437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66223239898682</t>
+    <t xml:space="preserve">8.59592533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6622314453125</t>
   </si>
   <si>
     <t xml:space="preserve">8.6682596206665</t>
@@ -668,67 +668,67 @@
     <t xml:space="preserve">8.5537281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50550270080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51153182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017604827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71045398712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75265312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69840049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71648406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52358722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4874210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38494491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25835514068604</t>
+    <t xml:space="preserve">8.5055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5115327835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71045589447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75265121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69839859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7164831161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52358818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48741912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38494396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25835609436035</t>
   </si>
   <si>
     <t xml:space="preserve">8.23424434661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16793537139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27041244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26438426971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58989524841309</t>
+    <t xml:space="preserve">8.16793441772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27041339874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26438331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5898962020874</t>
   </si>
   <si>
     <t xml:space="preserve">9.2951717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42175960540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28311634063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98774337768555</t>
+    <t xml:space="preserve">9.38559150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4217586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28311538696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98774433135986</t>
   </si>
   <si>
     <t xml:space="preserve">8.88526821136475</t>
@@ -737,46 +737,46 @@
     <t xml:space="preserve">8.84910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00582599639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993869781494</t>
+    <t xml:space="preserve">9.00582790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993965148926</t>
   </si>
   <si>
     <t xml:space="preserve">8.81896018981934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77073574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67428684234619</t>
+    <t xml:space="preserve">8.77073669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67428779602051</t>
   </si>
   <si>
     <t xml:space="preserve">8.74059581756592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90335178375244</t>
+    <t xml:space="preserve">8.90335369110107</t>
   </si>
   <si>
     <t xml:space="preserve">9.04802417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87924003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90937995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95760440826416</t>
+    <t xml:space="preserve">8.87923812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90937900543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95760345458984</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81293106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74662399291992</t>
+    <t xml:space="preserve">8.81293201446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74662303924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.65620422363281</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">8.49947643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14985179901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27643871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54769992828369</t>
+    <t xml:space="preserve">8.14985275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54770088195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.46330833435059</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">8.56578350067139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78882026672363</t>
+    <t xml:space="preserve">8.78881931304932</t>
   </si>
   <si>
     <t xml:space="preserve">8.80087566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79484748840332</t>
+    <t xml:space="preserve">8.794846534729</t>
   </si>
   <si>
     <t xml:space="preserve">8.78279209136963</t>
@@ -815,85 +815,85 @@
     <t xml:space="preserve">8.86718368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98171520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80690383911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6320915222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60797882080078</t>
+    <t xml:space="preserve">8.98171615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80690479278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63209056854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6079797744751</t>
   </si>
   <si>
     <t xml:space="preserve">8.46933650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36083316802979</t>
+    <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
     <t xml:space="preserve">8.93349170684814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75868129730225</t>
+    <t xml:space="preserve">8.75868034362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.87321186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04199409484863</t>
+    <t xml:space="preserve">9.04199600219727</t>
   </si>
   <si>
     <t xml:space="preserve">9.1926965713501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21077919006348</t>
+    <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
     <t xml:space="preserve">9.24091911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21680736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94554805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89129734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03596687316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07213497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12035942077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33675289154053</t>
+    <t xml:space="preserve">9.2168083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94554710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89129638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03596782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07213687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12036037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30493068695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33675479888916</t>
   </si>
   <si>
     <t xml:space="preserve">9.18400573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15854740142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13308906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851779937744</t>
+    <t xml:space="preserve">9.15854644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13309001922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851875305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.83395671844482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94215393066406</t>
+    <t xml:space="preserve">8.94215297698975</t>
   </si>
   <si>
     <t xml:space="preserve">9.03762054443359</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">8.75758171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73848724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89123725891113</t>
+    <t xml:space="preserve">8.73848915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89123630523682</t>
   </si>
   <si>
     <t xml:space="preserve">8.95488262176514</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">9.05035018920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22855758666992</t>
+    <t xml:space="preserve">9.22855567932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.2349214553833</t>
@@ -929,94 +929,94 @@
     <t xml:space="preserve">9.28583717346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29856491088867</t>
+    <t xml:space="preserve">9.2985668182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.19036960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34948253631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25401496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24765110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29220294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33038806915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38130569458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57860469818115</t>
+    <t xml:space="preserve">9.3494815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25401401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219276428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24764919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29220199584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33038902282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38130474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57860565185547</t>
   </si>
   <si>
     <t xml:space="preserve">9.54678249359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54041862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64861392974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79500007629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85864448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68680191040039</t>
+    <t xml:space="preserve">9.5404167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64861488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79499816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85864543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862602233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68680286407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.56587600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52768993377686</t>
+    <t xml:space="preserve">9.52768898010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.75681209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77590560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136489868164</t>
+    <t xml:space="preserve">9.77590465545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136299133301</t>
   </si>
   <si>
     <t xml:space="preserve">10.0750370025635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0877685546875</t>
+    <t xml:space="preserve">10.0877676010132</t>
   </si>
   <si>
     <t xml:space="preserve">10.1386823654175</t>
   </si>
   <si>
-    <t xml:space="preserve">10.23415184021</t>
+    <t xml:space="preserve">10.2341527938843</t>
   </si>
   <si>
     <t xml:space="preserve">10.1959648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.062310218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0050277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82682132720947</t>
+    <t xml:space="preserve">10.0623092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0050287246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82682228088379</t>
   </si>
   <si>
     <t xml:space="preserve">9.86500930786133</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">9.82045745849609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87137317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78226947784424</t>
+    <t xml:space="preserve">9.87137413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78227043151855</t>
   </si>
   <si>
     <t xml:space="preserve">9.71226024627686</t>
@@ -1040,31 +1040,31 @@
     <t xml:space="preserve">9.69953155517578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6804370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6931676864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134548187256</t>
+    <t xml:space="preserve">9.68043804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69316673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134452819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.53405380249023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52132511138916</t>
+    <t xml:space="preserve">9.52132415771484</t>
   </si>
   <si>
     <t xml:space="preserve">9.57223987579346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61679267883301</t>
+    <t xml:space="preserve">9.61679172515869</t>
   </si>
   <si>
     <t xml:space="preserve">9.67407321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62952041625977</t>
+    <t xml:space="preserve">9.62952136993408</t>
   </si>
   <si>
     <t xml:space="preserve">9.59769916534424</t>
@@ -1079,70 +1079,70 @@
     <t xml:space="preserve">9.75044822692871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89683151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91592502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87773895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0304861068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1323175430298</t>
+    <t xml:space="preserve">9.89683246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91592407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87773990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686750411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1323194503784</t>
   </si>
   <si>
     <t xml:space="preserve">9.93501853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84591484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85227966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83318710327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72498798370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9986629486084</t>
+    <t xml:space="preserve">9.84591579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85228061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72498989105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99866390228271</t>
   </si>
   <si>
     <t xml:space="preserve">9.96047592163086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0177574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9541130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1259546279907</t>
+    <t xml:space="preserve">10.0177583694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95411205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1259536743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0241212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94138240814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8841028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0368509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78863334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63588714599609</t>
+    <t xml:space="preserve">9.94138431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88410091400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0368499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78863430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.58497047424316</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">9.61042785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66770935058594</t>
+    <t xml:space="preserve">9.66770839691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.74408340454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73135471343994</t>
+    <t xml:space="preserve">9.73135375976562</t>
   </si>
   <si>
     <t xml:space="preserve">9.8077278137207</t>
@@ -1166,49 +1166,49 @@
     <t xml:space="preserve">9.73771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589542388916</t>
+    <t xml:space="preserve">9.70589733123779</t>
   </si>
   <si>
     <t xml:space="preserve">9.5595121383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47677230834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97320652008057</t>
+    <t xml:space="preserve">9.47677421569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97320556640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.97957038879395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0814027786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0559434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.291431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3041620254517</t>
+    <t xml:space="preserve">10.0814037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.055944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2914323806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3041610717773</t>
   </si>
   <si>
     <t xml:space="preserve">10.2023286819458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3105249404907</t>
+    <t xml:space="preserve">10.310525894165</t>
   </si>
   <si>
     <t xml:space="preserve">10.3232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736869812012</t>
+    <t xml:space="preserve">10.1736879348755</t>
   </si>
   <si>
     <t xml:space="preserve">10.1641407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1482305526733</t>
+    <t xml:space="preserve">10.1482286453247</t>
   </si>
   <si>
     <t xml:space="preserve">9.99229907989502</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">9.86819171905518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81727409362793</t>
+    <t xml:space="preserve">9.81727504730225</t>
   </si>
   <si>
     <t xml:space="preserve">9.77908706665039</t>
@@ -1238,31 +1238,31 @@
     <t xml:space="preserve">9.6517972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85546112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74726390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0082111358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98593330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92865467071533</t>
+    <t xml:space="preserve">9.8554630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74726581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0082101821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98593425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92865371704102</t>
   </si>
   <si>
     <t xml:space="preserve">9.94456481933594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97002410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0495796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1609573364258</t>
+    <t xml:space="preserve">9.9700231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0495805740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1609582901001</t>
   </si>
   <si>
     <t xml:space="preserve">10.3137073516846</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">10.4346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5301008224487</t>
+    <t xml:space="preserve">10.530101776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.638298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7655897140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8546934127808</t>
+    <t xml:space="preserve">10.765588760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8546924591064</t>
   </si>
   <si>
     <t xml:space="preserve">10.6319341659546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7178564071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5841999053955</t>
+    <t xml:space="preserve">10.7178544998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5841989517212</t>
   </si>
   <si>
     <t xml:space="preserve">10.6542100906372</t>
@@ -1313,37 +1313,37 @@
     <t xml:space="preserve">10.5269193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5396490097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4409980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5014619827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078248977661</t>
+    <t xml:space="preserve">10.5396480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4409990310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5014600753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078258514404</t>
   </si>
   <si>
     <t xml:space="preserve">10.2977962493896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.332802772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2596111297607</t>
+    <t xml:space="preserve">10.3328008651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2596101760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.2864847183228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2528915405273</t>
+    <t xml:space="preserve">10.252890586853</t>
   </si>
   <si>
     <t xml:space="preserve">10.1319522857666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0143737792969</t>
+    <t xml:space="preserve">10.0143728256226</t>
   </si>
   <si>
     <t xml:space="preserve">9.99421691894531</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">9.49702644348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55413627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77585506439209</t>
+    <t xml:space="preserve">9.5541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77585601806641</t>
   </si>
   <si>
     <t xml:space="preserve">9.88335704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86991882324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65491676330566</t>
+    <t xml:space="preserve">9.86991786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65491771697998</t>
   </si>
   <si>
     <t xml:space="preserve">9.67843341827393</t>
@@ -1385,37 +1385,37 @@
     <t xml:space="preserve">9.78257369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9001522064209</t>
+    <t xml:space="preserve">9.90015411376953</t>
   </si>
   <si>
     <t xml:space="preserve">9.80609130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76241779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82960605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69858837127686</t>
+    <t xml:space="preserve">9.76241683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8296070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69858932495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.76913642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60116767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61796379089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52390098571777</t>
+    <t xml:space="preserve">9.60116672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61796474456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52390003204346</t>
   </si>
   <si>
     <t xml:space="preserve">9.51718139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61124515533447</t>
+    <t xml:space="preserve">9.61124610900879</t>
   </si>
   <si>
     <t xml:space="preserve">9.59108829498291</t>
@@ -1424,28 +1424,28 @@
     <t xml:space="preserve">9.80945014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77249526977539</t>
+    <t xml:space="preserve">9.77249717712402</t>
   </si>
   <si>
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6515588760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163635253906</t>
+    <t xml:space="preserve">9.65155792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163730621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84976196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85648155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81616973876953</t>
+    <t xml:space="preserve">9.84976291656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85648250579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81616878509521</t>
   </si>
   <si>
     <t xml:space="preserve">9.74898052215576</t>
@@ -1460,34 +1460,34 @@
     <t xml:space="preserve">9.92366886138916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97070026397705</t>
+    <t xml:space="preserve">9.97070121765137</t>
   </si>
   <si>
     <t xml:space="preserve">10.0479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2125787734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.111795425415</t>
+    <t xml:space="preserve">10.2125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1117963790894</t>
   </si>
   <si>
     <t xml:space="preserve">9.9539041519165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0378875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0009365081787</t>
+    <t xml:space="preserve">10.0378885269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0009355545044</t>
   </si>
   <si>
     <t xml:space="preserve">10.0681238174438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748434066772</t>
+    <t xml:space="preserve">10.0916395187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748414993286</t>
   </si>
   <si>
     <t xml:space="preserve">9.8665599822998</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">9.71202659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73218250274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312271118164</t>
+    <t xml:space="preserve">9.7321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312175750732</t>
   </si>
   <si>
     <t xml:space="preserve">9.92702865600586</t>
@@ -1520,31 +1520,31 @@
     <t xml:space="preserve">9.93710708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96062278747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94382572174072</t>
+    <t xml:space="preserve">9.96062183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94382476806641</t>
   </si>
   <si>
     <t xml:space="preserve">10.1621866226196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1017169952393</t>
+    <t xml:space="preserve">10.1017179489136</t>
   </si>
   <si>
     <t xml:space="preserve">10.0882806777954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1554670333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1722660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1823425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2965621948242</t>
+    <t xml:space="preserve">10.1554679870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1722650527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1823434829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2965631484985</t>
   </si>
   <si>
     <t xml:space="preserve">10.4141426086426</t>
@@ -1553,25 +1553,25 @@
     <t xml:space="preserve">10.4309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3704681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99757671356201</t>
+    <t xml:space="preserve">10.3704700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9975757598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.88671684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96734046936035</t>
+    <t xml:space="preserve">9.96734237670898</t>
   </si>
   <si>
     <t xml:space="preserve">9.93038749694824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70866680145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69187164306641</t>
+    <t xml:space="preserve">9.70866870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">9.59444808959961</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">9.50038528442383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61460590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56421375274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41304111480713</t>
+    <t xml:space="preserve">9.61460494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56421279907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41304206848145</t>
   </si>
   <si>
     <t xml:space="preserve">9.43991565704346</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">9.40968227386475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.288743019104</t>
+    <t xml:space="preserve">9.28874206542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.2383508682251</t>
@@ -1610,88 +1610,88 @@
     <t xml:space="preserve">9.53397846221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66499614715576</t>
+    <t xml:space="preserve">9.66499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.62468338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65827655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835498809814</t>
+    <t xml:space="preserve">9.65827751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835403442383</t>
   </si>
   <si>
     <t xml:space="preserve">9.63476085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57429122924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71538734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51382350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59780788421631</t>
+    <t xml:space="preserve">9.57429313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71538543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51382160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59780693054199</t>
   </si>
   <si>
     <t xml:space="preserve">9.5574951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57765197753906</t>
+    <t xml:space="preserve">9.57765007019043</t>
   </si>
   <si>
     <t xml:space="preserve">9.81952857971191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87663841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91359043121338</t>
+    <t xml:space="preserve">9.87663650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9135913848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.0042963027954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.084921836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97405910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57093143463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64483833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515300750732</t>
+    <t xml:space="preserve">10.0849208831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97406005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57093238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64484024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515205383301</t>
   </si>
   <si>
     <t xml:space="preserve">9.74562072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89679431915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85984039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95054531097412</t>
+    <t xml:space="preserve">9.89679336547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85984134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9505443572998</t>
   </si>
   <si>
     <t xml:space="preserve">10.021092414856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0446071624756</t>
+    <t xml:space="preserve">10.0446090698242</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647640228271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327327728271</t>
+    <t xml:space="preserve">10.2327337265015</t>
   </si>
   <si>
     <t xml:space="preserve">10.3267974853516</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">10.2898445129395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.333517074585</t>
+    <t xml:space="preserve">10.3335161209106</t>
   </si>
   <si>
     <t xml:space="preserve">10.3133602142334</t>
@@ -1712,31 +1712,31 @@
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771886825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2764072418213</t>
+    <t xml:space="preserve">10.3771877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.276406288147</t>
   </si>
   <si>
     <t xml:space="preserve">10.1991405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2461729049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932024002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714826583862</t>
+    <t xml:space="preserve">10.2461738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932043075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714817047119</t>
   </si>
   <si>
     <t xml:space="preserve">10.1285924911499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2831249237061</t>
+    <t xml:space="preserve">10.2058582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2831258773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1890621185303</t>
@@ -1748,28 +1748,28 @@
     <t xml:space="preserve">10.2260160446167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730474472046</t>
+    <t xml:space="preserve">10.2730464935303</t>
   </si>
   <si>
     <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4275798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4342975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5451593399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6728162765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660976409912</t>
+    <t xml:space="preserve">10.4275817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4342966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5451574325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
     <t xml:space="preserve">10.7400035858154</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">10.5653142929077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6157064437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.62242603302</t>
+    <t xml:space="preserve">10.6157054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5921907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6224250793457</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534408569336</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725841522217</t>
+    <t xml:space="preserve">11.0725831985474</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591468811035</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">11.0322723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0692262649536</t>
+    <t xml:space="preserve">11.069224357605</t>
   </si>
   <si>
     <t xml:space="preserve">10.985239982605</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">10.9718017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0087566375732</t>
+    <t xml:space="preserve">11.0087575912476</t>
   </si>
   <si>
     <t xml:space="preserve">11.0860214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2036008834839</t>
+    <t xml:space="preserve">11.2035999298096</t>
   </si>
   <si>
     <t xml:space="preserve">11.1767253875732</t>
@@ -1835,148 +1835,148 @@
     <t xml:space="preserve">11.1733655929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2170391082764</t>
+    <t xml:space="preserve">11.2170381546021</t>
   </si>
   <si>
     <t xml:space="preserve">11.2002410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2271156311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976636886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35813331604</t>
+    <t xml:space="preserve">11.2271165847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581342697144</t>
   </si>
   <si>
     <t xml:space="preserve">11.4219627380371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5563364028931</t>
+    <t xml:space="preserve">11.5563383102417</t>
   </si>
   <si>
     <t xml:space="preserve">11.4521970748901</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4286804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4622755050659</t>
+    <t xml:space="preserve">11.4286813735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4622745513916</t>
   </si>
   <si>
     <t xml:space="preserve">11.5832138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5529775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6235246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6201658248901</t>
+    <t xml:space="preserve">11.552978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6235256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6201677322388</t>
   </si>
   <si>
     <t xml:space="preserve">11.6302442550659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5261039733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824314117432</t>
+    <t xml:space="preserve">11.5261030197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824323654175</t>
   </si>
   <si>
     <t xml:space="preserve">11.4689931869507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3245391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4152450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093059539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4253196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5636577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5849437713623</t>
+    <t xml:space="preserve">11.324538230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648519515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093050003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4253206253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5636587142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5849418640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5601119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3189077377319</t>
+    <t xml:space="preserve">11.3189067840576</t>
   </si>
   <si>
     <t xml:space="preserve">11.5459232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.414680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330955505371</t>
+    <t xml:space="preserve">11.4146814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330965042114</t>
   </si>
   <si>
     <t xml:space="preserve">11.2124938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763414382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.148645401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1238145828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2727937698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1805696487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2195863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2479648590088</t>
+    <t xml:space="preserve">11.2763423919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486444473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.123815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2727947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1805686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2195873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2479639053345</t>
   </si>
   <si>
     <t xml:space="preserve">11.3366422653198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4536981582642</t>
+    <t xml:space="preserve">11.4536991119385</t>
   </si>
   <si>
     <t xml:space="preserve">11.4288692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4785289764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4466037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7445640563965</t>
+    <t xml:space="preserve">11.4785270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4466028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175466537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7445631027222</t>
   </si>
   <si>
     <t xml:space="preserve">11.8119592666626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8332414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8403358459473</t>
+    <t xml:space="preserve">11.8332424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8403367996216</t>
   </si>
   <si>
     <t xml:space="preserve">11.7871284484863</t>
@@ -1985,103 +1985,103 @@
     <t xml:space="preserve">11.7481098175049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7126388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7977705001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935413360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.106372833252</t>
+    <t xml:space="preserve">11.7126398086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935422897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1063718795776</t>
   </si>
   <si>
     <t xml:space="preserve">12.1312017440796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0708980560303</t>
+    <t xml:space="preserve">12.0708990097046</t>
   </si>
   <si>
     <t xml:space="preserve">12.1418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1773138046265</t>
+    <t xml:space="preserve">12.1773147583008</t>
   </si>
   <si>
     <t xml:space="preserve">12.2092370986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2056913375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808605194092</t>
+    <t xml:space="preserve">12.2056903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560316085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808614730835</t>
   </si>
   <si>
     <t xml:space="preserve">12.1170120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9893159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.024787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0105972290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9751262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.996410369873</t>
+    <t xml:space="preserve">11.989315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105981826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9751253128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9964084625244</t>
   </si>
   <si>
     <t xml:space="preserve">11.8545236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9467487335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573917388916</t>
+    <t xml:space="preserve">11.9467506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573907852173</t>
   </si>
   <si>
     <t xml:space="preserve">11.6629800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884895324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707550048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6594324111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3437366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3792095184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430561065674</t>
+    <t xml:space="preserve">11.5884885787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6594314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3437376022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3792085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430570602417</t>
   </si>
   <si>
     <t xml:space="preserve">11.29407787323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4749803543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5069046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168670654297</t>
+    <t xml:space="preserve">11.4749794006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5069055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168661117554</t>
   </si>
   <si>
     <t xml:space="preserve">11.5778474807739</t>
@@ -2099,22 +2099,22 @@
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6842613220215</t>
+    <t xml:space="preserve">11.6487913131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6842622756958</t>
   </si>
   <si>
     <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7374687194824</t>
+    <t xml:space="preserve">11.7374696731567</t>
   </si>
   <si>
     <t xml:space="preserve">11.9432029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0921821594238</t>
+    <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
     <t xml:space="preserve">12.134747505188</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">12.2021436691284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1844081878662</t>
+    <t xml:space="preserve">12.1844062805176</t>
   </si>
   <si>
     <t xml:space="preserve">12.3014621734619</t>
@@ -2132,100 +2132,100 @@
     <t xml:space="preserve">12.4149703979492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3972358703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262948989868</t>
+    <t xml:space="preserve">12.397234916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262920379639</t>
   </si>
   <si>
     <t xml:space="preserve">12.2908229827881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6597242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058362960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6739120483398</t>
+    <t xml:space="preserve">12.6881008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.659725189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058382034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6739110946655</t>
   </si>
   <si>
     <t xml:space="preserve">12.7413082122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6987428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6703653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6136121749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5852355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759527206421</t>
+    <t xml:space="preserve">12.6987419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6703662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6136140823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5852346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759546279907</t>
   </si>
   <si>
     <t xml:space="preserve">12.4433498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5213861465454</t>
+    <t xml:space="preserve">12.5213871002197</t>
   </si>
   <si>
     <t xml:space="preserve">12.606517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5887813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6490821838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6774597167969</t>
+    <t xml:space="preserve">12.5887823104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6490831375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6774587631226</t>
   </si>
   <si>
     <t xml:space="preserve">12.8157978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7448558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477220535278</t>
+    <t xml:space="preserve">12.7448568344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441753387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477230072021</t>
   </si>
   <si>
     <t xml:space="preserve">12.8406286239624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.035719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215330123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0463609695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0534563064575</t>
+    <t xml:space="preserve">12.9080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215320587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0463628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0534572601318</t>
   </si>
   <si>
     <t xml:space="preserve">13.0499095916748</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0286264419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9364004135132</t>
+    <t xml:space="preserve">13.0286254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9364023208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.8938360214233</t>
@@ -2237,34 +2237,34 @@
     <t xml:space="preserve">13.1882467269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167692184448</t>
+    <t xml:space="preserve">13.1917934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139049530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338260650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167682647705</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5145816802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2662830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237195968628</t>
+    <t xml:space="preserve">13.5145845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2662858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237176895142</t>
   </si>
   <si>
     <t xml:space="preserve">13.2343606948853</t>
@@ -2273,13 +2273,13 @@
     <t xml:space="preserve">13.1527767181396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2591896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456804275513</t>
+    <t xml:space="preserve">13.2591905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456823348999</t>
   </si>
   <si>
     <t xml:space="preserve">12.9754199981689</t>
@@ -2288,16 +2288,16 @@
     <t xml:space="preserve">12.9612302780151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9399461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.918664932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9257583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9541368484497</t>
+    <t xml:space="preserve">12.9399471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9186639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9257593154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9541349411011</t>
   </si>
   <si>
     <t xml:space="preserve">13.0250797271729</t>
@@ -2306,43 +2306,43 @@
     <t xml:space="preserve">13.010890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1137590408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1314945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1776065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4613771438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520961761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0640983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1031160354614</t>
+    <t xml:space="preserve">13.1137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1314926147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1776075363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1208534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4613761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953420639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.06409740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1031150817871</t>
   </si>
   <si>
     <t xml:space="preserve">13.0747385025024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9115715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9789657592773</t>
+    <t xml:space="preserve">12.9115705490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.978964805603</t>
   </si>
   <si>
     <t xml:space="preserve">12.9860601425171</t>
@@ -2351,130 +2351,130 @@
     <t xml:space="preserve">12.9505882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654584884644</t>
+    <t xml:space="preserve">12.8654556274414</t>
   </si>
   <si>
     <t xml:space="preserve">12.7235717773438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8690061569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6916484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4823665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5462160110474</t>
+    <t xml:space="preserve">12.8690042495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5710430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6916475296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.482367515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546215057373</t>
   </si>
   <si>
     <t xml:space="preserve">12.7306671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0002508163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3230390548706</t>
+    <t xml:space="preserve">13.0002498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804727554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194923400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3230400085449</t>
   </si>
   <si>
     <t xml:space="preserve">13.3939800262451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3688583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2979164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2482557296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5352830886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4004917144775</t>
+    <t xml:space="preserve">12.3688592910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2979154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5352821350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4004907608032</t>
   </si>
   <si>
     <t xml:space="preserve">11.1628332138062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8116674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76171398162842</t>
+    <t xml:space="preserve">10.8116664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76171588897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.6127347946167</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36769008636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56278324127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01297760009766</t>
+    <t xml:space="preserve">8.36769199371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56278419494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01297855377197</t>
   </si>
   <si>
     <t xml:space="preserve">7.6972827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3673996925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569881439209</t>
+    <t xml:space="preserve">7.36740016937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569786071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.72565984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72920703887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58406734466553</t>
+    <t xml:space="preserve">7.72920799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58406639099121</t>
   </si>
   <si>
     <t xml:space="preserve">8.83236503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98134517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7791576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77206516265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398941040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5805196762085</t>
+    <t xml:space="preserve">8.98134613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77915859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77206420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58051872253418</t>
   </si>
   <si>
     <t xml:space="preserve">8.74723434448242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64436817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89976215362549</t>
+    <t xml:space="preserve">8.64436721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89976119995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.07002353668213</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">9.31832313537598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9387788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7898006439209</t>
+    <t xml:space="preserve">8.93878078460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78979969024658</t>
   </si>
   <si>
     <t xml:space="preserve">8.88911914825439</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">8.6301794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84300708770752</t>
+    <t xml:space="preserve">8.84300804138184</t>
   </si>
   <si>
     <t xml:space="preserve">8.77561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04164600372314</t>
+    <t xml:space="preserve">9.04164505004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.20126819610596</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">9.00972270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.176438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0345516204834</t>
+    <t xml:space="preserve">9.17643737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03455257415771</t>
   </si>
   <si>
     <t xml:space="preserve">9.09485340118408</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">9.20481491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12322998046875</t>
+    <t xml:space="preserve">9.12323093414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.08421230316162</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">8.91040229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044174194336</t>
+    <t xml:space="preserve">8.80044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">9.17269039154053</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">8.99536895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96212100982666</t>
+    <t xml:space="preserve">8.96212196350098</t>
   </si>
   <si>
     <t xml:space="preserve">9.20963287353516</t>
@@ -2573,10 +2573,10 @@
     <t xml:space="preserve">9.22440910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52363967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81178665161133</t>
+    <t xml:space="preserve">9.52364063262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81178569793701</t>
   </si>
   <si>
     <t xml:space="preserve">10.3031139373779</t>
@@ -2585,40 +2585,40 @@
     <t xml:space="preserve">10.3474454879761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6282052993774</t>
+    <t xml:space="preserve">10.6282043457031</t>
   </si>
   <si>
     <t xml:space="preserve">10.6540632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5395431518555</t>
+    <t xml:space="preserve">10.5395441055298</t>
   </si>
   <si>
     <t xml:space="preserve">10.3215856552124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9226131439209</t>
+    <t xml:space="preserve">9.92261219024658</t>
   </si>
   <si>
     <t xml:space="preserve">9.91891956329346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90414237976074</t>
+    <t xml:space="preserve">9.90414047241211</t>
   </si>
   <si>
     <t xml:space="preserve">10.1257934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.051908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92630577087402</t>
+    <t xml:space="preserve">10.0519094467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92630672454834</t>
   </si>
   <si>
     <t xml:space="preserve">10.0592975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0703811645508</t>
+    <t xml:space="preserve">10.0703802108765</t>
   </si>
   <si>
     <t xml:space="preserve">9.80070495605469</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">9.9152250289917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95216655731201</t>
+    <t xml:space="preserve">9.9521656036377</t>
   </si>
   <si>
     <t xml:space="preserve">9.94847202301025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2218427658081</t>
+    <t xml:space="preserve">10.2218418121338</t>
   </si>
   <si>
     <t xml:space="preserve">10.1553478240967</t>
@@ -2645,34 +2645,34 @@
     <t xml:space="preserve">10.2587852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1627368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675331115723</t>
+    <t xml:space="preserve">10.1627349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675426483154</t>
   </si>
   <si>
     <t xml:space="preserve">9.97063732147217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.07776927948</t>
+    <t xml:space="preserve">10.0777683258057</t>
   </si>
   <si>
     <t xml:space="preserve">10.1294870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070646286011</t>
+    <t xml:space="preserve">10.2070636749268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2107601165771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.114709854126</t>
+    <t xml:space="preserve">10.1147108078003</t>
   </si>
   <si>
     <t xml:space="preserve">10.1812057495117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3289747238159</t>
+    <t xml:space="preserve">10.3289737701416</t>
   </si>
   <si>
     <t xml:space="preserve">10.2772560119629</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">9.97433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46453380584717</t>
+    <t xml:space="preserve">9.46453285217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.35370635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40911865234375</t>
+    <t xml:space="preserve">9.40911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.55688762664795</t>
@@ -2705,31 +2705,31 @@
     <t xml:space="preserve">9.38695430755615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78592777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73051452636719</t>
+    <t xml:space="preserve">9.78592681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73051357269287</t>
   </si>
   <si>
     <t xml:space="preserve">9.68618488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53841590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70834922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62707614898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56058120727539</t>
+    <t xml:space="preserve">9.53841686248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70835018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62707710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56058025360107</t>
   </si>
   <si>
     <t xml:space="preserve">9.76376247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81917572021484</t>
+    <t xml:space="preserve">9.81917476654053</t>
   </si>
   <si>
     <t xml:space="preserve">9.7822322845459</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">9.60860538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62338256835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61968803405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57535839080811</t>
+    <t xml:space="preserve">9.62338161468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61968898773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">9.47192001342773</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">9.48669719696045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47561454772949</t>
+    <t xml:space="preserve">9.47561359405518</t>
   </si>
   <si>
     <t xml:space="preserve">9.46083831787109</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">9.36478900909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10619640350342</t>
+    <t xml:space="preserve">9.10619449615479</t>
   </si>
   <si>
     <t xml:space="preserve">8.75155353546143</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">8.70352745056152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66658401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59639549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359508514404</t>
+    <t xml:space="preserve">8.66658496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59639644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359413146973</t>
   </si>
   <si>
     <t xml:space="preserve">8.86976623535156</t>
@@ -2807,16 +2807,16 @@
     <t xml:space="preserve">9.1135835647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29829406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24288082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22071552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12466716766357</t>
+    <t xml:space="preserve">9.2982931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24288177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2207145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12466621398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.12097263336182</t>
@@ -2828,46 +2828,46 @@
     <t xml:space="preserve">8.96951007843018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03969955444336</t>
+    <t xml:space="preserve">9.01753520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03969860076904</t>
   </si>
   <si>
     <t xml:space="preserve">8.81435394287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82543659210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77371692657471</t>
+    <t xml:space="preserve">8.82543563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77371788024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.39321517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41907405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50404262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72199821472168</t>
+    <t xml:space="preserve">8.41907501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50404167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.721999168396</t>
   </si>
   <si>
     <t xml:space="preserve">8.89193058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01383972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14683151245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72312641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95955371856689</t>
+    <t xml:space="preserve">9.013840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14683055877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7231273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95955467224121</t>
   </si>
   <si>
     <t xml:space="preserve">9.9447774887085</t>
@@ -2879,19 +2879,19 @@
     <t xml:space="preserve">10.317892074585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4398012161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5136842727661</t>
+    <t xml:space="preserve">10.4398002624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5136833190918</t>
   </si>
   <si>
     <t xml:space="preserve">10.3954696655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4952144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5062952041626</t>
+    <t xml:space="preserve">10.495213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5062961578369</t>
   </si>
   <si>
     <t xml:space="preserve">10.6245107650757</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">10.6910057067871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5801782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6577577590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7648897171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713171005249</t>
+    <t xml:space="preserve">10.5801792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6577568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7648906707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7131700515747</t>
   </si>
   <si>
     <t xml:space="preserve">10.6097326278687</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">10.5838737487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6060390472412</t>
+    <t xml:space="preserve">10.6060380935669</t>
   </si>
   <si>
     <t xml:space="preserve">10.4065532684326</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">10.535849571228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5506258010864</t>
+    <t xml:space="preserve">10.5506267547607</t>
   </si>
   <si>
     <t xml:space="preserve">10.5617084503174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2624788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176349639893</t>
+    <t xml:space="preserve">10.2624778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176359176636</t>
   </si>
   <si>
     <t xml:space="preserve">10.6134271621704</t>
@@ -2960,22 +2960,22 @@
     <t xml:space="preserve">10.6392860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6836175918579</t>
+    <t xml:space="preserve">10.6836166381836</t>
   </si>
   <si>
     <t xml:space="preserve">10.7168645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.942211151123</t>
+    <t xml:space="preserve">10.9422101974487</t>
   </si>
   <si>
     <t xml:space="preserve">10.8276901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7205600738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6429815292358</t>
+    <t xml:space="preserve">10.7205610275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6429805755615</t>
   </si>
   <si>
     <t xml:space="preserve">10.4102468490601</t>
@@ -2993,46 +2993,46 @@
     <t xml:space="preserve">11.3929023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4778699874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145553588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6884384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6441087722778</t>
+    <t xml:space="preserve">11.4778690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.688437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6441078186035</t>
   </si>
   <si>
     <t xml:space="preserve">11.5997772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5739183425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6921319961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5665292739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4002914428711</t>
+    <t xml:space="preserve">11.5739192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6921329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5665302276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4002923965454</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4815626144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4557037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000352859497</t>
+    <t xml:space="preserve">11.4815635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4557046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000343322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.6995210647583</t>
@@ -3041,34 +3041,34 @@
     <t xml:space="preserve">11.4889526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6958284378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7290754318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8435945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8768434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.825122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1908502578735</t>
+    <t xml:space="preserve">11.6958274841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7290735244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8435955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251237869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908493041992</t>
   </si>
   <si>
     <t xml:space="preserve">12.2130146026611</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2795104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3866395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4900798797607</t>
+    <t xml:space="preserve">12.2795114517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3866405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4900808334351</t>
   </si>
   <si>
     <t xml:space="preserve">12.4383602142334</t>
@@ -3077,40 +3077,40 @@
     <t xml:space="preserve">12.4789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755588531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4568309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.360782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4161949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.412501335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309740066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5048551559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6045999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.66370677948</t>
+    <t xml:space="preserve">12.3755598068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4568338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3607807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4161968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309730529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5048561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6637058258057</t>
   </si>
   <si>
     <t xml:space="preserve">12.5824346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6600141525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858711242676</t>
+    <t xml:space="preserve">12.6600131988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858720779419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6378469467163</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">12.6119871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6230688095093</t>
+    <t xml:space="preserve">12.6230697631836</t>
   </si>
   <si>
     <t xml:space="preserve">12.5787410736084</t>
@@ -3131,52 +3131,52 @@
     <t xml:space="preserve">12.6489305496216</t>
   </si>
   <si>
-    <t xml:space="preserve">12.726508140564</t>
+    <t xml:space="preserve">12.7265071868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457483291626</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4679155349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3977251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3275337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5602693557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4420537948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5972108840942</t>
+    <t xml:space="preserve">12.4679136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39772605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3275356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5602703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4420547485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5972099304199</t>
   </si>
   <si>
     <t xml:space="preserve">12.7228136062622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8336400985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740190505981</t>
+    <t xml:space="preserve">12.8336410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740200042725</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9149112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9592437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368194580078</t>
+    <t xml:space="preserve">12.9149122238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9592428207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368213653564</t>
   </si>
   <si>
     <t xml:space="preserve">13.0626792907715</t>
@@ -3188,28 +3188,28 @@
     <t xml:space="preserve">12.8890523910522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479040145874</t>
+    <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
     <t xml:space="preserve">13.2438173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1184320449829</t>
+    <t xml:space="preserve">13.1184310913086</t>
   </si>
   <si>
     <t xml:space="preserve">12.9773731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910043716431</t>
+    <t xml:space="preserve">13.0910034179688</t>
   </si>
   <si>
     <t xml:space="preserve">13.2007160186768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2673263549805</t>
+    <t xml:space="preserve">13.1772060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2673273086548</t>
   </si>
   <si>
     <t xml:space="preserve">13.2830018997192</t>
@@ -3218,37 +3218,37 @@
     <t xml:space="preserve">13.3887929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5180969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4985065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4632415771484</t>
+    <t xml:space="preserve">13.5180988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985055923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4632425308228</t>
   </si>
   <si>
     <t xml:space="preserve">13.4201402664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4318952560425</t>
+    <t xml:space="preserve">13.4318933486938</t>
   </si>
   <si>
     <t xml:space="preserve">13.4397315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4514865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2359809875488</t>
+    <t xml:space="preserve">13.4514875411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2359800338745</t>
   </si>
   <si>
     <t xml:space="preserve">13.2712440490723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2320623397827</t>
+    <t xml:space="preserve">13.232063293457</t>
   </si>
   <si>
     <t xml:space="preserve">13.0518217086792</t>
@@ -3257,13 +3257,13 @@
     <t xml:space="preserve">13.3339366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1262683868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2477359771729</t>
+    <t xml:space="preserve">13.1262693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2477369308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.373122215271</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">13.3221826553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4358139038086</t>
+    <t xml:space="preserve">13.4358129501343</t>
   </si>
   <si>
     <t xml:space="preserve">13.196798324585</t>
@@ -3281,16 +3281,16 @@
     <t xml:space="preserve">12.9852104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3261003494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3300189971924</t>
+    <t xml:space="preserve">13.326099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.330020904541</t>
   </si>
   <si>
     <t xml:space="preserve">13.2634077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1654500961304</t>
+    <t xml:space="preserve">13.1654510498047</t>
   </si>
   <si>
     <t xml:space="preserve">13.1145153045654</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">12.8441514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.122350692749</t>
+    <t xml:space="preserve">13.1223516464233</t>
   </si>
   <si>
     <t xml:space="preserve">13.1576156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1301870346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046337127686</t>
+    <t xml:space="preserve">13.1301860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046346664429</t>
   </si>
   <si>
     <t xml:space="preserve">13.0674934387207</t>
@@ -3320,16 +3320,16 @@
     <t xml:space="preserve">12.9891300201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0283117294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2281436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
+    <t xml:space="preserve">13.0283126831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.228141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947559356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456926345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">13.569034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6160545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5376882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5416088104248</t>
+    <t xml:space="preserve">13.6160535812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5376892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5416069030762</t>
   </si>
   <si>
     <t xml:space="preserve">13.3770389556885</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">13.4436502456665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4240589141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848752975464</t>
+    <t xml:space="preserve">13.4240579605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848762512207</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
@@ -3365,67 +3365,67 @@
     <t xml:space="preserve">13.5337705612183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5964632034302</t>
+    <t xml:space="preserve">13.5964641571045</t>
   </si>
   <si>
     <t xml:space="preserve">13.6121377944946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5729532241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7414398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8393974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9060087203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923774719238</t>
+    <t xml:space="preserve">13.5729541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7414407730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8393964767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9060096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591548919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8315591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923793792725</t>
   </si>
   <si>
     <t xml:space="preserve">13.8824987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0039663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748294830322</t>
+    <t xml:space="preserve">14.0039653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748304367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.0901670455933</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2037973403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.364447593689</t>
+    <t xml:space="preserve">14.2037992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3644466400146</t>
   </si>
   <si>
     <t xml:space="preserve">14.5956268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3017559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4114675521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4271392822266</t>
+    <t xml:space="preserve">14.3017539978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4114685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4271402359009</t>
   </si>
   <si>
     <t xml:space="preserve">14.3997116088867</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014217376709</t>
+    <t xml:space="preserve">14.564281463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014226913452</t>
   </si>
   <si>
     <t xml:space="preserve">14.7288484573364</t>
@@ -3455,37 +3455,37 @@
     <t xml:space="preserve">14.6739931106567</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7249317169189</t>
+    <t xml:space="preserve">14.7249298095703</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494472503662</t>
+    <t xml:space="preserve">14.8494462966919</t>
   </si>
   <si>
     <t xml:space="preserve">14.9739608764648</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9217462539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9538793563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141277313232</t>
+    <t xml:space="preserve">14.9217472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141286849976</t>
   </si>
   <si>
     <t xml:space="preserve">15.1185598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0663414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1346282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426582336426</t>
+    <t xml:space="preserve">15.0663433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1346263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426601409912</t>
   </si>
   <si>
     <t xml:space="preserve">15.2310247421265</t>
@@ -3506,16 +3506,16 @@
     <t xml:space="preserve">15.2430753707886</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2792253494263</t>
+    <t xml:space="preserve">15.2511081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.279224395752</t>
   </si>
   <si>
     <t xml:space="preserve">15.38365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3716077804565</t>
+    <t xml:space="preserve">15.3716058731079</t>
   </si>
   <si>
     <t xml:space="preserve">15.4559545516968</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">14.9418277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6887817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7811622619629</t>
+    <t xml:space="preserve">14.6887807846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7811632156372</t>
   </si>
   <si>
     <t xml:space="preserve">14.7570638656616</t>
@@ -3539,58 +3539,58 @@
     <t xml:space="preserve">14.7168979644775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1867036819458</t>
+    <t xml:space="preserve">14.1867027282715</t>
   </si>
   <si>
     <t xml:space="preserve">14.299168586731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2429370880127</t>
+    <t xml:space="preserve">14.2429361343384</t>
   </si>
   <si>
     <t xml:space="preserve">14.5642652511597</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4919681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6124658584595</t>
+    <t xml:space="preserve">14.4919672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6124649047852</t>
   </si>
   <si>
     <t xml:space="preserve">14.9498615264893</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0221605300903</t>
+    <t xml:space="preserve">15.022162437439</t>
   </si>
   <si>
     <t xml:space="preserve">14.857479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9297771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8614978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213300704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6767311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731304168701</t>
+    <t xml:space="preserve">14.9297780990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8614959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6767320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731294631958</t>
   </si>
   <si>
     <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9016609191895</t>
+    <t xml:space="preserve">14.9016618728638</t>
   </si>
   <si>
     <t xml:space="preserve">15.0623264312744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0060949325562</t>
+    <t xml:space="preserve">15.0060958862305</t>
   </si>
   <si>
     <t xml:space="preserve">14.9659271240234</t>
@@ -3602,19 +3602,19 @@
     <t xml:space="preserve">15.1788082122803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8333806991577</t>
+    <t xml:space="preserve">14.8333787918091</t>
   </si>
   <si>
     <t xml:space="preserve">14.9177274703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8293619155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337959289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.058310508728</t>
+    <t xml:space="preserve">14.8293628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337949752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0583095550537</t>
   </si>
   <si>
     <t xml:space="preserve">15.0422449111938</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">14.8132972717285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9257621765137</t>
+    <t xml:space="preserve">14.9257612228394</t>
   </si>
   <si>
     <t xml:space="preserve">15.1466751098633</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">15.1627416610718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3754854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847658157349</t>
+    <t xml:space="preserve">14.3754863739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847648620605</t>
   </si>
   <si>
     <t xml:space="preserve">14.6727132797241</t>
@@ -3650,40 +3650,40 @@
     <t xml:space="preserve">14.9940462112427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7369804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9819955825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.957896232605</t>
+    <t xml:space="preserve">14.7369813919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9819946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9578952789307</t>
   </si>
   <si>
     <t xml:space="preserve">14.7450141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2270097732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8936290740967</t>
+    <t xml:space="preserve">15.2270078659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.893630027771</t>
   </si>
   <si>
     <t xml:space="preserve">14.5562334060669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5964002609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0300559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714685440063</t>
+    <t xml:space="preserve">14.596399307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.371467590332</t>
   </si>
   <si>
     <t xml:space="preserve">13.9256229400635</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8372583389282</t>
+    <t xml:space="preserve">13.8372573852539</t>
   </si>
   <si>
     <t xml:space="preserve">13.7770080566406</t>
@@ -3698,19 +3698,19 @@
     <t xml:space="preserve">12.993766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243762969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4958438873291</t>
+    <t xml:space="preserve">13.6243753433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4958448410034</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1746530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3875350952148</t>
+    <t xml:space="preserve">14.174654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3875341415405</t>
   </si>
   <si>
     <t xml:space="preserve">15.0824098587036</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">16.1789455413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8495855331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1628799438477</t>
+    <t xml:space="preserve">15.8495836257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
     <t xml:space="preserve">16.6850414276123</t>
@@ -3743,25 +3743,25 @@
     <t xml:space="preserve">16.9581737518311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3074779510498</t>
+    <t xml:space="preserve">16.3074798583984</t>
   </si>
   <si>
     <t xml:space="preserve">16.235179901123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0504131317139</t>
+    <t xml:space="preserve">16.0504169464111</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7331027984619</t>
+    <t xml:space="preserve">15.7331008911133</t>
   </si>
   <si>
     <t xml:space="preserve">15.6166210174561</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4840707778931</t>
+    <t xml:space="preserve">15.4840726852417</t>
   </si>
   <si>
     <t xml:space="preserve">15.4117727279663</t>
@@ -3773,43 +3773,43 @@
     <t xml:space="preserve">14.9980611801147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7932138442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080318450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5441818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4598340988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5401668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7048473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6204986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4518003463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2469549179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.009973526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2268695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2670364379883</t>
+    <t xml:space="preserve">14.7932147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5441827774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4598350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5401659011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7048482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204996109009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4518013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2469539642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0099725723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2268705368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2670373916626</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947364807129</t>
@@ -3818,37 +3818,37 @@
     <t xml:space="preserve">14.3112201690674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4558181762695</t>
+    <t xml:space="preserve">14.4558172225952</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7547540664673</t>
+    <t xml:space="preserve">14.7547550201416</t>
   </si>
   <si>
     <t xml:space="preserve">14.8230848312378</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5882034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5540399551392</t>
+    <t xml:space="preserve">14.8828716278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5882043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5540390014648</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2764539718628</t>
+    <t xml:space="preserve">14.4430055618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3789472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2764530181885</t>
   </si>
   <si>
     <t xml:space="preserve">14.4643564224243</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924503326416</t>
+    <t xml:space="preserve">13.3924493789673</t>
   </si>
   <si>
     <t xml:space="preserve">13.2344388961792</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881788253784</t>
+    <t xml:space="preserve">13.3881797790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3887,19 +3887,19 @@
     <t xml:space="preserve">13.3967208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2557916641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1917333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828479766846</t>
+    <t xml:space="preserve">13.2557926177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1917343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828470230103</t>
   </si>
   <si>
     <t xml:space="preserve">13.2686033248901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4266147613525</t>
+    <t xml:space="preserve">13.4266138076782</t>
   </si>
   <si>
     <t xml:space="preserve">13.2899570465088</t>
@@ -3908,13 +3908,13 @@
     <t xml:space="preserve">13.0038299560547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2942276000977</t>
+    <t xml:space="preserve">13.2942266464233</t>
   </si>
   <si>
     <t xml:space="preserve">13.1661100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4187641143799</t>
+    <t xml:space="preserve">12.4187631607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596923828125</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">12.7774896621704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3547058105469</t>
+    <t xml:space="preserve">12.3547048568726</t>
   </si>
   <si>
     <t xml:space="preserve">12.4401159286499</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838836669922</t>
+    <t xml:space="preserve">12.1838846206665</t>
   </si>
   <si>
     <t xml:space="preserve">12.1625299453735</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">12.3333530426025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4571990966797</t>
+    <t xml:space="preserve">12.4571981430054</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134323120117</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">12.4700107574463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.534068107605</t>
+    <t xml:space="preserve">12.5340690612793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408319473267</t>
@@ -3986,13 +3986,13 @@
     <t xml:space="preserve">12.8458185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141473770142</t>
+    <t xml:space="preserve">12.9141483306885</t>
   </si>
   <si>
     <t xml:space="preserve">13.0508050918579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191329956055</t>
+    <t xml:space="preserve">13.1191339492798</t>
   </si>
   <si>
     <t xml:space="preserve">13.2258977890015</t>
@@ -4001,16 +4001,16 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8970651626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7646780014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7006196975708</t>
+    <t xml:space="preserve">13.1618385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.897066116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7646789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7006206512451</t>
   </si>
   <si>
     <t xml:space="preserve">12.8757123947144</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">12.5041751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3931407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8330059051514</t>
+    <t xml:space="preserve">12.3931398391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8330068588257</t>
   </si>
   <si>
     <t xml:space="preserve">12.4828224182129</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7689485549927</t>
+    <t xml:space="preserve">12.768949508667</t>
   </si>
   <si>
     <t xml:space="preserve">13.1703805923462</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">12.9696645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.089241027832</t>
+    <t xml:space="preserve">13.0892400741577</t>
   </si>
   <si>
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7048902511597</t>
+    <t xml:space="preserve">12.704891204834</t>
   </si>
   <si>
     <t xml:space="preserve">12.7390546798706</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">12.4443864822388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1411790847778</t>
+    <t xml:space="preserve">12.1411781311035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0173320770264</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">11.9447326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7909927368164</t>
+    <t xml:space="preserve">11.7909936904907</t>
   </si>
   <si>
     <t xml:space="preserve">12.0045204162598</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091617584229</t>
+    <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
@@ -4136,10 +4136,10 @@
     <t xml:space="preserve">12.973934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0977821350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025182723999</t>
+    <t xml:space="preserve">13.0977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0251817703247</t>
   </si>
   <si>
     <t xml:space="preserve">13.153299331665</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">13.8493986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9433517456055</t>
+    <t xml:space="preserve">13.9433507919312</t>
   </si>
   <si>
     <t xml:space="preserve">14.2294778823853</t>
@@ -4166,28 +4166,28 @@
     <t xml:space="preserve">14.5839338302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5156049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7419443130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5796632766724</t>
+    <t xml:space="preserve">14.515604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
     <t xml:space="preserve">14.5027923583984</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4600868225098</t>
+    <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6266384124756</t>
+    <t xml:space="preserve">14.4686298370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6266393661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163200378418</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">14.6906976699829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7889194488525</t>
+    <t xml:space="preserve">14.7889204025269</t>
   </si>
   <si>
     <t xml:space="preserve">14.7462139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8999538421631</t>
+    <t xml:space="preserve">14.8999547958374</t>
   </si>
   <si>
     <t xml:space="preserve">14.8444366455078</t>
@@ -4223,28 +4223,28 @@
     <t xml:space="preserve">14.0928201675415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2508296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2892646789551</t>
+    <t xml:space="preserve">14.2508306503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2892637252808</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3490524291992</t>
+    <t xml:space="preserve">14.3490533828735</t>
   </si>
   <si>
     <t xml:space="preserve">14.3106184005737</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2593717575073</t>
+    <t xml:space="preserve">14.259370803833</t>
   </si>
   <si>
     <t xml:space="preserve">14.3618650436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1910419464111</t>
+    <t xml:space="preserve">14.1910429000854</t>
   </si>
   <si>
     <t xml:space="preserve">14.3276996612549</t>
@@ -4259,22 +4259,22 @@
     <t xml:space="preserve">14.8102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6736154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615188598633</t>
+    <t xml:space="preserve">14.6736164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615198135376</t>
   </si>
   <si>
     <t xml:space="preserve">14.8487071990967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9554719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.968282699585</t>
+    <t xml:space="preserve">14.9554710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9682817459106</t>
   </si>
   <si>
     <t xml:space="preserve">14.8358974456787</t>
@@ -4322,13 +4322,13 @@
     <t xml:space="preserve">15.5063734054565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5618886947632</t>
+    <t xml:space="preserve">15.5618906021118</t>
   </si>
   <si>
     <t xml:space="preserve">15.5832433700562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.600323677063</t>
+    <t xml:space="preserve">15.6003255844116</t>
   </si>
   <si>
     <t xml:space="preserve">15.5875129699707</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">15.6473016738892</t>
   </si>
   <si>
-    <t xml:space="preserve">15.685736656189</t>
+    <t xml:space="preserve">15.6857347488403</t>
   </si>
   <si>
     <t xml:space="preserve">15.4850196838379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5106430053711</t>
+    <t xml:space="preserve">15.5106449127197</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
@@ -4358,10 +4358,10 @@
     <t xml:space="preserve">15.9804019927979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8266630172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223934173584</t>
+    <t xml:space="preserve">15.8266649246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223915100098</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4370,10 +4370,10 @@
     <t xml:space="preserve">16.0231094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.027379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0658149719238</t>
+    <t xml:space="preserve">16.0273780822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0658130645752</t>
   </si>
   <si>
     <t xml:space="preserve">15.9078044891357</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">15.7327108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2031631469727</t>
+    <t xml:space="preserve">15.203161239624</t>
   </si>
   <si>
     <t xml:space="preserve">15.7540645599365</t>
@@ -4397,10 +4397,10 @@
     <t xml:space="preserve">15.0451526641846</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4508543014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081516265869</t>
+    <t xml:space="preserve">15.4508562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.1092128753662</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">15.2501392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4423131942749</t>
+    <t xml:space="preserve">15.4423151016235</t>
   </si>
   <si>
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985454559326</t>
+    <t xml:space="preserve">15.6985473632812</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
@@ -4427,19 +4427,19 @@
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437452316284</t>
+    <t xml:space="preserve">15.8437471389771</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0914402008057</t>
+    <t xml:space="preserve">16.091438293457</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0401916503906</t>
+    <t xml:space="preserve">16.040189743042</t>
   </si>
   <si>
     <t xml:space="preserve">16.1384143829346</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">16.3092365264893</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3434028625488</t>
+    <t xml:space="preserve">16.3434009552002</t>
   </si>
   <si>
     <t xml:space="preserve">16.219554901123</t>
@@ -4490,13 +4490,13 @@
     <t xml:space="preserve">15.9889430999756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1127891540527</t>
+    <t xml:space="preserve">16.1127910614014</t>
   </si>
   <si>
     <t xml:space="preserve">16.0316505432129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9120740890503</t>
+    <t xml:space="preserve">15.9120721817017</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">16.4688701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596569061279</t>
+    <t xml:space="preserve">16.2596549987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.332426071167</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">16.4188404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5188999176025</t>
+    <t xml:space="preserve">16.5189018249512</t>
   </si>
   <si>
     <t xml:space="preserve">16.6462478637695</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">16.9236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1010646820068</t>
+    <t xml:space="preserve">17.1010627746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2193164825439</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">16.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7963390350342</t>
+    <t xml:space="preserve">16.7963371276855</t>
   </si>
   <si>
     <t xml:space="preserve">16.6689910888672</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.6280574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235660552979</t>
+    <t xml:space="preserve">16.7235679626465</t>
   </si>
   <si>
     <t xml:space="preserve">16.6917304992676</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">16.9373321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4330787658691</t>
+    <t xml:space="preserve">17.5103969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4330806732178</t>
   </si>
   <si>
     <t xml:space="preserve">17.2056732177734</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">17.1783828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920261383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0692272186279</t>
+    <t xml:space="preserve">17.1920280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">17.2829914093018</t>
@@ -4616,13 +4616,13 @@
     <t xml:space="preserve">17.3648567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3739547729492</t>
+    <t xml:space="preserve">17.3739528656006</t>
   </si>
   <si>
     <t xml:space="preserve">17.3330192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3284702301025</t>
+    <t xml:space="preserve">17.3284721374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.5149459838867</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">17.5240421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6286487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4057922363281</t>
+    <t xml:space="preserve">17.6286506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4057903289795</t>
   </si>
   <si>
     <t xml:space="preserve">17.037389755249</t>
@@ -4649,16 +4649,16 @@
     <t xml:space="preserve">17.091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7190170288086</t>
+    <t xml:space="preserve">16.9737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7190189361572</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8736553192139</t>
+    <t xml:space="preserve">16.8736572265625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7417602539062</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">16.7645015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281764984131</t>
+    <t xml:space="preserve">16.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">16.8418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9282341003418</t>
+    <t xml:space="preserve">16.9282360076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.0737762451172</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">17.442174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4012432098389</t>
+    <t xml:space="preserve">17.4012413024902</t>
   </si>
   <si>
     <t xml:space="preserve">17.292085647583</t>
@@ -4691,13 +4691,13 @@
     <t xml:space="preserve">17.3011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6013603210449</t>
+    <t xml:space="preserve">17.6013622283936</t>
   </si>
   <si>
     <t xml:space="preserve">17.7150650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7332572937012</t>
+    <t xml:space="preserve">17.7332592010498</t>
   </si>
   <si>
     <t xml:space="preserve">18.0197906494141</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">18.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1926212310791</t>
+    <t xml:space="preserve">18.1926231384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.0470809936523</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">17.7878360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059093475342</t>
+    <t xml:space="preserve">17.6059074401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6832294464111</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">16.8918476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3239231109619</t>
+    <t xml:space="preserve">17.3239250183105</t>
   </si>
   <si>
     <t xml:space="preserve">17.4876575469971</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">17.0510349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2966327667236</t>
+    <t xml:space="preserve">17.2966346740723</t>
   </si>
   <si>
     <t xml:space="preserve">17.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1465454101562</t>
+    <t xml:space="preserve">17.1238040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1465473175049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2511539459229</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">17.8787994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8151245117188</t>
+    <t xml:space="preserve">17.8151226043701</t>
   </si>
   <si>
     <t xml:space="preserve">17.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4922046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.314826965332</t>
+    <t xml:space="preserve">17.4922065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3148288726807</t>
   </si>
   <si>
     <t xml:space="preserve">17.187479019165</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">17.242057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1419982910156</t>
+    <t xml:space="preserve">17.141996383667</t>
   </si>
   <si>
     <t xml:space="preserve">17.2284126281738</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">17.4103393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.414888381958</t>
+    <t xml:space="preserve">17.4148864746094</t>
   </si>
   <si>
     <t xml:space="preserve">17.496753692627</t>
@@ -4895,13 +4895,13 @@
     <t xml:space="preserve">17.9561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0061454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.901538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9515705108643</t>
+    <t xml:space="preserve">18.0061473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9015407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9515686035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.9379234313965</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">18.6201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5473785400391</t>
+    <t xml:space="preserve">18.5473766326904</t>
   </si>
   <si>
     <t xml:space="preserve">18.5655708312988</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">18.6656303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6929187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8202686309814</t>
+    <t xml:space="preserve">18.6929168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8202667236328</t>
   </si>
   <si>
     <t xml:space="preserve">18.629243850708</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">18.7565937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6838245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5564746856689</t>
+    <t xml:space="preserve">18.6838226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5564727783203</t>
   </si>
   <si>
     <t xml:space="preserve">18.8384590148926</t>
@@ -4985,25 +4985,25 @@
     <t xml:space="preserve">19.5024909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.139232635498</t>
+    <t xml:space="preserve">20.1392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9118232727051</t>
+    <t xml:space="preserve">19.9118251800537</t>
   </si>
   <si>
     <t xml:space="preserve">19.9664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0027885437012</t>
+    <t xml:space="preserve">20.0027866363525</t>
   </si>
   <si>
     <t xml:space="preserve">20.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1574230194092</t>
+    <t xml:space="preserve">20.1574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">20.0755577087402</t>
@@ -5012,16 +5012,16 @@
     <t xml:space="preserve">20.2120018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2847728729248</t>
+    <t xml:space="preserve">20.2847709655762</t>
   </si>
   <si>
     <t xml:space="preserve">20.393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5940456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6122398376465</t>
+    <t xml:space="preserve">20.5940475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6122417449951</t>
   </si>
   <si>
     <t xml:space="preserve">20.6759147644043</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">21.1034412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3399429321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127178192139</t>
+    <t xml:space="preserve">21.3399448394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127159118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.5309677124023</t>
@@ -5060,10 +5060,10 @@
     <t xml:space="preserve">20.8669376373291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0306701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7304916381836</t>
+    <t xml:space="preserve">21.0306720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7304935455322</t>
   </si>
   <si>
     <t xml:space="preserve">20.7577800750732</t>
@@ -5072,13 +5072,13 @@
     <t xml:space="preserve">20.6031436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7032051086426</t>
+    <t xml:space="preserve">20.7032032012939</t>
   </si>
   <si>
     <t xml:space="preserve">20.3393516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4394111633301</t>
+    <t xml:space="preserve">20.4394092559814</t>
   </si>
   <si>
     <t xml:space="preserve">20.4939880371094</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">20.6213359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7123012542725</t>
+    <t xml:space="preserve">20.7122993469238</t>
   </si>
   <si>
     <t xml:space="preserve">21.003381729126</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">21.2307891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7765674591064</t>
+    <t xml:space="preserve">21.7765693664551</t>
   </si>
   <si>
     <t xml:space="preserve">21.7401809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9039154052734</t>
+    <t xml:space="preserve">21.9039173126221</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949977874756</t>
@@ -6042,6 +6042,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.4500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2799987792969</t>
   </si>
 </sst>
 </file>
@@ -71198,7 +71201,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6512152778</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>2418449</v>
@@ -71219,6 +71222,32 @@
         <v>2009</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6496064815</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>1372960</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>32.6500015258789</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>32.1500015258789</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>32.5999984741211</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>32.2799987792969</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2010</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="2011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="2012">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,79 +38,79 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21390151977539</t>
+    <t xml:space="preserve">9.21390056610107</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31058883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13427257537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11720943450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02052307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76457977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8897066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0660228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95795917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75889205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29251003265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44607639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48588752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30957412719727</t>
+    <t xml:space="preserve">9.31058979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13427448272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11721134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02052116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76458072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88970851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06602191925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95795822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75889301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120227813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29251098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44607448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48588848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30957317352295</t>
   </si>
   <si>
     <t xml:space="preserve">8.04794406890869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93987894058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568593978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41662168502808</t>
+    <t xml:space="preserve">7.93988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319067001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668888092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662073135376</t>
   </si>
   <si>
     <t xml:space="preserve">7.23461818695068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1549916267395</t>
+    <t xml:space="preserve">7.15499114990234</t>
   </si>
   <si>
     <t xml:space="preserve">6.96161365509033</t>
@@ -122,241 +122,241 @@
     <t xml:space="preserve">6.47248077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81373643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23360157012939</t>
+    <t xml:space="preserve">6.8137354850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23360204696655</t>
   </si>
   <si>
     <t xml:space="preserve">6.34166574478149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59760808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62035703659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392292022705</t>
+    <t xml:space="preserve">6.59760761260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62035846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392339706421</t>
   </si>
   <si>
     <t xml:space="preserve">6.72842168807983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6601710319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89905023574829</t>
+    <t xml:space="preserve">6.66017150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89904928207397</t>
   </si>
   <si>
     <t xml:space="preserve">6.89336204528809</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95592594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28580665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268236160278</t>
+    <t xml:space="preserve">6.95592737197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2630558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28580713272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268188476562</t>
   </si>
   <si>
     <t xml:space="preserve">7.45643377304077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4507474899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680864334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24599313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3199315071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249492645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37112092971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575265884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79200172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731599807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89438009262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67256307601929</t>
+    <t xml:space="preserve">7.45074701309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680768966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24599361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31993055343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249540328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3711199760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750104904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79200267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437818527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256164550781</t>
   </si>
   <si>
     <t xml:space="preserve">7.57587337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53037261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4279956817627</t>
+    <t xml:space="preserve">7.53037023544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543130874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42799711227417</t>
   </si>
   <si>
     <t xml:space="preserve">7.48487186431885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41093254089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9843635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00711441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85354948043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05261516571045</t>
+    <t xml:space="preserve">7.41093349456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30287027359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755456924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98436307907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00711393356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85354852676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05261421203613</t>
   </si>
   <si>
     <t xml:space="preserve">7.13792991638184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16067886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43368244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4962477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47918367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862279891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75218963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181476593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456514358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80337715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77493953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018566131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39386987686157</t>
+    <t xml:space="preserve">7.16067838668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4336838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49624729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918462753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862422943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218915939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181619644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7863130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456562042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80337762832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77493906021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018613815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387083053589</t>
   </si>
   <si>
     <t xml:space="preserve">7.35405778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53606081008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05830192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517810821533</t>
+    <t xml:space="preserve">7.53606128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16636753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0583028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517858505249</t>
   </si>
   <si>
     <t xml:space="preserve">7.25168085098267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31798839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994874954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8484525680542</t>
+    <t xml:space="preserve">7.31798887252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994970321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84845352172852</t>
   </si>
   <si>
     <t xml:space="preserve">7.90873289108276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94490098953247</t>
+    <t xml:space="preserve">7.94490051269531</t>
   </si>
   <si>
     <t xml:space="preserve">7.85448026657104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81228542327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76406097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54705238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53499603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6615834236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7700891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42046594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17934370040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97439193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850416183472</t>
+    <t xml:space="preserve">7.81228351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76406049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54705381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53499698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42046451568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17934513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439384460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850463867188</t>
   </si>
   <si>
     <t xml:space="preserve">6.92014074325562</t>
@@ -368,67 +368,67 @@
     <t xml:space="preserve">7.40840911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54102420806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5832200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257341384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02498340606689</t>
+    <t xml:space="preserve">7.54102468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58321952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58257246017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02498292922974</t>
   </si>
   <si>
     <t xml:space="preserve">6.11841678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26308917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953664779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187379837036</t>
+    <t xml:space="preserve">6.26308822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953760147095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4318733215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.25103282928467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13047313690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91647911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92853546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76341342926025</t>
+    <t xml:space="preserve">6.13047361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91647863388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92853498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7634129524231</t>
   </si>
   <si>
     <t xml:space="preserve">6.69710540771484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87191772460938</t>
+    <t xml:space="preserve">6.8719162940979</t>
   </si>
   <si>
     <t xml:space="preserve">6.80560922622681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8417763710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8478045463562</t>
+    <t xml:space="preserve">6.84177684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738382339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84780502319336</t>
   </si>
   <si>
     <t xml:space="preserve">6.7754693031311</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">6.68504905700684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81163644790649</t>
+    <t xml:space="preserve">6.81163740158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.62476921081543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10098075866699</t>
+    <t xml:space="preserve">7.10098028182983</t>
   </si>
   <si>
     <t xml:space="preserve">7.07084035873413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79355192184448</t>
+    <t xml:space="preserve">6.79355335235596</t>
   </si>
   <si>
     <t xml:space="preserve">7.06481218338013</t>
@@ -461,34 +461,34 @@
     <t xml:space="preserve">7.20948505401611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29387617111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0828971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73930215835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04070138931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01658821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81766557693481</t>
+    <t xml:space="preserve">7.29387664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990339279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000082015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808391571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04070043563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01658916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766510009766</t>
   </si>
   <si>
     <t xml:space="preserve">6.74532842636108</t>
@@ -497,73 +497,73 @@
     <t xml:space="preserve">6.61271286010742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78149747848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93822479248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88397169113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079690933228</t>
+    <t xml:space="preserve">6.78149795532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425344467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247646331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93822431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88397312164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523195266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770854949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313310623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079643249512</t>
   </si>
   <si>
     <t xml:space="preserve">6.72724485397339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79957962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75135517120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59462881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56448936462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57654428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54640531539917</t>
+    <t xml:space="preserve">6.79958057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75135660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59462833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56448793411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57654476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668516159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54640483856201</t>
   </si>
   <si>
     <t xml:space="preserve">6.51626491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4981803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76944017410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986185073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383319854736</t>
+    <t xml:space="preserve">6.49818134307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383224487305</t>
   </si>
   <si>
     <t xml:space="preserve">7.18537282943726</t>
@@ -572,115 +572,115 @@
     <t xml:space="preserve">7.16728830337524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19742870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2697639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33004426956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31196069717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317798614502</t>
+    <t xml:space="preserve">7.19742918014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784942626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26976490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33004474639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31195974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317607879639</t>
   </si>
   <si>
     <t xml:space="preserve">7.09495306015015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98644876480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574771881104</t>
+    <t xml:space="preserve">6.98644924163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299365997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574914932251</t>
   </si>
   <si>
     <t xml:space="preserve">7.08892488479614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686853408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8779444694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0226149559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82369327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854856491089</t>
+    <t xml:space="preserve">7.07686805725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87794494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02261638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82369184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854713439941</t>
   </si>
   <si>
     <t xml:space="preserve">7.35415649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73392009735107</t>
+    <t xml:space="preserve">7.73392200469971</t>
   </si>
   <si>
     <t xml:space="preserve">8.30055332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68031597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45125198364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47536373138428</t>
+    <t xml:space="preserve">8.68031406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45125293731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47536277770996</t>
   </si>
   <si>
     <t xml:space="preserve">8.41508483886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33069229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.541672706604</t>
+    <t xml:space="preserve">8.33069133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54167175292969</t>
   </si>
   <si>
     <t xml:space="preserve">8.5597562789917</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63812065124512</t>
+    <t xml:space="preserve">8.6381196975708</t>
   </si>
   <si>
     <t xml:space="preserve">8.5838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59592533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6622314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6682596206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5537281036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5055046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5115327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71045589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75265121459961</t>
+    <t xml:space="preserve">8.59592437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66223239898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66826057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55372714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50550270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51153182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7104549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75265312194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.69839859008789</t>
@@ -698,52 +698,52 @@
     <t xml:space="preserve">8.38494396209717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25835609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23424434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16793441772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27041339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26438331604004</t>
+    <t xml:space="preserve">8.25835704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23424339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16793632507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27041244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26438426971436</t>
   </si>
   <si>
     <t xml:space="preserve">8.5898962020874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2951717376709</t>
+    <t xml:space="preserve">9.29517269134521</t>
   </si>
   <si>
     <t xml:space="preserve">9.38559150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4217586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28311538696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98774433135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88526821136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84910011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00582790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81896018981934</t>
+    <t xml:space="preserve">9.42175960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28311634063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98774242401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88526725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00582695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993869781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81895923614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.77073669433594</t>
@@ -755,73 +755,73 @@
     <t xml:space="preserve">8.74059581756592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90335369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04802417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87923812866211</t>
+    <t xml:space="preserve">8.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04802513122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87924098968506</t>
   </si>
   <si>
     <t xml:space="preserve">8.90937900543213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95760345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83101558685303</t>
+    <t xml:space="preserve">8.95760536193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83101463317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.81293201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74662303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65620422363281</t>
+    <t xml:space="preserve">8.74662494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6562032699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.49947643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14985275268555</t>
+    <t xml:space="preserve">8.14985084533691</t>
   </si>
   <si>
     <t xml:space="preserve">8.27644062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54770088195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46330833435059</t>
+    <t xml:space="preserve">8.54769897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46330738067627</t>
   </si>
   <si>
     <t xml:space="preserve">8.56578350067139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78881931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80087566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.794846534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78279209136963</t>
+    <t xml:space="preserve">8.78882026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78279113769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.86718368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98171615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80690479278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63209056854248</t>
+    <t xml:space="preserve">8.98171710968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80690383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6320915222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.6079797744751</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93349170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75868034362793</t>
+    <t xml:space="preserve">8.93349075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75867938995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.87321186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04199600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1926965713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24091911315918</t>
+    <t xml:space="preserve">9.04199504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19269466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21077823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2409200668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.2168083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94554710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89129638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03596782684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07213687896729</t>
+    <t xml:space="preserve">8.94554901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89129734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03596878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07213592529297</t>
   </si>
   <si>
     <t xml:space="preserve">9.12036037445068</t>
@@ -875,49 +875,49 @@
     <t xml:space="preserve">9.30493068695068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33675479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18400573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15854644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13309001922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851875305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83395671844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03762054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81486225128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758171081543</t>
+    <t xml:space="preserve">9.33675289154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18400382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15854740142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13308906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83395576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94215393066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03761959075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81486129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758266448975</t>
   </si>
   <si>
     <t xml:space="preserve">8.73848915100098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89123630523682</t>
+    <t xml:space="preserve">8.89123725891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.95488262176514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05035018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22855567932129</t>
+    <t xml:space="preserve">9.05034923553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22855758666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.2349214553833</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">9.1712760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28583717346191</t>
+    <t xml:space="preserve">9.28583812713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.2985668182373</t>
@@ -935,31 +935,31 @@
     <t xml:space="preserve">9.19036960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3494815826416</t>
+    <t xml:space="preserve">9.34948253631592</t>
   </si>
   <si>
     <t xml:space="preserve">9.25401401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22219276428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24764919281006</t>
+    <t xml:space="preserve">9.22219085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24765014648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.29220199584961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33038902282715</t>
+    <t xml:space="preserve">9.33039093017578</t>
   </si>
   <si>
     <t xml:space="preserve">9.38130474090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57860565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54678249359131</t>
+    <t xml:space="preserve">9.57860660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54678344726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.5404167175293</t>
@@ -968,28 +968,28 @@
     <t xml:space="preserve">9.64861488342285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79499816894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85864543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68680286407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56587600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52768898010254</t>
+    <t xml:space="preserve">9.79500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85864353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68680191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56587696075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52768993377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.75681209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77590465545654</t>
+    <t xml:space="preserve">9.77590560913086</t>
   </si>
   <si>
     <t xml:space="preserve">9.80136299133301</t>
@@ -998,46 +998,46 @@
     <t xml:space="preserve">10.0750370025635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0877676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1386823654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2341527938843</t>
+    <t xml:space="preserve">10.0877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1386842727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.23415184021</t>
   </si>
   <si>
     <t xml:space="preserve">10.1959648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0623092651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0050287246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82682228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86500930786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90319633483887</t>
+    <t xml:space="preserve">10.0623083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0050277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82682132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86500835418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90319538116455</t>
   </si>
   <si>
     <t xml:space="preserve">9.82045745849609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87137413024902</t>
+    <t xml:space="preserve">9.87137317657471</t>
   </si>
   <si>
     <t xml:space="preserve">9.78227043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71226024627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69953155517578</t>
+    <t xml:space="preserve">9.71226119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69953060150146</t>
   </si>
   <si>
     <t xml:space="preserve">9.68043804168701</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">9.69316673278809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66134452819824</t>
+    <t xml:space="preserve">9.66134548187256</t>
   </si>
   <si>
     <t xml:space="preserve">9.53405380249023</t>
@@ -1055,88 +1055,88 @@
     <t xml:space="preserve">9.52132415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57223987579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61679172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67407321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62952136993408</t>
+    <t xml:space="preserve">9.57224082946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61679267883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">9.59769916534424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89046669006348</t>
+    <t xml:space="preserve">9.89046764373779</t>
   </si>
   <si>
     <t xml:space="preserve">9.9477481842041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75044822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89683246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91592407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87773990631104</t>
+    <t xml:space="preserve">9.75044727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89683151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91592597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">10.0304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0686750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1323194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93501853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84591579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85228061676025</t>
+    <t xml:space="preserve">10.0686731338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1323184967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93501949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84591484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85227870941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.83318614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72498989105225</t>
+    <t xml:space="preserve">9.72498798370361</t>
   </si>
   <si>
     <t xml:space="preserve">9.99866390228271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96047592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0177583694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95411205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1259536743164</t>
+    <t xml:space="preserve">9.96047687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0177574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9541130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1259546279907</t>
   </si>
   <si>
     <t xml:space="preserve">10.0241212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94138431549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88410091400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0368499755859</t>
+    <t xml:space="preserve">9.94138336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8841028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0368509292603</t>
   </si>
   <si>
     <t xml:space="preserve">9.78863430023193</t>
@@ -1145,70 +1145,70 @@
     <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58497047424316</t>
+    <t xml:space="preserve">9.58496952056885</t>
   </si>
   <si>
     <t xml:space="preserve">9.61042785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66770839691162</t>
+    <t xml:space="preserve">9.6677074432373</t>
   </si>
   <si>
     <t xml:space="preserve">9.74408340454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73135375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8077278137207</t>
+    <t xml:space="preserve">9.73135471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80772686004639</t>
   </si>
   <si>
     <t xml:space="preserve">9.73771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589733123779</t>
+    <t xml:space="preserve">9.70589542388916</t>
   </si>
   <si>
     <t xml:space="preserve">9.5595121383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47677421569824</t>
+    <t xml:space="preserve">9.47677326202393</t>
   </si>
   <si>
     <t xml:space="preserve">9.97320556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97957038879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0814037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2914323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3041610717773</t>
+    <t xml:space="preserve">9.97957134246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0814018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0559434890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2914304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.304160118103</t>
   </si>
   <si>
     <t xml:space="preserve">10.2023286819458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.310525894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736879348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641407012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1482286453247</t>
+    <t xml:space="preserve">10.3105268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3232555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1482305526733</t>
   </si>
   <si>
     <t xml:space="preserve">9.99229907989502</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">9.76954174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86819171905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81727504730225</t>
+    <t xml:space="preserve">9.86819076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81727409362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.77908706665039</t>
@@ -1229,49 +1229,49 @@
     <t xml:space="preserve">9.8140926361084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80454540252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36857604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6517972946167</t>
+    <t xml:space="preserve">9.80454444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.368577003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65179634094238</t>
   </si>
   <si>
     <t xml:space="preserve">9.8554630279541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74726581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0082101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98593425750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92865371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94456481933594</t>
+    <t xml:space="preserve">9.74726676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0082120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98593521118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92865562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94456577301025</t>
   </si>
   <si>
     <t xml:space="preserve">9.9700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0495805740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1609582901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3137073516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2946128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455295562744</t>
+    <t xml:space="preserve">10.0495796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1609592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3137083053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2946138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455286026001</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346342086792</t>
@@ -1280,82 +1280,82 @@
     <t xml:space="preserve">10.530101776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.638298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.765588760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8546924591064</t>
+    <t xml:space="preserve">10.6382970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7655897140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8546915054321</t>
   </si>
   <si>
     <t xml:space="preserve">10.6319341659546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7178544998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5841989517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6542100906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.708309173584</t>
+    <t xml:space="preserve">10.7178564071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5841999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6542091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7083082199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796684265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269193649292</t>
+    <t xml:space="preserve">10.6796674728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269212722778</t>
   </si>
   <si>
     <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4409990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5014600753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078258514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2977962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3328008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2596101760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2864847183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.252890586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99421691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83968544006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49702644348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5541353225708</t>
+    <t xml:space="preserve">10.4409980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5014619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078248977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.297797203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3328018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2596092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2864856719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2528924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1319532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0143737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99421787261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83968639373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49702453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55413627624512</t>
   </si>
   <si>
     <t xml:space="preserve">9.77585601806641</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">9.88335704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86991786956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65491771697998</t>
+    <t xml:space="preserve">9.86991882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65491676330566</t>
   </si>
   <si>
     <t xml:space="preserve">9.67843341827393</t>
@@ -1376,43 +1376,43 @@
     <t xml:space="preserve">9.52054119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79937171936035</t>
+    <t xml:space="preserve">9.79937267303467</t>
   </si>
   <si>
     <t xml:space="preserve">9.75234031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78257369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90015411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80609130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76241683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8296070098877</t>
+    <t xml:space="preserve">9.78257465362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90015316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80608940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76241874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82960605621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.69858932495117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76913642883301</t>
+    <t xml:space="preserve">9.76913738250732</t>
   </si>
   <si>
     <t xml:space="preserve">9.60116672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61796474456787</t>
+    <t xml:space="preserve">9.61796283721924</t>
   </si>
   <si>
     <t xml:space="preserve">9.52390003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51718139648438</t>
+    <t xml:space="preserve">9.51718235015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.61124610900879</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">9.80945014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77249717712402</t>
+    <t xml:space="preserve">9.77249526977539</t>
   </si>
   <si>
     <t xml:space="preserve">9.7288236618042</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">9.65155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66163730621338</t>
+    <t xml:space="preserve">9.66163635253906</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">9.84976291656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85648250579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81616878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74898052215576</t>
+    <t xml:space="preserve">9.85648155212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8161678314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74898147583008</t>
   </si>
   <si>
     <t xml:space="preserve">9.89007568359375</t>
@@ -1457,25 +1457,25 @@
     <t xml:space="preserve">9.90351295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92366886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070121765137</t>
+    <t xml:space="preserve">9.92367172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070026397705</t>
   </si>
   <si>
     <t xml:space="preserve">10.0479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2125778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1117963790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9539041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0378885269165</t>
+    <t xml:space="preserve">10.2125768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.111795425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95390224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0378875732422</t>
   </si>
   <si>
     <t xml:space="preserve">10.0009355545044</t>
@@ -1487,28 +1487,28 @@
     <t xml:space="preserve">10.0916395187378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0748414993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8665599822998</t>
+    <t xml:space="preserve">10.0748424530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86655902862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.71202659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7321834564209</t>
+    <t xml:space="preserve">9.73218441009521</t>
   </si>
   <si>
     <t xml:space="preserve">9.85312175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92702865600586</t>
+    <t xml:space="preserve">9.92702770233154</t>
   </si>
   <si>
     <t xml:space="preserve">9.98077869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92031002044678</t>
+    <t xml:space="preserve">9.92031097412109</t>
   </si>
   <si>
     <t xml:space="preserve">9.63812065124512</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">9.93710708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96062183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94382476806641</t>
+    <t xml:space="preserve">9.9606237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94382572174072</t>
   </si>
   <si>
     <t xml:space="preserve">10.1621866226196</t>
@@ -1535,46 +1535,46 @@
     <t xml:space="preserve">10.0882806777954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1554679870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1722650527954</t>
+    <t xml:space="preserve">10.1554670333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1722640991211</t>
   </si>
   <si>
     <t xml:space="preserve">10.1823434829712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2965631484985</t>
+    <t xml:space="preserve">10.2965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">10.4141426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4309387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3704700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9975757598877</t>
+    <t xml:space="preserve">10.4309377670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3704690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99757671356201</t>
   </si>
   <si>
     <t xml:space="preserve">9.88671684265137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96734237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93038749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70866870880127</t>
+    <t xml:space="preserve">9.96734046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93038845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70866680145264</t>
   </si>
   <si>
     <t xml:space="preserve">9.69187068939209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59444808959961</t>
+    <t xml:space="preserve">9.59444904327393</t>
   </si>
   <si>
     <t xml:space="preserve">9.50038528442383</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">9.56421279907227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41304206848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43991565704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40968227386475</t>
+    <t xml:space="preserve">9.41304111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43991661071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40968132019043</t>
   </si>
   <si>
     <t xml:space="preserve">9.28874206542969</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">9.43655586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33241558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53397846221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66499519348145</t>
+    <t xml:space="preserve">9.33241653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53397750854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66499710083008</t>
   </si>
   <si>
     <t xml:space="preserve">9.62468338012695</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">9.65827751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66835403442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63476085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57429313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71538543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51382160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59780693054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5574951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57765007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81952857971191</t>
+    <t xml:space="preserve">9.66835498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6347599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57429122924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51382350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59780788421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55749416351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57765293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8195276260376</t>
   </si>
   <si>
     <t xml:space="preserve">9.87663650512695</t>
@@ -1652,43 +1652,43 @@
     <t xml:space="preserve">9.9135913848877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0042963027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0849208831787</t>
+    <t xml:space="preserve">10.0042953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.084921836853</t>
   </si>
   <si>
     <t xml:space="preserve">9.97406005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57093238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64484024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89679336547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85984134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9505443572998</t>
+    <t xml:space="preserve">9.57093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64483833312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89679431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85984039306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95054531097412</t>
   </si>
   <si>
     <t xml:space="preserve">10.021092414856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647640228271</t>
+    <t xml:space="preserve">10.0446071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647630691528</t>
   </si>
   <si>
     <t xml:space="preserve">10.2327337265015</t>
@@ -1703,49 +1703,49 @@
     <t xml:space="preserve">10.2898445129395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3335161209106</t>
+    <t xml:space="preserve">10.333517074585</t>
   </si>
   <si>
     <t xml:space="preserve">10.3133602142334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3839073181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3771877288818</t>
+    <t xml:space="preserve">10.3839063644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3771886825562</t>
   </si>
   <si>
     <t xml:space="preserve">10.276406288147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1991405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2461738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932043075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714817047119</t>
+    <t xml:space="preserve">10.1991386413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2461709976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932033538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
     <t xml:space="preserve">10.1285924911499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2831258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1890621185303</t>
+    <t xml:space="preserve">10.2058601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2831249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.189061164856</t>
   </si>
   <si>
     <t xml:space="preserve">10.2293748855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260160446167</t>
+    <t xml:space="preserve">10.2260141372681</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730464935303</t>
@@ -1754,88 +1754,88 @@
     <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4275817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4342966079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5451574325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.672815322876</t>
+    <t xml:space="preserve">10.4275798797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4342975616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5451583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6728172302246</t>
   </si>
   <si>
     <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7400035858154</t>
+    <t xml:space="preserve">10.7400026321411</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5653142929077</t>
+    <t xml:space="preserve">10.5653162002563</t>
   </si>
   <si>
     <t xml:space="preserve">10.6157054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5921907424927</t>
+    <t xml:space="preserve">10.5921897888184</t>
   </si>
   <si>
     <t xml:space="preserve">10.6224250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7534408569336</t>
+    <t xml:space="preserve">10.7534418106079</t>
   </si>
   <si>
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0591468811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0322723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.069224357605</t>
+    <t xml:space="preserve">11.0725841522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0591459274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0322704315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0692262649536</t>
   </si>
   <si>
     <t xml:space="preserve">10.985239982605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9718017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0087575912476</t>
+    <t xml:space="preserve">10.9718027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0087556838989</t>
   </si>
   <si>
     <t xml:space="preserve">11.0860214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1767253875732</t>
+    <t xml:space="preserve">11.2036008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1767263412476</t>
   </si>
   <si>
     <t xml:space="preserve">11.2304763793945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2237577438354</t>
+    <t xml:space="preserve">11.2237567901611</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733655929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2170381546021</t>
+    <t xml:space="preserve">11.2170391082764</t>
   </si>
   <si>
     <t xml:space="preserve">11.2002410888672</t>
@@ -1847,58 +1847,58 @@
     <t xml:space="preserve">11.297664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3581342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4219627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5563383102417</t>
+    <t xml:space="preserve">11.35813331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4219617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.556339263916</t>
   </si>
   <si>
     <t xml:space="preserve">11.4521970748901</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4286813735962</t>
+    <t xml:space="preserve">11.4286794662476</t>
   </si>
   <si>
     <t xml:space="preserve">11.4622745513916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5832138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.552978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6235256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6201677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6302442550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5261030197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824323654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4689931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.324538230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648519515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093050003052</t>
+    <t xml:space="preserve">11.583212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6235246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6201667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.526104927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824304580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4689922332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3245401382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4152421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093069076538</t>
   </si>
   <si>
     <t xml:space="preserve">11.4253206253052</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">11.3189067840576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5459232330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4146814346313</t>
+    <t xml:space="preserve">11.5459241867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4146795272827</t>
   </si>
   <si>
     <t xml:space="preserve">11.3330965042114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1486444473267</t>
+    <t xml:space="preserve">11.2124929428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.148645401001</t>
   </si>
   <si>
     <t xml:space="preserve">11.123815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2727947235107</t>
+    <t xml:space="preserve">11.2727937698364</t>
   </si>
   <si>
     <t xml:space="preserve">11.1805686950684</t>
@@ -1946,37 +1946,37 @@
     <t xml:space="preserve">11.2195873260498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2479639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3366422653198</t>
+    <t xml:space="preserve">11.2479629516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3366432189941</t>
   </si>
   <si>
     <t xml:space="preserve">11.4536991119385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4288692474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4785270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4466028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175466537476</t>
+    <t xml:space="preserve">11.4288702011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4785289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4466047286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175485610962</t>
   </si>
   <si>
     <t xml:space="preserve">11.7445631027222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8119592666626</t>
+    <t xml:space="preserve">11.8119583129883</t>
   </si>
   <si>
     <t xml:space="preserve">11.8332424163818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8403367996216</t>
+    <t xml:space="preserve">11.8403358459473</t>
   </si>
   <si>
     <t xml:space="preserve">11.7871284484863</t>
@@ -1985,34 +1985,34 @@
     <t xml:space="preserve">11.7481098175049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7126398086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935422897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1063718795776</t>
+    <t xml:space="preserve">11.7126407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7977705001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1312017440796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0708990097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1418418884277</t>
+    <t xml:space="preserve">12.0708980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1418428421021</t>
   </si>
   <si>
     <t xml:space="preserve">12.1773147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2092370986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2056903839111</t>
+    <t xml:space="preserve">12.2092380523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2056913375854</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560316085815</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">11.989315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0247888565063</t>
+    <t xml:space="preserve">12.024787902832</t>
   </si>
   <si>
     <t xml:space="preserve">12.0105981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0567111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9751253128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9964084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8545236587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9467506408691</t>
+    <t xml:space="preserve">12.056713104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9751272201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.996410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8545227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9467496871948</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573907852173</t>
@@ -2057,19 +2057,19 @@
     <t xml:space="preserve">11.5884885787964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5707530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6594314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3437376022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3792085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430570602417</t>
+    <t xml:space="preserve">11.5707540512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6594324111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3437366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3792104721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430561065674</t>
   </si>
   <si>
     <t xml:space="preserve">11.29407787323</t>
@@ -2078,271 +2078,271 @@
     <t xml:space="preserve">11.4749794006348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5069055557251</t>
+    <t xml:space="preserve">11.5069046020508</t>
   </si>
   <si>
     <t xml:space="preserve">11.6168661117554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5778474807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4678869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558847427368</t>
+    <t xml:space="preserve">11.5778465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.467887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820737838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558856964111</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487913131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6842622756958</t>
+    <t xml:space="preserve">11.6487903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6842613220215</t>
   </si>
   <si>
     <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7374696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9432029724121</t>
+    <t xml:space="preserve">11.7374687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9432020187378</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.134747505188</t>
+    <t xml:space="preserve">12.1347484588623</t>
   </si>
   <si>
     <t xml:space="preserve">12.2021436691284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1844062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3014621734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4149703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.397234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262920379639</t>
+    <t xml:space="preserve">12.1844081878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3014631271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4149713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262929916382</t>
   </si>
   <si>
     <t xml:space="preserve">12.2908229827881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6881008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.659725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058382034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6739110946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7413082122803</t>
+    <t xml:space="preserve">12.6881017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6597232818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058372497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7413063049316</t>
   </si>
   <si>
     <t xml:space="preserve">12.6987419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6703662872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6136140823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5852346420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5213871002197</t>
+    <t xml:space="preserve">12.6703653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5852336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5213861465454</t>
   </si>
   <si>
     <t xml:space="preserve">12.606517791748</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5887823104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6490831375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6774587631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8157978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7448568344116</t>
+    <t xml:space="preserve">12.5887813568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6490821838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6774597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8157987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.744854927063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441753387451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8477230072021</t>
+    <t xml:space="preserve">12.8477220535278</t>
   </si>
   <si>
     <t xml:space="preserve">12.8406286239624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080228805542</t>
+    <t xml:space="preserve">12.9080238342285</t>
   </si>
   <si>
     <t xml:space="preserve">13.0357208251953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0215320587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0463628768921</t>
+    <t xml:space="preserve">13.0215330123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0463619232178</t>
   </si>
   <si>
     <t xml:space="preserve">13.0534572601318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0499095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0286254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9364023208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8938360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1243991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1917934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139049530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167682647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2662858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2343606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1527767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2591905593872</t>
+    <t xml:space="preserve">13.0499105453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0286264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938341140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.124400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1917943954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422805786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139039993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338251113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167701721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145826339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2662839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2343597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.152777671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2591915130615</t>
   </si>
   <si>
     <t xml:space="preserve">13.2627363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1456823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9754199981689</t>
+    <t xml:space="preserve">13.1456813812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9754190444946</t>
   </si>
   <si>
     <t xml:space="preserve">12.9612302780151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9399471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9186639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9257593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9541349411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250797271729</t>
+    <t xml:space="preserve">12.9399480819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.918664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9257583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9541368484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250816345215</t>
   </si>
   <si>
     <t xml:space="preserve">13.010890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1137580871582</t>
+    <t xml:space="preserve">13.1137571334839</t>
   </si>
   <si>
     <t xml:space="preserve">13.1314926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1776075363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1208534240723</t>
+    <t xml:space="preserve">13.1776065826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1208524703979</t>
   </si>
   <si>
     <t xml:space="preserve">13.4613761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2520952224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953420639038</t>
+    <t xml:space="preserve">13.2520942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953411102295</t>
   </si>
   <si>
     <t xml:space="preserve">13.06409740448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9683256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1031150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0747385025024</t>
+    <t xml:space="preserve">12.9683265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1031160354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0747404098511</t>
   </si>
   <si>
     <t xml:space="preserve">12.9115705490112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.978964805603</t>
+    <t xml:space="preserve">12.9789657592773</t>
   </si>
   <si>
     <t xml:space="preserve">12.9860601425171</t>
@@ -2351,31 +2351,31 @@
     <t xml:space="preserve">12.9505882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654556274414</t>
+    <t xml:space="preserve">12.8654584884644</t>
   </si>
   <si>
     <t xml:space="preserve">12.7235717773438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8690042495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5710430145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6916475296021</t>
+    <t xml:space="preserve">12.8690052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.571044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6916484832764</t>
   </si>
   <si>
     <t xml:space="preserve">12.482367515564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.546215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7306671142578</t>
+    <t xml:space="preserve">12.5462160110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7306661605835</t>
   </si>
   <si>
     <t xml:space="preserve">13.0002498626709</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">13.0818338394165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2804727554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3230400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3939800262451</t>
+    <t xml:space="preserve">13.2804708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194913864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3230381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3939809799194</t>
   </si>
   <si>
     <t xml:space="preserve">12.3688592910767</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">12.2979154586792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2482566833496</t>
+    <t xml:space="preserve">12.2482557296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.5352821350098</t>
@@ -2411,79 +2411,79 @@
     <t xml:space="preserve">11.4004907608032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1628332138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8116664886475</t>
+    <t xml:space="preserve">11.1628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8116674423218</t>
   </si>
   <si>
     <t xml:space="preserve">9.76171588897705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6127347946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36769199371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56278419494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01297855377197</t>
+    <t xml:space="preserve">9.61273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36769104003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56278324127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01297664642334</t>
   </si>
   <si>
     <t xml:space="preserve">7.6972827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36740016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72565984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920799255371</t>
+    <t xml:space="preserve">7.36739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72565889358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920656204224</t>
   </si>
   <si>
     <t xml:space="preserve">8.58406639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83236503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98134613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77915859222412</t>
+    <t xml:space="preserve">8.83236408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98134422302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7791576385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.77206420898438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80398845672607</t>
+    <t xml:space="preserve">8.80398750305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.58051872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74723434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64436721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89976119995117</t>
+    <t xml:space="preserve">8.74723339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64436817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89976024627686</t>
   </si>
   <si>
     <t xml:space="preserve">9.07002353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13032531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31832313537598</t>
+    <t xml:space="preserve">9.13032627105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31832218170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.93878078460693</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">8.88911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84300804138184</t>
+    <t xml:space="preserve">8.63017845153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84300708770752</t>
   </si>
   <si>
     <t xml:space="preserve">8.77561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04164505004883</t>
+    <t xml:space="preserve">9.04164600372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.20126819610596</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">9.23319149017334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00972270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17643737792969</t>
+    <t xml:space="preserve">9.00972175598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17643642425537</t>
   </si>
   <si>
     <t xml:space="preserve">9.03455257415771</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">9.09485340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20481491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12323093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08421230316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91040229797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80044078826904</t>
+    <t xml:space="preserve">9.20481586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12322998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0842113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91040325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80044174194336</t>
   </si>
   <si>
     <t xml:space="preserve">9.17269039154053</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">9.05817031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78849411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96212196350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20963287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43867206573486</t>
+    <t xml:space="preserve">8.78849506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99536800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20963382720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43867301940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.22440910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52364063262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81178569793701</t>
+    <t xml:space="preserve">9.52363967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81178665161133</t>
   </si>
   <si>
     <t xml:space="preserve">10.3031139373779</t>
@@ -2588,97 +2588,97 @@
     <t xml:space="preserve">10.6282043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540632247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5395441055298</t>
+    <t xml:space="preserve">10.6540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5395431518555</t>
   </si>
   <si>
     <t xml:space="preserve">10.3215856552124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92261219024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91891956329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90414047241211</t>
+    <t xml:space="preserve">9.92261123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91891860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90414142608643</t>
   </si>
   <si>
     <t xml:space="preserve">10.1257934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0519094467163</t>
+    <t xml:space="preserve">10.0519104003906</t>
   </si>
   <si>
     <t xml:space="preserve">9.92630672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0592975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703802108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80070495605469</t>
+    <t xml:space="preserve">10.0592985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80070400238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.82656288146973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9152250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9521656036377</t>
+    <t xml:space="preserve">9.91522407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95216655731201</t>
   </si>
   <si>
     <t xml:space="preserve">9.94847202301025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2218418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1553478240967</t>
+    <t xml:space="preserve">10.2218427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553468704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.2587852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1627349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675426483154</t>
+    <t xml:space="preserve">10.1627368927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675331115723</t>
   </si>
   <si>
     <t xml:space="preserve">9.97063732147217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0777683258057</t>
+    <t xml:space="preserve">10.0777702331543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1294870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070636749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2107601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1147108078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3289737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2772560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0408267974854</t>
+    <t xml:space="preserve">10.2070655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2107591629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.114709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.181206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3289747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2772550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0408277511597</t>
   </si>
   <si>
     <t xml:space="preserve">9.98541450500488</t>
@@ -2696,34 +2696,34 @@
     <t xml:space="preserve">9.40911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63077163696289</t>
+    <t xml:space="preserve">9.55688571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63077068328857</t>
   </si>
   <si>
     <t xml:space="preserve">9.38695430755615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78592681884766</t>
+    <t xml:space="preserve">9.78592777252197</t>
   </si>
   <si>
     <t xml:space="preserve">9.73051357269287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68618488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53841686248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70835018157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62707710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56058025360107</t>
+    <t xml:space="preserve">9.68618297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53841495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70835113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62707614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56058120727539</t>
   </si>
   <si>
     <t xml:space="preserve">9.76376247406006</t>
@@ -2732,25 +2732,25 @@
     <t xml:space="preserve">9.81917476654053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7822322845459</t>
+    <t xml:space="preserve">9.78223323822021</t>
   </si>
   <si>
     <t xml:space="preserve">9.60860538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62338161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61968898773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57535934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47192001342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37217807769775</t>
+    <t xml:space="preserve">9.62338256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61968994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57535839080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47192096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37217712402344</t>
   </si>
   <si>
     <t xml:space="preserve">9.56796932220459</t>
@@ -2759,16 +2759,16 @@
     <t xml:space="preserve">9.48669719696045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47561359405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083831787109</t>
+    <t xml:space="preserve">9.47561454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083736419678</t>
   </si>
   <si>
     <t xml:space="preserve">9.36478900909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10619449615479</t>
+    <t xml:space="preserve">9.1061954498291</t>
   </si>
   <si>
     <t xml:space="preserve">8.75155353546143</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">8.70352745056152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66658496856689</t>
+    <t xml:space="preserve">8.66658592224121</t>
   </si>
   <si>
     <t xml:space="preserve">8.59639644622803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53359413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804752349854</t>
+    <t xml:space="preserve">8.53359508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804656982422</t>
   </si>
   <si>
     <t xml:space="preserve">8.88454341888428</t>
@@ -2798,121 +2798,121 @@
     <t xml:space="preserve">8.76632976531982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91779136657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14313697814941</t>
+    <t xml:space="preserve">8.91779041290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1431360244751</t>
   </si>
   <si>
     <t xml:space="preserve">9.1135835647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2982931137085</t>
+    <t xml:space="preserve">9.29829406738281</t>
   </si>
   <si>
     <t xml:space="preserve">9.24288177490234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2207145690918</t>
+    <t xml:space="preserve">9.22071552276611</t>
   </si>
   <si>
     <t xml:space="preserve">9.12466621398926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12097263336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80327129364014</t>
+    <t xml:space="preserve">9.12097358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80327033996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.96951007843018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01753520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03969860076904</t>
+    <t xml:space="preserve">9.01753425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03969955444336</t>
   </si>
   <si>
     <t xml:space="preserve">8.81435394287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82543563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77371788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39321517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41907501220703</t>
+    <t xml:space="preserve">8.82543659210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77371692657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39321422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41907405853271</t>
   </si>
   <si>
     <t xml:space="preserve">8.50404167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.721999168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89193058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.013840675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14683055877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7231273651123</t>
+    <t xml:space="preserve">8.72199821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89193153381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01383876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14683246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72312545776367</t>
   </si>
   <si>
     <t xml:space="preserve">9.95955467224121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9447774887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0740737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.317892074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4398002624512</t>
+    <t xml:space="preserve">9.94477844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0740756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3178911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4397993087769</t>
   </si>
   <si>
     <t xml:space="preserve">10.5136833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3954696655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.495213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5062961578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6245107650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910057067871</t>
+    <t xml:space="preserve">10.395468711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4952125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5062971115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6245098114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7094774246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">10.5801792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6577568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7648906707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7131700515747</t>
+    <t xml:space="preserve">10.6577577590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7648897171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.713171005249</t>
   </si>
   <si>
     <t xml:space="preserve">10.6097326278687</t>
@@ -2921,22 +2921,22 @@
     <t xml:space="preserve">10.5838737487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6060380935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4065532684326</t>
+    <t xml:space="preserve">10.6060390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4065523147583</t>
   </si>
   <si>
     <t xml:space="preserve">10.535849571228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5506267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617084503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2624778747559</t>
+    <t xml:space="preserve">10.5506258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2624788284302</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176359176636</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">10.7464179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6392860412598</t>
+    <t xml:space="preserve">10.6392869949341</t>
   </si>
   <si>
     <t xml:space="preserve">10.6836166381836</t>
@@ -2966,28 +2966,28 @@
     <t xml:space="preserve">10.7168645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9422101974487</t>
+    <t xml:space="preserve">10.9422121047974</t>
   </si>
   <si>
     <t xml:space="preserve">10.8276901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7205610275269</t>
+    <t xml:space="preserve">10.7205591201782</t>
   </si>
   <si>
     <t xml:space="preserve">10.6429805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4102468490601</t>
+    <t xml:space="preserve">10.4102458953857</t>
   </si>
   <si>
     <t xml:space="preserve">10.5321559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6946992874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0456485748291</t>
+    <t xml:space="preserve">10.6947002410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0456476211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.3929023742676</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">11.4778690338135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6145544052124</t>
+    <t xml:space="preserve">11.6145553588867</t>
   </si>
   <si>
     <t xml:space="preserve">11.688437461853</t>
@@ -3008,100 +3008,100 @@
     <t xml:space="preserve">11.5997772216797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5739192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6921329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5665302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4002923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5111169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4815635681152</t>
+    <t xml:space="preserve">11.5739183425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6921339035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367197036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5665292739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4002914428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.511116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4815626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.4557046890259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5000343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6995210647583</t>
+    <t xml:space="preserve">11.5000352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.699520111084</t>
   </si>
   <si>
     <t xml:space="preserve">11.4889526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6958274841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7290735244751</t>
+    <t xml:space="preserve">11.6958265304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7290744781494</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8768424987793</t>
+    <t xml:space="preserve">11.8768434524536</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1908493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2130146026611</t>
+    <t xml:space="preserve">12.1908502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2130155563354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795114517212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3866405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4900808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4383602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4789953231812</t>
+    <t xml:space="preserve">12.3866415023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4900798797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4383592605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4789962768555</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4568338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3607807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4161968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125022888184</t>
+    <t xml:space="preserve">12.4568319320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3607816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4161949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.412501335144</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048561096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6045989990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6637058258057</t>
+    <t xml:space="preserve">12.5048551559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6045999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6637077331543</t>
   </si>
   <si>
     <t xml:space="preserve">12.5824346542358</t>
@@ -3113,43 +3113,43 @@
     <t xml:space="preserve">12.6858720779419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6378469467163</t>
+    <t xml:space="preserve">12.6378479003906</t>
   </si>
   <si>
     <t xml:space="preserve">12.5344095230103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6119871139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6230697631836</t>
+    <t xml:space="preserve">12.611988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6230688095093</t>
   </si>
   <si>
     <t xml:space="preserve">12.5787410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265071868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4457483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.39772605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3275356292725</t>
+    <t xml:space="preserve">12.6489315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679145812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3977251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3275337219238</t>
   </si>
   <si>
     <t xml:space="preserve">12.5602703094482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4420547485352</t>
+    <t xml:space="preserve">12.4420537948608</t>
   </si>
   <si>
     <t xml:space="preserve">12.5972099304199</t>
@@ -3158,43 +3158,43 @@
     <t xml:space="preserve">12.7228136062622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8336410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740200042725</t>
+    <t xml:space="preserve">12.8336400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740190505981</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9149122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9592428207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368213653564</t>
+    <t xml:space="preserve">12.9149112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9592437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368194580078</t>
   </si>
   <si>
     <t xml:space="preserve">13.0626792907715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8890523910522</t>
+    <t xml:space="preserve">12.8816652297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8890514373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2438173294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1184310913086</t>
+    <t xml:space="preserve">13.2438163757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1184320449829</t>
   </si>
   <si>
     <t xml:space="preserve">12.9773731231689</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">13.2673273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2830018997192</t>
+    <t xml:space="preserve">13.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887929916382</t>
@@ -3230,22 +3230,22 @@
     <t xml:space="preserve">13.4201402664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4318933486938</t>
+    <t xml:space="preserve">13.4318943023682</t>
   </si>
   <si>
     <t xml:space="preserve">13.4397315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4514875411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102615356445</t>
+    <t xml:space="preserve">13.4514865875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102596282959</t>
   </si>
   <si>
     <t xml:space="preserve">13.2359800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712440490723</t>
+    <t xml:space="preserve">13.2712450027466</t>
   </si>
   <si>
     <t xml:space="preserve">13.232063293457</t>
@@ -3257,52 +3257,52 @@
     <t xml:space="preserve">13.3339366912842</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1262693405151</t>
+    <t xml:space="preserve">13.1262683868408</t>
   </si>
   <si>
     <t xml:space="preserve">13.1732873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2477369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.373122215271</t>
+    <t xml:space="preserve">13.2477359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3731212615967</t>
   </si>
   <si>
     <t xml:space="preserve">13.3221826553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4358129501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.196798324585</t>
+    <t xml:space="preserve">13.4358139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1967973709106</t>
   </si>
   <si>
     <t xml:space="preserve">12.9852104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.326099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.330020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2634077072144</t>
+    <t xml:space="preserve">13.3261013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3300189971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2634086608887</t>
   </si>
   <si>
     <t xml:space="preserve">13.1654510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7148475646973</t>
+    <t xml:space="preserve">13.1145143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7148485183716</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1223516464233</t>
+    <t xml:space="preserve">13.122350692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.1576156616211</t>
@@ -3317,19 +3317,19 @@
     <t xml:space="preserve">13.0674934387207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9891300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0283126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.228141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947559356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456926345825</t>
+    <t xml:space="preserve">12.9891290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0283117294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2281436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456935882568</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">13.569034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6160535812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5376892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5416069030762</t>
+    <t xml:space="preserve">13.6160545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5376873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5416088104248</t>
   </si>
   <si>
     <t xml:space="preserve">13.3770389556885</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">13.4436502456665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4240579605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848762512207</t>
+    <t xml:space="preserve">13.4240589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848752975464</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
@@ -3374,22 +3374,22 @@
     <t xml:space="preserve">13.5729541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7414407730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8393964767456</t>
+    <t xml:space="preserve">13.7414398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8393974304199</t>
   </si>
   <si>
     <t xml:space="preserve">13.9060096740723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6591548919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8315591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923793792725</t>
+    <t xml:space="preserve">13.6591577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923765182495</t>
   </si>
   <si>
     <t xml:space="preserve">13.8824987411499</t>
@@ -3398,31 +3398,31 @@
     <t xml:space="preserve">14.0039653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8589878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748304367065</t>
+    <t xml:space="preserve">13.8589897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748294830322</t>
   </si>
   <si>
     <t xml:space="preserve">14.0901670455933</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2037992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3644466400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3017539978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4114685058594</t>
+    <t xml:space="preserve">14.2037973403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3644485473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3017568588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4114675521851</t>
   </si>
   <si>
     <t xml:space="preserve">14.4271402359009</t>
@@ -3434,37 +3434,37 @@
     <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.564281463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014226913452</t>
+    <t xml:space="preserve">14.5642795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014207839966</t>
   </si>
   <si>
     <t xml:space="preserve">14.7288484573364</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6622362136841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6739931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7249298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851800918579</t>
+    <t xml:space="preserve">14.8072128295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816614151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6622371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6739940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7249307632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851810455322</t>
   </si>
   <si>
     <t xml:space="preserve">14.8494462966919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9739608764648</t>
+    <t xml:space="preserve">14.9739599227905</t>
   </si>
   <si>
     <t xml:space="preserve">14.9217472076416</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">14.95387840271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0141286849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1185598373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0663433074951</t>
+    <t xml:space="preserve">15.0141277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.118558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0663414001465</t>
   </si>
   <si>
     <t xml:space="preserve">15.1346263885498</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">15.1426601409912</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2310247421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.247091293335</t>
+    <t xml:space="preserve">15.2310237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470903396606</t>
   </si>
   <si>
     <t xml:space="preserve">15.3234081268311</t>
@@ -3500,46 +3500,46 @@
     <t xml:space="preserve">15.2591419219971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3475065231323</t>
+    <t xml:space="preserve">15.347508430481</t>
   </si>
   <si>
     <t xml:space="preserve">15.2430753707886</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2511081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.279224395752</t>
+    <t xml:space="preserve">15.25110912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2792263031006</t>
   </si>
   <si>
     <t xml:space="preserve">15.38365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3716058731079</t>
+    <t xml:space="preserve">15.3716068267822</t>
   </si>
   <si>
     <t xml:space="preserve">15.4559545516968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0743770599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6887807846069</t>
+    <t xml:space="preserve">15.0743780136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6887817382812</t>
   </si>
   <si>
     <t xml:space="preserve">14.7811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7570638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168979644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1867027282715</t>
+    <t xml:space="preserve">14.7570648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168989181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1867036819458</t>
   </si>
   <si>
     <t xml:space="preserve">14.299168586731</t>
@@ -3548,94 +3548,94 @@
     <t xml:space="preserve">14.2429361343384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642652511597</t>
+    <t xml:space="preserve">14.564266204834</t>
   </si>
   <si>
     <t xml:space="preserve">14.4919672012329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6124649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.022162437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.857479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297780990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8614959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6767320632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731294631958</t>
+    <t xml:space="preserve">14.6124658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498605728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0221614837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8574800491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6767311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731313705444</t>
   </si>
   <si>
     <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9016618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060958862305</t>
+    <t xml:space="preserve">14.9016609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060930252075</t>
   </si>
   <si>
     <t xml:space="preserve">14.9659271240234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2671747207642</t>
+    <t xml:space="preserve">15.2671737670898</t>
   </si>
   <si>
     <t xml:space="preserve">15.1788082122803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8333787918091</t>
+    <t xml:space="preserve">14.8333806991577</t>
   </si>
   <si>
     <t xml:space="preserve">14.9177274703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8293628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337949752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0583095550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422449111938</t>
+    <t xml:space="preserve">14.8293619155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337959289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.058310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422439575195</t>
   </si>
   <si>
     <t xml:space="preserve">14.8132972717285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9257612228394</t>
+    <t xml:space="preserve">14.9257621765137</t>
   </si>
   <si>
     <t xml:space="preserve">15.1466751098633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0382251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627416610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3754863739014</t>
+    <t xml:space="preserve">15.0382261276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627435684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3754844665527</t>
   </si>
   <si>
     <t xml:space="preserve">14.4999990463257</t>
@@ -3644,13 +3644,13 @@
     <t xml:space="preserve">14.6847648620605</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6727132797241</t>
+    <t xml:space="preserve">14.6727142333984</t>
   </si>
   <si>
     <t xml:space="preserve">14.9940462112427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7369813919067</t>
+    <t xml:space="preserve">14.7369794845581</t>
   </si>
   <si>
     <t xml:space="preserve">14.9819946289062</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">14.596399307251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0300540924072</t>
+    <t xml:space="preserve">14.0300559997559</t>
   </si>
   <si>
     <t xml:space="preserve">14.371467590332</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">13.0379495620728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7447376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.993766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6243753433228</t>
+    <t xml:space="preserve">12.7447366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9937658309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6243762969971</t>
   </si>
   <si>
     <t xml:space="preserve">13.4958448410034</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">14.174654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3875341415405</t>
+    <t xml:space="preserve">14.3875350952148</t>
   </si>
   <si>
     <t xml:space="preserve">15.0824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0502767562866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1667585372925</t>
+    <t xml:space="preserve">15.0502786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1667594909668</t>
   </si>
   <si>
     <t xml:space="preserve">15.3153743743896</t>
@@ -3728,40 +3728,40 @@
     <t xml:space="preserve">15.6005544662476</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1789455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8495836257935</t>
+    <t xml:space="preserve">16.1789474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8495845794678</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6850414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3074798583984</t>
+    <t xml:space="preserve">16.6850433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9581718444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3074779510498</t>
   </si>
   <si>
     <t xml:space="preserve">16.235179901123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0504169464111</t>
+    <t xml:space="preserve">16.0504150390625</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7331008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6166210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4840726852417</t>
+    <t xml:space="preserve">15.7331027984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6166219711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840717315674</t>
   </si>
   <si>
     <t xml:space="preserve">15.4117727279663</t>
@@ -3773,28 +3773,28 @@
     <t xml:space="preserve">14.9980611801147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7932147979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5441827774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4598350524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5401659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196672439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7048482894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6204996109009</t>
+    <t xml:space="preserve">14.7932138442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5441818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4598331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5401668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196691513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7048473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204986572266</t>
   </si>
   <si>
     <t xml:space="preserve">14.4518013000488</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268705368042</t>
+    <t xml:space="preserve">14.2268686294556</t>
   </si>
   <si>
     <t xml:space="preserve">14.2670373916626</t>
@@ -3815,28 +3815,28 @@
     <t xml:space="preserve">14.1947364807129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3112201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4558172225952</t>
+    <t xml:space="preserve">14.3112192153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4558181762695</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7547550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8230848312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8828716278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5882043838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5540390014648</t>
+    <t xml:space="preserve">14.7547540664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8230838775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8828706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5882034301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5540409088135</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
@@ -3845,10 +3845,10 @@
     <t xml:space="preserve">14.4430055618286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3789472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2764530181885</t>
+    <t xml:space="preserve">14.3789463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2764539718628</t>
   </si>
   <si>
     <t xml:space="preserve">14.4643564224243</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344388961792</t>
+    <t xml:space="preserve">13.3924503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881797790527</t>
+    <t xml:space="preserve">13.3881788253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3884,16 +3884,16 @@
     <t xml:space="preserve">13.5803537368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3967208862305</t>
+    <t xml:space="preserve">13.3967199325562</t>
   </si>
   <si>
     <t xml:space="preserve">13.2557926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828470230103</t>
+    <t xml:space="preserve">13.1917333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828479766846</t>
   </si>
   <si>
     <t xml:space="preserve">13.2686033248901</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038299560547</t>
+    <t xml:space="preserve">13.0038290023804</t>
   </si>
   <si>
     <t xml:space="preserve">13.2942266464233</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">13.1661100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4187631607056</t>
+    <t xml:space="preserve">12.4187641143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596923828125</t>
@@ -3926,28 +3926,28 @@
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568538665771</t>
+    <t xml:space="preserve">12.9568529129028</t>
   </si>
   <si>
     <t xml:space="preserve">12.995288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7774896621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3547048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4401159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230346679688</t>
+    <t xml:space="preserve">12.7774906158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3547058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4401168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230337142944</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838846206665</t>
+    <t xml:space="preserve">12.1838836669922</t>
   </si>
   <si>
     <t xml:space="preserve">12.1625299453735</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">12.3333530426025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4571981430054</t>
+    <t xml:space="preserve">12.4571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134323120117</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4700107574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5340690612793</t>
+    <t xml:space="preserve">12.470009803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.534068107605</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408319473267</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">12.8458185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141483306885</t>
+    <t xml:space="preserve">12.9141473770142</t>
   </si>
   <si>
     <t xml:space="preserve">13.0508050918579</t>
@@ -4001,19 +4001,19 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618385314941</t>
+    <t xml:space="preserve">13.1618394851685</t>
   </si>
   <si>
     <t xml:space="preserve">12.897066116333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7646789550781</t>
+    <t xml:space="preserve">12.7646780014038</t>
   </si>
   <si>
     <t xml:space="preserve">12.7006206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8757123947144</t>
+    <t xml:space="preserve">12.8757133483887</t>
   </si>
   <si>
     <t xml:space="preserve">12.576774597168</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">12.6579141616821</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5041751861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3931398391724</t>
+    <t xml:space="preserve">12.5041761398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3931407928467</t>
   </si>
   <si>
     <t xml:space="preserve">12.8330068588257</t>
@@ -4043,13 +4043,13 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.768949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1703805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9696645736694</t>
+    <t xml:space="preserve">12.7689485549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1703815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9696655273438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0892400741577</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.704891204834</t>
+    <t xml:space="preserve">12.7048902511597</t>
   </si>
   <si>
     <t xml:space="preserve">12.7390546798706</t>
@@ -4085,55 +4085,55 @@
     <t xml:space="preserve">12.3845996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1326370239258</t>
+    <t xml:space="preserve">12.1326360702515</t>
   </si>
   <si>
     <t xml:space="preserve">11.8550519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.73974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575433731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7909936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0045204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1582593917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2991876602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3632469177246</t>
+    <t xml:space="preserve">11.7397451400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7909927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0045213699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.158260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2991886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3632478713989</t>
   </si>
   <si>
     <t xml:space="preserve">12.5169858932495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3376235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6749973297119</t>
+    <t xml:space="preserve">12.3376226425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6749963760376</t>
   </si>
   <si>
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091608047485</t>
+    <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.973934173584</t>
+    <t xml:space="preserve">12.9739351272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.0977811813354</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">13.0251817703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.153299331665</t>
+    <t xml:space="preserve">13.1532983779907</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">13.8493986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9433507919312</t>
+    <t xml:space="preserve">13.9433517456055</t>
   </si>
   <si>
     <t xml:space="preserve">14.2294778823853</t>
@@ -4160,22 +4160,22 @@
     <t xml:space="preserve">14.4045705795288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6095561981201</t>
+    <t xml:space="preserve">14.6095571517944</t>
   </si>
   <si>
     <t xml:space="preserve">14.5839338302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.515604019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.741943359375</t>
+    <t xml:space="preserve">14.5156059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7419443130493</t>
   </si>
   <si>
     <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5027923583984</t>
+    <t xml:space="preserve">14.5027914047241</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600877761841</t>
@@ -4184,10 +4184,10 @@
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686298370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6266393661499</t>
+    <t xml:space="preserve">14.4686288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6266374588013</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163200378418</t>
@@ -4202,28 +4202,28 @@
     <t xml:space="preserve">14.7931909561157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6906976699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7889204025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7462139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8444366455078</t>
+    <t xml:space="preserve">14.6906967163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7889194488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7462129592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999538421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8444356918335</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2508306503296</t>
+    <t xml:space="preserve">14.0928192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2508296966553</t>
   </si>
   <si>
     <t xml:space="preserve">14.2892637252808</t>
@@ -4232,37 +4232,37 @@
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3490533828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3106184005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.259370803833</t>
+    <t xml:space="preserve">14.3490524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3106174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2593717575073</t>
   </si>
   <si>
     <t xml:space="preserve">14.3618650436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1910429000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3276996612549</t>
+    <t xml:space="preserve">14.1910419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3277006149292</t>
   </si>
   <si>
     <t xml:space="preserve">14.3917589187622</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7504844665527</t>
+    <t xml:space="preserve">14.7504854202271</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6736164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017320632935</t>
+    <t xml:space="preserve">14.6736154556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017311096191</t>
   </si>
   <si>
     <t xml:space="preserve">14.8615198135376</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">14.8487071990967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9554710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9682817459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8358974456787</t>
+    <t xml:space="preserve">14.9554719924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8358964920044</t>
   </si>
   <si>
     <t xml:space="preserve">15.168999671936</t>
@@ -4289,79 +4289,79 @@
     <t xml:space="preserve">15.3013868331909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2586803436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270092010498</t>
+    <t xml:space="preserve">15.2586793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971162796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270101547241</t>
   </si>
   <si>
     <t xml:space="preserve">15.3825263977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.28857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5021018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.416690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4679374694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4636669158936</t>
+    <t xml:space="preserve">15.2885732650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319948196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4679384231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4636659622192</t>
   </si>
   <si>
     <t xml:space="preserve">15.5063734054565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5618906021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6003255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686525344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473016738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6857347488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850196838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106449127197</t>
+    <t xml:space="preserve">15.5618896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.587513923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344900131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850206375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106420516968</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9804019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223915100098</t>
+    <t xml:space="preserve">15.9804029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223934173584</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4373,31 +4373,31 @@
     <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0658130645752</t>
+    <t xml:space="preserve">16.0658149719238</t>
   </si>
   <si>
     <t xml:space="preserve">15.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7327108383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.203161239624</t>
+    <t xml:space="preserve">15.7327117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2031631469727</t>
   </si>
   <si>
     <t xml:space="preserve">15.7540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8316259384155</t>
+    <t xml:space="preserve">14.8316249847412</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4508562088013</t>
+    <t xml:space="preserve">15.0451536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.450855255127</t>
   </si>
   <si>
     <t xml:space="preserve">15.4081497192383</t>
@@ -4409,25 +4409,25 @@
     <t xml:space="preserve">15.2501392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4423151016235</t>
+    <t xml:space="preserve">15.4423131942749</t>
   </si>
   <si>
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985473632812</t>
+    <t xml:space="preserve">15.6985464096069</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.621678352356</t>
+    <t xml:space="preserve">15.6216793060303</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437471389771</t>
+    <t xml:space="preserve">15.8437461853027</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">16.1683082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.040189743042</t>
+    <t xml:space="preserve">16.0401916503906</t>
   </si>
   <si>
     <t xml:space="preserve">16.1384143829346</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">16.2836132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3049659729004</t>
+    <t xml:space="preserve">16.3049640655518</t>
   </si>
   <si>
     <t xml:space="preserve">16.3092365264893</t>
@@ -4463,16 +4463,16 @@
     <t xml:space="preserve">16.1298732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2323665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1256008148193</t>
+    <t xml:space="preserve">16.232364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.125602722168</t>
   </si>
   <si>
     <t xml:space="preserve">15.8693695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9334297180176</t>
+    <t xml:space="preserve">15.9334278106689</t>
   </si>
   <si>
     <t xml:space="preserve">15.8053112030029</t>
@@ -4484,19 +4484,19 @@
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890721321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1127910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0316505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9120721817017</t>
+    <t xml:space="preserve">15.8907203674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1127891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0316524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.912073135376</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">16.4688701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596549987793</t>
+    <t xml:space="preserve">16.2596569061279</t>
   </si>
   <si>
     <t xml:space="preserve">16.332426071167</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">16.4188404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5189018249512</t>
+    <t xml:space="preserve">16.5188999176025</t>
   </si>
   <si>
     <t xml:space="preserve">16.6462478637695</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">16.9236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1010627746582</t>
+    <t xml:space="preserve">17.1010646820068</t>
   </si>
   <si>
     <t xml:space="preserve">17.2193164825439</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">16.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7963371276855</t>
+    <t xml:space="preserve">16.7963390350342</t>
   </si>
   <si>
     <t xml:space="preserve">16.6689910888672</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.6280574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235679626465</t>
+    <t xml:space="preserve">16.7235660552979</t>
   </si>
   <si>
     <t xml:space="preserve">16.6917304992676</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">16.9373321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5103969573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4330806732178</t>
+    <t xml:space="preserve">17.5103988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4330787658691</t>
   </si>
   <si>
     <t xml:space="preserve">17.2056732177734</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">17.1783828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0692253112793</t>
+    <t xml:space="preserve">17.1920261383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0692272186279</t>
   </si>
   <si>
     <t xml:space="preserve">17.2829914093018</t>
@@ -4616,13 +4616,13 @@
     <t xml:space="preserve">17.3648567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3739528656006</t>
+    <t xml:space="preserve">17.3739547729492</t>
   </si>
   <si>
     <t xml:space="preserve">17.3330192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3284721374512</t>
+    <t xml:space="preserve">17.3284702301025</t>
   </si>
   <si>
     <t xml:space="preserve">17.5149459838867</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">17.5240421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6286506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4057903289795</t>
+    <t xml:space="preserve">17.6286487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4057922363281</t>
   </si>
   <si>
     <t xml:space="preserve">17.037389755249</t>
@@ -4649,16 +4649,16 @@
     <t xml:space="preserve">17.091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7190189361572</t>
+    <t xml:space="preserve">16.9737167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7190170288086</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8736572265625</t>
+    <t xml:space="preserve">16.8736553192139</t>
   </si>
   <si>
     <t xml:space="preserve">16.7417602539062</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">16.7645015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281745910645</t>
+    <t xml:space="preserve">16.8281764984131</t>
   </si>
   <si>
     <t xml:space="preserve">16.8418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9282360076904</t>
+    <t xml:space="preserve">16.9282341003418</t>
   </si>
   <si>
     <t xml:space="preserve">17.0737762451172</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">17.442174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4012413024902</t>
+    <t xml:space="preserve">17.4012432098389</t>
   </si>
   <si>
     <t xml:space="preserve">17.292085647583</t>
@@ -4691,13 +4691,13 @@
     <t xml:space="preserve">17.3011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6013622283936</t>
+    <t xml:space="preserve">17.6013603210449</t>
   </si>
   <si>
     <t xml:space="preserve">17.7150650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7332592010498</t>
+    <t xml:space="preserve">17.7332572937012</t>
   </si>
   <si>
     <t xml:space="preserve">18.0197906494141</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">18.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1926231384277</t>
+    <t xml:space="preserve">18.1926212310791</t>
   </si>
   <si>
     <t xml:space="preserve">18.0470809936523</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">17.7878360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059074401855</t>
+    <t xml:space="preserve">17.6059093475342</t>
   </si>
   <si>
     <t xml:space="preserve">17.6832294464111</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">16.8918476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3239250183105</t>
+    <t xml:space="preserve">17.3239231109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.4876575469971</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">17.0510349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2966346740723</t>
+    <t xml:space="preserve">17.2966327667236</t>
   </si>
   <si>
     <t xml:space="preserve">17.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1238040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1465473175049</t>
+    <t xml:space="preserve">17.1238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1465454101562</t>
   </si>
   <si>
     <t xml:space="preserve">17.2511539459229</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">17.8787994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8151226043701</t>
+    <t xml:space="preserve">17.8151245117188</t>
   </si>
   <si>
     <t xml:space="preserve">17.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4922065734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3148288726807</t>
+    <t xml:space="preserve">17.4922046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">17.187479019165</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">17.242057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.141996383667</t>
+    <t xml:space="preserve">17.1419982910156</t>
   </si>
   <si>
     <t xml:space="preserve">17.2284126281738</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">17.4103393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4148864746094</t>
+    <t xml:space="preserve">17.414888381958</t>
   </si>
   <si>
     <t xml:space="preserve">17.496753692627</t>
@@ -4895,13 +4895,13 @@
     <t xml:space="preserve">17.9561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0061473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9015407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9515686035156</t>
+    <t xml:space="preserve">18.0061454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.901538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9515705108643</t>
   </si>
   <si>
     <t xml:space="preserve">17.9379234313965</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">18.6201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5473766326904</t>
+    <t xml:space="preserve">18.5473785400391</t>
   </si>
   <si>
     <t xml:space="preserve">18.5655708312988</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">18.6656303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6929168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8202667236328</t>
+    <t xml:space="preserve">18.6929187774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8202686309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.629243850708</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">18.7565937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6838226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.729305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5564727783203</t>
+    <t xml:space="preserve">18.6838245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7293033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5564746856689</t>
   </si>
   <si>
     <t xml:space="preserve">18.8384590148926</t>
@@ -4985,25 +4985,25 @@
     <t xml:space="preserve">19.5024909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1392307281494</t>
+    <t xml:space="preserve">20.139232635498</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9118251800537</t>
+    <t xml:space="preserve">19.9118232727051</t>
   </si>
   <si>
     <t xml:space="preserve">19.9664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0027866363525</t>
+    <t xml:space="preserve">20.0027885437012</t>
   </si>
   <si>
     <t xml:space="preserve">20.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1574249267578</t>
+    <t xml:space="preserve">20.1574230194092</t>
   </si>
   <si>
     <t xml:space="preserve">20.0755577087402</t>
@@ -5012,16 +5012,16 @@
     <t xml:space="preserve">20.2120018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2847709655762</t>
+    <t xml:space="preserve">20.2847728729248</t>
   </si>
   <si>
     <t xml:space="preserve">20.393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5940475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6122417449951</t>
+    <t xml:space="preserve">20.5940456390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6122398376465</t>
   </si>
   <si>
     <t xml:space="preserve">20.6759147644043</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">21.1034412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3399448394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127159118652</t>
+    <t xml:space="preserve">21.3399429321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127178192139</t>
   </si>
   <si>
     <t xml:space="preserve">21.5309677124023</t>
@@ -5060,10 +5060,10 @@
     <t xml:space="preserve">20.8669376373291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0306720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7304935455322</t>
+    <t xml:space="preserve">21.0306701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7304916381836</t>
   </si>
   <si>
     <t xml:space="preserve">20.7577800750732</t>
@@ -5072,13 +5072,13 @@
     <t xml:space="preserve">20.6031436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7032032012939</t>
+    <t xml:space="preserve">20.7032051086426</t>
   </si>
   <si>
     <t xml:space="preserve">20.3393516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4394092559814</t>
+    <t xml:space="preserve">20.4394111633301</t>
   </si>
   <si>
     <t xml:space="preserve">20.4939880371094</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">20.6213359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7122993469238</t>
+    <t xml:space="preserve">20.7123012542725</t>
   </si>
   <si>
     <t xml:space="preserve">21.003381729126</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">21.2307891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7765693664551</t>
+    <t xml:space="preserve">21.7765674591064</t>
   </si>
   <si>
     <t xml:space="preserve">21.7401809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9039173126221</t>
+    <t xml:space="preserve">21.9039154052734</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949977874756</t>
@@ -6045,6 +6045,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.2799987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.560001373291</t>
   </si>
 </sst>
 </file>
@@ -71227,7 +71230,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6496064815</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>1372960</v>
@@ -71248,6 +71251,32 @@
         <v>2010</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6496412037</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>2482109</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>32.7799987792969</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>32.2200012207031</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>32.3800010681152</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>32.560001373291</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2011</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="2014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="2015">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21390151977539</t>
+    <t xml:space="preserve">9.21390056610107</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31058883666992</t>
+    <t xml:space="preserve">9.31059074401855</t>
   </si>
   <si>
     <t xml:space="preserve">9.13427352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11721134185791</t>
+    <t xml:space="preserve">9.11721038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.02052307128906</t>
@@ -62,49 +62,49 @@
     <t xml:space="preserve">8.88970756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0660228729248</t>
+    <t xml:space="preserve">9.06602096557617</t>
   </si>
   <si>
     <t xml:space="preserve">8.95795822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75889110565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120227813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376522064209</t>
+    <t xml:space="preserve">8.75889205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376808166504</t>
   </si>
   <si>
     <t xml:space="preserve">8.29251003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44607448577881</t>
+    <t xml:space="preserve">8.44607543945312</t>
   </si>
   <si>
     <t xml:space="preserve">8.48588848114014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30957221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04794406890869</t>
+    <t xml:space="preserve">8.30957126617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04794311523438</t>
   </si>
   <si>
     <t xml:space="preserve">7.93987941741943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61568737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668888092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41662120819092</t>
+    <t xml:space="preserve">7.61568641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84318971633911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662073135376</t>
   </si>
   <si>
     <t xml:space="preserve">7.23461818695068</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">7.1549916267395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96161317825317</t>
+    <t xml:space="preserve">6.96161270141602</t>
   </si>
   <si>
     <t xml:space="preserve">6.74548482894897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47247982025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8137354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23360157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34166526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59760808944702</t>
+    <t xml:space="preserve">6.47248077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81373643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23360109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34166574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59760713577271</t>
   </si>
   <si>
     <t xml:space="preserve">6.62035799026489</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">6.77392244338989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66017007827759</t>
+    <t xml:space="preserve">6.72842073440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6601710319519</t>
   </si>
   <si>
     <t xml:space="preserve">6.89904975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89336347579956</t>
+    <t xml:space="preserve">6.89336252212524</t>
   </si>
   <si>
     <t xml:space="preserve">6.95592546463013</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">7.26305627822876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28580570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268188476562</t>
+    <t xml:space="preserve">7.28580617904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268236160278</t>
   </si>
   <si>
     <t xml:space="preserve">7.45643329620361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45074605941772</t>
+    <t xml:space="preserve">7.45074701309204</t>
   </si>
   <si>
     <t xml:space="preserve">7.37680721282959</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">7.24599361419678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37112045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575408935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750200271606</t>
+    <t xml:space="preserve">7.31993246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37111902236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750343322754</t>
   </si>
   <si>
     <t xml:space="preserve">7.79200172424316</t>
@@ -197,292 +197,292 @@
     <t xml:space="preserve">7.87731647491455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89437913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356315612793</t>
+    <t xml:space="preserve">7.89437866210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356506347656</t>
   </si>
   <si>
     <t xml:space="preserve">7.67256259918213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57587432861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543369293213</t>
+    <t xml:space="preserve">7.57587337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037214279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543226242065</t>
   </si>
   <si>
     <t xml:space="preserve">7.42799663543701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48487091064453</t>
+    <t xml:space="preserve">7.48487234115601</t>
   </si>
   <si>
     <t xml:space="preserve">7.41093349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755456924438</t>
+    <t xml:space="preserve">7.30286836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2175555229187</t>
   </si>
   <si>
     <t xml:space="preserve">6.98436403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00711441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85354900360107</t>
+    <t xml:space="preserve">7.00711393356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85355043411255</t>
   </si>
   <si>
     <t xml:space="preserve">7.05261468887329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13792943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067838668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4336838722229</t>
+    <t xml:space="preserve">7.13792896270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067934036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43368339538574</t>
   </si>
   <si>
     <t xml:space="preserve">7.49624681472778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4791841506958</t>
+    <t xml:space="preserve">7.47918319702148</t>
   </si>
   <si>
     <t xml:space="preserve">7.54743576049805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59862327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75218963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181428909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456466674805</t>
+    <t xml:space="preserve">7.59862422943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218915939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456562042236</t>
   </si>
   <si>
     <t xml:space="preserve">7.8033766746521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77493906021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018709182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35405731201172</t>
+    <t xml:space="preserve">7.7749400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018661499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35405778884888</t>
   </si>
   <si>
     <t xml:space="preserve">7.53606033325195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08105182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05830240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25168037414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798934936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84845161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90873098373413</t>
+    <t xml:space="preserve">7.08105230331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1663670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0583028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517763137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25167989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90873241424561</t>
   </si>
   <si>
     <t xml:space="preserve">7.94490051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85447978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228446960449</t>
+    <t xml:space="preserve">7.85448026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228351593018</t>
   </si>
   <si>
     <t xml:space="preserve">7.76405954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54705286026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.534996509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158485412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625677108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77008819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42046499252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17934417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97439289093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40840816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54102325439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58322095870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257293701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02498340606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11841630935669</t>
+    <t xml:space="preserve">7.54705190658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53499603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158533096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625629425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77008771896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42046594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17934465408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439336776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850511550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92014074325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1914005279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40840911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54102468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58257246017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02498388290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11841726303101</t>
   </si>
   <si>
     <t xml:space="preserve">6.26308917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35953664779663</t>
+    <t xml:space="preserve">6.35953760147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.43187284469604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25103330612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13047361373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91647863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92853450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790149688721</t>
+    <t xml:space="preserve">6.25103425979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1304726600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91647815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92853546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790054321289</t>
   </si>
   <si>
     <t xml:space="preserve">6.76341342926025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69710350036621</t>
+    <t xml:space="preserve">6.69710445404053</t>
   </si>
   <si>
     <t xml:space="preserve">6.87191581726074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80560874938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177589416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738477706909</t>
+    <t xml:space="preserve">6.80560779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84177684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738525390625</t>
   </si>
   <si>
     <t xml:space="preserve">6.8478045463562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77546834945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73327302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68504810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81163835525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62476873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10098028182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083940505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79355239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06481122970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948362350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387760162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808486938477</t>
+    <t xml:space="preserve">6.7754693031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73327207565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68504858016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81163692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476968765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10098075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07084035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7935528755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2094841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289575576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000177383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808439254761</t>
   </si>
   <si>
     <t xml:space="preserve">6.7393012046814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04069995880127</t>
+    <t xml:space="preserve">7.04070091247559</t>
   </si>
   <si>
     <t xml:space="preserve">7.01658916473389</t>
@@ -491,157 +491,157 @@
     <t xml:space="preserve">6.81766510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74532890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149747848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425392150879</t>
+    <t xml:space="preserve">6.74532794952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425249099731</t>
   </si>
   <si>
     <t xml:space="preserve">6.99247789382935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93822431564331</t>
+    <t xml:space="preserve">6.93822479248047</t>
   </si>
   <si>
     <t xml:space="preserve">6.88397312164307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98042249679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523290634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313215255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079643249512</t>
+    <t xml:space="preserve">6.98042058944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770998001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079738616943</t>
   </si>
   <si>
     <t xml:space="preserve">6.72724437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7995810508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75135660171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59462976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56448888778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57654476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668516159058</t>
+    <t xml:space="preserve">6.79957962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75135707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59462928771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56448936462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57654523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668563842773</t>
   </si>
   <si>
     <t xml:space="preserve">6.54640436172485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51626491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49818086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76944065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986042022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18537187576294</t>
+    <t xml:space="preserve">6.51626586914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49818181991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18537330627441</t>
   </si>
   <si>
     <t xml:space="preserve">7.1672887802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19742774963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26976633071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33004474639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31196165084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317655563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09495258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98644924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299127578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574819564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08892488479614</t>
+    <t xml:space="preserve">7.19742870330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784894943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33004426956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31196117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317750930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0949535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98644876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686853408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87794494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02261734008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82369232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35415697097778</t>
+    <t xml:space="preserve">6.87794399261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02261686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82369327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35415649414062</t>
   </si>
   <si>
     <t xml:space="preserve">7.73392009735107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30055332183838</t>
+    <t xml:space="preserve">8.30055236816406</t>
   </si>
   <si>
     <t xml:space="preserve">8.6803150177002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45125198364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47536373138428</t>
+    <t xml:space="preserve">8.45125102996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47536468505859</t>
   </si>
   <si>
     <t xml:space="preserve">8.41508388519287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33069133758545</t>
+    <t xml:space="preserve">8.33069229125977</t>
   </si>
   <si>
     <t xml:space="preserve">8.54167175292969</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">8.58386707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59592437744141</t>
+    <t xml:space="preserve">8.59592342376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.6622314453125</t>
@@ -665,40 +665,40 @@
     <t xml:space="preserve">8.66826057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55372714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50550365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5115327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017604827881</t>
+    <t xml:space="preserve">8.5537281036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51153182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017700195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.71045589447021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75265121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69839859008789</t>
+    <t xml:space="preserve">8.75265216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69840145111084</t>
   </si>
   <si>
     <t xml:space="preserve">8.71648502349854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52358913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48741912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38494396209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25835514068604</t>
+    <t xml:space="preserve">8.52358722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48742008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38494491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25835609436035</t>
   </si>
   <si>
     <t xml:space="preserve">8.23424530029297</t>
@@ -707,43 +707,43 @@
     <t xml:space="preserve">8.16793727874756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27041053771973</t>
+    <t xml:space="preserve">8.27041244506836</t>
   </si>
   <si>
     <t xml:space="preserve">8.26438331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58989715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29517078399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42176055908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28311538696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98774242401123</t>
+    <t xml:space="preserve">8.5898962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2951717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38559150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42175960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28311634063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98774337768555</t>
   </si>
   <si>
     <t xml:space="preserve">8.88526725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84910011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00582790374756</t>
+    <t xml:space="preserve">8.84909915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00582695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.02994060516357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8189582824707</t>
+    <t xml:space="preserve">8.81896018981934</t>
   </si>
   <si>
     <t xml:space="preserve">8.77073574066162</t>
@@ -752,73 +752,73 @@
     <t xml:space="preserve">8.67428779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74059581756592</t>
+    <t xml:space="preserve">8.7405948638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.90335273742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04802513122559</t>
+    <t xml:space="preserve">9.04802417755127</t>
   </si>
   <si>
     <t xml:space="preserve">8.87924003601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90937995910645</t>
+    <t xml:space="preserve">8.90938091278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.95760440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83101463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81293201446533</t>
+    <t xml:space="preserve">8.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81293296813965</t>
   </si>
   <si>
     <t xml:space="preserve">8.74662303924561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65620517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49947643280029</t>
+    <t xml:space="preserve">8.65620231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49947834014893</t>
   </si>
   <si>
     <t xml:space="preserve">8.14985179901123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27643871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54770088195801</t>
+    <t xml:space="preserve">8.27644062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54769897460938</t>
   </si>
   <si>
     <t xml:space="preserve">8.46330738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56578350067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78881931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80087661743164</t>
+    <t xml:space="preserve">8.5657844543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78882026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80087566375732</t>
   </si>
   <si>
     <t xml:space="preserve">8.79484748840332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78279113769531</t>
+    <t xml:space="preserve">8.78279209136963</t>
   </si>
   <si>
     <t xml:space="preserve">8.86718368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98171710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80690288543701</t>
+    <t xml:space="preserve">8.98171615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80690479278564</t>
   </si>
   <si>
     <t xml:space="preserve">8.63209056854248</t>
@@ -827,31 +827,31 @@
     <t xml:space="preserve">8.6079797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46933650970459</t>
+    <t xml:space="preserve">8.46933555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93349170684814</t>
+    <t xml:space="preserve">8.93349075317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.75867938995361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87321186065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04199600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19269561767578</t>
+    <t xml:space="preserve">8.87321090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04199504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19269466400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.21077919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24091911315918</t>
+    <t xml:space="preserve">9.2409200668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.2168083190918</t>
@@ -863,70 +863,70 @@
     <t xml:space="preserve">8.89129543304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03596782684326</t>
+    <t xml:space="preserve">9.03596687316895</t>
   </si>
   <si>
     <t xml:space="preserve">9.07213592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12035846710205</t>
+    <t xml:space="preserve">9.12036037445068</t>
   </si>
   <si>
     <t xml:space="preserve">9.304931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33675289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18400382995605</t>
+    <t xml:space="preserve">9.33675193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18400573730469</t>
   </si>
   <si>
     <t xml:space="preserve">9.15854740142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13308811187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851779937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83395576477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94215393066406</t>
+    <t xml:space="preserve">9.13308906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83395671844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94215297698975</t>
   </si>
   <si>
     <t xml:space="preserve">9.03762054443359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81486415863037</t>
+    <t xml:space="preserve">8.81486225128174</t>
   </si>
   <si>
     <t xml:space="preserve">8.75758171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73848724365234</t>
+    <t xml:space="preserve">8.73848819732666</t>
   </si>
   <si>
     <t xml:space="preserve">8.89123630523682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95488166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05035018920898</t>
+    <t xml:space="preserve">8.95488262176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0503511428833</t>
   </si>
   <si>
     <t xml:space="preserve">9.22855758666992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23491954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1712760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28583717346191</t>
+    <t xml:space="preserve">9.2349214553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17127513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28583812713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.29856586456299</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">9.3494815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25401306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12036037445068</t>
+    <t xml:space="preserve">9.25401496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219276428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.120361328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.24765014648438</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">9.29220199584961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33038997650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38130474090576</t>
+    <t xml:space="preserve">9.33038902282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38130569458008</t>
   </si>
   <si>
     <t xml:space="preserve">9.57860565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54678249359131</t>
+    <t xml:space="preserve">9.54678344726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.54041767120361</t>
@@ -974,55 +974,55 @@
     <t xml:space="preserve">9.79499816894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85864448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68680191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56587505340576</t>
+    <t xml:space="preserve">9.85864353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68680286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56587696075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.52768993377686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75681209564209</t>
+    <t xml:space="preserve">9.75681304931641</t>
   </si>
   <si>
     <t xml:space="preserve">9.77590560913086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80136203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0877676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1386842727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2341508865356</t>
+    <t xml:space="preserve">9.80136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750379562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1386833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.23415184021</t>
   </si>
   <si>
     <t xml:space="preserve">10.1959648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0623092651367</t>
+    <t xml:space="preserve">10.0623083114624</t>
   </si>
   <si>
     <t xml:space="preserve">10.0050277709961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82682228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86500930786133</t>
+    <t xml:space="preserve">9.82682132720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86500835418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.90319633483887</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">9.82045745849609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87137317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78226852416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71225929260254</t>
+    <t xml:space="preserve">9.87137508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78226757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71226119995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.69953060150146</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">9.68043804168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69316673278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53405475616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52132511138916</t>
+    <t xml:space="preserve">9.69316577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134357452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53405284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52132415771484</t>
   </si>
   <si>
     <t xml:space="preserve">9.57224082946777</t>
@@ -1067,40 +1067,40 @@
     <t xml:space="preserve">9.67407321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62952041625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59769725799561</t>
+    <t xml:space="preserve">9.62952136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59769916534424</t>
   </si>
   <si>
     <t xml:space="preserve">9.89046764373779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9477481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75044727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89683151245117</t>
+    <t xml:space="preserve">9.94774723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75044822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89683246612549</t>
   </si>
   <si>
     <t xml:space="preserve">9.91592502593994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8777379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0304861068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686740875244</t>
+    <t xml:space="preserve">9.87773895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686731338501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1323184967041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93501949310303</t>
+    <t xml:space="preserve">9.93501853942871</t>
   </si>
   <si>
     <t xml:space="preserve">9.84591579437256</t>
@@ -1109,37 +1109,37 @@
     <t xml:space="preserve">9.85227870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83318614959717</t>
+    <t xml:space="preserve">9.83318710327148</t>
   </si>
   <si>
     <t xml:space="preserve">9.72498893737793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9986629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96047592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0177564620972</t>
+    <t xml:space="preserve">9.99866485595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96047687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0177574157715</t>
   </si>
   <si>
     <t xml:space="preserve">9.9541130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1259536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0241222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94138431549072</t>
+    <t xml:space="preserve">10.1259546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0241212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94138240814209</t>
   </si>
   <si>
     <t xml:space="preserve">9.88410186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0368518829346</t>
+    <t xml:space="preserve">10.0368509292603</t>
   </si>
   <si>
     <t xml:space="preserve">9.78863525390625</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58496952056885</t>
+    <t xml:space="preserve">9.58497047424316</t>
   </si>
   <si>
     <t xml:space="preserve">9.61042881011963</t>
@@ -1160,28 +1160,28 @@
     <t xml:space="preserve">9.74408340454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73135375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80772972106934</t>
+    <t xml:space="preserve">9.73135471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.73771953582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5595121383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47677326202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97956943511963</t>
+    <t xml:space="preserve">9.70589542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55951118469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47677421569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97320652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97957038879395</t>
   </si>
   <si>
     <t xml:space="preserve">10.0814027786255</t>
@@ -1193,106 +1193,106 @@
     <t xml:space="preserve">10.2914323806763</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3041620254517</t>
+    <t xml:space="preserve">10.3041610717773</t>
   </si>
   <si>
     <t xml:space="preserve">10.2023286819458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3105268478394</t>
+    <t xml:space="preserve">10.3105249404907</t>
   </si>
   <si>
     <t xml:space="preserve">10.3232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641416549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1482305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99229907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76954078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86819171905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81727504730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77908802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80454540252686</t>
+    <t xml:space="preserve">10.1736879348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.148229598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99230003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7695426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86819076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81727600097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77908706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8140926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80454635620117</t>
   </si>
   <si>
     <t xml:space="preserve">9.36857604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85546207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74726390838623</t>
+    <t xml:space="preserve">9.65179634094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85546112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74726486206055</t>
   </si>
   <si>
     <t xml:space="preserve">10.0082120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98593425750732</t>
+    <t xml:space="preserve">9.98593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">9.92865467071533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94456577301025</t>
+    <t xml:space="preserve">9.94456481933594</t>
   </si>
   <si>
     <t xml:space="preserve">9.9700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0495796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1609592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3137083053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2946147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455305099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346323013306</t>
+    <t xml:space="preserve">10.049578666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1609601974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3137063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2946138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455295562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346332550049</t>
   </si>
   <si>
     <t xml:space="preserve">10.5301027297974</t>
   </si>
   <si>
-    <t xml:space="preserve">10.638298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.765588760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8546924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6319341659546</t>
+    <t xml:space="preserve">10.6382970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7655897140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8546934127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6319332122803</t>
   </si>
   <si>
     <t xml:space="preserve">10.7178544998169</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">10.5841999053955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6542100906372</t>
+    <t xml:space="preserve">10.6542081832886</t>
   </si>
   <si>
     <t xml:space="preserve">10.708309173584</t>
@@ -1316,25 +1316,25 @@
     <t xml:space="preserve">10.5269203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5396480560303</t>
+    <t xml:space="preserve">10.5396490097046</t>
   </si>
   <si>
     <t xml:space="preserve">10.4409980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5014629364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2977962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3328008651733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2596092224121</t>
+    <t xml:space="preserve">10.5014619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.297797203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.332802772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2596101760864</t>
   </si>
   <si>
     <t xml:space="preserve">10.2864847183228</t>
@@ -1349,43 +1349,43 @@
     <t xml:space="preserve">10.0143737792969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99421787261963</t>
+    <t xml:space="preserve">9.99421691894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.83968448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49702548980713</t>
+    <t xml:space="preserve">9.49702644348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.55413627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77585601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88335704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86991882324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65491580963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67843246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52054119110107</t>
+    <t xml:space="preserve">9.77585506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8699197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65491771697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67843151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52054214477539</t>
   </si>
   <si>
     <t xml:space="preserve">9.79937267303467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75233936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78257369995117</t>
+    <t xml:space="preserve">9.75234031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78257465362549</t>
   </si>
   <si>
     <t xml:space="preserve">9.90015411376953</t>
@@ -1394,43 +1394,43 @@
     <t xml:space="preserve">9.80608940124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76241779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82960510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69859027862549</t>
+    <t xml:space="preserve">9.76241683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8296070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69858932495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.76913547515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60116767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61796283721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52390098571777</t>
+    <t xml:space="preserve">9.60116577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61796379089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52390003204346</t>
   </si>
   <si>
     <t xml:space="preserve">9.51718235015869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61124610900879</t>
+    <t xml:space="preserve">9.61124515533447</t>
   </si>
   <si>
     <t xml:space="preserve">9.59108924865723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80945014953613</t>
+    <t xml:space="preserve">9.80945110321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.77249717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7288236618042</t>
+    <t xml:space="preserve">9.72882461547852</t>
   </si>
   <si>
     <t xml:space="preserve">9.65155792236328</t>
@@ -1445,25 +1445,25 @@
     <t xml:space="preserve">9.84976291656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85648059844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8161678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74897956848145</t>
+    <t xml:space="preserve">9.85648155212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81616973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74898052215576</t>
   </si>
   <si>
     <t xml:space="preserve">9.89007568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90351295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92366981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070217132568</t>
+    <t xml:space="preserve">9.9035120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92366886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070121765137</t>
   </si>
   <si>
     <t xml:space="preserve">10.0479679107666</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">10.2125768661499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.111795425415</t>
+    <t xml:space="preserve">10.1117963790894</t>
   </si>
   <si>
     <t xml:space="preserve">9.9539041519165</t>
@@ -1481,34 +1481,34 @@
     <t xml:space="preserve">10.0378885269165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0681247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748414993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86655902862549</t>
+    <t xml:space="preserve">10.0009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0681238174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916395187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748424530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8665599822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.71202659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73218154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312175750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92702770233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98077869415283</t>
+    <t xml:space="preserve">9.7321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85311985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92702865600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98077774047852</t>
   </si>
   <si>
     <t xml:space="preserve">9.92031097412109</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">9.63812065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76577758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93710708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96062278747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94382476806641</t>
+    <t xml:space="preserve">9.76577663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93710613250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96062183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94382572174072</t>
   </si>
   <si>
     <t xml:space="preserve">10.1621866226196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1017169952393</t>
+    <t xml:space="preserve">10.1017179489136</t>
   </si>
   <si>
     <t xml:space="preserve">10.0882797241211</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">10.1823434829712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2965631484985</t>
+    <t xml:space="preserve">10.2965612411499</t>
   </si>
   <si>
     <t xml:space="preserve">10.4141426086426</t>
@@ -1559,40 +1559,40 @@
     <t xml:space="preserve">10.3704700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9975757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88671588897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96734142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93038845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70866680145264</t>
+    <t xml:space="preserve">9.99757671356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88671684265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96734046936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93038749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70866775512695</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186973571777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59444808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50038623809814</t>
+    <t xml:space="preserve">9.59444904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50038528442383</t>
   </si>
   <si>
     <t xml:space="preserve">9.61460494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56421375274658</t>
+    <t xml:space="preserve">9.56421279907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.41304111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43991661071777</t>
+    <t xml:space="preserve">9.43991565704346</t>
   </si>
   <si>
     <t xml:space="preserve">9.40968132019043</t>
@@ -1607,76 +1607,76 @@
     <t xml:space="preserve">9.43655586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33241558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53397846221924</t>
+    <t xml:space="preserve">9.3324146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53397941589355</t>
   </si>
   <si>
     <t xml:space="preserve">9.66499614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62468433380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65827560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6347599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57429218292236</t>
+    <t xml:space="preserve">9.62468338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65827655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63476085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57429313659668</t>
   </si>
   <si>
     <t xml:space="preserve">9.71538639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51382350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59780693054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5574951171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57765197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8195276260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87663841247559</t>
+    <t xml:space="preserve">9.51382255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59780788421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55749416351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57765102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81952857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87663745880127</t>
   </si>
   <si>
     <t xml:space="preserve">9.9135913848877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0042943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.084921836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97406196594238</t>
+    <t xml:space="preserve">10.0042953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0849208831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97406101226807</t>
   </si>
   <si>
     <t xml:space="preserve">9.57093238830566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64483833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89679527282715</t>
+    <t xml:space="preserve">9.64484024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89679336547852</t>
   </si>
   <si>
     <t xml:space="preserve">9.85984134674072</t>
@@ -1688,37 +1688,37 @@
     <t xml:space="preserve">10.021092414856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0446090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647649765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327337265015</t>
+    <t xml:space="preserve">10.0446081161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647640228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327346801758</t>
   </si>
   <si>
     <t xml:space="preserve">10.3267965316772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3435945510864</t>
+    <t xml:space="preserve">10.3435955047607</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.333517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3133592605591</t>
+    <t xml:space="preserve">10.3335161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3133602142334</t>
   </si>
   <si>
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771886825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.276406288147</t>
+    <t xml:space="preserve">10.3771877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2764053344727</t>
   </si>
   <si>
     <t xml:space="preserve">10.1991405487061</t>
@@ -1730,58 +1730,58 @@
     <t xml:space="preserve">10.2932033538818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0714826583862</t>
+    <t xml:space="preserve">10.0714817047119</t>
   </si>
   <si>
     <t xml:space="preserve">10.1285924911499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2831258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.189061164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2293748855591</t>
+    <t xml:space="preserve">10.2058582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2831249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1890630722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2293758392334</t>
   </si>
   <si>
     <t xml:space="preserve">10.2260150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2730464935303</t>
+    <t xml:space="preserve">10.2730484008789</t>
   </si>
   <si>
     <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4275798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4342975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5451583862305</t>
+    <t xml:space="preserve">10.4275808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4342985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5451574325562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6089868545532</t>
   </si>
   <si>
-    <t xml:space="preserve">10.672815322876</t>
+    <t xml:space="preserve">10.6728162765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7400045394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5653162002563</t>
+    <t xml:space="preserve">10.7400035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.565315246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.6157054901123</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">10.5921907424927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.62242603302</t>
+    <t xml:space="preserve">10.6224241256714</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534408569336</t>
@@ -1799,31 +1799,31 @@
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725841522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0591459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0322713851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.069224357605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9852390289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9718027114868</t>
+    <t xml:space="preserve">11.0725831985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0591449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0322723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0692253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.985239982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9718017578125</t>
   </si>
   <si>
     <t xml:space="preserve">11.0087556838989</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0860233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2035999298096</t>
+    <t xml:space="preserve">11.0860223770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2036008834839</t>
   </si>
   <si>
     <t xml:space="preserve">11.1767263412476</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">11.2237577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1733655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2170372009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002420425415</t>
+    <t xml:space="preserve">11.1733665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002401351929</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271165847778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2976655960083</t>
+    <t xml:space="preserve">11.2976636886597</t>
   </si>
   <si>
     <t xml:space="preserve">11.3581342697144</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">11.4219617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5563383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521961212158</t>
+    <t xml:space="preserve">11.556339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521970748901</t>
   </si>
   <si>
     <t xml:space="preserve">11.4286804199219</t>
@@ -1871,22 +1871,22 @@
     <t xml:space="preserve">11.583212852478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.552978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6235265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6201667785645</t>
+    <t xml:space="preserve">11.5529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6235256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6201677322388</t>
   </si>
   <si>
     <t xml:space="preserve">11.6302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5261030197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824304580688</t>
+    <t xml:space="preserve">11.5261039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824323654175</t>
   </si>
   <si>
     <t xml:space="preserve">11.4689931869507</t>
@@ -1895,46 +1895,46 @@
     <t xml:space="preserve">11.3245401382446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3648529052734</t>
+    <t xml:space="preserve">11.3648538589478</t>
   </si>
   <si>
     <t xml:space="preserve">11.4152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5093059539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4253206253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5636587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.584942817688</t>
+    <t xml:space="preserve">11.5093050003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4253196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5636577606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5849409103394</t>
   </si>
   <si>
     <t xml:space="preserve">11.560112953186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3189067840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5459241867065</t>
+    <t xml:space="preserve">11.3189077377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5459222793579</t>
   </si>
   <si>
     <t xml:space="preserve">11.414680480957</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3330965042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2124929428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.148645401001</t>
+    <t xml:space="preserve">11.3330955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2124938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1486444473267</t>
   </si>
   <si>
     <t xml:space="preserve">11.1238145828247</t>
@@ -1943,40 +1943,40 @@
     <t xml:space="preserve">11.2727947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.180567741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2195863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2479629516602</t>
+    <t xml:space="preserve">11.1805696487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2195854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2479658126831</t>
   </si>
   <si>
     <t xml:space="preserve">11.3366432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4537000656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4288692474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4785289764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4466047286987</t>
+    <t xml:space="preserve">11.4536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4288682937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4785270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4466037750244</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175466537476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7445621490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8332414627075</t>
+    <t xml:space="preserve">11.7445640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119592666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8332424163818</t>
   </si>
   <si>
     <t xml:space="preserve">11.8403358459473</t>
@@ -1985,31 +1985,31 @@
     <t xml:space="preserve">11.7871284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7481088638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7126388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1063718795776</t>
+    <t xml:space="preserve">11.7481098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7126398086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7977705001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935422897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1312007904053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0708990097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1418409347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1773147583008</t>
+    <t xml:space="preserve">12.0708980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1418418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1773157119751</t>
   </si>
   <si>
     <t xml:space="preserve">12.2092370986938</t>
@@ -2018,31 +2018,31 @@
     <t xml:space="preserve">12.2056903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1560316085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1170120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9893159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247869491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0105991363525</t>
+    <t xml:space="preserve">12.1560306549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808605194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1170110702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.989315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.024787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105981826782</t>
   </si>
   <si>
     <t xml:space="preserve">12.0567111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9751262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.996410369873</t>
+    <t xml:space="preserve">11.9751272201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9964094161987</t>
   </si>
   <si>
     <t xml:space="preserve">11.8545246124268</t>
@@ -2057,19 +2057,19 @@
     <t xml:space="preserve">11.6629800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884895324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707540512085</t>
+    <t xml:space="preserve">11.5884885787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707530975342</t>
   </si>
   <si>
     <t xml:space="preserve">11.6594314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3437366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3792095184326</t>
+    <t xml:space="preserve">11.3437376022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3792085647583</t>
   </si>
   <si>
     <t xml:space="preserve">11.4430561065674</t>
@@ -2078,46 +2078,46 @@
     <t xml:space="preserve">11.2940769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4749813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5069046020508</t>
+    <t xml:space="preserve">11.4749803543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5069055557251</t>
   </si>
   <si>
     <t xml:space="preserve">11.6168661117554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5778474807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.467887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558847427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5388288497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6487903594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6842613220215</t>
+    <t xml:space="preserve">11.5778484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4678869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820756912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558856964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5388298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6487913131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6842603683472</t>
   </si>
   <si>
     <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7374706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9432020187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0921821594238</t>
+    <t xml:space="preserve">11.7374687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9432010650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
     <t xml:space="preserve">12.1347484588623</t>
@@ -2126,43 +2126,43 @@
     <t xml:space="preserve">12.2021436691284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1844081878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3014640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4149732589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3972368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2908220291138</t>
+    <t xml:space="preserve">12.1844072341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3014631271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4149723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3972358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2908210754395</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881017684937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.659725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6739139556885</t>
+    <t xml:space="preserve">12.6597232818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058362960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6739120483398</t>
   </si>
   <si>
     <t xml:space="preserve">12.7413082122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6987438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6703672409058</t>
+    <t xml:space="preserve">12.6987428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6703643798828</t>
   </si>
   <si>
     <t xml:space="preserve">12.6136121749878</t>
@@ -2171,118 +2171,118 @@
     <t xml:space="preserve">12.5852346420288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3759536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5213861465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6065187454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5887823104858</t>
+    <t xml:space="preserve">12.3759527206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5213851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.606517791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5887832641602</t>
   </si>
   <si>
     <t xml:space="preserve">12.6490821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6774606704712</t>
+    <t xml:space="preserve">12.6774597167969</t>
   </si>
   <si>
     <t xml:space="preserve">12.8157978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.744854927063</t>
+    <t xml:space="preserve">12.7448558807373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441743850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8477220535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8406267166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.035719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215291976929</t>
+    <t xml:space="preserve">12.8477230072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8406295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080219268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215320587158</t>
   </si>
   <si>
     <t xml:space="preserve">13.0463600158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0534553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0499086380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0286264419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9363985061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.893835067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1243991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1917934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422815322876</t>
+    <t xml:space="preserve">13.0534563064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0499095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0286254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9364023208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938341140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1243982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1917943954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422805786133</t>
   </si>
   <si>
     <t xml:space="preserve">13.6068096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6139039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997152328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145835876465</t>
+    <t xml:space="preserve">13.6139049530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338251113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167711257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145826339722</t>
   </si>
   <si>
     <t xml:space="preserve">13.266284942627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2237186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2343606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.152777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2591905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456823348999</t>
+    <t xml:space="preserve">13.2237167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2343597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1527767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2591896057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627382278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456832885742</t>
   </si>
   <si>
     <t xml:space="preserve">12.9754199981689</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">12.9399471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9186630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9257574081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9541368484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.010890007019</t>
+    <t xml:space="preserve">12.918664932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9257593154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9541358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250806808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0108919143677</t>
   </si>
   <si>
     <t xml:space="preserve">13.1137580871582</t>
@@ -2321,55 +2321,55 @@
     <t xml:space="preserve">13.1208524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4613761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520942687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953420639038</t>
+    <t xml:space="preserve">13.4613752365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520961761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953430175781</t>
   </si>
   <si>
     <t xml:space="preserve">13.06409740448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9683237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1031160354614</t>
+    <t xml:space="preserve">12.9683256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1031150817871</t>
   </si>
   <si>
     <t xml:space="preserve">13.0747385025024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9115715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.978964805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9860610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.950587272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.86545753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235727310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6916475296021</t>
+    <t xml:space="preserve">12.9115705490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9860591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9505891799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8654584884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5710458755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6916484832764</t>
   </si>
   <si>
     <t xml:space="preserve">12.4823665618896</t>
@@ -2378,22 +2378,22 @@
     <t xml:space="preserve">12.546215057373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7306661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3230381011963</t>
+    <t xml:space="preserve">12.7306680679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804727554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.323037147522</t>
   </si>
   <si>
     <t xml:space="preserve">13.3939800262451</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">12.2979164123535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2482557296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5352830886841</t>
+    <t xml:space="preserve">12.248254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5352821350098</t>
   </si>
   <si>
     <t xml:space="preserve">11.4004907608032</t>
@@ -2420,55 +2420,55 @@
     <t xml:space="preserve">10.8116664886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76171493530273</t>
+    <t xml:space="preserve">9.76171588897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.61273574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36769008636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56278228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01297664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69728326797485</t>
+    <t xml:space="preserve">8.36769104003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56278324127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01297760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69728231430054</t>
   </si>
   <si>
     <t xml:space="preserve">7.36739921569824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61569833755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72565984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920846939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58406734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83236503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98134613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77915859222412</t>
+    <t xml:space="preserve">7.61569786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72565937042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920703887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58406543731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83236598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98134517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77915954589844</t>
   </si>
   <si>
     <t xml:space="preserve">8.77206325531006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80398941040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58051872253418</t>
+    <t xml:space="preserve">8.80398845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5805196762085</t>
   </si>
   <si>
     <t xml:space="preserve">8.74723434448242</t>
@@ -2477,61 +2477,61 @@
     <t xml:space="preserve">8.64436817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89976215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07002449035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1303243637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31832313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93877983093262</t>
+    <t xml:space="preserve">8.89976119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07002353668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13032531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31832408905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93878078460693</t>
   </si>
   <si>
     <t xml:space="preserve">8.78979969024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88911819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63017845153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84300708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77561092376709</t>
+    <t xml:space="preserve">8.88911914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6301794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8430061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77561187744141</t>
   </si>
   <si>
     <t xml:space="preserve">9.04164695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20126819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43537902832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23319149017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00972175598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17643737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0345516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0948543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20481586456299</t>
+    <t xml:space="preserve">9.20126628875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43537998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23319244384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00972270965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.176438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03455257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09485340118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20481491088867</t>
   </si>
   <si>
     <t xml:space="preserve">9.12323093414307</t>
@@ -2540,34 +2540,34 @@
     <t xml:space="preserve">9.08421325683594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91040134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80044078826904</t>
+    <t xml:space="preserve">8.91040229797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80044174194336</t>
   </si>
   <si>
     <t xml:space="preserve">9.17269039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01014518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05817031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78849411010742</t>
+    <t xml:space="preserve">9.01014614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05817127227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78849601745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.99536895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96212291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20963382720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803791046143</t>
+    <t xml:space="preserve">8.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20963191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803695678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.43867206573486</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">9.81178665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3031148910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3474454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6282033920288</t>
+    <t xml:space="preserve">10.3031139373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3474464416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6282052993774</t>
   </si>
   <si>
     <t xml:space="preserve">10.6540632247925</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">10.0519094467163</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92630672454834</t>
+    <t xml:space="preserve">9.92630767822266</t>
   </si>
   <si>
     <t xml:space="preserve">10.0592975616455</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">10.0703802108765</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80070400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82656383514404</t>
+    <t xml:space="preserve">9.80070495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82656478881836</t>
   </si>
   <si>
     <t xml:space="preserve">9.91522407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9521656036377</t>
+    <t xml:space="preserve">9.95216751098633</t>
   </si>
   <si>
     <t xml:space="preserve">9.94847297668457</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">10.2587842941284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1627359390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.07776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1294870376587</t>
+    <t xml:space="preserve">10.1627349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0777683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.129487991333</t>
   </si>
   <si>
     <t xml:space="preserve">10.2070646286011</t>
@@ -2690,85 +2690,85 @@
     <t xml:space="preserve">9.97433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46453189849854</t>
+    <t xml:space="preserve">9.46453380584717</t>
   </si>
   <si>
     <t xml:space="preserve">9.35370635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40911865234375</t>
+    <t xml:space="preserve">9.40911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.55688762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63077068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78592681884766</t>
+    <t xml:space="preserve">9.63077163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38695526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78592777252197</t>
   </si>
   <si>
     <t xml:space="preserve">9.73051452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68618297576904</t>
+    <t xml:space="preserve">9.68618488311768</t>
   </si>
   <si>
     <t xml:space="preserve">9.53841590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70834922790527</t>
+    <t xml:space="preserve">9.70835018157959</t>
   </si>
   <si>
     <t xml:space="preserve">9.62707614898682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56058216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76376152038574</t>
+    <t xml:space="preserve">9.56058120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76376247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.81917476654053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78223419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60860538482666</t>
+    <t xml:space="preserve">9.78223323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60860633850098</t>
   </si>
   <si>
     <t xml:space="preserve">9.62338256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61968898773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57535934448242</t>
+    <t xml:space="preserve">9.61968803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57535839080811</t>
   </si>
   <si>
     <t xml:space="preserve">9.47192001342773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37217712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56796932220459</t>
+    <t xml:space="preserve">9.37217807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56797027587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.48669815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47561550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36478805541992</t>
+    <t xml:space="preserve">9.47561454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36478900909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.1061954498291</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">8.75155258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70352649688721</t>
+    <t xml:space="preserve">8.70352745056152</t>
   </si>
   <si>
     <t xml:space="preserve">8.66658496856689</t>
@@ -2786,133 +2786,133 @@
     <t xml:space="preserve">8.59639644622803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53359508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976718902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804847717285</t>
+    <t xml:space="preserve">8.53359413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976528167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804752349854</t>
   </si>
   <si>
     <t xml:space="preserve">8.88454341888428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76632881164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91779041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14313697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11358261108398</t>
+    <t xml:space="preserve">8.76632976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91779136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14313793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1135835647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.29829406738281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24287986755371</t>
+    <t xml:space="preserve">9.24288177490234</t>
   </si>
   <si>
     <t xml:space="preserve">9.2207145690918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1209716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80327033996582</t>
+    <t xml:space="preserve">9.12466716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12097263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80327129364014</t>
   </si>
   <si>
     <t xml:space="preserve">8.96951007843018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03969955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81435394287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82543659210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91040229797363</t>
+    <t xml:space="preserve">9.01753330230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03969764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81435298919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82543563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91040325164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.77371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39321517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41907501220703</t>
+    <t xml:space="preserve">8.39321613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41907405853271</t>
   </si>
   <si>
     <t xml:space="preserve">8.50404167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72199821472168</t>
+    <t xml:space="preserve">8.721999168396</t>
   </si>
   <si>
     <t xml:space="preserve">8.89193153381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01383972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14683055877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72312641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95955467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94477844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0740756988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.317892074585</t>
+    <t xml:space="preserve">9.013840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14683246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7231273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95955371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9447774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0740747451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3178911209106</t>
   </si>
   <si>
     <t xml:space="preserve">10.4398002624512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5136833190918</t>
+    <t xml:space="preserve">10.5136842727661</t>
   </si>
   <si>
     <t xml:space="preserve">10.395468711853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4952125549316</t>
+    <t xml:space="preserve">10.495213508606</t>
   </si>
   <si>
     <t xml:space="preserve">10.5062961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6245098114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910066604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5801801681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6577577590942</t>
+    <t xml:space="preserve">10.6245107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7094774246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910057067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5801792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6577568054199</t>
   </si>
   <si>
     <t xml:space="preserve">10.7648897171021</t>
@@ -2921,37 +2921,37 @@
     <t xml:space="preserve">10.7131700515747</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6097316741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838747024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4065523147583</t>
+    <t xml:space="preserve">10.6097326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838737487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060400009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4065532684326</t>
   </si>
   <si>
     <t xml:space="preserve">10.535849571228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5506258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617094039917</t>
+    <t xml:space="preserve">10.5506267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617084503174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2624788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4176359176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5764865875244</t>
+    <t xml:space="preserve">10.4176349639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5764856338501</t>
   </si>
   <si>
     <t xml:space="preserve">10.2809495925903</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">10.6983938217163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7464179992676</t>
+    <t xml:space="preserve">10.7464189529419</t>
   </si>
   <si>
     <t xml:space="preserve">10.6392860412598</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">10.8276901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7205591201782</t>
+    <t xml:space="preserve">10.7205600738525</t>
   </si>
   <si>
     <t xml:space="preserve">10.6429796218872</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">10.5321559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6947002410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0456495285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3929033279419</t>
+    <t xml:space="preserve">10.6946992874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3929023742676</t>
   </si>
   <si>
     <t xml:space="preserve">11.4778690338135</t>
@@ -3008,52 +3008,52 @@
     <t xml:space="preserve">11.6884384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5997772216797</t>
+    <t xml:space="preserve">11.6441087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599778175354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5739192962646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6921319961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5665302276611</t>
+    <t xml:space="preserve">11.6921329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.63671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5665311813354</t>
   </si>
   <si>
     <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4815645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4557046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6995210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4889535903931</t>
+    <t xml:space="preserve">11.5111179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4815635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4557037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6995220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4889526367188</t>
   </si>
   <si>
     <t xml:space="preserve">11.6958274841309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7290754318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8435964584351</t>
+    <t xml:space="preserve">11.7290744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8435945510864</t>
   </si>
   <si>
     <t xml:space="preserve">11.8768434524536</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1908502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2130136489868</t>
+    <t xml:space="preserve">12.1908493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2130146026611</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795114517212</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">12.4900808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4383602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4789962768555</t>
+    <t xml:space="preserve">12.4383592605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4789953231812</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755598068237</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">12.3607816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4161968231201</t>
+    <t xml:space="preserve">12.4161958694458</t>
   </si>
   <si>
     <t xml:space="preserve">12.412501335144</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048570632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6045999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6637058258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5824346542358</t>
+    <t xml:space="preserve">12.5048561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6637048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5824356079102</t>
   </si>
   <si>
     <t xml:space="preserve">12.6600122451782</t>
@@ -3119,19 +3119,19 @@
     <t xml:space="preserve">12.6858711242676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6378469467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344104766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.611988067627</t>
+    <t xml:space="preserve">12.6378479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344095230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6119871139526</t>
   </si>
   <si>
     <t xml:space="preserve">12.6230697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5787391662598</t>
+    <t xml:space="preserve">12.5787401199341</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489305496216</t>
@@ -3140,55 +3140,55 @@
     <t xml:space="preserve">12.726508140564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3977270126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3275337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5602684020996</t>
+    <t xml:space="preserve">12.4457483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679155349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3977251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3275346755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5602693557739</t>
   </si>
   <si>
     <t xml:space="preserve">12.4420547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5972099304199</t>
+    <t xml:space="preserve">12.5972108840942</t>
   </si>
   <si>
     <t xml:space="preserve">12.7228136062622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8336391448975</t>
+    <t xml:space="preserve">12.8336400985718</t>
   </si>
   <si>
     <t xml:space="preserve">12.9740190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631925582886</t>
+    <t xml:space="preserve">12.8631944656372</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149122238159</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9592437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368213653564</t>
+    <t xml:space="preserve">12.9592418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368204116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.0626802444458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881664276123</t>
+    <t xml:space="preserve">12.8816633224487</t>
   </si>
   <si>
     <t xml:space="preserve">12.8890523910522</t>
@@ -3200,16 +3200,16 @@
     <t xml:space="preserve">13.2438173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1184320449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9773721694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0910034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2007169723511</t>
+    <t xml:space="preserve">13.1184329986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9773731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910043716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2007160186768</t>
   </si>
   <si>
     <t xml:space="preserve">13.177206993103</t>
@@ -3218,34 +3218,34 @@
     <t xml:space="preserve">13.2673273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2830018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5180978775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4985065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4632415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4201412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4318943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397315979004</t>
+    <t xml:space="preserve">13.2830009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5180969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4632406234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4201402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4318933486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397325515747</t>
   </si>
   <si>
     <t xml:space="preserve">13.4514875411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102605819702</t>
+    <t xml:space="preserve">13.5102615356445</t>
   </si>
   <si>
     <t xml:space="preserve">13.2359800338745</t>
@@ -3257,49 +3257,49 @@
     <t xml:space="preserve">13.232063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0518207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3339376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1262693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732864379883</t>
+    <t xml:space="preserve">13.0518217086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3339366912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732883453369</t>
   </si>
   <si>
     <t xml:space="preserve">13.2477369308472</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3731203079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3221826553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4358129501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1967973709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9852094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3261013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3300189971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.263409614563</t>
+    <t xml:space="preserve">13.3731212615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3221836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4358148574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.196798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9852104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3261003494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3300199508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2634077072144</t>
   </si>
   <si>
     <t xml:space="preserve">13.1654510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145143508911</t>
+    <t xml:space="preserve">13.1145133972168</t>
   </si>
   <si>
     <t xml:space="preserve">12.7148485183716</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">12.8441514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1223516464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1576156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1301860809326</t>
+    <t xml:space="preserve">13.122350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1576147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1301851272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.2046346664429</t>
@@ -3329,34 +3329,34 @@
     <t xml:space="preserve">13.0283117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281436920166</t>
+    <t xml:space="preserve">13.2281427383423</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4749956130981</t>
+    <t xml:space="preserve">13.3456945419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4749965667725</t>
   </si>
   <si>
     <t xml:space="preserve">13.5690355300903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6160545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5376882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5416078567505</t>
+    <t xml:space="preserve">13.6160535812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5376892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5416088104248</t>
   </si>
   <si>
     <t xml:space="preserve">13.3770389556885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4436502456665</t>
+    <t xml:space="preserve">13.4436521530151</t>
   </si>
   <si>
     <t xml:space="preserve">13.4240570068359</t>
@@ -3365,145 +3365,145 @@
     <t xml:space="preserve">13.3848762512207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4123029708862</t>
+    <t xml:space="preserve">13.4123039245605</t>
   </si>
   <si>
     <t xml:space="preserve">13.5337715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5964641571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.612135887146</t>
+    <t xml:space="preserve">13.5964651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6121368408203</t>
   </si>
   <si>
     <t xml:space="preserve">13.5729532241821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7414407730103</t>
+    <t xml:space="preserve">13.7414388656616</t>
   </si>
   <si>
     <t xml:space="preserve">13.8393974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9060096740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.831561088562</t>
+    <t xml:space="preserve">13.9060087203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8315601348877</t>
   </si>
   <si>
     <t xml:space="preserve">13.7923774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8824977874756</t>
+    <t xml:space="preserve">13.8824987411499</t>
   </si>
   <si>
     <t xml:space="preserve">14.0039663314819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8589897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748294830322</t>
+    <t xml:space="preserve">13.8589878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748285293579</t>
   </si>
   <si>
     <t xml:space="preserve">14.0901679992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2037973403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.364447593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3017549514771</t>
+    <t xml:space="preserve">14.2037992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3644485473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3017568588257</t>
   </si>
   <si>
     <t xml:space="preserve">14.4349765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4114665985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4271392822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3997116088867</t>
+    <t xml:space="preserve">14.4114675521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4271421432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3997135162354</t>
   </si>
   <si>
     <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7288494110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8072137832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816623687744</t>
+    <t xml:space="preserve">14.564281463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7288484573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8072156906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816614151001</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6739940643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7249326705933</t>
+    <t xml:space="preserve">14.6739931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7249307632446</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739618301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9538774490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141286849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1185598373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0663423538208</t>
+    <t xml:space="preserve">14.8494453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9217462539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1185579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0663414001465</t>
   </si>
   <si>
     <t xml:space="preserve">15.1346263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310256958008</t>
+    <t xml:space="preserve">15.1426601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310247421265</t>
   </si>
   <si>
     <t xml:space="preserve">15.247091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3234081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2591428756714</t>
+    <t xml:space="preserve">15.3234062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2591419219971</t>
   </si>
   <si>
     <t xml:space="preserve">15.3475065231323</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">15.2430753707886</t>
   </si>
   <si>
-    <t xml:space="preserve">15.25110912323</t>
+    <t xml:space="preserve">15.2511081695557</t>
   </si>
   <si>
     <t xml:space="preserve">15.2792253494263</t>
@@ -3521,91 +3521,91 @@
     <t xml:space="preserve">15.38365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3716087341309</t>
+    <t xml:space="preserve">15.3716077804565</t>
   </si>
   <si>
     <t xml:space="preserve">15.4559545516968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0743780136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6887807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7811632156372</t>
+    <t xml:space="preserve">15.0743770599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6887798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7811613082886</t>
   </si>
   <si>
     <t xml:space="preserve">14.7570648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7168979644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1867036819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2991695404053</t>
+    <t xml:space="preserve">14.7168970108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1867046356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299168586731</t>
   </si>
   <si>
     <t xml:space="preserve">14.2429361343384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4919672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6124649047852</t>
+    <t xml:space="preserve">14.5642652511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4919662475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6124658584595</t>
   </si>
   <si>
     <t xml:space="preserve">14.9498624801636</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0221605300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8574800491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297761917114</t>
+    <t xml:space="preserve">15.0221614837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.857479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297771453857</t>
   </si>
   <si>
     <t xml:space="preserve">14.861496925354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8213300704956</t>
+    <t xml:space="preserve">14.8213310241699</t>
   </si>
   <si>
     <t xml:space="preserve">14.6767311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7731285095215</t>
+    <t xml:space="preserve">14.7731294631958</t>
   </si>
   <si>
     <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9016618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623273849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9659261703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788091659546</t>
+    <t xml:space="preserve">14.9016609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9659271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788101196289</t>
   </si>
   <si>
     <t xml:space="preserve">14.8333787918091</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">14.9177293777466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8293609619141</t>
+    <t xml:space="preserve">14.8293619155884</t>
   </si>
   <si>
     <t xml:space="preserve">14.9337949752808</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">15.058310508728</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0422430038452</t>
+    <t xml:space="preserve">15.0422449111938</t>
   </si>
   <si>
     <t xml:space="preserve">14.8132972717285</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">14.9257621765137</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1466760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0382270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627435684204</t>
+    <t xml:space="preserve">15.1466751098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0382251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627416610718</t>
   </si>
   <si>
     <t xml:space="preserve">14.3754863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4999980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847639083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6727123260498</t>
+    <t xml:space="preserve">14.4999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6727132797241</t>
   </si>
   <si>
     <t xml:space="preserve">14.9940462112427</t>
@@ -3662,58 +3662,58 @@
     <t xml:space="preserve">14.9819946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.957896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7450132369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270088195801</t>
+    <t xml:space="preserve">14.9578952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7450122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270078659058</t>
   </si>
   <si>
     <t xml:space="preserve">14.893630027771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562324523926</t>
+    <t xml:space="preserve">14.5562334060669</t>
   </si>
   <si>
     <t xml:space="preserve">14.5963973999023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0300550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9256229400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8372573852539</t>
+    <t xml:space="preserve">14.0300559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.371467590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9256219863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8372583389282</t>
   </si>
   <si>
     <t xml:space="preserve">13.7770080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379505157471</t>
+    <t xml:space="preserve">13.0379495620728</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447366714478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.993766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6243753433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4958438873291</t>
+    <t xml:space="preserve">12.9937677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6243762969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4958448410034</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1746549606323</t>
+    <t xml:space="preserve">14.1746530532837</t>
   </si>
   <si>
     <t xml:space="preserve">14.3875350952148</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">15.1667585372925</t>
   </si>
   <si>
-    <t xml:space="preserve">15.315375328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6005525588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1789474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8495826721191</t>
+    <t xml:space="preserve">15.3153743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6005544662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1789455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8495836257935</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
@@ -3746,13 +3746,13 @@
     <t xml:space="preserve">16.6850414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9581718444824</t>
+    <t xml:space="preserve">16.9581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.235179901123</t>
+    <t xml:space="preserve">16.2351779937744</t>
   </si>
   <si>
     <t xml:space="preserve">16.0504150390625</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">15.7331008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6166200637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.484073638916</t>
+    <t xml:space="preserve">15.6166210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840726852417</t>
   </si>
   <si>
     <t xml:space="preserve">15.4117727279663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4760398864746</t>
+    <t xml:space="preserve">15.476037979126</t>
   </si>
   <si>
     <t xml:space="preserve">14.9980611801147</t>
@@ -3782,40 +3782,40 @@
     <t xml:space="preserve">14.7932147979736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5080318450928</t>
+    <t xml:space="preserve">14.5080327987671</t>
   </si>
   <si>
     <t xml:space="preserve">14.5441818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4598321914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5401659011841</t>
+    <t xml:space="preserve">14.4598331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5401668548584</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196691513062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7048482894897</t>
+    <t xml:space="preserve">14.7048492431641</t>
   </si>
   <si>
     <t xml:space="preserve">14.6204986572266</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4518013000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2469539642334</t>
+    <t xml:space="preserve">14.4518003463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2469530105591</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2670364379883</t>
+    <t xml:space="preserve">14.2268686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.267035484314</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947374343872</t>
@@ -3824,19 +3824,19 @@
     <t xml:space="preserve">14.3112192153931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4558181762695</t>
+    <t xml:space="preserve">14.4558172225952</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7547550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8230838775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8828716278076</t>
+    <t xml:space="preserve">14.7547540664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8230848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8828706741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.5882034301758</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430046081543</t>
+    <t xml:space="preserve">14.4430065155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.3789463043213</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">14.2764539718628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4643573760986</t>
+    <t xml:space="preserve">14.4643564224243</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
@@ -3869,10 +3869,10 @@
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344398498535</t>
+    <t xml:space="preserve">13.3924503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344388961792</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3887,13 +3887,13 @@
     <t xml:space="preserve">13.336932182312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3967199325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2557926177979</t>
+    <t xml:space="preserve">13.5803537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3967208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2557916641235</t>
   </si>
   <si>
     <t xml:space="preserve">13.1917333602905</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">13.6828479766846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2686042785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4266138076782</t>
+    <t xml:space="preserve">13.2686033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4266147613525</t>
   </si>
   <si>
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038290023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2942266464233</t>
+    <t xml:space="preserve">13.0038299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2942276000977</t>
   </si>
   <si>
     <t xml:space="preserve">13.1661100387573</t>
@@ -3932,13 +3932,13 @@
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568529129028</t>
+    <t xml:space="preserve">12.9568538665771</t>
   </si>
   <si>
     <t xml:space="preserve">12.995288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7774906158447</t>
+    <t xml:space="preserve">12.7774896621704</t>
   </si>
   <si>
     <t xml:space="preserve">12.3547058105469</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">12.4401159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4230337142944</t>
+    <t xml:space="preserve">12.4230346679688</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">12.1838836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1625308990479</t>
+    <t xml:space="preserve">12.1625299453735</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095069885254</t>
@@ -3965,16 +3965,16 @@
     <t xml:space="preserve">12.4273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796140670776</t>
+    <t xml:space="preserve">12.1796131134033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333520889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4571981430054</t>
+    <t xml:space="preserve">12.3333530426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134323120117</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">12.4700107574463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5340690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.640832901001</t>
+    <t xml:space="preserve">12.534068107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6408319473267</t>
   </si>
   <si>
     <t xml:space="preserve">12.8458185195923</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">13.0508050918579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191339492798</t>
+    <t xml:space="preserve">13.1191329956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.2258977890015</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">13.1618394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.897066116333</t>
+    <t xml:space="preserve">12.8970651626587</t>
   </si>
   <si>
     <t xml:space="preserve">12.7646780014038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7006206512451</t>
+    <t xml:space="preserve">12.7006196975708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8757123947144</t>
@@ -4028,16 +4028,16 @@
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579151153564</t>
+    <t xml:space="preserve">12.6579141616821</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3931398391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8330068588257</t>
+    <t xml:space="preserve">12.3931407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8330059051514</t>
   </si>
   <si>
     <t xml:space="preserve">12.4828224182129</t>
@@ -4049,25 +4049,25 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.768949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1703815460205</t>
+    <t xml:space="preserve">12.7689485549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1703805923462</t>
   </si>
   <si>
     <t xml:space="preserve">12.9696645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0892400741577</t>
+    <t xml:space="preserve">13.089241027832</t>
   </si>
   <si>
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.704891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7390556335449</t>
+    <t xml:space="preserve">12.7048902511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7390546798706</t>
   </si>
   <si>
     <t xml:space="preserve">12.3248119354248</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">12.4443864822388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1411781311035</t>
+    <t xml:space="preserve">12.1411790847778</t>
   </si>
   <si>
     <t xml:space="preserve">12.0173320770264</t>
@@ -4094,25 +4094,25 @@
     <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8550510406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7397451400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447317123413</t>
+    <t xml:space="preserve">11.8550519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.73974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447326660156</t>
   </si>
   <si>
     <t xml:space="preserve">11.7909927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0045213699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.158260345459</t>
+    <t xml:space="preserve">12.0045204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1582593917847</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991876602173</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">12.3632469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5169868469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3376226425171</t>
+    <t xml:space="preserve">12.5169858932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3376235961914</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749973297119</t>
@@ -4139,16 +4139,16 @@
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9739351272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0977811813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0251817703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1532983779907</t>
+    <t xml:space="preserve">12.973934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0977821350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.025182723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.153299331665</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
@@ -4178,19 +4178,19 @@
     <t xml:space="preserve">14.7419443130493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.579662322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5027933120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600877761841</t>
+    <t xml:space="preserve">14.5796632766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5027923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600868225098</t>
   </si>
   <si>
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686298370361</t>
+    <t xml:space="preserve">14.4686279296875</t>
   </si>
   <si>
     <t xml:space="preserve">14.6266384124756</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">14.7163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7035083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.699236869812</t>
+    <t xml:space="preserve">14.7035093307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6992378234863</t>
   </si>
   <si>
     <t xml:space="preserve">14.7931909561157</t>
@@ -4211,22 +4211,22 @@
     <t xml:space="preserve">14.6906976699829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7889204025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7462129592896</t>
+    <t xml:space="preserve">14.7889194488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7462139129639</t>
   </si>
   <si>
     <t xml:space="preserve">14.8999538421631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8444356918335</t>
+    <t xml:space="preserve">14.8444366455078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928192138672</t>
+    <t xml:space="preserve">14.0928201675415</t>
   </si>
   <si>
     <t xml:space="preserve">14.2508296966553</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">14.3490524291992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3106174468994</t>
+    <t xml:space="preserve">14.3106184005737</t>
   </si>
   <si>
     <t xml:space="preserve">14.2593717575073</t>
@@ -4253,13 +4253,13 @@
     <t xml:space="preserve">14.1910419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3277006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504854202271</t>
+    <t xml:space="preserve">14.3276996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917589187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504844665527</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
@@ -4274,16 +4274,16 @@
     <t xml:space="preserve">14.8615188598633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.848708152771</t>
+    <t xml:space="preserve">14.8487071990967</t>
   </si>
   <si>
     <t xml:space="preserve">14.9554719924927</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9682836532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8358964920044</t>
+    <t xml:space="preserve">14.968282699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8358974456787</t>
   </si>
   <si>
     <t xml:space="preserve">15.168999671936</t>
@@ -4292,79 +4292,79 @@
     <t xml:space="preserve">15.2373285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3013877868652</t>
+    <t xml:space="preserve">15.3013868331909</t>
   </si>
   <si>
     <t xml:space="preserve">15.2586803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2971162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270101547241</t>
+    <t xml:space="preserve">15.2971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270092010498</t>
   </si>
   <si>
     <t xml:space="preserve">15.3825263977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2885751724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319948196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166898727417</t>
+    <t xml:space="preserve">15.28857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5021018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416690826416</t>
   </si>
   <si>
     <t xml:space="preserve">15.4679374694824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4636659622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063714981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5618877410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6003246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5875120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6857357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106420516968</t>
+    <t xml:space="preserve">15.4636669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063734054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5618886947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.600323677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5875129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473016738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.685736656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106430053711</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9804029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266639709473</t>
+    <t xml:space="preserve">15.9804019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266630172729</t>
   </si>
   <si>
     <t xml:space="preserve">15.8223934173584</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">16.0231094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0273780822754</t>
+    <t xml:space="preserve">16.027379989624</t>
   </si>
   <si>
     <t xml:space="preserve">16.0658149719238</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">15.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7327117919922</t>
+    <t xml:space="preserve">15.7327108383179</t>
   </si>
   <si>
     <t xml:space="preserve">15.2031631469727</t>
@@ -4394,25 +4394,25 @@
     <t xml:space="preserve">15.7540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8316249847412</t>
+    <t xml:space="preserve">14.8316259384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081497192383</t>
+    <t xml:space="preserve">15.0451526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4508543014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081516265869</t>
   </si>
   <si>
     <t xml:space="preserve">15.1092128753662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2501401901245</t>
+    <t xml:space="preserve">15.2501392364502</t>
   </si>
   <si>
     <t xml:space="preserve">15.4423131942749</t>
@@ -4421,25 +4421,25 @@
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985464096069</t>
+    <t xml:space="preserve">15.6985454559326</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6216773986816</t>
+    <t xml:space="preserve">15.621678352356</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437442779541</t>
+    <t xml:space="preserve">15.8437452316284</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.091438293457</t>
+    <t xml:space="preserve">16.0914402008057</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683082580566</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">16.0401916503906</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1384162902832</t>
+    <t xml:space="preserve">16.1384143829346</t>
   </si>
   <si>
     <t xml:space="preserve">16.2836132049561</t>
@@ -4457,10 +4457,10 @@
     <t xml:space="preserve">16.3049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3092346191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3434009552002</t>
+    <t xml:space="preserve">16.3092365264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3434028625488</t>
   </si>
   <si>
     <t xml:space="preserve">16.219554901123</t>
@@ -4472,37 +4472,37 @@
     <t xml:space="preserve">16.2323665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.125602722168</t>
+    <t xml:space="preserve">16.1256008148193</t>
   </si>
   <si>
     <t xml:space="preserve">15.8693695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9334278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8053102493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2067451477051</t>
+    <t xml:space="preserve">15.9334297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8053112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2067432403564</t>
   </si>
   <si>
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8907222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1127910614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0316524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.912073135376</t>
+    <t xml:space="preserve">15.890721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889430999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1127891540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0316505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9120740890503</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -6054,6 +6054,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.560001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0800018310547</t>
   </si>
 </sst>
 </file>
@@ -71288,7 +71291,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6511111111</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>1543395</v>
@@ -71309,6 +71312,32 @@
         <v>2004</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.693900463</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>2353573</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>33.3400001525879</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>32.9199981689453</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>33.0800018310547</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2014</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="2017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="2018">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21389961242676</t>
+    <t xml:space="preserve">9.21390056610107</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">9.31058979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13427257537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11721229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02052116394043</t>
+    <t xml:space="preserve">9.13427352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11721038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02052211761475</t>
   </si>
   <si>
     <t xml:space="preserve">8.76458072662354</t>
@@ -65,286 +65,286 @@
     <t xml:space="preserve">9.0660228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95796012878418</t>
+    <t xml:space="preserve">8.95795917510986</t>
   </si>
   <si>
     <t xml:space="preserve">8.75889205932617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57120227813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29250907897949</t>
+    <t xml:space="preserve">8.57120132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29251003265381</t>
   </si>
   <si>
     <t xml:space="preserve">8.44607543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48588943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30957221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04794311523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93987941741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568593978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84318828582764</t>
+    <t xml:space="preserve">8.48588752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30957317352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04794406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568784713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319067001343</t>
   </si>
   <si>
     <t xml:space="preserve">7.70668792724609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41662120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23461771011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15499114990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161317825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74548435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47248029708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81373453140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23360204696655</t>
+    <t xml:space="preserve">7.4166202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23461818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1549916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161270141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74548530578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47248077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81373596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23360157012939</t>
   </si>
   <si>
     <t xml:space="preserve">6.34166526794434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59760808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62035846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392244338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72842216491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66017055511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89904975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89336204528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95592403411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28580617904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643329620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45074605941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680768966675</t>
+    <t xml:space="preserve">6.59760713577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62035799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392339706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72842073440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66017007827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89905023574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89336252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95592546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26305627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28580760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643520355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4507474899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680816650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.24599266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31993246078491</t>
+    <t xml:space="preserve">7.31993198394775</t>
   </si>
   <si>
     <t xml:space="preserve">7.38249492645264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37111949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575408935547</t>
+    <t xml:space="preserve">7.37112092971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575361251831</t>
   </si>
   <si>
     <t xml:space="preserve">7.83750295639038</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79200077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731504440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89437770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67256355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037261962891</t>
+    <t xml:space="preserve">7.79200172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437818527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.3654317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42799615859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48487234115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41093349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755361557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98436403274536</t>
+    <t xml:space="preserve">7.42799663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48487186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41093254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30286979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755504608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9843635559082</t>
   </si>
   <si>
     <t xml:space="preserve">7.00711345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85355043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05261516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13792896270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43368244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4962477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4791841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743671417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75218915939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631544113159</t>
+    <t xml:space="preserve">6.85354852676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05261564254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13792943954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4336838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49624681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918558120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862422943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181619644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">7.85456562042236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80337810516357</t>
+    <t xml:space="preserve">7.80337762832642</t>
   </si>
   <si>
     <t xml:space="preserve">7.77493906021118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57018756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387083053589</t>
+    <t xml:space="preserve">7.5701847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387035369873</t>
   </si>
   <si>
     <t xml:space="preserve">7.35405731201172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53606081008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105325698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05830192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25168085098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798887252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84845209121704</t>
+    <t xml:space="preserve">7.53606128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16636800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0583028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517763137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25167989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994874954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84845161437988</t>
   </si>
   <si>
     <t xml:space="preserve">7.90873193740845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94490098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85447978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228399276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76406097412109</t>
+    <t xml:space="preserve">7.94490051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85448026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76405954360962</t>
   </si>
   <si>
     <t xml:space="preserve">7.54705286026001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53499555587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158437728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625581741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77008867263794</t>
+    <t xml:space="preserve">7.534996509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625677108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77008819580078</t>
   </si>
   <si>
     <t xml:space="preserve">7.42046499252319</t>
@@ -353,82 +353,82 @@
     <t xml:space="preserve">7.17934417724609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97439241409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40840816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54102468490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58322048187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257246017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02498435974121</t>
+    <t xml:space="preserve">6.97439289093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850368499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9201397895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19139909744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40840911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54102420806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832200050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58257341384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02498292922974</t>
   </si>
   <si>
     <t xml:space="preserve">6.11841678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26308917999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953664779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4318733215332</t>
+    <t xml:space="preserve">6.26308965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43187284469604</t>
   </si>
   <si>
     <t xml:space="preserve">6.25103330612183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1304726600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91647863388062</t>
+    <t xml:space="preserve">6.13047313690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91647911071777</t>
   </si>
   <si>
     <t xml:space="preserve">5.92853450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38967704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7634129524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69710445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87191581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177732467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84780502319336</t>
+    <t xml:space="preserve">6.38967657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790102005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76341342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69710493087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8719162940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560922622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8417763710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84780406951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.77546882629395</t>
@@ -437,118 +437,118 @@
     <t xml:space="preserve">6.73327350616455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68504762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81163740158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62476873397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10098123550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083940505981</t>
+    <t xml:space="preserve">6.68504905700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81163692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10098028182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07084035873413</t>
   </si>
   <si>
     <t xml:space="preserve">6.79355335235596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06481266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948553085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387521743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990386962891</t>
+    <t xml:space="preserve">7.06481313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948505401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990339279175</t>
   </si>
   <si>
     <t xml:space="preserve">7.34210109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808439254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7393012046814</t>
+    <t xml:space="preserve">7.08289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73930215835571</t>
   </si>
   <si>
     <t xml:space="preserve">7.04070043563843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01658916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81766414642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74533033370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271238327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247694015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93822431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88397312164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523290634155</t>
+    <t xml:space="preserve">7.01658868789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74532890319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247789382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93822574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88397216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98041963577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523195266724</t>
   </si>
   <si>
     <t xml:space="preserve">7.25770854949951</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70313262939453</t>
+    <t xml:space="preserve">6.70313310623169</t>
   </si>
   <si>
     <t xml:space="preserve">6.63079643249512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72724533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79958009719849</t>
+    <t xml:space="preserve">6.72724485397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79958057403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.75135707855225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59462785720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56448936462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57654428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54640531539917</t>
+    <t xml:space="preserve">6.59462928771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56448841094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57654476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5464038848877</t>
   </si>
   <si>
     <t xml:space="preserve">6.51626491546631</t>
@@ -557,52 +557,52 @@
     <t xml:space="preserve">6.4981803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76944065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986042022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383176803589</t>
+    <t xml:space="preserve">6.76944017410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383272171021</t>
   </si>
   <si>
     <t xml:space="preserve">7.1853723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16728925704956</t>
+    <t xml:space="preserve">7.1672887802124</t>
   </si>
   <si>
     <t xml:space="preserve">7.19742822647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28784894943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26976537704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33004426956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31196022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317655563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09495258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98644971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08892583847046</t>
+    <t xml:space="preserve">7.28784847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33004522323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31195974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317750930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09495306015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98644828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574819564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08892631530762</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686853408813</t>
@@ -611,67 +611,67 @@
     <t xml:space="preserve">6.8779444694519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02261829376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8236927986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854856491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35415649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73392152786255</t>
+    <t xml:space="preserve">7.02261638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82369184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35415601730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73392009735107</t>
   </si>
   <si>
     <t xml:space="preserve">8.30055332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68031692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45125198364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47536468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41508388519287</t>
+    <t xml:space="preserve">8.68031597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45125102996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47536373138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41508483886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.33069133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54167175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55975532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6381196975708</t>
+    <t xml:space="preserve">8.541672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5597562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63812065124512</t>
   </si>
   <si>
     <t xml:space="preserve">8.5838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59592533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66223335266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66826057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55372619628906</t>
+    <t xml:space="preserve">8.59592437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6622314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66826152801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55372714996338</t>
   </si>
   <si>
     <t xml:space="preserve">8.50550365447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5115327835083</t>
+    <t xml:space="preserve">8.51153182983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.65017604827881</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">8.69840049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7164831161499</t>
+    <t xml:space="preserve">8.71648406982422</t>
   </si>
   <si>
     <t xml:space="preserve">8.52358818054199</t>
@@ -695,31 +695,31 @@
     <t xml:space="preserve">8.48741912841797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38494300842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25835514068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23424434661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16793632507324</t>
+    <t xml:space="preserve">8.38494396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25835609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23424530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16793727874756</t>
   </si>
   <si>
     <t xml:space="preserve">8.27041244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26438522338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58989524841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29517078399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38559150695801</t>
+    <t xml:space="preserve">8.26438331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58989715576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2951717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38559246063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.42175960540771</t>
@@ -734,43 +734,43 @@
     <t xml:space="preserve">8.88526725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84909915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00582885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02994060516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81896114349365</t>
+    <t xml:space="preserve">8.84910106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00582790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993869781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8189582824707</t>
   </si>
   <si>
     <t xml:space="preserve">8.77073574066162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67428874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74059677124023</t>
+    <t xml:space="preserve">8.67428779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7405948638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.90335178375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04802322387695</t>
+    <t xml:space="preserve">9.04802513122559</t>
   </si>
   <si>
     <t xml:space="preserve">8.87923908233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90937995910645</t>
+    <t xml:space="preserve">8.90938091278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.95760345458984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83101558685303</t>
+    <t xml:space="preserve">8.83101463317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.81293201446533</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6562032699585</t>
+    <t xml:space="preserve">8.65620517730713</t>
   </si>
   <si>
     <t xml:space="preserve">8.49947643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14985370635986</t>
+    <t xml:space="preserve">8.14985179901123</t>
   </si>
   <si>
     <t xml:space="preserve">8.27643871307373</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">8.78881931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80087566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.794846534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78279113769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86718463897705</t>
+    <t xml:space="preserve">8.80087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484844207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78279209136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86718368530273</t>
   </si>
   <si>
     <t xml:space="preserve">8.98171615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80690383911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63209247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6079797744751</t>
+    <t xml:space="preserve">8.80690288543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6320915222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60797882080078</t>
   </si>
   <si>
     <t xml:space="preserve">8.46933650970459</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93349075317383</t>
+    <t xml:space="preserve">8.93348979949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.75867938995361</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">8.87321186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04199600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19269752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078014373779</t>
+    <t xml:space="preserve">9.04199504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19269561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21077919006348</t>
   </si>
   <si>
     <t xml:space="preserve">9.24091911315918</t>
@@ -860,46 +860,46 @@
     <t xml:space="preserve">8.94554805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89129638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03596782684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07213401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12036037445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30493068695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33675289154053</t>
+    <t xml:space="preserve">8.89129543304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03596878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07213687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12035942077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30492973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33675384521484</t>
   </si>
   <si>
     <t xml:space="preserve">9.18400573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15854644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13308811187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851779937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83395671844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94215202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03762149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81486320495605</t>
+    <t xml:space="preserve">9.15854835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13309001922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851875305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83395576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94215297698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03761959075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81486415863037</t>
   </si>
   <si>
     <t xml:space="preserve">8.75758266448975</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">8.73848819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89123821258545</t>
+    <t xml:space="preserve">8.89123725891113</t>
   </si>
   <si>
     <t xml:space="preserve">8.95488166809082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05034923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22855663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23492050170898</t>
+    <t xml:space="preserve">9.05035018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22855758666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2349214553833</t>
   </si>
   <si>
     <t xml:space="preserve">9.17127513885498</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">9.34948062896729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25401496887207</t>
+    <t xml:space="preserve">9.25401401519775</t>
   </si>
   <si>
     <t xml:space="preserve">9.22219181060791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24765110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29220294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33038902282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38130569458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57860660552979</t>
+    <t xml:space="preserve">9.24765014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29220199584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33038997650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38130474090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57860565185547</t>
   </si>
   <si>
     <t xml:space="preserve">9.54678344726562</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">9.54041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64861583709717</t>
+    <t xml:space="preserve">9.64861488342285</t>
   </si>
   <si>
     <t xml:space="preserve">9.79500007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85864353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862506866455</t>
+    <t xml:space="preserve">9.85864448547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862602233887</t>
   </si>
   <si>
     <t xml:space="preserve">9.68680286407471</t>
@@ -983,19 +983,19 @@
     <t xml:space="preserve">9.56587600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52768898010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75681304931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77590465545654</t>
+    <t xml:space="preserve">9.52769088745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75681209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77590656280518</t>
   </si>
   <si>
     <t xml:space="preserve">9.80136394500732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750379562378</t>
+    <t xml:space="preserve">10.0750389099121</t>
   </si>
   <si>
     <t xml:space="preserve">10.0877685546875</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">10.1386833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.23415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1959629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0623092651367</t>
+    <t xml:space="preserve">10.2341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1959638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0623083114624</t>
   </si>
   <si>
     <t xml:space="preserve">10.0050277709961</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">9.86500835418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90319633483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82045650482178</t>
+    <t xml:space="preserve">9.90319538116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82045745849609</t>
   </si>
   <si>
     <t xml:space="preserve">9.87137317657471</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">9.78226947784424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71225929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69953060150146</t>
+    <t xml:space="preserve">9.71226024627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69953155517578</t>
   </si>
   <si>
     <t xml:space="preserve">9.68043804168701</t>
@@ -1046,10 +1046,10 @@
     <t xml:space="preserve">9.69316577911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66134357452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53405284881592</t>
+    <t xml:space="preserve">9.66134548187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53405380249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.52132415771484</t>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">9.57224082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61679077148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.674072265625</t>
+    <t xml:space="preserve">9.61679172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67407417297363</t>
   </si>
   <si>
     <t xml:space="preserve">9.62952041625977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59769916534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89046764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9477481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75044822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89683246612549</t>
+    <t xml:space="preserve">9.59769821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89046669006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94774723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75044631958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">9.91592502593994</t>
@@ -1088,25 +1088,25 @@
     <t xml:space="preserve">9.8777379989624</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686721801758</t>
+    <t xml:space="preserve">10.0304861068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686740875244</t>
   </si>
   <si>
     <t xml:space="preserve">10.1323194503784</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93501853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84591579437256</t>
+    <t xml:space="preserve">9.93501949310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84591484069824</t>
   </si>
   <si>
     <t xml:space="preserve">9.85227966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83318710327148</t>
+    <t xml:space="preserve">9.83318614959717</t>
   </si>
   <si>
     <t xml:space="preserve">9.72498989105225</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">9.96047592163086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0177583694458</t>
+    <t xml:space="preserve">10.0177564620972</t>
   </si>
   <si>
     <t xml:space="preserve">9.9541130065918</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">10.0241212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94138526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88410186767578</t>
+    <t xml:space="preserve">9.94138336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8841028213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.0368509292603</t>
@@ -1145,121 +1145,121 @@
     <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58496952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61042881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66770839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74408435821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73135471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80772686004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73771953582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70589447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55951309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47677326202393</t>
+    <t xml:space="preserve">9.58497047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61042785644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6677074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74408340454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73135375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8077278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73771858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70589637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5595121383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47677421569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.97320652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97956943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0814037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2914323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3041620254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2023286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3105268478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3232536315918</t>
+    <t xml:space="preserve">9.97957134246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0814018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0559453964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.291431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3041610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2023305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.310525894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3232555389404</t>
   </si>
   <si>
     <t xml:space="preserve">10.1736869812012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1641416549683</t>
+    <t xml:space="preserve">10.1641407012939</t>
   </si>
   <si>
     <t xml:space="preserve">10.148229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9922981262207</t>
+    <t xml:space="preserve">9.99230003356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.76954078674316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86818981170654</t>
+    <t xml:space="preserve">9.86819076538086</t>
   </si>
   <si>
     <t xml:space="preserve">9.81727504730225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77908897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80454540252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36857509613037</t>
+    <t xml:space="preserve">9.77908802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81409358978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80454635620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36857414245605</t>
   </si>
   <si>
     <t xml:space="preserve">9.6517972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85546112060547</t>
+    <t xml:space="preserve">9.85546016693115</t>
   </si>
   <si>
     <t xml:space="preserve">9.74726581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0082101821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98593521118164</t>
+    <t xml:space="preserve">10.0082111358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98593425750732</t>
   </si>
   <si>
     <t xml:space="preserve">9.92865467071533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94456481933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9700231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0495796203613</t>
+    <t xml:space="preserve">9.94456577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97002220153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0495805740356</t>
   </si>
   <si>
     <t xml:space="preserve">10.1609592437744</t>
@@ -1268,28 +1268,28 @@
     <t xml:space="preserve">10.3137083053589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2946128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455295562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346342086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.530101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.638298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7655906677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8546924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6319332122803</t>
+    <t xml:space="preserve">10.2946138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455305099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5301008224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6382989883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.765588760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8546905517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6319341659546</t>
   </si>
   <si>
     <t xml:space="preserve">10.7178544998169</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">10.5841999053955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6542091369629</t>
+    <t xml:space="preserve">10.6542100906372</t>
   </si>
   <si>
     <t xml:space="preserve">10.7083082199097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7051248550415</t>
+    <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796674728394</t>
@@ -1313,55 +1313,55 @@
     <t xml:space="preserve">10.5269203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4409980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5014600753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078268051147</t>
+    <t xml:space="preserve">10.5396480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4409990310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5014610290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078248977661</t>
   </si>
   <si>
     <t xml:space="preserve">10.297797203064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.332802772522</t>
+    <t xml:space="preserve">10.3328018188477</t>
   </si>
   <si>
     <t xml:space="preserve">10.2596092224121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2864856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.252890586853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0143737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99421787261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83968544006348</t>
+    <t xml:space="preserve">10.2864847183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2528915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1319522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0143728256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.994215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83968448638916</t>
   </si>
   <si>
     <t xml:space="preserve">9.49702548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5541353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77585697174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88335704803467</t>
+    <t xml:space="preserve">9.55413627624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77585601806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88335609436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.86991786956787</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">9.65491771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67843151092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52054214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79937171936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75233936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7825756072998</t>
+    <t xml:space="preserve">9.67843341827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52054119110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79937267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75234031677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78257465362549</t>
   </si>
   <si>
     <t xml:space="preserve">9.90015316009521</t>
@@ -1391,106 +1391,106 @@
     <t xml:space="preserve">9.80609035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76241683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82960605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69858932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76913738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60116767883301</t>
+    <t xml:space="preserve">9.76241874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82960510253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69859027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76913642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60116672515869</t>
   </si>
   <si>
     <t xml:space="preserve">9.61796379089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52390003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51718139648438</t>
+    <t xml:space="preserve">9.52390098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51718235015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.61124420166016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59108734130859</t>
+    <t xml:space="preserve">9.59108924865723</t>
   </si>
   <si>
     <t xml:space="preserve">9.80945014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77249622344971</t>
+    <t xml:space="preserve">9.77249526977539</t>
   </si>
   <si>
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6515588760376</t>
+    <t xml:space="preserve">9.65155792236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.66163635253906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70530891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84976196289062</t>
+    <t xml:space="preserve">9.70530796051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84976291656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.85648155212402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8161678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74898052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89007568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9035120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92366981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0479679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2125768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.111795425415</t>
+    <t xml:space="preserve">9.81616878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74898147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89007377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90351295471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92367076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070121765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0479669570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1117963790894</t>
   </si>
   <si>
     <t xml:space="preserve">9.9539041519165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0378894805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0009365081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0681247711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916395187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748414993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86655902862549</t>
+    <t xml:space="preserve">10.0378885269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0009355545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0681238174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748424530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8665599822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.71202754974365</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">9.85312175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92702770233154</t>
+    <t xml:space="preserve">9.92702865600586</t>
   </si>
   <si>
     <t xml:space="preserve">9.98077869415283</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">9.63812065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76577663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93710613250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96062278747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94382667541504</t>
+    <t xml:space="preserve">9.76577758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93710803985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9606237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94382572174072</t>
   </si>
   <si>
     <t xml:space="preserve">10.1621866226196</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">10.1554679870605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1722660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1823425292969</t>
+    <t xml:space="preserve">10.1722650527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1823415756226</t>
   </si>
   <si>
     <t xml:space="preserve">10.2965631484985</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">10.3704700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9975757598877</t>
+    <t xml:space="preserve">9.99757671356201</t>
   </si>
   <si>
     <t xml:space="preserve">9.88671684265137</t>
@@ -1565,25 +1565,25 @@
     <t xml:space="preserve">9.96734142303467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93038940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70866870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69186973571777</t>
+    <t xml:space="preserve">9.93038749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70866680145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69187164306641</t>
   </si>
   <si>
     <t xml:space="preserve">9.59444808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50038623809814</t>
+    <t xml:space="preserve">9.50038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">9.61460494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56421375274658</t>
+    <t xml:space="preserve">9.56421279907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.41304111480713</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">9.40968036651611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.288743019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23835182189941</t>
+    <t xml:space="preserve">9.28874206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2383508682251</t>
   </si>
   <si>
     <t xml:space="preserve">9.43655586242676</t>
@@ -1607,28 +1607,28 @@
     <t xml:space="preserve">9.3324146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53397941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66499519348145</t>
+    <t xml:space="preserve">9.53397846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66499710083008</t>
   </si>
   <si>
     <t xml:space="preserve">9.62468242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835403442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63476181030273</t>
+    <t xml:space="preserve">9.65827655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6347599029541</t>
   </si>
   <si>
     <t xml:space="preserve">9.57429122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71538639068604</t>
+    <t xml:space="preserve">9.71538734436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.51382255554199</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">9.59780693054199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55749416351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57765197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8195276260376</t>
+    <t xml:space="preserve">9.5574951171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57765102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81952667236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.87663745880127</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">10.0849208831787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97406005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57093238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64483833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515300750732</t>
+    <t xml:space="preserve">9.97406101226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6448392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515110015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.74562072753906</t>
@@ -1676,40 +1676,40 @@
     <t xml:space="preserve">9.89679431915283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85984134674072</t>
+    <t xml:space="preserve">9.85984039306641</t>
   </si>
   <si>
     <t xml:space="preserve">9.9505443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0210905075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0446071624756</t>
+    <t xml:space="preserve">10.0210914611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0446081161499</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647640228271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327337265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3267984390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3435955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898426055908</t>
+    <t xml:space="preserve">10.2327327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3267974853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3435945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898445129395</t>
   </si>
   <si>
     <t xml:space="preserve">10.3335161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3133602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839073181152</t>
+    <t xml:space="preserve">10.3133592605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839082717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.3771886825562</t>
@@ -1721,34 +1721,34 @@
     <t xml:space="preserve">10.1991415023804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2461700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932033538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714836120605</t>
+    <t xml:space="preserve">10.2461719512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932024002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
     <t xml:space="preserve">10.1285924911499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058591842651</t>
+    <t xml:space="preserve">10.2058582305908</t>
   </si>
   <si>
     <t xml:space="preserve">10.2831249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1890630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2293748855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260141372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730484008789</t>
+    <t xml:space="preserve">10.189061164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2293758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260160446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730474472046</t>
   </si>
   <si>
     <t xml:space="preserve">10.3805475234985</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">10.4275798797607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4342975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5451583862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089878082275</t>
+    <t xml:space="preserve">10.4342985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5451574325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089868545532</t>
   </si>
   <si>
     <t xml:space="preserve">10.6728162765503</t>
@@ -1772,40 +1772,40 @@
     <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7400035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123456954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5653162002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6157073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5921907424927</t>
+    <t xml:space="preserve">10.7400026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.565315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6157064437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5921897888184</t>
   </si>
   <si>
     <t xml:space="preserve">10.6224250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7534408569336</t>
+    <t xml:space="preserve">10.7534399032593</t>
   </si>
   <si>
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.072582244873</t>
+    <t xml:space="preserve">11.0725831985474</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591468811035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0322713851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0692253112793</t>
+    <t xml:space="preserve">11.0322723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0692262649536</t>
   </si>
   <si>
     <t xml:space="preserve">10.985239982605</t>
@@ -1820,70 +1820,70 @@
     <t xml:space="preserve">11.0860214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2036008834839</t>
+    <t xml:space="preserve">11.2035999298096</t>
   </si>
   <si>
     <t xml:space="preserve">11.1767263412476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2304763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2237558364868</t>
+    <t xml:space="preserve">11.2304773330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2237577438354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733655929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2170381546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002410888672</t>
+    <t xml:space="preserve">11.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002420425415</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271165847778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.297664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4219627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5563383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521980285645</t>
+    <t xml:space="preserve">11.2976636886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.35813331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4219617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5563364028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521970748901</t>
   </si>
   <si>
     <t xml:space="preserve">11.4286804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622745513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5832138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.552978515625</t>
+    <t xml:space="preserve">11.4622755050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5832147598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5529775619507</t>
   </si>
   <si>
     <t xml:space="preserve">11.6235256195068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6201667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5261039733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824314117432</t>
+    <t xml:space="preserve">11.6201677322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6302433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5261030197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824304580688</t>
   </si>
   <si>
     <t xml:space="preserve">11.4689931869507</t>
@@ -1892,28 +1892,28 @@
     <t xml:space="preserve">11.3245391845703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3648509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4152421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093050003052</t>
+    <t xml:space="preserve">11.3648529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093069076538</t>
   </si>
   <si>
     <t xml:space="preserve">11.4253206253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5636587142944</t>
+    <t xml:space="preserve">11.5636596679688</t>
   </si>
   <si>
     <t xml:space="preserve">11.584942817688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.560112953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3189067840576</t>
+    <t xml:space="preserve">11.5601119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3189077377319</t>
   </si>
   <si>
     <t xml:space="preserve">11.5459241867065</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">11.2124929428101</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1486444473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1238145828247</t>
+    <t xml:space="preserve">11.2763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.148645401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1238164901733</t>
   </si>
   <si>
     <t xml:space="preserve">11.2727947235107</t>
@@ -1946,61 +1946,61 @@
     <t xml:space="preserve">11.2195873260498</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2479629516602</t>
+    <t xml:space="preserve">11.2479639053345</t>
   </si>
   <si>
     <t xml:space="preserve">11.3366432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4536981582642</t>
+    <t xml:space="preserve">11.4537000656128</t>
   </si>
   <si>
     <t xml:space="preserve">11.4288692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4785280227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4466037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175466537476</t>
+    <t xml:space="preserve">11.4785289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4466047286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175476074219</t>
   </si>
   <si>
     <t xml:space="preserve">11.7445631027222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8119592666626</t>
+    <t xml:space="preserve">11.8119583129883</t>
   </si>
   <si>
     <t xml:space="preserve">11.8332414627075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8403367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7871294021606</t>
+    <t xml:space="preserve">11.8403348922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7871284484863</t>
   </si>
   <si>
     <t xml:space="preserve">11.7481098175049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7126388549805</t>
+    <t xml:space="preserve">11.7126398086548</t>
   </si>
   <si>
     <t xml:space="preserve">11.7977695465088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8935432434082</t>
+    <t xml:space="preserve">11.8935422897339</t>
   </si>
   <si>
     <t xml:space="preserve">12.1063718795776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1312017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0708990097046</t>
+    <t xml:space="preserve">12.1312026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0708980560303</t>
   </si>
   <si>
     <t xml:space="preserve">12.1418418884277</t>
@@ -2009,34 +2009,34 @@
     <t xml:space="preserve">12.1773138046265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2092370986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2056913375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560316085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808614730835</t>
+    <t xml:space="preserve">12.2092380523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2056922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808624267578</t>
   </si>
   <si>
     <t xml:space="preserve">12.1170120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.989315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0247888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0105981826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567102432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9751253128052</t>
+    <t xml:space="preserve">11.9893140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.024787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105991363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9751272201538</t>
   </si>
   <si>
     <t xml:space="preserve">11.996410369873</t>
@@ -2051,46 +2051,46 @@
     <t xml:space="preserve">11.9573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6629791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884885787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707530975342</t>
+    <t xml:space="preserve">11.6629800796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884876251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707540512085</t>
   </si>
   <si>
     <t xml:space="preserve">11.6594324111938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3437356948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3792085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2940769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4749813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5069046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168661117554</t>
+    <t xml:space="preserve">11.3437366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3792095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430561065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.29407787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4749803543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5069055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168670654297</t>
   </si>
   <si>
     <t xml:space="preserve">11.5778474807739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4678888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820747375488</t>
+    <t xml:space="preserve">11.467887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820737838745</t>
   </si>
   <si>
     <t xml:space="preserve">11.6558856964111</t>
@@ -2099,49 +2099,49 @@
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487903594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6842622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7090921401978</t>
+    <t xml:space="preserve">11.6487913131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6842613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
     <t xml:space="preserve">11.7374687194824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9432039260864</t>
+    <t xml:space="preserve">11.9432020187378</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1347484588623</t>
+    <t xml:space="preserve">12.1347494125366</t>
   </si>
   <si>
     <t xml:space="preserve">12.2021427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1844072341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3014631271362</t>
+    <t xml:space="preserve">12.1844081878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3014640808105</t>
   </si>
   <si>
     <t xml:space="preserve">12.4149713516235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3972358703613</t>
+    <t xml:space="preserve">12.3972368240356</t>
   </si>
   <si>
     <t xml:space="preserve">12.3262929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2908229827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.688102722168</t>
+    <t xml:space="preserve">12.2908239364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6881008148193</t>
   </si>
   <si>
     <t xml:space="preserve">12.6597232818604</t>
@@ -2150,31 +2150,31 @@
     <t xml:space="preserve">12.7058372497559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6739130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7413063049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6987438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6703672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6136121749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5852336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5213842391968</t>
+    <t xml:space="preserve">12.6739120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7413082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6987409591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6703653335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5852346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5213861465454</t>
   </si>
   <si>
     <t xml:space="preserve">12.606517791748</t>
@@ -2183,85 +2183,85 @@
     <t xml:space="preserve">12.5887823104858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6490821838379</t>
+    <t xml:space="preserve">12.6490812301636</t>
   </si>
   <si>
     <t xml:space="preserve">12.6774597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8157968521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.744854927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441753387451</t>
+    <t xml:space="preserve">12.8157997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7448568344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441762924194</t>
   </si>
   <si>
     <t xml:space="preserve">12.8477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8406276702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0357189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0463619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0534553527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0499095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0286264419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9364013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8938341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1243982315063</t>
+    <t xml:space="preserve">12.8406295776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215320587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0463628768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0534572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0499105453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0286254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9364004135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.893835067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.124400138855</t>
   </si>
   <si>
     <t xml:space="preserve">13.1882476806641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139039993286</t>
+    <t xml:space="preserve">13.1917934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.642279624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.61390209198</t>
   </si>
   <si>
     <t xml:space="preserve">13.8338241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7167701721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997123718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2662839889526</t>
+    <t xml:space="preserve">13.7167692184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997152328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.266284942627</t>
   </si>
   <si>
     <t xml:space="preserve">13.2237176895142</t>
@@ -2270,25 +2270,25 @@
     <t xml:space="preserve">13.2343606948853</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1527786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2591915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9754190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612293243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9399480819702</t>
+    <t xml:space="preserve">13.152777671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2591896057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456823348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9754199981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9399471282959</t>
   </si>
   <si>
     <t xml:space="preserve">12.918664932251</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">12.9257583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9541368484497</t>
+    <t xml:space="preserve">12.9541358947754</t>
   </si>
   <si>
     <t xml:space="preserve">13.0250787734985</t>
@@ -2309,58 +2309,58 @@
     <t xml:space="preserve">13.1137571334839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1314926147461</t>
+    <t xml:space="preserve">13.1314935684204</t>
   </si>
   <si>
     <t xml:space="preserve">13.1776065826416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1208534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4613771438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520971298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953401565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0640983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683265686035</t>
+    <t xml:space="preserve">13.1208515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4613761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520942687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953420639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.06409740448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683256149292</t>
   </si>
   <si>
     <t xml:space="preserve">13.1031160354614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0747394561768</t>
+    <t xml:space="preserve">13.0747413635254</t>
   </si>
   <si>
     <t xml:space="preserve">12.9115705490112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.978967666626</t>
+    <t xml:space="preserve">12.9789657592773</t>
   </si>
   <si>
     <t xml:space="preserve">12.9860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9505891799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8654565811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235717773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690042495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5710430145264</t>
+    <t xml:space="preserve">12.9505882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.865460395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235708236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5710439682007</t>
   </si>
   <si>
     <t xml:space="preserve">12.9434957504272</t>
@@ -2369,52 +2369,52 @@
     <t xml:space="preserve">12.6916475296021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4823665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5462131500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7306671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194904327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3230400085449</t>
+    <t xml:space="preserve">12.482367515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5462160110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7306661605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194913864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3230381011963</t>
   </si>
   <si>
     <t xml:space="preserve">13.3939800262451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3688592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2979164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2482566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5352830886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4004907608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1628332138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8116664886475</t>
+    <t xml:space="preserve">12.3688583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2979154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2482557296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5352821350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4004917144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8116674423218</t>
   </si>
   <si>
     <t xml:space="preserve">9.76171493530273</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">9.61273574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36769104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56278133392334</t>
+    <t xml:space="preserve">8.36769008636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56278324127197</t>
   </si>
   <si>
     <t xml:space="preserve">8.01297760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69728374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36739873886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72565937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920656204224</t>
+    <t xml:space="preserve">7.69728326797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569833755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72566080093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920751571655</t>
   </si>
   <si>
     <t xml:space="preserve">8.58406639099121</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">8.77915859222412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77206420898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398845672607</t>
+    <t xml:space="preserve">8.77206325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398750305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.58051872253418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74723339080811</t>
+    <t xml:space="preserve">8.74723434448242</t>
   </si>
   <si>
     <t xml:space="preserve">8.64436817169189</t>
@@ -2483,10 +2483,10 @@
     <t xml:space="preserve">9.1303243637085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31832313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93878078460693</t>
+    <t xml:space="preserve">9.31832408905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93877983093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.7898006439209</t>
@@ -2495,70 +2495,70 @@
     <t xml:space="preserve">8.88912010192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84300804138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77561092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04164600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20126914978027</t>
+    <t xml:space="preserve">8.63017845153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84300708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04164695739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20126819610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.435378074646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23319149017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00972366333008</t>
+    <t xml:space="preserve">9.23319244384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00972270965576</t>
   </si>
   <si>
     <t xml:space="preserve">9.176438331604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03455352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0948543548584</t>
+    <t xml:space="preserve">9.0345516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09485340118408</t>
   </si>
   <si>
     <t xml:space="preserve">9.20481491088867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12323093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08421325683594</t>
+    <t xml:space="preserve">9.12322998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08421230316162</t>
   </si>
   <si>
     <t xml:space="preserve">8.91040325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044078826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17269134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01014709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05817127227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78849506378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96212196350098</t>
+    <t xml:space="preserve">8.80044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17269039154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01014614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05817031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78849315643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96212100982666</t>
   </si>
   <si>
     <t xml:space="preserve">9.20963287353516</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">9.39803695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43867206573486</t>
+    <t xml:space="preserve">9.43867301940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.22440910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52364158630371</t>
+    <t xml:space="preserve">9.52363967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.81178665161133</t>
@@ -2585,67 +2585,67 @@
     <t xml:space="preserve">10.3474445343018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6282033920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540632247925</t>
+    <t xml:space="preserve">10.6282052993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540641784668</t>
   </si>
   <si>
     <t xml:space="preserve">10.5395441055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3215847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92261123657227</t>
+    <t xml:space="preserve">10.3215856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9226131439209</t>
   </si>
   <si>
     <t xml:space="preserve">9.91891860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90414142608643</t>
+    <t xml:space="preserve">9.90414237976074</t>
   </si>
   <si>
     <t xml:space="preserve">10.1257934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.051908493042</t>
+    <t xml:space="preserve">10.0519094467163</t>
   </si>
   <si>
     <t xml:space="preserve">9.92630672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0592975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703802108765</t>
+    <t xml:space="preserve">10.0592985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703811645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.80070400238037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9152250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95216655731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94847297668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2218427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1553468704224</t>
+    <t xml:space="preserve">9.82656288146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91522407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9521656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94847202301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2218437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.155345916748</t>
   </si>
   <si>
     <t xml:space="preserve">10.2587852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1627349853516</t>
+    <t xml:space="preserve">10.1627368927002</t>
   </si>
   <si>
     <t xml:space="preserve">9.89675331115723</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">9.97063732147217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0777683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.129487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070646286011</t>
+    <t xml:space="preserve">10.0777702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1294870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070655822754</t>
   </si>
   <si>
     <t xml:space="preserve">10.2107601165771</t>
@@ -2669,40 +2669,40 @@
     <t xml:space="preserve">10.114709854126</t>
   </si>
   <si>
-    <t xml:space="preserve">10.181206703186</t>
+    <t xml:space="preserve">10.1812057495117</t>
   </si>
   <si>
     <t xml:space="preserve">10.3289737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2772560119629</t>
+    <t xml:space="preserve">10.2772550582886</t>
   </si>
   <si>
     <t xml:space="preserve">10.0408267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98541355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97433280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46453285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35370635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40911960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63077163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38695335388184</t>
+    <t xml:space="preserve">9.98541450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97433090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46453380584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3537073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40911865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55688571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63077068328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38695430755615</t>
   </si>
   <si>
     <t xml:space="preserve">9.78592681884766</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">9.53841590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70834922790527</t>
+    <t xml:space="preserve">9.70835018157959</t>
   </si>
   <si>
     <t xml:space="preserve">9.62707710266113</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">9.62338161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61968803405762</t>
+    <t xml:space="preserve">9.61968898773193</t>
   </si>
   <si>
     <t xml:space="preserve">9.57535839080811</t>
@@ -2759,67 +2759,67 @@
     <t xml:space="preserve">9.48669719696045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47561454772949</t>
+    <t xml:space="preserve">9.47561550140381</t>
   </si>
   <si>
     <t xml:space="preserve">9.46083831787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36478805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10619449615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75155353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70352840423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66658496856689</t>
+    <t xml:space="preserve">9.36478900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10619640350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75155258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70352745056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66658592224121</t>
   </si>
   <si>
     <t xml:space="preserve">8.59639644622803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53359413146973</t>
+    <t xml:space="preserve">8.53359508514404</t>
   </si>
   <si>
     <t xml:space="preserve">8.86976623535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81804847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88454246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76632881164551</t>
+    <t xml:space="preserve">8.81804752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88454341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76632976531982</t>
   </si>
   <si>
     <t xml:space="preserve">8.91779041290283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14313697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11358261108398</t>
+    <t xml:space="preserve">9.1431360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1135835647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.29829406738281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24288082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22071552276611</t>
+    <t xml:space="preserve">9.24288177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2207145690918</t>
   </si>
   <si>
     <t xml:space="preserve">9.12466716766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1209716796875</t>
+    <t xml:space="preserve">9.12097263336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.80327033996582</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">9.03969955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81435298919678</t>
+    <t xml:space="preserve">8.81435394287109</t>
   </si>
   <si>
     <t xml:space="preserve">8.82543659210205</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">8.77371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39321517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41907501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50404071807861</t>
+    <t xml:space="preserve">8.39321422576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41907405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50404262542725</t>
   </si>
   <si>
     <t xml:space="preserve">8.721999168396</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">9.01383972167969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14683055877686</t>
+    <t xml:space="preserve">9.14683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">9.72312641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95955371856689</t>
+    <t xml:space="preserve">9.95955467224121</t>
   </si>
   <si>
     <t xml:space="preserve">9.94477844238281</t>
@@ -2885,37 +2885,37 @@
     <t xml:space="preserve">10.5136833190918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3954696655273</t>
+    <t xml:space="preserve">10.395468711853</t>
   </si>
   <si>
     <t xml:space="preserve">10.4952125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5062961578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6245107650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7094755172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910057067871</t>
+    <t xml:space="preserve">10.5062952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6245098114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">10.5801792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6577568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7648887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713171005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.609733581543</t>
+    <t xml:space="preserve">10.6577587127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7648897171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7131700515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6097326278687</t>
   </si>
   <si>
     <t xml:space="preserve">10.5838737487793</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">10.4065523147583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.535849571228</t>
+    <t xml:space="preserve">10.5358486175537</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506258010864</t>
@@ -2945,22 +2945,22 @@
     <t xml:space="preserve">10.6134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5764846801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809495925903</t>
+    <t xml:space="preserve">10.5764856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809505462646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6983938217163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7464189529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6392879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6836175918579</t>
+    <t xml:space="preserve">10.7464179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6392860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6836166381836</t>
   </si>
   <si>
     <t xml:space="preserve">10.7168645858765</t>
@@ -2975,28 +2975,28 @@
     <t xml:space="preserve">10.7205600738525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6429815292358</t>
+    <t xml:space="preserve">10.6429805755615</t>
   </si>
   <si>
     <t xml:space="preserve">10.4102468490601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5321550369263</t>
+    <t xml:space="preserve">10.5321559906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.6947002410889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0456476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3929033279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4778690338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145544052124</t>
+    <t xml:space="preserve">11.0456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3929023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4778699874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145553588867</t>
   </si>
   <si>
     <t xml:space="preserve">11.6884384155273</t>
@@ -3005,55 +3005,55 @@
     <t xml:space="preserve">11.6441087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.599778175354</t>
+    <t xml:space="preserve">11.5997772216797</t>
   </si>
   <si>
     <t xml:space="preserve">11.5739183425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6921329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5665302276611</t>
+    <t xml:space="preserve">11.6921339035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367197036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5665292739868</t>
   </si>
   <si>
     <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4815635681152</t>
+    <t xml:space="preserve">11.511116027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4815626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.4557046890259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5000333786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6995220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4889526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6958265304565</t>
+    <t xml:space="preserve">11.5000343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.699520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4889535903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6958274841309</t>
   </si>
   <si>
     <t xml:space="preserve">11.7290744781494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8768444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.825122833252</t>
+    <t xml:space="preserve">11.8435964584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8768434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.1908493041992</t>
@@ -3065,52 +3065,52 @@
     <t xml:space="preserve">12.2795104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3866405487061</t>
+    <t xml:space="preserve">12.3866415023804</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900798797607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4383602142334</t>
+    <t xml:space="preserve">12.4383592605591</t>
   </si>
   <si>
     <t xml:space="preserve">12.4789962768555</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755588531494</t>
+    <t xml:space="preserve">12.3755598068237</t>
   </si>
   <si>
     <t xml:space="preserve">12.4568319320679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3607807159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4161968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125022888184</t>
+    <t xml:space="preserve">12.3607816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4161958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.412501335144</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048542022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6045989990234</t>
+    <t xml:space="preserve">12.5048561096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6045999526978</t>
   </si>
   <si>
     <t xml:space="preserve">12.66370677948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5824337005615</t>
+    <t xml:space="preserve">12.5824346542358</t>
   </si>
   <si>
     <t xml:space="preserve">12.6600131988525</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6858730316162</t>
+    <t xml:space="preserve">12.6858720779419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6378469467163</t>
@@ -3125,34 +3125,34 @@
     <t xml:space="preserve">12.6230697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5787391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.726508140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4457483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679136276245</t>
+    <t xml:space="preserve">12.5787410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6489295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265071868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.3977251052856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3275356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5602693557739</t>
+    <t xml:space="preserve">12.3275337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5602684020996</t>
   </si>
   <si>
     <t xml:space="preserve">12.4420557022095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5972108840942</t>
+    <t xml:space="preserve">12.5972089767456</t>
   </si>
   <si>
     <t xml:space="preserve">12.7228136062622</t>
@@ -3164,16 +3164,16 @@
     <t xml:space="preserve">12.9740190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9149131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9592428207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331249237061</t>
+    <t xml:space="preserve">12.8631935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9149112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9592437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331258773804</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368204116821</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">13.0626802444458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881664276123</t>
+    <t xml:space="preserve">12.8816652297974</t>
   </si>
   <si>
     <t xml:space="preserve">12.8890523910522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0479021072388</t>
+    <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
     <t xml:space="preserve">13.2438163757324</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">13.1184320449829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9773721694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0910043716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2007150650024</t>
+    <t xml:space="preserve">12.9773731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2007160186768</t>
   </si>
   <si>
     <t xml:space="preserve">13.1772060394287</t>
@@ -3218,10 +3218,10 @@
     <t xml:space="preserve">13.3887920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5180969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4985065460205</t>
+    <t xml:space="preserve">13.5180988311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985055923462</t>
   </si>
   <si>
     <t xml:space="preserve">13.4632425308228</t>
@@ -3236,46 +3236,46 @@
     <t xml:space="preserve">13.4397315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4514875411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102615356445</t>
+    <t xml:space="preserve">13.4514865875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102596282959</t>
   </si>
   <si>
     <t xml:space="preserve">13.2359800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2320623397827</t>
+    <t xml:space="preserve">13.2712450027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.232063293457</t>
   </si>
   <si>
     <t xml:space="preserve">13.0518217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3339366912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1262674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732873916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2477369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.373122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3221826553345</t>
+    <t xml:space="preserve">13.3339357376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732883453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2477359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3731212615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3221836090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.4358139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.196798324585</t>
+    <t xml:space="preserve">13.1967973709106</t>
   </si>
   <si>
     <t xml:space="preserve">12.9852104187012</t>
@@ -3284,34 +3284,34 @@
     <t xml:space="preserve">13.3261003494263</t>
   </si>
   <si>
-    <t xml:space="preserve">13.330020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2634077072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1654510498047</t>
+    <t xml:space="preserve">13.3300199508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2634086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.165452003479</t>
   </si>
   <si>
     <t xml:space="preserve">13.1145143508911</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7148485183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1223516464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1576166152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1301879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046356201172</t>
+    <t xml:space="preserve">12.7148475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.122350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1301860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046346664429</t>
   </si>
   <si>
     <t xml:space="preserve">13.0674934387207</t>
@@ -3323,46 +3323,46 @@
     <t xml:space="preserve">13.0283117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281427383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4749965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.569034576416</t>
+    <t xml:space="preserve">13.2281436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456945419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4749956130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5690355300903</t>
   </si>
   <si>
     <t xml:space="preserve">13.6160545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5376892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5416078567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3770399093628</t>
+    <t xml:space="preserve">13.5376882553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5416088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3770389556885</t>
   </si>
   <si>
     <t xml:space="preserve">13.4436502456665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4240579605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848762512207</t>
+    <t xml:space="preserve">13.4240589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848752975464</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5337715148926</t>
+    <t xml:space="preserve">13.5337705612183</t>
   </si>
   <si>
     <t xml:space="preserve">13.5964632034302</t>
@@ -3371,52 +3371,52 @@
     <t xml:space="preserve">13.6121368408203</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5729551315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7414388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8393964767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9060096740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591558456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8315591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8824987411499</t>
+    <t xml:space="preserve">13.5729541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7414398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8393974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9060087203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923765182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8824977874756</t>
   </si>
   <si>
     <t xml:space="preserve">14.0039653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8589868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0901679992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2037992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.364447593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3017549514771</t>
+    <t xml:space="preserve">13.8589897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0901670455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2037973403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3644485473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3017568588257</t>
   </si>
   <si>
     <t xml:space="preserve">14.4349775314331</t>
@@ -3425,37 +3425,37 @@
     <t xml:space="preserve">14.4114675521851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271402359009</t>
+    <t xml:space="preserve">14.4271392822266</t>
   </si>
   <si>
     <t xml:space="preserve">14.399712562561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6896648406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5642805099487</t>
+    <t xml:space="preserve">14.6896657943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5642795562744</t>
   </si>
   <si>
     <t xml:space="preserve">14.7014207839966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7288503646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816633224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6622371673584</t>
+    <t xml:space="preserve">14.7288484573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8072137832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816623687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6622362136841</t>
   </si>
   <si>
     <t xml:space="preserve">14.6739931106567</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7249307632446</t>
+    <t xml:space="preserve">14.7249298095703</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851810455322</t>
@@ -3464,55 +3464,55 @@
     <t xml:space="preserve">14.8494462966919</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9739608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9217462539673</t>
+    <t xml:space="preserve">14.9739599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9217472076416</t>
   </si>
   <si>
     <t xml:space="preserve">14.95387840271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0141286849976</t>
+    <t xml:space="preserve">15.0141277313232</t>
   </si>
   <si>
     <t xml:space="preserve">15.118558883667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0663433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1346254348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310247421265</t>
+    <t xml:space="preserve">15.0663414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1346263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310237884521</t>
   </si>
   <si>
     <t xml:space="preserve">15.2470903396606</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3234071731567</t>
+    <t xml:space="preserve">15.3234081268311</t>
   </si>
   <si>
     <t xml:space="preserve">15.2591419219971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.347505569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2430763244629</t>
+    <t xml:space="preserve">15.347508430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2430753707886</t>
   </si>
   <si>
     <t xml:space="preserve">15.25110912323</t>
   </si>
   <si>
-    <t xml:space="preserve">15.279224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3836574554443</t>
+    <t xml:space="preserve">15.2792263031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.38365650177</t>
   </si>
   <si>
     <t xml:space="preserve">15.3716068267822</t>
@@ -3521,109 +3521,109 @@
     <t xml:space="preserve">15.4559545516968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0743770599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6887807846069</t>
+    <t xml:space="preserve">15.0743780136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418287277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6887817382812</t>
   </si>
   <si>
     <t xml:space="preserve">14.7811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7570638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168979644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1867027282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2991676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2429351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5642652511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4919681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6124649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.022162437439</t>
+    <t xml:space="preserve">14.7570648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168989181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1867036819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299168586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2429361343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.564266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4919672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6124658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498605728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0221614837646</t>
   </si>
   <si>
     <t xml:space="preserve">14.8574800491333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9297780990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8614959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6767320632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731294631958</t>
+    <t xml:space="preserve">14.9297771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213291168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6767311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731313705444</t>
   </si>
   <si>
     <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9016618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623273849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9659280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671747207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788091659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333787918091</t>
+    <t xml:space="preserve">14.9016609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060930252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9659271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333806991577</t>
   </si>
   <si>
     <t xml:space="preserve">14.9177274703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8293628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337949752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0583095550537</t>
+    <t xml:space="preserve">14.8293619155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337959289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.058310508728</t>
   </si>
   <si>
     <t xml:space="preserve">15.0422439575195</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8132982254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9257612228394</t>
+    <t xml:space="preserve">14.8132972717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9257621765137</t>
   </si>
   <si>
     <t xml:space="preserve">15.1466751098633</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">15.0382261276245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1627426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3754863739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847658157349</t>
+    <t xml:space="preserve">15.1627435684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3754844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847648620605</t>
   </si>
   <si>
     <t xml:space="preserve">14.6727142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9940452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7369813919067</t>
+    <t xml:space="preserve">14.9940462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7369794845581</t>
   </si>
   <si>
     <t xml:space="preserve">14.9819946289062</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">14.596399307251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0300540924072</t>
+    <t xml:space="preserve">14.0300559997559</t>
   </si>
   <si>
     <t xml:space="preserve">14.371467590332</t>
@@ -3686,19 +3686,19 @@
     <t xml:space="preserve">13.8372573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7770090103149</t>
+    <t xml:space="preserve">13.7770080566406</t>
   </si>
   <si>
     <t xml:space="preserve">13.0379495620728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7447376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.993766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6243753433228</t>
+    <t xml:space="preserve">12.7447366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9937658309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6243762969971</t>
   </si>
   <si>
     <t xml:space="preserve">13.4958448410034</t>
@@ -3707,19 +3707,19 @@
     <t xml:space="preserve">13.7930755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1746549606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3875341415405</t>
+    <t xml:space="preserve">14.174654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3875350952148</t>
   </si>
   <si>
     <t xml:space="preserve">15.0824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0502767562866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1667585372925</t>
+    <t xml:space="preserve">15.0502786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1667594909668</t>
   </si>
   <si>
     <t xml:space="preserve">15.3153743743896</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">15.6005544662476</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1789455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8495826721191</t>
+    <t xml:space="preserve">16.1789474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8495845794678</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6850414276123</t>
+    <t xml:space="preserve">16.6850433349609</t>
   </si>
   <si>
     <t xml:space="preserve">16.9581718444824</t>
@@ -3755,46 +3755,46 @@
     <t xml:space="preserve">15.5523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.733099937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6166200637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.484073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.411771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4760389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9980621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7932147979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5441837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4598350524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5401649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7048492431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6205005645752</t>
+    <t xml:space="preserve">15.7331027984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6166219711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4117727279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.476037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9980611801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7932138442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5441818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4598331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5401668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196691513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7048473358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204986572266</t>
   </si>
   <si>
     <t xml:space="preserve">14.4518013000488</t>
@@ -3806,67 +3806,67 @@
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268695831299</t>
+    <t xml:space="preserve">14.2268686294556</t>
   </si>
   <si>
     <t xml:space="preserve">14.2670373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947374343872</t>
+    <t xml:space="preserve">14.1947364807129</t>
   </si>
   <si>
     <t xml:space="preserve">14.3112192153931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4558172225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8871421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7547550201416</t>
+    <t xml:space="preserve">14.4558181762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8871431350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7547540664673</t>
   </si>
   <si>
     <t xml:space="preserve">14.8230838775635</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828716278076</t>
+    <t xml:space="preserve">14.8828706741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.5882034301758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5540390014648</t>
+    <t xml:space="preserve">14.5540409088135</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430046081543</t>
+    <t xml:space="preserve">14.4430055618286</t>
   </si>
   <si>
     <t xml:space="preserve">14.3789463043213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2764530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643573760986</t>
+    <t xml:space="preserve">14.2764539718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643564224243</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2081241607666</t>
+    <t xml:space="preserve">14.2081251144409</t>
   </si>
   <si>
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344388961792</t>
+    <t xml:space="preserve">13.3924503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881797790527</t>
+    <t xml:space="preserve">13.3881788253784</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">13.1917333602905</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6828470230103</t>
+    <t xml:space="preserve">13.6828479766846</t>
   </si>
   <si>
     <t xml:space="preserve">13.2686033248901</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.294225692749</t>
+    <t xml:space="preserve">13.0038290023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2942266464233</t>
   </si>
   <si>
     <t xml:space="preserve">13.1661100387573</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">12.5596923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0678882598877</t>
+    <t xml:space="preserve">13.0678873062134</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276750564575</t>
@@ -3929,25 +3929,25 @@
     <t xml:space="preserve">12.9568529129028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9952878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7774896621704</t>
+    <t xml:space="preserve">12.995288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7774906158447</t>
   </si>
   <si>
     <t xml:space="preserve">12.3547058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4401159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230346679688</t>
+    <t xml:space="preserve">12.4401168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230337142944</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838846206665</t>
+    <t xml:space="preserve">12.1838836669922</t>
   </si>
   <si>
     <t xml:space="preserve">12.1625299453735</t>
@@ -3965,19 +3965,19 @@
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333520889282</t>
+    <t xml:space="preserve">12.3333530426025</t>
   </si>
   <si>
     <t xml:space="preserve">12.4571990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4700107574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5340690612793</t>
+    <t xml:space="preserve">12.7134323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.470009803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.534068107605</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408319473267</t>
@@ -4001,40 +4001,40 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8970670700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7646789550781</t>
+    <t xml:space="preserve">13.1618394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.897066116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7646780014038</t>
   </si>
   <si>
     <t xml:space="preserve">12.7006206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8757123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5767736434937</t>
+    <t xml:space="preserve">12.8757133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.576774597168</t>
   </si>
   <si>
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5041751861572</t>
+    <t xml:space="preserve">12.6579141616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5041761398315</t>
   </si>
   <si>
     <t xml:space="preserve">12.3931407928467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4828214645386</t>
+    <t xml:space="preserve">12.8330068588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4828224182129</t>
   </si>
   <si>
     <t xml:space="preserve">12.4486570358276</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.768949508667</t>
+    <t xml:space="preserve">12.7689485549927</t>
   </si>
   <si>
     <t xml:space="preserve">13.1703815460205</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.704891204834</t>
+    <t xml:space="preserve">12.7048902511597</t>
   </si>
   <si>
     <t xml:space="preserve">12.7390546798706</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">12.3248119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4443874359131</t>
+    <t xml:space="preserve">12.4443864822388</t>
   </si>
   <si>
     <t xml:space="preserve">12.1411781311035</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">12.0173320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251581192017</t>
+    <t xml:space="preserve">11.8251571655273</t>
   </si>
   <si>
     <t xml:space="preserve">11.9746265411377</t>
@@ -4085,34 +4085,34 @@
     <t xml:space="preserve">12.3845996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1326370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8550510406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.73974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575433731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7909936904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0045204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1582593917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2991876602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3632469177246</t>
+    <t xml:space="preserve">12.1326360702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8550519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7397451400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7909927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0045213699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.158260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2991886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3632478713989</t>
   </si>
   <si>
     <t xml:space="preserve">12.5169858932495</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091608047485</t>
+    <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
@@ -4151,55 +4151,55 @@
     <t xml:space="preserve">13.8493986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9433507919312</t>
+    <t xml:space="preserve">13.9433517456055</t>
   </si>
   <si>
     <t xml:space="preserve">14.2294778823853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4045696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6095561981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5839328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.515604019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.741943359375</t>
+    <t xml:space="preserve">14.4045705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6095571517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5839338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7419443130493</t>
   </si>
   <si>
     <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5027923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600887298584</t>
+    <t xml:space="preserve">14.5027914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686298370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6266393661499</t>
+    <t xml:space="preserve">14.4686288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6266374588013</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7035102844238</t>
+    <t xml:space="preserve">14.7035093307495</t>
   </si>
   <si>
     <t xml:space="preserve">14.6992378234863</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7931900024414</t>
+    <t xml:space="preserve">14.7931909561157</t>
   </si>
   <si>
     <t xml:space="preserve">14.6906967163086</t>
@@ -4208,118 +4208,118 @@
     <t xml:space="preserve">14.7889194488525</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7462139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8444366455078</t>
+    <t xml:space="preserve">14.7462129592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999538421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8444356918335</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2508306503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2892646789551</t>
+    <t xml:space="preserve">14.0928192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2508296966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2892637252808</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3490533828735</t>
+    <t xml:space="preserve">14.3490524291992</t>
   </si>
   <si>
     <t xml:space="preserve">14.3106174468994</t>
   </si>
   <si>
-    <t xml:space="preserve">14.259370803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3618659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1910429000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3276996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504844665527</t>
+    <t xml:space="preserve">14.2593717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3618650436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1910419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3277006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917589187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504854202271</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6736164093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017330169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615188598633</t>
+    <t xml:space="preserve">14.6736154556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615198135376</t>
   </si>
   <si>
     <t xml:space="preserve">14.8487071990967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9554710388184</t>
+    <t xml:space="preserve">14.9554719924927</t>
   </si>
   <si>
     <t xml:space="preserve">14.968282699585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8358974456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1689987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2373275756836</t>
+    <t xml:space="preserve">14.8358964920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.168999671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2373285293579</t>
   </si>
   <si>
     <t xml:space="preserve">15.3013868331909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2586803436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3825273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.28857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5021018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.416690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4679365158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4636669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063714981079</t>
+    <t xml:space="preserve">15.2586793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971162796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270101547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3825263977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2885732650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319948196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4679384231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4636659622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063734054565</t>
   </si>
   <si>
     <t xml:space="preserve">15.5618896484375</t>
@@ -4331,37 +4331,37 @@
     <t xml:space="preserve">15.6003246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5875120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473016738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6857347488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850196838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106439590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.664381980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9804019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223924636841</t>
+    <t xml:space="preserve">15.587513923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344900131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850206375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106420516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6643829345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9804029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223934173584</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4373,52 +4373,52 @@
     <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0658130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9078035354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7327108383179</t>
+    <t xml:space="preserve">16.0658149719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9078044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7327117919922</t>
   </si>
   <si>
     <t xml:space="preserve">15.2031631469727</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7540636062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8316259384155</t>
+    <t xml:space="preserve">15.7540645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8316249847412</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4508562088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081506729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1092119216919</t>
+    <t xml:space="preserve">15.0451536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.450855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1092128753662</t>
   </si>
   <si>
     <t xml:space="preserve">15.2501392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4423141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6259469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6985473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6729230880737</t>
+    <t xml:space="preserve">15.4423131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6259479522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6985464096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
     <t xml:space="preserve">15.6216793060303</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">16.091438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683101654053</t>
+    <t xml:space="preserve">16.1683082580566</t>
   </si>
   <si>
     <t xml:space="preserve">16.0401916503906</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">16.2836132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3049659729004</t>
+    <t xml:space="preserve">16.3049640655518</t>
   </si>
   <si>
     <t xml:space="preserve">16.3092365264893</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">16.232364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1256008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9334297180176</t>
+    <t xml:space="preserve">16.125602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9334278106689</t>
   </si>
   <si>
     <t xml:space="preserve">15.8053112030029</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890721321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1127910614014</t>
+    <t xml:space="preserve">15.8907203674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1127891540527</t>
   </si>
   <si>
     <t xml:space="preserve">16.0316524505615</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">16.4688701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596549987793</t>
+    <t xml:space="preserve">16.2596569061279</t>
   </si>
   <si>
     <t xml:space="preserve">16.332426071167</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">16.4188404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5189018249512</t>
+    <t xml:space="preserve">16.5188999176025</t>
   </si>
   <si>
     <t xml:space="preserve">16.6462478637695</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">16.9236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1010627746582</t>
+    <t xml:space="preserve">17.1010646820068</t>
   </si>
   <si>
     <t xml:space="preserve">17.2193164825439</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">16.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7963371276855</t>
+    <t xml:space="preserve">16.7963390350342</t>
   </si>
   <si>
     <t xml:space="preserve">16.6689910888672</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.6280574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235679626465</t>
+    <t xml:space="preserve">16.7235660552979</t>
   </si>
   <si>
     <t xml:space="preserve">16.6917304992676</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">16.9373321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5103969573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4330806732178</t>
+    <t xml:space="preserve">17.5103988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4330787658691</t>
   </si>
   <si>
     <t xml:space="preserve">17.2056732177734</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">17.1783828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0692253112793</t>
+    <t xml:space="preserve">17.1920261383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0692272186279</t>
   </si>
   <si>
     <t xml:space="preserve">17.2829914093018</t>
@@ -4616,13 +4616,13 @@
     <t xml:space="preserve">17.3648567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3739528656006</t>
+    <t xml:space="preserve">17.3739547729492</t>
   </si>
   <si>
     <t xml:space="preserve">17.3330192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3284721374512</t>
+    <t xml:space="preserve">17.3284702301025</t>
   </si>
   <si>
     <t xml:space="preserve">17.5149459838867</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">17.5240421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6286506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4057903289795</t>
+    <t xml:space="preserve">17.6286487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4057922363281</t>
   </si>
   <si>
     <t xml:space="preserve">17.037389755249</t>
@@ -4649,16 +4649,16 @@
     <t xml:space="preserve">17.091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7190189361572</t>
+    <t xml:space="preserve">16.9737167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7190170288086</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8736572265625</t>
+    <t xml:space="preserve">16.8736553192139</t>
   </si>
   <si>
     <t xml:space="preserve">16.7417602539062</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">16.7645015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281745910645</t>
+    <t xml:space="preserve">16.8281764984131</t>
   </si>
   <si>
     <t xml:space="preserve">16.8418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9282360076904</t>
+    <t xml:space="preserve">16.9282341003418</t>
   </si>
   <si>
     <t xml:space="preserve">17.0737762451172</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">17.442174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4012413024902</t>
+    <t xml:space="preserve">17.4012432098389</t>
   </si>
   <si>
     <t xml:space="preserve">17.292085647583</t>
@@ -4691,13 +4691,13 @@
     <t xml:space="preserve">17.3011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6013622283936</t>
+    <t xml:space="preserve">17.6013603210449</t>
   </si>
   <si>
     <t xml:space="preserve">17.7150650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7332592010498</t>
+    <t xml:space="preserve">17.7332572937012</t>
   </si>
   <si>
     <t xml:space="preserve">18.0197906494141</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">18.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1926231384277</t>
+    <t xml:space="preserve">18.1926212310791</t>
   </si>
   <si>
     <t xml:space="preserve">18.0470809936523</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">17.7878360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059074401855</t>
+    <t xml:space="preserve">17.6059093475342</t>
   </si>
   <si>
     <t xml:space="preserve">17.6832294464111</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">16.8918476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3239250183105</t>
+    <t xml:space="preserve">17.3239231109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.4876575469971</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">17.0510349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2966346740723</t>
+    <t xml:space="preserve">17.2966327667236</t>
   </si>
   <si>
     <t xml:space="preserve">17.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1238040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1465473175049</t>
+    <t xml:space="preserve">17.1238059997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1465454101562</t>
   </si>
   <si>
     <t xml:space="preserve">17.2511539459229</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">17.8787994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8151226043701</t>
+    <t xml:space="preserve">17.8151245117188</t>
   </si>
   <si>
     <t xml:space="preserve">17.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4922065734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3148288726807</t>
+    <t xml:space="preserve">17.4922046661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">17.187479019165</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">17.242057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.141996383667</t>
+    <t xml:space="preserve">17.1419982910156</t>
   </si>
   <si>
     <t xml:space="preserve">17.2284126281738</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">17.4103393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4148864746094</t>
+    <t xml:space="preserve">17.414888381958</t>
   </si>
   <si>
     <t xml:space="preserve">17.496753692627</t>
@@ -4895,13 +4895,13 @@
     <t xml:space="preserve">17.9561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0061473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9015407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9515686035156</t>
+    <t xml:space="preserve">18.0061454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.901538848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9515705108643</t>
   </si>
   <si>
     <t xml:space="preserve">17.9379234313965</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">18.6201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5473766326904</t>
+    <t xml:space="preserve">18.5473785400391</t>
   </si>
   <si>
     <t xml:space="preserve">18.5655708312988</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">18.6656303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6929168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8202667236328</t>
+    <t xml:space="preserve">18.6929187774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8202686309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.629243850708</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">18.7565937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6838226318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.729305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5564727783203</t>
+    <t xml:space="preserve">18.6838245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7293033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5564746856689</t>
   </si>
   <si>
     <t xml:space="preserve">18.8384590148926</t>
@@ -4985,25 +4985,25 @@
     <t xml:space="preserve">19.5024909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1392307281494</t>
+    <t xml:space="preserve">20.139232635498</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9118251800537</t>
+    <t xml:space="preserve">19.9118232727051</t>
   </si>
   <si>
     <t xml:space="preserve">19.9664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0027866363525</t>
+    <t xml:space="preserve">20.0027885437012</t>
   </si>
   <si>
     <t xml:space="preserve">20.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1574249267578</t>
+    <t xml:space="preserve">20.1574230194092</t>
   </si>
   <si>
     <t xml:space="preserve">20.0755577087402</t>
@@ -5012,16 +5012,16 @@
     <t xml:space="preserve">20.2120018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2847709655762</t>
+    <t xml:space="preserve">20.2847728729248</t>
   </si>
   <si>
     <t xml:space="preserve">20.393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5940475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6122417449951</t>
+    <t xml:space="preserve">20.5940456390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6122398376465</t>
   </si>
   <si>
     <t xml:space="preserve">20.6759147644043</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">21.1034412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3399448394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127159118652</t>
+    <t xml:space="preserve">21.3399429321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127178192139</t>
   </si>
   <si>
     <t xml:space="preserve">21.5309677124023</t>
@@ -5060,10 +5060,10 @@
     <t xml:space="preserve">20.8669376373291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0306720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7304935455322</t>
+    <t xml:space="preserve">21.0306701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7304916381836</t>
   </si>
   <si>
     <t xml:space="preserve">20.7577800750732</t>
@@ -5072,13 +5072,13 @@
     <t xml:space="preserve">20.6031436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7032032012939</t>
+    <t xml:space="preserve">20.7032051086426</t>
   </si>
   <si>
     <t xml:space="preserve">20.3393516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4394092559814</t>
+    <t xml:space="preserve">20.4394111633301</t>
   </si>
   <si>
     <t xml:space="preserve">20.4939880371094</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">20.6213359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7122993469238</t>
+    <t xml:space="preserve">20.7123012542725</t>
   </si>
   <si>
     <t xml:space="preserve">21.003381729126</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">21.2307891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7765693664551</t>
+    <t xml:space="preserve">21.7765674591064</t>
   </si>
   <si>
     <t xml:space="preserve">21.7401809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9039173126221</t>
+    <t xml:space="preserve">21.9039154052734</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949977874756</t>
@@ -6063,6 +6063,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.2599983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8699989318848</t>
   </si>
 </sst>
 </file>
@@ -71453,7 +71456,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911342593</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>1862793</v>
@@ -71474,6 +71477,32 @@
         <v>2016</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6938078704</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>2178201</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>33.0499992370605</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>32.5800018310547</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>33.0400009155273</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>32.8699989318848</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="2018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="2019">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31058979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13427352905273</t>
+    <t xml:space="preserve">9.31059074401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13427257537842</t>
   </si>
   <si>
     <t xml:space="preserve">9.11721038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02052211761475</t>
+    <t xml:space="preserve">9.02052116394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.76458072662354</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">8.88970756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0660228729248</t>
+    <t xml:space="preserve">9.06602382659912</t>
   </si>
   <si>
     <t xml:space="preserve">8.95795917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75889205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376522064209</t>
+    <t xml:space="preserve">8.75889301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376617431641</t>
   </si>
   <si>
     <t xml:space="preserve">8.29251003265381</t>
@@ -83,73 +83,73 @@
     <t xml:space="preserve">8.44607543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48588752746582</t>
+    <t xml:space="preserve">8.48588848114014</t>
   </si>
   <si>
     <t xml:space="preserve">8.30957317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04794406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93988037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568784713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4166202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23461818695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1549916267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74548530578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47248077392578</t>
+    <t xml:space="preserve">8.04794311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93987941741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568593978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.234619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15499210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74548482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47247934341431</t>
   </si>
   <si>
     <t xml:space="preserve">6.81373596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23360157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34166526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59760713577271</t>
+    <t xml:space="preserve">6.23360252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34166479110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59760808944702</t>
   </si>
   <si>
     <t xml:space="preserve">6.62035799026489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77392339706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72842073440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66017007827759</t>
+    <t xml:space="preserve">6.77392196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72842311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66017150878906</t>
   </si>
   <si>
     <t xml:space="preserve">6.89905023574829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89336252212524</t>
+    <t xml:space="preserve">6.8933629989624</t>
   </si>
   <si>
     <t xml:space="preserve">6.95592546463013</t>
@@ -158,61 +158,61 @@
     <t xml:space="preserve">7.26305627822876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28580760955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643520355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4507474899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24599266052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249492645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37112092971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575361251831</t>
+    <t xml:space="preserve">7.28580570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643281936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45074558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680864334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24599313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3199315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249444961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37111949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575456619263</t>
   </si>
   <si>
     <t xml:space="preserve">7.83750295639038</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79200172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731552124023</t>
+    <t xml:space="preserve">7.79200267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731647491455</t>
   </si>
   <si>
     <t xml:space="preserve">7.89437818527222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76356410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67256259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037357330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3654317855835</t>
+    <t xml:space="preserve">7.76356315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543273925781</t>
   </si>
   <si>
     <t xml:space="preserve">7.42799663543701</t>
@@ -221,115 +221,115 @@
     <t xml:space="preserve">7.48487186431885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41093254089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9843635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00711345672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85354852676392</t>
+    <t xml:space="preserve">7.41093349456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30286836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755456924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98436307907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00711393356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85354900360107</t>
   </si>
   <si>
     <t xml:space="preserve">7.05261564254761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13792943954468</t>
+    <t xml:space="preserve">7.13792848587036</t>
   </si>
   <si>
     <t xml:space="preserve">7.16067981719971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4336838722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49624681472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47918558120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862422943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75218963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456562042236</t>
+    <t xml:space="preserve">7.43368291854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4962477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862279891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218868255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181524276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456466674805</t>
   </si>
   <si>
     <t xml:space="preserve">7.80337762832642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77493906021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5701847076416</t>
+    <t xml:space="preserve">7.77493858337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
   </si>
   <si>
     <t xml:space="preserve">7.39387035369873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35405731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53606128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16636800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0583028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517763137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798934936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994874954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84845161437988</t>
+    <t xml:space="preserve">7.35405826568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53606033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105325698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16636657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05830192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25168085098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8484525680542</t>
   </si>
   <si>
     <t xml:space="preserve">7.90873193740845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94490051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85448026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76405954360962</t>
+    <t xml:space="preserve">7.94490098953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8544807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76406002044678</t>
   </si>
   <si>
     <t xml:space="preserve">7.54705286026001</t>
@@ -338,40 +338,40 @@
     <t xml:space="preserve">7.534996509552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66158390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625677108765</t>
+    <t xml:space="preserve">7.66158533096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625629425049</t>
   </si>
   <si>
     <t xml:space="preserve">7.77008819580078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42046499252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17934417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97439289093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850368499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9201397895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19139909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40840911865234</t>
+    <t xml:space="preserve">7.42046356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17934370040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439336776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92014074325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1914005279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4084095954895</t>
   </si>
   <si>
     <t xml:space="preserve">7.54102420806885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5832200050354</t>
+    <t xml:space="preserve">7.58322095870972</t>
   </si>
   <si>
     <t xml:space="preserve">6.58257341384888</t>
@@ -380,40 +380,40 @@
     <t xml:space="preserve">6.02498292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11841678619385</t>
+    <t xml:space="preserve">6.11841726303101</t>
   </si>
   <si>
     <t xml:space="preserve">6.26308965682983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25103330612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13047313690186</t>
+    <t xml:space="preserve">6.35953664779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4318733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25103282928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1304726600647</t>
   </si>
   <si>
     <t xml:space="preserve">5.91647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92853450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790102005005</t>
+    <t xml:space="preserve">5.92853593826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790197372437</t>
   </si>
   <si>
     <t xml:space="preserve">6.76341342926025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69710493087769</t>
+    <t xml:space="preserve">6.69710397720337</t>
   </si>
   <si>
     <t xml:space="preserve">6.8719162940979</t>
@@ -422,64 +422,64 @@
     <t xml:space="preserve">6.80560922622681</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8417763710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84780406951904</t>
+    <t xml:space="preserve">6.84177684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738573074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84780359268188</t>
   </si>
   <si>
     <t xml:space="preserve">6.77546882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73327350616455</t>
+    <t xml:space="preserve">6.73327159881592</t>
   </si>
   <si>
     <t xml:space="preserve">6.68504905700684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81163692474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62476825714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10098028182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07084035873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79355335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06481313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990339279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73930215835571</t>
+    <t xml:space="preserve">6.81163787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10098075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083988189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7935528755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387760162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210062026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289766311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000082015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808439254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73930168151855</t>
   </si>
   <si>
     <t xml:space="preserve">7.04070043563843</t>
@@ -494,97 +494,97 @@
     <t xml:space="preserve">6.74532890319824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61271333694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149652481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425249099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93822574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88397216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98041963577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523195266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770854949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313310623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079643249512</t>
+    <t xml:space="preserve">6.61271381378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149700164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93822526931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88397407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98042058944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313215255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079738616943</t>
   </si>
   <si>
     <t xml:space="preserve">6.72724485397339</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79958057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75135707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59462928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56448841094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57654476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668468475342</t>
+    <t xml:space="preserve">6.7995810508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75135660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59462785720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56449031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5765438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668563842773</t>
   </si>
   <si>
     <t xml:space="preserve">6.5464038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51626491546631</t>
+    <t xml:space="preserve">6.51626443862915</t>
   </si>
   <si>
     <t xml:space="preserve">6.4981803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76944017410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383272171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1853723526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1672887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26976442337036</t>
+    <t xml:space="preserve">6.76943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85985946655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18537282943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16728830337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784894943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26976585388184</t>
   </si>
   <si>
     <t xml:space="preserve">7.33004522323608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31195974349976</t>
+    <t xml:space="preserve">7.31196069717407</t>
   </si>
   <si>
     <t xml:space="preserve">7.14317750930786</t>
@@ -596,61 +596,61 @@
     <t xml:space="preserve">6.98644828796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67299222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574819564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08892631530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07686853408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8779444694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02261638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82369184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854904174805</t>
+    <t xml:space="preserve">6.67299270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08892393112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07686948776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87794494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02261590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8236927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854761123657</t>
   </si>
   <si>
     <t xml:space="preserve">7.35415601730347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73392009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055332183838</t>
+    <t xml:space="preserve">7.73392105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055236816406</t>
   </si>
   <si>
     <t xml:space="preserve">8.68031597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45125102996826</t>
+    <t xml:space="preserve">8.45125198364258</t>
   </si>
   <si>
     <t xml:space="preserve">8.47536373138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41508483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33069133758545</t>
+    <t xml:space="preserve">8.41508388519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33069229125977</t>
   </si>
   <si>
     <t xml:space="preserve">8.541672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5597562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63812065124512</t>
+    <t xml:space="preserve">8.55975532531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6381196975708</t>
   </si>
   <si>
     <t xml:space="preserve">8.5838680267334</t>
@@ -659,97 +659,97 @@
     <t xml:space="preserve">8.59592437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6622314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66826152801514</t>
+    <t xml:space="preserve">8.66223239898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6682596206665</t>
   </si>
   <si>
     <t xml:space="preserve">8.55372714996338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50550365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51153182983398</t>
+    <t xml:space="preserve">8.50550556182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5115327835083</t>
   </si>
   <si>
     <t xml:space="preserve">8.65017604827881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71045589447021</t>
+    <t xml:space="preserve">8.7104549407959</t>
   </si>
   <si>
     <t xml:space="preserve">8.75265216827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69840049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71648406982422</t>
+    <t xml:space="preserve">8.69840145111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7164831161499</t>
   </si>
   <si>
     <t xml:space="preserve">8.52358818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48741912841797</t>
+    <t xml:space="preserve">8.48742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">8.38494396209717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25835609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23424530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16793727874756</t>
+    <t xml:space="preserve">8.25835704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23424243927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16793632507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.27041244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26438331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58989715576172</t>
+    <t xml:space="preserve">8.26438426971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5898962020874</t>
   </si>
   <si>
     <t xml:space="preserve">9.2951717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38559246063232</t>
+    <t xml:space="preserve">9.38559150695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.42175960540771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28311538696289</t>
+    <t xml:space="preserve">9.28311634063721</t>
   </si>
   <si>
     <t xml:space="preserve">8.98774337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88526725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84910106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00582790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993869781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8189582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77073574066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67428779602051</t>
+    <t xml:space="preserve">8.88526821136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84910011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00582695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993965148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81896018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77073764801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67428684234619</t>
   </si>
   <si>
     <t xml:space="preserve">8.7405948638916</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">8.90335178375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04802513122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87923908233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90938091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95760345458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83101463317871</t>
+    <t xml:space="preserve">9.04802322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87923812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90937995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95760440826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83101654052734</t>
   </si>
   <si>
     <t xml:space="preserve">8.81293201446533</t>
@@ -779,61 +779,61 @@
     <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65620517730713</t>
+    <t xml:space="preserve">8.6562032699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.49947643280029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14985179901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27643871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54769992828369</t>
+    <t xml:space="preserve">8.14985275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27643966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54769897460938</t>
   </si>
   <si>
     <t xml:space="preserve">8.46330738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56578350067139</t>
+    <t xml:space="preserve">8.56578254699707</t>
   </si>
   <si>
     <t xml:space="preserve">8.78881931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80087661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484844207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78279209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86718368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98171615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80690288543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6320915222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60797882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46933650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36083221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93348979949951</t>
+    <t xml:space="preserve">8.80087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.794846534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78279113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86718273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98171520233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80690383911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63209247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6079797744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46933555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36083126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93349075317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.75867938995361</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">9.19269561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21077919006348</t>
+    <t xml:space="preserve">9.21078014373779</t>
   </si>
   <si>
     <t xml:space="preserve">9.24091911315918</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">8.94554805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89129543304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03596878051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07213687896729</t>
+    <t xml:space="preserve">8.89129638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03596782684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07213592529297</t>
   </si>
   <si>
     <t xml:space="preserve">9.12035942077637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30492973327637</t>
+    <t xml:space="preserve">9.30493068695068</t>
   </si>
   <si>
     <t xml:space="preserve">9.33675384521484</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">9.18400573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15854835510254</t>
+    <t xml:space="preserve">9.15854740142822</t>
   </si>
   <si>
     <t xml:space="preserve">9.13309001922607</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">8.94851875305176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83395576477051</t>
+    <t xml:space="preserve">8.83395671844482</t>
   </si>
   <si>
     <t xml:space="preserve">8.94215297698975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03761959075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81486415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758266448975</t>
+    <t xml:space="preserve">9.03762149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81486129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758075714111</t>
   </si>
   <si>
     <t xml:space="preserve">8.73848819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89123725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95488166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05035018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22855758666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2349214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17127513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28583812713623</t>
+    <t xml:space="preserve">8.89123821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95488262176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05034923553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22855567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23492240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1712760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28583717346191</t>
   </si>
   <si>
     <t xml:space="preserve">9.2985668182373</t>
@@ -935,31 +935,31 @@
     <t xml:space="preserve">9.19036960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34948062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25401401519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24765014648438</t>
+    <t xml:space="preserve">9.34948253631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25401496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219276428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24765110015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.29220199584961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33038997650146</t>
+    <t xml:space="preserve">9.33038902282715</t>
   </si>
   <si>
     <t xml:space="preserve">9.38130474090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57860565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54678344726562</t>
+    <t xml:space="preserve">9.57860660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54678249359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.54041767120361</t>
@@ -971,103 +971,103 @@
     <t xml:space="preserve">9.79500007629395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85864448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68680286407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56587600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52769088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75681209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77590656280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750389099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0877685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1386833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2341499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1959638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0623083114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0050277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82682228088379</t>
+    <t xml:space="preserve">9.85864353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68680191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56587505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52768898010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75681304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750379562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1386823654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.23415184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1959648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0623092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0050287246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82682132720947</t>
   </si>
   <si>
     <t xml:space="preserve">9.86500835418701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90319538116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82045745849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87137317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78226947784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71226024627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69953155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68043804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69316577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134548187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53405380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52132415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57224082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61679172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67407417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62952041625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59769821166992</t>
+    <t xml:space="preserve">9.90319633483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82045841217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87137508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78227138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71225929260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69953060150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6804370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69316673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134357452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53405284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52132511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57223987579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61679267883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.674072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62952136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59770011901855</t>
   </si>
   <si>
     <t xml:space="preserve">9.89046669006348</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">9.75044631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89683151245117</t>
+    <t xml:space="preserve">9.89683246612549</t>
   </si>
   <si>
     <t xml:space="preserve">9.91592502593994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8777379989624</t>
+    <t xml:space="preserve">9.87773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">10.0304861068726</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">10.0686740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1323194503784</t>
+    <t xml:space="preserve">10.1323184967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.93501949310303</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">9.84591484069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85227966308594</t>
+    <t xml:space="preserve">9.85227870941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.83318614959717</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">9.96047592163086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0177564620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9541130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1259546279907</t>
+    <t xml:space="preserve">10.0177574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95411205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1259527206421</t>
   </si>
   <si>
     <t xml:space="preserve">10.0241212844849</t>
@@ -1133,31 +1133,31 @@
     <t xml:space="preserve">9.94138336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8841028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0368509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78863430023193</t>
+    <t xml:space="preserve">9.88410377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0368499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78863525390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58497047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61042785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6677074432373</t>
+    <t xml:space="preserve">9.58497142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61042976379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66770839691162</t>
   </si>
   <si>
     <t xml:space="preserve">9.74408340454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73135375976562</t>
+    <t xml:space="preserve">9.73135471343994</t>
   </si>
   <si>
     <t xml:space="preserve">9.8077278137207</t>
@@ -1172,79 +1172,79 @@
     <t xml:space="preserve">9.5595121383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47677421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97320652008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97957134246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0814018249512</t>
+    <t xml:space="preserve">9.47677326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97956943511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0814027786255</t>
   </si>
   <si>
     <t xml:space="preserve">10.0559453964233</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291431427002</t>
+    <t xml:space="preserve">10.2914323806763</t>
   </si>
   <si>
     <t xml:space="preserve">10.3041610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023305892944</t>
+    <t xml:space="preserve">10.2023286819458</t>
   </si>
   <si>
     <t xml:space="preserve">10.310525894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3232555389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736869812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641407012939</t>
+    <t xml:space="preserve">10.3232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736879348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641426086426</t>
   </si>
   <si>
     <t xml:space="preserve">10.148229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99230003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76954078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86819076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81727504730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77908802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81409358978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80454635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36857414245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85546016693115</t>
+    <t xml:space="preserve">9.99229907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76954174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86819267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81727409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77908897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8140926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36857604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65179824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85546112060547</t>
   </si>
   <si>
     <t xml:space="preserve">9.74726581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0082111358643</t>
+    <t xml:space="preserve">10.0082120895386</t>
   </si>
   <si>
     <t xml:space="preserve">9.98593425750732</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">9.94456577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97002220153809</t>
+    <t xml:space="preserve">9.9700231552124</t>
   </si>
   <si>
     <t xml:space="preserve">10.0495805740356</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">10.1609592437744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3137083053589</t>
+    <t xml:space="preserve">10.3137063980103</t>
   </si>
   <si>
     <t xml:space="preserve">10.2946138381958</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">10.3455305099487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5301008224487</t>
+    <t xml:space="preserve">10.4346342086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.530101776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.6382989883423</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">10.765588760376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8546905517578</t>
+    <t xml:space="preserve">10.8546924591064</t>
   </si>
   <si>
     <t xml:space="preserve">10.6319341659546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7178544998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5841999053955</t>
+    <t xml:space="preserve">10.7178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5841989517212</t>
   </si>
   <si>
     <t xml:space="preserve">10.6542100906372</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796674728394</t>
+    <t xml:space="preserve">10.6796684265137</t>
   </si>
   <si>
     <t xml:space="preserve">10.5269203186035</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4409990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5014610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078248977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.297797203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3328018188477</t>
+    <t xml:space="preserve">10.4409980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5014600753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078268051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2977962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.332802772522</t>
   </si>
   <si>
     <t xml:space="preserve">10.2596092224121</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">10.2864847183228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2528915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.994215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83968448638916</t>
+    <t xml:space="preserve">10.2528896331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1319532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0143737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99421691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83968544006348</t>
   </si>
   <si>
     <t xml:space="preserve">9.49702548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55413627624512</t>
+    <t xml:space="preserve">9.55413436889648</t>
   </si>
   <si>
     <t xml:space="preserve">9.77585601806641</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">9.88335609436035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86991786956787</t>
+    <t xml:space="preserve">9.86991882324219</t>
   </si>
   <si>
     <t xml:space="preserve">9.65491771697998</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">9.67843341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52054119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79937267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75234031677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78257465362549</t>
+    <t xml:space="preserve">9.52054214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79937076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75233936309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7825756072998</t>
   </si>
   <si>
     <t xml:space="preserve">9.90015316009521</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">9.76241874694824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82960510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69859027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76913642883301</t>
+    <t xml:space="preserve">9.82960605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69858932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76913738250732</t>
   </si>
   <si>
     <t xml:space="preserve">9.60116672515869</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">9.51718235015869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61124420166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59108924865723</t>
+    <t xml:space="preserve">9.61124515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59108829498291</t>
   </si>
   <si>
     <t xml:space="preserve">9.80945014953613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77249526977539</t>
+    <t xml:space="preserve">9.77249622344971</t>
   </si>
   <si>
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65155792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163635253906</t>
+    <t xml:space="preserve">9.65155982971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163730621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">9.74898147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89007377624512</t>
+    <t xml:space="preserve">9.89007568359375</t>
   </si>
   <si>
     <t xml:space="preserve">9.90351295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92367076873779</t>
+    <t xml:space="preserve">9.92366886138916</t>
   </si>
   <si>
     <t xml:space="preserve">9.97070121765137</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">10.0479669570923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2125778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1117963790894</t>
+    <t xml:space="preserve">10.2125768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1117973327637</t>
   </si>
   <si>
     <t xml:space="preserve">9.9539041519165</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">10.0378885269165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009355545044</t>
+    <t xml:space="preserve">10.0009365081787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0681238174438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916385650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748424530029</t>
+    <t xml:space="preserve">10.0916395187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748414993286</t>
   </si>
   <si>
     <t xml:space="preserve">9.8665599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71202754974365</t>
+    <t xml:space="preserve">9.71202659606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.73218250274658</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">9.92702865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98077869415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92031002044678</t>
+    <t xml:space="preserve">9.98077964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92030906677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.63812065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76577758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93710803985596</t>
+    <t xml:space="preserve">9.76577663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93710708618164</t>
   </si>
   <si>
     <t xml:space="preserve">9.9606237411499</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">10.1017169952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0882806777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554679870605</t>
+    <t xml:space="preserve">10.0882797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1554670333862</t>
   </si>
   <si>
     <t xml:space="preserve">10.1722650527954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1823415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2965631484985</t>
+    <t xml:space="preserve">10.1823425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2965621948242</t>
   </si>
   <si>
     <t xml:space="preserve">10.4141416549683</t>
@@ -1553,37 +1553,37 @@
     <t xml:space="preserve">10.4309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3704700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99757671356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88671684265137</t>
+    <t xml:space="preserve">10.3704690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9975757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88671588897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.96734142303467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93038749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70866680145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69187164306641</t>
+    <t xml:space="preserve">9.93038845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70866775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69187068939209</t>
   </si>
   <si>
     <t xml:space="preserve">9.59444808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50038433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61460494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56421279907227</t>
+    <t xml:space="preserve">9.50038528442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61460399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56421375274658</t>
   </si>
   <si>
     <t xml:space="preserve">9.41304111480713</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">9.43991565704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40968036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28874206542969</t>
+    <t xml:space="preserve">9.40968227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.288743019104</t>
   </si>
   <si>
     <t xml:space="preserve">9.2383508682251</t>
@@ -1610,31 +1610,31 @@
     <t xml:space="preserve">9.53397846221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66499710083008</t>
+    <t xml:space="preserve">9.66499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.62468242645264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65827655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835594177246</t>
+    <t xml:space="preserve">9.658278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835498809814</t>
   </si>
   <si>
     <t xml:space="preserve">9.6347599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57429122924805</t>
+    <t xml:space="preserve">9.57429218292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.71538734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51382255554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59780693054199</t>
+    <t xml:space="preserve">9.51382350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59780788421631</t>
   </si>
   <si>
     <t xml:space="preserve">9.5574951171875</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">9.57765102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81952667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87663745880127</t>
+    <t xml:space="preserve">9.8195276260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87663650512695</t>
   </si>
   <si>
     <t xml:space="preserve">9.9135913848877</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">10.0042953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0849208831787</t>
+    <t xml:space="preserve">10.084921836853</t>
   </si>
   <si>
     <t xml:space="preserve">9.97406101226807</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">9.6448392868042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68515110015869</t>
+    <t xml:space="preserve">9.68515205383301</t>
   </si>
   <si>
     <t xml:space="preserve">9.74562072753906</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">9.89679431915283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85984039306641</t>
+    <t xml:space="preserve">9.85984134674072</t>
   </si>
   <si>
     <t xml:space="preserve">9.9505443572998</t>
@@ -1685,16 +1685,16 @@
     <t xml:space="preserve">10.0210914611816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0446081161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647640228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3267974853516</t>
+    <t xml:space="preserve">10.0446071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647630691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327337265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3267984390259</t>
   </si>
   <si>
     <t xml:space="preserve">10.3435945510864</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">10.2898445129395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3335161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3133592605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3839082717896</t>
+    <t xml:space="preserve">10.333517074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3133602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.3771886825562</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">10.276406288147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1991415023804</t>
+    <t xml:space="preserve">10.1991395950317</t>
   </si>
   <si>
     <t xml:space="preserve">10.2461719512939</t>
@@ -1730,22 +1730,22 @@
     <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1285924911499</t>
+    <t xml:space="preserve">10.1285934448242</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058582305908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2831249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.189061164856</t>
+    <t xml:space="preserve">10.2831258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1890630722046</t>
   </si>
   <si>
     <t xml:space="preserve">10.2293758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260160446167</t>
+    <t xml:space="preserve">10.2260150909424</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730474472046</t>
@@ -1754,49 +1754,49 @@
     <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4275798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4342985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5451574325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6728162765503</t>
+    <t xml:space="preserve">10.4275808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4342994689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5451583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672815322876</t>
   </si>
   <si>
     <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7400026321411</t>
+    <t xml:space="preserve">10.7400035858154</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.565315246582</t>
+    <t xml:space="preserve">10.5653162002563</t>
   </si>
   <si>
     <t xml:space="preserve">10.6157064437866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5921897888184</t>
+    <t xml:space="preserve">10.5921907424927</t>
   </si>
   <si>
     <t xml:space="preserve">10.6224250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7534399032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9785213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0725831985474</t>
+    <t xml:space="preserve">10.7534418106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9785203933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0725841522217</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591468811035</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">11.0322723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0692262649536</t>
+    <t xml:space="preserve">11.069224357605</t>
   </si>
   <si>
     <t xml:space="preserve">10.985239982605</t>
@@ -1814,16 +1814,16 @@
     <t xml:space="preserve">10.9718027114868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0087566375732</t>
+    <t xml:space="preserve">11.0087547302246</t>
   </si>
   <si>
     <t xml:space="preserve">11.0860214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1767263412476</t>
+    <t xml:space="preserve">11.2036018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1767272949219</t>
   </si>
   <si>
     <t xml:space="preserve">11.2304773330688</t>
@@ -1838,64 +1838,64 @@
     <t xml:space="preserve">11.2170391082764</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2002420425415</t>
+    <t xml:space="preserve">11.2002410888672</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271165847778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2976636886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35813331604</t>
+    <t xml:space="preserve">11.2976655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3581342697144</t>
   </si>
   <si>
     <t xml:space="preserve">11.4219617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5563364028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521970748901</t>
+    <t xml:space="preserve">11.5563383102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521961212158</t>
   </si>
   <si>
     <t xml:space="preserve">11.4286804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622755050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5832147598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5529775619507</t>
+    <t xml:space="preserve">11.4622745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.583212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.552978515625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6235256195068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6201677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6302433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5261030197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4689931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3245391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4152431488037</t>
+    <t xml:space="preserve">11.6201667785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5261039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824314117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.468994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3245401382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648519515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.415244102478</t>
   </si>
   <si>
     <t xml:space="preserve">11.5093069076538</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">11.4253206253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5636596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.584942817688</t>
+    <t xml:space="preserve">11.5636577606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5849418640137</t>
   </si>
   <si>
     <t xml:space="preserve">11.5601119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3189077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5459241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.414680480957</t>
+    <t xml:space="preserve">11.3189067840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5459232330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4146814346313</t>
   </si>
   <si>
     <t xml:space="preserve">11.3330955505371</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">11.148645401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1238164901733</t>
+    <t xml:space="preserve">11.1238145828247</t>
   </si>
   <si>
     <t xml:space="preserve">11.2727947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2195873260498</t>
+    <t xml:space="preserve">11.180567741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2195863723755</t>
   </si>
   <si>
     <t xml:space="preserve">11.2479639053345</t>
@@ -1952,34 +1952,34 @@
     <t xml:space="preserve">11.3366432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4537000656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4288692474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4785289764404</t>
+    <t xml:space="preserve">11.4536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4288682937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4785280227661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4466047286987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5175476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7445631027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119583129883</t>
+    <t xml:space="preserve">11.5175466537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7445640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119592666626</t>
   </si>
   <si>
     <t xml:space="preserve">11.8332414627075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8403348922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7871284484863</t>
+    <t xml:space="preserve">11.8403358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7871294021606</t>
   </si>
   <si>
     <t xml:space="preserve">11.7481098175049</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">11.7126398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7977695465088</t>
+    <t xml:space="preserve">11.7977705001831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8935422897339</t>
@@ -1997,28 +1997,28 @@
     <t xml:space="preserve">12.1063718795776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1312026977539</t>
+    <t xml:space="preserve">12.1312007904053</t>
   </si>
   <si>
     <t xml:space="preserve">12.0708980560303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1418418884277</t>
+    <t xml:space="preserve">12.1418428421021</t>
   </si>
   <si>
     <t xml:space="preserve">12.1773138046265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2092380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2056922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808624267578</t>
+    <t xml:space="preserve">12.2092370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2056894302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560306549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808605194092</t>
   </si>
   <si>
     <t xml:space="preserve">12.1170120239258</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">11.9893140792847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.024787902832</t>
+    <t xml:space="preserve">12.0247888565063</t>
   </si>
   <si>
     <t xml:space="preserve">12.0105991363525</t>
@@ -2036,37 +2036,37 @@
     <t xml:space="preserve">12.0567121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9751272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.996410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8545246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9467496871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573907852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6629800796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884876251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707540512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6594324111938</t>
+    <t xml:space="preserve">11.9751262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9964094161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8545236587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9467506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6629791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884885787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707530975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6594314575195</t>
   </si>
   <si>
     <t xml:space="preserve">11.3437366485596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3792095184326</t>
+    <t xml:space="preserve">11.3792085647583</t>
   </si>
   <si>
     <t xml:space="preserve">11.4430561065674</t>
@@ -2078,19 +2078,19 @@
     <t xml:space="preserve">11.4749803543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5069055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168670654297</t>
+    <t xml:space="preserve">11.5069046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168661117554</t>
   </si>
   <si>
     <t xml:space="preserve">11.5778474807739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.467887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820737838745</t>
+    <t xml:space="preserve">11.4678888320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820756912231</t>
   </si>
   <si>
     <t xml:space="preserve">11.6558856964111</t>
@@ -2099,25 +2099,25 @@
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487913131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6842613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7090911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7374687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9432020187378</t>
+    <t xml:space="preserve">11.6487903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6842603683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7090902328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7374696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9432029724121</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1347494125366</t>
+    <t xml:space="preserve">12.1347484588623</t>
   </si>
   <si>
     <t xml:space="preserve">12.2021427154541</t>
@@ -2126,49 +2126,49 @@
     <t xml:space="preserve">12.1844081878662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3014640808105</t>
+    <t xml:space="preserve">12.3014631271362</t>
   </si>
   <si>
     <t xml:space="preserve">12.4149713516235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3972368240356</t>
+    <t xml:space="preserve">12.397234916687</t>
   </si>
   <si>
     <t xml:space="preserve">12.3262929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2908239364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6881008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6597232818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6739120483398</t>
+    <t xml:space="preserve">12.2908229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6881017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6597242355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058353424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6739130020142</t>
   </si>
   <si>
     <t xml:space="preserve">12.7413082122803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6987409591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6703653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6136112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5852346420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759536743164</t>
+    <t xml:space="preserve">12.6987428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6703643798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6136121749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5852355957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759517669678</t>
   </si>
   <si>
     <t xml:space="preserve">12.4433498382568</t>
@@ -2177,61 +2177,61 @@
     <t xml:space="preserve">12.5213861465454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.606517791748</t>
+    <t xml:space="preserve">12.6065187454224</t>
   </si>
   <si>
     <t xml:space="preserve">12.5887823104858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6490812301636</t>
+    <t xml:space="preserve">12.6490831375122</t>
   </si>
   <si>
     <t xml:space="preserve">12.6774597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7448568344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441762924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8406295776367</t>
+    <t xml:space="preserve">12.8157978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.744854927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8406286239624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0357208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215320587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0463628768921</t>
+    <t xml:space="preserve">13.0357189178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0463619232178</t>
   </si>
   <si>
     <t xml:space="preserve">13.0534572601318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0499105453491</t>
+    <t xml:space="preserve">13.0499095916748</t>
   </si>
   <si>
     <t xml:space="preserve">13.0286254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9364004135132</t>
+    <t xml:space="preserve">12.9364013671875</t>
   </si>
   <si>
     <t xml:space="preserve">12.893835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.124400138855</t>
+    <t xml:space="preserve">13.1243991851807</t>
   </si>
   <si>
     <t xml:space="preserve">13.1882476806641</t>
@@ -2243,46 +2243,46 @@
     <t xml:space="preserve">13.642279624939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.61390209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338241577148</t>
+    <t xml:space="preserve">13.6068077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139059066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338251113892</t>
   </si>
   <si>
     <t xml:space="preserve">13.7167692184448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5997152328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.266284942627</t>
+    <t xml:space="preserve">13.5997142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2662839889526</t>
   </si>
   <si>
     <t xml:space="preserve">13.2237176895142</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2343606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.152777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2591896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627363204956</t>
+    <t xml:space="preserve">13.2343597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1527786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2591924667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627372741699</t>
   </si>
   <si>
     <t xml:space="preserve">13.1456823348999</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9754199981689</t>
+    <t xml:space="preserve">12.9754190444946</t>
   </si>
   <si>
     <t xml:space="preserve">12.9612312316895</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">12.9399471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.918664932251</t>
+    <t xml:space="preserve">12.9186639785767</t>
   </si>
   <si>
     <t xml:space="preserve">12.9257583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9541358947754</t>
+    <t xml:space="preserve">12.9541368484497</t>
   </si>
   <si>
     <t xml:space="preserve">13.0250787734985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.010890007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137571334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1314935684204</t>
+    <t xml:space="preserve">13.0108909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1314926147461</t>
   </si>
   <si>
     <t xml:space="preserve">13.1776065826416</t>
@@ -2318,28 +2318,28 @@
     <t xml:space="preserve">13.1208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4613761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520942687988</t>
+    <t xml:space="preserve">13.4613771438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520952224731</t>
   </si>
   <si>
     <t xml:space="preserve">13.1953420639038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.06409740448</t>
+    <t xml:space="preserve">13.0640983581543</t>
   </si>
   <si>
     <t xml:space="preserve">12.9683256149292</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1031160354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0747413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9115705490112</t>
+    <t xml:space="preserve">13.1031179428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0747394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9115724563599</t>
   </si>
   <si>
     <t xml:space="preserve">12.9789657592773</t>
@@ -2348,58 +2348,58 @@
     <t xml:space="preserve">12.9860591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9505882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.865460395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235708236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690052032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5710439682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434957504272</t>
+    <t xml:space="preserve">12.9505891799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8654594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690042495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5710458755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434947967529</t>
   </si>
   <si>
     <t xml:space="preserve">12.6916475296021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.482367515564</t>
+    <t xml:space="preserve">12.482364654541</t>
   </si>
   <si>
     <t xml:space="preserve">12.5462160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7306661605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194913864136</t>
+    <t xml:space="preserve">12.7306671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002489089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804727554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194904327393</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3939800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3688583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2979154586792</t>
+    <t xml:space="preserve">13.3939790725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3688592910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2979145050049</t>
   </si>
   <si>
     <t xml:space="preserve">12.2482557296753</t>
@@ -2408,43 +2408,43 @@
     <t xml:space="preserve">11.5352821350098</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4004917144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8116674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76171493530273</t>
+    <t xml:space="preserve">11.4004907608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1628341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8116664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76171588897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.61273574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36769008636475</t>
+    <t xml:space="preserve">8.36769199371338</t>
   </si>
   <si>
     <t xml:space="preserve">8.56278324127197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01297760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69728326797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36739921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569833755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72566080093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920751571655</t>
+    <t xml:space="preserve">8.01297664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69728183746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36739873886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72565937042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920656204224</t>
   </si>
   <si>
     <t xml:space="preserve">8.58406639099121</t>
@@ -2453,16 +2453,16 @@
     <t xml:space="preserve">8.83236598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98134517669678</t>
+    <t xml:space="preserve">8.98134422302246</t>
   </si>
   <si>
     <t xml:space="preserve">8.77915859222412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77206325531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398750305176</t>
+    <t xml:space="preserve">8.77206420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398941040039</t>
   </si>
   <si>
     <t xml:space="preserve">8.58051872253418</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">9.07002353668213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1303243637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31832408905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93877983093262</t>
+    <t xml:space="preserve">9.13032531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31832313537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9387788772583</t>
   </si>
   <si>
     <t xml:space="preserve">8.7898006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88912010192871</t>
+    <t xml:space="preserve">8.88911914825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.63017845153809</t>
@@ -2501,25 +2501,25 @@
     <t xml:space="preserve">8.84300708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77561187744141</t>
+    <t xml:space="preserve">8.77561092376709</t>
   </si>
   <si>
     <t xml:space="preserve">9.04164695739746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20126819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.435378074646</t>
+    <t xml:space="preserve">9.20126914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43537902832031</t>
   </si>
   <si>
     <t xml:space="preserve">9.23319244384766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00972270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.176438331604</t>
+    <t xml:space="preserve">9.00972175598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17643928527832</t>
   </si>
   <si>
     <t xml:space="preserve">9.0345516204834</t>
@@ -2528,22 +2528,22 @@
     <t xml:space="preserve">9.09485340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20481491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12322998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08421230316162</t>
+    <t xml:space="preserve">9.20481586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12323093414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08421325683594</t>
   </si>
   <si>
     <t xml:space="preserve">8.91040325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17269039154053</t>
+    <t xml:space="preserve">8.80043983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17269134521484</t>
   </si>
   <si>
     <t xml:space="preserve">9.01014614105225</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">9.05817031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78849315643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99536991119385</t>
+    <t xml:space="preserve">8.78849506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99536895751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.96212100982666</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">9.39803695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43867301940918</t>
+    <t xml:space="preserve">9.43867206573486</t>
   </si>
   <si>
     <t xml:space="preserve">9.22440910339355</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">10.3474445343018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6282052993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5395441055298</t>
+    <t xml:space="preserve">10.6282043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540632247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5395431518555</t>
   </si>
   <si>
     <t xml:space="preserve">10.3215856552124</t>
@@ -2609,70 +2609,70 @@
     <t xml:space="preserve">10.1257934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0519094467163</t>
+    <t xml:space="preserve">10.051908493042</t>
   </si>
   <si>
     <t xml:space="preserve">9.92630672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0592985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80070400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82656288146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91522407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9521656036377</t>
+    <t xml:space="preserve">10.0592975616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703802108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80070495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82656478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9152250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95216655731201</t>
   </si>
   <si>
     <t xml:space="preserve">9.94847202301025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2218437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.155345916748</t>
+    <t xml:space="preserve">10.2218427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553468704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.2587852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1627368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675331115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0777702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1294870376587</t>
+    <t xml:space="preserve">10.1627359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0777683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.129487991333</t>
   </si>
   <si>
     <t xml:space="preserve">10.2070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2107601165771</t>
+    <t xml:space="preserve">10.2107610702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.114709854126</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1812057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3289737701416</t>
+    <t xml:space="preserve">10.181206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3289728164673</t>
   </si>
   <si>
     <t xml:space="preserve">10.2772550582886</t>
@@ -2687,16 +2687,16 @@
     <t xml:space="preserve">9.97433090209961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46453380584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3537073135376</t>
+    <t xml:space="preserve">9.46453285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35370540618896</t>
   </si>
   <si>
     <t xml:space="preserve">9.40911865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55688571929932</t>
+    <t xml:space="preserve">9.55688858032227</t>
   </si>
   <si>
     <t xml:space="preserve">9.63077068328857</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">9.38695430755615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78592681884766</t>
+    <t xml:space="preserve">9.78592777252197</t>
   </si>
   <si>
     <t xml:space="preserve">9.73051452636719</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">9.68618392944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53841590881348</t>
+    <t xml:space="preserve">9.53841686248779</t>
   </si>
   <si>
     <t xml:space="preserve">9.70835018157959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62707710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56058120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76376247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917476654053</t>
+    <t xml:space="preserve">9.62707614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56058216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76376152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917381286621</t>
   </si>
   <si>
     <t xml:space="preserve">9.78223323822021</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">9.62338161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61968898773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57535839080811</t>
+    <t xml:space="preserve">9.61968803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57535743713379</t>
   </si>
   <si>
     <t xml:space="preserve">9.47192001342773</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">9.37217807769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56796932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48669719696045</t>
+    <t xml:space="preserve">9.56797027587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48669815063477</t>
   </si>
   <si>
     <t xml:space="preserve">9.47561550140381</t>
@@ -2768,40 +2768,40 @@
     <t xml:space="preserve">9.36478900909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10619640350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75155258178711</t>
+    <t xml:space="preserve">9.1061954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75155353546143</t>
   </si>
   <si>
     <t xml:space="preserve">8.70352745056152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66658592224121</t>
+    <t xml:space="preserve">8.66658496856689</t>
   </si>
   <si>
     <t xml:space="preserve">8.59639644622803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53359508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804752349854</t>
+    <t xml:space="preserve">8.53359413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804847717285</t>
   </si>
   <si>
     <t xml:space="preserve">8.88454341888428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76632976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91779041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1431360244751</t>
+    <t xml:space="preserve">8.76632881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91779136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14313697814941</t>
   </si>
   <si>
     <t xml:space="preserve">9.1135835647583</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">9.24288177490234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2207145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12466716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12097263336182</t>
+    <t xml:space="preserve">9.22071647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1209716796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.80327033996582</t>
@@ -2831,25 +2831,25 @@
     <t xml:space="preserve">9.01753425598145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03969955444336</t>
+    <t xml:space="preserve">9.03969860076904</t>
   </si>
   <si>
     <t xml:space="preserve">8.81435394287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82543659210205</t>
+    <t xml:space="preserve">8.82543563842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.77371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39321422576904</t>
+    <t xml:space="preserve">8.39321517944336</t>
   </si>
   <si>
     <t xml:space="preserve">8.41907405853271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404262542725</t>
+    <t xml:space="preserve">8.50404071807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.721999168396</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">8.89193153381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01383972167969</t>
+    <t xml:space="preserve">9.01383876800537</t>
   </si>
   <si>
     <t xml:space="preserve">9.14683151245117</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">9.72312641143799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95955467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94477844238281</t>
+    <t xml:space="preserve">9.95955371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9447774887085</t>
   </si>
   <si>
     <t xml:space="preserve">10.0740747451782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3178911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4398002624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5136833190918</t>
+    <t xml:space="preserve">10.317892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4398012161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5136842727661</t>
   </si>
   <si>
     <t xml:space="preserve">10.395468711853</t>
@@ -2891,46 +2891,46 @@
     <t xml:space="preserve">10.4952125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5062952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6245098114014</t>
+    <t xml:space="preserve">10.5062961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6245088577271</t>
   </si>
   <si>
     <t xml:space="preserve">10.7094764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6910066604614</t>
+    <t xml:space="preserve">10.6910047531128</t>
   </si>
   <si>
     <t xml:space="preserve">10.5801792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6577587127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7648897171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7131700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6097326278687</t>
+    <t xml:space="preserve">10.6577577590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7648887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.713171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.609733581543</t>
   </si>
   <si>
     <t xml:space="preserve">10.5838737487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6060390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4065523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5358486175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506258010864</t>
+    <t xml:space="preserve">10.6060400009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4065532684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.535849571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506267547607</t>
   </si>
   <si>
     <t xml:space="preserve">10.5617094039917</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">10.6134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5764856338501</t>
+    <t xml:space="preserve">10.5764865875244</t>
   </si>
   <si>
     <t xml:space="preserve">10.2809505462646</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">10.6983938217163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7464179992676</t>
+    <t xml:space="preserve">10.7464189529419</t>
   </si>
   <si>
     <t xml:space="preserve">10.6392860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6836166381836</t>
+    <t xml:space="preserve">10.6836185455322</t>
   </si>
   <si>
     <t xml:space="preserve">10.7168645858765</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">10.942211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8276901245117</t>
+    <t xml:space="preserve">10.827691078186</t>
   </si>
   <si>
     <t xml:space="preserve">10.7205600738525</t>
@@ -2981,52 +2981,52 @@
     <t xml:space="preserve">10.4102468490601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5321559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6947002410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0456485748291</t>
+    <t xml:space="preserve">10.5321550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6946992874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0456476211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.3929023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4778699874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145553588867</t>
+    <t xml:space="preserve">11.4778690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145544052124</t>
   </si>
   <si>
     <t xml:space="preserve">11.6884384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441087722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5997772216797</t>
+    <t xml:space="preserve">11.6441078186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599778175354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5739183425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6921339035034</t>
+    <t xml:space="preserve">11.6921319961548</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367197036743</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5665292739868</t>
+    <t xml:space="preserve">11.5665302276611</t>
   </si>
   <si>
     <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.511116027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4815626144409</t>
+    <t xml:space="preserve">11.5111169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4815635681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4557046890259</t>
@@ -3035,19 +3035,19 @@
     <t xml:space="preserve">11.5000343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.699520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4889535903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6958274841309</t>
+    <t xml:space="preserve">11.6995220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6958265304565</t>
   </si>
   <si>
     <t xml:space="preserve">11.7290744781494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435964584351</t>
+    <t xml:space="preserve">11.8435955047607</t>
   </si>
   <si>
     <t xml:space="preserve">11.8768434524536</t>
@@ -3056,22 +3056,22 @@
     <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1908493041992</t>
+    <t xml:space="preserve">12.1908483505249</t>
   </si>
   <si>
     <t xml:space="preserve">12.2130155563354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2795104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3866415023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4900798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4383592605591</t>
+    <t xml:space="preserve">12.2795114517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3866405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4900808334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4383602142334</t>
   </si>
   <si>
     <t xml:space="preserve">12.4789962768555</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">12.4568319320679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3607816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4161958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.412501335144</t>
+    <t xml:space="preserve">12.3607807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4161968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125003814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309730529785</t>
@@ -3098,61 +3098,61 @@
     <t xml:space="preserve">12.5048561096191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6045999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.66370677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5824346542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6600131988525</t>
+    <t xml:space="preserve">12.6045989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6637048721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5824356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6600112915039</t>
   </si>
   <si>
     <t xml:space="preserve">12.6858720779419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6378469467163</t>
+    <t xml:space="preserve">12.6378479003906</t>
   </si>
   <si>
     <t xml:space="preserve">12.5344104766846</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6119871139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6230697631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5787410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6489295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265071868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679145812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3977251052856</t>
+    <t xml:space="preserve">12.611988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6230707168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5787401199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.726508140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4457483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39772605896</t>
   </si>
   <si>
     <t xml:space="preserve">12.3275337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5602684020996</t>
+    <t xml:space="preserve">12.5602693557739</t>
   </si>
   <si>
     <t xml:space="preserve">12.4420557022095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5972089767456</t>
+    <t xml:space="preserve">12.5972108840942</t>
   </si>
   <si>
     <t xml:space="preserve">12.7228136062622</t>
@@ -3164,46 +3164,46 @@
     <t xml:space="preserve">12.9740190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9149112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9592437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331258773804</t>
+    <t xml:space="preserve">12.8631944656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9149131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9592428207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331268310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.0368204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0626802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8816652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8890523910522</t>
+    <t xml:space="preserve">13.0626811981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.881664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8890514373779</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2438163757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1184320449829</t>
+    <t xml:space="preserve">13.2438173294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1184310913086</t>
   </si>
   <si>
     <t xml:space="preserve">12.9773731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2007160186768</t>
+    <t xml:space="preserve">13.0910043716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2007150650024</t>
   </si>
   <si>
     <t xml:space="preserve">13.1772060394287</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">13.2673273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2830018997192</t>
+    <t xml:space="preserve">13.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887920379639</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">13.4985055923462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4632425308228</t>
+    <t xml:space="preserve">13.4632415771484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4201402664185</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">13.4318943023682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397315979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4514865875244</t>
+    <t xml:space="preserve">13.4397306442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.451488494873</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102596282959</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">13.2712450027466</t>
   </si>
   <si>
-    <t xml:space="preserve">13.232063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0518217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3339357376099</t>
+    <t xml:space="preserve">13.2320623397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0518207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3339385986328</t>
   </si>
   <si>
     <t xml:space="preserve">13.1262683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1732883453369</t>
+    <t xml:space="preserve">13.1732864379883</t>
   </si>
   <si>
     <t xml:space="preserve">13.2477359771729</t>
@@ -3269,52 +3269,52 @@
     <t xml:space="preserve">13.3731212615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3221836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4358139038086</t>
+    <t xml:space="preserve">13.3221826553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4358129501343</t>
   </si>
   <si>
     <t xml:space="preserve">13.1967973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9852104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3261003494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3300199508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2634086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.165452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1145143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7148475646973</t>
+    <t xml:space="preserve">12.9852094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3261013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.330020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2634077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1654500961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1145153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7148485183716</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1576156616211</t>
+    <t xml:space="preserve">13.1223497390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1576166152954</t>
   </si>
   <si>
     <t xml:space="preserve">13.1301860809326</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2046346664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0674934387207</t>
+    <t xml:space="preserve">13.2046356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.067494392395</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891290664673</t>
@@ -3323,31 +3323,31 @@
     <t xml:space="preserve">13.0283117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
+    <t xml:space="preserve">13.2281446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456916809082</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5690355300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6160545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5376882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5416088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3770389556885</t>
+    <t xml:space="preserve">13.569034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6160535812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5376892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5416069030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3770399093628</t>
   </si>
   <si>
     <t xml:space="preserve">13.4436502456665</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">13.4240589141846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3848752975464</t>
+    <t xml:space="preserve">13.384877204895</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5337705612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5964632034302</t>
+    <t xml:space="preserve">13.5337715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5964641571045</t>
   </si>
   <si>
     <t xml:space="preserve">13.6121368408203</t>
@@ -3377,31 +3377,31 @@
     <t xml:space="preserve">13.7414398193359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8393974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9060087203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923765182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8824977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0039653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748285293579</t>
+    <t xml:space="preserve">13.8393964767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9060077667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591558456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8315591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8824987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0039663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748304367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.0901670455933</t>
@@ -3413,103 +3413,103 @@
     <t xml:space="preserve">14.3644485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5956287384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3017568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349775314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4114675521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4271392822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.399712562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6896657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7288484573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8072137832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816623687744</t>
+    <t xml:space="preserve">14.5956268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3017549514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4114665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4271402359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3997135162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6896667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.564281463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7288494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8072166442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816614151001</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622362136841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6739931106567</t>
+    <t xml:space="preserve">14.6739940643311</t>
   </si>
   <si>
     <t xml:space="preserve">14.7249298095703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7851810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494462966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739599227905</t>
+    <t xml:space="preserve">14.7851819992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739608764648</t>
   </si>
   <si>
     <t xml:space="preserve">14.9217472076416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.95387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141277313232</t>
+    <t xml:space="preserve">14.9538774490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141286849976</t>
   </si>
   <si>
     <t xml:space="preserve">15.118558883667</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0663414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1346263885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310237884521</t>
+    <t xml:space="preserve">15.0663423538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1346254348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310247421265</t>
   </si>
   <si>
     <t xml:space="preserve">15.2470903396606</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3234081268311</t>
+    <t xml:space="preserve">15.3234071731567</t>
   </si>
   <si>
     <t xml:space="preserve">15.2591419219971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.347508430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2430753707886</t>
+    <t xml:space="preserve">15.347505569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2430763244629</t>
   </si>
   <si>
     <t xml:space="preserve">15.25110912323</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2792263031006</t>
+    <t xml:space="preserve">15.279224395752</t>
   </si>
   <si>
     <t xml:space="preserve">15.38365650177</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">15.4559545516968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0743780136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418287277222</t>
+    <t xml:space="preserve">15.0743761062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418277740479</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887817382812</t>
@@ -3533,97 +3533,97 @@
     <t xml:space="preserve">14.7811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7570648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168989181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1867036819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.299168586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2429361343384</t>
+    <t xml:space="preserve">14.7570657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168979644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1867027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2991676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2429351806641</t>
   </si>
   <si>
     <t xml:space="preserve">14.564266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4919672012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6124658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498605728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0221614837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8574800491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213291168213</t>
+    <t xml:space="preserve">14.4919681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6124649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498634338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.022162437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8574810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297780990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8614950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213310241699</t>
   </si>
   <si>
     <t xml:space="preserve">14.6767311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7731313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9699449539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9016609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060930252075</t>
+    <t xml:space="preserve">14.7731304168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9699440002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9016618728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060939788818</t>
   </si>
   <si>
     <t xml:space="preserve">14.9659271240234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2671737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333806991577</t>
+    <t xml:space="preserve">15.2671728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788091659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333787918091</t>
   </si>
   <si>
     <t xml:space="preserve">14.9177274703979</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8293619155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337959289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.058310508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422439575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8132972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9257621765137</t>
+    <t xml:space="preserve">14.8293628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337949752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0583114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422430038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8132963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9257612228394</t>
   </si>
   <si>
     <t xml:space="preserve">15.1466751098633</t>
@@ -3632,31 +3632,31 @@
     <t xml:space="preserve">15.0382261276245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1627435684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3754844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4999990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6727142333984</t>
+    <t xml:space="preserve">15.1627416610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3754854202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847658157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6727151870728</t>
   </si>
   <si>
     <t xml:space="preserve">14.9940462112427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7369794845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9819946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9578952789307</t>
+    <t xml:space="preserve">14.7369804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9819936752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.957896232605</t>
   </si>
   <si>
     <t xml:space="preserve">14.7450141906738</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">15.2270078659058</t>
   </si>
   <si>
-    <t xml:space="preserve">14.893630027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5562334060669</t>
+    <t xml:space="preserve">14.8936309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5562343597412</t>
   </si>
   <si>
     <t xml:space="preserve">14.596399307251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0300559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.371467590332</t>
+    <t xml:space="preserve">14.0300550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714685440063</t>
   </si>
   <si>
     <t xml:space="preserve">13.9256229400635</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">13.7770080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379495620728</t>
+    <t xml:space="preserve">13.0379505157471</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447366714478</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">12.9937658309937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243762969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4958448410034</t>
+    <t xml:space="preserve">13.6243753433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4958457946777</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930755615234</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">14.3875350952148</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0824098587036</t>
+    <t xml:space="preserve">15.0824089050293</t>
   </si>
   <si>
     <t xml:space="preserve">15.0502786636353</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1667594909668</t>
+    <t xml:space="preserve">15.1667585372925</t>
   </si>
   <si>
     <t xml:space="preserve">15.3153743743896</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">15.6005544662476</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1789474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8495845794678</t>
+    <t xml:space="preserve">16.1789455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8495826721191</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6850433349609</t>
+    <t xml:space="preserve">16.6850414276123</t>
   </si>
   <si>
     <t xml:space="preserve">16.9581718444824</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">16.3074779510498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.235179901123</t>
+    <t xml:space="preserve">16.2351779937744</t>
   </si>
   <si>
     <t xml:space="preserve">16.0504150390625</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">15.5523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7331027984619</t>
+    <t xml:space="preserve">15.733099937439</t>
   </si>
   <si>
     <t xml:space="preserve">15.6166219711304</t>
@@ -3767,37 +3767,37 @@
     <t xml:space="preserve">15.4117727279663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.476037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9980611801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7932138442993</t>
+    <t xml:space="preserve">15.4760389328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9980602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7932147979736</t>
   </si>
   <si>
     <t xml:space="preserve">14.5080337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5441818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4598331451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5401668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196691513062</t>
+    <t xml:space="preserve">14.5441827774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4598340988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5401649475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196662902832</t>
   </si>
   <si>
     <t xml:space="preserve">14.7048473358154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6204986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4518013000488</t>
+    <t xml:space="preserve">14.6205005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4518003463745</t>
   </si>
   <si>
     <t xml:space="preserve">14.2469539642334</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2670373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947364807129</t>
+    <t xml:space="preserve">14.2268695831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2670364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947374343872</t>
   </si>
   <si>
     <t xml:space="preserve">14.3112192153931</t>
@@ -3821,52 +3821,52 @@
     <t xml:space="preserve">14.4558181762695</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8871431350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7547540664673</t>
+    <t xml:space="preserve">14.8871421813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7547550201416</t>
   </si>
   <si>
     <t xml:space="preserve">14.8230838775635</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8828706741333</t>
+    <t xml:space="preserve">14.8828716278076</t>
   </si>
   <si>
     <t xml:space="preserve">14.5882034301758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5540409088135</t>
+    <t xml:space="preserve">14.5540390014648</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430055618286</t>
+    <t xml:space="preserve">14.4430046081543</t>
   </si>
   <si>
     <t xml:space="preserve">14.3789463043213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2764539718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643564224243</t>
+    <t xml:space="preserve">14.2764530181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643573760986</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2081251144409</t>
+    <t xml:space="preserve">14.2081241607666</t>
   </si>
   <si>
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344398498535</t>
+    <t xml:space="preserve">13.3924493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344388961792</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881788253784</t>
+    <t xml:space="preserve">13.3881797790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">13.1917333602905</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6828479766846</t>
+    <t xml:space="preserve">13.6828470230103</t>
   </si>
   <si>
     <t xml:space="preserve">13.2686033248901</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038290023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2942266464233</t>
+    <t xml:space="preserve">13.0038299560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.294225692749</t>
   </si>
   <si>
     <t xml:space="preserve">13.1661100387573</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">12.5596923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0678873062134</t>
+    <t xml:space="preserve">13.0678882598877</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276750564575</t>
@@ -3929,25 +3929,25 @@
     <t xml:space="preserve">12.9568529129028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.995288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7774906158447</t>
+    <t xml:space="preserve">12.9952878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7774896621704</t>
   </si>
   <si>
     <t xml:space="preserve">12.3547058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4401168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230337142944</t>
+    <t xml:space="preserve">12.4401159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230346679688</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838836669922</t>
+    <t xml:space="preserve">12.1838846206665</t>
   </si>
   <si>
     <t xml:space="preserve">12.1625299453735</t>
@@ -3965,19 +3965,19 @@
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333530426025</t>
+    <t xml:space="preserve">12.3333520889282</t>
   </si>
   <si>
     <t xml:space="preserve">12.4571990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7134323120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.470009803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.534068107605</t>
+    <t xml:space="preserve">12.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4700107574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5340690612793</t>
   </si>
   <si>
     <t xml:space="preserve">12.6408319473267</t>
@@ -4001,40 +4001,40 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.897066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7646780014038</t>
+    <t xml:space="preserve">13.1618385314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8970670700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7646789550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.7006206512451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8757133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.576774597168</t>
+    <t xml:space="preserve">12.8757123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5767736434937</t>
   </si>
   <si>
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579141616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5041761398315</t>
+    <t xml:space="preserve">12.6579151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5041751861572</t>
   </si>
   <si>
     <t xml:space="preserve">12.3931407928467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8330068588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4828224182129</t>
+    <t xml:space="preserve">12.8330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4828214645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.4486570358276</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7689485549927</t>
+    <t xml:space="preserve">12.768949508667</t>
   </si>
   <si>
     <t xml:space="preserve">13.1703815460205</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7048902511597</t>
+    <t xml:space="preserve">12.704891204834</t>
   </si>
   <si>
     <t xml:space="preserve">12.7390546798706</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">12.3248119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4443864822388</t>
+    <t xml:space="preserve">12.4443874359131</t>
   </si>
   <si>
     <t xml:space="preserve">12.1411781311035</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">12.0173320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8251571655273</t>
+    <t xml:space="preserve">11.8251581192017</t>
   </si>
   <si>
     <t xml:space="preserve">11.9746265411377</t>
@@ -4085,34 +4085,34 @@
     <t xml:space="preserve">12.3845996856689</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1326360702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8550519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7397451400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7909927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0045213699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.158260345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2991886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3632478713989</t>
+    <t xml:space="preserve">12.1326370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8550510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.73974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7909936904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0045204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1582593917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2991876602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3632469177246</t>
   </si>
   <si>
     <t xml:space="preserve">12.5169858932495</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091617584229</t>
+    <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
@@ -4151,55 +4151,55 @@
     <t xml:space="preserve">13.8493986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9433517456055</t>
+    <t xml:space="preserve">13.9433507919312</t>
   </si>
   <si>
     <t xml:space="preserve">14.2294778823853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4045705795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6095571517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5839338302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7419443130493</t>
+    <t xml:space="preserve">14.4045696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6095561981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5839328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.515604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741943359375</t>
   </si>
   <si>
     <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5027914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600877761841</t>
+    <t xml:space="preserve">14.5027923583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6266374588013</t>
+    <t xml:space="preserve">14.4686298370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6266393661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7035093307495</t>
+    <t xml:space="preserve">14.7035102844238</t>
   </si>
   <si>
     <t xml:space="preserve">14.6992378234863</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7931909561157</t>
+    <t xml:space="preserve">14.7931900024414</t>
   </si>
   <si>
     <t xml:space="preserve">14.6906967163086</t>
@@ -4208,118 +4208,118 @@
     <t xml:space="preserve">14.7889194488525</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7462129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999538421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8444356918335</t>
+    <t xml:space="preserve">14.7462139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8444366455078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2508296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2892637252808</t>
+    <t xml:space="preserve">14.0928201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2508306503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2892646789551</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3490524291992</t>
+    <t xml:space="preserve">14.3490533828735</t>
   </si>
   <si>
     <t xml:space="preserve">14.3106174468994</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2593717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3618650436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1910419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3277006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917589187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504854202271</t>
+    <t xml:space="preserve">14.259370803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3618659973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1910429000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3276996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504844665527</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6736154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615198135376</t>
+    <t xml:space="preserve">14.6736164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017330169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615188598633</t>
   </si>
   <si>
     <t xml:space="preserve">14.8487071990967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9554719924927</t>
+    <t xml:space="preserve">14.9554710388184</t>
   </si>
   <si>
     <t xml:space="preserve">14.968282699585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8358964920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.168999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2373285293579</t>
+    <t xml:space="preserve">14.8358974456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1689987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2373275756836</t>
   </si>
   <si>
     <t xml:space="preserve">15.3013868331909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2586793899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270101547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3825263977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2885732650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319948196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4679384231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4636659622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063734054565</t>
+    <t xml:space="preserve">15.2586803436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3825273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.28857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5021018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4679365158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4636669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063714981079</t>
   </si>
   <si>
     <t xml:space="preserve">15.5618896484375</t>
@@ -4331,37 +4331,37 @@
     <t xml:space="preserve">15.6003246307373</t>
   </si>
   <si>
-    <t xml:space="preserve">15.587513923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344900131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6857357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850206375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106420516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9804029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223934173584</t>
+    <t xml:space="preserve">15.5875120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473016738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857347488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106439590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664381980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9804019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223924636841</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4373,52 +4373,52 @@
     <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0658149719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9078044891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7327117919922</t>
+    <t xml:space="preserve">16.0658130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9078035354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7327108383179</t>
   </si>
   <si>
     <t xml:space="preserve">15.2031631469727</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7540645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8316249847412</t>
+    <t xml:space="preserve">15.7540636062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8316259384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1092128753662</t>
+    <t xml:space="preserve">15.0451526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4508562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081506729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1092119216919</t>
   </si>
   <si>
     <t xml:space="preserve">15.2501392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4423131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6259479522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6985464096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.672924041748</t>
+    <t xml:space="preserve">15.4423141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6259469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6985473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6729230880737</t>
   </si>
   <si>
     <t xml:space="preserve">15.6216793060303</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">16.091438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1683082580566</t>
+    <t xml:space="preserve">16.1683101654053</t>
   </si>
   <si>
     <t xml:space="preserve">16.0401916503906</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">16.2836132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3049640655518</t>
+    <t xml:space="preserve">16.3049659729004</t>
   </si>
   <si>
     <t xml:space="preserve">16.3092365264893</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">16.232364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.125602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8693695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9334278106689</t>
+    <t xml:space="preserve">16.1256008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8693685531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9334297180176</t>
   </si>
   <si>
     <t xml:space="preserve">15.8053112030029</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8907203674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889421463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1127891540527</t>
+    <t xml:space="preserve">15.890721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1127910614014</t>
   </si>
   <si>
     <t xml:space="preserve">16.0316524505615</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">16.4688701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596569061279</t>
+    <t xml:space="preserve">16.2596549987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.332426071167</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">16.4188404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5188999176025</t>
+    <t xml:space="preserve">16.5189018249512</t>
   </si>
   <si>
     <t xml:space="preserve">16.6462478637695</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">16.9236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1010646820068</t>
+    <t xml:space="preserve">17.1010627746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2193164825439</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">16.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7963390350342</t>
+    <t xml:space="preserve">16.7963371276855</t>
   </si>
   <si>
     <t xml:space="preserve">16.6689910888672</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.6280574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235660552979</t>
+    <t xml:space="preserve">16.7235679626465</t>
   </si>
   <si>
     <t xml:space="preserve">16.6917304992676</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">16.9373321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4330787658691</t>
+    <t xml:space="preserve">17.5103969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4330806732178</t>
   </si>
   <si>
     <t xml:space="preserve">17.2056732177734</t>
@@ -4604,10 +4604,10 @@
     <t xml:space="preserve">17.1783828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920261383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0692272186279</t>
+    <t xml:space="preserve">17.1920280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">17.2829914093018</t>
@@ -4616,13 +4616,13 @@
     <t xml:space="preserve">17.3648567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3739547729492</t>
+    <t xml:space="preserve">17.3739528656006</t>
   </si>
   <si>
     <t xml:space="preserve">17.3330192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3284702301025</t>
+    <t xml:space="preserve">17.3284721374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.5149459838867</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">17.5240421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6286487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4057922363281</t>
+    <t xml:space="preserve">17.6286506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4057903289795</t>
   </si>
   <si>
     <t xml:space="preserve">17.037389755249</t>
@@ -4649,16 +4649,16 @@
     <t xml:space="preserve">17.091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7190170288086</t>
+    <t xml:space="preserve">16.9737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7190189361572</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8736553192139</t>
+    <t xml:space="preserve">16.8736572265625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7417602539062</t>
@@ -4667,13 +4667,13 @@
     <t xml:space="preserve">16.7645015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281764984131</t>
+    <t xml:space="preserve">16.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">16.8418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9282341003418</t>
+    <t xml:space="preserve">16.9282360076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.0737762451172</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">17.442174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4012432098389</t>
+    <t xml:space="preserve">17.4012413024902</t>
   </si>
   <si>
     <t xml:space="preserve">17.292085647583</t>
@@ -4691,13 +4691,13 @@
     <t xml:space="preserve">17.3011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6013603210449</t>
+    <t xml:space="preserve">17.6013622283936</t>
   </si>
   <si>
     <t xml:space="preserve">17.7150650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7332572937012</t>
+    <t xml:space="preserve">17.7332592010498</t>
   </si>
   <si>
     <t xml:space="preserve">18.0197906494141</t>
@@ -4712,7 +4712,7 @@
     <t xml:space="preserve">18.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1926212310791</t>
+    <t xml:space="preserve">18.1926231384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.0470809936523</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">17.7878360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059093475342</t>
+    <t xml:space="preserve">17.6059074401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6832294464111</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">16.8918476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3239231109619</t>
+    <t xml:space="preserve">17.3239250183105</t>
   </si>
   <si>
     <t xml:space="preserve">17.4876575469971</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">17.0510349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2966327667236</t>
+    <t xml:space="preserve">17.2966346740723</t>
   </si>
   <si>
     <t xml:space="preserve">17.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1465454101562</t>
+    <t xml:space="preserve">17.1238040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1465473175049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2511539459229</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">17.8787994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8151245117188</t>
+    <t xml:space="preserve">17.8151226043701</t>
   </si>
   <si>
     <t xml:space="preserve">17.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4922046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.314826965332</t>
+    <t xml:space="preserve">17.4922065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3148288726807</t>
   </si>
   <si>
     <t xml:space="preserve">17.187479019165</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">17.242057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1419982910156</t>
+    <t xml:space="preserve">17.141996383667</t>
   </si>
   <si>
     <t xml:space="preserve">17.2284126281738</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">17.4103393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.414888381958</t>
+    <t xml:space="preserve">17.4148864746094</t>
   </si>
   <si>
     <t xml:space="preserve">17.496753692627</t>
@@ -4895,13 +4895,13 @@
     <t xml:space="preserve">17.9561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0061454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.901538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9515705108643</t>
+    <t xml:space="preserve">18.0061473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9015407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9515686035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.9379234313965</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">18.6201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5473785400391</t>
+    <t xml:space="preserve">18.5473766326904</t>
   </si>
   <si>
     <t xml:space="preserve">18.5655708312988</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">18.6656303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6929187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8202686309814</t>
+    <t xml:space="preserve">18.6929168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8202667236328</t>
   </si>
   <si>
     <t xml:space="preserve">18.629243850708</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">18.7565937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6838245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5564746856689</t>
+    <t xml:space="preserve">18.6838226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5564727783203</t>
   </si>
   <si>
     <t xml:space="preserve">18.8384590148926</t>
@@ -4985,25 +4985,25 @@
     <t xml:space="preserve">19.5024909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.139232635498</t>
+    <t xml:space="preserve">20.1392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9118232727051</t>
+    <t xml:space="preserve">19.9118251800537</t>
   </si>
   <si>
     <t xml:space="preserve">19.9664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0027885437012</t>
+    <t xml:space="preserve">20.0027866363525</t>
   </si>
   <si>
     <t xml:space="preserve">20.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1574230194092</t>
+    <t xml:space="preserve">20.1574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">20.0755577087402</t>
@@ -5012,16 +5012,16 @@
     <t xml:space="preserve">20.2120018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2847728729248</t>
+    <t xml:space="preserve">20.2847709655762</t>
   </si>
   <si>
     <t xml:space="preserve">20.393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5940456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6122398376465</t>
+    <t xml:space="preserve">20.5940475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6122417449951</t>
   </si>
   <si>
     <t xml:space="preserve">20.6759147644043</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">21.1034412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3399429321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127178192139</t>
+    <t xml:space="preserve">21.3399448394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127159118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.5309677124023</t>
@@ -5060,10 +5060,10 @@
     <t xml:space="preserve">20.8669376373291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0306701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7304916381836</t>
+    <t xml:space="preserve">21.0306720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7304935455322</t>
   </si>
   <si>
     <t xml:space="preserve">20.7577800750732</t>
@@ -5072,13 +5072,13 @@
     <t xml:space="preserve">20.6031436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7032051086426</t>
+    <t xml:space="preserve">20.7032032012939</t>
   </si>
   <si>
     <t xml:space="preserve">20.3393516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4394111633301</t>
+    <t xml:space="preserve">20.4394092559814</t>
   </si>
   <si>
     <t xml:space="preserve">20.4939880371094</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">20.6213359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7123012542725</t>
+    <t xml:space="preserve">20.7122993469238</t>
   </si>
   <si>
     <t xml:space="preserve">21.003381729126</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">21.2307891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7765674591064</t>
+    <t xml:space="preserve">21.7765693664551</t>
   </si>
   <si>
     <t xml:space="preserve">21.7401809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9039154052734</t>
+    <t xml:space="preserve">21.9039173126221</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949977874756</t>
@@ -6066,6 +6066,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.8699989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -71482,7 +71485,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6938078704</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>2178201</v>
@@ -71503,6 +71506,32 @@
         <v>2017</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6909722222</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>1964366</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>33.2299995422363</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>32.7099990844727</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>32.8899993896484</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>33.2000007629395</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="2023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="2024">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21390056610107</t>
+    <t xml:space="preserve">9.21390151977539</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31058979034424</t>
+    <t xml:space="preserve">9.31059169769287</t>
   </si>
   <si>
     <t xml:space="preserve">9.13427352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11721229553223</t>
+    <t xml:space="preserve">9.11721038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.02052116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76457977294922</t>
+    <t xml:space="preserve">8.76458072662354</t>
   </si>
   <si>
     <t xml:space="preserve">8.88970851898193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06602382659912</t>
+    <t xml:space="preserve">9.06602191925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.95795822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75889205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29251098632812</t>
+    <t xml:space="preserve">8.75889301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120227813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29250907897949</t>
   </si>
   <si>
     <t xml:space="preserve">8.44607448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48588752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30957221984863</t>
+    <t xml:space="preserve">8.48588848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30957317352295</t>
   </si>
   <si>
     <t xml:space="preserve">8.04794311523438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93987941741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568784713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4166202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23461818695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15499114990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74548530578613</t>
+    <t xml:space="preserve">7.93988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668840408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41661977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23461866378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15499210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161222457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74548435211182</t>
   </si>
   <si>
     <t xml:space="preserve">6.47248125076294</t>
@@ -128,73 +128,73 @@
     <t xml:space="preserve">6.23360204696655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34166574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59760761260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62035751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392244338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72842121124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66017150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89905071258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89336156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95592594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305675506592</t>
+    <t xml:space="preserve">6.34166526794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59760713577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62035799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72842216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66017055511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89905023574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89336347579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95592498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2630558013916</t>
   </si>
   <si>
     <t xml:space="preserve">7.28580713272095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34268188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4507474899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680673599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24599266052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3199315071106</t>
+    <t xml:space="preserve">7.34268140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643377304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45074605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2459921836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31993103027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.38249492645264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3711199760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575361251831</t>
+    <t xml:space="preserve">7.37112045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575265884399</t>
   </si>
   <si>
     <t xml:space="preserve">7.83750152587891</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79200172424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731552124023</t>
+    <t xml:space="preserve">7.79200077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731647491455</t>
   </si>
   <si>
     <t xml:space="preserve">7.89437961578369</t>
@@ -209,310 +209,310 @@
     <t xml:space="preserve">7.57587337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53037309646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543226242065</t>
+    <t xml:space="preserve">7.53037357330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543130874634</t>
   </si>
   <si>
     <t xml:space="preserve">7.42799663543701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48487091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41093158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755456924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98436307907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00711441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85354852676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05261421203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1379280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067886352539</t>
+    <t xml:space="preserve">7.48487186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41093254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30286979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98436403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00711345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85354995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05261516571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13792943954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067934036255</t>
   </si>
   <si>
     <t xml:space="preserve">7.43368339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49624729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47918367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862422943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75218915939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7863130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456562042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80337572097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77493810653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018423080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387035369873</t>
+    <t xml:space="preserve">7.4962477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4791841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218820571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181715011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631353378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456705093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80337858200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77493953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387083053589</t>
   </si>
   <si>
     <t xml:space="preserve">7.35405778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53605985641479</t>
+    <t xml:space="preserve">7.53605842590332</t>
   </si>
   <si>
     <t xml:space="preserve">7.08105230331421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1663670539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05830192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25168037414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798982620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8484525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94490051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85447931289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228542327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76405954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54705333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53499603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625534057617</t>
+    <t xml:space="preserve">7.16636800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05830144882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25168085098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84845209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90873432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94490003585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85447978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76406002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54705381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53499698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158533096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625486373901</t>
   </si>
   <si>
     <t xml:space="preserve">7.77008867263794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42046594619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17934417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97439289093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850416183472</t>
+    <t xml:space="preserve">7.42046403884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17934465408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439336776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850511550903</t>
   </si>
   <si>
     <t xml:space="preserve">6.92014026641846</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19140005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40840911865234</t>
+    <t xml:space="preserve">7.19140148162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40840816497803</t>
   </si>
   <si>
     <t xml:space="preserve">7.54102373123169</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58322048187256</t>
+    <t xml:space="preserve">7.58322143554688</t>
   </si>
   <si>
     <t xml:space="preserve">6.58257246017456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02498245239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11841773986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26308870315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953664779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25103235244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1304726600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91647863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92853498458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967800140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790102005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76341390609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69710445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87191677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560874938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177732467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8478045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77546834945679</t>
+    <t xml:space="preserve">6.02498340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11841821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26308917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4318733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25103330612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13047361373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91647958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92853546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967704772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7634129524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69710540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87191581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8417763710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84780406951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77546882629395</t>
   </si>
   <si>
     <t xml:space="preserve">6.73327302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68504953384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81163549423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62476921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10098075866699</t>
+    <t xml:space="preserve">6.68504858016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81163740158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476825714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10097980499268</t>
   </si>
   <si>
     <t xml:space="preserve">7.07084083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7935528755188</t>
+    <t xml:space="preserve">6.79355335235596</t>
   </si>
   <si>
     <t xml:space="preserve">7.06481170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2094841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990530014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000129699707</t>
+    <t xml:space="preserve">7.20948457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000034332275</t>
   </si>
   <si>
     <t xml:space="preserve">6.90808439254761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7393012046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04069948196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01658773422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81766605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74532794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149747848511</t>
+    <t xml:space="preserve">6.73930072784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04070091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01658916473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74532842636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149700164795</t>
   </si>
   <si>
     <t xml:space="preserve">6.94425296783447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99247789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93822479248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88397359848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042106628418</t>
+    <t xml:space="preserve">6.99247646331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93822431564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88397216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98042058944702</t>
   </si>
   <si>
     <t xml:space="preserve">7.15523195266724</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">7.25770854949951</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70313215255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72724485397339</t>
+    <t xml:space="preserve">6.70313358306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72724533081055</t>
   </si>
   <si>
     <t xml:space="preserve">6.7995810508728</t>
@@ -536,46 +536,46 @@
     <t xml:space="preserve">6.75135660171509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59462833404541</t>
+    <t xml:space="preserve">6.59462881088257</t>
   </si>
   <si>
     <t xml:space="preserve">6.56448936462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57654523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54640483856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51626539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49818086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76944017410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383272171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18537282943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16728925704956</t>
+    <t xml:space="preserve">6.57654476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60668468475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54640436172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51626491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49818134307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76944065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18537187576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16728973388672</t>
   </si>
   <si>
     <t xml:space="preserve">7.19742822647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2878475189209</t>
+    <t xml:space="preserve">7.28784799575806</t>
   </si>
   <si>
     <t xml:space="preserve">7.26976442337036</t>
@@ -584,64 +584,64 @@
     <t xml:space="preserve">7.33004426956177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31196069717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1431770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09495162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98644828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574962615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08892583847046</t>
+    <t xml:space="preserve">7.31195974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0949535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98644876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08892440795898</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686758041382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8779444694519</t>
+    <t xml:space="preserve">6.87794399261475</t>
   </si>
   <si>
     <t xml:space="preserve">7.02261734008789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82369184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854904174805</t>
+    <t xml:space="preserve">6.8236927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854808807373</t>
   </si>
   <si>
     <t xml:space="preserve">7.35415697097778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73392105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6803150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45125198364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47536373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41508388519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33069133758545</t>
+    <t xml:space="preserve">7.73392057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68031692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45125293731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47536468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41508483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33069324493408</t>
   </si>
   <si>
     <t xml:space="preserve">8.54167175292969</t>
@@ -665,43 +665,43 @@
     <t xml:space="preserve">8.6682596206665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55372714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5055046081543</t>
+    <t xml:space="preserve">8.5537281036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50550365447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.5115327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65017509460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71045684814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75265312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69840145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71648502349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52358722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48741817474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38494396209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25835609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23424530029297</t>
+    <t xml:space="preserve">8.65017604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71045589447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75265216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69839954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71648406982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52358913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48742008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38494300842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25835418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23424339294434</t>
   </si>
   <si>
     <t xml:space="preserve">8.16793632507324</t>
@@ -731,28 +731,28 @@
     <t xml:space="preserve">8.98774433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88526821136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84909915924072</t>
+    <t xml:space="preserve">8.88526725769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84910011291504</t>
   </si>
   <si>
     <t xml:space="preserve">9.00582790374756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02993965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81895923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77073574066162</t>
+    <t xml:space="preserve">9.02993869781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81896114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77073669433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.67428874969482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74059391021729</t>
+    <t xml:space="preserve">8.74059581756592</t>
   </si>
   <si>
     <t xml:space="preserve">8.90335178375244</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">9.04802417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87924003601074</t>
+    <t xml:space="preserve">8.87924098968506</t>
   </si>
   <si>
     <t xml:space="preserve">8.90937995910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95760345458984</t>
+    <t xml:space="preserve">8.95760250091553</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101654052734</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">8.81293201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74662303924561</t>
+    <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.6562032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49947738647461</t>
+    <t xml:space="preserve">8.49947547912598</t>
   </si>
   <si>
     <t xml:space="preserve">8.14985275268555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27643966674805</t>
+    <t xml:space="preserve">8.27644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.54770088195801</t>
@@ -797,43 +797,43 @@
     <t xml:space="preserve">8.46330833435059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5657844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78882026672363</t>
+    <t xml:space="preserve">8.56578350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78881931304932</t>
   </si>
   <si>
     <t xml:space="preserve">8.80087566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79484939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.782790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86718368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98171615600586</t>
+    <t xml:space="preserve">8.79484844207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78279113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86718463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98171424865723</t>
   </si>
   <si>
     <t xml:space="preserve">8.80690383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63209056854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6079797744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46933555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36083221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93349170684814</t>
+    <t xml:space="preserve">8.6320915222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60798072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46933650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36083126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93349075317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.7586784362793</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">9.04199504852295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1926965713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078014373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2409200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21680736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94554710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89129543304443</t>
+    <t xml:space="preserve">9.19269561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21077919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24091911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2168083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94554805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89129638671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.03596878051758</t>
@@ -869,49 +869,49 @@
     <t xml:space="preserve">9.07213497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12035846710205</t>
+    <t xml:space="preserve">9.12035942077637</t>
   </si>
   <si>
     <t xml:space="preserve">9.30493068695068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33675289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.184006690979</t>
+    <t xml:space="preserve">9.33675384521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18400478363037</t>
   </si>
   <si>
     <t xml:space="preserve">9.15854740142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13308811187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851684570312</t>
+    <t xml:space="preserve">9.13309001922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851779937744</t>
   </si>
   <si>
     <t xml:space="preserve">8.83395671844482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94215488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03762054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81486415863037</t>
+    <t xml:space="preserve">8.94215393066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03761959075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81486320495605</t>
   </si>
   <si>
     <t xml:space="preserve">8.75758266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73848819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89123630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95488262176514</t>
+    <t xml:space="preserve">8.73848915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89123725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95488166809082</t>
   </si>
   <si>
     <t xml:space="preserve">9.05035018920898</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">9.22855663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23492050170898</t>
+    <t xml:space="preserve">9.2349214553833</t>
   </si>
   <si>
     <t xml:space="preserve">9.1712760925293</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">9.28583812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2985668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3494815826416</t>
+    <t xml:space="preserve">9.29856586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34948348999023</t>
   </si>
   <si>
     <t xml:space="preserve">9.25401401519775</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">9.29220199584961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33038902282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38130569458008</t>
+    <t xml:space="preserve">9.33038806915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38130474090576</t>
   </si>
   <si>
     <t xml:space="preserve">9.57860565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54678344726562</t>
+    <t xml:space="preserve">9.54678249359131</t>
   </si>
   <si>
     <t xml:space="preserve">9.54041862487793</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">9.79499912261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85864448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862411499023</t>
+    <t xml:space="preserve">9.85864353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862697601318</t>
   </si>
   <si>
     <t xml:space="preserve">9.68680191040039</t>
@@ -986,34 +986,34 @@
     <t xml:space="preserve">9.56587696075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52769088745117</t>
+    <t xml:space="preserve">9.52768898010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.75681209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77590560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0877676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1386842727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2341508865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1959638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062310218811</t>
+    <t xml:space="preserve">9.77590656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0877666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1386833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1959648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0623092651367</t>
   </si>
   <si>
     <t xml:space="preserve">10.0050287246704</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">9.86500930786133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90319633483887</t>
+    <t xml:space="preserve">9.90319728851318</t>
   </si>
   <si>
     <t xml:space="preserve">9.82045745849609</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">9.87137413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78226947784424</t>
+    <t xml:space="preserve">9.78226852416992</t>
   </si>
   <si>
     <t xml:space="preserve">9.71226024627686</t>
@@ -1046,64 +1046,64 @@
     <t xml:space="preserve">9.6804370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69316577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134357452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53405380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52132511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57224082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61679172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.674072265625</t>
+    <t xml:space="preserve">9.69316673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53405284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52132415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57224178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61679363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67407321929932</t>
   </si>
   <si>
     <t xml:space="preserve">9.62952041625977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59769916534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89046764373779</t>
+    <t xml:space="preserve">9.59769821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89046669006348</t>
   </si>
   <si>
     <t xml:space="preserve">9.9477481842041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75044631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89683246612549</t>
+    <t xml:space="preserve">9.75044822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">9.91592502593994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87773704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686731338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1323184967041</t>
+    <t xml:space="preserve">9.87773895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0304861068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1323194503784</t>
   </si>
   <si>
     <t xml:space="preserve">9.93501853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84591484069824</t>
+    <t xml:space="preserve">9.84591579437256</t>
   </si>
   <si>
     <t xml:space="preserve">9.85227966308594</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">9.83318614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72498893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99866390228271</t>
+    <t xml:space="preserve">9.72499084472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9986629486084</t>
   </si>
   <si>
     <t xml:space="preserve">9.96047687530518</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0177574157715</t>
+    <t xml:space="preserve">10.0177564620972</t>
   </si>
   <si>
     <t xml:space="preserve">9.95411396026611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.125955581665</t>
+    <t xml:space="preserve">10.1259536743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0241212844849</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">9.94138336181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8841028213501</t>
+    <t xml:space="preserve">9.88410186767578</t>
   </si>
   <si>
     <t xml:space="preserve">10.0368509292603</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">9.78863430023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5849723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61042785644531</t>
+    <t xml:space="preserve">9.63588523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58497047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61042881011963</t>
   </si>
   <si>
     <t xml:space="preserve">9.66770935058594</t>
@@ -1163,31 +1163,31 @@
     <t xml:space="preserve">9.73135375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80772876739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737717628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70589637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55951118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47677326202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97957038879395</t>
+    <t xml:space="preserve">9.8077278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73771858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70589447021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5595121383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47677230834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97320461273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97957134246826</t>
   </si>
   <si>
     <t xml:space="preserve">10.0814027786255</t>
   </si>
   <si>
-    <t xml:space="preserve">10.055944442749</t>
+    <t xml:space="preserve">10.0559453964233</t>
   </si>
   <si>
     <t xml:space="preserve">10.291431427002</t>
@@ -1199,22 +1199,22 @@
     <t xml:space="preserve">10.2023286819458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3105249404907</t>
+    <t xml:space="preserve">10.310525894165</t>
   </si>
   <si>
     <t xml:space="preserve">10.3232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641407012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1482315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9922981262207</t>
+    <t xml:space="preserve">10.1736869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641416549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.148229598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99229907989502</t>
   </si>
   <si>
     <t xml:space="preserve">9.76954174041748</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">9.86819076538086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81727600097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77908802032471</t>
+    <t xml:space="preserve">9.81727504730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77908897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.8140926361084</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">9.65179634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85546112060547</t>
+    <t xml:space="preserve">9.85546207427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.74726486206055</t>
@@ -1253,52 +1253,52 @@
     <t xml:space="preserve">9.98593425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92865467071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94456577301025</t>
+    <t xml:space="preserve">9.92865562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94456481933594</t>
   </si>
   <si>
     <t xml:space="preserve">9.97002410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.049578666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1609592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3137073516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2946147918701</t>
+    <t xml:space="preserve">10.0495796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1609601974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3137083053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2946138381958</t>
   </si>
   <si>
     <t xml:space="preserve">10.3455305099487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346342086792</t>
+    <t xml:space="preserve">10.4346323013306</t>
   </si>
   <si>
     <t xml:space="preserve">10.530101776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6382989883423</t>
+    <t xml:space="preserve">10.6382970809937</t>
   </si>
   <si>
     <t xml:space="preserve">10.765588760376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8546924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6319351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5841989517212</t>
+    <t xml:space="preserve">10.8546915054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6319341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178544998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5841999053955</t>
   </si>
   <si>
     <t xml:space="preserve">10.6542100906372</t>
@@ -1310,22 +1310,22 @@
     <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796674728394</t>
+    <t xml:space="preserve">10.6796684265137</t>
   </si>
   <si>
     <t xml:space="preserve">10.5269203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5396490097046</t>
+    <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
     <t xml:space="preserve">10.4409980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5014610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078248977661</t>
+    <t xml:space="preserve">10.5014619827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078258514404</t>
   </si>
   <si>
     <t xml:space="preserve">10.297797203064</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">10.2596092224121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2864847183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2528896331787</t>
+    <t xml:space="preserve">10.2864856719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.252890586853</t>
   </si>
   <si>
     <t xml:space="preserve">10.1319522857666</t>
@@ -1349,22 +1349,22 @@
     <t xml:space="preserve">10.0143728256226</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99421787261963</t>
+    <t xml:space="preserve">9.99421691894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.83968448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49702644348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5541353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77585506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88335800170898</t>
+    <t xml:space="preserve">9.49702453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55413627624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77585601806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88335609436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.86991882324219</t>
@@ -1373,52 +1373,52 @@
     <t xml:space="preserve">9.65491676330566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67843151092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52054214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79937076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75233936309814</t>
+    <t xml:space="preserve">9.67843246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52054023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79937267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75234031677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.78257465362549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90015411376953</t>
+    <t xml:space="preserve">9.90015316009521</t>
   </si>
   <si>
     <t xml:space="preserve">9.80609035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76241779327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82960510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69858932495117</t>
+    <t xml:space="preserve">9.76241874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82960605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6985912322998</t>
   </si>
   <si>
     <t xml:space="preserve">9.76913642883301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60116577148438</t>
+    <t xml:space="preserve">9.60116672515869</t>
   </si>
   <si>
     <t xml:space="preserve">9.61796379089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52390003204346</t>
+    <t xml:space="preserve">9.52390098571777</t>
   </si>
   <si>
     <t xml:space="preserve">9.51718235015869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61124515533447</t>
+    <t xml:space="preserve">9.61124610900879</t>
   </si>
   <si>
     <t xml:space="preserve">9.59108924865723</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65155696868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163539886475</t>
+    <t xml:space="preserve">9.6515588760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163730621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84976196289062</t>
+    <t xml:space="preserve">9.84976291656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.85648155212402</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">9.81616878509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74898052215576</t>
+    <t xml:space="preserve">9.74897956848145</t>
   </si>
   <si>
     <t xml:space="preserve">9.89007568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90351295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92366886138916</t>
+    <t xml:space="preserve">9.9035120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92366981506348</t>
   </si>
   <si>
     <t xml:space="preserve">9.97070217132568</t>
@@ -1478,121 +1478,121 @@
     <t xml:space="preserve">9.95390319824219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0378885269165</t>
+    <t xml:space="preserve">10.0378875732422</t>
   </si>
   <si>
     <t xml:space="preserve">10.0009365081787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0681238174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916395187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748414993286</t>
+    <t xml:space="preserve">10.0681228637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748424530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.8665599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71202659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312271118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92702770233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98077964782715</t>
+    <t xml:space="preserve">9.71202754974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73218154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312175750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92702865600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98077869415283</t>
   </si>
   <si>
     <t xml:space="preserve">9.92031002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6381196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76577663421631</t>
+    <t xml:space="preserve">9.63812160491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76577758789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.93710708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9606237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94382667541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1621866226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1017169952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0882806777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554670333862</t>
+    <t xml:space="preserve">9.96062278747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94382572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1621875762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1017179489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0882797241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1554679870605</t>
   </si>
   <si>
     <t xml:space="preserve">10.1722650527954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1823425292969</t>
+    <t xml:space="preserve">10.1823434829712</t>
   </si>
   <si>
     <t xml:space="preserve">10.2965631484985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4141435623169</t>
+    <t xml:space="preserve">10.4141426086426</t>
   </si>
   <si>
     <t xml:space="preserve">10.4309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3704690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99757766723633</t>
+    <t xml:space="preserve">10.3704700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9975757598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.88671588897705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96734237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93038845062256</t>
+    <t xml:space="preserve">9.96734142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93038654327393</t>
   </si>
   <si>
     <t xml:space="preserve">9.70866775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69186973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59444808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50038623809814</t>
+    <t xml:space="preserve">9.69187068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59444713592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50038528442383</t>
   </si>
   <si>
     <t xml:space="preserve">9.61460494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56421279907227</t>
+    <t xml:space="preserve">9.56421375274658</t>
   </si>
   <si>
     <t xml:space="preserve">9.41304111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43991756439209</t>
+    <t xml:space="preserve">9.43991661071777</t>
   </si>
   <si>
     <t xml:space="preserve">9.40968132019043</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">9.288743019104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2383508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43655681610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3324146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53397750854492</t>
+    <t xml:space="preserve">9.23835182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43655586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33241558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53397846221924</t>
   </si>
   <si>
     <t xml:space="preserve">9.66499614715576</t>
@@ -1628,37 +1628,37 @@
     <t xml:space="preserve">9.63476085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57429218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71538639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51382350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59780788421631</t>
+    <t xml:space="preserve">9.57429122924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71538734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51382255554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59780693054199</t>
   </si>
   <si>
     <t xml:space="preserve">9.5574951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57765197753906</t>
+    <t xml:space="preserve">9.57765102386475</t>
   </si>
   <si>
     <t xml:space="preserve">9.8195276260376</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87663841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9135913848877</t>
+    <t xml:space="preserve">9.87663745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91359043121338</t>
   </si>
   <si>
     <t xml:space="preserve">10.0042963027954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0849208831787</t>
+    <t xml:space="preserve">10.084921836853</t>
   </si>
   <si>
     <t xml:space="preserve">9.97406101226807</t>
@@ -1670,43 +1670,43 @@
     <t xml:space="preserve">9.6448392868042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68515014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89679431915283</t>
+    <t xml:space="preserve">9.68515300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562072753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89679527282715</t>
   </si>
   <si>
     <t xml:space="preserve">9.85984134674072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95054531097412</t>
+    <t xml:space="preserve">9.95054626464844</t>
   </si>
   <si>
     <t xml:space="preserve">10.021092414856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0446081161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647640228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3267974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3435945510864</t>
+    <t xml:space="preserve">10.0446071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647630691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327346801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3267965316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3435955047607</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898435592651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3335161209106</t>
+    <t xml:space="preserve">10.333517074585</t>
   </si>
   <si>
     <t xml:space="preserve">10.3133602142334</t>
@@ -1715,22 +1715,22 @@
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771867752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2764072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1991405487061</t>
+    <t xml:space="preserve">10.3771877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.276406288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1991395950317</t>
   </si>
   <si>
     <t xml:space="preserve">10.2461719512939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2932024002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714836120605</t>
+    <t xml:space="preserve">10.2932033538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
     <t xml:space="preserve">10.1285934448242</t>
@@ -1739,16 +1739,16 @@
     <t xml:space="preserve">10.2058591842651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2831249237061</t>
+    <t xml:space="preserve">10.2831268310547</t>
   </si>
   <si>
     <t xml:space="preserve">10.189061164856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2293739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260141372681</t>
+    <t xml:space="preserve">10.2293748855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260150909424</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730474472046</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4275798797607</t>
+    <t xml:space="preserve">10.4275789260864</t>
   </si>
   <si>
     <t xml:space="preserve">10.4342985153198</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">10.6089859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.672815322876</t>
+    <t xml:space="preserve">10.6728162765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7400045394897</t>
+    <t xml:space="preserve">10.7400035858154</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123466491699</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">10.5653162002563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6157054901123</t>
+    <t xml:space="preserve">10.6157064437866</t>
   </si>
   <si>
     <t xml:space="preserve">10.5921907424927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.62242603302</t>
+    <t xml:space="preserve">10.6224241256714</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534408569336</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725841522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0591449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0322704315186</t>
+    <t xml:space="preserve">11.0725831985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0591468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0322713851929</t>
   </si>
   <si>
     <t xml:space="preserve">11.0692253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.985239982605</t>
+    <t xml:space="preserve">10.9852409362793</t>
   </si>
   <si>
     <t xml:space="preserve">10.9718017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0087556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0860214233398</t>
+    <t xml:space="preserve">11.0087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0860223770142</t>
   </si>
   <si>
     <t xml:space="preserve">11.2035999298096</t>
@@ -1829,64 +1829,64 @@
     <t xml:space="preserve">11.1767263412476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2304763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2237577438354</t>
+    <t xml:space="preserve">11.2304754257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2237567901611</t>
   </si>
   <si>
     <t xml:space="preserve">11.1733655929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2271156311035</t>
+    <t xml:space="preserve">11.2170381546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2271165847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.297664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.35813331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4219608306885</t>
+    <t xml:space="preserve">11.3581342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4219617843628</t>
   </si>
   <si>
     <t xml:space="preserve">11.556339263916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521951675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4286804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4622735977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.583212852478</t>
+    <t xml:space="preserve">11.4521970748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4286813735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4622745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5832138061523</t>
   </si>
   <si>
     <t xml:space="preserve">11.552978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6235256195068</t>
+    <t xml:space="preserve">11.6235246658325</t>
   </si>
   <si>
     <t xml:space="preserve">11.6201667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6302442550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5261030197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824304580688</t>
+    <t xml:space="preserve">11.6302461624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.526104927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824314117432</t>
   </si>
   <si>
     <t xml:space="preserve">11.4689931869507</t>
@@ -1898,19 +1898,19 @@
     <t xml:space="preserve">11.3648519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4152431488037</t>
+    <t xml:space="preserve">11.4152421951294</t>
   </si>
   <si>
     <t xml:space="preserve">11.5093050003052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4253206253052</t>
+    <t xml:space="preserve">11.4253215789795</t>
   </si>
   <si>
     <t xml:space="preserve">11.5636587142944</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5849418640137</t>
+    <t xml:space="preserve">11.584942817688</t>
   </si>
   <si>
     <t xml:space="preserve">11.560112953186</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">11.3189077377319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5459222793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.414680480957</t>
+    <t xml:space="preserve">11.5459232330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4146795272827</t>
   </si>
   <si>
     <t xml:space="preserve">11.3330955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124929428101</t>
+    <t xml:space="preserve">11.2124938964844</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1486444473267</t>
+    <t xml:space="preserve">11.148645401001</t>
   </si>
   <si>
     <t xml:space="preserve">11.1238145828247</t>
@@ -1946,25 +1946,25 @@
     <t xml:space="preserve">11.1805686950684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2195863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2479648590088</t>
+    <t xml:space="preserve">11.2195873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2479639053345</t>
   </si>
   <si>
     <t xml:space="preserve">11.3366422653198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4536991119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4288682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4785280227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4466037750244</t>
+    <t xml:space="preserve">11.4536981582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4288702011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4785289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4466047286987</t>
   </si>
   <si>
     <t xml:space="preserve">11.5175476074219</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">11.7445631027222</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8119583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8332433700562</t>
+    <t xml:space="preserve">11.811957359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8332414627075</t>
   </si>
   <si>
     <t xml:space="preserve">11.8403358459473</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">11.7871284484863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7481107711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7126388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7977705001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935432434082</t>
+    <t xml:space="preserve">11.7481098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7126398086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935441970825</t>
   </si>
   <si>
     <t xml:space="preserve">12.1063709259033</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">12.1312007904053</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0708999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1418428421021</t>
+    <t xml:space="preserve">12.0708990097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1418409347534</t>
   </si>
   <si>
     <t xml:space="preserve">12.1773147583008</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">12.2092370986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2056913375854</t>
+    <t xml:space="preserve">12.2056903839111</t>
   </si>
   <si>
     <t xml:space="preserve">12.1560306549072</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">12.1808605194092</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1170110702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9893159866333</t>
+    <t xml:space="preserve">12.1170129776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.989315032959</t>
   </si>
   <si>
     <t xml:space="preserve">12.024787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0105981826782</t>
+    <t xml:space="preserve">12.0105972290039</t>
   </si>
   <si>
     <t xml:space="preserve">12.0567111968994</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">11.9964094161987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8545246124268</t>
+    <t xml:space="preserve">11.8545236587524</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467506408691</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">11.9573907852173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6629800796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5884885787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707530975342</t>
+    <t xml:space="preserve">11.6629791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5884895324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707540512085</t>
   </si>
   <si>
     <t xml:space="preserve">11.6594314575195</t>
@@ -2072,88 +2072,88 @@
     <t xml:space="preserve">11.3792085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4430570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2940759658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4749813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5069055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168651580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5778493881226</t>
+    <t xml:space="preserve">11.4430561065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2940769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4749803543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5069036483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168661117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5778474807739</t>
   </si>
   <si>
     <t xml:space="preserve">11.467887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4820747375488</t>
+    <t xml:space="preserve">11.4820737838745</t>
   </si>
   <si>
     <t xml:space="preserve">11.6558847427368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5388307571411</t>
+    <t xml:space="preserve">11.5388278961182</t>
   </si>
   <si>
     <t xml:space="preserve">11.6487903594971</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6842603683472</t>
+    <t xml:space="preserve">11.6842613220215</t>
   </si>
   <si>
     <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7374696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9432010650635</t>
+    <t xml:space="preserve">11.7374687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9432020187378</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921821594238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1347465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2021436691284</t>
+    <t xml:space="preserve">12.1347494125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2021446228027</t>
   </si>
   <si>
     <t xml:space="preserve">12.1844072341919</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3014640808105</t>
+    <t xml:space="preserve">12.3014631271362</t>
   </si>
   <si>
     <t xml:space="preserve">12.4149723052979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3972368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2908220291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6881008148193</t>
+    <t xml:space="preserve">12.397234916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2908229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.688099861145</t>
   </si>
   <si>
     <t xml:space="preserve">12.6597232818604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7058372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6739130020142</t>
+    <t xml:space="preserve">12.7058362960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6739139556885</t>
   </si>
   <si>
     <t xml:space="preserve">12.741307258606</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">12.6987428665161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6703662872314</t>
+    <t xml:space="preserve">12.6703653335571</t>
   </si>
   <si>
     <t xml:space="preserve">12.6136121749878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5852336883545</t>
+    <t xml:space="preserve">12.5852355957031</t>
   </si>
   <si>
     <t xml:space="preserve">12.3759527206421</t>
@@ -2183,31 +2183,31 @@
     <t xml:space="preserve">12.6065168380737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5887832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6490821838379</t>
+    <t xml:space="preserve">12.5887823104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6490831375122</t>
   </si>
   <si>
     <t xml:space="preserve">12.6774606704712</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8157978057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7448577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441734313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8406267166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080219268799</t>
+    <t xml:space="preserve">12.8157987594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7448539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441753387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8406276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080228805542</t>
   </si>
   <si>
     <t xml:space="preserve">13.0357208251953</t>
@@ -2219,43 +2219,43 @@
     <t xml:space="preserve">13.0463619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0534534454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0499086380005</t>
+    <t xml:space="preserve">13.0534553527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0499076843262</t>
   </si>
   <si>
     <t xml:space="preserve">13.0286254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9364004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8938331604004</t>
+    <t xml:space="preserve">12.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938360214233</t>
   </si>
   <si>
     <t xml:space="preserve">13.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1882457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1917943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.642279624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068105697632</t>
+    <t xml:space="preserve">13.1882476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1917934417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6422786712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068086624146</t>
   </si>
   <si>
     <t xml:space="preserve">13.6139039993286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8338251113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167701721191</t>
+    <t xml:space="preserve">13.8338260650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167692184448</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997142791748</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">13.2662839889526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2237186431885</t>
+    <t xml:space="preserve">13.2237167358398</t>
   </si>
   <si>
     <t xml:space="preserve">13.2343606948853</t>
@@ -2276,40 +2276,40 @@
     <t xml:space="preserve">13.1527767181396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2591915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627363204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9754190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612302780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9399471282959</t>
+    <t xml:space="preserve">13.2591905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627382278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9754199981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612293243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9399461746216</t>
   </si>
   <si>
     <t xml:space="preserve">12.9186639785767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9257574081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9541358947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250806808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.010890007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137580871582</t>
+    <t xml:space="preserve">12.9257593154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9541368484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0108909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137571334839</t>
   </si>
   <si>
     <t xml:space="preserve">13.1314935684204</t>
@@ -2333,34 +2333,34 @@
     <t xml:space="preserve">13.0640983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9683256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1031160354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0747394561768</t>
+    <t xml:space="preserve">12.9683246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1031150817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0747404098511</t>
   </si>
   <si>
     <t xml:space="preserve">12.9115705490112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9789657592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9860591888428</t>
+    <t xml:space="preserve">12.9789667129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9860610961914</t>
   </si>
   <si>
     <t xml:space="preserve">12.9505891799927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.86545753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235736846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690042495728</t>
+    <t xml:space="preserve">12.8654594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690052032471</t>
   </si>
   <si>
     <t xml:space="preserve">12.5710458755493</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">12.9434947967529</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6916484832764</t>
+    <t xml:space="preserve">12.6916475296021</t>
   </si>
   <si>
     <t xml:space="preserve">12.4823665618896</t>
@@ -2384,40 +2384,40 @@
     <t xml:space="preserve">13.0002489089966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0818319320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804727554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194923400879</t>
+    <t xml:space="preserve">13.0818328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194913864136</t>
   </si>
   <si>
     <t xml:space="preserve">13.323037147522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3939809799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3688592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2979164123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.248254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5352830886841</t>
+    <t xml:space="preserve">13.3939819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3688583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2979154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2482576370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5352821350098</t>
   </si>
   <si>
     <t xml:space="preserve">11.4004917144775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1628332138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8116664886475</t>
+    <t xml:space="preserve">11.1628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8116655349731</t>
   </si>
   <si>
     <t xml:space="preserve">9.76171493530273</t>
@@ -2429,25 +2429,25 @@
     <t xml:space="preserve">8.36769104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56278228759766</t>
+    <t xml:space="preserve">8.56278324127197</t>
   </si>
   <si>
     <t xml:space="preserve">8.01297760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69728326797485</t>
+    <t xml:space="preserve">7.69728231430054</t>
   </si>
   <si>
     <t xml:space="preserve">7.36739826202393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61569833755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72566032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920846939087</t>
+    <t xml:space="preserve">7.61569881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72566080093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920703887939</t>
   </si>
   <si>
     <t xml:space="preserve">8.58406639099121</t>
@@ -2456,25 +2456,25 @@
     <t xml:space="preserve">8.83236503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98134613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77915859222412</t>
+    <t xml:space="preserve">8.98134517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77915954589844</t>
   </si>
   <si>
     <t xml:space="preserve">8.77206420898438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80398750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5805196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74723529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64436912536621</t>
+    <t xml:space="preserve">8.80398845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58051872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74723434448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64436817169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.89976119995117</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">9.13032531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31832313537598</t>
+    <t xml:space="preserve">9.31832408905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.93878078460693</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">8.78979969024658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88911914825439</t>
+    <t xml:space="preserve">8.88912010192871</t>
   </si>
   <si>
     <t xml:space="preserve">8.6301794052124</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">8.84300708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77560997009277</t>
+    <t xml:space="preserve">8.77561187744141</t>
   </si>
   <si>
     <t xml:space="preserve">9.04164600372314</t>
@@ -2513,25 +2513,25 @@
     <t xml:space="preserve">9.20126724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43537902832031</t>
+    <t xml:space="preserve">9.435378074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.23319149017334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00972270965576</t>
+    <t xml:space="preserve">9.00972366333008</t>
   </si>
   <si>
     <t xml:space="preserve">9.176438331604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0345516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0948543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20481395721436</t>
+    <t xml:space="preserve">9.03455257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09485244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20481491088867</t>
   </si>
   <si>
     <t xml:space="preserve">9.12323093414307</t>
@@ -2543,10 +2543,10 @@
     <t xml:space="preserve">8.91040229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17268943786621</t>
+    <t xml:space="preserve">8.80044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17269039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.01014518737793</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">9.05817031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78849411010742</t>
+    <t xml:space="preserve">8.78849601745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.99536991119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96212196350098</t>
+    <t xml:space="preserve">8.96212291717529</t>
   </si>
   <si>
     <t xml:space="preserve">9.20963287353516</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">9.22440910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52364063262939</t>
+    <t xml:space="preserve">9.52363967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.81178665161133</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">10.3474454879761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6282043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540632247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5395431518555</t>
+    <t xml:space="preserve">10.6282052993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5395441055298</t>
   </si>
   <si>
     <t xml:space="preserve">10.3215856552124</t>
@@ -2606,19 +2606,19 @@
     <t xml:space="preserve">9.91891860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90414237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1257925033569</t>
+    <t xml:space="preserve">9.90414047241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1257944107056</t>
   </si>
   <si>
     <t xml:space="preserve">10.0519094467163</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92630672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0592985153198</t>
+    <t xml:space="preserve">9.92630767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0592966079712</t>
   </si>
   <si>
     <t xml:space="preserve">10.0703802108765</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">9.80070495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82656383514404</t>
+    <t xml:space="preserve">9.82656288146973</t>
   </si>
   <si>
     <t xml:space="preserve">9.91522407531738</t>
@@ -2642,34 +2642,34 @@
     <t xml:space="preserve">10.2218427658081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.155345916748</t>
+    <t xml:space="preserve">10.1553468704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.2587852478027</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1627368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675331115723</t>
+    <t xml:space="preserve">10.1627349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675426483154</t>
   </si>
   <si>
     <t xml:space="preserve">9.97063732147217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0777702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1294870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2107591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1147089004517</t>
+    <t xml:space="preserve">10.0777683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.129487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070646286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2107601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1147108078003</t>
   </si>
   <si>
     <t xml:space="preserve">10.1812057495117</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">10.3289747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2772541046143</t>
+    <t xml:space="preserve">10.2772560119629</t>
   </si>
   <si>
     <t xml:space="preserve">10.0408267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98541450500488</t>
+    <t xml:space="preserve">9.98541355133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.97433090209961</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">9.46453285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3537073135376</t>
+    <t xml:space="preserve">9.35370635986328</t>
   </si>
   <si>
     <t xml:space="preserve">9.40911865234375</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">9.55688762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63077068328857</t>
+    <t xml:space="preserve">9.63077163696289</t>
   </si>
   <si>
     <t xml:space="preserve">9.38695430755615</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">9.78592681884766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73051452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68618297576904</t>
+    <t xml:space="preserve">9.7305154800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68618392944336</t>
   </si>
   <si>
     <t xml:space="preserve">9.53841590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70834922790527</t>
+    <t xml:space="preserve">9.70835018157959</t>
   </si>
   <si>
     <t xml:space="preserve">9.6270751953125</t>
@@ -2729,16 +2729,16 @@
     <t xml:space="preserve">9.56058120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76376152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78223323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60860633850098</t>
+    <t xml:space="preserve">9.76376247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78223419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60860538482666</t>
   </si>
   <si>
     <t xml:space="preserve">9.62338256835938</t>
@@ -2750,73 +2750,73 @@
     <t xml:space="preserve">9.57535839080811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47192096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37217903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56796932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48669719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47561550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36478900909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10619640350342</t>
+    <t xml:space="preserve">9.47192001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37217807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56796836853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47561454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36478805541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1061954498291</t>
   </si>
   <si>
     <t xml:space="preserve">8.75155258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70352745056152</t>
+    <t xml:space="preserve">8.70352649688721</t>
   </si>
   <si>
     <t xml:space="preserve">8.66658592224121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59639739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976623535156</t>
+    <t xml:space="preserve">8.59639644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976528167725</t>
   </si>
   <si>
     <t xml:space="preserve">8.81804847717285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88454437255859</t>
+    <t xml:space="preserve">8.88454341888428</t>
   </si>
   <si>
     <t xml:space="preserve">8.76632881164551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91779041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14313697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11358261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2982931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24288082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2207145690918</t>
+    <t xml:space="preserve">8.91779136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14313793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1135835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29829406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24287986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22071552276611</t>
   </si>
   <si>
     <t xml:space="preserve">9.12466621398926</t>
@@ -2834,37 +2834,37 @@
     <t xml:space="preserve">9.01753425598145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03969955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81435394287109</t>
+    <t xml:space="preserve">9.03969860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81435489654541</t>
   </si>
   <si>
     <t xml:space="preserve">8.82543659210205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77371788024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39321422576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41907405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50404167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72200012207031</t>
+    <t xml:space="preserve">8.77371883392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39321517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41907501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5040397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72199726104736</t>
   </si>
   <si>
     <t xml:space="preserve">8.89193058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01383972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14683055877686</t>
+    <t xml:space="preserve">9.013840675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14683246612549</t>
   </si>
   <si>
     <t xml:space="preserve">9.72312545776367</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">10.0740747451782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3178911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4398002624512</t>
+    <t xml:space="preserve">10.317892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4398012161255</t>
   </si>
   <si>
     <t xml:space="preserve">10.5136833190918</t>
@@ -2891,19 +2891,19 @@
     <t xml:space="preserve">10.395468711853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4952125549316</t>
+    <t xml:space="preserve">10.495213508606</t>
   </si>
   <si>
     <t xml:space="preserve">10.5062961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6245088577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910057067871</t>
+    <t xml:space="preserve">10.6245107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7094755172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910047531128</t>
   </si>
   <si>
     <t xml:space="preserve">10.5801792144775</t>
@@ -2912,19 +2912,19 @@
     <t xml:space="preserve">10.6577577590942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7648887634277</t>
+    <t xml:space="preserve">10.7648906707764</t>
   </si>
   <si>
     <t xml:space="preserve">10.7131700515747</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6097326278687</t>
+    <t xml:space="preserve">10.609733581543</t>
   </si>
   <si>
     <t xml:space="preserve">10.5838737487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6060390472412</t>
+    <t xml:space="preserve">10.6060400009155</t>
   </si>
   <si>
     <t xml:space="preserve">10.4065523147583</t>
@@ -2933,28 +2933,28 @@
     <t xml:space="preserve">10.535849571228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5506267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2624788284302</t>
+    <t xml:space="preserve">10.5506258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617084503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2624797821045</t>
   </si>
   <si>
     <t xml:space="preserve">10.4176349639893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6134262084961</t>
+    <t xml:space="preserve">10.6134281158447</t>
   </si>
   <si>
     <t xml:space="preserve">10.5764856338501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2809505462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6983938217163</t>
+    <t xml:space="preserve">10.2809495925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.698392868042</t>
   </si>
   <si>
     <t xml:space="preserve">10.7464179992676</t>
@@ -2963,40 +2963,40 @@
     <t xml:space="preserve">10.6392860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6836166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7168655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.942211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.827691078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7205591201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6429796218872</t>
+    <t xml:space="preserve">10.6836175918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7168645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9422121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8276901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7205581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6429815292358</t>
   </si>
   <si>
     <t xml:space="preserve">10.4102468490601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5321559906006</t>
+    <t xml:space="preserve">10.5321550369263</t>
   </si>
   <si>
     <t xml:space="preserve">10.6947002410889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0456485748291</t>
+    <t xml:space="preserve">11.0456476211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.3929023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4778699874878</t>
+    <t xml:space="preserve">11.4778690338135</t>
   </si>
   <si>
     <t xml:space="preserve">11.6145544052124</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">11.6884384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6441078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5997762680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5739192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6921329498291</t>
+    <t xml:space="preserve">11.6441087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5997791290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.573917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6921319961548</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367197036743</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4815626144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4557046890259</t>
+    <t xml:space="preserve">11.5111179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4815645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4557037353516</t>
   </si>
   <si>
     <t xml:space="preserve">11.5000343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.699520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4889535903931</t>
+    <t xml:space="preserve">11.6995220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4889526367188</t>
   </si>
   <si>
     <t xml:space="preserve">11.6958274841309</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">11.8435955047607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8768444061279</t>
+    <t xml:space="preserve">11.8768434524536</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251237869263</t>
@@ -3062,34 +3062,34 @@
     <t xml:space="preserve">12.1908493041992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2130155563354</t>
+    <t xml:space="preserve">12.2130146026611</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795114517212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3866424560547</t>
+    <t xml:space="preserve">12.3866415023804</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900798797607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4383592605591</t>
+    <t xml:space="preserve">12.4383602142334</t>
   </si>
   <si>
     <t xml:space="preserve">12.4789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755598068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4568319320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.360782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4161968231201</t>
+    <t xml:space="preserve">12.3755588531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4568328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3607807159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4161958694458</t>
   </si>
   <si>
     <t xml:space="preserve">12.4125003814697</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048570632935</t>
+    <t xml:space="preserve">12.5048561096191</t>
   </si>
   <si>
     <t xml:space="preserve">12.6045989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">12.66370677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5824346542358</t>
+    <t xml:space="preserve">12.6637058258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5824356079102</t>
   </si>
   <si>
     <t xml:space="preserve">12.6600122451782</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">12.6858711242676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.637845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5344104766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.611988067627</t>
+    <t xml:space="preserve">12.6378479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5344095230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6119890213013</t>
   </si>
   <si>
     <t xml:space="preserve">12.6230697631836</t>
@@ -3134,40 +3134,40 @@
     <t xml:space="preserve">12.6489305496216</t>
   </si>
   <si>
-    <t xml:space="preserve">12.726508140564</t>
+    <t xml:space="preserve">12.7265090942383</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457492828369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4679136276245</t>
+    <t xml:space="preserve">12.4679145812988</t>
   </si>
   <si>
     <t xml:space="preserve">12.3977251052856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3275337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5602693557739</t>
+    <t xml:space="preserve">12.3275346755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5602684020996</t>
   </si>
   <si>
     <t xml:space="preserve">12.4420557022095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5972089767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7228136062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8336410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740200042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631935119629</t>
+    <t xml:space="preserve">12.5972108840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7228126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8336391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631925582886</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149122238159</t>
@@ -3176,22 +3176,22 @@
     <t xml:space="preserve">12.9592437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0331268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368213653564</t>
+    <t xml:space="preserve">13.0331249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368204116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.0626802444458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.881664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8890523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0479030609131</t>
+    <t xml:space="preserve">12.8816633224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8890514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0479040145874</t>
   </si>
   <si>
     <t xml:space="preserve">13.2438173294067</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">13.1184320449829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9773731231689</t>
+    <t xml:space="preserve">12.9773721694946</t>
   </si>
   <si>
     <t xml:space="preserve">13.0910034179688</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">13.1772060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2673273086548</t>
+    <t xml:space="preserve">13.2673263549805</t>
   </si>
   <si>
     <t xml:space="preserve">13.2830009460449</t>
@@ -3224,31 +3224,31 @@
     <t xml:space="preserve">13.5180978775024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4985065460205</t>
+    <t xml:space="preserve">13.4985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">13.4632415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201402664185</t>
+    <t xml:space="preserve">13.4201412200928</t>
   </si>
   <si>
     <t xml:space="preserve">13.4318943023682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4397315979004</t>
+    <t xml:space="preserve">13.4397325515747</t>
   </si>
   <si>
     <t xml:space="preserve">13.4514875411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102605819702</t>
+    <t xml:space="preserve">13.5102615356445</t>
   </si>
   <si>
     <t xml:space="preserve">13.2359790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712450027466</t>
+    <t xml:space="preserve">13.2712440490723</t>
   </si>
   <si>
     <t xml:space="preserve">13.232063293457</t>
@@ -3257,67 +3257,67 @@
     <t xml:space="preserve">13.0518217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3339376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1262693405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2477369308472</t>
+    <t xml:space="preserve">13.3339366912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2477359771729</t>
   </si>
   <si>
     <t xml:space="preserve">13.3731203079224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3221836090088</t>
+    <t xml:space="preserve">13.3221826553345</t>
   </si>
   <si>
     <t xml:space="preserve">13.4358139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1967973709106</t>
+    <t xml:space="preserve">13.196798324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.9852104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3261003494263</t>
+    <t xml:space="preserve">13.3261013031006</t>
   </si>
   <si>
     <t xml:space="preserve">13.3300199508667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.263409614563</t>
+    <t xml:space="preserve">13.2634086608887</t>
   </si>
   <si>
     <t xml:space="preserve">13.1654510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7148485183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441505432129</t>
+    <t xml:space="preserve">13.1145133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7148475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441514968872</t>
   </si>
   <si>
     <t xml:space="preserve">13.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1576166152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1301860809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.067494392395</t>
+    <t xml:space="preserve">13.1576156616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1301870346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046346664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0674934387207</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891290664673</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">13.2947549819946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3456935882568</t>
+    <t xml:space="preserve">13.3456945419312</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
@@ -3350,67 +3350,67 @@
     <t xml:space="preserve">13.5416088104248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3770389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4436502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4240579605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848752975464</t>
+    <t xml:space="preserve">13.3770399093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4436511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4240570068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848762512207</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5337705612183</t>
+    <t xml:space="preserve">13.5337715148926</t>
   </si>
   <si>
     <t xml:space="preserve">13.5964641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6121368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5729541778564</t>
+    <t xml:space="preserve">13.612135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5729532241821</t>
   </si>
   <si>
     <t xml:space="preserve">13.7414398193359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8393974304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9060096740723</t>
+    <t xml:space="preserve">13.8393983840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9060087203979</t>
   </si>
   <si>
     <t xml:space="preserve">13.6591567993164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8824987411499</t>
+    <t xml:space="preserve">13.8315591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8824977874756</t>
   </si>
   <si>
     <t xml:space="preserve">14.0039663314819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8589897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0901689529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2037973403931</t>
+    <t xml:space="preserve">13.8589878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748285293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0901679992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2037982940674</t>
   </si>
   <si>
     <t xml:space="preserve">14.364447593689</t>
@@ -3419,16 +3419,16 @@
     <t xml:space="preserve">14.595627784729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3017539978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349775314331</t>
+    <t xml:space="preserve">14.3017559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349784851074</t>
   </si>
   <si>
     <t xml:space="preserve">14.4114675521851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271392822266</t>
+    <t xml:space="preserve">14.4271411895752</t>
   </si>
   <si>
     <t xml:space="preserve">14.3997135162354</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014217376709</t>
+    <t xml:space="preserve">14.564281463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014198303223</t>
   </si>
   <si>
     <t xml:space="preserve">14.7288475036621</t>
@@ -3449,49 +3449,49 @@
     <t xml:space="preserve">14.8072156906128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8816633224487</t>
+    <t xml:space="preserve">14.8816623687744</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6739931106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7249317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739608764648</t>
+    <t xml:space="preserve">14.6739950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7249307632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851800918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739599227905</t>
   </si>
   <si>
     <t xml:space="preserve">14.921745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9538774490356</t>
+    <t xml:space="preserve">14.9538793563843</t>
   </si>
   <si>
     <t xml:space="preserve">15.0141286849976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.118558883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0663442611694</t>
+    <t xml:space="preserve">15.1185579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0663423538208</t>
   </si>
   <si>
     <t xml:space="preserve">15.1346263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310247421265</t>
+    <t xml:space="preserve">15.1426610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310256958008</t>
   </si>
   <si>
     <t xml:space="preserve">15.247091293335</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">15.3234081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2591428756714</t>
+    <t xml:space="preserve">15.2591409683228</t>
   </si>
   <si>
     <t xml:space="preserve">15.3475065231323</t>
@@ -3512,34 +3512,34 @@
     <t xml:space="preserve">15.2511081695557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2792263031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.38365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3716068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4559564590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0743761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418287277222</t>
+    <t xml:space="preserve">15.2792253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3836545944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3716087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4559545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0743780136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418277740479</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887807846069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7811613082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7570638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168979644775</t>
+    <t xml:space="preserve">14.7811632156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7570657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168960571289</t>
   </si>
   <si>
     <t xml:space="preserve">14.1867036819458</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">14.299168586731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2429370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5642652511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4919672012329</t>
+    <t xml:space="preserve">14.2429361343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.564266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4919681549072</t>
   </si>
   <si>
     <t xml:space="preserve">14.6124649047852</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">15.0221605300903</t>
   </si>
   <si>
-    <t xml:space="preserve">14.857479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8614959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213300704956</t>
+    <t xml:space="preserve">14.8574800491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297780990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213319778442</t>
   </si>
   <si>
     <t xml:space="preserve">14.6767311096191</t>
@@ -3587,43 +3587,43 @@
     <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9016609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060939788818</t>
+    <t xml:space="preserve">14.9016618728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060930252075</t>
   </si>
   <si>
     <t xml:space="preserve">14.9659261703491</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2671747207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788101196289</t>
+    <t xml:space="preserve">15.2671737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788091659546</t>
   </si>
   <si>
     <t xml:space="preserve">14.8333787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9177284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8293619155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0583114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422439575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8132963180542</t>
+    <t xml:space="preserve">14.9177293777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8293628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337949752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.058310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422449111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8132972717285</t>
   </si>
   <si>
     <t xml:space="preserve">14.9257621765137</t>
@@ -3632,28 +3632,28 @@
     <t xml:space="preserve">15.1466760635376</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0382270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627426147461</t>
+    <t xml:space="preserve">15.0382261276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627416610718</t>
   </si>
   <si>
     <t xml:space="preserve">14.3754863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4999990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847648620605</t>
+    <t xml:space="preserve">14.4999980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847639083862</t>
   </si>
   <si>
     <t xml:space="preserve">14.6727142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9940452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7369794845581</t>
+    <t xml:space="preserve">14.9940462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7369804382324</t>
   </si>
   <si>
     <t xml:space="preserve">14.9819946289062</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">14.957896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7450122833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270078659058</t>
+    <t xml:space="preserve">14.7450132369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270069122314</t>
   </si>
   <si>
     <t xml:space="preserve">14.893630027771</t>
@@ -3674,22 +3674,22 @@
     <t xml:space="preserve">14.5562324523926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.596399307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0300559997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9256229400635</t>
+    <t xml:space="preserve">14.5963973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0300550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714666366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9256219863892</t>
   </si>
   <si>
     <t xml:space="preserve">13.8372583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7770080566406</t>
+    <t xml:space="preserve">13.7770090103149</t>
   </si>
   <si>
     <t xml:space="preserve">13.0379505157471</t>
@@ -3698,46 +3698,46 @@
     <t xml:space="preserve">12.7447366714478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9937677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6243762969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4958438873291</t>
+    <t xml:space="preserve">12.993766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6243753433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4958448410034</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1746549606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3875350952148</t>
+    <t xml:space="preserve">14.174654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3875341415405</t>
   </si>
   <si>
     <t xml:space="preserve">15.0824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0502777099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1667594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.315375328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6005525588989</t>
+    <t xml:space="preserve">15.0502786636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1667604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3153734207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6005544662476</t>
   </si>
   <si>
     <t xml:space="preserve">16.1789455413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8495845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1628837585449</t>
+    <t xml:space="preserve">15.8495826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
     <t xml:space="preserve">16.6850414276123</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">16.3074798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.235179901123</t>
+    <t xml:space="preserve">16.2351779937744</t>
   </si>
   <si>
     <t xml:space="preserve">16.0504150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523548126221</t>
+    <t xml:space="preserve">15.5523567199707</t>
   </si>
   <si>
     <t xml:space="preserve">15.7331008911133</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">15.4117727279663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4760398864746</t>
+    <t xml:space="preserve">15.476037979126</t>
   </si>
   <si>
     <t xml:space="preserve">14.9980611801147</t>
@@ -3779,46 +3779,46 @@
     <t xml:space="preserve">14.7932147979736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5080327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5441818237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4598321914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5401649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196691513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7048463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6204996109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4518003463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2469539642334</t>
+    <t xml:space="preserve">14.5080337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5441827774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4598331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5401668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7048482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4518013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2469530105591</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2670373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947383880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3112192153931</t>
+    <t xml:space="preserve">14.2268686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2670364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3112182617188</t>
   </si>
   <si>
     <t xml:space="preserve">14.4558181762695</t>
@@ -6081,6 +6081,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.8300018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.310001373291</t>
   </si>
 </sst>
 </file>
@@ -71653,7 +71656,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911111111</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>3112275</v>
@@ -71674,6 +71677,32 @@
         <v>2022</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6912384259</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>3535464</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>34.7000007629395</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>34.3199996948242</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>34.310001373291</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -47,31 +47,31 @@
     <t xml:space="preserve">9.31058979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13427352905273</t>
+    <t xml:space="preserve">9.13427257537842</t>
   </si>
   <si>
     <t xml:space="preserve">9.11721134185791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02052307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76458072662354</t>
+    <t xml:space="preserve">9.02052116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76457977294922</t>
   </si>
   <si>
     <t xml:space="preserve">8.88970756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0660228729248</t>
+    <t xml:space="preserve">9.06602096557617</t>
   </si>
   <si>
     <t xml:space="preserve">8.95795822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75889301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120227813721</t>
+    <t xml:space="preserve">8.75889205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120132446289</t>
   </si>
   <si>
     <t xml:space="preserve">8.63376522064209</t>
@@ -92,28 +92,28 @@
     <t xml:space="preserve">8.04794311523438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93987941741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568689346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668935775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41662168502808</t>
+    <t xml:space="preserve">7.93987894058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568784713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668792724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4166202545166</t>
   </si>
   <si>
     <t xml:space="preserve">7.23461771011353</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15499210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161365509033</t>
+    <t xml:space="preserve">7.1549916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161317825317</t>
   </si>
   <si>
     <t xml:space="preserve">6.74548482894897</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">6.47248029708862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81373596191406</t>
+    <t xml:space="preserve">6.81373643875122</t>
   </si>
   <si>
     <t xml:space="preserve">6.23360204696655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34166622161865</t>
+    <t xml:space="preserve">6.34166526794434</t>
   </si>
   <si>
     <t xml:space="preserve">6.59760713577271</t>
@@ -140,34 +140,34 @@
     <t xml:space="preserve">6.77392292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6601710319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89905118942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8933629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95592641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28580760955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643377304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45074701309204</t>
+    <t xml:space="preserve">6.72842216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66017055511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89904975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89336252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26305532455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28580617904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643329620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45074653625488</t>
   </si>
   <si>
     <t xml:space="preserve">7.37680768966675</t>
@@ -176,361 +176,361 @@
     <t xml:space="preserve">7.24599266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31993246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249540328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37111949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750247955322</t>
+    <t xml:space="preserve">7.31993103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3711199760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750200271606</t>
   </si>
   <si>
     <t xml:space="preserve">7.79200124740601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87731647491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89437913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67256355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037357330322</t>
+    <t xml:space="preserve">7.87731599807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437818527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256212234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587385177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037214279175</t>
   </si>
   <si>
     <t xml:space="preserve">7.3654317855835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42799663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48487234115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4109320640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286836624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2175555229187</t>
+    <t xml:space="preserve">7.4279956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48487281799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41093349456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30286979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755456924438</t>
   </si>
   <si>
     <t xml:space="preserve">6.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00711441040039</t>
+    <t xml:space="preserve">7.00711488723755</t>
   </si>
   <si>
     <t xml:space="preserve">6.85354900360107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05261659622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13792896270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43368339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49624824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47918462753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862375259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75218963623047</t>
+    <t xml:space="preserve">7.05261468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13792848587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4336838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4962477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4791841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218820571899</t>
   </si>
   <si>
     <t xml:space="preserve">7.83181524276733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78631496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456562042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8033766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77493953704834</t>
+    <t xml:space="preserve">7.7863130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80337810516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7749400138855</t>
   </si>
   <si>
     <t xml:space="preserve">7.57018566131592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39387083053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35405778884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53606081008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105325698853</t>
+    <t xml:space="preserve">7.39386987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35405731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53606033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105278015137</t>
   </si>
   <si>
     <t xml:space="preserve">7.16636657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0583028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25168037414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84845352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90873336791992</t>
+    <t xml:space="preserve">7.05830192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25168132781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90873193740845</t>
   </si>
   <si>
     <t xml:space="preserve">7.94490146636963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85447883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76406097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54705286026001</t>
+    <t xml:space="preserve">7.85448026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228446960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76406002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54705333709717</t>
   </si>
   <si>
     <t xml:space="preserve">7.534996509552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66158390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7700891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42046499252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17934465408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9743914604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850416183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014074325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40840816497803</t>
+    <t xml:space="preserve">7.66158485412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42046546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17934417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439241409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850511550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92014122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4084095954895</t>
   </si>
   <si>
     <t xml:space="preserve">7.54102420806885</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58322095870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257389068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02498340606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11841678619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26308870315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953760147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187379837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25103187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1304726600647</t>
+    <t xml:space="preserve">7.58322048187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58257293701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02498292922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11841630935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26308965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43187236785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25103330612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13047361373901</t>
   </si>
   <si>
     <t xml:space="preserve">5.91647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92853546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76341342926025</t>
+    <t xml:space="preserve">5.92853498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967847824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790149688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76341390609741</t>
   </si>
   <si>
     <t xml:space="preserve">6.69710445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87191677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177589416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84780406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77546834945679</t>
+    <t xml:space="preserve">6.87191724777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560874938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84177684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8478045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77546882629395</t>
   </si>
   <si>
     <t xml:space="preserve">6.73327302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68504905700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81163644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62476921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10097932815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07084083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79355144500732</t>
+    <t xml:space="preserve">6.68505001068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81163692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10098075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07084035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79355382919312</t>
   </si>
   <si>
     <t xml:space="preserve">7.06481218338013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20948505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210062026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808534622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73930072784424</t>
+    <t xml:space="preserve">7.20948457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990530014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000082015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808439254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7393012046814</t>
   </si>
   <si>
     <t xml:space="preserve">7.04070043563843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01658868789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81766414642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74532842636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149557113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425249099731</t>
+    <t xml:space="preserve">7.01658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74532794952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271381378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149604797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425296783447</t>
   </si>
   <si>
     <t xml:space="preserve">6.99247646331787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93822383880615</t>
+    <t xml:space="preserve">6.93822431564331</t>
   </si>
   <si>
     <t xml:space="preserve">6.88397312164307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98042011260986</t>
+    <t xml:space="preserve">6.98041963577271</t>
   </si>
   <si>
     <t xml:space="preserve">7.15523242950439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25770854949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72724533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79958009719849</t>
+    <t xml:space="preserve">7.25770807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313215255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79958057403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.75135707855225</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.59462833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56448936462402</t>
+    <t xml:space="preserve">6.56448841094971</t>
   </si>
   <si>
     <t xml:space="preserve">6.57654523849487</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">6.60668516159058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54640340805054</t>
+    <t xml:space="preserve">6.5464038848877</t>
   </si>
   <si>
     <t xml:space="preserve">6.51626491546631</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">6.49818086624146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76944017410278</t>
+    <t xml:space="preserve">6.76944065093994</t>
   </si>
   <si>
     <t xml:space="preserve">6.85986042022705</t>
@@ -566,97 +566,97 @@
     <t xml:space="preserve">6.85383224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18537187576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1672887802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784847259521</t>
+    <t xml:space="preserve">7.18537282943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16728830337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742727279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784942626953</t>
   </si>
   <si>
     <t xml:space="preserve">7.26976490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33004522323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31196165084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317655563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09495306015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98644781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574819564819</t>
+    <t xml:space="preserve">7.33004474639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31196022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317750930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09495258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98644828796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574962615967</t>
   </si>
   <si>
     <t xml:space="preserve">7.08892440795898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686758041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8779444694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02261638641357</t>
+    <t xml:space="preserve">7.07686901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87794399261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02261781692505</t>
   </si>
   <si>
     <t xml:space="preserve">6.8236927986145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43854904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73391962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68031597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45125389099121</t>
+    <t xml:space="preserve">7.43854808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35415649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73392009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6803150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45125102996826</t>
   </si>
   <si>
     <t xml:space="preserve">8.47536373138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41508388519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33069229125977</t>
+    <t xml:space="preserve">8.41508293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33069133758545</t>
   </si>
   <si>
     <t xml:space="preserve">8.54167175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55975532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63812065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59592437744141</t>
+    <t xml:space="preserve">8.5597562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6381196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58386898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59592533111572</t>
   </si>
   <si>
     <t xml:space="preserve">8.66223239898682</t>
@@ -665,34 +665,34 @@
     <t xml:space="preserve">8.66826057434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55372619628906</t>
+    <t xml:space="preserve">8.55372714996338</t>
   </si>
   <si>
     <t xml:space="preserve">8.50550365447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5115327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017700195312</t>
+    <t xml:space="preserve">8.51153182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017604827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.71045589447021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75265026092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69839954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7164831161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52358913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4874210357666</t>
+    <t xml:space="preserve">8.75265216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69840049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71648406982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52358818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48742008209229</t>
   </si>
   <si>
     <t xml:space="preserve">8.38494396209717</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">8.23424339294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16793727874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27041149139404</t>
+    <t xml:space="preserve">8.16793632507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27041244506836</t>
   </si>
   <si>
     <t xml:space="preserve">8.26438522338867</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">8.5898962020874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29517078399658</t>
+    <t xml:space="preserve">9.2951717376709</t>
   </si>
   <si>
     <t xml:space="preserve">9.38559246063232</t>
@@ -728,67 +728,67 @@
     <t xml:space="preserve">9.28311538696289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98774242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88526725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84909820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00582790374756</t>
+    <t xml:space="preserve">8.98774433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88526821136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84910011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00582695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.02993869781494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81896018981934</t>
+    <t xml:space="preserve">8.81895923614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.77073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67428874969482</t>
+    <t xml:space="preserve">8.67428779602051</t>
   </si>
   <si>
     <t xml:space="preserve">8.74059581756592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90335083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04802322387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87924003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90937900543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95760440826416</t>
+    <t xml:space="preserve">8.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04802417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87923908233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90937995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95760345458984</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81293201446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74662399291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6562032699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49947738647461</t>
+    <t xml:space="preserve">8.81293106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74662494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65620422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49947643280029</t>
   </si>
   <si>
     <t xml:space="preserve">8.14985179901123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27643966674805</t>
+    <t xml:space="preserve">8.27644062042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.54769992828369</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">8.46330833435059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56578254699707</t>
+    <t xml:space="preserve">8.5657844543457</t>
   </si>
   <si>
     <t xml:space="preserve">8.78881931304932</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">8.79484844207764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78279304504395</t>
+    <t xml:space="preserve">8.78279209136963</t>
   </si>
   <si>
     <t xml:space="preserve">8.86718368530273</t>
@@ -824,129 +824,129 @@
     <t xml:space="preserve">8.6320915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6079797744751</t>
+    <t xml:space="preserve">8.60798072814941</t>
   </si>
   <si>
     <t xml:space="preserve">8.46933555603027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36083126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93349266052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75867938995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87321186065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04199504852295</t>
+    <t xml:space="preserve">8.36083221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93349170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7586784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87321090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04199600219727</t>
   </si>
   <si>
     <t xml:space="preserve">9.19269561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21077919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24092102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21680927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94554805755615</t>
+    <t xml:space="preserve">9.21078014373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24091911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21680736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94554710388184</t>
   </si>
   <si>
     <t xml:space="preserve">8.89129543304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03596687316895</t>
+    <t xml:space="preserve">9.03596782684326</t>
   </si>
   <si>
     <t xml:space="preserve">9.07213592529297</t>
   </si>
   <si>
+    <t xml:space="preserve">9.12036037445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30492973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33675479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18400573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15854740142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13308906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851779937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83395671844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94215202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03762149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81486225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73848819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89123725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95488262176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05035018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22855663299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2349214553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1712760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28583812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29856586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34948253631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25401592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219181060791</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.12035942077637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33675289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18400478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15854835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13309001922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851779937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83395671844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03762054443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81486320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73848819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89123630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9548807144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05035018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22855663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2349214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17127513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28583812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2985668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34948253631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25401306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219276428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12036037445068</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.24765014648438</t>
   </si>
   <si>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">9.33038806915283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38130474090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57860565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54678249359131</t>
+    <t xml:space="preserve">9.38130569458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57860660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54678344726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.54041767120361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64861392974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79500007629395</t>
+    <t xml:space="preserve">9.64861488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79499912261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.85864448547363</t>
@@ -989,37 +989,37 @@
     <t xml:space="preserve">9.52768898010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75681304931641</t>
+    <t xml:space="preserve">9.75681209564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.77590560913086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750389099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0877666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1386833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1959638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0623092651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0050296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82682132720947</t>
+    <t xml:space="preserve">9.80136299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750398635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0877676010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1386842727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2341508865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1959648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.062310218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0050287246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82682228088379</t>
   </si>
   <si>
     <t xml:space="preserve">9.86500930786133</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">9.78227043151855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71225929260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69953060150146</t>
+    <t xml:space="preserve">9.71226119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6995325088501</t>
   </si>
   <si>
     <t xml:space="preserve">9.68043804168701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69316673278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134357452393</t>
+    <t xml:space="preserve">9.69316577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134452819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.53405284881592</t>
@@ -1058,73 +1058,73 @@
     <t xml:space="preserve">9.52132511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57224082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61679172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67407131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62952136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59769821166992</t>
+    <t xml:space="preserve">9.57224178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61679267883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67407321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6295223236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59770011901855</t>
   </si>
   <si>
     <t xml:space="preserve">9.89046669006348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9477481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75044631958008</t>
+    <t xml:space="preserve">9.94774913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75044822692871</t>
   </si>
   <si>
     <t xml:space="preserve">9.89683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91592597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8777379989624</t>
+    <t xml:space="preserve">9.91592407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">10.0304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0686750411987</t>
+    <t xml:space="preserve">10.0686731338501</t>
   </si>
   <si>
     <t xml:space="preserve">10.1323194503784</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93501853942871</t>
+    <t xml:space="preserve">9.93501949310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.84591579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85227966308594</t>
+    <t xml:space="preserve">9.85228061676025</t>
   </si>
   <si>
     <t xml:space="preserve">9.83318710327148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72498893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99866390228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96047592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0177583694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95411205291748</t>
+    <t xml:space="preserve">9.72498989105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9986629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96047782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0177564620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95411109924316</t>
   </si>
   <si>
     <t xml:space="preserve">10.1259536743164</t>
@@ -1133,10 +1133,10 @@
     <t xml:space="preserve">10.0241212844849</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94138336181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8841028213501</t>
+    <t xml:space="preserve">9.94138240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88410186767578</t>
   </si>
   <si>
     <t xml:space="preserve">10.0368509292603</t>
@@ -1148,28 +1148,28 @@
     <t xml:space="preserve">9.63588523864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58497047424316</t>
+    <t xml:space="preserve">9.58497142791748</t>
   </si>
   <si>
     <t xml:space="preserve">9.61042785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66770839691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74408340454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73135566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80772876739502</t>
+    <t xml:space="preserve">9.6677074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74408435821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73135471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8077278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.73771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589542388916</t>
+    <t xml:space="preserve">9.70589637756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.5595121383667</t>
@@ -1178,46 +1178,46 @@
     <t xml:space="preserve">9.47677326202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97320556640625</t>
+    <t xml:space="preserve">9.97320652008057</t>
   </si>
   <si>
     <t xml:space="preserve">9.97957038879395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0814037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0559463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2914333343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.304162979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2023296356201</t>
+    <t xml:space="preserve">10.0814018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.055944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2914323806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3041620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2023286819458</t>
   </si>
   <si>
     <t xml:space="preserve">10.310525894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3232526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736869812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641407012939</t>
+    <t xml:space="preserve">10.3232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736879348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641416549683</t>
   </si>
   <si>
     <t xml:space="preserve">10.148229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99230003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76954174041748</t>
+    <t xml:space="preserve">9.99229907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76954078674316</t>
   </si>
   <si>
     <t xml:space="preserve">9.86819076538086</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">9.81727504730225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77908706665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81409168243408</t>
+    <t xml:space="preserve">9.77908897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8140926361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.80454635620117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36857604980469</t>
+    <t xml:space="preserve">9.368577003479</t>
   </si>
   <si>
     <t xml:space="preserve">9.65179824829102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85546207427979</t>
+    <t xml:space="preserve">9.85546112060547</t>
   </si>
   <si>
     <t xml:space="preserve">9.74726486206055</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">10.0082111358643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98593521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92865467071533</t>
+    <t xml:space="preserve">9.98593425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92865371704102</t>
   </si>
   <si>
     <t xml:space="preserve">9.94456577301025</t>
@@ -1271,40 +1271,40 @@
     <t xml:space="preserve">10.3137063980103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2946128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455305099487</t>
+    <t xml:space="preserve">10.2946147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455295562744</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.530101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6382970809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7655878067017</t>
+    <t xml:space="preserve">10.5301008224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.638298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.765588760376</t>
   </si>
   <si>
     <t xml:space="preserve">10.8546924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6319332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5841989517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6542110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.708309173584</t>
+    <t xml:space="preserve">10.6319341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178544998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5841979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6542091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7083072662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7051258087158</t>
@@ -1319,31 +1319,31 @@
     <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4409980773926</t>
+    <t xml:space="preserve">10.4409971237183</t>
   </si>
   <si>
     <t xml:space="preserve">10.5014610290527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5078258514404</t>
+    <t xml:space="preserve">10.5078248977661</t>
   </si>
   <si>
     <t xml:space="preserve">10.297797203064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3328018188477</t>
+    <t xml:space="preserve">10.3328008651733</t>
   </si>
   <si>
     <t xml:space="preserve">10.2596092224121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2864847183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2528896331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319513320923</t>
+    <t xml:space="preserve">10.2864856719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2528915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1319532394409</t>
   </si>
   <si>
     <t xml:space="preserve">10.0143737792969</t>
@@ -1355,16 +1355,16 @@
     <t xml:space="preserve">9.83968448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49702548980713</t>
+    <t xml:space="preserve">9.49702644348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.5541353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77585601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88335609436035</t>
+    <t xml:space="preserve">9.77585506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88335704803467</t>
   </si>
   <si>
     <t xml:space="preserve">9.86991882324219</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">9.65491771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67843341827393</t>
+    <t xml:space="preserve">9.67843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">9.52054119110107</t>
@@ -1391,37 +1391,37 @@
     <t xml:space="preserve">9.90015411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80609130859375</t>
+    <t xml:space="preserve">9.80609035491943</t>
   </si>
   <si>
     <t xml:space="preserve">9.76241779327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82960605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6985912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76913547515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60116577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61796474456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52390003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51718330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61124610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59108924865723</t>
+    <t xml:space="preserve">9.8296070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69859027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76913833618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60116672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61796283721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52390098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51718235015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61124515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59108829498291</t>
   </si>
   <si>
     <t xml:space="preserve">9.80945014953613</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6515588760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163730621338</t>
+    <t xml:space="preserve">9.65155792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163635253906</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84976196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85648059844971</t>
+    <t xml:space="preserve">9.84976100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85648250579834</t>
   </si>
   <si>
     <t xml:space="preserve">9.81616878509521</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">9.89007568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9035120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92366886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0479669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2125759124756</t>
+    <t xml:space="preserve">9.90351390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92366981506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070217132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2125778198242</t>
   </si>
   <si>
     <t xml:space="preserve">10.1117963790894</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95390510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0378885269165</t>
+    <t xml:space="preserve">9.95390319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0378894805908</t>
   </si>
   <si>
     <t xml:space="preserve">10.0009355545044</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">10.0681228637695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916395187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748414993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8665599822998</t>
+    <t xml:space="preserve">10.0916404724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748434066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86655902862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.71202754974365</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">9.92702865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98077869415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92030906677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63812160491943</t>
+    <t xml:space="preserve">9.98077964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92031002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6381196975708</t>
   </si>
   <si>
     <t xml:space="preserve">9.76577758789062</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">9.93710613250732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96062278747559</t>
+    <t xml:space="preserve">9.96062183380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.94382572174072</t>
@@ -1535,10 +1535,10 @@
     <t xml:space="preserve">10.1017179489136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0882797241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554679870605</t>
+    <t xml:space="preserve">10.0882806777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1554689407349</t>
   </si>
   <si>
     <t xml:space="preserve">10.1722640991211</t>
@@ -1556,19 +1556,19 @@
     <t xml:space="preserve">10.4309396743774</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3704690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9975757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88671684265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96734237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93038654327393</t>
+    <t xml:space="preserve">10.3704700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99757671356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88671588897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96734142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93038845062256</t>
   </si>
   <si>
     <t xml:space="preserve">9.70866775512695</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">9.59444808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50038623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61460399627686</t>
+    <t xml:space="preserve">9.50038433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61460494995117</t>
   </si>
   <si>
     <t xml:space="preserve">9.56421375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41304111480713</t>
+    <t xml:space="preserve">9.41304016113281</t>
   </si>
   <si>
     <t xml:space="preserve">9.43991565704346</t>
@@ -1598,19 +1598,19 @@
     <t xml:space="preserve">9.40968132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28874397277832</t>
+    <t xml:space="preserve">9.288743019104</t>
   </si>
   <si>
     <t xml:space="preserve">9.23835182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43655681610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33241558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53397750854492</t>
+    <t xml:space="preserve">9.43655586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3324146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53397846221924</t>
   </si>
   <si>
     <t xml:space="preserve">9.66499614715576</t>
@@ -1619,37 +1619,37 @@
     <t xml:space="preserve">9.62468338012695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63476085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57429218292236</t>
+    <t xml:space="preserve">9.65827655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63476181030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57429122924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.71538639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51382255554199</t>
+    <t xml:space="preserve">9.51382160186768</t>
   </si>
   <si>
     <t xml:space="preserve">9.59780788421631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5574951171875</t>
+    <t xml:space="preserve">9.55749607086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.57765102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81952857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87663745880127</t>
+    <t xml:space="preserve">9.8195276260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87663841247559</t>
   </si>
   <si>
     <t xml:space="preserve">9.9135913848877</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">10.0042953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0849199295044</t>
+    <t xml:space="preserve">10.0849208831787</t>
   </si>
   <si>
     <t xml:space="preserve">9.97406101226807</t>
@@ -1667,40 +1667,40 @@
     <t xml:space="preserve">9.57093238830566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6448392868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89679431915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85984230041504</t>
+    <t xml:space="preserve">9.64483833312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562072753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89679336547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85984134674072</t>
   </si>
   <si>
     <t xml:space="preserve">9.95054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.021092414856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0446071624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0647630691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327337265015</t>
+    <t xml:space="preserve">10.0210914611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0446081161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0647640228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327327728271</t>
   </si>
   <si>
     <t xml:space="preserve">10.3267974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3435955047607</t>
+    <t xml:space="preserve">10.3435945510864</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898435592651</t>
@@ -1712,55 +1712,55 @@
     <t xml:space="preserve">10.3133602142334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3839063644409</t>
+    <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.3771877288818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2764072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1991395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2461709976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932024002075</t>
+    <t xml:space="preserve">10.276406288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1991415023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2461719512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932043075562</t>
   </si>
   <si>
     <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1285934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2058591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2831249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1890630722046</t>
+    <t xml:space="preserve">10.1285924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2058582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2831258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1890621185303</t>
   </si>
   <si>
     <t xml:space="preserve">10.2293748855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3805484771729</t>
+    <t xml:space="preserve">10.2260160446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730474472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275798797607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4342985153198</t>
+    <t xml:space="preserve">10.4342975616455</t>
   </si>
   <si>
     <t xml:space="preserve">10.5451583862305</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">10.6728162765503</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6660966873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7400026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123466491699</t>
+    <t xml:space="preserve">10.6660985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7400035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123456954956</t>
   </si>
   <si>
     <t xml:space="preserve">10.565315246582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6157073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5921897888184</t>
+    <t xml:space="preserve">10.6157054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.592191696167</t>
   </si>
   <si>
     <t xml:space="preserve">10.6224250793457</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725831985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0591449737549</t>
+    <t xml:space="preserve">11.072585105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0591459274292</t>
   </si>
   <si>
     <t xml:space="preserve">11.0322723388672</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">11.0692253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.985239982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9718017578125</t>
+    <t xml:space="preserve">10.9852409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9718036651611</t>
   </si>
   <si>
     <t xml:space="preserve">11.0087556838989</t>
@@ -1823,25 +1823,25 @@
     <t xml:space="preserve">11.0860223770142</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2035989761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1767253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2304754257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2237567901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1733655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2170372009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002420425415</t>
+    <t xml:space="preserve">11.2036008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1767263412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2304763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2237577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1733646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2170391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002410888672</t>
   </si>
   <si>
     <t xml:space="preserve">11.2271156311035</t>
@@ -1850,37 +1850,37 @@
     <t xml:space="preserve">11.2976636886597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.35813331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4219608306885</t>
+    <t xml:space="preserve">11.3581342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4219617843628</t>
   </si>
   <si>
     <t xml:space="preserve">11.5563383102417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521961212158</t>
+    <t xml:space="preserve">11.4521970748901</t>
   </si>
   <si>
     <t xml:space="preserve">11.4286813735962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622735977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5832138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5529794692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6235246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6201677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6302452087402</t>
+    <t xml:space="preserve">11.4622755050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.583212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5529775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6235256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6201658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6302442550659</t>
   </si>
   <si>
     <t xml:space="preserve">11.5261039733887</t>
@@ -1889,43 +1889,43 @@
     <t xml:space="preserve">11.4824314117432</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4689950942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3245391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.415244102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093050003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4253196716309</t>
+    <t xml:space="preserve">11.468994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3245401382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648519515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4253215789795</t>
   </si>
   <si>
     <t xml:space="preserve">11.5636587142944</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5849418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.560112953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3189086914062</t>
+    <t xml:space="preserve">11.5849437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5601119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3189067840576</t>
   </si>
   <si>
     <t xml:space="preserve">11.5459232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4146795272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330955505371</t>
+    <t xml:space="preserve">11.4146814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330965042114</t>
   </si>
   <si>
     <t xml:space="preserve">11.2124938964844</t>
@@ -1940,70 +1940,70 @@
     <t xml:space="preserve">11.1238145828247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2727937698364</t>
+    <t xml:space="preserve">11.2727947235107</t>
   </si>
   <si>
     <t xml:space="preserve">11.1805696487427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2195873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2479648590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3366432189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4536991119385</t>
+    <t xml:space="preserve">11.2195863723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2479639053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3366422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4536981582642</t>
   </si>
   <si>
     <t xml:space="preserve">11.4288692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4785280227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4466037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7445631027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8119583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8332414627075</t>
+    <t xml:space="preserve">11.4785289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.446605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175466537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7445640563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8119592666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8332424163818</t>
   </si>
   <si>
     <t xml:space="preserve">11.8403358459473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7871284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7481088638306</t>
+    <t xml:space="preserve">11.7871294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7481098175049</t>
   </si>
   <si>
     <t xml:space="preserve">11.7126388549805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935422897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1063709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1312007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0708980560303</t>
+    <t xml:space="preserve">11.7977685928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1063718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1312017440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0708999633789</t>
   </si>
   <si>
     <t xml:space="preserve">12.1418418884277</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">12.1773147583008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2092361450195</t>
+    <t xml:space="preserve">12.2092370986938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2056903839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1560306549072</t>
+    <t xml:space="preserve">12.1560316085815</t>
   </si>
   <si>
     <t xml:space="preserve">12.1808605194092</t>
@@ -2030,25 +2030,25 @@
     <t xml:space="preserve">11.9893159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.024787902832</t>
+    <t xml:space="preserve">12.0247869491577</t>
   </si>
   <si>
     <t xml:space="preserve">12.0105981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0567111968994</t>
+    <t xml:space="preserve">12.0567121505737</t>
   </si>
   <si>
     <t xml:space="preserve">11.9751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9964094161987</t>
+    <t xml:space="preserve">11.996410369873</t>
   </si>
   <si>
     <t xml:space="preserve">11.8545236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9467506408691</t>
+    <t xml:space="preserve">11.9467496871948</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573917388916</t>
@@ -2066,55 +2066,55 @@
     <t xml:space="preserve">11.6594314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3437366485596</t>
+    <t xml:space="preserve">11.3437376022339</t>
   </si>
   <si>
     <t xml:space="preserve">11.3792095184326</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4430561065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2940769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4749803543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5069046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168661117554</t>
+    <t xml:space="preserve">11.4430570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.29407787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4749813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5069055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168670654297</t>
   </si>
   <si>
     <t xml:space="preserve">11.5778474807739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.467887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558847427368</t>
+    <t xml:space="preserve">11.4678859710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820737838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558837890625</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487903594971</t>
+    <t xml:space="preserve">11.6487913131714</t>
   </si>
   <si>
     <t xml:space="preserve">11.6842613220215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090911865234</t>
+    <t xml:space="preserve">11.7090921401978</t>
   </si>
   <si>
     <t xml:space="preserve">11.7374687194824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9432020187378</t>
+    <t xml:space="preserve">11.9432029724121</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921831130981</t>
@@ -2126,34 +2126,34 @@
     <t xml:space="preserve">12.2021436691284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1844062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3014640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4149723052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.397234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3262929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2908229827881</t>
+    <t xml:space="preserve">12.1844072341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3014612197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4149703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.39723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3262939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2908239364624</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6597232818604</t>
+    <t xml:space="preserve">12.6597242355347</t>
   </si>
   <si>
     <t xml:space="preserve">12.7058362960815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6739130020142</t>
+    <t xml:space="preserve">12.6739120483398</t>
   </si>
   <si>
     <t xml:space="preserve">12.7413082122803</t>
@@ -2162,22 +2162,22 @@
     <t xml:space="preserve">12.6987428665161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6703662872314</t>
+    <t xml:space="preserve">12.6703643798828</t>
   </si>
   <si>
     <t xml:space="preserve">12.6136121749878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5852355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5213842391968</t>
+    <t xml:space="preserve">12.5852346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5213851928711</t>
   </si>
   <si>
     <t xml:space="preserve">12.6065168380737</t>
@@ -2186,55 +2186,55 @@
     <t xml:space="preserve">12.5887823104858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6490821838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6774606704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8157997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7448558807373</t>
+    <t xml:space="preserve">12.6490840911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6774616241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8157978057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.744854927063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441743850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8477220535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8406276702881</t>
+    <t xml:space="preserve">12.8477210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8406286239624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0357208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0463609695435</t>
+    <t xml:space="preserve">13.035719871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215330123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0463600158691</t>
   </si>
   <si>
     <t xml:space="preserve">13.0534563064575</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0499086380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0286254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9364013671875</t>
+    <t xml:space="preserve">13.0499095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0286245346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9364023208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.893835067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1243991851807</t>
+    <t xml:space="preserve">13.124400138855</t>
   </si>
   <si>
     <t xml:space="preserve">13.1882467269897</t>
@@ -2243,91 +2243,91 @@
     <t xml:space="preserve">13.1917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6422786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338251113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167701721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997133255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145826339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.266284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2343616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1527757644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2591896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627382278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456832885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9754199981689</t>
+    <t xml:space="preserve">13.6422805786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2662858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2343606948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2591915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627372741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456813812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9754190444946</t>
   </si>
   <si>
     <t xml:space="preserve">12.9612302780151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9399471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9186639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9257593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9541358947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250797271729</t>
+    <t xml:space="preserve">12.9399490356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9186630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9257574081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9541368484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250787734985</t>
   </si>
   <si>
     <t xml:space="preserve">13.010890007019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1137571334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1314926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1776065826416</t>
+    <t xml:space="preserve">13.1137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1314945220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1776056289673</t>
   </si>
   <si>
     <t xml:space="preserve">13.1208524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4613771438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520952224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953420639038</t>
+    <t xml:space="preserve">13.4613761901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520961761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953430175781</t>
   </si>
   <si>
     <t xml:space="preserve">13.0640983581543</t>
@@ -2336,67 +2336,67 @@
     <t xml:space="preserve">12.9683246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1031160354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0747404098511</t>
+    <t xml:space="preserve">13.1031141281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0747385025024</t>
   </si>
   <si>
     <t xml:space="preserve">12.9115705490112</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9789667129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9860610961914</t>
+    <t xml:space="preserve">12.9789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9860601425171</t>
   </si>
   <si>
     <t xml:space="preserve">12.9505891799927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235727310181</t>
+    <t xml:space="preserve">12.86545753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235717773438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8690052032471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5710458755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6916465759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4823665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5462141036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7306671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.323037147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3939828872681</t>
+    <t xml:space="preserve">12.571044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434967041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6916494369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4823656082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7306661605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002508163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818357467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3230400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3939800262451</t>
   </si>
   <si>
     <t xml:space="preserve">12.3688583374023</t>
@@ -2408,49 +2408,49 @@
     <t xml:space="preserve">12.2482566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5352821350098</t>
+    <t xml:space="preserve">11.5352830886841</t>
   </si>
   <si>
     <t xml:space="preserve">11.4004917144775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1628332138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8116655349731</t>
+    <t xml:space="preserve">11.1628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8116674423218</t>
   </si>
   <si>
     <t xml:space="preserve">9.76171493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36769104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56278324127197</t>
+    <t xml:space="preserve">9.6127347946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36769199371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56278228759766</t>
   </si>
   <si>
     <t xml:space="preserve">8.01297760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69728231430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36739826202393</t>
+    <t xml:space="preserve">7.6972827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3673996925354</t>
   </si>
   <si>
     <t xml:space="preserve">7.61569881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72566032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920703887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58406639099121</t>
+    <t xml:space="preserve">7.72565984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58406734466553</t>
   </si>
   <si>
     <t xml:space="preserve">8.83236503601074</t>
@@ -2459,40 +2459,40 @@
     <t xml:space="preserve">8.98134517669678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77915954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77206420898438</t>
+    <t xml:space="preserve">8.7791576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77206516265869</t>
   </si>
   <si>
     <t xml:space="preserve">8.80398845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58051872253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74723529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64436912536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89976119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07002449035645</t>
+    <t xml:space="preserve">8.5805196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74723434448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64436817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89976215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07002353668213</t>
   </si>
   <si>
     <t xml:space="preserve">9.13032531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31832313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93878078460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78979969024658</t>
+    <t xml:space="preserve">9.31832408905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9387788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7898006439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.88912010192871</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">8.77561187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04164695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20126724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.435378074646</t>
+    <t xml:space="preserve">9.04164600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20126819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43537902832031</t>
   </si>
   <si>
     <t xml:space="preserve">9.23319244384766</t>
@@ -2525,388 +2525,388 @@
     <t xml:space="preserve">9.176438331604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0345516204834</t>
+    <t xml:space="preserve">9.03455257415771</t>
   </si>
   <si>
     <t xml:space="preserve">9.09485340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20481491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12323093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0842113494873</t>
+    <t xml:space="preserve">9.20481586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12322998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08421230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91040229797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17269039154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01014614105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05817031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78849411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96212100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20963287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43867206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22441005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52364063262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81178569793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3031148910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3474454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6282052993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540632247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5395441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3215866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92261219024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91891765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90414142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1257934570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.051908493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92630672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0592975616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703802108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80070400238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82656383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91522407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9521656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94847297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2218418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553478240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2587852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1627359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.07776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.129487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2107601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.114709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3289737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2772550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0408267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98541450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97433185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46453285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35370635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40911960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55688762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63077068328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38695430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78592777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73051357269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68618392944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53841590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70835018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62707710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56058120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76376247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78223323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60860538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62338161468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61968898773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57535839080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47192001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37217712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56796932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47561359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36478900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1061954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75155258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70352745056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66658401489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59639644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88454341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76632976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91779041290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14313697814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1135835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29829406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24287986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22071552276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12466716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12097263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80327129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96951007843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01753425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03969860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81435298919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82543563842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.91040325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17269039154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01014518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05817031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78849601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99536991119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96212291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20963287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43867206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22440910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52363967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81178665161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3031148910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3474454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6282052993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5395441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3215856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9226131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91891860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90414047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1257944107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519094467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92630767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0592966079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703802108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80070495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82656288146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91522407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95216655731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94847202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2218427658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1553468704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2587852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1627349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0777683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.129487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070646286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2107601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1147108078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3289747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2772560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0408267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98541355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97433090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46453285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35370635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40911865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63077163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78592681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7305154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68618392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53841590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70835018157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6270751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56058120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76376247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78223419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60860538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62338256835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61968898773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57535839080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47192001342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37217807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56796836853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48669815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47561454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36478805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1061954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75155258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70352649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66658592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59639644622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976528167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88454341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76632881164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91779136657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14313793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1135835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29829406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24287986755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22071552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12097263336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80327129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96951007843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03969860076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81435489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82543659210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91040229797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77371883392334</t>
+    <t xml:space="preserve">8.77371788024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.39321517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41907501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5040397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72199726104736</t>
+    <t xml:space="preserve">8.41907596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50404167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72199821472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.89193058013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.013840675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14683246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72312545776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95955467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9447774887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0740747451782</t>
+    <t xml:space="preserve">9.01383972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14683151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72312641143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95955371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94477844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0740737915039</t>
   </si>
   <si>
     <t xml:space="preserve">10.317892074585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4398012161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5136833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.395468711853</t>
+    <t xml:space="preserve">10.4398002624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5136842727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3954696655273</t>
   </si>
   <si>
     <t xml:space="preserve">10.495213508606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5062961578369</t>
+    <t xml:space="preserve">10.5062952041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.6245107650757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7094755172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910047531128</t>
+    <t xml:space="preserve">10.7094774246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910066604614</t>
   </si>
   <si>
     <t xml:space="preserve">10.5801792144775</t>
@@ -2915,49 +2915,49 @@
     <t xml:space="preserve">10.6577577590942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7648906707764</t>
+    <t xml:space="preserve">10.7648897171021</t>
   </si>
   <si>
     <t xml:space="preserve">10.7131700515747</t>
   </si>
   <si>
-    <t xml:space="preserve">10.609733581543</t>
+    <t xml:space="preserve">10.6097326278687</t>
   </si>
   <si>
     <t xml:space="preserve">10.5838737487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6060400009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4065523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.535849571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506258010864</t>
+    <t xml:space="preserve">10.6060390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4065532684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358486175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506267547607</t>
   </si>
   <si>
     <t xml:space="preserve">10.5617084503174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2624797821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176349639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5764856338501</t>
+    <t xml:space="preserve">10.2624778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176359176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5764846801758</t>
   </si>
   <si>
     <t xml:space="preserve">10.2809495925903</t>
   </si>
   <si>
-    <t xml:space="preserve">10.698392868042</t>
+    <t xml:space="preserve">10.6983938217163</t>
   </si>
   <si>
     <t xml:space="preserve">10.7464179992676</t>
@@ -2966,37 +2966,37 @@
     <t xml:space="preserve">10.6392860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6836175918579</t>
+    <t xml:space="preserve">10.6836166381836</t>
   </si>
   <si>
     <t xml:space="preserve">10.7168645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9422121047974</t>
+    <t xml:space="preserve">10.9422101974487</t>
   </si>
   <si>
     <t xml:space="preserve">10.8276901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7205581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6429815292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4102468490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5321550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6947002410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0456476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3929023742676</t>
+    <t xml:space="preserve">10.7205600738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6429805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4102458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5321559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6946992874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0456485748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3929033279419</t>
   </si>
   <si>
     <t xml:space="preserve">11.4778690338135</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">11.6441087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5997791290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.573917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6921319961548</t>
+    <t xml:space="preserve">11.5997772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5739192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6921329498291</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367197036743</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5111179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4815645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4557037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000343322754</t>
+    <t xml:space="preserve">11.5111169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4815635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4557046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000352859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.6995220184326</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">11.4889526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6958274841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7290744781494</t>
+    <t xml:space="preserve">11.6958284378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7290754318237</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435955047607</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1908493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2130146026611</t>
+    <t xml:space="preserve">12.1908502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2130155563354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795114517212</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">12.3866415023804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4900798797607</t>
+    <t xml:space="preserve">12.4900808334351</t>
   </si>
   <si>
     <t xml:space="preserve">12.4383602142334</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">12.4789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755588531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4568328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3607807159424</t>
+    <t xml:space="preserve">12.3755598068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4568319320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3607816696167</t>
   </si>
   <si>
     <t xml:space="preserve">12.4161958694458</t>
@@ -3098,22 +3098,22 @@
     <t xml:space="preserve">12.4125003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4309730529785</t>
+    <t xml:space="preserve">12.4309720993042</t>
   </si>
   <si>
     <t xml:space="preserve">12.5048561096191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6045989990234</t>
+    <t xml:space="preserve">12.6045999526978</t>
   </si>
   <si>
     <t xml:space="preserve">12.6637058258057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6600122451782</t>
+    <t xml:space="preserve">12.5824337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6600131988525</t>
   </si>
   <si>
     <t xml:space="preserve">12.6858711242676</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">12.6378479003906</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5344095230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6119890213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6230697631836</t>
+    <t xml:space="preserve">12.5344114303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.611988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6230688095093</t>
   </si>
   <si>
     <t xml:space="preserve">12.5787391662598</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">12.6489305496216</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265090942383</t>
+    <t xml:space="preserve">12.726508140564</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457492828369</t>
@@ -3149,49 +3149,49 @@
     <t xml:space="preserve">12.3977251052856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3275346755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5602684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4420557022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5972108840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7228126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8336391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631925582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9149122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9592437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0331249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0626802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8816633224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8890514373779</t>
+    <t xml:space="preserve">12.3275327682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5602693557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4420547485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5972118377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7228136062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8336400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740200042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9149112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9592418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0331258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0626783370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.881664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8890533447266</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479040145874</t>
@@ -3200,22 +3200,22 @@
     <t xml:space="preserve">13.2438173294067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1184320449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9773721694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0910034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2007160186768</t>
+    <t xml:space="preserve">13.1184301376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9773731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910053253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2007169723511</t>
   </si>
   <si>
     <t xml:space="preserve">13.1772060394287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2673263549805</t>
+    <t xml:space="preserve">13.2673273086548</t>
   </si>
   <si>
     <t xml:space="preserve">13.2830009460449</t>
@@ -3227,16 +3227,16 @@
     <t xml:space="preserve">13.5180978775024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4985074996948</t>
+    <t xml:space="preserve">13.4985065460205</t>
   </si>
   <si>
     <t xml:space="preserve">13.4632415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4318943023682</t>
+    <t xml:space="preserve">13.4201393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4318933486938</t>
   </si>
   <si>
     <t xml:space="preserve">13.4397325515747</t>
@@ -3248,34 +3248,34 @@
     <t xml:space="preserve">13.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2359790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.232063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0518217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3339366912842</t>
+    <t xml:space="preserve">13.2359809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2320623397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0518207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3339376449585</t>
   </si>
   <si>
     <t xml:space="preserve">13.1262683868408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1732873916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2477359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3731203079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3221826553345</t>
+    <t xml:space="preserve">13.1732883453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2477369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3731212615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3221817016602</t>
   </si>
   <si>
     <t xml:space="preserve">13.4358139038086</t>
@@ -3284,25 +3284,25 @@
     <t xml:space="preserve">13.196798324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9852104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3261013031006</t>
+    <t xml:space="preserve">12.9852094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3261003494263</t>
   </si>
   <si>
     <t xml:space="preserve">13.3300199508667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2634086608887</t>
+    <t xml:space="preserve">13.2634077072144</t>
   </si>
   <si>
     <t xml:space="preserve">13.1654510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7148475646973</t>
+    <t xml:space="preserve">13.1145153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7148485183716</t>
   </si>
   <si>
     <t xml:space="preserve">12.8441514968872</t>
@@ -3314,28 +3314,28 @@
     <t xml:space="preserve">13.1576156616211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1301870346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046346664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0674934387207</t>
+    <t xml:space="preserve">13.1301860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.067494392395</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891290664673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0283117294312</t>
+    <t xml:space="preserve">13.0283126831055</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2947549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
+    <t xml:space="preserve">13.2947568893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456926345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">13.5376892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5416088104248</t>
+    <t xml:space="preserve">13.5416078567505</t>
   </si>
   <si>
     <t xml:space="preserve">13.3770399093628</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">13.4436511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4240570068359</t>
+    <t xml:space="preserve">13.4240579605103</t>
   </si>
   <si>
     <t xml:space="preserve">13.3848762512207</t>
@@ -3374,31 +3374,31 @@
     <t xml:space="preserve">13.5964641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.612135887146</t>
+    <t xml:space="preserve">13.6121368408203</t>
   </si>
   <si>
     <t xml:space="preserve">13.5729532241821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7414398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8393983840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9060087203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8315591812134</t>
+    <t xml:space="preserve">13.7414407730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8393974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9060096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591548919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8315601348877</t>
   </si>
   <si>
     <t xml:space="preserve">13.7923774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8824977874756</t>
+    <t xml:space="preserve">13.8824987411499</t>
   </si>
   <si>
     <t xml:space="preserve">14.0039663314819</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">13.8589878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6748285293579</t>
+    <t xml:space="preserve">13.6748304367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.0901679992676</t>
@@ -3416,19 +3416,19 @@
     <t xml:space="preserve">14.2037982940674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.364447593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.595627784729</t>
+    <t xml:space="preserve">14.3644495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5956268310547</t>
   </si>
   <si>
     <t xml:space="preserve">14.3017559051514</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4349784851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4114675521851</t>
+    <t xml:space="preserve">14.4349765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4114656448364</t>
   </si>
   <si>
     <t xml:space="preserve">14.4271411895752</t>
@@ -3440,61 +3440,61 @@
     <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.564281463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7288475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8072156906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816623687744</t>
+    <t xml:space="preserve">14.5642795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7288484573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816604614258</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6739950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7249307632446</t>
+    <t xml:space="preserve">14.6739931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7249317169189</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739599227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9538793563843</t>
+    <t xml:space="preserve">14.8494462966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739589691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9217472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95387840271</t>
   </si>
   <si>
     <t xml:space="preserve">15.0141286849976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1185579299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0663423538208</t>
+    <t xml:space="preserve">15.1185598373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0663433074951</t>
   </si>
   <si>
     <t xml:space="preserve">15.1346263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310256958008</t>
+    <t xml:space="preserve">15.1426601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310266494751</t>
   </si>
   <si>
     <t xml:space="preserve">15.247091293335</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">15.3234081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2591409683228</t>
+    <t xml:space="preserve">15.2591400146484</t>
   </si>
   <si>
     <t xml:space="preserve">15.3475065231323</t>
@@ -3521,13 +3521,13 @@
     <t xml:space="preserve">15.3836545944214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3716087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4559545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0743780136108</t>
+    <t xml:space="preserve">15.3716077804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4559564590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0743770599365</t>
   </si>
   <si>
     <t xml:space="preserve">14.9418277740479</t>
@@ -3557,34 +3557,34 @@
     <t xml:space="preserve">14.564266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4919681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6124649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498624801636</t>
+    <t xml:space="preserve">14.4919672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6124668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498615264893</t>
   </si>
   <si>
     <t xml:space="preserve">15.0221605300903</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8574800491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297780990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213319778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6767311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731304168701</t>
+    <t xml:space="preserve">14.857479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8614959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6767320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731294631958</t>
   </si>
   <si>
     <t xml:space="preserve">14.9699449539185</t>
@@ -3593,19 +3593,19 @@
     <t xml:space="preserve">14.9016618728638</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0623254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060930252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9659261703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2671737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788091659546</t>
+    <t xml:space="preserve">15.0623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9659271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2671747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788101196289</t>
   </si>
   <si>
     <t xml:space="preserve">14.8333787918091</t>
@@ -3623,19 +3623,19 @@
     <t xml:space="preserve">15.058310508728</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0422449111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8132972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9257621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1466760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0382261276245</t>
+    <t xml:space="preserve">15.0422458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8132963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9257612228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1466751098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0382251739502</t>
   </si>
   <si>
     <t xml:space="preserve">15.1627416610718</t>
@@ -3644,58 +3644,58 @@
     <t xml:space="preserve">14.3754863739014</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4999980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847639083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6727142333984</t>
+    <t xml:space="preserve">14.4999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6727132797241</t>
   </si>
   <si>
     <t xml:space="preserve">14.9940462112427</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7369804382324</t>
+    <t xml:space="preserve">14.7369794845581</t>
   </si>
   <si>
     <t xml:space="preserve">14.9819946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.957896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7450132369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270069122314</t>
+    <t xml:space="preserve">14.9578952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7450122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270078659058</t>
   </si>
   <si>
     <t xml:space="preserve">14.893630027771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562324523926</t>
+    <t xml:space="preserve">14.5562334060669</t>
   </si>
   <si>
     <t xml:space="preserve">14.5963973999023</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0300550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714666366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9256219863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8372583389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7770090103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379505157471</t>
+    <t xml:space="preserve">14.0300559997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.371467590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9256229400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8372592926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7770080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379495620728</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447366714478</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">12.993766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243753433228</t>
+    <t xml:space="preserve">13.6243762969971</t>
   </si>
   <si>
     <t xml:space="preserve">13.4958448410034</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">13.7930746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.174654006958</t>
+    <t xml:space="preserve">14.1746530532837</t>
   </si>
   <si>
     <t xml:space="preserve">14.3875341415405</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">15.0824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0502786636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1667604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3153734207153</t>
+    <t xml:space="preserve">15.0502767562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1667585372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3153743743896</t>
   </si>
   <si>
     <t xml:space="preserve">15.6005544662476</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">16.1789455413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8495826721191</t>
+    <t xml:space="preserve">15.8495836257935</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">16.6850414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9581718444824</t>
+    <t xml:space="preserve">16.9581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074798583984</t>
@@ -3758,16 +3758,16 @@
     <t xml:space="preserve">16.0504150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523567199707</t>
+    <t xml:space="preserve">15.5523548126221</t>
   </si>
   <si>
     <t xml:space="preserve">15.7331008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6166219711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.484073638916</t>
+    <t xml:space="preserve">15.6166210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840726852417</t>
   </si>
   <si>
     <t xml:space="preserve">15.4117727279663</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">15.476037979126</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9980611801147</t>
+    <t xml:space="preserve">14.9980602264404</t>
   </si>
   <si>
     <t xml:space="preserve">14.7932147979736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5080337524414</t>
+    <t xml:space="preserve">14.5080327987671</t>
   </si>
   <si>
     <t xml:space="preserve">14.5441827774048</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">14.4598331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5401668548584</t>
+    <t xml:space="preserve">14.5401678085327</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196681976318</t>
@@ -3806,16 +3806,16 @@
     <t xml:space="preserve">14.4518013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2469530105591</t>
+    <t xml:space="preserve">14.2469520568848</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2670364379883</t>
+    <t xml:space="preserve">14.2268695831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.267035484314</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947374343872</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">14.3112182617188</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4558181762695</t>
+    <t xml:space="preserve">14.4558172225952</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
@@ -3833,31 +3833,31 @@
     <t xml:space="preserve">14.7547550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8230838775635</t>
+    <t xml:space="preserve">14.8230848312378</t>
   </si>
   <si>
     <t xml:space="preserve">14.8828716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5882034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5540399551392</t>
+    <t xml:space="preserve">14.5882043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5540390014648</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2764539718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643573760986</t>
+    <t xml:space="preserve">14.4430055618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3789472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2764530181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643564224243</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">13.3924493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2344398498535</t>
+    <t xml:space="preserve">13.2344388961792</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3881,28 +3881,28 @@
     <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881788253784</t>
+    <t xml:space="preserve">13.3881797790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3967199325562</t>
+    <t xml:space="preserve">13.5803537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3967208862305</t>
   </si>
   <si>
     <t xml:space="preserve">13.2557926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828479766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2686042785645</t>
+    <t xml:space="preserve">13.1917343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828470230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2686033248901</t>
   </si>
   <si>
     <t xml:space="preserve">13.4266138076782</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038290023804</t>
+    <t xml:space="preserve">13.0038299560547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2942266464233</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">13.1661100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4187641143799</t>
+    <t xml:space="preserve">12.4187631607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596923828125</t>
@@ -3932,31 +3932,31 @@
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568529129028</t>
+    <t xml:space="preserve">12.9568538665771</t>
   </si>
   <si>
     <t xml:space="preserve">12.995288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7774906158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3547058105469</t>
+    <t xml:space="preserve">12.7774896621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3547048568726</t>
   </si>
   <si>
     <t xml:space="preserve">12.4401159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4230337142944</t>
+    <t xml:space="preserve">12.4230346679688</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1625308990479</t>
+    <t xml:space="preserve">12.1838846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1625299453735</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095069885254</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">12.4273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796140670776</t>
+    <t xml:space="preserve">12.1796131134033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333520889282</t>
+    <t xml:space="preserve">12.3333530426025</t>
   </si>
   <si>
     <t xml:space="preserve">12.4571981430054</t>
@@ -3986,13 +3986,13 @@
     <t xml:space="preserve">12.5340690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.640832901001</t>
+    <t xml:space="preserve">12.6408319473267</t>
   </si>
   <si>
     <t xml:space="preserve">12.8458185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141473770142</t>
+    <t xml:space="preserve">12.9141483306885</t>
   </si>
   <si>
     <t xml:space="preserve">13.0508050918579</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618394851685</t>
+    <t xml:space="preserve">13.1618385314941</t>
   </si>
   <si>
     <t xml:space="preserve">12.897066116333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7646780014038</t>
+    <t xml:space="preserve">12.7646789550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.7006206512451</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579151153564</t>
+    <t xml:space="preserve">12.6579141616821</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041751861572</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">12.768949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1703815460205</t>
+    <t xml:space="preserve">13.1703805923462</t>
   </si>
   <si>
     <t xml:space="preserve">12.9696645736694</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">12.704891204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7390556335449</t>
+    <t xml:space="preserve">12.7390546798706</t>
   </si>
   <si>
     <t xml:space="preserve">12.3248119354248</t>
@@ -4094,25 +4094,25 @@
     <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8550510406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7397451400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7909927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0045213699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.158260345459</t>
+    <t xml:space="preserve">11.8550519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.73974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7909936904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0045204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1582593917847</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991876602173</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">12.3632469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5169868469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3376226425171</t>
+    <t xml:space="preserve">12.5169858932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3376235961914</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749973297119</t>
@@ -4133,13 +4133,13 @@
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091617584229</t>
+    <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9739351272583</t>
+    <t xml:space="preserve">12.973934173584</t>
   </si>
   <si>
     <t xml:space="preserve">13.0977811813354</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">13.0251817703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532983779907</t>
+    <t xml:space="preserve">13.153299331665</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">13.8493986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9433517456055</t>
+    <t xml:space="preserve">13.9433507919312</t>
   </si>
   <si>
     <t xml:space="preserve">14.2294778823853</t>
@@ -4172,16 +4172,16 @@
     <t xml:space="preserve">14.5839338302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5156049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7419443130493</t>
+    <t xml:space="preserve">14.515604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741943359375</t>
   </si>
   <si>
     <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5027933120728</t>
+    <t xml:space="preserve">14.5027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600877761841</t>
@@ -4193,16 +4193,16 @@
     <t xml:space="preserve">14.4686298370361</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6266384124756</t>
+    <t xml:space="preserve">14.6266393661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7035083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.699236869812</t>
+    <t xml:space="preserve">14.7035093307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6992378234863</t>
   </si>
   <si>
     <t xml:space="preserve">14.7931909561157</t>
@@ -4214,76 +4214,76 @@
     <t xml:space="preserve">14.7889204025269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7462129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999538421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8444356918335</t>
+    <t xml:space="preserve">14.7462139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8444366455078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2508296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2892646789551</t>
+    <t xml:space="preserve">14.0928201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2508306503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2892637252808</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3490524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3106174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2593717575073</t>
+    <t xml:space="preserve">14.3490533828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3106184005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.259370803833</t>
   </si>
   <si>
     <t xml:space="preserve">14.3618650436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1910419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3277006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504854202271</t>
+    <t xml:space="preserve">14.1910429000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3276996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917589187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504844665527</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6736154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.848708152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9682836532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8358964920044</t>
+    <t xml:space="preserve">14.6736164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615198135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8487071990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9682817459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8358974456787</t>
   </si>
   <si>
     <t xml:space="preserve">15.168999671936</t>
@@ -4292,82 +4292,82 @@
     <t xml:space="preserve">15.2373285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3013877868652</t>
+    <t xml:space="preserve">15.3013868331909</t>
   </si>
   <si>
     <t xml:space="preserve">15.2586803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2971162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270101547241</t>
+    <t xml:space="preserve">15.2971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270092010498</t>
   </si>
   <si>
     <t xml:space="preserve">15.3825263977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2885751724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319948196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166898727417</t>
+    <t xml:space="preserve">15.28857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5021018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416690826416</t>
   </si>
   <si>
     <t xml:space="preserve">15.4679374694824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4636659622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063714981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5618877410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6003246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5875120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6857357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106420516968</t>
+    <t xml:space="preserve">15.4636669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063734054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5618906021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6003255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5875129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473016738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857347488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106449127197</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9804029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223934173584</t>
+    <t xml:space="preserve">15.9804019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266649246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223915100098</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4379,31 +4379,31 @@
     <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0658149719238</t>
+    <t xml:space="preserve">16.0658130645752</t>
   </si>
   <si>
     <t xml:space="preserve">15.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7327117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2031631469727</t>
+    <t xml:space="preserve">15.7327108383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.203161239624</t>
   </si>
   <si>
     <t xml:space="preserve">15.7540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8316249847412</t>
+    <t xml:space="preserve">14.8316259384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450855255127</t>
+    <t xml:space="preserve">15.0451526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4508562088013</t>
   </si>
   <si>
     <t xml:space="preserve">15.4081497192383</t>
@@ -4412,28 +4412,28 @@
     <t xml:space="preserve">15.1092128753662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2501401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4423131942749</t>
+    <t xml:space="preserve">15.2501392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4423151016235</t>
   </si>
   <si>
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985464096069</t>
+    <t xml:space="preserve">15.6985473632812</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6216773986816</t>
+    <t xml:space="preserve">15.621678352356</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437442779541</t>
+    <t xml:space="preserve">15.8437471389771</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
@@ -4445,10 +4445,10 @@
     <t xml:space="preserve">16.1683082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0401916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1384162902832</t>
+    <t xml:space="preserve">16.040189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1384143829346</t>
   </si>
   <si>
     <t xml:space="preserve">16.2836132049561</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">16.3049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3092346191406</t>
+    <t xml:space="preserve">16.3092365264893</t>
   </si>
   <si>
     <t xml:space="preserve">16.3434009552002</t>
@@ -4472,37 +4472,37 @@
     <t xml:space="preserve">16.2323665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.125602722168</t>
+    <t xml:space="preserve">16.1256008148193</t>
   </si>
   <si>
     <t xml:space="preserve">15.8693695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9334278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8053102493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2067451477051</t>
+    <t xml:space="preserve">15.9334297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8053112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2067432403564</t>
   </si>
   <si>
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8907222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889440536499</t>
+    <t xml:space="preserve">15.890721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889430999756</t>
   </si>
   <si>
     <t xml:space="preserve">16.1127910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0316524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.912073135376</t>
+    <t xml:space="preserve">16.0316505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9120721817017</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">16.4688701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596569061279</t>
+    <t xml:space="preserve">16.2596549987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.332426071167</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">16.4188404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5188999176025</t>
+    <t xml:space="preserve">16.5189018249512</t>
   </si>
   <si>
     <t xml:space="preserve">16.6462478637695</t>
@@ -4544,7 +4544,7 @@
     <t xml:space="preserve">16.9236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1010646820068</t>
+    <t xml:space="preserve">17.1010627746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2193164825439</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">16.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7963390350342</t>
+    <t xml:space="preserve">16.7963371276855</t>
   </si>
   <si>
     <t xml:space="preserve">16.6689910888672</t>
@@ -4574,7 +4574,7 @@
     <t xml:space="preserve">16.6280574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235660552979</t>
+    <t xml:space="preserve">16.7235679626465</t>
   </si>
   <si>
     <t xml:space="preserve">16.6917304992676</t>
@@ -4586,10 +4586,10 @@
     <t xml:space="preserve">16.9373321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4330787658691</t>
+    <t xml:space="preserve">17.5103969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4330806732178</t>
   </si>
   <si>
     <t xml:space="preserve">17.2056732177734</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">17.1783828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920261383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0692272186279</t>
+    <t xml:space="preserve">17.1920280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">17.2829914093018</t>
@@ -4622,13 +4622,13 @@
     <t xml:space="preserve">17.3648567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3739547729492</t>
+    <t xml:space="preserve">17.3739528656006</t>
   </si>
   <si>
     <t xml:space="preserve">17.3330192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3284702301025</t>
+    <t xml:space="preserve">17.3284721374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.5149459838867</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">17.5240421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6286487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4057922363281</t>
+    <t xml:space="preserve">17.6286506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4057903289795</t>
   </si>
   <si>
     <t xml:space="preserve">17.037389755249</t>
@@ -4655,16 +4655,16 @@
     <t xml:space="preserve">17.091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7190170288086</t>
+    <t xml:space="preserve">16.9737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7190189361572</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8736553192139</t>
+    <t xml:space="preserve">16.8736572265625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7417602539062</t>
@@ -4673,13 +4673,13 @@
     <t xml:space="preserve">16.7645015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281764984131</t>
+    <t xml:space="preserve">16.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">16.8418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9282341003418</t>
+    <t xml:space="preserve">16.9282360076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.0737762451172</t>
@@ -4688,7 +4688,7 @@
     <t xml:space="preserve">17.442174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4012432098389</t>
+    <t xml:space="preserve">17.4012413024902</t>
   </si>
   <si>
     <t xml:space="preserve">17.292085647583</t>
@@ -4697,13 +4697,13 @@
     <t xml:space="preserve">17.3011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6013603210449</t>
+    <t xml:space="preserve">17.6013622283936</t>
   </si>
   <si>
     <t xml:space="preserve">17.7150650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7332572937012</t>
+    <t xml:space="preserve">17.7332592010498</t>
   </si>
   <si>
     <t xml:space="preserve">18.0197906494141</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">18.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1926212310791</t>
+    <t xml:space="preserve">18.1926231384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.0470809936523</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">17.7878360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059093475342</t>
+    <t xml:space="preserve">17.6059074401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6832294464111</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">16.8918476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3239231109619</t>
+    <t xml:space="preserve">17.3239250183105</t>
   </si>
   <si>
     <t xml:space="preserve">17.4876575469971</t>
@@ -4796,16 +4796,16 @@
     <t xml:space="preserve">17.0510349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2966327667236</t>
+    <t xml:space="preserve">17.2966346740723</t>
   </si>
   <si>
     <t xml:space="preserve">17.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1465454101562</t>
+    <t xml:space="preserve">17.1238040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1465473175049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2511539459229</t>
@@ -4823,16 +4823,16 @@
     <t xml:space="preserve">17.8787994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8151245117188</t>
+    <t xml:space="preserve">17.8151226043701</t>
   </si>
   <si>
     <t xml:space="preserve">17.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4922046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.314826965332</t>
+    <t xml:space="preserve">17.4922065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3148288726807</t>
   </si>
   <si>
     <t xml:space="preserve">17.187479019165</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">17.242057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1419982910156</t>
+    <t xml:space="preserve">17.141996383667</t>
   </si>
   <si>
     <t xml:space="preserve">17.2284126281738</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">17.4103393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.414888381958</t>
+    <t xml:space="preserve">17.4148864746094</t>
   </si>
   <si>
     <t xml:space="preserve">17.496753692627</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">17.9561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0061454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.901538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9515705108643</t>
+    <t xml:space="preserve">18.0061473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9015407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9515686035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.9379234313965</t>
@@ -4934,7 +4934,7 @@
     <t xml:space="preserve">18.6201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5473785400391</t>
+    <t xml:space="preserve">18.5473766326904</t>
   </si>
   <si>
     <t xml:space="preserve">18.5655708312988</t>
@@ -4949,10 +4949,10 @@
     <t xml:space="preserve">18.6656303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6929187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8202686309814</t>
+    <t xml:space="preserve">18.6929168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8202667236328</t>
   </si>
   <si>
     <t xml:space="preserve">18.629243850708</t>
@@ -4964,13 +4964,13 @@
     <t xml:space="preserve">18.7565937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6838245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5564746856689</t>
+    <t xml:space="preserve">18.6838226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5564727783203</t>
   </si>
   <si>
     <t xml:space="preserve">18.8384590148926</t>
@@ -4991,25 +4991,25 @@
     <t xml:space="preserve">19.5024909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.139232635498</t>
+    <t xml:space="preserve">20.1392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9118232727051</t>
+    <t xml:space="preserve">19.9118251800537</t>
   </si>
   <si>
     <t xml:space="preserve">19.9664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0027885437012</t>
+    <t xml:space="preserve">20.0027866363525</t>
   </si>
   <si>
     <t xml:space="preserve">20.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1574230194092</t>
+    <t xml:space="preserve">20.1574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">20.0755577087402</t>
@@ -5018,16 +5018,16 @@
     <t xml:space="preserve">20.2120018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2847728729248</t>
+    <t xml:space="preserve">20.2847709655762</t>
   </si>
   <si>
     <t xml:space="preserve">20.393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5940456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6122398376465</t>
+    <t xml:space="preserve">20.5940475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6122417449951</t>
   </si>
   <si>
     <t xml:space="preserve">20.6759147644043</t>
@@ -5048,10 +5048,10 @@
     <t xml:space="preserve">21.1034412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3399429321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127178192139</t>
+    <t xml:space="preserve">21.3399448394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127159118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.5309677124023</t>
@@ -5066,10 +5066,10 @@
     <t xml:space="preserve">20.8669376373291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0306701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7304916381836</t>
+    <t xml:space="preserve">21.0306720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7304935455322</t>
   </si>
   <si>
     <t xml:space="preserve">20.7577800750732</t>
@@ -5078,13 +5078,13 @@
     <t xml:space="preserve">20.6031436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7032051086426</t>
+    <t xml:space="preserve">20.7032032012939</t>
   </si>
   <si>
     <t xml:space="preserve">20.3393516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4394111633301</t>
+    <t xml:space="preserve">20.4394092559814</t>
   </si>
   <si>
     <t xml:space="preserve">20.4939880371094</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">20.6213359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7123012542725</t>
+    <t xml:space="preserve">20.7122993469238</t>
   </si>
   <si>
     <t xml:space="preserve">21.003381729126</t>
@@ -5117,13 +5117,13 @@
     <t xml:space="preserve">21.2307891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7765674591064</t>
+    <t xml:space="preserve">21.7765693664551</t>
   </si>
   <si>
     <t xml:space="preserve">21.7401809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9039154052734</t>
+    <t xml:space="preserve">21.9039173126221</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949977874756</t>
@@ -71714,7 +71714,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6910648148</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>2600105</v>
@@ -71735,6 +71735,32 @@
         <v>2025</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.691087963</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>2053685</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>33.7000007629395</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>33.2599983215332</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>33.6199989318848</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>33.2599983215332</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="2026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="2027">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21390056610107</t>
+    <t xml:space="preserve">9.21389961242676</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">9.31058883666992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13427352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11721134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02052307128906</t>
+    <t xml:space="preserve">9.13427448272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11721229553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02052211761475</t>
   </si>
   <si>
     <t xml:space="preserve">8.76458072662354</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">8.95795822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75889301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120323181152</t>
+    <t xml:space="preserve">8.75889205932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120227813721</t>
   </si>
   <si>
     <t xml:space="preserve">8.63376617431641</t>
@@ -80,49 +80,49 @@
     <t xml:space="preserve">8.29251003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44607543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48588943481445</t>
+    <t xml:space="preserve">8.44607639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48588848114014</t>
   </si>
   <si>
     <t xml:space="preserve">8.30957317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04794311523438</t>
+    <t xml:space="preserve">8.04794406890869</t>
   </si>
   <si>
     <t xml:space="preserve">7.93987941741943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61568737030029</t>
+    <t xml:space="preserve">7.61568641662598</t>
   </si>
   <si>
     <t xml:space="preserve">7.84319067001343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70668840408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41662168502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23461675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1549916267395</t>
+    <t xml:space="preserve">7.70668745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23461818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15499210357666</t>
   </si>
   <si>
     <t xml:space="preserve">6.96161365509033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74548435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47248077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81373500823975</t>
+    <t xml:space="preserve">6.74548482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47248125076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81373453140259</t>
   </si>
   <si>
     <t xml:space="preserve">6.23360157012939</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">6.34166526794434</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59760761260986</t>
+    <t xml:space="preserve">6.59760808944702</t>
   </si>
   <si>
     <t xml:space="preserve">6.62035799026489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77392292022705</t>
+    <t xml:space="preserve">6.77392339706421</t>
   </si>
   <si>
     <t xml:space="preserve">6.72842216491699</t>
@@ -146,88 +146,88 @@
     <t xml:space="preserve">6.6601710319519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89904975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8933629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95592451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28580665588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643377304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4507474899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24599170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31993246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249444961548</t>
+    <t xml:space="preserve">6.89905023574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89336156845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95592641830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26305532455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28580617904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643329620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45074605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680673599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24599361419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3199315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249540328979</t>
   </si>
   <si>
     <t xml:space="preserve">7.37112045288086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90575361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750247955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79200267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731695175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89437913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67256259918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587289810181</t>
+    <t xml:space="preserve">7.90575265884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79200172424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437866210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587337493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.53037261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3654317855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42799663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48487091064453</t>
+    <t xml:space="preserve">7.36543226242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42799520492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48487234115601</t>
   </si>
   <si>
     <t xml:space="preserve">7.41093349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30287027359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755504608154</t>
+    <t xml:space="preserve">7.30286836624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755361557007</t>
   </si>
   <si>
     <t xml:space="preserve">6.98436403274536</t>
@@ -236,106 +236,106 @@
     <t xml:space="preserve">7.00711441040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85354900360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05261421203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13792753219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067934036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43368291854858</t>
+    <t xml:space="preserve">6.85354995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05261468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13792896270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43368339538574</t>
   </si>
   <si>
     <t xml:space="preserve">7.4962477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47918462753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743719100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862375259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75219011306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83181619644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456705093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80337619781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77493953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018613815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387035369873</t>
+    <t xml:space="preserve">7.4791841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862470626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218915939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83181476593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456562042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8033766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77493906021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018661499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387083053589</t>
   </si>
   <si>
     <t xml:space="preserve">7.35405683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53605985641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105230331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05830240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517763137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25167942047119</t>
+    <t xml:space="preserve">7.53606033325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1663670539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05830192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517906188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25167989730835</t>
   </si>
   <si>
     <t xml:space="preserve">7.31798839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73994874954224</t>
+    <t xml:space="preserve">7.73994827270508</t>
   </si>
   <si>
     <t xml:space="preserve">7.8484525680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90873336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94490003585815</t>
+    <t xml:space="preserve">7.90873146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94490051269531</t>
   </si>
   <si>
     <t xml:space="preserve">7.85447931289673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81228399276733</t>
+    <t xml:space="preserve">7.81228351593018</t>
   </si>
   <si>
     <t xml:space="preserve">7.76406049728394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54705333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53499555587769</t>
+    <t xml:space="preserve">7.54705142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53499603271484</t>
   </si>
   <si>
     <t xml:space="preserve">7.66158437728882</t>
@@ -344,37 +344,37 @@
     <t xml:space="preserve">7.80625629425049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77008819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42046546936035</t>
+    <t xml:space="preserve">7.77008867263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42046403884888</t>
   </si>
   <si>
     <t xml:space="preserve">7.17934465408325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97439289093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850511550903</t>
+    <t xml:space="preserve">6.97439193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850463867188</t>
   </si>
   <si>
     <t xml:space="preserve">6.92014122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19140195846558</t>
+    <t xml:space="preserve">7.19140100479126</t>
   </si>
   <si>
     <t xml:space="preserve">7.40840864181519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54102468490601</t>
+    <t xml:space="preserve">7.54102373123169</t>
   </si>
   <si>
     <t xml:space="preserve">7.58322095870972</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58257389068604</t>
+    <t xml:space="preserve">6.58257246017456</t>
   </si>
   <si>
     <t xml:space="preserve">6.02498292922974</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">6.11841726303101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26309013366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35953617095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187284469604</t>
+    <t xml:space="preserve">6.26308917999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35953712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43187379837036</t>
   </si>
   <si>
     <t xml:space="preserve">6.25103282928467</t>
@@ -398,139 +398,139 @@
     <t xml:space="preserve">6.1304726600647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91647863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9285364151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967609405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7634129524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69710397720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8719162940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560731887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177684783936</t>
+    <t xml:space="preserve">5.91647911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92853546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790197372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76341247558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69710445404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87191724777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560970306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8417763710022</t>
   </si>
   <si>
     <t xml:space="preserve">6.75738430023193</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84780359268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77546882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73327350616455</t>
+    <t xml:space="preserve">6.8478045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77546834945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73327302932739</t>
   </si>
   <si>
     <t xml:space="preserve">6.68504858016968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81163644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62476921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10097980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07084035873413</t>
+    <t xml:space="preserve">6.81163692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10098075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07084083557129</t>
   </si>
   <si>
     <t xml:space="preserve">6.7935528755188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06481218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948362350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289575576782</t>
+    <t xml:space="preserve">7.06481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948553085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387617111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289527893066</t>
   </si>
   <si>
     <t xml:space="preserve">6.89000129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90808582305908</t>
+    <t xml:space="preserve">6.90808439254761</t>
   </si>
   <si>
     <t xml:space="preserve">6.7393012046814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04070138931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01658916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81766510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74532794952393</t>
+    <t xml:space="preserve">7.04070043563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01658964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74532842636108</t>
   </si>
   <si>
     <t xml:space="preserve">6.61271381378174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78149604797363</t>
+    <t xml:space="preserve">6.78149700164795</t>
   </si>
   <si>
     <t xml:space="preserve">6.94425296783447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99247741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93822526931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88397312164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042154312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770807266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72724533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79957914352417</t>
+    <t xml:space="preserve">6.99247789382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93822479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88397216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523195266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770711898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313310623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079786300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72724390029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79958057403564</t>
   </si>
   <si>
     <t xml:space="preserve">6.75135707855225</t>
@@ -542,28 +542,28 @@
     <t xml:space="preserve">6.56448936462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57654571533203</t>
+    <t xml:space="preserve">6.57654476165771</t>
   </si>
   <si>
     <t xml:space="preserve">6.60668563842773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54640436172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51626586914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49817991256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76944065093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85986089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383224487305</t>
+    <t xml:space="preserve">6.54640340805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51626491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49818086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7694411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85985994338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383367538452</t>
   </si>
   <si>
     <t xml:space="preserve">7.18537378311157</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">7.19742822647095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28784847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26976442337036</t>
+    <t xml:space="preserve">7.28784894943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26976490020752</t>
   </si>
   <si>
     <t xml:space="preserve">7.33004426956177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3119592666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317750930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09495306015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98644924163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574914932251</t>
+    <t xml:space="preserve">7.31196117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317655563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0949535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98644876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574867248535</t>
   </si>
   <si>
     <t xml:space="preserve">7.0889253616333</t>
@@ -611,55 +611,55 @@
     <t xml:space="preserve">6.8779444694519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02261686325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82369136810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73391962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68031597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45125293731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47536468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41508293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33069229125977</t>
+    <t xml:space="preserve">7.02261638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8236927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854808807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35415649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73392009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6803150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45125102996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47536373138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41508388519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33069133758545</t>
   </si>
   <si>
     <t xml:space="preserve">8.54167079925537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55975532531738</t>
+    <t xml:space="preserve">8.5597562789917</t>
   </si>
   <si>
     <t xml:space="preserve">8.6381196975708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58386707305908</t>
+    <t xml:space="preserve">8.5838680267334</t>
   </si>
   <si>
     <t xml:space="preserve">8.59592437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66223239898682</t>
+    <t xml:space="preserve">8.6622314453125</t>
   </si>
   <si>
     <t xml:space="preserve">8.6682596206665</t>
@@ -668,19 +668,19 @@
     <t xml:space="preserve">8.5537281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50550270080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51153373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71045589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75265216827393</t>
+    <t xml:space="preserve">8.5055046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51153182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71045684814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75265312194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.69840049743652</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">8.71648406982422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52358818054199</t>
+    <t xml:space="preserve">8.52358722686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.48742008209229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38494205474854</t>
+    <t xml:space="preserve">8.38494491577148</t>
   </si>
   <si>
     <t xml:space="preserve">8.25835704803467</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">8.23424434661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16793537139893</t>
+    <t xml:space="preserve">8.16793632507324</t>
   </si>
   <si>
     <t xml:space="preserve">8.27041244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26438331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58989524841309</t>
+    <t xml:space="preserve">8.26438426971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5898962020874</t>
   </si>
   <si>
     <t xml:space="preserve">9.2951717376709</t>
@@ -722,40 +722,40 @@
     <t xml:space="preserve">9.38559150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4217586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28311538696289</t>
+    <t xml:space="preserve">9.42175960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28311634063721</t>
   </si>
   <si>
     <t xml:space="preserve">8.98774337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88526821136475</t>
+    <t xml:space="preserve">8.88526725769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00582695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993965148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81895923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77073669433594</t>
+    <t xml:space="preserve">9.00582790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993869781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81896018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77073764801025</t>
   </si>
   <si>
     <t xml:space="preserve">8.67428779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74059581756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90335178375244</t>
+    <t xml:space="preserve">8.7405948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90335273742676</t>
   </si>
   <si>
     <t xml:space="preserve">9.04802417755127</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">8.87923908233643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90937995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95760154724121</t>
+    <t xml:space="preserve">8.90938091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95760250091553</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81293201446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74662303924561</t>
+    <t xml:space="preserve">8.81293106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.65620422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49947643280029</t>
+    <t xml:space="preserve">8.49947547912598</t>
   </si>
   <si>
     <t xml:space="preserve">8.14985179901123</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">8.27644062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54769802093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46330833435059</t>
+    <t xml:space="preserve">8.54769897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46330738067627</t>
   </si>
   <si>
     <t xml:space="preserve">8.56578350067139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78882122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80087661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.794846534729</t>
+    <t xml:space="preserve">8.78882026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484748840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.78279209136963</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">8.86718368530273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98171424865723</t>
+    <t xml:space="preserve">8.98171520233154</t>
   </si>
   <si>
     <t xml:space="preserve">8.80690383911133</t>
@@ -824,34 +824,34 @@
     <t xml:space="preserve">8.6320915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6079797744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46933555603027</t>
+    <t xml:space="preserve">8.60798072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46933650970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93349170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75868034362793</t>
+    <t xml:space="preserve">8.93349075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75867938995361</t>
   </si>
   <si>
     <t xml:space="preserve">8.87321186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04199600219727</t>
+    <t xml:space="preserve">9.04199504852295</t>
   </si>
   <si>
     <t xml:space="preserve">9.19269561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21077919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24092102050781</t>
+    <t xml:space="preserve">9.21078014373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2409200668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.21680736541748</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">9.03596687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07213592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12035942077637</t>
+    <t xml:space="preserve">9.07213497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12036037445068</t>
   </si>
   <si>
     <t xml:space="preserve">9.30493068695068</t>
@@ -878,49 +878,49 @@
     <t xml:space="preserve">9.33675289154053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.184006690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15854740142822</t>
+    <t xml:space="preserve">9.18400573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15854835510254</t>
   </si>
   <si>
     <t xml:space="preserve">9.13308906555176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94851684570312</t>
+    <t xml:space="preserve">8.94851779937744</t>
   </si>
   <si>
     <t xml:space="preserve">8.83395671844482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03762054443359</t>
+    <t xml:space="preserve">8.94215393066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03762149810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.81486320495605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73848819732666</t>
+    <t xml:space="preserve">8.75758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73848915100098</t>
   </si>
   <si>
     <t xml:space="preserve">8.89123725891113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95488166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0503511428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22855663299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23492050170898</t>
+    <t xml:space="preserve">8.95488262176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05035018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22855567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2349214553833</t>
   </si>
   <si>
     <t xml:space="preserve">9.1712760925293</t>
@@ -935,25 +935,25 @@
     <t xml:space="preserve">9.19036960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3494815826416</t>
+    <t xml:space="preserve">9.34948348999023</t>
   </si>
   <si>
     <t xml:space="preserve">9.25401401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22219085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24765014648438</t>
+    <t xml:space="preserve">9.22219276428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24764919281006</t>
   </si>
   <si>
     <t xml:space="preserve">9.29220294952393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33038902282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38130474090576</t>
+    <t xml:space="preserve">9.33038711547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38130569458008</t>
   </si>
   <si>
     <t xml:space="preserve">9.57860469818115</t>
@@ -965,49 +965,49 @@
     <t xml:space="preserve">9.54041862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64861392974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79499816894531</t>
+    <t xml:space="preserve">9.64861488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79499912261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.85864353179932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71862602233887</t>
+    <t xml:space="preserve">9.71862506866455</t>
   </si>
   <si>
     <t xml:space="preserve">9.68680286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56587600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52768993377686</t>
+    <t xml:space="preserve">9.56587505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52769088745117</t>
   </si>
   <si>
     <t xml:space="preserve">9.75681209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77590465545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750379562378</t>
+    <t xml:space="preserve">9.77590656280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750389099121</t>
   </si>
   <si>
     <t xml:space="preserve">10.0877676010132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1386833190918</t>
+    <t xml:space="preserve">10.1386823654175</t>
   </si>
   <si>
     <t xml:space="preserve">10.2341508865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1959657669067</t>
+    <t xml:space="preserve">10.1959667205811</t>
   </si>
   <si>
     <t xml:space="preserve">10.062310218811</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">9.82682132720947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86500930786133</t>
+    <t xml:space="preserve">9.86500835418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.90319633483887</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">9.87137317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78227043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71225929260254</t>
+    <t xml:space="preserve">9.78226947784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71226024627686</t>
   </si>
   <si>
     <t xml:space="preserve">9.69953060150146</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">9.6804370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69316673278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134357452393</t>
+    <t xml:space="preserve">9.6931676864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134452819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.53405380249023</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">9.57224082946777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61679172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67407417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62952041625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59769916534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89046764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9477481842041</t>
+    <t xml:space="preserve">9.61679267883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67407321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62952136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59769821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89046669006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94774627685547</t>
   </si>
   <si>
     <t xml:space="preserve">9.75044727325439</t>
@@ -1082,34 +1082,34 @@
     <t xml:space="preserve">9.89683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91592597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8777379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0304880142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1323204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93501853942871</t>
+    <t xml:space="preserve">9.91592502593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87773895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0304870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1323194503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93501949310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.84591579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85227966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83318710327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72498798370361</t>
+    <t xml:space="preserve">9.85228061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72498893737793</t>
   </si>
   <si>
     <t xml:space="preserve">9.99866390228271</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">9.96047687530518</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0177564620972</t>
+    <t xml:space="preserve">10.0177574157715</t>
   </si>
   <si>
     <t xml:space="preserve">9.9541130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1259536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0241222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94138431549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8841028213501</t>
+    <t xml:space="preserve">10.1259546279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0241212844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94138240814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88410186767578</t>
   </si>
   <si>
     <t xml:space="preserve">10.0368518829346</t>
@@ -1142,58 +1142,58 @@
     <t xml:space="preserve">9.78863430023193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58496952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61042785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66770935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7440824508667</t>
+    <t xml:space="preserve">9.63588619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58497047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61043071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66770839691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74408340454102</t>
   </si>
   <si>
     <t xml:space="preserve">9.73135280609131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8077278137207</t>
+    <t xml:space="preserve">9.80772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.73771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55951309204102</t>
+    <t xml:space="preserve">9.70589637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5595121383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.47677421569824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97320652008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97957134246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0814027786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0559453964233</t>
+    <t xml:space="preserve">9.97320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97957038879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0814018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.055944442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.291431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3041610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2023296356201</t>
+    <t xml:space="preserve">10.3041620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2023286819458</t>
   </si>
   <si>
     <t xml:space="preserve">10.310525894165</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">10.1641416549683</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1482305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9922981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76954078674316</t>
+    <t xml:space="preserve">10.148229598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99230003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7695426940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.86819076538086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81727600097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77908706665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8140926361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80454540252686</t>
+    <t xml:space="preserve">9.81727409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77908897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80454635620117</t>
   </si>
   <si>
     <t xml:space="preserve">9.36857604980469</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">9.6517972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85546207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74726390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0082111358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98593521118164</t>
+    <t xml:space="preserve">9.85546112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74726486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0082120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98593330383301</t>
   </si>
   <si>
     <t xml:space="preserve">9.92865467071533</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">9.94456577301025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97002410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04958152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1609582901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3137083053589</t>
+    <t xml:space="preserve">9.9700231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.049578666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1609592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3137073516846</t>
   </si>
   <si>
     <t xml:space="preserve">10.2946128845215</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">10.3455305099487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346332550049</t>
+    <t xml:space="preserve">10.4346342086792</t>
   </si>
   <si>
     <t xml:space="preserve">10.530101776123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.765588760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8546934127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6319341659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178554534912</t>
+    <t xml:space="preserve">10.6382970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7655897140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8546924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6319351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178535461426</t>
   </si>
   <si>
     <t xml:space="preserve">10.5841989517212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6542091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.708309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7051267623901</t>
+    <t xml:space="preserve">10.6542100906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7083082199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
     <t xml:space="preserve">10.6796684265137</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">10.5269193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5396490097046</t>
+    <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
     <t xml:space="preserve">10.4409980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5014600753784</t>
+    <t xml:space="preserve">10.5014610290527</t>
   </si>
   <si>
     <t xml:space="preserve">10.5078248977661</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">10.2977962493896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3328008651733</t>
+    <t xml:space="preserve">10.3328018188477</t>
   </si>
   <si>
     <t xml:space="preserve">10.2596101760864</t>
@@ -1337,49 +1337,49 @@
     <t xml:space="preserve">10.2864847183228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2528896331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319513320923</t>
+    <t xml:space="preserve">10.252890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1319522857666</t>
   </si>
   <si>
     <t xml:space="preserve">10.0143737792969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99421691894531</t>
+    <t xml:space="preserve">9.994215965271</t>
   </si>
   <si>
     <t xml:space="preserve">9.83968448638916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49702453613281</t>
+    <t xml:space="preserve">9.49702644348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.55413627624512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77585601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88335609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86991882324219</t>
+    <t xml:space="preserve">9.77585411071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88335800170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8699197769165</t>
   </si>
   <si>
     <t xml:space="preserve">9.65491771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67843246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52054119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79937076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75233936309814</t>
+    <t xml:space="preserve">9.67843151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52054214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79937267303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75234127044678</t>
   </si>
   <si>
     <t xml:space="preserve">9.78257465362549</t>
@@ -1391,136 +1391,136 @@
     <t xml:space="preserve">9.80609035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76241874694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82960510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69858932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76913642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60116767883301</t>
+    <t xml:space="preserve">9.76241683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82960605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69858837127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76913547515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60116577148438</t>
   </si>
   <si>
     <t xml:space="preserve">9.61796474456787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52390098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51718235015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61124610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59108924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80945014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77249717712402</t>
+    <t xml:space="preserve">9.52390003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51718139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61124515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59108829498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80945110321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77249526977539</t>
   </si>
   <si>
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65155696868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163444519043</t>
+    <t xml:space="preserve">9.65155792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163730621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84976291656494</t>
+    <t xml:space="preserve">9.84976100921631</t>
   </si>
   <si>
     <t xml:space="preserve">9.85648155212402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8161678314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74898147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89007663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90351390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92366886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0479669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2125787734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1117963790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9539041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0378894805908</t>
+    <t xml:space="preserve">9.81616973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74898052215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89007568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9035120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92366790771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070217132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2125768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.111795425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95390510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0378885269165</t>
   </si>
   <si>
     <t xml:space="preserve">10.0009355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0681238174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916395187378</t>
+    <t xml:space="preserve">10.0681228637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916404724121</t>
   </si>
   <si>
     <t xml:space="preserve">10.0748424530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8665599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71202659606934</t>
+    <t xml:space="preserve">9.86655902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71202754974365</t>
   </si>
   <si>
     <t xml:space="preserve">9.7321834564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85312175750732</t>
+    <t xml:space="preserve">9.85312080383301</t>
   </si>
   <si>
     <t xml:space="preserve">9.92702865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98077964782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92031002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63812255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76577758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93710803985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96062183380127</t>
+    <t xml:space="preserve">9.98077774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92030906677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63812160491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76577663421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93710613250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9606237411499</t>
   </si>
   <si>
     <t xml:space="preserve">9.94382572174072</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">10.1621866226196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1017198562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0882797241211</t>
+    <t xml:space="preserve">10.1017179489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0882806777954</t>
   </si>
   <si>
     <t xml:space="preserve">10.1554679870605</t>
@@ -1550,34 +1550,34 @@
     <t xml:space="preserve">10.4141426086426</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4309387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3704700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9975757598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88671684265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96734046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93038940429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70866775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69187164306641</t>
+    <t xml:space="preserve">10.4309396743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3704690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99757671356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88671779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96734142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93038749694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70866870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69186973571777</t>
   </si>
   <si>
     <t xml:space="preserve">9.59444904327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50038528442383</t>
+    <t xml:space="preserve">9.50038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">9.61460494995117</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">9.56421375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4130392074585</t>
+    <t xml:space="preserve">9.41304111480713</t>
   </si>
   <si>
     <t xml:space="preserve">9.43991565704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40968036651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28874397277832</t>
+    <t xml:space="preserve">9.40968132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.288743019104</t>
   </si>
   <si>
     <t xml:space="preserve">9.2383508682251</t>
@@ -1604,25 +1604,25 @@
     <t xml:space="preserve">9.43655586242676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33241558074951</t>
+    <t xml:space="preserve">9.3324146270752</t>
   </si>
   <si>
     <t xml:space="preserve">9.53397941589355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62468242645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65827560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63476085662842</t>
+    <t xml:space="preserve">9.66499710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62468338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65827655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6347599029541</t>
   </si>
   <si>
     <t xml:space="preserve">9.57429218292236</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">9.51382255554199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59780693054199</t>
+    <t xml:space="preserve">9.59780788421631</t>
   </si>
   <si>
     <t xml:space="preserve">9.5574951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57765197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8195276260376</t>
+    <t xml:space="preserve">9.57765102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81952857971191</t>
   </si>
   <si>
     <t xml:space="preserve">9.87663745880127</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">9.9135913848877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0042943954468</t>
+    <t xml:space="preserve">10.0042953491211</t>
   </si>
   <si>
     <t xml:space="preserve">10.0849208831787</t>
@@ -1661,34 +1661,34 @@
     <t xml:space="preserve">9.97406101226807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57093238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6448392868042</t>
+    <t xml:space="preserve">9.57093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64483833312988</t>
   </si>
   <si>
     <t xml:space="preserve">9.68515110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74562072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89679336547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85984134674072</t>
+    <t xml:space="preserve">9.74562168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89679431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85984039306641</t>
   </si>
   <si>
     <t xml:space="preserve">9.95054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0210914611816</t>
+    <t xml:space="preserve">10.0210933685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.0446081161499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0647630691528</t>
+    <t xml:space="preserve">10.0647640228271</t>
   </si>
   <si>
     <t xml:space="preserve">10.2327346801758</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">10.3267974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3435935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898435592651</t>
+    <t xml:space="preserve">10.3435964584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898426055908</t>
   </si>
   <si>
     <t xml:space="preserve">10.3335161209106</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2764053344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1991395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2461738586426</t>
+    <t xml:space="preserve">10.3771867752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.276406288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1991405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2461719512939</t>
   </si>
   <si>
     <t xml:space="preserve">10.2932024002075</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0714817047119</t>
+    <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
     <t xml:space="preserve">10.1285934448242</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">10.2058591842651</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2831258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1890621185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2293758392334</t>
+    <t xml:space="preserve">10.2831249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1890630722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2293748855591</t>
   </si>
   <si>
     <t xml:space="preserve">10.2260150909424</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">10.2730474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805465698242</t>
+    <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275798797607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4342985153198</t>
+    <t xml:space="preserve">10.4342975616455</t>
   </si>
   <si>
     <t xml:space="preserve">10.5451583862305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6089859008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6728143692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660976409912</t>
+    <t xml:space="preserve">10.6089868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672815322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
     <t xml:space="preserve">10.7400045394897</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">10.565315246582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6157064437866</t>
+    <t xml:space="preserve">10.6157054901123</t>
   </si>
   <si>
     <t xml:space="preserve">10.5921907424927</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">10.6224250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7534408569336</t>
+    <t xml:space="preserve">10.7534418106079</t>
   </si>
   <si>
     <t xml:space="preserve">10.9785203933716</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">11.0725841522217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591468811035</t>
+    <t xml:space="preserve">11.0591459274292</t>
   </si>
   <si>
     <t xml:space="preserve">11.0322713851929</t>
@@ -1808,16 +1808,16 @@
     <t xml:space="preserve">11.0692253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.985239982605</t>
+    <t xml:space="preserve">10.9852409362793</t>
   </si>
   <si>
     <t xml:space="preserve">10.9718017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0087556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0860233306885</t>
+    <t xml:space="preserve">11.0087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0860223770142</t>
   </si>
   <si>
     <t xml:space="preserve">11.2036008834839</t>
@@ -1826,31 +1826,31 @@
     <t xml:space="preserve">11.1767263412476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2304763793945</t>
+    <t xml:space="preserve">11.2304754257202</t>
   </si>
   <si>
     <t xml:space="preserve">11.2237577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1733665466309</t>
+    <t xml:space="preserve">11.1733655929565</t>
   </si>
   <si>
     <t xml:space="preserve">11.2170381546021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2002401351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2271165847778</t>
+    <t xml:space="preserve">11.2002410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2271156311035</t>
   </si>
   <si>
     <t xml:space="preserve">11.297664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3581342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4219617843628</t>
+    <t xml:space="preserve">11.35813331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4219608306885</t>
   </si>
   <si>
     <t xml:space="preserve">11.5563383102417</t>
@@ -1862,46 +1862,46 @@
     <t xml:space="preserve">11.4286804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622745513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5832138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5529775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6235256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6201667785645</t>
+    <t xml:space="preserve">11.4622735977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.583212852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5529766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6235246658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6201677322388</t>
   </si>
   <si>
     <t xml:space="preserve">11.6302442550659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.526104927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4824323654175</t>
+    <t xml:space="preserve">11.5261039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4824314117432</t>
   </si>
   <si>
     <t xml:space="preserve">11.4689931869507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.324538230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648519515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4152431488037</t>
+    <t xml:space="preserve">11.3245410919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.415244102478</t>
   </si>
   <si>
     <t xml:space="preserve">11.5093050003052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4253215789795</t>
+    <t xml:space="preserve">11.4253196716309</t>
   </si>
   <si>
     <t xml:space="preserve">11.5636587142944</t>
@@ -1910,22 +1910,22 @@
     <t xml:space="preserve">11.5849418640137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.560112953186</t>
+    <t xml:space="preserve">11.5601119995117</t>
   </si>
   <si>
     <t xml:space="preserve">11.3189077377319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5459232330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4146795272827</t>
+    <t xml:space="preserve">11.5459222793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.414680480957</t>
   </si>
   <si>
     <t xml:space="preserve">11.3330955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124919891357</t>
+    <t xml:space="preserve">11.2124938964844</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763423919678</t>
@@ -1934,31 +1934,31 @@
     <t xml:space="preserve">11.1486444473267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.123815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2727947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2195873260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2479639053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3366422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4536991119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4288682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4785280227661</t>
+    <t xml:space="preserve">11.1238145828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2727956771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1805696487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2195854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2479648590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3366432189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4536981582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4288692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4785261154175</t>
   </si>
   <si>
     <t xml:space="preserve">11.4466047286987</t>
@@ -1967,31 +1967,31 @@
     <t xml:space="preserve">11.5175466537476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7445640563965</t>
+    <t xml:space="preserve">11.7445650100708</t>
   </si>
   <si>
     <t xml:space="preserve">11.8119592666626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8332414627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8403367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7871294021606</t>
+    <t xml:space="preserve">11.8332424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8403358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.787127494812</t>
   </si>
   <si>
     <t xml:space="preserve">11.7481098175049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7126398086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7977705001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935432434082</t>
+    <t xml:space="preserve">11.7126388549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935403823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.1063709259033</t>
@@ -2000,43 +2000,43 @@
     <t xml:space="preserve">12.1312017440796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0708990097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1418428421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1773147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2092361450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2056894302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560297012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1170120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9893140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.024787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0105991363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9751262664795</t>
+    <t xml:space="preserve">12.0708980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1418418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1773157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2092370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2056903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560306549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808605194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1170110702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.989315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0247888565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105981826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9751272201538</t>
   </si>
   <si>
     <t xml:space="preserve">11.996410369873</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">11.8545236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9467506408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573907852173</t>
+    <t xml:space="preserve">11.9467496871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573926925659</t>
   </si>
   <si>
     <t xml:space="preserve">11.6629800796509</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">11.6594314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3437376022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.379207611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.443058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.29407787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4749813079834</t>
+    <t xml:space="preserve">11.3437366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3792095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430561065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2940769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4749803543091</t>
   </si>
   <si>
     <t xml:space="preserve">11.5069046020508</t>
@@ -2084,16 +2084,16 @@
     <t xml:space="preserve">11.6168661117554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5778474807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.467887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6558847427368</t>
+    <t xml:space="preserve">11.5778493881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4678869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820756912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6558856964111</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388288497925</t>
@@ -2105,19 +2105,19 @@
     <t xml:space="preserve">11.6842613220215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7374696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9432029724121</t>
+    <t xml:space="preserve">11.7090902328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7374687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9432020187378</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1347484588623</t>
+    <t xml:space="preserve">12.134747505188</t>
   </si>
   <si>
     <t xml:space="preserve">12.2021427154541</t>
@@ -2126,28 +2126,28 @@
     <t xml:space="preserve">12.1844072341919</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3014621734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4149732589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3972358703613</t>
+    <t xml:space="preserve">12.3014631271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4149713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.397234916687</t>
   </si>
   <si>
     <t xml:space="preserve">12.3262929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2908229827881</t>
+    <t xml:space="preserve">12.2908210754395</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881017684937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6597232818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058353424072</t>
+    <t xml:space="preserve">12.6597242355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058362960815</t>
   </si>
   <si>
     <t xml:space="preserve">12.6739120483398</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">12.741307258606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6987409591675</t>
+    <t xml:space="preserve">12.6987428665161</t>
   </si>
   <si>
     <t xml:space="preserve">12.6703643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6136131286621</t>
+    <t xml:space="preserve">12.6136121749878</t>
   </si>
   <si>
     <t xml:space="preserve">12.5852346420288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3759527206421</t>
+    <t xml:space="preserve">12.3759517669678</t>
   </si>
   <si>
     <t xml:space="preserve">12.4433479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5213851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6065187454224</t>
+    <t xml:space="preserve">12.5213861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.606517791748</t>
   </si>
   <si>
     <t xml:space="preserve">12.5887823104858</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">12.6490821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6774587631226</t>
+    <t xml:space="preserve">12.6774597167969</t>
   </si>
   <si>
     <t xml:space="preserve">12.8157978057861</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">12.8406286239624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.035719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215301513672</t>
+    <t xml:space="preserve">12.9080219268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215320587158</t>
   </si>
   <si>
     <t xml:space="preserve">13.0463600158691</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">13.0286254882812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9364013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.893835067749</t>
+    <t xml:space="preserve">12.9364023208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938341140747</t>
   </si>
   <si>
     <t xml:space="preserve">13.1243991851807</t>
@@ -2240,43 +2240,43 @@
     <t xml:space="preserve">13.1917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6422786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338260650635</t>
+    <t xml:space="preserve">13.6422805786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139059066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338251113892</t>
   </si>
   <si>
     <t xml:space="preserve">13.7167692184448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5997142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145835876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2662830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2343606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.152777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2591905593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627353668213</t>
+    <t xml:space="preserve">13.5997123718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.266284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2343597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1527767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2591896057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627372741699</t>
   </si>
   <si>
     <t xml:space="preserve">13.1456823348999</t>
@@ -2288,19 +2288,19 @@
     <t xml:space="preserve">12.9612312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9399461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.918664932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9257583618164</t>
+    <t xml:space="preserve">12.9399480819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9186658859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9257593154907</t>
   </si>
   <si>
     <t xml:space="preserve">12.9541358947754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0250797271729</t>
+    <t xml:space="preserve">13.0250806808472</t>
   </si>
   <si>
     <t xml:space="preserve">13.0108909606934</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">13.1137580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1314935684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1776056289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1208515167236</t>
+    <t xml:space="preserve">13.1314926147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1776065826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1208524703979</t>
   </si>
   <si>
     <t xml:space="preserve">13.4613761901855</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2520980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953420639038</t>
+    <t xml:space="preserve">13.2520952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953430175781</t>
   </si>
   <si>
     <t xml:space="preserve">13.06409740448</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">12.9115715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9789657592773</t>
+    <t xml:space="preserve">12.9789667129517</t>
   </si>
   <si>
     <t xml:space="preserve">12.9860601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9505891799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8654594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235736846924</t>
+    <t xml:space="preserve">12.9505882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8654584884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235717773438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8690052032471</t>
@@ -2363,40 +2363,40 @@
     <t xml:space="preserve">12.571044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9434938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6916475296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4823665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.546215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7306680679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194913864136</t>
+    <t xml:space="preserve">12.9434947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6916484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4823656082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5462160110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7306671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818319320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804727554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194904327393</t>
   </si>
   <si>
     <t xml:space="preserve">13.3230381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3939790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3688583374023</t>
+    <t xml:space="preserve">13.3939800262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3688592910767</t>
   </si>
   <si>
     <t xml:space="preserve">12.2979154586792</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">11.4004907608032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8116655349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76171588897705</t>
+    <t xml:space="preserve">11.1628332138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8116664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76171493530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.61273574829102</t>
@@ -2432,37 +2432,37 @@
     <t xml:space="preserve">8.01297664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69728183746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36739873886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569738388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72566032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58406543731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83236694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98134422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77915859222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77206420898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398750305176</t>
+    <t xml:space="preserve">7.69728326797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72565937042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920703887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58406639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83236598968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98134517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77915954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77206325531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398845672607</t>
   </si>
   <si>
     <t xml:space="preserve">8.5805196762085</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">8.64436817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89976215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07002353668213</t>
+    <t xml:space="preserve">8.89976119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07002258300781</t>
   </si>
   <si>
     <t xml:space="preserve">9.13032531738281</t>
@@ -2489,22 +2489,22 @@
     <t xml:space="preserve">8.93877983093262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7898006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88912010192871</t>
+    <t xml:space="preserve">8.78979969024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88911914825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.63017845153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84300804138184</t>
+    <t xml:space="preserve">8.8430061340332</t>
   </si>
   <si>
     <t xml:space="preserve">8.77561187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04164600372314</t>
+    <t xml:space="preserve">9.04164695739746</t>
   </si>
   <si>
     <t xml:space="preserve">9.20126819610596</t>
@@ -2516,337 +2516,337 @@
     <t xml:space="preserve">9.23319244384766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00972175598145</t>
+    <t xml:space="preserve">9.00972270965576</t>
   </si>
   <si>
     <t xml:space="preserve">9.176438331604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0345516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09485340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20481491088867</t>
+    <t xml:space="preserve">9.03455257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0948543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20481395721436</t>
   </si>
   <si>
     <t xml:space="preserve">9.12323093414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08421230316162</t>
+    <t xml:space="preserve">9.08421325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91040325164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80044078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17269134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01014709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05817127227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78849601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99536895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96212291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20963191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803600311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43867206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22440910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52363967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81178665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3031139373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3474464416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6282062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540632247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5395431518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3215856552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9226131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91891860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90414237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1257944107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.051908493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92630672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0592975616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0703802108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80070495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82656383514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9152250289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95216751098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94847297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2218427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1553478240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2587842941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1627359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0777683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1294870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070646286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2107601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.114709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3289737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2772550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0408267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98541450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97433185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46453380584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35370635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40911960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55688762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63077163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38695430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78592777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7305154800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68618392944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53841590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70835018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62707614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56058120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76376247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78223323822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60860538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62338161468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61968803405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57535839080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47192096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37217807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56796932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48669815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47561359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36478900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1061954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75155258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70352649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66658496856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59639644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804752349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88454341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76632881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91779136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14313793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1135835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29829406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24288177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22071552276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12466716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12097263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80327129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96951007843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01753425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03969860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81435298919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82543563842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.91040229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044078826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17269134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01014518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05817031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78849506378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96212196350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20963287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43867301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22441005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52363967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81178569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3031139373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3474445343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6282033920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5395450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3215856552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92261409759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91891860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90414237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1257944107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519094467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92630767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0592975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0703811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80070495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91522407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95216655731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94847202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2218418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1553468704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2587842941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1627359390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.07776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.129487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2107601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1147108078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.181206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3289737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2772550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.040825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98541450500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97433090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46453285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35370540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40911865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63077068328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38695526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78592777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73051452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68618392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53841590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70834922790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62707614898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56058216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76376152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78223323822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60860633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62338161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61968803405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57535839080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47192001342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37217807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56796932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48669815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47561454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36478900909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1061954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75155258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70352745056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66658496856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59639549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804847717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88454246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76632881164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91779041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14313793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11358261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2982931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24288082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22071552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12097263336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80327033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96951007843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03969955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81435394287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82543563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91040420532227</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.77371692657471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39321613311768</t>
+    <t xml:space="preserve">8.39321517944336</t>
   </si>
   <si>
     <t xml:space="preserve">8.41907501220703</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">8.50404167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.721999168396</t>
+    <t xml:space="preserve">8.72199821472168</t>
   </si>
   <si>
     <t xml:space="preserve">8.89193153381348</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">9.14683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72312545776367</t>
+    <t xml:space="preserve">9.7231273651123</t>
   </si>
   <si>
     <t xml:space="preserve">9.95955371856689</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">10.3178911209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4398002624512</t>
+    <t xml:space="preserve">10.4398012161255</t>
   </si>
   <si>
     <t xml:space="preserve">10.5136833190918</t>
@@ -2891,22 +2891,22 @@
     <t xml:space="preserve">10.3954696655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4952125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5062971115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6245088577271</t>
+    <t xml:space="preserve">10.495213508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5062961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6245107650757</t>
   </si>
   <si>
     <t xml:space="preserve">10.7094764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6910047531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5801792144775</t>
+    <t xml:space="preserve">10.6910057067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5801801681519</t>
   </si>
   <si>
     <t xml:space="preserve">10.6577577590942</t>
@@ -2918,16 +2918,16 @@
     <t xml:space="preserve">10.713171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.609733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838747024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060400009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4065523147583</t>
+    <t xml:space="preserve">10.6097316741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838737487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4065542221069</t>
   </si>
   <si>
     <t xml:space="preserve">10.5358505249023</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">10.5506267547607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5617084503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2624807357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176349639893</t>
+    <t xml:space="preserve">10.5617074966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2624788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176359176636</t>
   </si>
   <si>
     <t xml:space="preserve">10.6134271621704</t>
@@ -2960,19 +2960,19 @@
     <t xml:space="preserve">10.7464189529419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6392869949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6836166381836</t>
+    <t xml:space="preserve">10.6392860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6836175918579</t>
   </si>
   <si>
     <t xml:space="preserve">10.7168645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9422121047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.827691078186</t>
+    <t xml:space="preserve">10.942211151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8276901245117</t>
   </si>
   <si>
     <t xml:space="preserve">10.7205600738525</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">10.6429805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4102478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5321550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6946983337402</t>
+    <t xml:space="preserve">10.4102468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5321559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6946992874146</t>
   </si>
   <si>
     <t xml:space="preserve">11.0456485748291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3929033279419</t>
+    <t xml:space="preserve">11.3929023742676</t>
   </si>
   <si>
     <t xml:space="preserve">11.4778699874878</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6145553588867</t>
+    <t xml:space="preserve">11.6145544052124</t>
   </si>
   <si>
     <t xml:space="preserve">11.6884384155273</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">11.599778175354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5739192962646</t>
+    <t xml:space="preserve">11.5739183425903</t>
   </si>
   <si>
     <t xml:space="preserve">11.6921329498291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6367197036743</t>
+    <t xml:space="preserve">11.63671875</t>
   </si>
   <si>
     <t xml:space="preserve">11.5665302276611</t>
@@ -3032,25 +3032,25 @@
     <t xml:space="preserve">11.4815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4557037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6995210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4889516830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6958274841309</t>
+    <t xml:space="preserve">11.4557046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6995220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6958284378052</t>
   </si>
   <si>
     <t xml:space="preserve">11.7290744781494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435955047607</t>
+    <t xml:space="preserve">11.8435945510864</t>
   </si>
   <si>
     <t xml:space="preserve">11.8768434524536</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1908493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2130155563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2795114517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3866415023804</t>
+    <t xml:space="preserve">12.1908502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2130146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2795124053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3866395950317</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900808334351</t>
@@ -3080,22 +3080,22 @@
     <t xml:space="preserve">12.4789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755588531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4568328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3607816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4161949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309720993042</t>
+    <t xml:space="preserve">12.3755598068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4568319320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.360782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4161958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.412501335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
     <t xml:space="preserve">12.5048561096191</t>
@@ -3104,19 +3104,19 @@
     <t xml:space="preserve">12.6045989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6637048721313</t>
+    <t xml:space="preserve">12.6637058258057</t>
   </si>
   <si>
     <t xml:space="preserve">12.5824356079102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6600112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858720779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6378479003906</t>
+    <t xml:space="preserve">12.6600122451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858711242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6378469467163</t>
   </si>
   <si>
     <t xml:space="preserve">12.5344095230103</t>
@@ -3125,16 +3125,16 @@
     <t xml:space="preserve">12.6119871139526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6230707168579</t>
+    <t xml:space="preserve">12.6230697631836</t>
   </si>
   <si>
     <t xml:space="preserve">12.5787401199341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6489295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.726508140564</t>
+    <t xml:space="preserve">12.6489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265090942383</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457483291626</t>
@@ -3152,19 +3152,19 @@
     <t xml:space="preserve">12.5602693557739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4420557022095</t>
+    <t xml:space="preserve">12.4420547485352</t>
   </si>
   <si>
     <t xml:space="preserve">12.5972108840942</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7228126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8336410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740200042725</t>
+    <t xml:space="preserve">12.7228136062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8336400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740190505981</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631944656372</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">13.0331268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0368213653564</t>
+    <t xml:space="preserve">13.0368204116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.0626802444458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8816633224487</t>
+    <t xml:space="preserve">12.881664276123</t>
   </si>
   <si>
     <t xml:space="preserve">12.8890514373779</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2438182830811</t>
+    <t xml:space="preserve">13.2438173294067</t>
   </si>
   <si>
     <t xml:space="preserve">13.1184320449829</t>
@@ -3215,46 +3215,46 @@
     <t xml:space="preserve">13.2673273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2829999923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3887929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5180978775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4985055923462</t>
+    <t xml:space="preserve">13.2830009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5180969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">13.4632415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201402664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4318952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.451488494873</t>
+    <t xml:space="preserve">13.4201412200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4318943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4514875411987</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2359790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712450027466</t>
+    <t xml:space="preserve">13.2359809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712440490723</t>
   </si>
   <si>
     <t xml:space="preserve">13.2320623397827</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0518207550049</t>
+    <t xml:space="preserve">13.0518217086792</t>
   </si>
   <si>
     <t xml:space="preserve">13.3339366912842</t>
@@ -3266,28 +3266,28 @@
     <t xml:space="preserve">13.1732873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2477378845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3731212615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3221826553345</t>
+    <t xml:space="preserve">13.2477369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3731203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3221836090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.4358139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.196798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9852094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.326099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3300189971924</t>
+    <t xml:space="preserve">13.1967992782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9852104187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3261003494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3300199508667</t>
   </si>
   <si>
     <t xml:space="preserve">13.2634077072144</t>
@@ -3296,49 +3296,49 @@
     <t xml:space="preserve">13.1654510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7148485183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441514968872</t>
+    <t xml:space="preserve">13.1145143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7148475646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441524505615</t>
   </si>
   <si>
     <t xml:space="preserve">13.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1576166152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1301860809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.067494392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.989128112793</t>
+    <t xml:space="preserve">13.1576147079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1301870346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046337127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0674934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9891300201416</t>
   </si>
   <si>
     <t xml:space="preserve">13.0283126831055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947568893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4749956130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5690355300903</t>
+    <t xml:space="preserve">13.2281427383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947559356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456945419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4749965667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5690364837646</t>
   </si>
   <si>
     <t xml:space="preserve">13.6160545349121</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">13.5416078567505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3770380020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4436502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4240579605103</t>
+    <t xml:space="preserve">13.3770389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4436521530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4240570068359</t>
   </si>
   <si>
     <t xml:space="preserve">13.3848762512207</t>
@@ -3368,49 +3368,49 @@
     <t xml:space="preserve">13.5337715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5964632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.612135887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5729532241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7414407730103</t>
+    <t xml:space="preserve">13.5964641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6121368408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5729541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7414398193359</t>
   </si>
   <si>
     <t xml:space="preserve">13.8393974304199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9060087203979</t>
+    <t xml:space="preserve">13.9060096740723</t>
   </si>
   <si>
     <t xml:space="preserve">13.6591558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8315601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923774719238</t>
+    <t xml:space="preserve">13.8315591812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923784255981</t>
   </si>
   <si>
     <t xml:space="preserve">13.8824987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0039663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589868545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748304367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0901660919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2037982940674</t>
+    <t xml:space="preserve">14.0039672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748294830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0901679992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2037973403931</t>
   </si>
   <si>
     <t xml:space="preserve">14.3644485473633</t>
@@ -3419,61 +3419,61 @@
     <t xml:space="preserve">14.5956268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3017559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349775314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4114656448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4271411895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3997116088867</t>
+    <t xml:space="preserve">14.3017568588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349784851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4114665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4271402359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.399712562561</t>
   </si>
   <si>
     <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642805099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014207839966</t>
+    <t xml:space="preserve">14.5642795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014198303223</t>
   </si>
   <si>
     <t xml:space="preserve">14.7288484573364</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816614151001</t>
+    <t xml:space="preserve">14.8072156906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816623687744</t>
   </si>
   <si>
     <t xml:space="preserve">14.6622371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6739931106567</t>
+    <t xml:space="preserve">14.6739950180054</t>
   </si>
   <si>
     <t xml:space="preserve">14.7249298095703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7851810455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9538774490356</t>
+    <t xml:space="preserve">14.7851800918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494462966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739589691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9217472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95387840271</t>
   </si>
   <si>
     <t xml:space="preserve">15.0141286849976</t>
@@ -3488,58 +3488,58 @@
     <t xml:space="preserve">15.1346263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426591873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310247421265</t>
+    <t xml:space="preserve">15.1426601409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310266494751</t>
   </si>
   <si>
     <t xml:space="preserve">15.247091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3234090805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2591419219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3475074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2430772781372</t>
+    <t xml:space="preserve">15.3234081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2591400146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3475065231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2430753707886</t>
   </si>
   <si>
     <t xml:space="preserve">15.2511081695557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.279224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.38365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3716068267822</t>
+    <t xml:space="preserve">15.2792253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3836545944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3716077804565</t>
   </si>
   <si>
     <t xml:space="preserve">15.4559564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0743751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418287277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6887798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7811613082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7570638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168979644775</t>
+    <t xml:space="preserve">15.0743770599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6887807846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7811632156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7570657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168960571289</t>
   </si>
   <si>
     <t xml:space="preserve">14.1867036819458</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">14.299168586731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2429370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5642652511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4919662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6124649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498624801636</t>
+    <t xml:space="preserve">14.2429361343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.564266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4919672012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6124668121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498615264893</t>
   </si>
   <si>
     <t xml:space="preserve">15.0221605300903</t>
@@ -3569,73 +3569,73 @@
     <t xml:space="preserve">14.857479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9297780990601</t>
+    <t xml:space="preserve">14.9297771453857</t>
   </si>
   <si>
     <t xml:space="preserve">14.8614959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8213300704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6767311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731304168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9699459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9016599655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623273849487</t>
+    <t xml:space="preserve">14.8213310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6767320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9699449539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9016618728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623264312744</t>
   </si>
   <si>
     <t xml:space="preserve">15.0060939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9659261703491</t>
+    <t xml:space="preserve">14.9659271240234</t>
   </si>
   <si>
     <t xml:space="preserve">15.2671747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1788110733032</t>
+    <t xml:space="preserve">15.1788101196289</t>
   </si>
   <si>
     <t xml:space="preserve">14.8333787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9177284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8293619155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9337940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0583124160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422439575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8132953643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9257621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1466760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0382261276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627426147461</t>
+    <t xml:space="preserve">14.9177293777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8293628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9337949752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.058310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8132963180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9257612228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1466751098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0382251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627416610718</t>
   </si>
   <si>
     <t xml:space="preserve">14.3754863739014</t>
@@ -3644,37 +3644,37 @@
     <t xml:space="preserve">14.4999990463257</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6847658157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6727142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9940452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7369785308838</t>
+    <t xml:space="preserve">14.6847648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6727132797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9940462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7369794845581</t>
   </si>
   <si>
     <t xml:space="preserve">14.9819946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.957896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7450132369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270088195801</t>
+    <t xml:space="preserve">14.9578952789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7450122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270078659058</t>
   </si>
   <si>
     <t xml:space="preserve">14.893630027771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562324523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.596399307251</t>
+    <t xml:space="preserve">14.5562334060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5963973999023</t>
   </si>
   <si>
     <t xml:space="preserve">14.0300559997559</t>
@@ -3686,34 +3686,34 @@
     <t xml:space="preserve">13.9256229400635</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8372583389282</t>
+    <t xml:space="preserve">13.8372592926025</t>
   </si>
   <si>
     <t xml:space="preserve">13.7770080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379505157471</t>
+    <t xml:space="preserve">13.0379495620728</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447366714478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9937677383423</t>
+    <t xml:space="preserve">12.993766784668</t>
   </si>
   <si>
     <t xml:space="preserve">13.6243762969971</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4958438873291</t>
+    <t xml:space="preserve">13.4958448410034</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.174654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3875350952148</t>
+    <t xml:space="preserve">14.1746530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3875341415405</t>
   </si>
   <si>
     <t xml:space="preserve">15.0824098587036</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">15.0502767562866</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1667594909668</t>
+    <t xml:space="preserve">15.1667585372925</t>
   </si>
   <si>
     <t xml:space="preserve">15.3153743743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6005525588989</t>
+    <t xml:space="preserve">15.6005544662476</t>
   </si>
   <si>
     <t xml:space="preserve">16.1789455413818</t>
@@ -3737,19 +3737,19 @@
     <t xml:space="preserve">15.8495836257935</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1628837585449</t>
+    <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
     <t xml:space="preserve">16.6850414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9581718444824</t>
+    <t xml:space="preserve">16.9581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">16.3074798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.235179901123</t>
+    <t xml:space="preserve">16.2351779937744</t>
   </si>
   <si>
     <t xml:space="preserve">16.0504150390625</t>
@@ -3767,43 +3767,43 @@
     <t xml:space="preserve">15.4840726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4117736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4760389328003</t>
+    <t xml:space="preserve">15.4117727279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.476037979126</t>
   </si>
   <si>
     <t xml:space="preserve">14.9980602264404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7932138442993</t>
+    <t xml:space="preserve">14.7932147979736</t>
   </si>
   <si>
     <t xml:space="preserve">14.5080327987671</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5441818237305</t>
+    <t xml:space="preserve">14.5441827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.4598331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5401649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196691513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7048463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6204996109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4518003463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2469539642334</t>
+    <t xml:space="preserve">14.5401678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7048482894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4518013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2469520568848</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">14.2268695831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2670364379883</t>
+    <t xml:space="preserve">14.267035484314</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947374343872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3112192153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4558181762695</t>
+    <t xml:space="preserve">14.3112182617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4558172225952</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
@@ -3830,31 +3830,31 @@
     <t xml:space="preserve">14.7547550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8230838775635</t>
+    <t xml:space="preserve">14.8230848312378</t>
   </si>
   <si>
     <t xml:space="preserve">14.8828716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5882034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5540399551392</t>
+    <t xml:space="preserve">14.5882043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5540390014648</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2764539718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643573760986</t>
+    <t xml:space="preserve">14.4430055618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3789472579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2764530181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643564224243</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">13.3924493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2344398498535</t>
+    <t xml:space="preserve">13.2344388961792</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3878,28 +3878,28 @@
     <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3881788253784</t>
+    <t xml:space="preserve">13.3881797790527</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3967199325562</t>
+    <t xml:space="preserve">13.5803537368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3967208862305</t>
   </si>
   <si>
     <t xml:space="preserve">13.2557926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917333602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828479766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2686042785645</t>
+    <t xml:space="preserve">13.1917343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828470230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2686033248901</t>
   </si>
   <si>
     <t xml:space="preserve">13.4266138076782</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038290023804</t>
+    <t xml:space="preserve">13.0038299560547</t>
   </si>
   <si>
     <t xml:space="preserve">13.2942266464233</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">13.1661100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4187641143799</t>
+    <t xml:space="preserve">12.4187631607056</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596923828125</t>
@@ -3929,31 +3929,31 @@
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568529129028</t>
+    <t xml:space="preserve">12.9568538665771</t>
   </si>
   <si>
     <t xml:space="preserve">12.995288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7774906158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3547058105469</t>
+    <t xml:space="preserve">12.7774896621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3547048568726</t>
   </si>
   <si>
     <t xml:space="preserve">12.4401159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4230337142944</t>
+    <t xml:space="preserve">12.4230346679688</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1625308990479</t>
+    <t xml:space="preserve">12.1838846206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1625299453735</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095069885254</t>
@@ -3962,13 +3962,13 @@
     <t xml:space="preserve">12.4273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796140670776</t>
+    <t xml:space="preserve">12.1796131134033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333520889282</t>
+    <t xml:space="preserve">12.3333530426025</t>
   </si>
   <si>
     <t xml:space="preserve">12.4571981430054</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">12.5340690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.640832901001</t>
+    <t xml:space="preserve">12.6408319473267</t>
   </si>
   <si>
     <t xml:space="preserve">12.8458185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141473770142</t>
+    <t xml:space="preserve">12.9141483306885</t>
   </si>
   <si>
     <t xml:space="preserve">13.0508050918579</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618394851685</t>
+    <t xml:space="preserve">13.1618385314941</t>
   </si>
   <si>
     <t xml:space="preserve">12.897066116333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7646780014038</t>
+    <t xml:space="preserve">12.7646789550781</t>
   </si>
   <si>
     <t xml:space="preserve">12.7006206512451</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579151153564</t>
+    <t xml:space="preserve">12.6579141616821</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041751861572</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">12.768949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1703815460205</t>
+    <t xml:space="preserve">13.1703805923462</t>
   </si>
   <si>
     <t xml:space="preserve">12.9696645736694</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">12.704891204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7390556335449</t>
+    <t xml:space="preserve">12.7390546798706</t>
   </si>
   <si>
     <t xml:space="preserve">12.3248119354248</t>
@@ -4091,25 +4091,25 @@
     <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8550510406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7397451400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575443267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7909927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0045213699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.158260345459</t>
+    <t xml:space="preserve">11.8550519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.73974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575433731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7909936904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0045204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1582593917847</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991876602173</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">12.3632469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5169868469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3376226425171</t>
+    <t xml:space="preserve">12.5169858932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3376235961914</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749973297119</t>
@@ -4130,13 +4130,13 @@
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091617584229</t>
+    <t xml:space="preserve">12.7091608047485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9739351272583</t>
+    <t xml:space="preserve">12.973934173584</t>
   </si>
   <si>
     <t xml:space="preserve">13.0977811813354</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">13.0251817703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532983779907</t>
+    <t xml:space="preserve">13.153299331665</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">13.8493986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9433517456055</t>
+    <t xml:space="preserve">13.9433507919312</t>
   </si>
   <si>
     <t xml:space="preserve">14.2294778823853</t>
@@ -4169,16 +4169,16 @@
     <t xml:space="preserve">14.5839338302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5156049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7419443130493</t>
+    <t xml:space="preserve">14.515604019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741943359375</t>
   </si>
   <si>
     <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5027933120728</t>
+    <t xml:space="preserve">14.5027923583984</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600877761841</t>
@@ -4190,16 +4190,16 @@
     <t xml:space="preserve">14.4686298370361</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6266384124756</t>
+    <t xml:space="preserve">14.6266393661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.7163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7035083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.699236869812</t>
+    <t xml:space="preserve">14.7035093307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6992378234863</t>
   </si>
   <si>
     <t xml:space="preserve">14.7931909561157</t>
@@ -4211,76 +4211,76 @@
     <t xml:space="preserve">14.7889204025269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7462129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999538421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8444356918335</t>
+    <t xml:space="preserve">14.7462139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8444366455078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2508296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2892646789551</t>
+    <t xml:space="preserve">14.0928201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2508306503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2892637252808</t>
   </si>
   <si>
     <t xml:space="preserve">14.3960285186768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3490524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3106174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2593717575073</t>
+    <t xml:space="preserve">14.3490533828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3106184005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.259370803833</t>
   </si>
   <si>
     <t xml:space="preserve">14.3618650436401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1910419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3277006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504854202271</t>
+    <t xml:space="preserve">14.1910429000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3276996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917589187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504844665527</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6736154556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8615188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.848708152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554719924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9682836532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8358964920044</t>
+    <t xml:space="preserve">14.6736164093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8615198135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8487071990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9682817459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8358974456787</t>
   </si>
   <si>
     <t xml:space="preserve">15.168999671936</t>
@@ -4289,82 +4289,82 @@
     <t xml:space="preserve">15.2373285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3013877868652</t>
+    <t xml:space="preserve">15.3013868331909</t>
   </si>
   <si>
     <t xml:space="preserve">15.2586803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2971162796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270101547241</t>
+    <t xml:space="preserve">15.2971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270092010498</t>
   </si>
   <si>
     <t xml:space="preserve">15.3825263977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2885751724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319948196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.502100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4166898727417</t>
+    <t xml:space="preserve">15.28857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5021018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.416690826416</t>
   </si>
   <si>
     <t xml:space="preserve">15.4679374694824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4636659622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063714981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5618877410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832424163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6003246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5875120162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344881057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6857357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106420516968</t>
+    <t xml:space="preserve">15.4636669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063734054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5618906021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832433700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6003255844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5875129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686525344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473016738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857347488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106449127197</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9804029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223934173584</t>
+    <t xml:space="preserve">15.9804019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266649246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223915100098</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4376,31 +4376,31 @@
     <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0658149719238</t>
+    <t xml:space="preserve">16.0658130645752</t>
   </si>
   <si>
     <t xml:space="preserve">15.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7327117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2031631469727</t>
+    <t xml:space="preserve">15.7327108383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.203161239624</t>
   </si>
   <si>
     <t xml:space="preserve">15.7540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8316249847412</t>
+    <t xml:space="preserve">14.8316259384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.450855255127</t>
+    <t xml:space="preserve">15.0451526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4508562088013</t>
   </si>
   <si>
     <t xml:space="preserve">15.4081497192383</t>
@@ -4409,28 +4409,28 @@
     <t xml:space="preserve">15.1092128753662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2501401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4423131942749</t>
+    <t xml:space="preserve">15.2501392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4423151016235</t>
   </si>
   <si>
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985464096069</t>
+    <t xml:space="preserve">15.6985473632812</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6216773986816</t>
+    <t xml:space="preserve">15.621678352356</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437442779541</t>
+    <t xml:space="preserve">15.8437471389771</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
@@ -4442,10 +4442,10 @@
     <t xml:space="preserve">16.1683082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0401916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1384162902832</t>
+    <t xml:space="preserve">16.040189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1384143829346</t>
   </si>
   <si>
     <t xml:space="preserve">16.2836132049561</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">16.3049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3092346191406</t>
+    <t xml:space="preserve">16.3092365264893</t>
   </si>
   <si>
     <t xml:space="preserve">16.3434009552002</t>
@@ -4469,37 +4469,37 @@
     <t xml:space="preserve">16.2323665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.125602722168</t>
+    <t xml:space="preserve">16.1256008148193</t>
   </si>
   <si>
     <t xml:space="preserve">15.8693695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9334278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8053102493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2067451477051</t>
+    <t xml:space="preserve">15.9334297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8053112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2067432403564</t>
   </si>
   <si>
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8907222747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889440536499</t>
+    <t xml:space="preserve">15.890721321106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889430999756</t>
   </si>
   <si>
     <t xml:space="preserve">16.1127910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0316524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.912073135376</t>
+    <t xml:space="preserve">16.0316505432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9120721817017</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">16.4688701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596569061279</t>
+    <t xml:space="preserve">16.2596549987793</t>
   </si>
   <si>
     <t xml:space="preserve">16.332426071167</t>
@@ -4532,7 +4532,7 @@
     <t xml:space="preserve">16.4188404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5188999176025</t>
+    <t xml:space="preserve">16.5189018249512</t>
   </si>
   <si>
     <t xml:space="preserve">16.6462478637695</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">16.9236850738525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1010646820068</t>
+    <t xml:space="preserve">17.1010627746582</t>
   </si>
   <si>
     <t xml:space="preserve">17.2193164825439</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">16.9054927825928</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7963390350342</t>
+    <t xml:space="preserve">16.7963371276855</t>
   </si>
   <si>
     <t xml:space="preserve">16.6689910888672</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">16.6280574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7235660552979</t>
+    <t xml:space="preserve">16.7235679626465</t>
   </si>
   <si>
     <t xml:space="preserve">16.6917304992676</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">16.9373321533203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4330787658691</t>
+    <t xml:space="preserve">17.5103969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4330806732178</t>
   </si>
   <si>
     <t xml:space="preserve">17.2056732177734</t>
@@ -4607,10 +4607,10 @@
     <t xml:space="preserve">17.1783828735352</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1920261383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0692272186279</t>
+    <t xml:space="preserve">17.1920280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0692253112793</t>
   </si>
   <si>
     <t xml:space="preserve">17.2829914093018</t>
@@ -4619,13 +4619,13 @@
     <t xml:space="preserve">17.3648567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3739547729492</t>
+    <t xml:space="preserve">17.3739528656006</t>
   </si>
   <si>
     <t xml:space="preserve">17.3330192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3284702301025</t>
+    <t xml:space="preserve">17.3284721374512</t>
   </si>
   <si>
     <t xml:space="preserve">17.5149459838867</t>
@@ -4634,10 +4634,10 @@
     <t xml:space="preserve">17.5240421295166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6286487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4057922363281</t>
+    <t xml:space="preserve">17.6286506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4057903289795</t>
   </si>
   <si>
     <t xml:space="preserve">17.037389755249</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">17.091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7190170288086</t>
+    <t xml:space="preserve">16.9737148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7190189361572</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8736553192139</t>
+    <t xml:space="preserve">16.8736572265625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7417602539062</t>
@@ -4670,13 +4670,13 @@
     <t xml:space="preserve">16.7645015716553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8281764984131</t>
+    <t xml:space="preserve">16.8281745910645</t>
   </si>
   <si>
     <t xml:space="preserve">16.8418197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9282341003418</t>
+    <t xml:space="preserve">16.9282360076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.0737762451172</t>
@@ -4685,7 +4685,7 @@
     <t xml:space="preserve">17.442174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4012432098389</t>
+    <t xml:space="preserve">17.4012413024902</t>
   </si>
   <si>
     <t xml:space="preserve">17.292085647583</t>
@@ -4694,13 +4694,13 @@
     <t xml:space="preserve">17.3011837005615</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6013603210449</t>
+    <t xml:space="preserve">17.6013622283936</t>
   </si>
   <si>
     <t xml:space="preserve">17.7150650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7332572937012</t>
+    <t xml:space="preserve">17.7332592010498</t>
   </si>
   <si>
     <t xml:space="preserve">18.0197906494141</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">18.1243991851807</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1926212310791</t>
+    <t xml:space="preserve">18.1926231384277</t>
   </si>
   <si>
     <t xml:space="preserve">18.0470809936523</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">17.7878360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059093475342</t>
+    <t xml:space="preserve">17.6059074401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6832294464111</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">16.8918476104736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3239231109619</t>
+    <t xml:space="preserve">17.3239250183105</t>
   </si>
   <si>
     <t xml:space="preserve">17.4876575469971</t>
@@ -4793,16 +4793,16 @@
     <t xml:space="preserve">17.0510349273682</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2966327667236</t>
+    <t xml:space="preserve">17.2966346740723</t>
   </si>
   <si>
     <t xml:space="preserve">17.1829299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1238059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1465454101562</t>
+    <t xml:space="preserve">17.1238040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1465473175049</t>
   </si>
   <si>
     <t xml:space="preserve">17.2511539459229</t>
@@ -4820,16 +4820,16 @@
     <t xml:space="preserve">17.8787994384766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8151245117188</t>
+    <t xml:space="preserve">17.8151226043701</t>
   </si>
   <si>
     <t xml:space="preserve">17.7014198303223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4922046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.314826965332</t>
+    <t xml:space="preserve">17.4922065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3148288726807</t>
   </si>
   <si>
     <t xml:space="preserve">17.187479019165</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">17.242057800293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1419982910156</t>
+    <t xml:space="preserve">17.141996383667</t>
   </si>
   <si>
     <t xml:space="preserve">17.2284126281738</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">17.4103393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.414888381958</t>
+    <t xml:space="preserve">17.4148864746094</t>
   </si>
   <si>
     <t xml:space="preserve">17.496753692627</t>
@@ -4898,13 +4898,13 @@
     <t xml:space="preserve">17.9561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0061454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.901538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9515705108643</t>
+    <t xml:space="preserve">18.0061473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9015407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9515686035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.9379234313965</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">18.6201477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5473785400391</t>
+    <t xml:space="preserve">18.5473766326904</t>
   </si>
   <si>
     <t xml:space="preserve">18.5655708312988</t>
@@ -4946,10 +4946,10 @@
     <t xml:space="preserve">18.6656303405762</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6929187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8202686309814</t>
+    <t xml:space="preserve">18.6929168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8202667236328</t>
   </si>
   <si>
     <t xml:space="preserve">18.629243850708</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">18.7565937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6838245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7293033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5564746856689</t>
+    <t xml:space="preserve">18.6838226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.729305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5564727783203</t>
   </si>
   <si>
     <t xml:space="preserve">18.8384590148926</t>
@@ -4988,25 +4988,25 @@
     <t xml:space="preserve">19.5024909973145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.139232635498</t>
+    <t xml:space="preserve">20.1392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">19.9391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9118232727051</t>
+    <t xml:space="preserve">19.9118251800537</t>
   </si>
   <si>
     <t xml:space="preserve">19.9664039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0027885437012</t>
+    <t xml:space="preserve">20.0027866363525</t>
   </si>
   <si>
     <t xml:space="preserve">20.1665210723877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1574230194092</t>
+    <t xml:space="preserve">20.1574249267578</t>
   </si>
   <si>
     <t xml:space="preserve">20.0755577087402</t>
@@ -5015,16 +5015,16 @@
     <t xml:space="preserve">20.2120018005371</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2847728729248</t>
+    <t xml:space="preserve">20.2847709655762</t>
   </si>
   <si>
     <t xml:space="preserve">20.393928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5940456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6122398376465</t>
+    <t xml:space="preserve">20.5940475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6122417449951</t>
   </si>
   <si>
     <t xml:space="preserve">20.6759147644043</t>
@@ -5045,10 +5045,10 @@
     <t xml:space="preserve">21.1034412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3399429321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4127178192139</t>
+    <t xml:space="preserve">21.3399448394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4127159118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.5309677124023</t>
@@ -5063,10 +5063,10 @@
     <t xml:space="preserve">20.8669376373291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0306701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7304916381836</t>
+    <t xml:space="preserve">21.0306720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7304935455322</t>
   </si>
   <si>
     <t xml:space="preserve">20.7577800750732</t>
@@ -5075,13 +5075,13 @@
     <t xml:space="preserve">20.6031436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7032051086426</t>
+    <t xml:space="preserve">20.7032032012939</t>
   </si>
   <si>
     <t xml:space="preserve">20.3393516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4394111633301</t>
+    <t xml:space="preserve">20.4394092559814</t>
   </si>
   <si>
     <t xml:space="preserve">20.4939880371094</t>
@@ -5090,7 +5090,7 @@
     <t xml:space="preserve">20.6213359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7123012542725</t>
+    <t xml:space="preserve">20.7122993469238</t>
   </si>
   <si>
     <t xml:space="preserve">21.003381729126</t>
@@ -5114,13 +5114,13 @@
     <t xml:space="preserve">21.2307891845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7765674591064</t>
+    <t xml:space="preserve">21.7765693664551</t>
   </si>
   <si>
     <t xml:space="preserve">21.7401809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9039154052734</t>
+    <t xml:space="preserve">21.9039173126221</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949977874756</t>
@@ -6090,6 +6090,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.7700004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.810001373291</t>
   </si>
 </sst>
 </file>
@@ -71766,7 +71769,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6918634259</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>2723392</v>
@@ -71787,6 +71790,32 @@
         <v>2025</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6910069444</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>1927428</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>33.2000007629395</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>32.5800018310547</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>32.7700004577637</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>32.810001373291</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>2026</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21389961242676</t>
+    <t xml:space="preserve">9.21390151977539</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31058883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13427448272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11721229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02052211761475</t>
+    <t xml:space="preserve">9.31058979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13427352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11721038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02052116394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.76458072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8897066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0660228729248</t>
+    <t xml:space="preserve">8.88970756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06602191925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.95795822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75889205932617</t>
+    <t xml:space="preserve">8.75889110565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.57120227813721</t>
@@ -80,196 +80,196 @@
     <t xml:space="preserve">8.29251003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44607639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48588848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30957317352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04794406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93987941741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41662073135376</t>
+    <t xml:space="preserve">8.44607448577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48588752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30957221984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04794311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93987846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568784713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84318923950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662168502808</t>
   </si>
   <si>
     <t xml:space="preserve">7.23461818695068</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15499210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161365509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74548482894897</t>
+    <t xml:space="preserve">7.1549916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74548578262329</t>
   </si>
   <si>
     <t xml:space="preserve">6.47248125076294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81373453140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23360157012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34166526794434</t>
+    <t xml:space="preserve">6.81373596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23360204696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34166574478149</t>
   </si>
   <si>
     <t xml:space="preserve">6.59760808944702</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62035799026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392339706421</t>
+    <t xml:space="preserve">6.62035894393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392292022705</t>
   </si>
   <si>
     <t xml:space="preserve">6.72842216491699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6601710319519</t>
+    <t xml:space="preserve">6.66017246246338</t>
   </si>
   <si>
     <t xml:space="preserve">6.89905023574829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89336156845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95592641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305532455444</t>
+    <t xml:space="preserve">6.89336204528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95592546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26305723190308</t>
   </si>
   <si>
     <t xml:space="preserve">7.28580617904663</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34268236160278</t>
+    <t xml:space="preserve">7.34268283843994</t>
   </si>
   <si>
     <t xml:space="preserve">7.45643329620361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45074605941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680673599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24599361419678</t>
+    <t xml:space="preserve">7.45074701309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24599266052246</t>
   </si>
   <si>
     <t xml:space="preserve">7.3199315071106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38249540328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37112045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575265884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750343322754</t>
+    <t xml:space="preserve">7.38249397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37111902236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750200271606</t>
   </si>
   <si>
     <t xml:space="preserve">7.79200172424316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87731647491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89437866210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356315612793</t>
+    <t xml:space="preserve">7.87731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356172561646</t>
   </si>
   <si>
     <t xml:space="preserve">7.67256164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57587337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543226242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42799520492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48487234115601</t>
+    <t xml:space="preserve">7.57587432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3654317855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42799615859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48487186431885</t>
   </si>
   <si>
     <t xml:space="preserve">7.41093349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30286836624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755361557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98436403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00711441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85354995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05261468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13792896270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067981719971</t>
+    <t xml:space="preserve">7.30286979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755456924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98436260223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00711393356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85354900360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05261421203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13793039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067838668823</t>
   </si>
   <si>
     <t xml:space="preserve">7.43368339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4962477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4791841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743671417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862470626831</t>
+    <t xml:space="preserve">7.49624633789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862327575684</t>
   </si>
   <si>
     <t xml:space="preserve">7.75218915939331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83181476593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631496429443</t>
+    <t xml:space="preserve">7.83181571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631353378296</t>
   </si>
   <si>
     <t xml:space="preserve">7.85456562042236</t>
@@ -281,94 +281,94 @@
     <t xml:space="preserve">7.77493906021118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57018661499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387083053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35405683517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53606033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105278015137</t>
+    <t xml:space="preserve">7.57018613815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387178421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35405826568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53605890274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105182647705</t>
   </si>
   <si>
     <t xml:space="preserve">7.1663670539856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05830192565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11517906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8484525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94490051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85447931289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81228351593018</t>
+    <t xml:space="preserve">7.05830144882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11517953872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25168085098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798887252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994874954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84845399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90873193740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94489908218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85447978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81228303909302</t>
   </si>
   <si>
     <t xml:space="preserve">7.76406049728394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54705142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53499603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158437728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625629425049</t>
+    <t xml:space="preserve">7.54705286026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.534996509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158485412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625581741333</t>
   </si>
   <si>
     <t xml:space="preserve">7.77008867263794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42046403884888</t>
+    <t xml:space="preserve">7.42046499252319</t>
   </si>
   <si>
     <t xml:space="preserve">7.17934465408325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97439193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140100479126</t>
+    <t xml:space="preserve">6.97439241409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92014026641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140195846558</t>
   </si>
   <si>
     <t xml:space="preserve">7.40840864181519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54102373123169</t>
+    <t xml:space="preserve">7.54102420806885</t>
   </si>
   <si>
     <t xml:space="preserve">7.58322095870972</t>
@@ -380,31 +380,31 @@
     <t xml:space="preserve">6.02498292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11841726303101</t>
+    <t xml:space="preserve">6.11841773986816</t>
   </si>
   <si>
     <t xml:space="preserve">6.26308917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187379837036</t>
+    <t xml:space="preserve">6.35953569412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4318733215332</t>
   </si>
   <si>
     <t xml:space="preserve">6.25103282928467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1304726600647</t>
+    <t xml:space="preserve">6.13047361373901</t>
   </si>
   <si>
     <t xml:space="preserve">5.91647911071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92853546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967657089233</t>
+    <t xml:space="preserve">5.92853593826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967704772949</t>
   </si>
   <si>
     <t xml:space="preserve">6.43790197372437</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">6.76341247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69710445404053</t>
+    <t xml:space="preserve">6.69710540771484</t>
   </si>
   <si>
     <t xml:space="preserve">6.87191724777222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80560970306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8417763710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738430023193</t>
+    <t xml:space="preserve">6.80560922622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84177732467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738525390625</t>
   </si>
   <si>
     <t xml:space="preserve">6.8478045463562</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">6.77546834945679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73327302932739</t>
+    <t xml:space="preserve">6.73327350616455</t>
   </si>
   <si>
     <t xml:space="preserve">6.68504858016968</t>
@@ -446,34 +446,34 @@
     <t xml:space="preserve">6.62476873397827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10098075866699</t>
+    <t xml:space="preserve">7.10098123550415</t>
   </si>
   <si>
     <t xml:space="preserve">7.07084083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7935528755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06481266021729</t>
+    <t xml:space="preserve">6.79355335235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06481218338013</t>
   </si>
   <si>
     <t xml:space="preserve">7.20948553085327</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29387617111206</t>
+    <t xml:space="preserve">7.29387664794922</t>
   </si>
   <si>
     <t xml:space="preserve">7.29990386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34210014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08289527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000129699707</t>
+    <t xml:space="preserve">7.34210109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000177383423</t>
   </si>
   <si>
     <t xml:space="preserve">6.90808439254761</t>
@@ -485,94 +485,94 @@
     <t xml:space="preserve">7.04070043563843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01658964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81766557693481</t>
+    <t xml:space="preserve">7.0165901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8176646232605</t>
   </si>
   <si>
     <t xml:space="preserve">6.74532842636108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61271381378174</t>
+    <t xml:space="preserve">6.61271333694458</t>
   </si>
   <si>
     <t xml:space="preserve">6.78149700164795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94425296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247789382935</t>
+    <t xml:space="preserve">6.94425344467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247646331787</t>
   </si>
   <si>
     <t xml:space="preserve">6.93822479248047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88397216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523195266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770711898804</t>
+    <t xml:space="preserve">6.88397264480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9804220199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770807266235</t>
   </si>
   <si>
     <t xml:space="preserve">6.70313310623169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63079786300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72724390029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79958057403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75135707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59462833404541</t>
+    <t xml:space="preserve">6.63079643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79957914352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75135660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59462928771973</t>
   </si>
   <si>
     <t xml:space="preserve">6.56448936462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57654476165771</t>
+    <t xml:space="preserve">6.57654428482056</t>
   </si>
   <si>
     <t xml:space="preserve">6.60668563842773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54640340805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51626491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49818086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7694411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85985994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18537378311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16728925704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742822647095</t>
+    <t xml:space="preserve">6.5464038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51626634597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4981803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76944017410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986185073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383272171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1853723526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16728973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742918014526</t>
   </si>
   <si>
     <t xml:space="preserve">7.28784894943237</t>
@@ -581,70 +581,70 @@
     <t xml:space="preserve">7.26976490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33004426956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31196117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317655563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0949535369873</t>
+    <t xml:space="preserve">7.33004474639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31195974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1431770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09495162963867</t>
   </si>
   <si>
     <t xml:space="preserve">6.98644876480103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67299318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0889253616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07686805725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8779444694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02261638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8236927986145</t>
+    <t xml:space="preserve">6.67299270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08892488479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07686901092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87794589996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02261686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82369327545166</t>
   </si>
   <si>
     <t xml:space="preserve">7.43854808807373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35415649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73392009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6803150177002</t>
+    <t xml:space="preserve">7.35415697097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73391962051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68031597137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.45125102996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47536373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41508388519287</t>
+    <t xml:space="preserve">8.47536468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41508293151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.33069133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54167079925537</t>
+    <t xml:space="preserve">8.541672706604</t>
   </si>
   <si>
     <t xml:space="preserve">8.5597562789917</t>
@@ -653,67 +653,67 @@
     <t xml:space="preserve">8.6381196975708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5838680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59592437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6622314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6682596206665</t>
+    <t xml:space="preserve">8.58386707305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59592533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66223239898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66825866699219</t>
   </si>
   <si>
     <t xml:space="preserve">8.5537281036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5055046081543</t>
+    <t xml:space="preserve">8.50550270080566</t>
   </si>
   <si>
     <t xml:space="preserve">8.51153182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65017604827881</t>
+    <t xml:space="preserve">8.65017509460449</t>
   </si>
   <si>
     <t xml:space="preserve">8.71045684814453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75265312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69840049743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71648406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52358722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48742008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38494491577148</t>
+    <t xml:space="preserve">8.75265216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69839954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7164831161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52358818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48741912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38494396209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.25835704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23424434661865</t>
+    <t xml:space="preserve">8.23424339294434</t>
   </si>
   <si>
     <t xml:space="preserve">8.16793632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27041244506836</t>
+    <t xml:space="preserve">8.27041149139404</t>
   </si>
   <si>
     <t xml:space="preserve">8.26438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5898962020874</t>
+    <t xml:space="preserve">8.58989524841309</t>
   </si>
   <si>
     <t xml:space="preserve">9.2951717376709</t>
@@ -722,49 +722,49 @@
     <t xml:space="preserve">9.38559150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42175960540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28311634063721</t>
+    <t xml:space="preserve">9.4217586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28311538696289</t>
   </si>
   <si>
     <t xml:space="preserve">8.98774337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88526725769043</t>
+    <t xml:space="preserve">8.88526821136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.84910011291504</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00582790374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993869781494</t>
+    <t xml:space="preserve">9.00582695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993965148926</t>
   </si>
   <si>
     <t xml:space="preserve">8.81896018981934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77073764801025</t>
+    <t xml:space="preserve">8.77073669433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.67428779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7405948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90335273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04802417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87923908233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90938091278076</t>
+    <t xml:space="preserve">8.74059581756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04802513122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87924003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90937900543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.95760250091553</t>
@@ -773,58 +773,58 @@
     <t xml:space="preserve">8.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81293106079102</t>
+    <t xml:space="preserve">8.81293201446533</t>
   </si>
   <si>
     <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65620422363281</t>
+    <t xml:space="preserve">8.65620231628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.49947547912598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14985179901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27644062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54769897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46330738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56578350067139</t>
+    <t xml:space="preserve">8.14985275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27643966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54769992828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46330833435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5657844543457</t>
   </si>
   <si>
     <t xml:space="preserve">8.78882026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80087566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78279209136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86718368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98171520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80690383911133</t>
+    <t xml:space="preserve">8.80087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484844207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78279113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86718273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98171615600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80690288543701</t>
   </si>
   <si>
     <t xml:space="preserve">8.6320915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60798072814941</t>
+    <t xml:space="preserve">8.6079797744751</t>
   </si>
   <si>
     <t xml:space="preserve">8.46933650970459</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93349075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75867938995361</t>
+    <t xml:space="preserve">8.93349170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7586784362793</t>
   </si>
   <si>
     <t xml:space="preserve">8.87321186065674</t>
@@ -845,31 +845,31 @@
     <t xml:space="preserve">9.04199504852295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19269561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21078014373779</t>
+    <t xml:space="preserve">9.19269466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21077823638916</t>
   </si>
   <si>
     <t xml:space="preserve">9.2409200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21680736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94554710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89129638671875</t>
+    <t xml:space="preserve">9.2168083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94554805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89129543304443</t>
   </si>
   <si>
     <t xml:space="preserve">9.03596687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07213497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12036037445068</t>
+    <t xml:space="preserve">9.07213687896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12035942077637</t>
   </si>
   <si>
     <t xml:space="preserve">9.30493068695068</t>
@@ -878,91 +878,91 @@
     <t xml:space="preserve">9.33675289154053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18400573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15854835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13308906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851779937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83395671844482</t>
+    <t xml:space="preserve">9.18400382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15854740142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13308811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851875305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83395576477051</t>
   </si>
   <si>
     <t xml:space="preserve">8.94215393066406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03762149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81486320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75758171081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73848915100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89123725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95488262176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05035018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22855567932129</t>
+    <t xml:space="preserve">9.03762054443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81486225128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75758266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73848819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89123821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9548807144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0503511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22855758666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.2349214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1712760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28583717346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2985668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34948348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25401401519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219276428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24764919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29220294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33038711547852</t>
+    <t xml:space="preserve">9.17127513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28583812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29856586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3494815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25401496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24765014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29220199584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33038806915283</t>
   </si>
   <si>
     <t xml:space="preserve">9.38130569458008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57860469818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54678344726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54041862487793</t>
+    <t xml:space="preserve">9.57860660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54678249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54041767120361</t>
   </si>
   <si>
     <t xml:space="preserve">9.64861488342285</t>
@@ -977,43 +977,43 @@
     <t xml:space="preserve">9.71862506866455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68680286407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56587505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52769088745117</t>
+    <t xml:space="preserve">9.68680095672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56587791442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52768898010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.75681209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77590656280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750389099121</t>
+    <t xml:space="preserve">9.77590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750379562378</t>
   </si>
   <si>
     <t xml:space="preserve">10.0877676010132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1386823654175</t>
+    <t xml:space="preserve">10.1386833190918</t>
   </si>
   <si>
     <t xml:space="preserve">10.2341508865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1959667205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062310218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0050287246704</t>
+    <t xml:space="preserve">10.1959638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0623083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0050277709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.82682132720947</t>
@@ -1028,31 +1028,31 @@
     <t xml:space="preserve">9.82045745849609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87137317657471</t>
+    <t xml:space="preserve">9.87137222290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.78226947784424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71226024627686</t>
+    <t xml:space="preserve">9.71225929260254</t>
   </si>
   <si>
     <t xml:space="preserve">9.69953060150146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6804370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6931676864624</t>
+    <t xml:space="preserve">9.68043804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69316482543945</t>
   </si>
   <si>
     <t xml:space="preserve">9.66134452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53405380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52132415771484</t>
+    <t xml:space="preserve">9.53405284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52132511138916</t>
   </si>
   <si>
     <t xml:space="preserve">9.57224082946777</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">9.61679267883301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67407321929932</t>
+    <t xml:space="preserve">9.67407131195068</t>
   </si>
   <si>
     <t xml:space="preserve">9.62952136993408</t>
@@ -1070,61 +1070,61 @@
     <t xml:space="preserve">9.59769821166992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89046669006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94774627685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75044727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89683151245117</t>
+    <t xml:space="preserve">9.89046764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94774723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75044822692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89683055877686</t>
   </si>
   <si>
     <t xml:space="preserve">9.91592502593994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87773895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1323194503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93501949310303</t>
+    <t xml:space="preserve">9.8777379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0304861068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1323175430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93501758575439</t>
   </si>
   <si>
     <t xml:space="preserve">9.84591579437256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85228061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72498893737793</t>
+    <t xml:space="preserve">9.8522777557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83318519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72498798370361</t>
   </si>
   <si>
     <t xml:space="preserve">9.99866390228271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96047687530518</t>
+    <t xml:space="preserve">9.96047782897949</t>
   </si>
   <si>
     <t xml:space="preserve">10.0177574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9541130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1259546279907</t>
+    <t xml:space="preserve">9.95411205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1259536743164</t>
   </si>
   <si>
     <t xml:space="preserve">10.0241212844849</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">9.88410186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0368518829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78863430023193</t>
+    <t xml:space="preserve">10.0368499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78863525390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.63588619232178</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">9.58497047424316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61043071746826</t>
+    <t xml:space="preserve">9.61042785644531</t>
   </si>
   <si>
     <t xml:space="preserve">9.66770839691162</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">9.74408340454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73135280609131</t>
+    <t xml:space="preserve">9.73135375976562</t>
   </si>
   <si>
     <t xml:space="preserve">9.80772876739502</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">9.73771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589637756348</t>
+    <t xml:space="preserve">9.70589447021484</t>
   </si>
   <si>
     <t xml:space="preserve">9.5595121383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47677421569824</t>
+    <t xml:space="preserve">9.47677326202393</t>
   </si>
   <si>
     <t xml:space="preserve">9.97320556640625</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">10.055944442749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3041620254517</t>
+    <t xml:space="preserve">10.2914323806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.304160118103</t>
   </si>
   <si>
     <t xml:space="preserve">10.2023286819458</t>
@@ -1199,22 +1199,22 @@
     <t xml:space="preserve">10.310525894165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641416549683</t>
+    <t xml:space="preserve">10.3232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736879348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641407012939</t>
   </si>
   <si>
     <t xml:space="preserve">10.148229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99230003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7695426940918</t>
+    <t xml:space="preserve">9.9922981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76954174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.86819076538086</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">9.81727409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77908897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81409168243408</t>
+    <t xml:space="preserve">9.77908802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8140926361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.80454635620117</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">9.36857604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85546112060547</t>
+    <t xml:space="preserve">9.65179824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85546207427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.74726486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0082120895386</t>
+    <t xml:space="preserve">10.0082111358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.98593330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92865467071533</t>
+    <t xml:space="preserve">9.92865562438965</t>
   </si>
   <si>
     <t xml:space="preserve">9.94456577301025</t>
@@ -1259,40 +1259,40 @@
     <t xml:space="preserve">9.9700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.049578666687</t>
+    <t xml:space="preserve">10.0495796203613</t>
   </si>
   <si>
     <t xml:space="preserve">10.1609592437744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3137073516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2946128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455305099487</t>
+    <t xml:space="preserve">10.3137083053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2946147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455295562744</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.530101776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6382970809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7655897140503</t>
+    <t xml:space="preserve">10.5301008224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.638298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7655878067017</t>
   </si>
   <si>
     <t xml:space="preserve">10.8546924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6319351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178535461426</t>
+    <t xml:space="preserve">10.6319341659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178544998169</t>
   </si>
   <si>
     <t xml:space="preserve">10.5841989517212</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">10.6542100906372</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7083082199097</t>
+    <t xml:space="preserve">10.7083072662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796684265137</t>
+    <t xml:space="preserve">10.6796674728394</t>
   </si>
   <si>
     <t xml:space="preserve">10.5269193649292</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">10.5396480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4409980773926</t>
+    <t xml:space="preserve">10.4409990310669</t>
   </si>
   <si>
     <t xml:space="preserve">10.5014610290527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5078248977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2977962493896</t>
+    <t xml:space="preserve">10.5078258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.297797203064</t>
   </si>
   <si>
     <t xml:space="preserve">10.3328018188477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2596101760864</t>
+    <t xml:space="preserve">10.2596092224121</t>
   </si>
   <si>
     <t xml:space="preserve">10.2864847183228</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">10.252890586853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1319522857666</t>
+    <t xml:space="preserve">10.1319513320923</t>
   </si>
   <si>
     <t xml:space="preserve">10.0143737792969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.994215965271</t>
+    <t xml:space="preserve">9.99421691894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.83968448638916</t>
@@ -1355,97 +1355,97 @@
     <t xml:space="preserve">9.49702644348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55413627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77585411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88335800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8699197769165</t>
+    <t xml:space="preserve">9.5541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77585601806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88335514068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86991786956787</t>
   </si>
   <si>
     <t xml:space="preserve">9.65491771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67843151092529</t>
+    <t xml:space="preserve">9.67843246459961</t>
   </si>
   <si>
     <t xml:space="preserve">9.52054214477539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79937267303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75234127044678</t>
+    <t xml:space="preserve">9.79937171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75234031677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.78257465362549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90015411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80609035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76241683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82960605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69858837127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76913547515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60116577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61796474456787</t>
+    <t xml:space="preserve">9.90015316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80609130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76241779327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8296070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69859027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76913738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60116672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61796379089355</t>
   </si>
   <si>
     <t xml:space="preserve">9.52390003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51718139648438</t>
+    <t xml:space="preserve">9.51718235015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.61124515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59108829498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80945110321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77249526977539</t>
+    <t xml:space="preserve">9.59108924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80945014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77249717712402</t>
   </si>
   <si>
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65155792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163730621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70530796051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84976100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85648155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81616973876953</t>
+    <t xml:space="preserve">9.6515588760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70530891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84976196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85648059844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8161678314209</t>
   </si>
   <si>
     <t xml:space="preserve">9.74898052215576</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">9.89007568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9035120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92366790771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070217132568</t>
+    <t xml:space="preserve">9.90351390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92366886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070026397705</t>
   </si>
   <si>
     <t xml:space="preserve">10.0479679107666</t>
@@ -1469,52 +1469,52 @@
     <t xml:space="preserve">10.2125768661499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.111795425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95390510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0378885269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0009355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0681228637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916404724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0748424530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86655902862549</t>
+    <t xml:space="preserve">10.1117963790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95390319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0378875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.000937461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0681238174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916385650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0748414993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8665599822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.71202754974365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312080383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92702865600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98077774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92030906677246</t>
+    <t xml:space="preserve">9.73218250274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312175750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92702770233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98077964782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92031002044678</t>
   </si>
   <si>
     <t xml:space="preserve">9.63812160491943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76577663421631</t>
+    <t xml:space="preserve">9.76577758789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.93710613250732</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">9.9606237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94382572174072</t>
+    <t xml:space="preserve">9.94382667541504</t>
   </si>
   <si>
     <t xml:space="preserve">10.1621866226196</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">10.1017179489136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0882806777954</t>
+    <t xml:space="preserve">10.0882797241211</t>
   </si>
   <si>
     <t xml:space="preserve">10.1554679870605</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">10.2965621948242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4141426086426</t>
+    <t xml:space="preserve">10.4141416549683</t>
   </si>
   <si>
     <t xml:space="preserve">10.4309396743774</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">10.3704690933228</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99757671356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88671779632568</t>
+    <t xml:space="preserve">9.9975757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88671588897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.96734142303467</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">9.70866870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69186973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59444904327393</t>
+    <t xml:space="preserve">9.69187164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59444808959961</t>
   </si>
   <si>
     <t xml:space="preserve">9.50038433074951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61460494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56421375274658</t>
+    <t xml:space="preserve">9.61460399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56421279907227</t>
   </si>
   <si>
     <t xml:space="preserve">9.41304111480713</t>
@@ -1592,16 +1592,16 @@
     <t xml:space="preserve">9.43991565704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40968132019043</t>
+    <t xml:space="preserve">9.40968227386475</t>
   </si>
   <si>
     <t xml:space="preserve">9.288743019104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2383508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43655586242676</t>
+    <t xml:space="preserve">9.23835277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43655681610107</t>
   </si>
   <si>
     <t xml:space="preserve">9.3324146270752</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">9.53397941589355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66499710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62468338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65827655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6347599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57429218292236</t>
+    <t xml:space="preserve">9.66499614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62468242645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65827751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63476085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57429122924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.71538639068604</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">9.59780788421631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5574951171875</t>
+    <t xml:space="preserve">9.55749416351318</t>
   </si>
   <si>
     <t xml:space="preserve">9.57765102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81952857971191</t>
+    <t xml:space="preserve">9.8195276260376</t>
   </si>
   <si>
     <t xml:space="preserve">9.87663745880127</t>
@@ -1655,52 +1655,52 @@
     <t xml:space="preserve">10.0042953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0849208831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97406101226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57093143463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64483833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562168121338</t>
+    <t xml:space="preserve">10.084921836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97405910491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57093238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6448392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562072753906</t>
   </si>
   <si>
     <t xml:space="preserve">9.89679431915283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85984039306641</t>
+    <t xml:space="preserve">9.85984134674072</t>
   </si>
   <si>
     <t xml:space="preserve">9.95054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0210933685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0446081161499</t>
+    <t xml:space="preserve">10.021092414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0446071624756</t>
   </si>
   <si>
     <t xml:space="preserve">10.0647640228271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327346801758</t>
+    <t xml:space="preserve">10.2327327728271</t>
   </si>
   <si>
     <t xml:space="preserve">10.3267974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3435964584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898426055908</t>
+    <t xml:space="preserve">10.3435945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898435592651</t>
   </si>
   <si>
     <t xml:space="preserve">10.3335161209106</t>
@@ -1712,25 +1712,25 @@
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771867752075</t>
+    <t xml:space="preserve">10.3771896362305</t>
   </si>
   <si>
     <t xml:space="preserve">10.276406288147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1991405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2461719512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932024002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714826583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1285934448242</t>
+    <t xml:space="preserve">10.1991415023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2461709976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932033538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714817047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1285924911499</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058591842651</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">10.2293748855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730474472046</t>
+    <t xml:space="preserve">10.2260141372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730464935303</t>
   </si>
   <si>
     <t xml:space="preserve">10.3805475234985</t>
@@ -1760,61 +1760,61 @@
     <t xml:space="preserve">10.4342975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5451583862305</t>
+    <t xml:space="preserve">10.5451574325562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6089868545532</t>
   </si>
   <si>
-    <t xml:space="preserve">10.672815322876</t>
+    <t xml:space="preserve">10.6728162765503</t>
   </si>
   <si>
     <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7400045394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.565315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6157054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5921907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6224250793457</t>
+    <t xml:space="preserve">10.7400035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123476028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5653162002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6157064437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5921897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6224241256714</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534418106079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9785203933716</t>
+    <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
     <t xml:space="preserve">11.0725841522217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0591459274292</t>
+    <t xml:space="preserve">11.0591468811035</t>
   </si>
   <si>
     <t xml:space="preserve">11.0322713851929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0692253112793</t>
+    <t xml:space="preserve">11.069224357605</t>
   </si>
   <si>
     <t xml:space="preserve">10.9852409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9718017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0087566375732</t>
+    <t xml:space="preserve">10.9718027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0087556838989</t>
   </si>
   <si>
     <t xml:space="preserve">11.0860223770142</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">11.1767263412476</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2304754257202</t>
+    <t xml:space="preserve">11.2304763793945</t>
   </si>
   <si>
     <t xml:space="preserve">11.2237577438354</t>
@@ -1838,49 +1838,49 @@
     <t xml:space="preserve">11.2170381546021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2002410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2271156311035</t>
+    <t xml:space="preserve">11.2002420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2271175384521</t>
   </si>
   <si>
     <t xml:space="preserve">11.297664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.35813331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4219608306885</t>
+    <t xml:space="preserve">11.3581342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4219636917114</t>
   </si>
   <si>
     <t xml:space="preserve">11.5563383102417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521970748901</t>
+    <t xml:space="preserve">11.4521961212158</t>
   </si>
   <si>
     <t xml:space="preserve">11.4286804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622735977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.583212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5529766082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6235246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6201677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6302442550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5261039733887</t>
+    <t xml:space="preserve">11.4622745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5832138061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.552978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6235256195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6201658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.526104927063</t>
   </si>
   <si>
     <t xml:space="preserve">11.4824314117432</t>
@@ -1889,34 +1889,34 @@
     <t xml:space="preserve">11.4689931869507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3245410919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.415244102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093050003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4253196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5636587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5849418640137</t>
+    <t xml:space="preserve">11.3245391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4253206253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5636596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.584942817688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5601119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3189077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5459222793579</t>
+    <t xml:space="preserve">11.3189067840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5459241867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.414680480957</t>
@@ -1925,10 +1925,10 @@
     <t xml:space="preserve">11.3330955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763423919678</t>
+    <t xml:space="preserve">11.2124929428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">11.1486444473267</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">11.1238145828247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2727956771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1805696487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2195854187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2479648590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3366432189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4536981582642</t>
+    <t xml:space="preserve">11.2727947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1805686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2195873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2479639053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3366422653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4537000656128</t>
   </si>
   <si>
     <t xml:space="preserve">11.4288692474365</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4785261154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4466047286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5175466537476</t>
+    <t xml:space="preserve">11.4785289764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4466037750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5175476074219</t>
   </si>
   <si>
     <t xml:space="preserve">11.7445650100708</t>
@@ -1973,43 +1973,43 @@
     <t xml:space="preserve">11.8119592666626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8332424163818</t>
+    <t xml:space="preserve">11.8332414627075</t>
   </si>
   <si>
     <t xml:space="preserve">11.8403358459473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.787127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7481098175049</t>
+    <t xml:space="preserve">11.7871284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7481107711792</t>
   </si>
   <si>
     <t xml:space="preserve">11.7126388549805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935403823853</t>
+    <t xml:space="preserve">11.7977705001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935422897339</t>
   </si>
   <si>
     <t xml:space="preserve">12.1063709259033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1312017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0708980560303</t>
+    <t xml:space="preserve">12.1312007904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0708999633789</t>
   </si>
   <si>
     <t xml:space="preserve">12.1418418884277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1773157119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2092370986938</t>
+    <t xml:space="preserve">12.1773138046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2092380523682</t>
   </si>
   <si>
     <t xml:space="preserve">12.2056903839111</t>
@@ -2021,37 +2021,37 @@
     <t xml:space="preserve">12.1808605194092</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1170110702515</t>
+    <t xml:space="preserve">12.1170129776001</t>
   </si>
   <si>
     <t xml:space="preserve">11.989315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0247888565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0105981826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0567111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9751272201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.996410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8545236587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9467496871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573926925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6629800796509</t>
+    <t xml:space="preserve">12.0247869491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105991363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0567121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9751262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9964113235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8545246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9467506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6629791259766</t>
   </si>
   <si>
     <t xml:space="preserve">11.5884885787964</t>
@@ -2060,52 +2060,52 @@
     <t xml:space="preserve">11.5707530975342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6594314575195</t>
+    <t xml:space="preserve">11.6594305038452</t>
   </si>
   <si>
     <t xml:space="preserve">11.3437366485596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3792095184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430561065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2940769195557</t>
+    <t xml:space="preserve">11.3792085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.29407787323</t>
   </si>
   <si>
     <t xml:space="preserve">11.4749803543091</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5069046020508</t>
+    <t xml:space="preserve">11.5069055557251</t>
   </si>
   <si>
     <t xml:space="preserve">11.6168661117554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5778493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4678869247437</t>
+    <t xml:space="preserve">11.5778474807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4678888320923</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820756912231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6558856964111</t>
+    <t xml:space="preserve">11.6558847427368</t>
   </si>
   <si>
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487903594971</t>
+    <t xml:space="preserve">11.6487894058228</t>
   </si>
   <si>
     <t xml:space="preserve">11.6842613220215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7090902328491</t>
+    <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
     <t xml:space="preserve">11.7374687194824</t>
@@ -2120,46 +2120,46 @@
     <t xml:space="preserve">12.134747505188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2021427154541</t>
+    <t xml:space="preserve">12.2021436691284</t>
   </si>
   <si>
     <t xml:space="preserve">12.1844072341919</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3014631271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4149713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.397234916687</t>
+    <t xml:space="preserve">12.3014640808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4149723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3972368240356</t>
   </si>
   <si>
     <t xml:space="preserve">12.3262929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2908210754395</t>
+    <t xml:space="preserve">12.2908229827881</t>
   </si>
   <si>
     <t xml:space="preserve">12.6881017684937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6597242355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058362960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6739120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.741307258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6987428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6703643798828</t>
+    <t xml:space="preserve">12.6597232818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058382034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6739130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7413091659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6987438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6703653335571</t>
   </si>
   <si>
     <t xml:space="preserve">12.6136121749878</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">12.5852346420288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3759517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5213861465454</t>
+    <t xml:space="preserve">12.3759527206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5213851928711</t>
   </si>
   <si>
     <t xml:space="preserve">12.606517791748</t>
@@ -2186,25 +2186,25 @@
     <t xml:space="preserve">12.6490821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6774597167969</t>
+    <t xml:space="preserve">12.6774616241455</t>
   </si>
   <si>
     <t xml:space="preserve">12.8157978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7448558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441753387451</t>
+    <t xml:space="preserve">12.7448568344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441743850708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8477230072021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8406286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080219268799</t>
+    <t xml:space="preserve">12.8406276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080238342285</t>
   </si>
   <si>
     <t xml:space="preserve">13.0357208251953</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">13.0463600158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0534563064575</t>
+    <t xml:space="preserve">13.0534553527832</t>
   </si>
   <si>
     <t xml:space="preserve">13.0499095916748</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0286254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9364023208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8938341140747</t>
+    <t xml:space="preserve">13.0286264419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9364013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938331604004</t>
   </si>
   <si>
     <t xml:space="preserve">13.1243991851807</t>
@@ -2237,61 +2237,61 @@
     <t xml:space="preserve">13.1882467269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917934417725</t>
+    <t xml:space="preserve">13.1917943954468</t>
   </si>
   <si>
     <t xml:space="preserve">13.6422805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6068077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139059066772</t>
+    <t xml:space="preserve">13.6068105697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139049530029</t>
   </si>
   <si>
     <t xml:space="preserve">13.8338251113892</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7167692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997123718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145816802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.266284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237176895142</t>
+    <t xml:space="preserve">13.7167711257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997152328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145845413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2662839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237186431885</t>
   </si>
   <si>
     <t xml:space="preserve">13.2343597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1527767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2591896057129</t>
+    <t xml:space="preserve">13.152777671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2591905593872</t>
   </si>
   <si>
     <t xml:space="preserve">13.2627372741699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1456823348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9754199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9399480819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9186658859253</t>
+    <t xml:space="preserve">13.1456813812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9754190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612302780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9399461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9186630249023</t>
   </si>
   <si>
     <t xml:space="preserve">12.9257593154907</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">12.9541358947754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0250806808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0108909606934</t>
+    <t xml:space="preserve">13.0250797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0108890533447</t>
   </si>
   <si>
     <t xml:space="preserve">13.1137580871582</t>
@@ -2312,43 +2312,43 @@
     <t xml:space="preserve">13.1314926147461</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1776065826416</t>
+    <t xml:space="preserve">13.1776056289673</t>
   </si>
   <si>
     <t xml:space="preserve">13.1208524703979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4613761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520952224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.06409740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1031169891357</t>
+    <t xml:space="preserve">13.4613752365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520961761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0640983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1031160354614</t>
   </si>
   <si>
     <t xml:space="preserve">13.0747394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9115715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9789667129517</t>
+    <t xml:space="preserve">12.9115705490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9789657592773</t>
   </si>
   <si>
     <t xml:space="preserve">12.9860601425171</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9505882263184</t>
+    <t xml:space="preserve">12.950587272644</t>
   </si>
   <si>
     <t xml:space="preserve">12.8654584884644</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">12.7235717773438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8690052032471</t>
+    <t xml:space="preserve">12.8690032958984</t>
   </si>
   <si>
     <t xml:space="preserve">12.571044921875</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">12.9434947967529</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6916484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4823656082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5462160110474</t>
+    <t xml:space="preserve">12.6916475296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4823665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546215057373</t>
   </si>
   <si>
     <t xml:space="preserve">12.7306671142578</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">13.0002479553223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0818319320679</t>
+    <t xml:space="preserve">13.0818338394165</t>
   </si>
   <si>
     <t xml:space="preserve">13.2804727554321</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">13.3194904327393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3230381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3939800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3688592910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2979154586792</t>
+    <t xml:space="preserve">13.3230390548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3939809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3688583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2979145050049</t>
   </si>
   <si>
     <t xml:space="preserve">12.2482557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5352821350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4004907608032</t>
+    <t xml:space="preserve">11.5352830886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4004917144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.1628332138062</t>
@@ -2417,49 +2417,49 @@
     <t xml:space="preserve">10.8116664886475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76171493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61273574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36769104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56278324127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01297664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69728326797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36739921569824</t>
+    <t xml:space="preserve">9.76171588897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61273670196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36769199371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56278228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01297855377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6972827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36739826202393</t>
   </si>
   <si>
     <t xml:space="preserve">7.61569786071777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72565937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72920703887939</t>
+    <t xml:space="preserve">7.72566032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72920656204224</t>
   </si>
   <si>
     <t xml:space="preserve">8.58406639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83236598968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98134517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77915954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77206325531006</t>
+    <t xml:space="preserve">8.83236694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98134422302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77915859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77206516265869</t>
   </si>
   <si>
     <t xml:space="preserve">8.80398845672607</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">8.5805196762085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74723529815674</t>
+    <t xml:space="preserve">8.74723434448242</t>
   </si>
   <si>
     <t xml:space="preserve">8.64436817169189</t>
@@ -2477,49 +2477,49 @@
     <t xml:space="preserve">8.89976119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07002258300781</t>
+    <t xml:space="preserve">9.07002449035645</t>
   </si>
   <si>
     <t xml:space="preserve">9.13032531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31832408905029</t>
+    <t xml:space="preserve">9.31832218170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.93877983093262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78979969024658</t>
+    <t xml:space="preserve">8.7898006439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.88911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63017845153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8430061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04164695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20126819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43537902832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23319244384766</t>
+    <t xml:space="preserve">8.6301794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84300804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77561092376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04164600372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20126914978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.435378074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23319149017334</t>
   </si>
   <si>
     <t xml:space="preserve">9.00972270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.176438331604</t>
+    <t xml:space="preserve">9.17643928527832</t>
   </si>
   <si>
     <t xml:space="preserve">9.03455257415771</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">9.0948543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20481395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12323093414307</t>
+    <t xml:space="preserve">9.20481491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12323188781738</t>
   </si>
   <si>
     <t xml:space="preserve">9.08421325683594</t>
@@ -2540,58 +2540,58 @@
     <t xml:space="preserve">8.91040325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80044078826904</t>
+    <t xml:space="preserve">8.80043983459473</t>
   </si>
   <si>
     <t xml:space="preserve">9.17269134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01014709472656</t>
+    <t xml:space="preserve">9.01014614105225</t>
   </si>
   <si>
     <t xml:space="preserve">9.05817127227783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78849601745605</t>
+    <t xml:space="preserve">8.78849506378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.99536895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96212291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20963191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43867206573486</t>
+    <t xml:space="preserve">8.96212196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20963287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43867301940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.22440910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52363967895508</t>
+    <t xml:space="preserve">9.52364063262939</t>
   </si>
   <si>
     <t xml:space="preserve">9.81178665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3031139373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3474464416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6282062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6540632247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5395431518555</t>
+    <t xml:space="preserve">10.3031148910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3474454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6282043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5395450592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.3215856552124</t>
@@ -2603,16 +2603,16 @@
     <t xml:space="preserve">9.91891860961914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90414237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1257944107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.051908493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92630672454834</t>
+    <t xml:space="preserve">9.90414142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1257934570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0519094467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92630767822266</t>
   </si>
   <si>
     <t xml:space="preserve">10.0592975616455</t>
@@ -2621,16 +2621,16 @@
     <t xml:space="preserve">10.0703802108765</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80070495605469</t>
+    <t xml:space="preserve">9.80070400238037</t>
   </si>
   <si>
     <t xml:space="preserve">9.82656383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9152250289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95216751098633</t>
+    <t xml:space="preserve">9.91522407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95216655731201</t>
   </si>
   <si>
     <t xml:space="preserve">9.94847297668457</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">10.2218427658081</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1553478240967</t>
+    <t xml:space="preserve">10.1553468704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.2587842941284</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">10.1627359390259</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89675331115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063732147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0777683258057</t>
+    <t xml:space="preserve">9.89675426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.07776927948</t>
   </si>
   <si>
     <t xml:space="preserve">10.1294870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070646286011</t>
+    <t xml:space="preserve">10.2070655822754</t>
   </si>
   <si>
     <t xml:space="preserve">10.2107601165771</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">10.114709854126</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1812057495117</t>
+    <t xml:space="preserve">10.1812076568604</t>
   </si>
   <si>
     <t xml:space="preserve">10.3289737701416</t>
@@ -2681,16 +2681,16 @@
     <t xml:space="preserve">10.0408267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98541450500488</t>
+    <t xml:space="preserve">9.9854154586792</t>
   </si>
   <si>
     <t xml:space="preserve">9.97433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46453380584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35370635986328</t>
+    <t xml:space="preserve">9.46453285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35370540618896</t>
   </si>
   <si>
     <t xml:space="preserve">9.40911960601807</t>
@@ -2702,31 +2702,31 @@
     <t xml:space="preserve">9.63077163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38695430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78592777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7305154800415</t>
+    <t xml:space="preserve">9.38695335388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78592681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73051357269287</t>
   </si>
   <si>
     <t xml:space="preserve">9.68618392944336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53841590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70835018157959</t>
+    <t xml:space="preserve">9.53841686248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70834827423096</t>
   </si>
   <si>
     <t xml:space="preserve">9.62707614898682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56058120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76376247406006</t>
+    <t xml:space="preserve">9.56058216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76376152038574</t>
   </si>
   <si>
     <t xml:space="preserve">9.81917572021484</t>
@@ -2738,34 +2738,34 @@
     <t xml:space="preserve">9.60860538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62338161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61968803405762</t>
+    <t xml:space="preserve">9.62338256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61968898773193</t>
   </si>
   <si>
     <t xml:space="preserve">9.57535839080811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47192096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37217807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56796932220459</t>
+    <t xml:space="preserve">9.47192001342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37217712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56797027587891</t>
   </si>
   <si>
     <t xml:space="preserve">9.48669815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47561359405518</t>
+    <t xml:space="preserve">9.47561550140381</t>
   </si>
   <si>
     <t xml:space="preserve">9.46083927154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36478900909424</t>
+    <t xml:space="preserve">9.36478805541992</t>
   </si>
   <si>
     <t xml:space="preserve">9.1061954498291</t>
@@ -2774,52 +2774,52 @@
     <t xml:space="preserve">8.75155258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70352649688721</t>
+    <t xml:space="preserve">8.70352745056152</t>
   </si>
   <si>
     <t xml:space="preserve">8.66658496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59639644622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86976623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88454341888428</t>
+    <t xml:space="preserve">8.59639739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86976718902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81804847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88454246520996</t>
   </si>
   <si>
     <t xml:space="preserve">8.76632881164551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91779136657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14313793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1135835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29829406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24288177490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22071552276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12466716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12097263336182</t>
+    <t xml:space="preserve">8.91779041290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14313697814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11358261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2982931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24287986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2207145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1209716796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.80327129364014</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">8.96951007843018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01753425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03969860076904</t>
+    <t xml:space="preserve">9.01753520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03969955444336</t>
   </si>
   <si>
     <t xml:space="preserve">8.81435298919678</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">8.82543563842773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91040229797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77371692657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39321517944336</t>
+    <t xml:space="preserve">8.91040420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77371788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39321422576904</t>
   </si>
   <si>
     <t xml:space="preserve">8.41907501220703</t>
@@ -2855,22 +2855,22 @@
     <t xml:space="preserve">8.50404167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72199821472168</t>
+    <t xml:space="preserve">8.721999168396</t>
   </si>
   <si>
     <t xml:space="preserve">8.89193153381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01383972167969</t>
+    <t xml:space="preserve">9.013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.14683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7231273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95955371856689</t>
+    <t xml:space="preserve">9.72312545776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95955467224121</t>
   </si>
   <si>
     <t xml:space="preserve">9.9447774887085</t>
@@ -2879,34 +2879,34 @@
     <t xml:space="preserve">10.0740747451782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3178911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4398012161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5136833190918</t>
+    <t xml:space="preserve">10.317892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4398002624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5136842727661</t>
   </si>
   <si>
     <t xml:space="preserve">10.3954696655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.495213508606</t>
+    <t xml:space="preserve">10.4952125549316</t>
   </si>
   <si>
     <t xml:space="preserve">10.5062961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6245107650757</t>
+    <t xml:space="preserve">10.6245098114014</t>
   </si>
   <si>
     <t xml:space="preserve">10.7094764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6910057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5801801681519</t>
+    <t xml:space="preserve">10.6910047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5801792144775</t>
   </si>
   <si>
     <t xml:space="preserve">10.6577577590942</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">10.713171005249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6097316741943</t>
+    <t xml:space="preserve">10.6097326278687</t>
   </si>
   <si>
     <t xml:space="preserve">10.5838737487793</t>
@@ -2927,34 +2927,34 @@
     <t xml:space="preserve">10.6060390472412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4065542221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5358505249023</t>
+    <t xml:space="preserve">10.4065532684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.535849571228</t>
   </si>
   <si>
     <t xml:space="preserve">10.5506267547607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5617074966431</t>
+    <t xml:space="preserve">10.5617094039917</t>
   </si>
   <si>
     <t xml:space="preserve">10.2624788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4176359176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134271621704</t>
+    <t xml:space="preserve">10.4176349639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134262084961</t>
   </si>
   <si>
     <t xml:space="preserve">10.5764856338501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6983938217163</t>
+    <t xml:space="preserve">10.280948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.698392868042</t>
   </si>
   <si>
     <t xml:space="preserve">10.7464189529419</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">10.942211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8276901245117</t>
+    <t xml:space="preserve">10.827691078186</t>
   </si>
   <si>
     <t xml:space="preserve">10.7205600738525</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">10.6429805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4102468490601</t>
+    <t xml:space="preserve">10.4102478027344</t>
   </si>
   <si>
     <t xml:space="preserve">10.5321559906006</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">10.6946992874146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0456485748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3929023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4778699874878</t>
+    <t xml:space="preserve">11.0456476211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3929033279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4778690338135</t>
   </si>
   <si>
     <t xml:space="preserve">11.6145544052124</t>
@@ -3011,19 +3011,19 @@
     <t xml:space="preserve">11.599778175354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5739183425903</t>
+    <t xml:space="preserve">11.5739192962646</t>
   </si>
   <si>
     <t xml:space="preserve">11.6921329498291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.63671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5665302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4002923965454</t>
+    <t xml:space="preserve">11.6367197036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5665311813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111179351807</t>
@@ -3038,46 +3038,46 @@
     <t xml:space="preserve">11.5000343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6995220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4889526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6958284378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7290744781494</t>
+    <t xml:space="preserve">11.6995210647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4889516830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6958265304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7290735244751</t>
   </si>
   <si>
     <t xml:space="preserve">11.8435945510864</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8768434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8251237869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1908502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2130146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2795124053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3866395950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4900808334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4383602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4789953231812</t>
+    <t xml:space="preserve">11.8768444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.825122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1908493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2130155563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2795104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3866415023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4900798797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4383592605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4789972305298</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755598068237</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">12.360782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4161958694458</t>
+    <t xml:space="preserve">12.4161968231201</t>
   </si>
   <si>
     <t xml:space="preserve">12.412501335144</t>
@@ -3098,52 +3098,52 @@
     <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048561096191</t>
+    <t xml:space="preserve">12.5048551559448</t>
   </si>
   <si>
     <t xml:space="preserve">12.6045989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6637058258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5824356079102</t>
+    <t xml:space="preserve">12.66370677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5824337005615</t>
   </si>
   <si>
     <t xml:space="preserve">12.6600122451782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6858711242676</t>
+    <t xml:space="preserve">12.6858720779419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6378469467163</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5344095230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6119871139526</t>
+    <t xml:space="preserve">12.5344104766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.611988067627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6230697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5787401199341</t>
+    <t xml:space="preserve">12.5787391662598</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489305496216</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265090942383</t>
+    <t xml:space="preserve">12.726508140564</t>
   </si>
   <si>
     <t xml:space="preserve">12.4457483291626</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4679145812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3977251052856</t>
+    <t xml:space="preserve">12.4679136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3977241516113</t>
   </si>
   <si>
     <t xml:space="preserve">12.3275346755981</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">12.5602693557739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4420547485352</t>
+    <t xml:space="preserve">12.4420557022095</t>
   </si>
   <si>
     <t xml:space="preserve">12.5972108840942</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">12.9740190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631944656372</t>
+    <t xml:space="preserve">12.8631935119629</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149131774902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9592418670654</t>
+    <t xml:space="preserve">12.9592437744141</t>
   </si>
   <si>
     <t xml:space="preserve">13.0331268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0368204116821</t>
+    <t xml:space="preserve">13.0368213653564</t>
   </si>
   <si>
     <t xml:space="preserve">13.0626802444458</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">12.881664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8890514373779</t>
+    <t xml:space="preserve">12.8890523910522</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2438173294067</t>
+    <t xml:space="preserve">13.2438163757324</t>
   </si>
   <si>
     <t xml:space="preserve">13.1184320449829</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">13.0910043716431</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2007160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.177206993103</t>
+    <t xml:space="preserve">13.2007150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1772060394287</t>
   </si>
   <si>
     <t xml:space="preserve">13.2673273086548</t>
@@ -3218,25 +3218,25 @@
     <t xml:space="preserve">13.2830009460449</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3887939453125</t>
+    <t xml:space="preserve">13.3887929916382</t>
   </si>
   <si>
     <t xml:space="preserve">13.5180969238281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4985074996948</t>
+    <t xml:space="preserve">13.4985065460205</t>
   </si>
   <si>
     <t xml:space="preserve">13.4632415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4201412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4318943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397315979004</t>
+    <t xml:space="preserve">13.4201402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4318952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397306442261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4514875411987</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">13.0518217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3339366912842</t>
+    <t xml:space="preserve">13.3339385986328</t>
   </si>
   <si>
     <t xml:space="preserve">13.1262683868408</t>
@@ -3266,55 +3266,55 @@
     <t xml:space="preserve">13.1732873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2477369308472</t>
+    <t xml:space="preserve">13.2477359771729</t>
   </si>
   <si>
     <t xml:space="preserve">13.3731203079224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3221836090088</t>
+    <t xml:space="preserve">13.3221826553345</t>
   </si>
   <si>
     <t xml:space="preserve">13.4358139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1967992782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9852104187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3261003494263</t>
+    <t xml:space="preserve">13.196798324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9852113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3261013031006</t>
   </si>
   <si>
     <t xml:space="preserve">13.3300199508667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2634077072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1654510498047</t>
+    <t xml:space="preserve">13.2634086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1654500961304</t>
   </si>
   <si>
     <t xml:space="preserve">13.1145143508911</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7148475646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441524505615</t>
+    <t xml:space="preserve">12.7148494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441505432129</t>
   </si>
   <si>
     <t xml:space="preserve">13.122350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1576147079468</t>
+    <t xml:space="preserve">13.1576166152954</t>
   </si>
   <si>
     <t xml:space="preserve">13.1301870346069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2046337127686</t>
+    <t xml:space="preserve">13.2046346664429</t>
   </si>
   <si>
     <t xml:space="preserve">13.0674934387207</t>
@@ -3323,43 +3323,43 @@
     <t xml:space="preserve">12.9891300201416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0283126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2281427383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2947559356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
+    <t xml:space="preserve">13.0283117294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2281436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2947549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456926345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749965667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5690364837646</t>
+    <t xml:space="preserve">13.569034576416</t>
   </si>
   <si>
     <t xml:space="preserve">13.6160545349121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5376892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5416078567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3770389556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4436521530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4240570068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848762512207</t>
+    <t xml:space="preserve">13.5376882553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5416069030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3770399093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4436502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4240579605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848752975464</t>
   </si>
   <si>
     <t xml:space="preserve">13.4123029708862</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">13.5337715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5964641571045</t>
+    <t xml:space="preserve">13.5964632034302</t>
   </si>
   <si>
     <t xml:space="preserve">13.6121368408203</t>
@@ -3389,40 +3389,40 @@
     <t xml:space="preserve">13.6591558456421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8315591812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7923784255981</t>
+    <t xml:space="preserve">13.8315601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7923774719238</t>
   </si>
   <si>
     <t xml:space="preserve">13.8824987411499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0039672851562</t>
+    <t xml:space="preserve">14.0039663314819</t>
   </si>
   <si>
     <t xml:space="preserve">13.8589878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6748294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0901679992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2037973403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3644485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5956268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3017568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349784851074</t>
+    <t xml:space="preserve">13.6748304367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0901689529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2037982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.364447593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.595627784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3017549514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349775314331</t>
   </si>
   <si>
     <t xml:space="preserve">14.4114665985107</t>
@@ -3431,94 +3431,94 @@
     <t xml:space="preserve">14.4271402359009</t>
   </si>
   <si>
-    <t xml:space="preserve">14.399712562561</t>
+    <t xml:space="preserve">14.3997135162354</t>
   </si>
   <si>
     <t xml:space="preserve">14.6896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014198303223</t>
+    <t xml:space="preserve">14.5642786026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014207839966</t>
   </si>
   <si>
     <t xml:space="preserve">14.7288484573364</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8072156906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8816623687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6622371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6739950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7249298095703</t>
+    <t xml:space="preserve">14.8072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8816614151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6622362136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6739921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7249317169189</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851800918579</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8494462966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739589691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9217472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141286849976</t>
+    <t xml:space="preserve">14.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739618301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.921745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9538774490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141277313232</t>
   </si>
   <si>
     <t xml:space="preserve">15.1185598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0663433074951</t>
+    <t xml:space="preserve">15.0663423538208</t>
   </si>
   <si>
     <t xml:space="preserve">15.1346263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310266494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.247091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3234081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2591400146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3475065231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2430753707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2511081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2792253494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3836545944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3716077804565</t>
+    <t xml:space="preserve">15.1426591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310247421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470903396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3234090805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2591419219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3475074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2430744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.25110912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.279224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3836574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3716087341309</t>
   </si>
   <si>
     <t xml:space="preserve">15.4559564590454</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">14.9418277740479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6887807846069</t>
+    <t xml:space="preserve">14.6887798309326</t>
   </si>
   <si>
     <t xml:space="preserve">14.7811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7570657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168960571289</t>
+    <t xml:space="preserve">14.7570648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168970108032</t>
   </si>
   <si>
     <t xml:space="preserve">14.1867036819458</t>
@@ -3551,106 +3551,106 @@
     <t xml:space="preserve">14.2429361343384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.564266204834</t>
+    <t xml:space="preserve">14.5642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">14.4919672012329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6124668121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498615264893</t>
+    <t xml:space="preserve">14.6124658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498624801636</t>
   </si>
   <si>
     <t xml:space="preserve">15.0221605300903</t>
   </si>
   <si>
-    <t xml:space="preserve">14.857479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9297771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8614959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6767320632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7731294631958</t>
+    <t xml:space="preserve">14.8574800491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9297761917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213300704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6767311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7731285095215</t>
   </si>
   <si>
     <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9016618728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0060939788818</t>
+    <t xml:space="preserve">14.9016609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623273849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0060949325562</t>
   </si>
   <si>
     <t xml:space="preserve">14.9659271240234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2671747207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788101196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333787918091</t>
+    <t xml:space="preserve">15.2671728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788091659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333797454834</t>
   </si>
   <si>
     <t xml:space="preserve">14.9177293777466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8293628692627</t>
+    <t xml:space="preserve">14.8293609619141</t>
   </si>
   <si>
     <t xml:space="preserve">14.9337949752808</t>
   </si>
   <si>
-    <t xml:space="preserve">15.058310508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8132963180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9257612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1466751098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0382251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627416610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3754863739014</t>
+    <t xml:space="preserve">15.0583114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422430038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8132972717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9257621765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1466760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0382270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627435684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3754854202271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4999990463257</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6847648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6727132797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9940462112427</t>
+    <t xml:space="preserve">14.6847639083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6727123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9940452575684</t>
   </si>
   <si>
     <t xml:space="preserve">14.7369794845581</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">14.9578952789307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7450122833252</t>
+    <t xml:space="preserve">14.7450132369995</t>
   </si>
   <si>
     <t xml:space="preserve">15.2270078659058</t>
@@ -3680,13 +3680,13 @@
     <t xml:space="preserve">14.0300559997559</t>
   </si>
   <si>
-    <t xml:space="preserve">14.371467590332</t>
+    <t xml:space="preserve">14.3714685440063</t>
   </si>
   <si>
     <t xml:space="preserve">13.9256229400635</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8372592926025</t>
+    <t xml:space="preserve">13.8372573852539</t>
   </si>
   <si>
     <t xml:space="preserve">13.7770080566406</t>
@@ -3704,22 +3704,22 @@
     <t xml:space="preserve">13.6243762969971</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4958448410034</t>
+    <t xml:space="preserve">13.4958438873291</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1746530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3875341415405</t>
+    <t xml:space="preserve">14.1746549606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3875360488892</t>
   </si>
   <si>
     <t xml:space="preserve">15.0824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0502767562866</t>
+    <t xml:space="preserve">15.0502777099609</t>
   </si>
   <si>
     <t xml:space="preserve">15.1667585372925</t>
@@ -3728,28 +3728,28 @@
     <t xml:space="preserve">15.3153743743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6005544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1789455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8495836257935</t>
+    <t xml:space="preserve">15.6005525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1789474487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8495826721191</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6850414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3074798583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2351779937744</t>
+    <t xml:space="preserve">16.6850395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9581718444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3074779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.235179901123</t>
   </si>
   <si>
     <t xml:space="preserve">16.0504150390625</t>
@@ -3758,19 +3758,19 @@
     <t xml:space="preserve">15.5523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7331008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6166210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4840726852417</t>
+    <t xml:space="preserve">15.7331018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6166200637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.484073638916</t>
   </si>
   <si>
     <t xml:space="preserve">15.4117727279663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.476037979126</t>
+    <t xml:space="preserve">15.4760398864746</t>
   </si>
   <si>
     <t xml:space="preserve">14.9980602264404</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">14.7932147979736</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5080327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5441827774048</t>
+    <t xml:space="preserve">14.5080318450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5441818237305</t>
   </si>
   <si>
     <t xml:space="preserve">14.4598331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5401678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196681976318</t>
+    <t xml:space="preserve">14.5401659011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196691513062</t>
   </si>
   <si>
     <t xml:space="preserve">14.7048482894897</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">14.4518013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2469520568848</t>
+    <t xml:space="preserve">14.2469539642334</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
@@ -3812,13 +3812,13 @@
     <t xml:space="preserve">14.2268695831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.267035484314</t>
+    <t xml:space="preserve">14.2670364379883</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947374343872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3112182617188</t>
+    <t xml:space="preserve">14.3112192153931</t>
   </si>
   <si>
     <t xml:space="preserve">14.4558172225952</t>
@@ -3830,16 +3830,16 @@
     <t xml:space="preserve">14.7547550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8230848312378</t>
+    <t xml:space="preserve">14.8230838775635</t>
   </si>
   <si>
     <t xml:space="preserve">14.8828716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5882043838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5540390014648</t>
+    <t xml:space="preserve">14.5882034301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5540399551392</t>
   </si>
   <si>
     <t xml:space="preserve">14.4771709442139</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">14.4430055618286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3789472579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2764530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643564224243</t>
+    <t xml:space="preserve">14.3789463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2764539718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643583297729</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
@@ -3869,37 +3869,37 @@
     <t xml:space="preserve">13.3924493789673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2344388961792</t>
+    <t xml:space="preserve">13.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7896108627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3881797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.336932182312</t>
+    <t xml:space="preserve">13.7896118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3881788253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369331359863</t>
   </si>
   <si>
     <t xml:space="preserve">13.5803537368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3967208862305</t>
+    <t xml:space="preserve">13.3967199325562</t>
   </si>
   <si>
     <t xml:space="preserve">13.2557926177979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6828470230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2686033248901</t>
+    <t xml:space="preserve">13.1917333602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6828479766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2686042785645</t>
   </si>
   <si>
     <t xml:space="preserve">13.4266138076782</t>
@@ -3914,31 +3914,31 @@
     <t xml:space="preserve">13.2942266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1661100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4187631607056</t>
+    <t xml:space="preserve">13.1661109924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4187641143799</t>
   </si>
   <si>
     <t xml:space="preserve">12.5596923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0678873062134</t>
+    <t xml:space="preserve">13.0678882598877</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568538665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.995288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7774896621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3547048568726</t>
+    <t xml:space="preserve">12.9568529129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9952878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7774906158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3547058105469</t>
   </si>
   <si>
     <t xml:space="preserve">12.4401159286499</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">12.1838846206665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1625299453735</t>
+    <t xml:space="preserve">12.1625308990479</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095069885254</t>
@@ -3968,10 +3968,10 @@
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333530426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4571981430054</t>
+    <t xml:space="preserve">12.3333520889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134323120117</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">12.5340690612793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6408319473267</t>
+    <t xml:space="preserve">12.640832901001</t>
   </si>
   <si>
     <t xml:space="preserve">12.8458185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9141483306885</t>
+    <t xml:space="preserve">12.9141473770142</t>
   </si>
   <si>
     <t xml:space="preserve">13.0508050918579</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">13.1234045028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1618385314941</t>
+    <t xml:space="preserve">13.1618394851685</t>
   </si>
   <si>
     <t xml:space="preserve">12.897066116333</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579141616821</t>
+    <t xml:space="preserve">12.6579151153564</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3931398391724</t>
+    <t xml:space="preserve">12.3931407928467</t>
   </si>
   <si>
     <t xml:space="preserve">12.8330068588257</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4828224182129</t>
+    <t xml:space="preserve">12.4828214645386</t>
   </si>
   <si>
     <t xml:space="preserve">12.4486570358276</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">12.768949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1703805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9696645736694</t>
+    <t xml:space="preserve">13.1703815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9696655273438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0892400741577</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">12.704891204834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7390546798706</t>
+    <t xml:space="preserve">12.7390556335449</t>
   </si>
   <si>
     <t xml:space="preserve">12.3248119354248</t>
@@ -4091,25 +4091,25 @@
     <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8550519943237</t>
+    <t xml:space="preserve">11.8550510406494</t>
   </si>
   <si>
     <t xml:space="preserve">11.73974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9575433731079</t>
+    <t xml:space="preserve">11.9575443267822</t>
   </si>
   <si>
     <t xml:space="preserve">11.9447326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7909936904907</t>
+    <t xml:space="preserve">11.7909927368164</t>
   </si>
   <si>
     <t xml:space="preserve">12.0045204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1582593917847</t>
+    <t xml:space="preserve">12.158260345459</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991876602173</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">12.5169858932495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3376235961914</t>
+    <t xml:space="preserve">12.3376226425171</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749973297119</t>
@@ -4130,13 +4130,13 @@
     <t xml:space="preserve">12.6878080368042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7091608047485</t>
+    <t xml:space="preserve">12.7091617584229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.973934173584</t>
+    <t xml:space="preserve">12.9739351272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.0977811813354</t>
@@ -4145,13 +4145,13 @@
     <t xml:space="preserve">13.0251817703247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.153299331665</t>
+    <t xml:space="preserve">13.1532983779907</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8493986129761</t>
+    <t xml:space="preserve">13.8493995666504</t>
   </si>
   <si>
     <t xml:space="preserve">13.9433507919312</t>
@@ -4169,22 +4169,22 @@
     <t xml:space="preserve">14.5839338302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.515604019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.741943359375</t>
+    <t xml:space="preserve">14.5156049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7419443130493</t>
   </si>
   <si>
     <t xml:space="preserve">14.579662322998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5027923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600877761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2679119110107</t>
+    <t xml:space="preserve">14.5027933120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2679128646851</t>
   </si>
   <si>
     <t xml:space="preserve">14.4686298370361</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">14.6992378234863</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7931909561157</t>
+    <t xml:space="preserve">14.7931900024414</t>
   </si>
   <si>
     <t xml:space="preserve">14.6906976699829</t>
@@ -4226,58 +4226,58 @@
     <t xml:space="preserve">14.0928201675415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2508306503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2892637252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3960285186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3490533828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3106184005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.259370803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3618650436401</t>
+    <t xml:space="preserve">14.2508296966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2892656326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3960294723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3490524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3106174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2593717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3618659973145</t>
   </si>
   <si>
     <t xml:space="preserve">14.1910429000854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3276996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917589187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8102722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6736164093018</t>
+    <t xml:space="preserve">14.3277006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504854202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8102731704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6736154556274</t>
   </si>
   <si>
     <t xml:space="preserve">14.8017320632935</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8615198135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8487071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9554710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9682817459106</t>
+    <t xml:space="preserve">14.8615188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.848708152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9554719924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9682836532593</t>
   </si>
   <si>
     <t xml:space="preserve">14.8358974456787</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">15.168999671936</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2373285293579</t>
+    <t xml:space="preserve">15.2373275756836</t>
   </si>
   <si>
     <t xml:space="preserve">15.3013868331909</t>
@@ -4301,70 +4301,70 @@
     <t xml:space="preserve">15.3270092010498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3825263977051</t>
+    <t xml:space="preserve">15.3825254440308</t>
   </si>
   <si>
     <t xml:space="preserve">15.28857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5319957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5021018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.416690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4679374694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4636669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063734054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5618906021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6003255844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686525344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473016738892</t>
+    <t xml:space="preserve">15.5319938659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5020999908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166889190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4679365158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4636650085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5618877410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6003227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5875120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6472997665405</t>
   </si>
   <si>
     <t xml:space="preserve">15.6857347488403</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4850196838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106449127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6643829345703</t>
+    <t xml:space="preserve">15.4850177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106420516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.664381980896</t>
   </si>
   <si>
     <t xml:space="preserve">15.9804019927979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8266649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8223915100098</t>
+    <t xml:space="preserve">15.8266639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8223924636841</t>
   </si>
   <si>
     <t xml:space="preserve">15.8864517211914</t>
@@ -4379,16 +4379,16 @@
     <t xml:space="preserve">16.0658130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9078044891357</t>
+    <t xml:space="preserve">15.9078035354614</t>
   </si>
   <si>
     <t xml:space="preserve">15.7327108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">15.203161239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7540645599365</t>
+    <t xml:space="preserve">15.2031631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7540636062622</t>
   </si>
   <si>
     <t xml:space="preserve">14.8316259384155</t>
@@ -4397,10 +4397,10 @@
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4508562088013</t>
+    <t xml:space="preserve">15.0451536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4508543014526</t>
   </si>
   <si>
     <t xml:space="preserve">15.4081497192383</t>
@@ -4412,25 +4412,25 @@
     <t xml:space="preserve">15.2501392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4423151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6259479522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6985473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.672924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.621678352356</t>
+    <t xml:space="preserve">15.4423131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6259469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6985454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6729230880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6216773986816</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437471389771</t>
+    <t xml:space="preserve">15.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">16.1683082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.040189743042</t>
+    <t xml:space="preserve">16.0401916503906</t>
   </si>
   <si>
     <t xml:space="preserve">16.1384143829346</t>
@@ -4466,19 +4466,19 @@
     <t xml:space="preserve">16.1298732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2323665618896</t>
+    <t xml:space="preserve">16.232364654541</t>
   </si>
   <si>
     <t xml:space="preserve">16.1256008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8693695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9334297180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8053112030029</t>
+    <t xml:space="preserve">15.8693685531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9334278106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8053092956543</t>
   </si>
   <si>
     <t xml:space="preserve">16.2067432403564</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">15.890721321106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9889430999756</t>
+    <t xml:space="preserve">15.9889440536499</t>
   </si>
   <si>
     <t xml:space="preserve">16.1127910614014</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">16.0316505432129</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9120721817017</t>
+    <t xml:space="preserve">15.912073135376</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -71795,7 +71795,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6910069444</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>1927428</v>
@@ -71816,6 +71816,32 @@
         <v>2026</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6912962963</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>1796608</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>33.2799987792969</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>32.8499984741211</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>33.0299987792969</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -44,88 +44,88 @@
     <t xml:space="preserve">G.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31059074401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13427352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11721134185791</t>
+    <t xml:space="preserve">9.31058979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13427257537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11721038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.02052116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76457977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8897066116333</t>
+    <t xml:space="preserve">8.76458072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88970756530762</t>
   </si>
   <si>
     <t xml:space="preserve">9.0660228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95796012878418</t>
+    <t xml:space="preserve">8.95795822143555</t>
   </si>
   <si>
     <t xml:space="preserve">8.75889301300049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57120227813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376522064209</t>
+    <t xml:space="preserve">8.57120132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376617431641</t>
   </si>
   <si>
     <t xml:space="preserve">8.29251003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44607543945312</t>
+    <t xml:space="preserve">8.44607448577881</t>
   </si>
   <si>
     <t xml:space="preserve">8.48588752746582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30957221984863</t>
+    <t xml:space="preserve">8.30957317352295</t>
   </si>
   <si>
     <t xml:space="preserve">8.04794311523438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93988037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61568784713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84318971633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70668840408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4166202545166</t>
+    <t xml:space="preserve">7.93987989425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61568689346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84318923950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70668697357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41662120819092</t>
   </si>
   <si>
     <t xml:space="preserve">7.23461866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15499067306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96161317825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74548435211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47247982025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8137354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23360157012939</t>
+    <t xml:space="preserve">7.1549916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74548387527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47248077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81373453140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23360204696655</t>
   </si>
   <si>
     <t xml:space="preserve">6.34166574478149</t>
@@ -134,103 +134,103 @@
     <t xml:space="preserve">6.59760761260986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62035799026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77392387390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72842264175415</t>
+    <t xml:space="preserve">6.62035751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77392292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72842216491699</t>
   </si>
   <si>
     <t xml:space="preserve">6.66017150878906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89905023574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89336204528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95592641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305675506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28580713272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34268188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45643377304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4507474899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680673599243</t>
+    <t xml:space="preserve">6.89904975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8933629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2630558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28580570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34268236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45643329620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45074605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680721282959</t>
   </si>
   <si>
     <t xml:space="preserve">7.24599266052246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249540328979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37112092971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750247955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79200124740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731599807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89437913894653</t>
+    <t xml:space="preserve">7.3199315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249588012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37111902236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79200220108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731695175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437818527222</t>
   </si>
   <si>
     <t xml:space="preserve">7.76356410980225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67256355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587289810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037309646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543130874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4279956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48487186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41093349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30286836624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21755409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9843635559082</t>
+    <t xml:space="preserve">7.67256212234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037214279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543226242065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42799711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48487329483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30286931991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21755456924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98436403274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.00711393356323</t>
@@ -242,118 +242,118 @@
     <t xml:space="preserve">7.05261468887329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13792896270752</t>
+    <t xml:space="preserve">7.13792848587036</t>
   </si>
   <si>
     <t xml:space="preserve">7.16067934036255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4336838722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4962477684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47918367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743623733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862375259399</t>
+    <t xml:space="preserve">7.43368291854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49624681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918510437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743528366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862327575684</t>
   </si>
   <si>
     <t xml:space="preserve">7.75218820571899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83181571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78631448745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85456562042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80337810516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77493906021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018566131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39387035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35405683517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53606128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105325698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0583028793335</t>
+    <t xml:space="preserve">7.83181619644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85456609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80337715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77493810653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39387083053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35405731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53605985641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105278015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16636753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05830335617065</t>
   </si>
   <si>
     <t xml:space="preserve">7.11517858505249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25168037414551</t>
+    <t xml:space="preserve">7.25168132781982</t>
   </si>
   <si>
     <t xml:space="preserve">7.31798839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73994779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84845352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90873146057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94490098953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85448169708252</t>
+    <t xml:space="preserve">7.73994827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8484525680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90873289108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94490051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85447931289673</t>
   </si>
   <si>
     <t xml:space="preserve">7.81228446960449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76406002044678</t>
+    <t xml:space="preserve">7.76406097412109</t>
   </si>
   <si>
     <t xml:space="preserve">7.54705333709717</t>
   </si>
   <si>
-    <t xml:space="preserve">7.534996509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158485412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80625629425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7700891494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42046308517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17934465408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97439384460449</t>
+    <t xml:space="preserve">7.53499603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158390045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80625581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42046499252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17934417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97439289093018</t>
   </si>
   <si>
     <t xml:space="preserve">6.99850511550903</t>
@@ -362,73 +362,73 @@
     <t xml:space="preserve">6.92014074325562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1914005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4084095954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54102373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5832200050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58257341384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02498388290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11841726303101</t>
+    <t xml:space="preserve">7.19140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40840911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54102420806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58322095870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58257389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02498340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11841630935669</t>
   </si>
   <si>
     <t xml:space="preserve">6.26308917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35953712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43187284469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25103330612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1304726600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91647863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92853593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38967704772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43790149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76341247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69710445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87191534042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80561017990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8417763710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8478045463562</t>
+    <t xml:space="preserve">6.35953664779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4318733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25103235244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13047313690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91647815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92853546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38967752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43790197372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7634129524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69710493087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8719162940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84177684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84780406951904</t>
   </si>
   <si>
     <t xml:space="preserve">6.77546882629395</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">6.73327255249023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68504905700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81163740158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6247673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10098028182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083988189697</t>
+    <t xml:space="preserve">6.68504810333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81163787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476873397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10098075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07084035873413</t>
   </si>
   <si>
     <t xml:space="preserve">6.79355239868164</t>
@@ -458,52 +458,52 @@
     <t xml:space="preserve">7.06481218338013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2094841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29387617111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990434646606</t>
+    <t xml:space="preserve">7.20948457717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2938756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990482330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.34210014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89000129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90808439254761</t>
+    <t xml:space="preserve">7.08289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89000034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90808486938477</t>
   </si>
   <si>
     <t xml:space="preserve">6.73930072784424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04070043563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01658916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8176646232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74532890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247741699219</t>
+    <t xml:space="preserve">7.04070091247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01658773422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766557693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74532842636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149604797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247694015503</t>
   </si>
   <si>
     <t xml:space="preserve">6.93822479248047</t>
@@ -512,223 +512,223 @@
     <t xml:space="preserve">6.88397264480591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523290634155</t>
+    <t xml:space="preserve">6.98042011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523242950439</t>
   </si>
   <si>
     <t xml:space="preserve">7.25770807266235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70313310623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72724628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79958057403564</t>
+    <t xml:space="preserve">6.70313358306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79958200454712</t>
   </si>
   <si>
     <t xml:space="preserve">6.75135660171509</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59462881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56449031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57654476165771</t>
+    <t xml:space="preserve">6.59462833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56448888778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57654523849487</t>
   </si>
   <si>
     <t xml:space="preserve">6.60668516159058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5464038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51626443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4981803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76944017410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85985994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18537330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16728830337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26976490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33004426956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31196022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317750930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0949535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98644828796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67299270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83574867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08892345428467</t>
+    <t xml:space="preserve">6.54640436172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51626491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49817991256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76944065093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85986137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1853723526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1672887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742870330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784894943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26976442337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33004379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31196117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09495258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98644876480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67299318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83574914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0889253616333</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87794494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02261686325073</t>
+    <t xml:space="preserve">6.8779444694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02261638641357</t>
   </si>
   <si>
     <t xml:space="preserve">6.82369327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43854856491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35415649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73391962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6803150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45125293731689</t>
+    <t xml:space="preserve">7.43854761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35415697097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73391914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68031597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45125198364258</t>
   </si>
   <si>
     <t xml:space="preserve">8.47536373138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41508388519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33069229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54167175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55975437164307</t>
+    <t xml:space="preserve">8.41508293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33069133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.541672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55975532531738</t>
   </si>
   <si>
     <t xml:space="preserve">8.63812065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58386707305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59592628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66223049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6682596206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55372905731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5055046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5115327835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7104549407959</t>
+    <t xml:space="preserve">8.5838680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59592533111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6622314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66826057434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55372714996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50550365447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51153182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017604827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71045589447021</t>
   </si>
   <si>
     <t xml:space="preserve">8.75265216827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69840145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7164831161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52358818054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48742008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38494491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25835609436035</t>
+    <t xml:space="preserve">8.69839954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71648406982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52358722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4874210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38494396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25835514068604</t>
   </si>
   <si>
     <t xml:space="preserve">8.23424434661865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16793537139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27041149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26438426971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5898962020874</t>
+    <t xml:space="preserve">8.16793632507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27041244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26438331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58989715576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.2951717376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38559246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42175769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28311538696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98774433135986</t>
+    <t xml:space="preserve">9.38559150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42175960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28311729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98774242401123</t>
   </si>
   <si>
     <t xml:space="preserve">8.88526821136475</t>
@@ -737,22 +737,22 @@
     <t xml:space="preserve">8.84909915924072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00582695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02993869781494</t>
+    <t xml:space="preserve">9.00582790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993774414062</t>
   </si>
   <si>
     <t xml:space="preserve">8.81896018981934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7707347869873</t>
+    <t xml:space="preserve">8.77073669433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.67428779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74059581756592</t>
+    <t xml:space="preserve">8.7405948638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.90335178375244</t>
@@ -761,46 +761,46 @@
     <t xml:space="preserve">9.04802322387695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87923908233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90937900543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95760250091553</t>
+    <t xml:space="preserve">8.87924003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90937995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95760345458984</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81293201446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74662494659424</t>
+    <t xml:space="preserve">8.8129301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74662399291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.6562032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49947738647461</t>
+    <t xml:space="preserve">8.49947547912598</t>
   </si>
   <si>
     <t xml:space="preserve">8.14985275268555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27643871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54769992828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46330547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56578254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78882026672363</t>
+    <t xml:space="preserve">8.27643966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54769897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46330833435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5657844543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.788818359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.80087661743164</t>
@@ -812,55 +812,55 @@
     <t xml:space="preserve">8.78279209136963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86718368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98171520233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80690288543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6320915222168</t>
+    <t xml:space="preserve">8.86718273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98171424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80690574645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63209247589111</t>
   </si>
   <si>
     <t xml:space="preserve">8.6079797744751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46933555603027</t>
+    <t xml:space="preserve">8.46933650970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.36083126068115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93349075317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75867938995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87321090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04199600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1926965713501</t>
+    <t xml:space="preserve">8.93349170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75868034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87321281433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04199695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19269561767578</t>
   </si>
   <si>
     <t xml:space="preserve">9.21077919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2409200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21680641174316</t>
+    <t xml:space="preserve">9.24091911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21680736541748</t>
   </si>
   <si>
     <t xml:space="preserve">8.94554805755615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89129734039307</t>
+    <t xml:space="preserve">8.89129447937012</t>
   </si>
   <si>
     <t xml:space="preserve">9.03596782684326</t>
@@ -869,67 +869,67 @@
     <t xml:space="preserve">9.07213497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12035846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33675384521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18400478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15854740142822</t>
+    <t xml:space="preserve">9.12035942077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30492973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33675479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18400573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15854644775391</t>
   </si>
   <si>
     <t xml:space="preserve">9.13308906555176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94851684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83395671844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94215297698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03762054443359</t>
+    <t xml:space="preserve">8.94851779937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83395576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94215202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03762149810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.81486225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73848819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89123630523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95488262176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05035018920898</t>
+    <t xml:space="preserve">8.75758075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73848915100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89123821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9548807144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0503511428833</t>
   </si>
   <si>
     <t xml:space="preserve">9.22855663299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2349214553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17127704620361</t>
+    <t xml:space="preserve">9.23492050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1712760925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.28583717346191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29856586456299</t>
+    <t xml:space="preserve">9.2985668182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.19036960601807</t>
@@ -938,40 +938,40 @@
     <t xml:space="preserve">9.34948253631592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25401496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24765014648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29220294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33038806915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38130569458008</t>
+    <t xml:space="preserve">9.25401401519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24765110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29220104217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33038902282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38130474090576</t>
   </si>
   <si>
     <t xml:space="preserve">9.57860660552979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54678153991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5404167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64861488342285</t>
+    <t xml:space="preserve">9.54678249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54041957855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64861583709717</t>
   </si>
   <si>
     <t xml:space="preserve">9.79499912261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85864353179932</t>
+    <t xml:space="preserve">9.85864448547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.71862602233887</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">9.68680191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56587696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52768898010254</t>
+    <t xml:space="preserve">9.56587600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52768993377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.75681209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77590560913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750370025635</t>
+    <t xml:space="preserve">9.77590465545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750389099121</t>
   </si>
   <si>
     <t xml:space="preserve">10.0877676010132</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">10.2341508865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1959638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0623083114624</t>
+    <t xml:space="preserve">10.1959657669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0623092651367</t>
   </si>
   <si>
     <t xml:space="preserve">10.0050287246704</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">9.82682132720947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86500930786133</t>
+    <t xml:space="preserve">9.86501026153564</t>
   </si>
   <si>
     <t xml:space="preserve">9.90319633483887</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">9.82045841217041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87137317657471</t>
+    <t xml:space="preserve">9.87137413024902</t>
   </si>
   <si>
     <t xml:space="preserve">9.78226947784424</t>
@@ -1040,31 +1040,31 @@
     <t xml:space="preserve">9.69953155517578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6804370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69316577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53405284881592</t>
+    <t xml:space="preserve">9.68043804168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69316673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66134548187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53405380249023</t>
   </si>
   <si>
     <t xml:space="preserve">9.52132511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57223987579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61679267883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67407131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6295223236084</t>
+    <t xml:space="preserve">9.57224082946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61679077148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67407321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62952041625977</t>
   </si>
   <si>
     <t xml:space="preserve">9.59770011901855</t>
@@ -1076,58 +1076,58 @@
     <t xml:space="preserve">9.94774913787842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75044727325439</t>
+    <t xml:space="preserve">9.75044631958008</t>
   </si>
   <si>
     <t xml:space="preserve">9.89683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91592502593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87773895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0304870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686731338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1323184967041</t>
+    <t xml:space="preserve">9.91592407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8777379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0304861068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1323194503784</t>
   </si>
   <si>
     <t xml:space="preserve">9.93501949310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84591484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85227870941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72498893737793</t>
+    <t xml:space="preserve">9.84591579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85227966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8331880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72498989105225</t>
   </si>
   <si>
     <t xml:space="preserve">9.9986629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96047496795654</t>
+    <t xml:space="preserve">9.96047782897949</t>
   </si>
   <si>
     <t xml:space="preserve">10.0177574157715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95411109924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1259546279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0241222381592</t>
+    <t xml:space="preserve">9.9541130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1259536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0241203308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.94138336181641</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">10.0368509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63588714599609</t>
+    <t xml:space="preserve">9.78863334655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.58497047424316</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">9.66770839691162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74408340454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73135471343994</t>
+    <t xml:space="preserve">9.74408435821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73135375976562</t>
   </si>
   <si>
     <t xml:space="preserve">9.80772876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73771858215332</t>
+    <t xml:space="preserve">9.737717628479</t>
   </si>
   <si>
     <t xml:space="preserve">9.70589637756348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5595121383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47677230834961</t>
+    <t xml:space="preserve">9.55951118469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47677326202393</t>
   </si>
   <si>
     <t xml:space="preserve">9.97320556640625</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">10.0814018249512</t>
   </si>
   <si>
-    <t xml:space="preserve">10.055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2914323806763</t>
+    <t xml:space="preserve">10.0559453964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.291431427002</t>
   </si>
   <si>
     <t xml:space="preserve">10.3041620254517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2023286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3105249404907</t>
+    <t xml:space="preserve">10.2023296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105268478394</t>
   </si>
   <si>
     <t xml:space="preserve">10.3232536315918</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736879348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1641416549683</t>
+    <t xml:space="preserve">10.1736869812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1641407012939</t>
   </si>
   <si>
     <t xml:space="preserve">10.1482305526733</t>
@@ -1214,37 +1214,37 @@
     <t xml:space="preserve">9.99229907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76954174041748</t>
+    <t xml:space="preserve">9.76954078674316</t>
   </si>
   <si>
     <t xml:space="preserve">9.86819171905518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81727409362793</t>
+    <t xml:space="preserve">9.81727600097656</t>
   </si>
   <si>
     <t xml:space="preserve">9.77908802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81409168243408</t>
+    <t xml:space="preserve">9.8140926361084</t>
   </si>
   <si>
     <t xml:space="preserve">9.80454540252686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36857604980469</t>
+    <t xml:space="preserve">9.368577003479</t>
   </si>
   <si>
     <t xml:space="preserve">9.6517972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85546112060547</t>
+    <t xml:space="preserve">9.85546207427979</t>
   </si>
   <si>
     <t xml:space="preserve">9.74726486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0082111358643</t>
+    <t xml:space="preserve">10.0082120895386</t>
   </si>
   <si>
     <t xml:space="preserve">9.98593425750732</t>
@@ -1253,163 +1253,163 @@
     <t xml:space="preserve">9.92865467071533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94456577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9700231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0495805740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1609582901001</t>
+    <t xml:space="preserve">9.94456481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97002410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0495796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1609601974487</t>
   </si>
   <si>
     <t xml:space="preserve">10.3137083053589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2946138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455286026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346351623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5301008224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6382999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.765588760376</t>
+    <t xml:space="preserve">10.2946147918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455295562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.530101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6382989883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7655897140503</t>
   </si>
   <si>
     <t xml:space="preserve">10.8546924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6319341659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5841999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6542100906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7083082199097</t>
+    <t xml:space="preserve">10.6319332122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7178564071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5841979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6542091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7083072662354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7051258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6796674728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269193649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5396490097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4409980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5014610290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078248977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2977962493896</t>
+    <t xml:space="preserve">10.6796684265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269184112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5396480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4409971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5014600753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078258514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.297797203064</t>
   </si>
   <si>
     <t xml:space="preserve">10.3328018188477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2596101760864</t>
+    <t xml:space="preserve">10.2596082687378</t>
   </si>
   <si>
     <t xml:space="preserve">10.2864847183228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.252890586853</t>
+    <t xml:space="preserve">10.2528915405273</t>
   </si>
   <si>
     <t xml:space="preserve">10.1319522857666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99421691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83968544006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49702453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55413627624512</t>
+    <t xml:space="preserve">10.0143737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99421787261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49702644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">9.77585506439209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88335514068604</t>
+    <t xml:space="preserve">9.88335704803467</t>
   </si>
   <si>
     <t xml:space="preserve">9.86991882324219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65491771697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67843341827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52054119110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79937171936035</t>
+    <t xml:space="preserve">9.65491676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67843246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52054214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79937076568604</t>
   </si>
   <si>
     <t xml:space="preserve">9.75234031677246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7825756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9001522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80609130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76241683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8296070098877</t>
+    <t xml:space="preserve">9.78257369995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90015316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80608940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76241874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82960605621338</t>
   </si>
   <si>
     <t xml:space="preserve">9.69859027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76913642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60116767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61796474456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52390193939209</t>
+    <t xml:space="preserve">9.76913738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60116672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61796379089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52390098571777</t>
   </si>
   <si>
     <t xml:space="preserve">9.51718235015869</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">9.59108829498291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80945110321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77249526977539</t>
+    <t xml:space="preserve">9.80945014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77249622344971</t>
   </si>
   <si>
     <t xml:space="preserve">9.7288236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6515588760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163635253906</t>
+    <t xml:space="preserve">9.65155601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163539886475</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
@@ -1448,40 +1448,40 @@
     <t xml:space="preserve">9.81616878509521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74898052215576</t>
+    <t xml:space="preserve">9.74897956848145</t>
   </si>
   <si>
     <t xml:space="preserve">9.89007568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90351295471191</t>
+    <t xml:space="preserve">9.90351390838623</t>
   </si>
   <si>
     <t xml:space="preserve">9.92366981506348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97070026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0479669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2125768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1117973327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95390319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0378885269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0009365081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0681238174438</t>
+    <t xml:space="preserve">9.97070121765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1117963790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9539041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0378894805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0009355545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0681247711182</t>
   </si>
   <si>
     <t xml:space="preserve">10.0916395187378</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">9.8665599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71202754974365</t>
+    <t xml:space="preserve">9.71202659606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.73218250274658</t>
@@ -1502,64 +1502,64 @@
     <t xml:space="preserve">9.85312271118164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92702674865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98077964782715</t>
+    <t xml:space="preserve">9.92702865600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98077869415283</t>
   </si>
   <si>
     <t xml:space="preserve">9.92031002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63812160491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76577663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93710803985596</t>
+    <t xml:space="preserve">9.63812065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76577758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93710613250732</t>
   </si>
   <si>
     <t xml:space="preserve">9.96062278747559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94382476806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1621856689453</t>
+    <t xml:space="preserve">9.94382667541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1621875762939</t>
   </si>
   <si>
     <t xml:space="preserve">10.1017169952393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0882806777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554679870605</t>
+    <t xml:space="preserve">10.0882787704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1554670333862</t>
   </si>
   <si>
     <t xml:space="preserve">10.1722650527954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1823425292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2965621948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4141426086426</t>
+    <t xml:space="preserve">10.1823434829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2965631484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4141435623169</t>
   </si>
   <si>
     <t xml:space="preserve">10.4309396743774</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3704690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99757671356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88671588897705</t>
+    <t xml:space="preserve">10.3704700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9975757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88671684265137</t>
   </si>
   <si>
     <t xml:space="preserve">9.96734142303467</t>
@@ -1577,109 +1577,109 @@
     <t xml:space="preserve">9.59444808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50038528442383</t>
+    <t xml:space="preserve">9.50038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">9.61460494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56421184539795</t>
+    <t xml:space="preserve">9.56421375274658</t>
   </si>
   <si>
     <t xml:space="preserve">9.41304111480713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43991661071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40968227386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28874206542969</t>
+    <t xml:space="preserve">9.43991565704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40968036651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.288743019104</t>
   </si>
   <si>
     <t xml:space="preserve">9.23835182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43655681610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3324146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53397941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66499614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62468338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65827655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66835594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63476085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57429218292236</t>
+    <t xml:space="preserve">9.43655490875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33241558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53397846221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66499519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62468242645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65827560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66835403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6347599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57429122924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.71538639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51382160186768</t>
+    <t xml:space="preserve">9.51382350921631</t>
   </si>
   <si>
     <t xml:space="preserve">9.59780788421631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55749320983887</t>
+    <t xml:space="preserve">9.55749607086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.57765102386475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81952857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87663745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91359043121338</t>
+    <t xml:space="preserve">9.8195276260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87663841247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9135913848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.0042953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0849208831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97405910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57093143463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6448392868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562072753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89679431915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85984134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95054340362549</t>
+    <t xml:space="preserve">10.084921836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97406005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57093238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64483833312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89679336547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85984230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95054531097412</t>
   </si>
   <si>
     <t xml:space="preserve">10.0210933685303</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">10.0446081161499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0647640228271</t>
+    <t xml:space="preserve">10.0647649765015</t>
   </si>
   <si>
     <t xml:space="preserve">10.2327337265015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3267974853516</t>
+    <t xml:space="preserve">10.3267965316772</t>
   </si>
   <si>
     <t xml:space="preserve">10.3435935974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2898435592651</t>
+    <t xml:space="preserve">10.2898445129395</t>
   </si>
   <si>
     <t xml:space="preserve">10.3335161209106</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2764072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1991405487061</t>
+    <t xml:space="preserve">10.3771886825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2764053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1991415023804</t>
   </si>
   <si>
     <t xml:space="preserve">10.2461719512939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2932033538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714817047119</t>
+    <t xml:space="preserve">10.2932024002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714836120605</t>
   </si>
   <si>
     <t xml:space="preserve">10.1285924911499</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">10.2058582305908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2831268310547</t>
+    <t xml:space="preserve">10.2831258773804</t>
   </si>
   <si>
     <t xml:space="preserve">10.1890621185303</t>
@@ -1745,61 +1745,61 @@
     <t xml:space="preserve">10.2293748855591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260150909424</t>
+    <t xml:space="preserve">10.2260160446167</t>
   </si>
   <si>
     <t xml:space="preserve">10.2730474472046</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805475234985</t>
+    <t xml:space="preserve">10.3805484771729</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275798797607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4342985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5451574325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6089878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6728162765503</t>
+    <t xml:space="preserve">10.4342975616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5451583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6089868545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.672815322876</t>
   </si>
   <si>
     <t xml:space="preserve">10.6660966873169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7400035858154</t>
+    <t xml:space="preserve">10.7400026321411</t>
   </si>
   <si>
     <t xml:space="preserve">10.6123466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5653142929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6157064437866</t>
+    <t xml:space="preserve">10.565315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6157054901123</t>
   </si>
   <si>
     <t xml:space="preserve">10.5921907424927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6224250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7534408569336</t>
+    <t xml:space="preserve">10.6224241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7534418106079</t>
   </si>
   <si>
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0725841522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0591478347778</t>
+    <t xml:space="preserve">11.072585105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0591468811035</t>
   </si>
   <si>
     <t xml:space="preserve">11.0322713851929</t>
@@ -1814,40 +1814,40 @@
     <t xml:space="preserve">10.9718017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0087566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0860214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2036008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1767253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2304773330688</t>
+    <t xml:space="preserve">11.0087556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0860204696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2035999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1767244338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2304763793945</t>
   </si>
   <si>
     <t xml:space="preserve">11.2237577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1733665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2170400619507</t>
+    <t xml:space="preserve">11.1733655929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2170391082764</t>
   </si>
   <si>
     <t xml:space="preserve">11.2002410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2271165847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2976636886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3581323623657</t>
+    <t xml:space="preserve">11.2271156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.35813331604</t>
   </si>
   <si>
     <t xml:space="preserve">11.4219627380371</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">11.556339263916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4521970748901</t>
+    <t xml:space="preserve">11.4521961212158</t>
   </si>
   <si>
     <t xml:space="preserve">11.4286804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4622735977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.583212852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5529775619507</t>
+    <t xml:space="preserve">11.4622745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5832138061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.552978515625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6235265731812</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">11.6201667785645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6302461624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.526104927063</t>
+    <t xml:space="preserve">11.6302442550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5261030197144</t>
   </si>
   <si>
     <t xml:space="preserve">11.4824314117432</t>
@@ -1889,34 +1889,34 @@
     <t xml:space="preserve">11.468994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3245401382446</t>
+    <t xml:space="preserve">11.3245391845703</t>
   </si>
   <si>
     <t xml:space="preserve">11.3648519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4152431488037</t>
+    <t xml:space="preserve">11.415244102478</t>
   </si>
   <si>
     <t xml:space="preserve">11.5093059539795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4253215789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5636587142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.584942817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5601119995117</t>
+    <t xml:space="preserve">11.4253206253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5636596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5849418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.560112953186</t>
   </si>
   <si>
     <t xml:space="preserve">11.3189077377319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5459232330322</t>
+    <t xml:space="preserve">11.5459241867065</t>
   </si>
   <si>
     <t xml:space="preserve">11.414680480957</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">11.3330955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2124938964844</t>
+    <t xml:space="preserve">11.2124929428101</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763414382935</t>
@@ -1934,31 +1934,31 @@
     <t xml:space="preserve">11.1486444473267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1238136291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2727956771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1805696487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2195863723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2479648590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3366413116455</t>
+    <t xml:space="preserve">11.1238145828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2727937698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1805686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2195873260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2479639053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3366432189941</t>
   </si>
   <si>
     <t xml:space="preserve">11.4536981582642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4288682937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4785270690918</t>
+    <t xml:space="preserve">11.4288692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4785280227661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4466047286987</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">11.7445640563965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8119592666626</t>
+    <t xml:space="preserve">11.8119583129883</t>
   </si>
   <si>
     <t xml:space="preserve">11.8332424163818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8403367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7871294021606</t>
+    <t xml:space="preserve">11.8403358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7871284484863</t>
   </si>
   <si>
     <t xml:space="preserve">11.7481098175049</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">11.7126398086548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7977705001831</t>
+    <t xml:space="preserve">11.7977695465088</t>
   </si>
   <si>
     <t xml:space="preserve">11.8935432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.106369972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1312017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0708980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1418418884277</t>
+    <t xml:space="preserve">12.1063718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.131199836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0708990097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1418409347534</t>
   </si>
   <si>
     <t xml:space="preserve">12.1773147583008</t>
@@ -2012,40 +2012,40 @@
     <t xml:space="preserve">12.2092370986938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2056903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560297012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1808614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1170110702515</t>
+    <t xml:space="preserve">12.2056913375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560306549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1808605194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1170120239258</t>
   </si>
   <si>
     <t xml:space="preserve">11.989315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0247869491577</t>
+    <t xml:space="preserve">12.0247888565063</t>
   </si>
   <si>
     <t xml:space="preserve">12.0105981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0567121505737</t>
+    <t xml:space="preserve">12.0567111968994</t>
   </si>
   <si>
     <t xml:space="preserve">11.9751272201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9964113235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8545246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9467496871948</t>
+    <t xml:space="preserve">11.9964094161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8545236587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9467515945435</t>
   </si>
   <si>
     <t xml:space="preserve">11.9573907852173</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">11.6594324111938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3437385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3792085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430561065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2940788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4749803543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5069055557251</t>
+    <t xml:space="preserve">11.3437366485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3792095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430551528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2940769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4749822616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5069046020508</t>
   </si>
   <si>
     <t xml:space="preserve">11.6168661117554</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">11.467887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4820747375488</t>
+    <t xml:space="preserve">11.4820756912231</t>
   </si>
   <si>
     <t xml:space="preserve">11.6558856964111</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487913131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6842613220215</t>
+    <t xml:space="preserve">11.6487903594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6842622756958</t>
   </si>
   <si>
     <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7374696731567</t>
+    <t xml:space="preserve">11.7374687194824</t>
   </si>
   <si>
     <t xml:space="preserve">11.9432020187378</t>
@@ -2120,16 +2120,16 @@
     <t xml:space="preserve">12.134747505188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2021436691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1844081878662</t>
+    <t xml:space="preserve">12.2021446228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1844062805176</t>
   </si>
   <si>
     <t xml:space="preserve">12.3014631271362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4149713516235</t>
+    <t xml:space="preserve">12.4149723052979</t>
   </si>
   <si>
     <t xml:space="preserve">12.3972358703613</t>
@@ -2138,112 +2138,112 @@
     <t xml:space="preserve">12.3262939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2908229827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6881017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6597242355347</t>
+    <t xml:space="preserve">12.2908220291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6881008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6597232818604</t>
   </si>
   <si>
     <t xml:space="preserve">12.7058362960815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6739120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.741307258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6987419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6703653335571</t>
+    <t xml:space="preserve">12.6739130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7413082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6987428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6703662872314</t>
   </si>
   <si>
     <t xml:space="preserve">12.6136121749878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5852346420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5213851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6065168380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5887823104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6490821838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6774597167969</t>
+    <t xml:space="preserve">12.5852336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759527206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5213861465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6065187454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5887832641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6490831375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6774616241455</t>
   </si>
   <si>
     <t xml:space="preserve">12.8157978057861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.744854927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441753387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477230072021</t>
+    <t xml:space="preserve">12.7448568344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477210998535</t>
   </si>
   <si>
     <t xml:space="preserve">12.8406276702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.035719871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0215311050415</t>
+    <t xml:space="preserve">12.9080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0357208251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0215301513672</t>
   </si>
   <si>
     <t xml:space="preserve">13.0463600158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0534563064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0499095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0286264419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9364013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8938331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1243982315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1917943954468</t>
+    <t xml:space="preserve">13.0534543991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0499086380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0286254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9364004135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8938341140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.124400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1917953491211</t>
   </si>
   <si>
     <t xml:space="preserve">13.6422805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6068086624146</t>
+    <t xml:space="preserve">13.6068105697632</t>
   </si>
   <si>
     <t xml:space="preserve">13.6139030456543</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">13.8338260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7167692184448</t>
+    <t xml:space="preserve">13.7167701721191</t>
   </si>
   <si>
     <t xml:space="preserve">13.5997152328491</t>
@@ -2261,25 +2261,25 @@
     <t xml:space="preserve">13.5145845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2662830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2343578338623</t>
+    <t xml:space="preserve">13.2662839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2343597412109</t>
   </si>
   <si>
     <t xml:space="preserve">13.1527767181396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2591896057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456832885742</t>
+    <t xml:space="preserve">13.2591915130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2627363204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456823348999</t>
   </si>
   <si>
     <t xml:space="preserve">12.9754190444946</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">12.9612312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9399471282959</t>
+    <t xml:space="preserve">12.9399480819702</t>
   </si>
   <si>
     <t xml:space="preserve">12.918664932251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9257593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9541339874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0250778198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0108909606934</t>
+    <t xml:space="preserve">12.9257583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9541358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0250797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.010890007019</t>
   </si>
   <si>
     <t xml:space="preserve">13.1137580871582</t>
@@ -2312,25 +2312,25 @@
     <t xml:space="preserve">13.1314935684204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1776065826416</t>
+    <t xml:space="preserve">13.1776056289673</t>
   </si>
   <si>
     <t xml:space="preserve">13.1208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4613761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2520971298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0641002655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9683265686035</t>
+    <t xml:space="preserve">13.4613780975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2520952224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0640983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9683256149292</t>
   </si>
   <si>
     <t xml:space="preserve">13.1031160354614</t>
@@ -2339,67 +2339,67 @@
     <t xml:space="preserve">13.0747385025024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9115715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.978964805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9860610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9505891799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8654594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7235727310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690052032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6916494369507</t>
+    <t xml:space="preserve">12.9115705490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9860591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.950587272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.86545753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7235717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5710458755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6916484832764</t>
   </si>
   <si>
     <t xml:space="preserve">12.4823665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5462160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7306671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818338394165</t>
+    <t xml:space="preserve">12.546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7306680679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818319320679</t>
   </si>
   <si>
     <t xml:space="preserve">13.2804718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3194894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3230390548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3939800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3688583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2979145050049</t>
+    <t xml:space="preserve">13.3194913864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3230400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3939809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.368857383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2979154586792</t>
   </si>
   <si>
     <t xml:space="preserve">12.2482557296753</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">11.1628332138062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8116674423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76171493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6127347946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36769104003906</t>
+    <t xml:space="preserve">10.8116664886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76171398162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61273574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36769008636475</t>
   </si>
   <si>
     <t xml:space="preserve">8.56278324127197</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">8.01297760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6972827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3673996925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569786071777</t>
+    <t xml:space="preserve">7.69728231430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36739873886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569881439209</t>
   </si>
   <si>
     <t xml:space="preserve">7.72565984725952</t>
@@ -2453,16 +2453,16 @@
     <t xml:space="preserve">8.83236503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98134613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77915668487549</t>
+    <t xml:space="preserve">8.98134517669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77915859222412</t>
   </si>
   <si>
     <t xml:space="preserve">8.77206420898438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80398941040039</t>
+    <t xml:space="preserve">8.80398750305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.58051872253418</t>
@@ -2471,46 +2471,46 @@
     <t xml:space="preserve">8.74723434448242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64436912536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89976215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07002353668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1303243637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31832313537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93877983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78979969024658</t>
+    <t xml:space="preserve">8.64436817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89976024627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07002258300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13032627105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31832408905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9387788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7898006439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.88912010192871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63018035888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84300708770752</t>
+    <t xml:space="preserve">8.6301794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8430061340332</t>
   </si>
   <si>
     <t xml:space="preserve">8.77561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04164695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20126724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43537902832031</t>
+    <t xml:space="preserve">9.04164505004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20126819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.435378074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.23319149017334</t>
@@ -2519,31 +2519,31 @@
     <t xml:space="preserve">9.00972270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17643737792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03455066680908</t>
+    <t xml:space="preserve">9.176438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03455257415771</t>
   </si>
   <si>
     <t xml:space="preserve">9.09485340118408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20481586456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12323188781738</t>
+    <t xml:space="preserve">9.20481491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12323093414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.08421230316162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91040325164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80044078826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17269134521484</t>
+    <t xml:space="preserve">8.91040229797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17269039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.01014614105225</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">8.78849506378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96212100982666</t>
+    <t xml:space="preserve">8.99536991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96212196350098</t>
   </si>
   <si>
     <t xml:space="preserve">9.20963191986084</t>
@@ -2567,34 +2567,34 @@
     <t xml:space="preserve">9.39803600311279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43867206573486</t>
+    <t xml:space="preserve">9.43867301940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.22440910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52363872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81178569793701</t>
+    <t xml:space="preserve">9.52363967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81178665161133</t>
   </si>
   <si>
     <t xml:space="preserve">10.3031139373779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3474454879761</t>
+    <t xml:space="preserve">10.3474445343018</t>
   </si>
   <si>
     <t xml:space="preserve">10.6282052993774</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6540641784668</t>
+    <t xml:space="preserve">10.6540632247925</t>
   </si>
   <si>
     <t xml:space="preserve">10.5395431518555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3215856552124</t>
+    <t xml:space="preserve">10.3215866088867</t>
   </si>
   <si>
     <t xml:space="preserve">9.9226131439209</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">9.90414142608643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1257934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.051908493042</t>
+    <t xml:space="preserve">10.1257925033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0519094467163</t>
   </si>
   <si>
     <t xml:space="preserve">9.92630767822266</t>
@@ -2618,37 +2618,37 @@
     <t xml:space="preserve">10.0592975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0703811645508</t>
+    <t xml:space="preserve">10.0703792572021</t>
   </si>
   <si>
     <t xml:space="preserve">9.80070495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82656383514404</t>
+    <t xml:space="preserve">9.82656478881836</t>
   </si>
   <si>
     <t xml:space="preserve">9.91522407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95216751098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94847297668457</t>
+    <t xml:space="preserve">9.95216655731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94847202301025</t>
   </si>
   <si>
     <t xml:space="preserve">10.2218418121338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1553478240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2587842941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1627368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675426483154</t>
+    <t xml:space="preserve">10.155345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2587852478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1627359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675331115723</t>
   </si>
   <si>
     <t xml:space="preserve">9.97063732147217</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">10.2070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2107601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.114709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.181206703186</t>
+    <t xml:space="preserve">10.2107591629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1147108078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812057495117</t>
   </si>
   <si>
     <t xml:space="preserve">10.3289747238159</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">10.2772550582886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0408267974854</t>
+    <t xml:space="preserve">10.040825843811</t>
   </si>
   <si>
     <t xml:space="preserve">9.98541450500488</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">9.97433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46453380584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35370635986328</t>
+    <t xml:space="preserve">9.46453285217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35370540618896</t>
   </si>
   <si>
     <t xml:space="preserve">9.40911865234375</t>
@@ -2699,25 +2699,25 @@
     <t xml:space="preserve">9.55688762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63077163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38695526123047</t>
+    <t xml:space="preserve">9.63077068328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38695430755615</t>
   </si>
   <si>
     <t xml:space="preserve">9.78592777252197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7305154800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68618488311768</t>
+    <t xml:space="preserve">9.73051357269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68618392944336</t>
   </si>
   <si>
     <t xml:space="preserve">9.53841686248779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70835113525391</t>
+    <t xml:space="preserve">9.70834922790527</t>
   </si>
   <si>
     <t xml:space="preserve">9.62707614898682</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">9.56058120727539</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76376247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81917572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78223419189453</t>
+    <t xml:space="preserve">9.76376152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81917476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78223323822021</t>
   </si>
   <si>
     <t xml:space="preserve">9.60860633850098</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">9.62338256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61968898773193</t>
+    <t xml:space="preserve">9.61968994140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.57535839080811</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">9.56796932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48669815063477</t>
+    <t xml:space="preserve">9.48669719696045</t>
   </si>
   <si>
     <t xml:space="preserve">9.47561454772949</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">9.36478900909424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10619449615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75155258178711</t>
+    <t xml:space="preserve">9.1061954498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75155162811279</t>
   </si>
   <si>
     <t xml:space="preserve">8.70352649688721</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">8.66658496856689</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59639644622803</t>
+    <t xml:space="preserve">8.59639739990234</t>
   </si>
   <si>
     <t xml:space="preserve">8.53359413146973</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">8.86976623535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81804752349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88454246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76632976531982</t>
+    <t xml:space="preserve">8.81804847717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88454341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76632881164551</t>
   </si>
   <si>
     <t xml:space="preserve">8.91779136657715</t>
@@ -2807,16 +2807,16 @@
     <t xml:space="preserve">9.1135835647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29829406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24288177490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22071647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12466716766357</t>
+    <t xml:space="preserve">9.2982931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24288082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2207145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12466621398926</t>
   </si>
   <si>
     <t xml:space="preserve">9.12097263336182</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">8.80327129364014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96950912475586</t>
+    <t xml:space="preserve">8.96951103210449</t>
   </si>
   <si>
     <t xml:space="preserve">9.01753425598145</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">9.03969955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81435298919678</t>
+    <t xml:space="preserve">8.81435394287109</t>
   </si>
   <si>
     <t xml:space="preserve">8.82543563842773</t>
@@ -2843,43 +2843,43 @@
     <t xml:space="preserve">8.77371788024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39321517944336</t>
+    <t xml:space="preserve">8.39321422576904</t>
   </si>
   <si>
     <t xml:space="preserve">8.41907501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50404167175293</t>
+    <t xml:space="preserve">8.50404071807861</t>
   </si>
   <si>
     <t xml:space="preserve">8.72199821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89193153381348</t>
+    <t xml:space="preserve">8.89193058013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.01383972167969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14683246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72312641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95955371856689</t>
+    <t xml:space="preserve">9.14683055877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72312545776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95955467224121</t>
   </si>
   <si>
     <t xml:space="preserve">9.94477844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0740747451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.317892074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4398012161255</t>
+    <t xml:space="preserve">10.0740756988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3178911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4398021697998</t>
   </si>
   <si>
     <t xml:space="preserve">10.5136833190918</t>
@@ -2888,31 +2888,31 @@
     <t xml:space="preserve">10.3954696655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.495213508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5062961578369</t>
+    <t xml:space="preserve">10.4952125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5062971115112</t>
   </si>
   <si>
     <t xml:space="preserve">10.6245098114014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910057067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5801801681519</t>
+    <t xml:space="preserve">10.7094755172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910047531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5801792144775</t>
   </si>
   <si>
     <t xml:space="preserve">10.6577587127686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7648887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.713171005249</t>
+    <t xml:space="preserve">10.7648897171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7131700515747</t>
   </si>
   <si>
     <t xml:space="preserve">10.6097326278687</t>
@@ -2924,109 +2924,109 @@
     <t xml:space="preserve">10.6060390472412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4065532684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.535849571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5617094039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2624788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176359176636</t>
+    <t xml:space="preserve">10.406551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5358505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5617084503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2624797821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176349639893</t>
   </si>
   <si>
     <t xml:space="preserve">10.6134271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5764846801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2809495925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6983938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7464189529419</t>
+    <t xml:space="preserve">10.5764856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2809505462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.698392868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7464179992676</t>
   </si>
   <si>
     <t xml:space="preserve">10.6392860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6836166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7168645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.942211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8276901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7205600738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6429815292358</t>
+    <t xml:space="preserve">10.6836156845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7168655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9422121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.827691078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7205581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6429805755615</t>
   </si>
   <si>
     <t xml:space="preserve">10.4102468490601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5321559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6946992874146</t>
+    <t xml:space="preserve">10.5321550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6947002410889</t>
   </si>
   <si>
     <t xml:space="preserve">11.0456485748291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3929023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4778690338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6884393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6441078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5997772216797</t>
+    <t xml:space="preserve">11.3929033279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4778709411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6884384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6441087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599778175354</t>
   </si>
   <si>
     <t xml:space="preserve">11.5739183425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6921329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.63671875</t>
+    <t xml:space="preserve">11.6921310424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367197036743</t>
   </si>
   <si>
     <t xml:space="preserve">11.5665302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4002923965454</t>
+    <t xml:space="preserve">11.4002904891968</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4815626144409</t>
+    <t xml:space="preserve">11.4815635681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.4557046890259</t>
@@ -3044,19 +3044,19 @@
     <t xml:space="preserve">11.6958274841309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7290754318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8435945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8768424987793</t>
+    <t xml:space="preserve">11.7290744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8435955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8768434524536</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251237869263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1908502578735</t>
+    <t xml:space="preserve">12.1908483505249</t>
   </si>
   <si>
     <t xml:space="preserve">12.2130155563354</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">12.2795114517212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3866405487061</t>
+    <t xml:space="preserve">12.3866415023804</t>
   </si>
   <si>
     <t xml:space="preserve">12.4900808334351</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">12.4383602142334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4789953231812</t>
+    <t xml:space="preserve">12.4789962768555</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4568319320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.360782623291</t>
+    <t xml:space="preserve">12.4568328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3607816696167</t>
   </si>
   <si>
     <t xml:space="preserve">12.4161958694458</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">12.4309730529785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048551559448</t>
+    <t xml:space="preserve">12.5048570632935</t>
   </si>
   <si>
     <t xml:space="preserve">12.6045989990234</t>
@@ -3104,28 +3104,28 @@
     <t xml:space="preserve">12.66370677948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5824346542358</t>
+    <t xml:space="preserve">12.5824337005615</t>
   </si>
   <si>
     <t xml:space="preserve">12.6600112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6858720779419</t>
+    <t xml:space="preserve">12.6858711242676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6378469467163</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5344095230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6119871139526</t>
+    <t xml:space="preserve">12.5344104766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.611988067627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6230697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5787410736084</t>
+    <t xml:space="preserve">12.5787391662598</t>
   </si>
   <si>
     <t xml:space="preserve">12.6489305496216</t>
@@ -3137,19 +3137,19 @@
     <t xml:space="preserve">12.4457492828369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4679155349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3977251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3275337219238</t>
+    <t xml:space="preserve">12.4679145812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3977241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3275346755981</t>
   </si>
   <si>
     <t xml:space="preserve">12.5602693557739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4420547485352</t>
+    <t xml:space="preserve">12.4420557022095</t>
   </si>
   <si>
     <t xml:space="preserve">12.5972108840942</t>
@@ -3158,19 +3158,19 @@
     <t xml:space="preserve">12.7228136062622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8336410522461</t>
+    <t xml:space="preserve">12.8336400985718</t>
   </si>
   <si>
     <t xml:space="preserve">12.9740190505981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631944656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9149122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9592418670654</t>
+    <t xml:space="preserve">12.8631935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9149112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9592447280884</t>
   </si>
   <si>
     <t xml:space="preserve">13.0331258773804</t>
@@ -3179,46 +3179,46 @@
     <t xml:space="preserve">13.0368204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0626811981201</t>
+    <t xml:space="preserve">13.0626802444458</t>
   </si>
   <si>
     <t xml:space="preserve">12.881664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8890514373779</t>
+    <t xml:space="preserve">12.8890523910522</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2438163757324</t>
+    <t xml:space="preserve">13.2438182830811</t>
   </si>
   <si>
     <t xml:space="preserve">13.1184320449829</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9773731231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0910043716431</t>
+    <t xml:space="preserve">12.9773721694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0910034179688</t>
   </si>
   <si>
     <t xml:space="preserve">13.2007160186768</t>
   </si>
   <si>
-    <t xml:space="preserve">13.177206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2673263549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2830018997192</t>
+    <t xml:space="preserve">13.1772060394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2673273086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2830009460449</t>
   </si>
   <si>
     <t xml:space="preserve">13.3887929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5180978775024</t>
+    <t xml:space="preserve">13.5180969238281</t>
   </si>
   <si>
     <t xml:space="preserve">13.4985065460205</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">13.4201402664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4318943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397315979004</t>
+    <t xml:space="preserve">13.4318952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397306442261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4514875411987</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2359809875488</t>
+    <t xml:space="preserve">13.5102605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2359800338745</t>
   </si>
   <si>
     <t xml:space="preserve">13.2712440490723</t>
@@ -3254,22 +3254,22 @@
     <t xml:space="preserve">13.0518207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3339366912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1262683868408</t>
+    <t xml:space="preserve">13.3339376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1262693405151</t>
   </si>
   <si>
     <t xml:space="preserve">13.1732883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2477359771729</t>
+    <t xml:space="preserve">13.2477369308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.3731212615967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3221826553345</t>
+    <t xml:space="preserve">13.3221836090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.4358139038086</t>
@@ -3281,37 +3281,37 @@
     <t xml:space="preserve">12.9852104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3261003494263</t>
+    <t xml:space="preserve">13.3261013031006</t>
   </si>
   <si>
     <t xml:space="preserve">13.3300189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2634077072144</t>
+    <t xml:space="preserve">13.263409614563</t>
   </si>
   <si>
     <t xml:space="preserve">13.1654510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1145153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7148475646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8441524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.122350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1576156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1301870346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2046337127686</t>
+    <t xml:space="preserve">13.1145143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7148485183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8441514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1223516464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1576166152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1301860809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2046356201172</t>
   </si>
   <si>
     <t xml:space="preserve">13.0674934387207</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">13.2281436920166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2947549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3456945419312</t>
+    <t xml:space="preserve">13.2947559356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3456926345825</t>
   </si>
   <si>
     <t xml:space="preserve">13.4749956130981</t>
@@ -3338,22 +3338,22 @@
     <t xml:space="preserve">13.5690355300903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6160545349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5376873016357</t>
+    <t xml:space="preserve">13.6160554885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5376892089844</t>
   </si>
   <si>
     <t xml:space="preserve">13.5416078567505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3770380020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4436511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4240589141846</t>
+    <t xml:space="preserve">13.3770389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4436502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4240579605103</t>
   </si>
   <si>
     <t xml:space="preserve">13.3848752975464</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">13.7414398193359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8393983840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9060087203979</t>
+    <t xml:space="preserve">13.8393974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9060096740723</t>
   </si>
   <si>
     <t xml:space="preserve">13.6591558456421</t>
@@ -3389,22 +3389,22 @@
     <t xml:space="preserve">13.8315601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7923784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8824977874756</t>
+    <t xml:space="preserve">13.7923793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8824996948242</t>
   </si>
   <si>
     <t xml:space="preserve">14.0039663314819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8589887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6748294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0901670455933</t>
+    <t xml:space="preserve">13.8589878082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6748304367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0901679992676</t>
   </si>
   <si>
     <t xml:space="preserve">14.2037973403931</t>
@@ -3416,34 +3416,34 @@
     <t xml:space="preserve">14.595627784729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3017568588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4349775314331</t>
+    <t xml:space="preserve">14.3017549514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4349765777588</t>
   </si>
   <si>
     <t xml:space="preserve">14.4114675521851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271392822266</t>
+    <t xml:space="preserve">14.4271402359009</t>
   </si>
   <si>
     <t xml:space="preserve">14.399712562561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6896667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5642795562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7014217376709</t>
+    <t xml:space="preserve">14.6896686553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5642805099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7014207839966</t>
   </si>
   <si>
     <t xml:space="preserve">14.7288484573364</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8072147369385</t>
+    <t xml:space="preserve">14.8072166442871</t>
   </si>
   <si>
     <t xml:space="preserve">14.8816623687744</t>
@@ -3455,94 +3455,94 @@
     <t xml:space="preserve">14.6739931106567</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7249298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7851800918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8494453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9739599227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9217462539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141277313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1185579299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0663414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1346282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426601409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2310228347778</t>
+    <t xml:space="preserve">14.7249307632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7851810455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9739608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.921745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9538774490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141286849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1185598373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0663433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1346263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2310247421265</t>
   </si>
   <si>
     <t xml:space="preserve">15.247091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3234081268311</t>
+    <t xml:space="preserve">15.3234090805054</t>
   </si>
   <si>
     <t xml:space="preserve">15.2591419219971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3475065231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2430753707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2511100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2792253494263</t>
+    <t xml:space="preserve">15.3475074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2430772781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2511081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.279224395752</t>
   </si>
   <si>
     <t xml:space="preserve">15.38365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3716077804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4559545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0743770599365</t>
+    <t xml:space="preserve">15.3716068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4559564590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0743751525879</t>
   </si>
   <si>
     <t xml:space="preserve">14.9418287277222</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6887817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7811632156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7570648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168989181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1867046356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2991695404053</t>
+    <t xml:space="preserve">14.6887798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7811613082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7570638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168979644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1867036819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299168586731</t>
   </si>
   <si>
     <t xml:space="preserve">14.2429370880127</t>
@@ -3554,100 +3554,100 @@
     <t xml:space="preserve">14.4919662475586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6124658584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0221614837646</t>
+    <t xml:space="preserve">14.6124649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0221605300903</t>
   </si>
   <si>
     <t xml:space="preserve">14.857479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9297771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861496925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213291168213</t>
+    <t xml:space="preserve">14.9297780990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8614959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213300704956</t>
   </si>
   <si>
     <t xml:space="preserve">14.6767311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7731313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9699449539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9016609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0623264312744</t>
+    <t xml:space="preserve">14.7731304168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9699459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9016599655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0623273849487</t>
   </si>
   <si>
     <t xml:space="preserve">15.0060939788818</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9659271240234</t>
+    <t xml:space="preserve">14.9659261703491</t>
   </si>
   <si>
     <t xml:space="preserve">15.2671747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1788082122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9177274703979</t>
+    <t xml:space="preserve">15.1788110733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9177284240723</t>
   </si>
   <si>
     <t xml:space="preserve">14.8293619155884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9337968826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.058310508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422449111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8132972717285</t>
+    <t xml:space="preserve">14.9337940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0583124160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422439575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8132953643799</t>
   </si>
   <si>
     <t xml:space="preserve">14.9257621765137</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1466751098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0382251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1627435684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3754844665527</t>
+    <t xml:space="preserve">15.1466760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0382261276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1627426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3754863739014</t>
   </si>
   <si>
     <t xml:space="preserve">14.4999990463257</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6847648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6727132797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9940462112427</t>
+    <t xml:space="preserve">14.6847658157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6727142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9940452575684</t>
   </si>
   <si>
     <t xml:space="preserve">14.7369785308838</t>
@@ -3656,19 +3656,19 @@
     <t xml:space="preserve">14.9819946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9578952789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7450141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270078659058</t>
+    <t xml:space="preserve">14.957896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7450132369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270088195801</t>
   </si>
   <si>
     <t xml:space="preserve">14.893630027771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5562334060669</t>
+    <t xml:space="preserve">14.5562324523926</t>
   </si>
   <si>
     <t xml:space="preserve">14.596399307251</t>
@@ -3686,28 +3686,28 @@
     <t xml:space="preserve">13.8372583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7770071029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379495620728</t>
+    <t xml:space="preserve">13.7770080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379505157471</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447366714478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.993766784668</t>
+    <t xml:space="preserve">12.9937677383423</t>
   </si>
   <si>
     <t xml:space="preserve">13.6243762969971</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4958448410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1746530532837</t>
+    <t xml:space="preserve">13.4958438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930746078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.174654006958</t>
   </si>
   <si>
     <t xml:space="preserve">14.3875350952148</t>
@@ -3716,34 +3716,34 @@
     <t xml:space="preserve">15.0824098587036</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0502786636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1667585372925</t>
+    <t xml:space="preserve">15.0502767562866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1667594909668</t>
   </si>
   <si>
     <t xml:space="preserve">15.3153743743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6005544662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1789474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8495855331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1628818511963</t>
+    <t xml:space="preserve">15.6005525588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1789455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8495836257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1628837585449</t>
   </si>
   <si>
     <t xml:space="preserve">16.6850414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3074779510498</t>
+    <t xml:space="preserve">16.9581718444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3074798583984</t>
   </si>
   <si>
     <t xml:space="preserve">16.235179901123</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">15.5523548126221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7331027984619</t>
+    <t xml:space="preserve">15.7331008911133</t>
   </si>
   <si>
     <t xml:space="preserve">15.6166210174561</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">15.4840726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4117727279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.476037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9980611801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.793212890625</t>
+    <t xml:space="preserve">15.4117736816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4760389328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9980602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7932138442993</t>
   </si>
   <si>
     <t xml:space="preserve">14.5080327987671</t>
@@ -3785,16 +3785,16 @@
     <t xml:space="preserve">14.4598331451416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5401668548584</t>
+    <t xml:space="preserve">14.5401649475098</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196691513062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7048473358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6204986572266</t>
+    <t xml:space="preserve">14.7048463821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6204996109009</t>
   </si>
   <si>
     <t xml:space="preserve">14.4518003463745</t>
@@ -3806,31 +3806,31 @@
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2670373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947364807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3112201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4558172225952</t>
+    <t xml:space="preserve">14.2268695831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2670364379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3112192153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4558181762695</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7547540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8230848312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8828706741333</t>
+    <t xml:space="preserve">14.7547550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8230838775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8828716278076</t>
   </si>
   <si>
     <t xml:space="preserve">14.5882034301758</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430065155029</t>
+    <t xml:space="preserve">14.4430046081543</t>
   </si>
   <si>
     <t xml:space="preserve">14.3789463043213</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">14.2764539718628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4643564224243</t>
+    <t xml:space="preserve">14.4643573760986</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344388961792</t>
+    <t xml:space="preserve">13.3924493789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344398498535</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
@@ -3881,13 +3881,13 @@
     <t xml:space="preserve">13.336932182312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5803537368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3967208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2557916641235</t>
+    <t xml:space="preserve">13.5803527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3967199325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2557926177979</t>
   </si>
   <si>
     <t xml:space="preserve">13.1917333602905</t>
@@ -3896,19 +3896,19 @@
     <t xml:space="preserve">13.6828479766846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2686033248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4266147613525</t>
+    <t xml:space="preserve">13.2686042785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4266138076782</t>
   </si>
   <si>
     <t xml:space="preserve">13.2899570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0038299560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2942276000977</t>
+    <t xml:space="preserve">13.0038290023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2942266464233</t>
   </si>
   <si>
     <t xml:space="preserve">13.1661100387573</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568538665771</t>
+    <t xml:space="preserve">12.9568529129028</t>
   </si>
   <si>
     <t xml:space="preserve">12.995288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7774896621704</t>
+    <t xml:space="preserve">12.7774906158447</t>
   </si>
   <si>
     <t xml:space="preserve">12.3547058105469</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">12.4401159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4230346679688</t>
+    <t xml:space="preserve">12.4230337142944</t>
   </si>
   <si>
     <t xml:space="preserve">12.542610168457</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">12.1838836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1625299453735</t>
+    <t xml:space="preserve">12.1625308990479</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095069885254</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">12.4273052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1796131134033</t>
+    <t xml:space="preserve">12.1796140670776</t>
   </si>
   <si>
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333530426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4571990966797</t>
+    <t xml:space="preserve">12.3333520889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4571981430054</t>
   </si>
   <si>
     <t xml:space="preserve">12.7134323120117</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">12.4700107574463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.534068107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6408319473267</t>
+    <t xml:space="preserve">12.5340690612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.640832901001</t>
   </si>
   <si>
     <t xml:space="preserve">12.8458185195923</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">13.0508050918579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191329956055</t>
+    <t xml:space="preserve">13.1191339492798</t>
   </si>
   <si>
     <t xml:space="preserve">13.2258977890015</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">13.1618394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8970651626587</t>
+    <t xml:space="preserve">12.897066116333</t>
   </si>
   <si>
     <t xml:space="preserve">12.7646780014038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7006196975708</t>
+    <t xml:space="preserve">12.7006206512451</t>
   </si>
   <si>
     <t xml:space="preserve">12.8757123947144</t>
@@ -4022,16 +4022,16 @@
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579141616821</t>
+    <t xml:space="preserve">12.6579151153564</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3931407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8330059051514</t>
+    <t xml:space="preserve">12.3931398391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8330068588257</t>
   </si>
   <si>
     <t xml:space="preserve">12.4828224182129</t>
@@ -4043,25 +4043,25 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7689485549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1703805923462</t>
+    <t xml:space="preserve">12.768949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1703815460205</t>
   </si>
   <si>
     <t xml:space="preserve">12.9696645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.089241027832</t>
+    <t xml:space="preserve">13.0892400741577</t>
   </si>
   <si>
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7048902511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7390546798706</t>
+    <t xml:space="preserve">12.704891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7390556335449</t>
   </si>
   <si>
     <t xml:space="preserve">12.3248119354248</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">12.4443864822388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1411790847778</t>
+    <t xml:space="preserve">12.1411781311035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0173320770264</t>
@@ -4088,25 +4088,25 @@
     <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8550519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.73974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9575433731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9447326660156</t>
+    <t xml:space="preserve">11.8550510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7397451400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9575443267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9447317123413</t>
   </si>
   <si>
     <t xml:space="preserve">11.7909927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0045204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1582593917847</t>
+    <t xml:space="preserve">12.0045213699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.158260345459</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991876602173</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">12.3632469177246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5169858932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3376235961914</t>
+    <t xml:space="preserve">12.5169868469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3376226425171</t>
   </si>
   <si>
     <t xml:space="preserve">12.6749973297119</t>
@@ -4133,16 +4133,16 @@
     <t xml:space="preserve">12.8714418411255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.973934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0977821350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.025182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.153299331665</t>
+    <t xml:space="preserve">12.9739351272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0251817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1532983779907</t>
   </si>
   <si>
     <t xml:space="preserve">13.6657648086548</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">14.7419443130493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5796632766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5027923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600868225098</t>
+    <t xml:space="preserve">14.579662322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5027933120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.2679119110107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4686279296875</t>
+    <t xml:space="preserve">14.4686298370361</t>
   </si>
   <si>
     <t xml:space="preserve">14.6266384124756</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">14.7163200378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7035093307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6992378234863</t>
+    <t xml:space="preserve">14.7035083770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.699236869812</t>
   </si>
   <si>
     <t xml:space="preserve">14.7931909561157</t>
@@ -4205,22 +4205,22 @@
     <t xml:space="preserve">14.6906976699829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7889194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7462139129639</t>
+    <t xml:space="preserve">14.7889204025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7462129592896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8999538421631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8444366455078</t>
+    <t xml:space="preserve">14.8444356918335</t>
   </si>
   <si>
     <t xml:space="preserve">14.1440658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0928201675415</t>
+    <t xml:space="preserve">14.0928192138672</t>
   </si>
   <si>
     <t xml:space="preserve">14.2508296966553</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">14.3490524291992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3106184005737</t>
+    <t xml:space="preserve">14.3106174468994</t>
   </si>
   <si>
     <t xml:space="preserve">14.2593717575073</t>
@@ -4247,13 +4247,13 @@
     <t xml:space="preserve">14.1910419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3276996612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3917589187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7504844665527</t>
+    <t xml:space="preserve">14.3277006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3917598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7504854202271</t>
   </si>
   <si>
     <t xml:space="preserve">14.8102722167969</t>
@@ -4268,16 +4268,16 @@
     <t xml:space="preserve">14.8615188598633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8487071990967</t>
+    <t xml:space="preserve">14.848708152771</t>
   </si>
   <si>
     <t xml:space="preserve">14.9554719924927</t>
   </si>
   <si>
-    <t xml:space="preserve">14.968282699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8358974456787</t>
+    <t xml:space="preserve">14.9682836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8358964920044</t>
   </si>
   <si>
     <t xml:space="preserve">15.168999671936</t>
@@ -4286,79 +4286,79 @@
     <t xml:space="preserve">15.2373285293579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3013868331909</t>
+    <t xml:space="preserve">15.3013877868652</t>
   </si>
   <si>
     <t xml:space="preserve">15.2586803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2971153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3270092010498</t>
+    <t xml:space="preserve">15.2971162796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3270101547241</t>
   </si>
   <si>
     <t xml:space="preserve">15.3825263977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.28857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5319957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5021018981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.416690826416</t>
+    <t xml:space="preserve">15.2885751724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5319948196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4166898727417</t>
   </si>
   <si>
     <t xml:space="preserve">15.4679374694824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4636669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5063734054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5618886947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5832433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.600323677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6686525344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6473016738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.685736656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4850196838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5106430053711</t>
+    <t xml:space="preserve">15.4636659622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5063714981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5618877410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5832424163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6003246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5875120162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6686515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344881057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6473007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6857357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4850187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5106420516968</t>
   </si>
   <si>
     <t xml:space="preserve">15.6643829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9804019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8266630172729</t>
+    <t xml:space="preserve">15.9804029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8266639709473</t>
   </si>
   <si>
     <t xml:space="preserve">15.8223934173584</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">16.0231094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.027379989624</t>
+    <t xml:space="preserve">16.0273780822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.0658149719238</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">15.9078044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7327108383179</t>
+    <t xml:space="preserve">15.7327117919922</t>
   </si>
   <si>
     <t xml:space="preserve">15.2031631469727</t>
@@ -4388,25 +4388,25 @@
     <t xml:space="preserve">15.7540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8316259384155</t>
+    <t xml:space="preserve">14.8316249847412</t>
   </si>
   <si>
     <t xml:space="preserve">14.9810962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4508543014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4081516265869</t>
+    <t xml:space="preserve">15.0451536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.450855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4081497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.1092128753662</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2501392364502</t>
+    <t xml:space="preserve">15.2501401901245</t>
   </si>
   <si>
     <t xml:space="preserve">15.4423131942749</t>
@@ -4415,25 +4415,25 @@
     <t xml:space="preserve">15.6259479522705</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6985454559326</t>
+    <t xml:space="preserve">15.6985464096069</t>
   </si>
   <si>
     <t xml:space="preserve">15.672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.621678352356</t>
+    <t xml:space="preserve">15.6216773986816</t>
   </si>
   <si>
     <t xml:space="preserve">15.7241697311401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8437452316284</t>
+    <t xml:space="preserve">15.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">16.0743560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0914402008057</t>
+    <t xml:space="preserve">16.091438293457</t>
   </si>
   <si>
     <t xml:space="preserve">16.1683082580566</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">16.0401916503906</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1384143829346</t>
+    <t xml:space="preserve">16.1384162902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.2836132049561</t>
@@ -4451,10 +4451,10 @@
     <t xml:space="preserve">16.3049659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3092365264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3434028625488</t>
+    <t xml:space="preserve">16.3092346191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3434009552002</t>
   </si>
   <si>
     <t xml:space="preserve">16.219554901123</t>
@@ -4466,37 +4466,37 @@
     <t xml:space="preserve">16.2323665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1256008148193</t>
+    <t xml:space="preserve">16.125602722168</t>
   </si>
   <si>
     <t xml:space="preserve">15.8693695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9334297180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8053112030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2067432403564</t>
+    <t xml:space="preserve">15.9334278106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8053102493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2067451477051</t>
   </si>
   <si>
     <t xml:space="preserve">16.1085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.890721321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9889430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1127891540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0316505432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9120740890503</t>
+    <t xml:space="preserve">15.8907222747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9889440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1127910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0316524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.912073135376</t>
   </si>
   <si>
     <t xml:space="preserve">15.9547805786133</t>
@@ -71896,7 +71896,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.693125</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>3260916</v>
@@ -71917,6 +71917,32 @@
         <v>2020</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6915856482</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>3019278</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>34.1399993896484</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>33.6699981689453</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>33.7599983215332</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>34.060001373291</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="2031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="2032">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21389961242676</t>
+    <t xml:space="preserve">9.21390056610107</t>
   </si>
   <si>
     <t xml:space="preserve">G.MI</t>
@@ -47,67 +47,67 @@
     <t xml:space="preserve">9.31058883666992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13427257537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11721229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02052116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76457977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8897066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06602191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95795822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75889205932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57120227813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63376712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29251098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44607543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48588752746582</t>
+    <t xml:space="preserve">9.13427352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11721134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02052211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76458072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88970756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0660228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95795917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75889301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57120132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63376426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29251003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44607639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48588943481445</t>
   </si>
   <si>
     <t xml:space="preserve">8.30957317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04794216156006</t>
+    <t xml:space="preserve">8.04794311523438</t>
   </si>
   <si>
     <t xml:space="preserve">7.93987941741943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61568784713745</t>
+    <t xml:space="preserve">7.61568593978882</t>
   </si>
   <si>
     <t xml:space="preserve">7.84319067001343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70668745040894</t>
+    <t xml:space="preserve">7.70668792724609</t>
   </si>
   <si>
     <t xml:space="preserve">7.41662120819092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23461818695068</t>
+    <t xml:space="preserve">7.234619140625</t>
   </si>
   <si>
     <t xml:space="preserve">7.1549916267395</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">6.96161413192749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74548530578613</t>
+    <t xml:space="preserve">6.74548435211182</t>
   </si>
   <si>
     <t xml:space="preserve">6.47248125076294</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">6.23360061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34166526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59760808944702</t>
+    <t xml:space="preserve">6.34166574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59760761260986</t>
   </si>
   <si>
     <t xml:space="preserve">6.62035799026489</t>
@@ -140,85 +140,85 @@
     <t xml:space="preserve">6.77392292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66017198562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89904928207397</t>
+    <t xml:space="preserve">6.72842216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66017150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89905071258545</t>
   </si>
   <si>
     <t xml:space="preserve">6.8933629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95592498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26305675506592</t>
+    <t xml:space="preserve">6.95592546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26305627822876</t>
   </si>
   <si>
     <t xml:space="preserve">7.28580665588379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34268188476562</t>
+    <t xml:space="preserve">7.34268140792847</t>
   </si>
   <si>
     <t xml:space="preserve">7.45643377304077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4507474899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37680816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24599313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31993103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38249492645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37112092971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90575456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83750343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79200267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87731647491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89437961578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76356315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6725606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57587337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53037309646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36543226242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42799711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48487186431885</t>
+    <t xml:space="preserve">7.45074605941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37680768966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24599266052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3199315071106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38249540328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37111949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90575408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83750247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79200124740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87731599807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89437913894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76356506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67256355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57587289810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53037261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36543273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42799615859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48487091064453</t>
   </si>
   <si>
     <t xml:space="preserve">7.41093254089355</t>
@@ -227,61 +227,61 @@
     <t xml:space="preserve">7.30286979675293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21755409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98436450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00711441040039</t>
+    <t xml:space="preserve">7.2175555229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98436403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00711488723755</t>
   </si>
   <si>
     <t xml:space="preserve">6.85354995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05261516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13792943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16067981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43368291854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49624729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47918319702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54743528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59862375259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75218820571899</t>
+    <t xml:space="preserve">7.05261468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13792896270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16067886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43368339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49624681472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47918462753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54743623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59862279891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75218915939331</t>
   </si>
   <si>
     <t xml:space="preserve">7.83181571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7863130569458</t>
+    <t xml:space="preserve">7.78631448745728</t>
   </si>
   <si>
     <t xml:space="preserve">7.85456562042236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80337762832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7749400138855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018613815308</t>
+    <t xml:space="preserve">7.80337810516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77493906021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018661499023</t>
   </si>
   <si>
     <t xml:space="preserve">7.39387083053589</t>
@@ -290,88 +290,88 @@
     <t xml:space="preserve">7.35405778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53606081008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08105325698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16636753082275</t>
+    <t xml:space="preserve">7.53605937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08105230331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16636657714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.05830192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11517810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25168228149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31798791885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73994827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84845304489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90873336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94490051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85448026657104</t>
+    <t xml:space="preserve">7.11517858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25168180465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73994779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84845352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90873146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.944899559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85447978973389</t>
   </si>
   <si>
     <t xml:space="preserve">7.81228351593018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76405954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54705286026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53499603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66158390045166</t>
+    <t xml:space="preserve">7.76405906677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54705333709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.534996509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66158294677734</t>
   </si>
   <si>
     <t xml:space="preserve">7.80625534057617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77008962631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42046403884888</t>
+    <t xml:space="preserve">7.77008771896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42046499252319</t>
   </si>
   <si>
     <t xml:space="preserve">7.17934465408325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97439384460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99850511550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92014074325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19140100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40840816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54102373123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58322095870972</t>
+    <t xml:space="preserve">6.97439193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99850368499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92013931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40840768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54102468490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5832200050354</t>
   </si>
   <si>
     <t xml:space="preserve">6.58257246017456</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">6.02498292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11841630935669</t>
+    <t xml:space="preserve">6.11841726303101</t>
   </si>
   <si>
     <t xml:space="preserve">6.26308965682983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35953712463379</t>
+    <t xml:space="preserve">6.35953760147095</t>
   </si>
   <si>
     <t xml:space="preserve">6.4318733215332</t>
@@ -398,52 +398,52 @@
     <t xml:space="preserve">6.13047361373901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91647911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92853546142578</t>
+    <t xml:space="preserve">5.91647958755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92853498458862</t>
   </si>
   <si>
     <t xml:space="preserve">6.38967704772949</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43790149688721</t>
+    <t xml:space="preserve">6.43790102005005</t>
   </si>
   <si>
     <t xml:space="preserve">6.76341247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69710493087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87191677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80560827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84177780151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75738430023193</t>
+    <t xml:space="preserve">6.69710445404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87191534042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80560874938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84177684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75738477706909</t>
   </si>
   <si>
     <t xml:space="preserve">6.8478045463562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7754693031311</t>
+    <t xml:space="preserve">6.77546882629395</t>
   </si>
   <si>
     <t xml:space="preserve">6.73327302932739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68504810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81163549423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62476921081543</t>
+    <t xml:space="preserve">6.68504905700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81163597106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62476825714111</t>
   </si>
   <si>
     <t xml:space="preserve">7.10098075866699</t>
@@ -455,97 +455,97 @@
     <t xml:space="preserve">6.7935528755188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06481266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20948457717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2938756942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29990482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34210109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0828971862793</t>
+    <t xml:space="preserve">7.06481313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20948505401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29387760162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29990530014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34210157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08289623260498</t>
   </si>
   <si>
     <t xml:space="preserve">6.8899998664856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90808582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7393012046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04070091247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01658916473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81766557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74532842636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61271381378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78149700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94425439834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99247789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93822526931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88397312164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25770998001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70313262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63079738616943</t>
+    <t xml:space="preserve">6.90808391571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73930072784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04069995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81766510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74532747268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61271238327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78149604797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94425201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99247646331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93822479248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88397264480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98042058944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15523195266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25770807266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70313119888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63079643249512</t>
   </si>
   <si>
     <t xml:space="preserve">6.72724437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79958009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75135660171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59462881088257</t>
+    <t xml:space="preserve">6.7995810508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75135707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59462833404541</t>
   </si>
   <si>
     <t xml:space="preserve">6.56448888778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57654619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60668420791626</t>
+    <t xml:space="preserve">6.57654523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6066837310791</t>
   </si>
   <si>
     <t xml:space="preserve">6.54640436172485</t>
@@ -554,88 +554,88 @@
     <t xml:space="preserve">6.51626491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49818134307861</t>
+    <t xml:space="preserve">6.49818086624146</t>
   </si>
   <si>
     <t xml:space="preserve">6.76944017410278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85986137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85383319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18537282943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16728830337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19742822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28784704208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26976442337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33004379272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3119592666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14317750930786</t>
+    <t xml:space="preserve">6.85986089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85383224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1853723526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1672887802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19742774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28784847259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26976490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33004426956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31196069717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14317655563354</t>
   </si>
   <si>
     <t xml:space="preserve">7.09495258331299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98644924163818</t>
+    <t xml:space="preserve">6.98644733428955</t>
   </si>
   <si>
     <t xml:space="preserve">6.67299222946167</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83574914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08892345428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07686853408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87794494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02261543273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8236927986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43854856491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35415601730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73391914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30055236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68031597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45125198364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47536468505859</t>
+    <t xml:space="preserve">6.83574724197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0889253616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07686948776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87794351577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02261686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82369136810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43854904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35415649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73392057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30055332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6803150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45125293731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47536277770996</t>
   </si>
   <si>
     <t xml:space="preserve">8.41508388519287</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">8.541672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5597562789917</t>
+    <t xml:space="preserve">8.55975532531738</t>
   </si>
   <si>
     <t xml:space="preserve">8.63811874389648</t>
@@ -656,70 +656,70 @@
     <t xml:space="preserve">8.5838680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59592437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66223335266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66826057434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55372714996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50550365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51153182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65017604827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7104549407959</t>
+    <t xml:space="preserve">8.59592342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6622314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6682596206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55372619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50550270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51153087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65017414093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71045589447021</t>
   </si>
   <si>
     <t xml:space="preserve">8.75265216827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69839954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71648406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52358913421631</t>
+    <t xml:space="preserve">8.69840049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7164831161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52358722686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.48741912841797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3849458694458</t>
+    <t xml:space="preserve">8.38494396209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.25835609436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23424339294434</t>
+    <t xml:space="preserve">8.23424434661865</t>
   </si>
   <si>
     <t xml:space="preserve">8.16793632507324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27041149139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26438426971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58989715576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2951717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38559055328369</t>
+    <t xml:space="preserve">8.27041244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26438522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5898962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29517269134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38559150695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.4217586517334</t>
@@ -734,31 +734,31 @@
     <t xml:space="preserve">8.88526821136475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84909915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00582885742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02994155883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81895923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77073669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67428874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7405948638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90335273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04802417755127</t>
+    <t xml:space="preserve">8.84910106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00582790374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02993965148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8189582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7707347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67428684234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74059677124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04802513122559</t>
   </si>
   <si>
     <t xml:space="preserve">8.87923908233643</t>
@@ -767,19 +767,19 @@
     <t xml:space="preserve">8.90937995910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95760250091553</t>
+    <t xml:space="preserve">8.95760345458984</t>
   </si>
   <si>
     <t xml:space="preserve">8.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81293201446533</t>
+    <t xml:space="preserve">8.81293106079102</t>
   </si>
   <si>
     <t xml:space="preserve">8.74662494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65620422363281</t>
+    <t xml:space="preserve">8.6562032699585</t>
   </si>
   <si>
     <t xml:space="preserve">8.49947547912598</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">8.27644062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54770088195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46330833435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56578350067139</t>
+    <t xml:space="preserve">8.54769992828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46330738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56578254699707</t>
   </si>
   <si>
     <t xml:space="preserve">8.78882026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80087757110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79484939575195</t>
+    <t xml:space="preserve">8.80087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79484844207764</t>
   </si>
   <si>
     <t xml:space="preserve">8.78279113769531</t>
@@ -818,19 +818,19 @@
     <t xml:space="preserve">8.98171520233154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80690479278564</t>
+    <t xml:space="preserve">8.80690383911133</t>
   </si>
   <si>
     <t xml:space="preserve">8.6320915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60798072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46933650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36083126068115</t>
+    <t xml:space="preserve">8.60797786712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46933555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36083221435547</t>
   </si>
   <si>
     <t xml:space="preserve">8.93349170684814</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">8.87321281433105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04199504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19269561767578</t>
+    <t xml:space="preserve">9.04199600219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1926965713501</t>
   </si>
   <si>
     <t xml:space="preserve">9.21077919006348</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">9.24091911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2168083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94554805755615</t>
+    <t xml:space="preserve">9.21680641174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94554710388184</t>
   </si>
   <si>
     <t xml:space="preserve">8.89129638671875</t>
@@ -866,10 +866,10 @@
     <t xml:space="preserve">9.03596878051758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07213497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12035942077637</t>
+    <t xml:space="preserve">9.07213592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12036037445068</t>
   </si>
   <si>
     <t xml:space="preserve">9.304931640625</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">9.18400478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15854740142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13308906555176</t>
+    <t xml:space="preserve">9.15854644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13309001922607</t>
   </si>
   <si>
     <t xml:space="preserve">8.94851779937744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83395767211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94215393066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03762245178223</t>
+    <t xml:space="preserve">8.83395671844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94215202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03762149810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.81486320495605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75758266448975</t>
+    <t xml:space="preserve">8.75758171081543</t>
   </si>
   <si>
     <t xml:space="preserve">8.73848819732666</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">8.89123821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95488262176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05035018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22855663299561</t>
+    <t xml:space="preserve">8.95488166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05034923553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22855567932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.2349214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17127513885498</t>
+    <t xml:space="preserve">9.1712760925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.28583717346191</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">9.2985668182373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34948348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25401592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22219276428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24764919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29220199584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33038997650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38130569458008</t>
+    <t xml:space="preserve">9.19037055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3494815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25401496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22219181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24765014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29220104217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33038806915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38130474090576</t>
   </si>
   <si>
     <t xml:space="preserve">9.57860565185547</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">9.54678249359131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54041767120361</t>
+    <t xml:space="preserve">9.54041862487793</t>
   </si>
   <si>
     <t xml:space="preserve">9.64861488342285</t>
@@ -971,49 +971,49 @@
     <t xml:space="preserve">9.79499912261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85864448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71862411499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68680286407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56587696075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52768993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75681114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77590465545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750379562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0877676010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1386833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.23415184021</t>
+    <t xml:space="preserve">9.85864353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71862506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68680191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56587600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52768898010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75681209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77590560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80136299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750389099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0877685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1386823654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2341508865356</t>
   </si>
   <si>
     <t xml:space="preserve">10.1959648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.062310218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0050287246704</t>
+    <t xml:space="preserve">10.0623092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0050296783447</t>
   </si>
   <si>
     <t xml:space="preserve">9.82682132720947</t>
@@ -1031,43 +1031,43 @@
     <t xml:space="preserve">9.87137317657471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78226852416992</t>
+    <t xml:space="preserve">9.78226947784424</t>
   </si>
   <si>
     <t xml:space="preserve">9.71226119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69953060150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6804370880127</t>
+    <t xml:space="preserve">9.69953155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68043804168701</t>
   </si>
   <si>
     <t xml:space="preserve">9.69316673278809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66134452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53405380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52132415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57224082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61679267883301</t>
+    <t xml:space="preserve">9.66134548187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53405284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52132320404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57224178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61679363250732</t>
   </si>
   <si>
     <t xml:space="preserve">9.674072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6295223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59770011901855</t>
+    <t xml:space="preserve">9.62952136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59769916534424</t>
   </si>
   <si>
     <t xml:space="preserve">9.89046764373779</t>
@@ -1076,22 +1076,22 @@
     <t xml:space="preserve">9.94774723052979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75044822692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89683246612549</t>
+    <t xml:space="preserve">9.75044727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89683151245117</t>
   </si>
   <si>
     <t xml:space="preserve">9.91592502593994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87773990631104</t>
+    <t xml:space="preserve">9.87773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">10.0304870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0686731338501</t>
+    <t xml:space="preserve">10.0686721801758</t>
   </si>
   <si>
     <t xml:space="preserve">10.1323194503784</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">9.93501853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84591484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85227966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83318710327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72498893737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99866390228271</t>
+    <t xml:space="preserve">9.84591579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85228061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72498989105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9986629486084</t>
   </si>
   <si>
     <t xml:space="preserve">9.96047592163086</t>
@@ -1121,34 +1121,34 @@
     <t xml:space="preserve">10.0177564620972</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95411205291748</t>
+    <t xml:space="preserve">9.9541130065918</t>
   </si>
   <si>
     <t xml:space="preserve">10.1259536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0241222381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94138336181641</t>
+    <t xml:space="preserve">10.0241231918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94138240814209</t>
   </si>
   <si>
     <t xml:space="preserve">9.88410186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0368518829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63588619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58497142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.610426902771</t>
+    <t xml:space="preserve">10.0368509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78863430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63588523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58497047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61042881011963</t>
   </si>
   <si>
     <t xml:space="preserve">9.66770839691162</t>
@@ -1157,67 +1157,67 @@
     <t xml:space="preserve">9.7440824508667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73135471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80772686004639</t>
+    <t xml:space="preserve">9.73135375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8077278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.73771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70589637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55951118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47677421569824</t>
+    <t xml:space="preserve">9.70589542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5595121383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47677230834961</t>
   </si>
   <si>
     <t xml:space="preserve">9.97320556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97956943511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0814018249512</t>
+    <t xml:space="preserve">9.97957038879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0814037322998</t>
   </si>
   <si>
     <t xml:space="preserve">10.055944442749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.291431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.304160118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2023296356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.310525894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736879348755</t>
+    <t xml:space="preserve">10.2914323806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3041620254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2023286819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3105249404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736869812012</t>
   </si>
   <si>
     <t xml:space="preserve">10.1641416549683</t>
   </si>
   <si>
-    <t xml:space="preserve">10.148229598999</t>
+    <t xml:space="preserve">10.1482305526733</t>
   </si>
   <si>
     <t xml:space="preserve">9.99229907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76954174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86819076538086</t>
+    <t xml:space="preserve">9.76954364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86819171905518</t>
   </si>
   <si>
     <t xml:space="preserve">9.81727504730225</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">9.80454540252686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.368577003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6517972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85546112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74726486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0082092285156</t>
+    <t xml:space="preserve">9.36857509613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65179824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85546207427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74726390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0082111358643</t>
   </si>
   <si>
     <t xml:space="preserve">9.98593521118164</t>
@@ -1253,31 +1253,31 @@
     <t xml:space="preserve">9.92865467071533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94456577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9700231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0495805740356</t>
+    <t xml:space="preserve">9.94456481933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97002410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0495796203613</t>
   </si>
   <si>
     <t xml:space="preserve">10.1609592437744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3137083053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2946147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3455305099487</t>
+    <t xml:space="preserve">10.3137063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2946138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3455295562744</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346342086792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5301008224487</t>
+    <t xml:space="preserve">10.530101776123</t>
   </si>
   <si>
     <t xml:space="preserve">10.638298034668</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">10.765588760376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8546924591064</t>
+    <t xml:space="preserve">10.8546915054321</t>
   </si>
   <si>
     <t xml:space="preserve">10.6319341659546</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">10.7178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5841999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6542081832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7083072662354</t>
+    <t xml:space="preserve">10.5841979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6542091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7083082199097</t>
   </si>
   <si>
     <t xml:space="preserve">10.7051258087158</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">10.6796674728394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5269203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.539647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4409980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5014619827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5078268051147</t>
+    <t xml:space="preserve">10.5269193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5396480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4409990310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5014629364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5078258514404</t>
   </si>
   <si>
     <t xml:space="preserve">10.297797203064</t>
@@ -1334,25 +1334,25 @@
     <t xml:space="preserve">10.2596111297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2864847183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2528915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0143728256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.994215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83968353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49702644348145</t>
+    <t xml:space="preserve">10.2864856719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.252890586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1319513320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0143737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99421691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49702548980713</t>
   </si>
   <si>
     <t xml:space="preserve">9.5541353225708</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">9.77585506439209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88335800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8699197769165</t>
+    <t xml:space="preserve">9.88335609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86991882324219</t>
   </si>
   <si>
     <t xml:space="preserve">9.65491771697998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67843246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52054214477539</t>
+    <t xml:space="preserve">9.67843341827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52054119110107</t>
   </si>
   <si>
     <t xml:space="preserve">9.79937076568604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75233936309814</t>
+    <t xml:space="preserve">9.75234031677246</t>
   </si>
   <si>
     <t xml:space="preserve">9.78257465362549</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">9.90015316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80609130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76241683959961</t>
+    <t xml:space="preserve">9.80609035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76241779327393</t>
   </si>
   <si>
     <t xml:space="preserve">9.82960605621338</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">9.60116672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61796283721924</t>
+    <t xml:space="preserve">9.61796379089355</t>
   </si>
   <si>
     <t xml:space="preserve">9.52390003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51718235015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61124515533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59108734130859</t>
+    <t xml:space="preserve">9.51718139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61124610900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59108829498291</t>
   </si>
   <si>
     <t xml:space="preserve">9.80945014953613</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">9.77249622344971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72882461547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65155696868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66163539886475</t>
+    <t xml:space="preserve">9.7288236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65155792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66163635253906</t>
   </si>
   <si>
     <t xml:space="preserve">9.70530796051025</t>
@@ -1445,82 +1445,82 @@
     <t xml:space="preserve">9.85648155212402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81616878509521</t>
+    <t xml:space="preserve">9.81616973876953</t>
   </si>
   <si>
     <t xml:space="preserve">9.74898052215576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89007663726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90351295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92366981506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97070121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0479669570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2125759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1117963790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9539041519165</t>
+    <t xml:space="preserve">9.89007568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90351390838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92367076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97070026397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.047966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2125778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.111795425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95390224456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0378885269165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0009355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0681228637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916395187378</t>
+    <t xml:space="preserve">10.0009365081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0681219100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916404724121</t>
   </si>
   <si>
     <t xml:space="preserve">10.0748424530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8665599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71202850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73218441009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85312175750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92702960968018</t>
+    <t xml:space="preserve">9.86655902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71202754974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85312271118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92702770233154</t>
   </si>
   <si>
     <t xml:space="preserve">9.98077869415283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92031097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63812160491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76577663421631</t>
+    <t xml:space="preserve">9.92031002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63812065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76577758789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.93710708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9606237411499</t>
+    <t xml:space="preserve">9.96062183380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.94382667541504</t>
@@ -1532,19 +1532,19 @@
     <t xml:space="preserve">10.1017179489136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0882797241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1554679870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1722660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1823434829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2965621948242</t>
+    <t xml:space="preserve">10.0882806777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1554670333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1722650527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1823425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2965631484985</t>
   </si>
   <si>
     <t xml:space="preserve">10.4141426086426</t>
@@ -1559,16 +1559,16 @@
     <t xml:space="preserve">9.9975757598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88671779632568</t>
+    <t xml:space="preserve">9.88671588897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.96734142303467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93038845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70866870880127</t>
+    <t xml:space="preserve">9.93038940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70866680145264</t>
   </si>
   <si>
     <t xml:space="preserve">9.69187164306641</t>
@@ -1577,31 +1577,31 @@
     <t xml:space="preserve">9.59444808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50038719177246</t>
+    <t xml:space="preserve">9.50038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">9.61460494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56421184539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41304016113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43991661071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4096794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28874397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2383508682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43655681610107</t>
+    <t xml:space="preserve">9.56421279907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41304111480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43991565704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40968132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28874206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23835182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43655586242676</t>
   </si>
   <si>
     <t xml:space="preserve">9.3324146270752</t>
@@ -1613,22 +1613,22 @@
     <t xml:space="preserve">9.66499614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62468242645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65827751159668</t>
+    <t xml:space="preserve">9.62468338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65827655792236</t>
   </si>
   <si>
     <t xml:space="preserve">9.66835594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63476181030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57429218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71538734436035</t>
+    <t xml:space="preserve">9.63476085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57429027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71538543701172</t>
   </si>
   <si>
     <t xml:space="preserve">9.51382255554199</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">9.5574951171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57765197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8195276260376</t>
+    <t xml:space="preserve">9.57765102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81952667236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.87663745880127</t>
@@ -1655,34 +1655,34 @@
     <t xml:space="preserve">10.0042953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0849208831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97406101226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57093238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6448392868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74562168121338</t>
+    <t xml:space="preserve">10.084921836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97406005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57093143463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64483833312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515205383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74562072753906</t>
   </si>
   <si>
     <t xml:space="preserve">9.89679336547852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85984039306641</t>
+    <t xml:space="preserve">9.85984134674072</t>
   </si>
   <si>
     <t xml:space="preserve">9.95054531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0210914611816</t>
+    <t xml:space="preserve">10.0210933685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.0446081161499</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">10.3267965316772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3435955047607</t>
+    <t xml:space="preserve">10.3435945510864</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898435592651</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">10.3839073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3771896362305</t>
+    <t xml:space="preserve">10.3771877288818</t>
   </si>
   <si>
     <t xml:space="preserve">10.2764072418213</t>
@@ -1721,43 +1721,43 @@
     <t xml:space="preserve">10.1991405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2461719512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2932033538818</t>
+    <t xml:space="preserve">10.2461709976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2932043075562</t>
   </si>
   <si>
     <t xml:space="preserve">10.0714826583862</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1285934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2058582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2831249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1890630722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2293739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2730484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3805484771729</t>
+    <t xml:space="preserve">10.1285924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2058601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2831258773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1890621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2293748855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260160446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2730474472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3805475234985</t>
   </si>
   <si>
     <t xml:space="preserve">10.4275808334351</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4342975616455</t>
+    <t xml:space="preserve">10.4342994689941</t>
   </si>
   <si>
     <t xml:space="preserve">10.5451583862305</t>
@@ -1766,16 +1766,16 @@
     <t xml:space="preserve">10.6089878082275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.672815322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6660966873169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7400026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6123466491699</t>
+    <t xml:space="preserve">10.6728162765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6660985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7400016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6123476028442</t>
   </si>
   <si>
     <t xml:space="preserve">10.5653142929077</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">10.9785213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.072585105896</t>
+    <t xml:space="preserve">11.0725841522217</t>
   </si>
   <si>
     <t xml:space="preserve">11.0591449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0322732925415</t>
+    <t xml:space="preserve">11.0322723388672</t>
   </si>
   <si>
     <t xml:space="preserve">11.0692262649536</t>
@@ -1811,37 +1811,37 @@
     <t xml:space="preserve">10.985239982605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9718027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0087566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0860223770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2035999298096</t>
+    <t xml:space="preserve">10.9718017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0087556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0860214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2036018371582</t>
   </si>
   <si>
     <t xml:space="preserve">11.1767253875732</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2304754257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2237577438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1733665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2170391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2002410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2271175384521</t>
+    <t xml:space="preserve">11.2304763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2237586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1733655929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2170381546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2002420425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2271165847778</t>
   </si>
   <si>
     <t xml:space="preserve">11.297664642334</t>
@@ -1850,22 +1850,22 @@
     <t xml:space="preserve">11.3581342697144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4219608306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5563383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4521970748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4286813735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4622755050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.583212852478</t>
+    <t xml:space="preserve">11.4219627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5563373565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4521980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4286823272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4622745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5832138061523</t>
   </si>
   <si>
     <t xml:space="preserve">11.5529775619507</t>
@@ -1874,37 +1874,37 @@
     <t xml:space="preserve">11.6235256195068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6201667785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6302442550659</t>
+    <t xml:space="preserve">11.6201677322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6302433013916</t>
   </si>
   <si>
     <t xml:space="preserve">11.5261039733887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4824314117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.468994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3245391845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648519515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5093050003052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4253196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5636577606201</t>
+    <t xml:space="preserve">11.4824304580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4689931869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.324538230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648529052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4152450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5093059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4253215789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5636587142944</t>
   </si>
   <si>
     <t xml:space="preserve">11.584942817688</t>
@@ -1919,13 +1919,13 @@
     <t xml:space="preserve">11.5459232330322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4146795272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330965042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2124948501587</t>
+    <t xml:space="preserve">11.414680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330945968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2124938964844</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763414382935</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">11.1805696487427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2195863723755</t>
+    <t xml:space="preserve">11.2195873260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.2479639053345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3366432189941</t>
+    <t xml:space="preserve">11.3366413116455</t>
   </si>
   <si>
     <t xml:space="preserve">11.4536991119385</t>
@@ -1958,43 +1958,43 @@
     <t xml:space="preserve">11.4288682937622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4785280227661</t>
+    <t xml:space="preserve">11.4785289764404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4466047286987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5175466537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7445631027222</t>
+    <t xml:space="preserve">11.5175457000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7445640563965</t>
   </si>
   <si>
     <t xml:space="preserve">11.8119592666626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8332433700562</t>
+    <t xml:space="preserve">11.8332424163818</t>
   </si>
   <si>
     <t xml:space="preserve">11.8403358459473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7871284484863</t>
+    <t xml:space="preserve">11.7871294021606</t>
   </si>
   <si>
     <t xml:space="preserve">11.7481098175049</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7126407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7977705001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8935422897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1063718795776</t>
+    <t xml:space="preserve">11.7126398086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7977685928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8935432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1063709259033</t>
   </si>
   <si>
     <t xml:space="preserve">12.1312007904053</t>
@@ -2003,13 +2003,13 @@
     <t xml:space="preserve">12.0708990097046</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1418428421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1773157119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2092370986938</t>
+    <t xml:space="preserve">12.1418418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1773147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2092380523682</t>
   </si>
   <si>
     <t xml:space="preserve">12.2056903839111</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">12.1560316085815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1808614730835</t>
+    <t xml:space="preserve">12.1808605194092</t>
   </si>
   <si>
     <t xml:space="preserve">12.1170120239258</t>
@@ -2027,64 +2027,64 @@
     <t xml:space="preserve">11.9893159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.024787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0105981826782</t>
+    <t xml:space="preserve">12.0247869491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0105991363525</t>
   </si>
   <si>
     <t xml:space="preserve">12.056713104248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9751281738281</t>
+    <t xml:space="preserve">11.9751272201538</t>
   </si>
   <si>
     <t xml:space="preserve">11.996410369873</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8545255661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9467506408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9573917388916</t>
+    <t xml:space="preserve">11.8545236587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9467496871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9573907852173</t>
   </si>
   <si>
     <t xml:space="preserve">11.6629800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5884885787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707530975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6594324111938</t>
+    <t xml:space="preserve">11.5884876251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707540512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6594305038452</t>
   </si>
   <si>
     <t xml:space="preserve">11.3437376022339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3792085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430561065674</t>
+    <t xml:space="preserve">11.3792095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430570602417</t>
   </si>
   <si>
     <t xml:space="preserve">11.29407787323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4749822616577</t>
+    <t xml:space="preserve">11.4749803543091</t>
   </si>
   <si>
     <t xml:space="preserve">11.5069055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6168661117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5778493881226</t>
+    <t xml:space="preserve">11.6168670654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5778474807739</t>
   </si>
   <si>
     <t xml:space="preserve">11.4678869247437</t>
@@ -2096,28 +2096,28 @@
     <t xml:space="preserve">11.6558847427368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5388298034668</t>
+    <t xml:space="preserve">11.5388288497925</t>
   </si>
   <si>
     <t xml:space="preserve">11.6487913131714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6842603683472</t>
+    <t xml:space="preserve">11.6842613220215</t>
   </si>
   <si>
     <t xml:space="preserve">11.7090911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7374677658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9432010650635</t>
+    <t xml:space="preserve">11.7374687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9432020187378</t>
   </si>
   <si>
     <t xml:space="preserve">12.0921831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.134747505188</t>
+    <t xml:space="preserve">12.1347484588623</t>
   </si>
   <si>
     <t xml:space="preserve">12.2021436691284</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">12.3014631271362</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4149723052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3972368240356</t>
+    <t xml:space="preserve">12.4149732589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3972358703613</t>
   </si>
   <si>
     <t xml:space="preserve">12.3262939453125</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">12.6881008148193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.659725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7058362960815</t>
+    <t xml:space="preserve">12.6597242355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7058353424072</t>
   </si>
   <si>
     <t xml:space="preserve">12.6739120483398</t>
@@ -2159,19 +2159,19 @@
     <t xml:space="preserve">12.6987438201904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6703643798828</t>
+    <t xml:space="preserve">12.6703662872314</t>
   </si>
   <si>
     <t xml:space="preserve">12.6136121749878</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5852327346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3759517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4433479309082</t>
+    <t xml:space="preserve">12.5852346420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3759536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4433488845825</t>
   </si>
   <si>
     <t xml:space="preserve">12.5213842391968</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">12.5887813568115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6490821838379</t>
+    <t xml:space="preserve">12.6490812301636</t>
   </si>
   <si>
     <t xml:space="preserve">12.6774616241455</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8157997131348</t>
+    <t xml:space="preserve">12.8157978057861</t>
   </si>
   <si>
     <t xml:space="preserve">12.744854927063</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">12.8406286239624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.035719871521</t>
+    <t xml:space="preserve">12.9080238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0357208251953</t>
   </si>
   <si>
     <t xml:space="preserve">13.0215320587158</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">13.0463609695435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0534543991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0499076843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0286254882812</t>
+    <t xml:space="preserve">13.0534563064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0499095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0286245346069</t>
   </si>
   <si>
     <t xml:space="preserve">12.9364023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8938331604004</t>
+    <t xml:space="preserve">12.893835067749</t>
   </si>
   <si>
     <t xml:space="preserve">13.1243991851807</t>
@@ -2237,58 +2237,58 @@
     <t xml:space="preserve">13.1882467269897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1917934417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6422805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6068086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6139030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8338241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7167701721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5997142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5145826339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2662868499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2237186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2343606948853</t>
+    <t xml:space="preserve">13.1917915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.642279624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6068105697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6139039993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8338260650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7167682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5997152328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5145816802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2662858963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2237176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2343597412109</t>
   </si>
   <si>
     <t xml:space="preserve">13.1527767181396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2591905593872</t>
+    <t xml:space="preserve">13.2591915130615</t>
   </si>
   <si>
     <t xml:space="preserve">13.2627363204956</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1456832885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9754199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612302780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9399480819702</t>
+    <t xml:space="preserve">13.1456842422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9754190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9399471282959</t>
   </si>
   <si>
     <t xml:space="preserve">12.918664932251</t>
@@ -2300,19 +2300,19 @@
     <t xml:space="preserve">12.9541358947754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0250816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.010890007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1137571334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1314926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1776075363159</t>
+    <t xml:space="preserve">13.0250797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0108890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1314935684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.177604675293</t>
   </si>
   <si>
     <t xml:space="preserve">13.1208515167236</t>
@@ -2321,28 +2321,28 @@
     <t xml:space="preserve">13.4613771438599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2520952224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1953420639038</t>
+    <t xml:space="preserve">13.2520961761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1953411102295</t>
   </si>
   <si>
     <t xml:space="preserve">13.0640993118286</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9683237075806</t>
+    <t xml:space="preserve">12.9683246612549</t>
   </si>
   <si>
     <t xml:space="preserve">13.1031169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0747375488281</t>
+    <t xml:space="preserve">13.0747394561768</t>
   </si>
   <si>
     <t xml:space="preserve">12.9115695953369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.978967666626</t>
+    <t xml:space="preserve">12.9789667129517</t>
   </si>
   <si>
     <t xml:space="preserve">12.9860591888428</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">12.86545753479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7235708236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8690052032471</t>
+    <t xml:space="preserve">12.7235717773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8690042495728</t>
   </si>
   <si>
     <t xml:space="preserve">12.571044921875</t>
@@ -2369,43 +2369,43 @@
     <t xml:space="preserve">12.6916484832764</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4823656082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5462141036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7306671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0002489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0818328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804727554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3194923400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3230381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3939800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3688592910767</t>
+    <t xml:space="preserve">12.4823665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7306652069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0002498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0818347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3194904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3230400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3939790725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3688583374023</t>
   </si>
   <si>
     <t xml:space="preserve">12.2979164123535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2482566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5352830886841</t>
+    <t xml:space="preserve">12.2482557296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5352840423584</t>
   </si>
   <si>
     <t xml:space="preserve">11.4004917144775</t>
@@ -2426,22 +2426,22 @@
     <t xml:space="preserve">8.36769199371338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56278228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01297664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69728231430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36739921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61569833755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72565937042236</t>
+    <t xml:space="preserve">8.56278324127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01297760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6972827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3673996925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61569881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72565984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.72920703887939</t>
@@ -2453,19 +2453,19 @@
     <t xml:space="preserve">8.83236598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98134422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77915859222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77206516265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80398750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58051872253418</t>
+    <t xml:space="preserve">8.98134613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7791576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77206420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80398845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5805196762085</t>
   </si>
   <si>
     <t xml:space="preserve">8.74723434448242</t>
@@ -2474,19 +2474,19 @@
     <t xml:space="preserve">8.64436912536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89976119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07002449035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13032531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31832408905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93877983093262</t>
+    <t xml:space="preserve">8.89976215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07002353668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1303243637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31832218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93878078460693</t>
   </si>
   <si>
     <t xml:space="preserve">8.78979969024658</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">8.6301794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84300708770752</t>
+    <t xml:space="preserve">8.84300804138184</t>
   </si>
   <si>
     <t xml:space="preserve">8.77561092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04164695739746</t>
+    <t xml:space="preserve">9.04164600372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.20126724243164</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">9.43537902832031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23319244384766</t>
+    <t xml:space="preserve">9.23319149017334</t>
   </si>
   <si>
     <t xml:space="preserve">9.00972270965576</t>
@@ -2522,28 +2522,28 @@
     <t xml:space="preserve">9.176438331604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0345516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09485530853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20481491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12322998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08421230316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91040229797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17269134521484</t>
+    <t xml:space="preserve">9.03455257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0948543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20481586456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12323093414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08421325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91040420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80044078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17269039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.01014614105225</t>
@@ -2552,130 +2552,130 @@
     <t xml:space="preserve">9.05817127227783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78849601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99536895751953</t>
+    <t xml:space="preserve">8.78849506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99536991119385</t>
   </si>
   <si>
     <t xml:space="preserve">8.96212100982666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20963287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39803791046143</t>
+    <t xml:space="preserve">9.20963191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39803695678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.43867206573486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22440910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52363967895508</t>
+    <t xml:space="preserve">9.22440814971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52364063262939</t>
   </si>
   <si>
     <t xml:space="preserve">9.81178665161133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3031148910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3474435806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6282043457031</t>
+    <t xml:space="preserve">10.3031139373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3474454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6282052993774</t>
   </si>
   <si>
     <t xml:space="preserve">10.6540632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5395431518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.321587562561</t>
+    <t xml:space="preserve">10.5395441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3215866088867</t>
   </si>
   <si>
     <t xml:space="preserve">9.92261219024658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91891860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90414047241211</t>
+    <t xml:space="preserve">9.91891956329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90414142608643</t>
   </si>
   <si>
     <t xml:space="preserve">10.1257934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.051908493042</t>
+    <t xml:space="preserve">10.0519094467163</t>
   </si>
   <si>
     <t xml:space="preserve">9.92630672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0592985153198</t>
+    <t xml:space="preserve">10.0592975616455</t>
   </si>
   <si>
     <t xml:space="preserve">10.0703802108765</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80070400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9152250289917</t>
+    <t xml:space="preserve">9.80070495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82656478881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91522407531738</t>
   </si>
   <si>
     <t xml:space="preserve">9.95216655731201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94847106933594</t>
+    <t xml:space="preserve">9.94847297668457</t>
   </si>
   <si>
     <t xml:space="preserve">10.2218418121338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1553468704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2587862014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1627349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89675426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97063636779785</t>
+    <t xml:space="preserve">10.1553478240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2587842941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1627359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89675331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97063827514648</t>
   </si>
   <si>
     <t xml:space="preserve">10.0777683258057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1294889450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070665359497</t>
+    <t xml:space="preserve">10.1294870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070646286011</t>
   </si>
   <si>
     <t xml:space="preserve">10.2107601165771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1147089004517</t>
+    <t xml:space="preserve">10.114709854126</t>
   </si>
   <si>
     <t xml:space="preserve">10.1812057495117</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3289737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2772550582886</t>
+    <t xml:space="preserve">10.3289747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2772560119629</t>
   </si>
   <si>
     <t xml:space="preserve">10.0408267974854</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">9.97433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46453285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35370540618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40911865234375</t>
+    <t xml:space="preserve">9.46453189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3537073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.55688762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63076972961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38695430755615</t>
+    <t xml:space="preserve">9.63077163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38695526123047</t>
   </si>
   <si>
     <t xml:space="preserve">9.78592777252197</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">9.53841590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70834922790527</t>
+    <t xml:space="preserve">9.70835018157959</t>
   </si>
   <si>
     <t xml:space="preserve">9.62707614898682</t>
@@ -2729,25 +2729,25 @@
     <t xml:space="preserve">9.76376247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81917476654053</t>
+    <t xml:space="preserve">9.81917572021484</t>
   </si>
   <si>
     <t xml:space="preserve">9.78223323822021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60860538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62338161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61968994140625</t>
+    <t xml:space="preserve">9.60860633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62338256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61968898773193</t>
   </si>
   <si>
     <t xml:space="preserve">9.57535839080811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47192192077637</t>
+    <t xml:space="preserve">9.47192001342773</t>
   </si>
   <si>
     <t xml:space="preserve">9.37217712402344</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">9.48669719696045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47561550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46083831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36478996276855</t>
+    <t xml:space="preserve">9.47561454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46083927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36478900909424</t>
   </si>
   <si>
     <t xml:space="preserve">9.1061954498291</t>
@@ -2774,16 +2774,16 @@
     <t xml:space="preserve">8.75155258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70352840423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66658592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59639739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53359508514404</t>
+    <t xml:space="preserve">8.70352745056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66658401489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59639644622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53359413146973</t>
   </si>
   <si>
     <t xml:space="preserve">8.86976623535156</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">8.88454341888428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76632881164551</t>
+    <t xml:space="preserve">8.76632976531982</t>
   </si>
   <si>
     <t xml:space="preserve">8.91779041290283</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">9.12466716766357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1209716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80327033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96951007843018</t>
+    <t xml:space="preserve">9.12097263336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80327129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96950912475586</t>
   </si>
   <si>
     <t xml:space="preserve">9.01753425598145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03969955444336</t>
+    <t xml:space="preserve">9.03969860076904</t>
   </si>
   <si>
     <t xml:space="preserve">8.81435298919678</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">8.39321517944336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41907405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50404071807861</t>
+    <t xml:space="preserve">8.41907501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50404167175293</t>
   </si>
   <si>
     <t xml:space="preserve">8.721999168396</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">8.89193153381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01383876800537</t>
+    <t xml:space="preserve">9.013840675354</t>
   </si>
   <si>
     <t xml:space="preserve">9.14683151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72312641143799</t>
+    <t xml:space="preserve">9.7231273651123</t>
   </si>
   <si>
     <t xml:space="preserve">9.95955371856689</t>
@@ -2876,58 +2876,58 @@
     <t xml:space="preserve">9.9447774887085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0740737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.317892074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4397993087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5136842727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3954696655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4952125549316</t>
+    <t xml:space="preserve">10.0740747451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3178911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4398002624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5136833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.395468711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.495213508606</t>
   </si>
   <si>
     <t xml:space="preserve">10.5062961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6245088577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7094755172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6910047531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5801792144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6577587127686</t>
+    <t xml:space="preserve">10.6245107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6910066604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5801782608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6577577590942</t>
   </si>
   <si>
     <t xml:space="preserve">10.7648897171021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7131700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.609733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838737487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6060390472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4065542221069</t>
+    <t xml:space="preserve">10.7131690979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6097326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838747024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6060400009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4065523147583</t>
   </si>
   <si>
     <t xml:space="preserve">10.535849571228</t>
@@ -2936,43 +2936,43 @@
     <t xml:space="preserve">10.5506258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5617084503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2624788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4176349639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6134262084961</t>
+    <t xml:space="preserve">10.5617094039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2624778747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4176359176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6134281158447</t>
   </si>
   <si>
     <t xml:space="preserve">10.5764846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2809505462646</t>
+    <t xml:space="preserve">10.2809495925903</t>
   </si>
   <si>
     <t xml:space="preserve">10.6983938217163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7464189529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6392879486084</t>
+    <t xml:space="preserve">10.7464179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6392869949341</t>
   </si>
   <si>
     <t xml:space="preserve">10.6836175918579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7168655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.942211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.827691078186</t>
+    <t xml:space="preserve">10.7168645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9422121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8276901245117</t>
   </si>
   <si>
     <t xml:space="preserve">10.7205600738525</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">10.5321559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6946992874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0456485748291</t>
+    <t xml:space="preserve">10.6947002410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0456476211548</t>
   </si>
   <si>
     <t xml:space="preserve">11.3929033279419</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4778699874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6145553588867</t>
+    <t xml:space="preserve">11.4778690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6145544052124</t>
   </si>
   <si>
     <t xml:space="preserve">11.6884384155273</t>
@@ -3008,22 +3008,22 @@
     <t xml:space="preserve">11.6441087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.599778175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5739183425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6921319961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367206573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5665302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4002923965454</t>
+    <t xml:space="preserve">11.5997772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5739192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6921329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367197036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5665311813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4002914428711</t>
   </si>
   <si>
     <t xml:space="preserve">11.5111169815063</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">11.4815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4557046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000333786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6995220184326</t>
+    <t xml:space="preserve">11.4557037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6995229721069</t>
   </si>
   <si>
     <t xml:space="preserve">11.4889526367188</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">11.7290754318237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8435955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8768444061279</t>
+    <t xml:space="preserve">11.8435945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8768434524536</t>
   </si>
   <si>
     <t xml:space="preserve">11.8251237869263</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">12.1908493041992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2130155563354</t>
+    <t xml:space="preserve">12.2130146026611</t>
   </si>
   <si>
     <t xml:space="preserve">12.2795114517212</t>
@@ -3077,67 +3077,67 @@
     <t xml:space="preserve">12.4383592605591</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4789962768555</t>
+    <t xml:space="preserve">12.4789953231812</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4568319320679</t>
+    <t xml:space="preserve">12.4568328857422</t>
   </si>
   <si>
     <t xml:space="preserve">12.3607816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4161958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.412501335144</t>
+    <t xml:space="preserve">12.4161949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125003814697</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309720993042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5048551559448</t>
+    <t xml:space="preserve">12.5048561096191</t>
   </si>
   <si>
     <t xml:space="preserve">12.6045999526978</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6637058258057</t>
+    <t xml:space="preserve">12.6637048721313</t>
   </si>
   <si>
     <t xml:space="preserve">12.5824346542358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6600131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6858720779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6378469467163</t>
+    <t xml:space="preserve">12.6600141525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6858711242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6378479003906</t>
   </si>
   <si>
     <t xml:space="preserve">12.5344104766846</t>
   </si>
   <si>
-    <t xml:space="preserve">12.611988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6230697631836</t>
+    <t xml:space="preserve">12.6119871139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6230688095093</t>
   </si>
   <si>
     <t xml:space="preserve">12.5787391662598</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.726508140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4457483291626</t>
+    <t xml:space="preserve">12.6489295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265071868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4457492828369</t>
   </si>
   <si>
     <t xml:space="preserve">12.4679145812988</t>
@@ -3146,28 +3146,28 @@
     <t xml:space="preserve">12.3977251052856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3275346755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5602684020996</t>
+    <t xml:space="preserve">12.3275337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5602693557739</t>
   </si>
   <si>
     <t xml:space="preserve">12.4420557022095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5972118377686</t>
+    <t xml:space="preserve">12.5972108840942</t>
   </si>
   <si>
     <t xml:space="preserve">12.7228136062622</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8336400985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9740190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631935119629</t>
+    <t xml:space="preserve">12.8336391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9740200042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631925582886</t>
   </si>
   <si>
     <t xml:space="preserve">12.9149112701416</t>
@@ -3176,25 +3176,25 @@
     <t xml:space="preserve">12.9592418670654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0331258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0368204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0626802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.881664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8890514373779</t>
+    <t xml:space="preserve">13.0331268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0368213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0626792907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8816633224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8890523910522</t>
   </si>
   <si>
     <t xml:space="preserve">13.0479030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2438173294067</t>
+    <t xml:space="preserve">13.2438163757324</t>
   </si>
   <si>
     <t xml:space="preserve">13.1184310913086</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">12.9773731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0910053253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2007150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1772060394287</t>
+    <t xml:space="preserve">13.0910043716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2007169723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.177206993103</t>
   </si>
   <si>
     <t xml:space="preserve">13.2673273086548</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">13.3887929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5180988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4985065460205</t>
+    <t xml:space="preserve">13.5180978775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4985055923462</t>
   </si>
   <si>
     <t xml:space="preserve">13.4632406234741</t>
@@ -3233,25 +3233,25 @@
     <t xml:space="preserve">13.4201402664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4318943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4397306442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.451488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102605819702</t>
+    <t xml:space="preserve">13.4318933486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4397315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4514875411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102615356445</t>
   </si>
   <si>
     <t xml:space="preserve">13.2359800338745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712450027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.232063293457</t>
+    <t xml:space="preserve">13.2712459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2320623397827</t>
   </si>
   <si>
     <t xml:space="preserve">13.0518207550049</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">13.3339376449585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1262674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1732873916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2477359771729</t>
+    <t xml:space="preserve">13.1262683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1732883453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2477369308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.3731212615967</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">13.4358139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1967973709106</t>
+    <t xml:space="preserve">13.196798324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.9852094650269</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">13.2634077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1654510498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1145153045654</t>
+    <t xml:space="preserve">13.1654500961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1145143508911</t>
   </si>
   <si>
     <t xml:space="preserve">12.7148485183716</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">12.8441514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1223497390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1576166152954</t>
+    <t xml:space="preserve">13.122350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1576156616211</t>
   </si>
   <si>
     <t xml:space="preserve">13.1301860809326</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">13.067494392395</t>
   </si>
   <si>
-    <t xml:space="preserve">12.989128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0283117294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2281446456909</t>
+    <t xml:space="preserve">12.9891290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0283126831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2281436920166</t>
   </si>
   <si>
     <t xml:space="preserve">13.2947559356689</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">13.4749956130981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5690355300903</t>
+    <t xml:space="preserve">13.569034576416</t>
   </si>
   <si>
     <t xml:space="preserve">13.6160545349121</t>
@@ -3347,16 +3347,16 @@
     <t xml:space="preserve">13.5376892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5416069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3770399093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4436511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4240589141846</t>
+    <t xml:space="preserve">13.5416078567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3770389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4436521530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4240579605103</t>
   </si>
   <si>
     <t xml:space="preserve">13.3848762512207</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">13.4123029708862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5337705612183</t>
+    <t xml:space="preserve">13.5337715148926</t>
   </si>
   <si>
     <t xml:space="preserve">13.5964641571045</t>
@@ -3374,22 +3374,22 @@
     <t xml:space="preserve">13.6121368408203</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5729541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7414398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8393964767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9060077667236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6591567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8315591812134</t>
+    <t xml:space="preserve">13.5729532241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7414407730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8393974304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9060087203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6591548919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8315601348877</t>
   </si>
   <si>
     <t xml:space="preserve">13.7923774719238</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">14.0039663314819</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8589868545532</t>
+    <t xml:space="preserve">13.8589878082275</t>
   </si>
   <si>
     <t xml:space="preserve">13.6748304367065</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">14.0901679992676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2037982940674</t>
+    <t xml:space="preserve">14.2037992477417</t>
   </si>
   <si>
     <t xml:space="preserve">14.3644485473633</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">14.5956268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3017549514771</t>
+    <t xml:space="preserve">14.3017559051514</t>
   </si>
   <si>
     <t xml:space="preserve">14.4349765777588</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">14.4114665985107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4271402359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3997116088867</t>
+    <t xml:space="preserve">14.4271421432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.399712562561</t>
   </si>
   <si>
     <t xml:space="preserve">14.6896667480469</t>
@@ -3440,25 +3440,25 @@
     <t xml:space="preserve">14.564281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7014198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7288494110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8072147369385</t>
+    <t xml:space="preserve">14.7014207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7288503646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8072156906128</t>
   </si>
   <si>
     <t xml:space="preserve">14.8816614151001</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6622381210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6739921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7249298095703</t>
+    <t xml:space="preserve">14.6622371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6739931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7249307632446</t>
   </si>
   <si>
     <t xml:space="preserve">14.7851800918579</t>
@@ -3467,124 +3467,124 @@
     <t xml:space="preserve">14.8494453430176</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9739608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9538774490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0141267776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.118558883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0663423538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1346254348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426591873169</t>
+    <t xml:space="preserve">14.9739599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9217462539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0141277313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1185579299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0663414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1346263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426601409912</t>
   </si>
   <si>
     <t xml:space="preserve">15.2310247421265</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2470903396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3234071731567</t>
+    <t xml:space="preserve">15.247091293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3234062194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.2591419219971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.347505569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2430763244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.25110912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.279224395752</t>
+    <t xml:space="preserve">15.3475065231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2430753707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2511081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2792253494263</t>
   </si>
   <si>
     <t xml:space="preserve">15.38365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3716068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4559564590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0743761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9418277740479</t>
+    <t xml:space="preserve">15.3716077804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4559545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0743770599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9418287277222</t>
   </si>
   <si>
     <t xml:space="preserve">14.6887798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7811622619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7570638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7168960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1867036819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2991676330566</t>
+    <t xml:space="preserve">14.7811613082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7570648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7168970108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1867046356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.299168586731</t>
   </si>
   <si>
     <t xml:space="preserve">14.2429361343384</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5642642974854</t>
+    <t xml:space="preserve">14.5642652511597</t>
   </si>
   <si>
     <t xml:space="preserve">14.4919662475586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6124649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9498615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0221605300903</t>
+    <t xml:space="preserve">14.6124658584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9498624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0221614837646</t>
   </si>
   <si>
     <t xml:space="preserve">14.857479095459</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9297761917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8614950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8213291168213</t>
+    <t xml:space="preserve">14.9297771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861496925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8213310241699</t>
   </si>
   <si>
     <t xml:space="preserve">14.6767311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7731285095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9699440002441</t>
+    <t xml:space="preserve">14.7731294631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9699449539185</t>
   </si>
   <si>
     <t xml:space="preserve">14.9016609191895</t>
@@ -3599,67 +3599,67 @@
     <t xml:space="preserve">14.9659271240234</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2671728134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1788091659546</t>
+    <t xml:space="preserve">15.2671747207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1788101196289</t>
   </si>
   <si>
     <t xml:space="preserve">14.8333787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9177274703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8293609619141</t>
+    <t xml:space="preserve">14.9177293777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8293619155884</t>
   </si>
   <si>
     <t xml:space="preserve">14.9337949752808</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0583114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0422430038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8132963180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9257612228394</t>
+    <t xml:space="preserve">15.058310508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0422449111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8132972717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9257621765137</t>
   </si>
   <si>
     <t xml:space="preserve">15.1466751098633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0382261276245</t>
+    <t xml:space="preserve">15.0382251739502</t>
   </si>
   <si>
     <t xml:space="preserve">15.1627416610718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3754854202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4999980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6847639083862</t>
+    <t xml:space="preserve">14.3754863739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6847648620605</t>
   </si>
   <si>
     <t xml:space="preserve">14.6727132797241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.994044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7369785308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9819936752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9578943252563</t>
+    <t xml:space="preserve">14.9940462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7369804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9819946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9578952789307</t>
   </si>
   <si>
     <t xml:space="preserve">14.7450122833252</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">15.2270078659058</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8936290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5562324523926</t>
+    <t xml:space="preserve">14.893630027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5562334060669</t>
   </si>
   <si>
     <t xml:space="preserve">14.5963973999023</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">14.0300559997559</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3714685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9256229400635</t>
+    <t xml:space="preserve">14.371467590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9256219863892</t>
   </si>
   <si>
     <t xml:space="preserve">13.8372583389282</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">13.7770080566406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379505157471</t>
+    <t xml:space="preserve">13.0379495620728</t>
   </si>
   <si>
     <t xml:space="preserve">12.7447366714478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.993766784668</t>
+    <t xml:space="preserve">12.9937677383423</t>
   </si>
   <si>
     <t xml:space="preserve">13.6243762969971</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">13.7930746078491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1746549606323</t>
+    <t xml:space="preserve">14.1746530532837</t>
   </si>
   <si>
     <t xml:space="preserve">14.3875350952148</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0824089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0502767562866</t>
+    <t xml:space="preserve">15.0824098587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0502786636353</t>
   </si>
   <si>
     <t xml:space="preserve">15.1667585372925</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">15.3153743743896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6005525588989</t>
+    <t xml:space="preserve">15.6005544662476</t>
   </si>
   <si>
     <t xml:space="preserve">16.1789455413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8495826721191</t>
+    <t xml:space="preserve">15.8495836257935</t>
   </si>
   <si>
     <t xml:space="preserve">16.1628818511963</t>
@@ -3743,58 +3743,58 @@
     <t xml:space="preserve">16.6850414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9581718444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3074779510498</t>
+    <t xml:space="preserve">16.9581737518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3074798583984</t>
   </si>
   <si>
     <t xml:space="preserve">16.2351779937744</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0504131317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5523529052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.733099937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6166200637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4840717315674</t>
+    <t xml:space="preserve">16.0504150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5523548126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7331008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6166210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4840726852417</t>
   </si>
   <si>
     <t xml:space="preserve">15.4117727279663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4760389328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9980602264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.793212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5080318450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5441808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4598321914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5401649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7048473358154</t>
+    <t xml:space="preserve">15.476037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9980611801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7932147979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5080327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5441818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4598331451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5401668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196691513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7048492431641</t>
   </si>
   <si>
     <t xml:space="preserve">14.6204986572266</t>
@@ -3803,37 +3803,37 @@
     <t xml:space="preserve">14.4518003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2469539642334</t>
+    <t xml:space="preserve">14.2469530105591</t>
   </si>
   <si>
     <t xml:space="preserve">14.0099725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2268695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2670373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947383880615</t>
+    <t xml:space="preserve">14.2268686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.267035484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947374343872</t>
   </si>
   <si>
     <t xml:space="preserve">14.3112192153931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4558162689209</t>
+    <t xml:space="preserve">14.4558172225952</t>
   </si>
   <si>
     <t xml:space="preserve">14.8871431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7547550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8230838775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8828716278076</t>
+    <t xml:space="preserve">14.7547540664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8230848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8828706741333</t>
   </si>
   <si>
     <t xml:space="preserve">14.5882034301758</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">14.4771709442139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4430055618286</t>
+    <t xml:space="preserve">14.4430065155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.3789463043213</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">14.2764539718628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4643583297729</t>
+    <t xml:space="preserve">14.4643564224243</t>
   </si>
   <si>
     <t xml:space="preserve">14.3704071044922</t>
@@ -3866,31 +3866,31 @@
     <t xml:space="preserve">14.0800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924493789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2344398498535</t>
+    <t xml:space="preserve">13.3924503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2344388961792</t>
   </si>
   <si>
     <t xml:space="preserve">13.251522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7896118164062</t>
+    <t xml:space="preserve">13.7896108627319</t>
   </si>
   <si>
     <t xml:space="preserve">13.3881788253784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369331359863</t>
+    <t xml:space="preserve">13.336932182312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5803537368774</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3967199325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2557926177979</t>
+    <t xml:space="preserve">13.3967208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2557916641235</t>
   </si>
   <si>
     <t xml:space="preserve">13.1917333602905</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">13.6828479766846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2686042785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4266138076782</t>
+    <t xml:space="preserve">13.2686033248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4266147613525</t>
   </si>
   <si>
     <t xml:space="preserve">13.2899570465088</t>
@@ -3911,10 +3911,10 @@
     <t xml:space="preserve">13.0038299560547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2942266464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1661109924316</t>
+    <t xml:space="preserve">13.2942276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1661100387573</t>
   </si>
   <si>
     <t xml:space="preserve">12.4187641143799</t>
@@ -3923,19 +3923,19 @@
     <t xml:space="preserve">12.5596923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0678882598877</t>
+    <t xml:space="preserve">13.0678873062134</t>
   </si>
   <si>
     <t xml:space="preserve">13.1276750564575</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568529129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9952878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7774906158447</t>
+    <t xml:space="preserve">12.9568538665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.995288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7774896621704</t>
   </si>
   <si>
     <t xml:space="preserve">12.3547058105469</t>
@@ -3950,10 +3950,10 @@
     <t xml:space="preserve">12.542610168457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838846206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1625308990479</t>
+    <t xml:space="preserve">12.1838836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1625299453735</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095069885254</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">12.1369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3333520889282</t>
+    <t xml:space="preserve">12.3333530426025</t>
   </si>
   <si>
     <t xml:space="preserve">12.4571990966797</t>
@@ -3980,10 +3980,10 @@
     <t xml:space="preserve">12.4700107574463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5340690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.640832901001</t>
+    <t xml:space="preserve">12.534068107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6408319473267</t>
   </si>
   <si>
     <t xml:space="preserve">12.8458185195923</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">13.0508050918579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191339492798</t>
+    <t xml:space="preserve">13.1191329956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.2258977890015</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">13.1618394851685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.897066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7646789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7006206512451</t>
+    <t xml:space="preserve">12.8970651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7646780014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7006196975708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8757123947144</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">12.5084457397461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6579151153564</t>
+    <t xml:space="preserve">12.6579141616821</t>
   </si>
   <si>
     <t xml:space="preserve">12.5041751861572</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">12.3931407928467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8330068588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4828214645386</t>
+    <t xml:space="preserve">12.8330059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4828224182129</t>
   </si>
   <si>
     <t xml:space="preserve">12.4486570358276</t>
@@ -4046,25 +4046,25 @@
     <t xml:space="preserve">12.5383396148682</t>
   </si>
   <si>
-    <t xml:space="preserve">12.768949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1703815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9696655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0892400741577</t>
+    <t xml:space="preserve">12.7689485549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1703805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9696645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.089241027832</t>
   </si>
   <si>
     <t xml:space="preserve">13.0422649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.704891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7390556335449</t>
+    <t xml:space="preserve">12.7048902511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7390546798706</t>
   </si>
   <si>
     <t xml:space="preserve">12.3248119354248</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">12.4443864822388</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1411781311035</t>
+    <t xml:space="preserve">12.1411790847778</t>
   </si>
   <si>
     <t xml:space="preserve">12.0173320770264</t>
@@ -4091,13 +4091,13 @@
     <t xml:space="preserve">12.1326370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8550510406494</t>
+    <t xml:space="preserve">11.8550519943237</t>
   </si>
   <si>
     <t xml:space="preserve">11.73974609375</t>
   </si>
   <si>
-   